--- a/Rasterized animal populations/Zonal statistics/Summary.xlsx
+++ b/Rasterized animal populations/Zonal statistics/Summary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hawkj\Documents\Github\KE.beef.spatial\Rasterized animal populations\Zonal statistics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFB6A4D7-13E3-455A-88D8-15EA86AAEF33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79D9F9AE-4D87-4B1A-9F51-CD6323A12095}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="20928" windowHeight="12432" activeTab="2" xr2:uid="{3882C52B-09A6-47D1-94BA-1F6173569800}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="20928" windowHeight="12432" xr2:uid="{3882C52B-09A6-47D1-94BA-1F6173569800}"/>
   </bookViews>
   <sheets>
     <sheet name="Herd_decision_tree" sheetId="1" r:id="rId1"/>
@@ -163,9 +163,6 @@
     <t>Farm decomposition</t>
   </si>
   <si>
-    <t>Breed decompositon (by farmtype)</t>
-  </si>
-  <si>
     <t>Gatsby</t>
   </si>
   <si>
@@ -206,6 +203,9 @@
   </si>
   <si>
     <t>Absolute growth (M hd)</t>
+  </si>
+  <si>
+    <t>Breed decompositon (by farm-type)</t>
   </si>
 </sst>
 </file>
@@ -631,7 +631,7 @@
     <col min="2" max="4" width="15.26171875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.26171875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="28.47265625" customWidth="1"/>
-    <col min="8" max="8" width="11.68359375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="31.734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.55000000000000004">
@@ -685,7 +685,7 @@
         <v>3.5000000000000001E-3</v>
       </c>
       <c r="K2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.55000000000000004">
@@ -714,7 +714,7 @@
         <v>0.68</v>
       </c>
       <c r="K3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.55000000000000004">
@@ -747,7 +747,7 @@
         <v>39</v>
       </c>
       <c r="H5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I5">
         <v>0.85</v>
@@ -762,7 +762,7 @@
       <c r="D6" s="6"/>
       <c r="E6" s="6"/>
       <c r="H6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I6">
         <v>0.7</v>
@@ -777,13 +777,13 @@
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
       <c r="H7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I7">
         <v>0.35</v>
       </c>
       <c r="K7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.55000000000000004">
@@ -822,7 +822,7 @@
         <v>3.2182882934235675</v>
       </c>
       <c r="G9" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="H9" t="s">
         <v>11</v>
@@ -831,7 +831,7 @@
         <v>0.6</v>
       </c>
       <c r="K9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.55000000000000004">
@@ -858,7 +858,7 @@
         <v>0.6</v>
       </c>
       <c r="K10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.55000000000000004">
@@ -873,7 +873,7 @@
         <v>0.5</v>
       </c>
       <c r="K11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.55000000000000004">
@@ -1201,7 +1201,7 @@
         <v>34</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -1343,13 +1343,13 @@
         <v>5</v>
       </c>
       <c r="C1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" t="s">
         <v>50</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>51</v>
-      </c>
-      <c r="E1" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -1414,7 +1414,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B5">
         <f>Herd_decision_tree!E27</f>
@@ -1477,10 +1477,10 @@
         <v>2020</v>
       </c>
       <c r="C1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" t="s">
         <v>53</v>
-      </c>
-      <c r="D1" t="s">
-        <v>54</v>
       </c>
       <c r="E1">
         <v>2050</v>
@@ -1548,7 +1548,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B5">
         <f>Validate_2020!B5</f>

--- a/Rasterized animal populations/Zonal statistics/Summary.xlsx
+++ b/Rasterized animal populations/Zonal statistics/Summary.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hawkj\Documents\Github\KE.beef.spatial\Rasterized animal populations\Zonal statistics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79D9F9AE-4D87-4B1A-9F51-CD6323A12095}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DE5D4DB-39FB-48E6-BBA8-43DE7A5F9781}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="20928" windowHeight="12432" xr2:uid="{3882C52B-09A6-47D1-94BA-1F6173569800}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="20928" windowHeight="12432" activeTab="1" xr2:uid="{3882C52B-09A6-47D1-94BA-1F6173569800}"/>
   </bookViews>
   <sheets>
     <sheet name="Herd_decision_tree" sheetId="1" r:id="rId1"/>
-    <sheet name="Validate_2020" sheetId="2" r:id="rId2"/>
-    <sheet name="Projections" sheetId="3" r:id="rId3"/>
+    <sheet name="Herd_decision_tree_old" sheetId="4" r:id="rId2"/>
+    <sheet name="Validate_2020" sheetId="2" r:id="rId3"/>
+    <sheet name="Projections" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,8 +41,27 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={0B974C83-E393-4D24-9238-9ECDE1F8DB25}</author>
+  </authors>
+  <commentList>
+    <comment ref="G34" authorId="0" shapeId="0" xr:uid="{0B974C83-E393-4D24-9238-9ECDE1F8DB25}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    https://gemini.google.com/app/cb2f8387004cee95
+Total boran should be 1 to 1.5 M</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="61">
   <si>
     <t>Comm</t>
   </si>
@@ -206,6 +226,24 @@
   </si>
   <si>
     <t>Breed decompositon (by farm-type)</t>
+  </si>
+  <si>
+    <t>Frac boran to total herd --  Cowcalf</t>
+  </si>
+  <si>
+    <t>Frac boran to total herd --  Finisher</t>
+  </si>
+  <si>
+    <t>KNBS (2023) -- FRAC Zebu total herd</t>
+  </si>
+  <si>
+    <t>KNBS (2023) -- FRAC Boran total herd</t>
+  </si>
+  <si>
+    <t>Boran -- Subsistence</t>
+  </si>
+  <si>
+    <t>Boran -- Commercial</t>
   </si>
 </sst>
 </file>
@@ -216,7 +254,7 @@
     <numFmt numFmtId="164" formatCode="0.00000"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -249,13 +287,32 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -270,7 +327,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -290,6 +347,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -305,6 +368,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="James Hawkins" id="{94C87838-5F63-4687-96E8-E5DFC56D834F}" userId="bb158497c03b6847" providerId="Windows Live"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -622,6 +691,21 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="G34" dT="2026-06-15T04:34:52.86" personId="{94C87838-5F63-4687-96E8-E5DFC56D834F}" id="{0B974C83-E393-4D24-9238-9ECDE1F8DB25}">
+    <text>https://gemini.google.com/app/cb2f8387004cee95
+Total boran should be 1 to 1.5 M</text>
+    <extLst>
+      <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
+        <xltc2:checksum>914658385</xltc2:checksum>
+        <xltc2:hyperlink startIndex="0" length="46" url="https://gemini.google.com/app/cb2f8387004cee95"/>
+      </x:ext>
+    </extLst>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{183B811A-D787-470A-BC9B-ADC2FAC32699}">
   <dimension ref="A1:K40"/>
@@ -708,6 +792,685 @@
         <v>15.480416807542506</v>
       </c>
       <c r="H3" t="s">
+        <v>55</v>
+      </c>
+      <c r="I3">
+        <v>0.68</v>
+      </c>
+      <c r="K3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="5">
+        <f>SUM(B2:B3)</f>
+        <v>4.8014806451976018</v>
+      </c>
+      <c r="C4" s="5">
+        <f>SUM(C2:C3)</f>
+        <v>6.3993096329112626</v>
+      </c>
+      <c r="D4" s="5">
+        <f>SUM(D2:D3)</f>
+        <v>5.5578048764834245</v>
+      </c>
+      <c r="E4" s="6">
+        <f>SUM(B4:D4)</f>
+        <v>16.758595154592289</v>
+      </c>
+      <c r="H4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I4">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="G5" t="s">
+        <v>54</v>
+      </c>
+      <c r="H5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5">
+        <v>0.6</v>
+      </c>
+      <c r="K5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="H6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6">
+        <v>0.6</v>
+      </c>
+      <c r="K6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="H7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7">
+        <v>0.5</v>
+      </c>
+      <c r="K7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="6">
+        <f>B3</f>
+        <v>4.5806949930214902</v>
+      </c>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6">
+        <f t="shared" ref="E8:E18" si="0">SUM(B8:D8)</f>
+        <v>4.5806949930214902</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="6">
+        <f>B8*I9</f>
+        <v>1.6490501974877365</v>
+      </c>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6">
+        <f t="shared" si="0"/>
+        <v>1.6490501974877365</v>
+      </c>
+      <c r="H9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I9">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="6">
+        <f>(B4-B9-B23-B27)</f>
+        <v>2.9316447955337539</v>
+      </c>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6">
+        <f t="shared" si="0"/>
+        <v>2.9316447955337539</v>
+      </c>
+      <c r="H10" t="s">
+        <v>58</v>
+      </c>
+      <c r="I10">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6">
+        <f>C3</f>
+        <v>5.9316142707009298</v>
+      </c>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6">
+        <f t="shared" si="0"/>
+        <v>5.9316142707009298</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6">
+        <f>C4*I9</f>
+        <v>2.3037514678480546</v>
+      </c>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6">
+        <f t="shared" si="0"/>
+        <v>2.3037514678480546</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6">
+        <f>C4-C13-C23-C27</f>
+        <v>3.6278628028528752</v>
+      </c>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6">
+        <f t="shared" si="0"/>
+        <v>3.6278628028528752</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6">
+        <f>D3</f>
+        <v>4.9681075438200857</v>
+      </c>
+      <c r="E16" s="6">
+        <f t="shared" si="0"/>
+        <v>4.9681075438200857</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6">
+        <f>D4*I9</f>
+        <v>2.000809755534033</v>
+      </c>
+      <c r="E17" s="6">
+        <f t="shared" si="0"/>
+        <v>2.000809755534033</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6">
+        <f>D4-D17-D23-D27</f>
+        <v>2.9672977882860532</v>
+      </c>
+      <c r="E18" s="6">
+        <f t="shared" si="0"/>
+        <v>2.9672977882860532</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" s="10">
+        <f>SUM(B13:B14)+SUM(B9:B10)</f>
+        <v>4.5806949930214902</v>
+      </c>
+      <c r="C21" s="10">
+        <f>SUM(C13:C14)+SUM(C9:C10)</f>
+        <v>5.9316142707009298</v>
+      </c>
+      <c r="D21" s="10">
+        <f>SUM(D13:D14)+SUM(D17:D18)</f>
+        <v>4.9681075438200857</v>
+      </c>
+      <c r="E21" s="10">
+        <f>SUM(B21:D21)</f>
+        <v>15.480416807542506</v>
+      </c>
+      <c r="F21" s="11"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="3"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" s="6">
+        <f>B4*$I2</f>
+        <v>1.6805182258191605E-2</v>
+      </c>
+      <c r="C23" s="6">
+        <f t="shared" ref="C23:D23" si="1">C4*$I2</f>
+        <v>2.239758371518942E-2</v>
+      </c>
+      <c r="D23" s="6">
+        <f>D4*$I2</f>
+        <v>1.9452317067691988E-2</v>
+      </c>
+      <c r="E23" s="6">
+        <f>SUM(B23:D23)</f>
+        <v>5.8655083041073017E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24" s="6">
+        <f>B23*$I4</f>
+        <v>1.1427523935570293E-2</v>
+      </c>
+      <c r="C24" s="6">
+        <f>C23*$I4</f>
+        <v>1.5230356926328808E-2</v>
+      </c>
+      <c r="D24" s="6">
+        <f>D23*$I4</f>
+        <v>1.3227575606030552E-2</v>
+      </c>
+      <c r="E24" s="6">
+        <f t="shared" ref="E24:E29" si="2">SUM(B24:D24)</f>
+        <v>3.9885456467929653E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25" s="6">
+        <f>B23*(1-$I4)</f>
+        <v>5.3776583226213129E-3</v>
+      </c>
+      <c r="C25" s="6">
+        <f>C23*(1-$I4)</f>
+        <v>7.1672267888606136E-3</v>
+      </c>
+      <c r="D25" s="6">
+        <f>D23*(1-$I4)</f>
+        <v>6.2247414616614354E-3</v>
+      </c>
+      <c r="E25" s="6">
+        <f t="shared" si="2"/>
+        <v>1.8769626573143364E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="3"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="6">
+        <f>B4-B23-SUM(B3)</f>
+        <v>0.20398046991792018</v>
+      </c>
+      <c r="C27" s="6">
+        <f t="shared" ref="C27:D27" si="3">C4-C23-SUM(C3)</f>
+        <v>0.44529777849514307</v>
+      </c>
+      <c r="D27" s="6">
+        <f t="shared" si="3"/>
+        <v>0.57024501559564644</v>
+      </c>
+      <c r="E27" s="6">
+        <f t="shared" si="2"/>
+        <v>1.2195232640087097</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B28" s="6">
+        <f>B27*($I3)</f>
+        <v>0.13870671954418573</v>
+      </c>
+      <c r="C28" s="6">
+        <f t="shared" ref="C28:D28" si="4">C27*($I3)</f>
+        <v>0.30280248937669729</v>
+      </c>
+      <c r="D28" s="6">
+        <f t="shared" si="4"/>
+        <v>0.38776661060503959</v>
+      </c>
+      <c r="E28" s="6">
+        <f t="shared" si="2"/>
+        <v>0.82927581952592266</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B29" s="6">
+        <f>B27*(1-$I3)</f>
+        <v>6.5273750373734452E-2</v>
+      </c>
+      <c r="C29" s="6">
+        <f t="shared" ref="C29:D29" si="5">C27*(1-$I3)</f>
+        <v>0.14249528911844575</v>
+      </c>
+      <c r="D29" s="6">
+        <f t="shared" si="5"/>
+        <v>0.18247840499060683</v>
+      </c>
+      <c r="E29" s="6">
+        <f t="shared" si="2"/>
+        <v>0.39024744448278703</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="3"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B31" s="6">
+        <f>SUM(B9:B10,B13:B14,B24:B25,B28:B29)</f>
+        <v>4.8014806451976018</v>
+      </c>
+      <c r="C31" s="6">
+        <f>SUM(C9:C10,C13:C14,C24:C25,C28:C29)</f>
+        <v>6.3993096329112626</v>
+      </c>
+      <c r="D31" s="6">
+        <f>SUM(D9:D10,D13:D14,D28:D29,D17:D18)</f>
+        <v>5.538352559415733</v>
+      </c>
+      <c r="E31" s="6">
+        <f>SUM(B31:D31)</f>
+        <v>16.739142837524597</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B35" s="4">
+        <f>SUM(B9,B13)</f>
+        <v>1.6490501974877365</v>
+      </c>
+      <c r="C35" s="4">
+        <f t="shared" ref="C35" si="6">SUM(C9,C13)</f>
+        <v>2.3037514678480546</v>
+      </c>
+      <c r="D35" s="4">
+        <f>SUM(D13,D17)</f>
+        <v>2.000809755534033</v>
+      </c>
+      <c r="E35" s="4">
+        <f>SUM(B35:D35)</f>
+        <v>5.9536114208698239</v>
+      </c>
+      <c r="F35">
+        <f>E35/E$38</f>
+        <v>0.35525718987479571</v>
+      </c>
+      <c r="G35">
+        <v>0.36</v>
+      </c>
+      <c r="H35">
+        <f>(F35-G35)</f>
+        <v>-4.7428101252042776E-3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B36" s="4">
+        <f>SUM(B10,B14,B24,B28)</f>
+        <v>3.0817790390135098</v>
+      </c>
+      <c r="C36" s="4">
+        <f t="shared" ref="C36" si="7">SUM(C10,C14,C24,C28)</f>
+        <v>3.9458956491559012</v>
+      </c>
+      <c r="D36" s="4">
+        <f>SUM(D14,D18,D24,D28)</f>
+        <v>3.3682919744971231</v>
+      </c>
+      <c r="E36" s="4">
+        <f t="shared" ref="E36:E37" si="8">SUM(B36:D36)</f>
+        <v>10.395966662666535</v>
+      </c>
+      <c r="F36">
+        <f t="shared" ref="F36:F37" si="9">E36/E$38</f>
+        <v>0.62033640449973937</v>
+      </c>
+      <c r="G36">
+        <v>0.61</v>
+      </c>
+      <c r="H36">
+        <f>ABS(F36-G36)</f>
+        <v>1.0336404499739382E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B37" s="6">
+        <f>SUM(B25,B29)</f>
+        <v>7.0651408696355764E-2</v>
+      </c>
+      <c r="C37" s="6">
+        <f t="shared" ref="C37" si="10">SUM(C25,C29)</f>
+        <v>0.14966251590730636</v>
+      </c>
+      <c r="D37" s="6">
+        <f>SUM(D25,D29)</f>
+        <v>0.18870314645226827</v>
+      </c>
+      <c r="E37" s="4">
+        <f t="shared" si="8"/>
+        <v>0.40901707105593038</v>
+      </c>
+      <c r="F37">
+        <f t="shared" si="9"/>
+        <v>2.4406405625464919E-2</v>
+      </c>
+      <c r="G37">
+        <v>0.03</v>
+      </c>
+      <c r="H37">
+        <f>ABS(F37-G37)</f>
+        <v>5.5935943745350804E-3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B38" s="4">
+        <f>SUM(B35:B37)</f>
+        <v>4.8014806451976018</v>
+      </c>
+      <c r="C38" s="4">
+        <f t="shared" ref="C38:D38" si="11">SUM(C35:C37)</f>
+        <v>6.3993096329112626</v>
+      </c>
+      <c r="D38" s="4">
+        <f t="shared" si="11"/>
+        <v>5.5578048764834245</v>
+      </c>
+      <c r="E38" s="4">
+        <f>SUM(B38:D38)</f>
+        <v>16.758595154592289</v>
+      </c>
+      <c r="H38">
+        <f>SUM(H35:H37)</f>
+        <v>1.1187188749070185E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" s="7"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDE56320-BEC2-4269-9329-43A80C09A702}">
+  <dimension ref="A1:K41"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="18.5234375" customWidth="1"/>
+    <col min="2" max="4" width="15.26171875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.26171875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.47265625" customWidth="1"/>
+    <col min="8" max="8" width="31.734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="3"/>
+      <c r="B1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="5">
+        <f>220785.652176112/1000000</f>
+        <v>0.22078565217611199</v>
+      </c>
+      <c r="C2" s="5">
+        <f>467695.362210333/1000000</f>
+        <v>0.46769536221033298</v>
+      </c>
+      <c r="D2" s="5">
+        <f>589697.332663339/1000000</f>
+        <v>0.58969733266333901</v>
+      </c>
+      <c r="E2" s="6">
+        <f>SUM(B2:D2)</f>
+        <v>1.2781783470497841</v>
+      </c>
+      <c r="G2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2">
+        <v>3.5000000000000001E-3</v>
+      </c>
+      <c r="K2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="5">
+        <f>4580694.99302149/1000000</f>
+        <v>4.5806949930214902</v>
+      </c>
+      <c r="C3" s="5">
+        <f>5931614.27070093/1000000</f>
+        <v>5.9316142707009298</v>
+      </c>
+      <c r="D3" s="5">
+        <v>4.9681075438200857</v>
+      </c>
+      <c r="E3" s="6">
+        <f>SUM(B3:D3)</f>
+        <v>15.480416807542506</v>
+      </c>
+      <c r="H3" t="s">
         <v>8</v>
       </c>
       <c r="I3">
@@ -750,7 +1513,7 @@
         <v>44</v>
       </c>
       <c r="I5">
-        <v>0.85</v>
+        <v>0.73913039999999997</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.55000000000000004">
@@ -765,7 +1528,7 @@
         <v>45</v>
       </c>
       <c r="I6">
-        <v>0.7</v>
+        <v>0.53480000000000005</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.55000000000000004">
@@ -780,7 +1543,7 @@
         <v>46</v>
       </c>
       <c r="I7">
-        <v>0.35</v>
+        <v>5.67E-2</v>
       </c>
       <c r="K7" t="s">
         <v>42</v>
@@ -792,16 +1555,16 @@
       </c>
       <c r="B8" s="6">
         <f>B3*I5</f>
-        <v>3.8935907440682667</v>
+        <v>3.3857309224699712</v>
       </c>
       <c r="C8" s="6">
         <f>C3*I6</f>
-        <v>4.1521299894906507</v>
+        <v>3.1722273119708575</v>
       </c>
       <c r="D8" s="6"/>
       <c r="E8" s="6">
         <f t="shared" ref="E8:E18" si="0">SUM(B8:D8)</f>
-        <v>8.0457207335589178</v>
+        <v>6.5579582344408287</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.55000000000000004">
@@ -810,16 +1573,16 @@
       </c>
       <c r="B9" s="6">
         <f>B8*(1-I9)</f>
-        <v>1.5574362976273068</v>
+        <v>2.9645459957147069</v>
       </c>
       <c r="C9" s="6">
         <f>C8*(1-I9)</f>
-        <v>1.6608519957962604</v>
+        <v>2.7776022343616829</v>
       </c>
       <c r="D9" s="6"/>
       <c r="E9" s="6">
         <f t="shared" si="0"/>
-        <v>3.2182882934235675</v>
+        <v>5.7421482300763902</v>
       </c>
       <c r="G9" t="s">
         <v>54</v>
@@ -828,7 +1591,8 @@
         <v>11</v>
       </c>
       <c r="I9">
-        <v>0.6</v>
+        <f>(0.1244)</f>
+        <v>0.1244</v>
       </c>
       <c r="K9" t="s">
         <v>43</v>
@@ -840,22 +1604,23 @@
       </c>
       <c r="B10" s="6">
         <f>B8*(I9)</f>
-        <v>2.3361544464409598</v>
+        <v>0.42118492675526442</v>
       </c>
       <c r="C10" s="6">
         <f>C8*(I9)</f>
-        <v>2.4912779936943905</v>
+        <v>0.39462507760917465</v>
       </c>
       <c r="D10" s="6"/>
       <c r="E10" s="6">
         <f t="shared" si="0"/>
-        <v>4.8274324401353503</v>
+        <v>0.81581000436443907</v>
       </c>
       <c r="H10" t="s">
         <v>12</v>
       </c>
       <c r="I10">
-        <v>0.6</v>
+        <f>(0.07)</f>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="K10" t="s">
         <v>43</v>
@@ -870,7 +1635,8 @@
         <v>14</v>
       </c>
       <c r="I11">
-        <v>0.5</v>
+        <f>(0.08)</f>
+        <v>0.08</v>
       </c>
       <c r="K11" t="s">
         <v>42</v>
@@ -882,19 +1648,19 @@
       </c>
       <c r="B12" s="6">
         <f>B3*(1-I5)</f>
-        <v>0.68710424895322364</v>
+        <v>1.194964070551519</v>
       </c>
       <c r="C12" s="6">
         <f>C3*(1-I6)</f>
-        <v>1.7794842812102791</v>
+        <v>2.7593869587300723</v>
       </c>
       <c r="D12" s="6">
         <f>D3*(1-I6)</f>
-        <v>1.4904322631460258</v>
+        <v>2.3111636293851037</v>
       </c>
       <c r="E12" s="6">
         <f t="shared" si="0"/>
-        <v>3.9570207933095283</v>
+        <v>6.265514658666695</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.55000000000000004">
@@ -903,19 +1669,19 @@
       </c>
       <c r="B13" s="6">
         <f>B$12*(1-I10)</f>
-        <v>0.27484169958128946</v>
+        <v>1.1113165856129126</v>
       </c>
       <c r="C13" s="6">
         <f>C12*(1-I10)</f>
-        <v>0.71179371248411172</v>
+        <v>2.5662298716189671</v>
       </c>
       <c r="D13" s="6">
         <f>D12*(1-I10)</f>
-        <v>0.59617290525841038</v>
+        <v>2.1493821753281463</v>
       </c>
       <c r="E13" s="6">
         <f t="shared" si="0"/>
-        <v>1.5828083173238117</v>
+        <v>5.8269286325600262</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.55000000000000004">
@@ -924,19 +1690,19 @@
       </c>
       <c r="B14" s="6">
         <f>B$12*(I10)</f>
-        <v>0.41226254937193418</v>
+        <v>8.364748493860634E-2</v>
       </c>
       <c r="C14" s="6">
         <f>C12*(I10)</f>
-        <v>1.0676905687261675</v>
+        <v>0.19315708711110507</v>
       </c>
       <c r="D14" s="6">
         <f>D12*(I10)</f>
-        <v>0.89425935788761546</v>
+        <v>0.16178145405695726</v>
       </c>
       <c r="E14" s="6">
         <f t="shared" si="0"/>
-        <v>2.3742124759857171</v>
+        <v>0.43858602610666869</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.55000000000000004">
@@ -953,11 +1719,11 @@
       <c r="C16" s="6"/>
       <c r="D16" s="6">
         <f>D3*I7</f>
-        <v>1.7388376403370298</v>
+        <v>0.28169169773459884</v>
       </c>
       <c r="E16" s="6">
         <f t="shared" si="0"/>
-        <v>1.7388376403370298</v>
+        <v>0.28169169773459884</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -968,11 +1734,11 @@
       <c r="C17" s="6"/>
       <c r="D17" s="6">
         <f>D$16*(1-I11)</f>
-        <v>0.86941882016851491</v>
+        <v>0.25915636191583097</v>
       </c>
       <c r="E17" s="6">
         <f t="shared" si="0"/>
-        <v>0.86941882016851491</v>
+        <v>0.25915636191583097</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -983,11 +1749,11 @@
       <c r="C18" s="6"/>
       <c r="D18" s="6">
         <f>D$16*(I11)</f>
-        <v>0.86941882016851491</v>
+        <v>2.2535335818767908E-2</v>
       </c>
       <c r="E18" s="6">
         <f t="shared" si="0"/>
-        <v>0.86941882016851491</v>
+        <v>2.2535335818767908E-2</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -1016,11 +1782,11 @@
       </c>
       <c r="D21" s="6">
         <f>SUM(D13:D14)+SUM(D17:D18)</f>
-        <v>3.2292699034830559</v>
+        <v>2.5928553271197026</v>
       </c>
       <c r="E21" s="6">
         <f>SUM(B21:D21)</f>
-        <v>13.741579167205476</v>
+        <v>13.105164590842122</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -1184,156 +1950,155 @@
       </c>
       <c r="D31" s="6">
         <f>SUM(D9:D10,D13:D14,D28:D29,D17:D18)</f>
-        <v>3.7995149190787023</v>
+        <v>3.163100342715349</v>
       </c>
       <c r="E31" s="6">
         <f>SUM(B31:D31)</f>
-        <v>15.000305197187568</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <v>14.363890620824215</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="G34" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="G34" s="3"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="3" t="s">
         <v>23</v>
       </c>
       <c r="B35" s="4">
         <f>SUM(B9,B13)</f>
-        <v>1.8322779972085963</v>
+        <v>4.0758625813276197</v>
       </c>
       <c r="C35" s="4">
-        <f t="shared" ref="C35" si="8">SUM(C9,C13)</f>
-        <v>2.372645708280372</v>
+        <f t="shared" ref="C35:D36" si="8">SUM(C9,C13)</f>
+        <v>5.3438321059806499</v>
       </c>
       <c r="D35" s="4">
         <f>SUM(D13,D17)</f>
-        <v>1.4655917254269253</v>
+        <v>2.4085385372439774</v>
       </c>
       <c r="E35" s="4">
         <f>SUM(B35:D35)</f>
-        <v>5.6705154309158941</v>
+        <v>11.828233224552246</v>
       </c>
       <c r="F35">
-        <f>E35/E$38</f>
-        <v>0.37753708244184403</v>
-      </c>
-      <c r="G35">
-        <v>0.36</v>
-      </c>
-      <c r="H35">
-        <f>(F35-G35)</f>
-        <v>1.7537082441844043E-2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <f>E35/E$39</f>
+        <v>0.82364679983907818</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="3" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="B36" s="4">
-        <f>SUM(B10,B14,B24,B28)</f>
-        <v>2.89855123929265</v>
+        <f>SUM(B10,B14)</f>
+        <v>0.50483241169387072</v>
       </c>
       <c r="C36" s="4">
-        <f t="shared" ref="C36" si="9">SUM(C10,C14,C24,C28)</f>
-        <v>3.8770014087235842</v>
+        <f t="shared" si="8"/>
+        <v>0.58778216472027967</v>
       </c>
       <c r="D36" s="4">
-        <f>SUM(D14,D18,D24,D28)</f>
-        <v>2.1646723642672003</v>
-      </c>
-      <c r="E36" s="4">
-        <f t="shared" ref="E36:E37" si="10">SUM(B36:D36)</f>
-        <v>8.9402250122834346</v>
+        <f t="shared" si="8"/>
+        <v>0.16178145405695726</v>
+      </c>
+      <c r="E36" s="12">
+        <f>SUM(B36:D36)</f>
+        <v>1.2543960304711077</v>
       </c>
       <c r="F36">
-        <f t="shared" ref="F36:F37" si="11">E36/E$38</f>
-        <v>0.59523098184496404</v>
-      </c>
-      <c r="G36">
-        <v>0.61</v>
-      </c>
-      <c r="H36">
-        <f>ABS(F36-G36)</f>
-        <v>1.4769018155035951E-2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <f>E36/E$39</f>
+        <v>8.73485715587487E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B37" s="4">
+        <f>SUM(B24,B28)</f>
+        <v>0.15013424347975601</v>
+      </c>
+      <c r="C37" s="4">
+        <f t="shared" ref="C37:D37" si="9">SUM(C24,C28)</f>
+        <v>0.31803284630302608</v>
+      </c>
+      <c r="D37" s="4">
+        <f t="shared" si="9"/>
+        <v>0.40099418621107014</v>
+      </c>
+      <c r="E37" s="4">
+        <f>SUM(B37:D37)</f>
+        <v>0.86916127599385229</v>
+      </c>
+      <c r="F37">
+        <f>E37/E$39</f>
+        <v>6.052314744947767E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B37" s="6">
+      <c r="B38" s="6">
         <f>SUM(B25,B29)</f>
         <v>7.0651408696355764E-2</v>
       </c>
-      <c r="C37" s="6">
-        <f t="shared" ref="C37" si="12">SUM(C25,C29)</f>
+      <c r="C38" s="6">
+        <f t="shared" ref="C38" si="10">SUM(C25,C29)</f>
         <v>0.14966251590730636</v>
       </c>
-      <c r="D37" s="6">
+      <c r="D38" s="6">
         <f>SUM(D25,D29)</f>
         <v>0.18870314645226827</v>
       </c>
-      <c r="E37" s="4">
-        <f t="shared" si="10"/>
+      <c r="E38" s="4">
+        <f t="shared" ref="E38" si="11">SUM(B38:D38)</f>
         <v>0.40901707105593038</v>
       </c>
-      <c r="F37">
-        <f t="shared" si="11"/>
-        <v>2.7231935713191914E-2</v>
-      </c>
-      <c r="G37">
-        <v>0.03</v>
-      </c>
-      <c r="H37">
-        <f>ABS(F37-G37)</f>
-        <v>2.7680642868080849E-3</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="3" t="s">
+      <c r="F38">
+        <f>E38/E$39</f>
+        <v>2.8481481152695366E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B38" s="4">
-        <f>SUM(B35:B37)</f>
+      <c r="B39" s="4">
+        <f>SUM(B35:B38)</f>
         <v>4.8014806451976018</v>
       </c>
-      <c r="C38" s="4">
-        <f t="shared" ref="C38:D38" si="13">SUM(C35:C37)</f>
+      <c r="C39" s="4">
+        <f t="shared" ref="C39:D39" si="12">SUM(C35:C38)</f>
         <v>6.3993096329112626</v>
       </c>
-      <c r="D38" s="4">
-        <f t="shared" si="13"/>
-        <v>3.8189672361463938</v>
-      </c>
-      <c r="E38" s="4">
-        <f>SUM(B38:D38)</f>
-        <v>15.019757514255259</v>
-      </c>
-      <c r="H38">
-        <f>SUM(H35:H37)</f>
-        <v>3.5074164883688079E-2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="7"/>
+      <c r="D39" s="4">
+        <f t="shared" si="12"/>
+        <v>3.160017323964273</v>
+      </c>
+      <c r="E39" s="4">
+        <f>SUM(B39:D39)</f>
+        <v>14.360807602073137</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DC88038-24E0-4487-8E9E-ADD8D4CE8257}">
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
@@ -1357,19 +2122,19 @@
         <v>15</v>
       </c>
       <c r="B2">
-        <f>Herd_decision_tree!E8</f>
-        <v>8.0457207335589178</v>
+        <f>Herd_decision_tree_old!E8</f>
+        <v>6.5579582344408287</v>
       </c>
       <c r="C2">
         <f>B2/$B$7</f>
-        <v>0.43443985307938637</v>
+        <v>0.36670762604152596</v>
       </c>
       <c r="D2">
         <v>0.43</v>
       </c>
       <c r="E2">
         <f>ABS(C2-D2)</f>
-        <v>4.43985307938638E-3</v>
+        <v>6.3292373958474035E-2</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -1377,19 +2142,19 @@
         <v>18</v>
       </c>
       <c r="B3">
-        <f>Herd_decision_tree!E12</f>
-        <v>3.9570207933095283</v>
+        <f>Herd_decision_tree_old!E12</f>
+        <v>6.265514658666695</v>
       </c>
       <c r="C3">
         <f t="shared" ref="C3:C6" si="0">B3/$B$7</f>
-        <v>0.21366482742895962</v>
+        <v>0.3503547787696385</v>
       </c>
       <c r="D3">
         <v>0.28999999999999998</v>
       </c>
       <c r="E3">
         <f t="shared" ref="E3:E6" si="1">ABS(C3-D3)</f>
-        <v>7.6335172571040361E-2</v>
+        <v>6.0354778769638517E-2</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -1397,19 +2162,19 @@
         <v>13</v>
       </c>
       <c r="B4">
-        <f>Herd_decision_tree!E16</f>
-        <v>1.7388376403370298</v>
+        <f>Herd_decision_tree_old!E16</f>
+        <v>0.28169169773459884</v>
       </c>
       <c r="C4">
         <f t="shared" si="0"/>
-        <v>9.3890950731865139E-2</v>
+        <v>1.5751624218855627E-2</v>
       </c>
       <c r="D4">
         <v>0.1</v>
       </c>
       <c r="E4">
         <f t="shared" si="1"/>
-        <v>6.1090492681348668E-3</v>
+        <v>8.4248375781144386E-2</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -1417,19 +2182,19 @@
         <v>48</v>
       </c>
       <c r="B5">
-        <f>Herd_decision_tree!E27</f>
+        <f>Herd_decision_tree_old!E27</f>
         <v>1.2195232640087097</v>
       </c>
       <c r="C5">
         <f t="shared" si="0"/>
-        <v>6.5849850521531014E-2</v>
+        <v>6.819324934068885E-2</v>
       </c>
       <c r="D5">
         <v>0.04</v>
       </c>
       <c r="E5">
         <f t="shared" si="1"/>
-        <v>2.5849850521531013E-2</v>
+        <v>2.8193249340688849E-2</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -1437,29 +2202,29 @@
         <v>26</v>
       </c>
       <c r="B6">
-        <f>Herd_decision_tree!E23</f>
+        <f>Herd_decision_tree_old!E23</f>
         <v>5.8655083041073017E-2</v>
       </c>
       <c r="C6">
         <f t="shared" si="0"/>
-        <v>3.1671625827673117E-3</v>
+        <v>3.2798724066736094E-3</v>
       </c>
       <c r="D6">
         <v>2.0000000000000001E-4</v>
       </c>
       <c r="E6">
         <f t="shared" si="1"/>
-        <v>2.9671625827673116E-3</v>
+        <v>3.0798724066736093E-3</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B7">
         <f>SUM(B2:B6)+3.5</f>
-        <v>18.519757514255261</v>
+        <v>17.883342937891904</v>
       </c>
       <c r="E7">
         <f>SUM(E2:E6)</f>
-        <v>0.11570108802285993</v>
+        <v>0.2391686502566194</v>
       </c>
     </row>
   </sheetData>
@@ -1467,7 +2232,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD6A4001-CB5D-4E56-8C0D-2957A97A30B1}">
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
@@ -1492,18 +2257,18 @@
       </c>
       <c r="B2">
         <f>Validate_2020!B2</f>
-        <v>8.0457207335589178</v>
+        <v>6.5579582344408287</v>
       </c>
       <c r="C2">
         <v>0.05</v>
       </c>
       <c r="D2">
         <f>B2*C2*30</f>
-        <v>12.068581100338378</v>
+        <v>9.8369373516612448</v>
       </c>
       <c r="E2">
         <f>B2+D2</f>
-        <v>20.114301833897294</v>
+        <v>16.394895586102074</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -1512,18 +2277,18 @@
       </c>
       <c r="B3">
         <f>Validate_2020!B3</f>
-        <v>3.9570207933095283</v>
+        <v>6.265514658666695</v>
       </c>
       <c r="C3">
         <v>0.05</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:D6" si="0">B3*C3*30</f>
-        <v>5.9355311899642933</v>
+        <v>9.3982719880000438</v>
       </c>
       <c r="E3">
         <f t="shared" ref="E3:E6" si="1">B3+D3</f>
-        <v>9.8925519832738225</v>
+        <v>15.66378664666674</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -1532,18 +2297,18 @@
       </c>
       <c r="B4">
         <f>Validate_2020!B4</f>
-        <v>1.7388376403370298</v>
+        <v>0.28169169773459884</v>
       </c>
       <c r="C4">
         <v>0.05</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
-        <v>2.6082564605055447</v>
+        <v>0.4225375466018983</v>
       </c>
       <c r="E4">
         <f t="shared" si="1"/>
-        <v>4.3470941008425745</v>
+        <v>0.70422924433649714</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">

--- a/Rasterized animal populations/Zonal statistics/Summary.xlsx
+++ b/Rasterized animal populations/Zonal statistics/Summary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JHawkins\Documents\Github\KE.beef.spatial\Rasterized animal populations\Zonal statistics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EDDB6ED-CCE9-4C62-8457-46535436E35A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C98A1DC-C804-45B9-BE40-B32C1E7CBE2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" activeTab="1" xr2:uid="{3882C52B-09A6-47D1-94BA-1F6173569800}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{3882C52B-09A6-47D1-94BA-1F6173569800}"/>
   </bookViews>
   <sheets>
     <sheet name="Validate_2020" sheetId="2" r:id="rId1"/>
@@ -30,6 +30,16 @@
     <externalReference r:id="rId13"/>
     <externalReference r:id="rId14"/>
     <externalReference r:id="rId15"/>
+    <externalReference r:id="rId16"/>
+    <externalReference r:id="rId17"/>
+    <externalReference r:id="rId18"/>
+    <externalReference r:id="rId19"/>
+    <externalReference r:id="rId20"/>
+    <externalReference r:id="rId21"/>
+    <externalReference r:id="rId22"/>
+    <externalReference r:id="rId23"/>
+    <externalReference r:id="rId24"/>
+    <externalReference r:id="rId25"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -74,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="61">
   <si>
     <t>Comm</t>
   </si>
@@ -254,6 +264,9 @@
   </si>
   <si>
     <t>Excel method</t>
+  </si>
+  <si>
+    <t>Delta total</t>
   </si>
 </sst>
 </file>
@@ -261,8 +274,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="169" formatCode="0.00000000"/>
-    <numFmt numFmtId="170" formatCode="0.000000000"/>
+    <numFmt numFmtId="164" formatCode="0.00000000"/>
+    <numFmt numFmtId="165" formatCode="0.000000000"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -340,12 +353,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="170" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -376,35 +389,55 @@
       <sheetName val="Raster_logic"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="35">
+          <cell r="F35">
+            <v>0.53615960099750615</v>
+          </cell>
           <cell r="G35">
-            <v>0.27042835936947801</v>
+            <v>0.38312009613345605</v>
           </cell>
         </row>
         <row r="36">
+          <cell r="F36">
+            <v>0.36159600997506236</v>
+          </cell>
           <cell r="G36">
-            <v>2.535976312755476</v>
+            <v>2.7950424483806726</v>
           </cell>
         </row>
         <row r="37">
+          <cell r="F37">
+            <v>2.4937655860349127E-3</v>
+          </cell>
           <cell r="G37">
-            <v>112.96352583586625</v>
+            <v>86.466565349544069</v>
           </cell>
         </row>
         <row r="38">
+          <cell r="F38">
+            <v>4.9875311720698257E-2</v>
+          </cell>
           <cell r="G38">
-            <v>1.7484802431610944</v>
+            <v>1.0372340425531916</v>
           </cell>
         </row>
         <row r="39">
+          <cell r="F39">
+            <v>4.9875311720698257E-2</v>
+          </cell>
           <cell r="G39">
-            <v>9.3750034539928144</v>
+            <v>7.6101823708206684</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="G40">
+            <v>1.354588821344141</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -454,6 +487,182 @@
 </externalLink>
 </file>
 
+<file path=xl/externalLinks/externalLink12.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Pastoral_Zebu_2050"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>8554757.4814370908</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Pastoral_Boran_2050"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>1215408.67359516</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Agpastoral_Boran_2050"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>488402.05019366002</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Mixed_Boran_2050"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>35153.269665965803</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink16.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Cowcalf_Exotic_2050"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>1503165.94333724</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink17.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Finisher_Exotic_2050"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>432162.57168335503</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink18.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Agpastoral_Zebu_2050"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>6488770.1197828101</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink19.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Mixed_Zebu_2050"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>404262.59496554697</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
@@ -468,6 +677,50 @@
         <row r="2">
           <cell r="K2">
             <v>7912803.5780913802</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink20.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Cowcalf_Boran_2050"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>1806208.69891036</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink21.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Finisher_Boran_2050"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>918345.45531155204</v>
           </cell>
         </row>
       </sheetData>
@@ -1000,29 +1253,31 @@
       </c>
       <c r="B2">
         <f>Herd_decision_tree!E8</f>
-        <v>7.837059449452795</v>
+        <v>6.99195979776652</v>
       </c>
       <c r="C2" s="6">
         <f>B2/$B$7</f>
-        <v>0.61071857623800974</v>
+        <v>0.51509165724121786</v>
       </c>
       <c r="D2">
-        <v>0.43</v>
+        <f>[1]FAO_2019_animal_trends!$F$35</f>
+        <v>0.53615960099750615</v>
       </c>
       <c r="E2">
         <f>D2/D$7</f>
-        <v>0.54292929292929293</v>
+        <v>0.53615960099750626</v>
       </c>
       <c r="F2" s="6">
         <f>E2-5*G2*E2*0.96/100</f>
-        <v>0.53588176598814896</v>
+        <v>0.52629975213940838</v>
       </c>
       <c r="G2">
-        <v>0.27042835936947801</v>
+        <f>[1]FAO_2019_animal_trends!$G$35</f>
+        <v>0.38312009613345605</v>
       </c>
       <c r="H2">
         <f>ABS(F2-C2)</f>
-        <v>7.4836810249860775E-2</v>
+        <v>1.1208094898190524E-2</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -1031,29 +1286,31 @@
       </c>
       <c r="B3">
         <f>Herd_decision_tree!E12</f>
-        <v>3.435592315937023</v>
+        <v>4.5255644973891247</v>
       </c>
       <c r="C3" s="6">
         <f t="shared" ref="C3:C6" si="0">B3/$B$7</f>
-        <v>0.26772542192082077</v>
+        <v>0.33339443937546859</v>
       </c>
       <c r="D3">
-        <v>0.28999999999999998</v>
+        <f>[1]FAO_2019_animal_trends!$F$36</f>
+        <v>0.36159600997506236</v>
       </c>
       <c r="E3">
         <f t="shared" ref="E3:E6" si="1">D3/D$7</f>
-        <v>0.36616161616161613</v>
+        <v>0.36159600997506242</v>
       </c>
       <c r="F3" s="6">
-        <f t="shared" ref="F3:F6" si="2">E3-5*G3*E3*0.95/100</f>
-        <v>0.32205419986337536</v>
+        <f>E3-5*G3*E3*0.95/100</f>
+        <v>0.31358889061540685</v>
       </c>
       <c r="G3">
-        <v>2.535976312755476</v>
+        <f>[1]FAO_2019_animal_trends!$G$36</f>
+        <v>2.7950424483806726</v>
       </c>
       <c r="H3">
-        <f t="shared" ref="H3:H6" si="3">ABS(F3-C3)</f>
-        <v>5.4328777942554585E-2</v>
+        <f>ABS(F3-C3)</f>
+        <v>1.9805548760061742E-2</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1062,29 +1319,31 @@
       </c>
       <c r="B4">
         <f>Herd_decision_tree!E16</f>
-        <v>0.28169169773459884</v>
+        <v>0.7785024521166074</v>
       </c>
       <c r="C4" s="6">
         <f t="shared" si="0"/>
-        <v>2.1951390529588735E-2</v>
+        <v>5.7351605247385556E-2</v>
       </c>
       <c r="D4">
-        <v>0.03</v>
+        <f>[1]FAO_2019_animal_trends!$F$39</f>
+        <v>4.9875311720698257E-2</v>
       </c>
       <c r="E4">
         <f t="shared" si="1"/>
-        <v>3.7878787878787873E-2</v>
+        <v>4.9875311720698264E-2</v>
       </c>
       <c r="F4" s="6">
-        <f t="shared" si="2"/>
-        <v>2.1010883936944742E-2</v>
+        <f t="shared" ref="F3:F6" si="2">E4-5*G4*E4*0.95/100</f>
+        <v>4.6666186084097429E-2</v>
       </c>
       <c r="G4">
-        <v>9.3750034539928144</v>
+        <f>[1]FAO_2019_animal_trends!$G$40</f>
+        <v>1.354588821344141</v>
       </c>
       <c r="H4">
-        <f t="shared" si="3"/>
-        <v>9.4050659264399358E-4</v>
+        <f t="shared" ref="H3:H6" si="3">ABS(F4-C4)</f>
+        <v>1.0685419163288128E-2</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -1093,29 +1352,31 @@
       </c>
       <c r="B5">
         <f>Herd_decision_tree!E27</f>
-        <v>1.2446611567405994</v>
+        <v>1.219523264008711</v>
       </c>
       <c r="C5" s="6">
         <f t="shared" si="0"/>
-        <v>9.6992717031953612E-2</v>
+        <v>8.9841228678563756E-2</v>
       </c>
       <c r="D5">
-        <v>0.04</v>
+        <f>[1]FAO_2019_animal_trends!$F$38</f>
+        <v>4.9875311720698257E-2</v>
       </c>
       <c r="E5">
         <f t="shared" si="1"/>
-        <v>5.0505050505050504E-2</v>
+        <v>4.9875311720698264E-2</v>
       </c>
       <c r="F5" s="6">
         <f t="shared" si="2"/>
-        <v>4.6310464063123634E-2</v>
+        <v>4.7418024088714393E-2</v>
       </c>
       <c r="G5">
-        <v>1.7484802431610944</v>
+        <f>[1]FAO_2019_animal_trends!$G$38</f>
+        <v>1.0372340425531916</v>
       </c>
       <c r="H5">
         <f t="shared" si="3"/>
-        <v>5.0682252968829979E-2</v>
+        <v>4.2423204589849363E-2</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -1124,43 +1385,45 @@
       </c>
       <c r="B6">
         <f>Herd_decision_tree!E23</f>
-        <v>3.3517190309184576E-2</v>
+        <v>5.8655083041073017E-2</v>
       </c>
       <c r="C6" s="6">
         <f t="shared" si="0"/>
-        <v>2.6118942796271452E-3</v>
+        <v>4.3210694573642397E-3</v>
       </c>
       <c r="D6">
-        <v>2E-3</v>
+        <f>[1]FAO_2019_animal_trends!$F$37</f>
+        <v>2.4937655860349127E-3</v>
       </c>
       <c r="E6">
         <f t="shared" si="1"/>
-        <v>2.525252525252525E-3</v>
+        <v>2.4937655860349131E-3</v>
       </c>
       <c r="F6" s="6">
         <f t="shared" si="2"/>
-        <v>-1.1024665346473853E-2</v>
+        <v>-7.7485333020033496E-3</v>
       </c>
       <c r="G6">
-        <v>112.96352583586625</v>
+        <f>[1]FAO_2019_animal_trends!$G$37</f>
+        <v>86.466565349544069</v>
       </c>
       <c r="H6">
         <f t="shared" si="3"/>
-        <v>1.3636559626100997E-2</v>
+        <v>1.2069602759367588E-2</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B7">
         <f>SUM(B2:B6)</f>
-        <v>12.832521810174201</v>
+        <v>13.574205094322036</v>
       </c>
       <c r="D7">
         <f>SUM(D2:D6)</f>
-        <v>0.79200000000000004</v>
+        <v>0.99999999999999989</v>
       </c>
       <c r="H7">
         <f>SUM(H2:H6)</f>
-        <v>0.19442490737999032</v>
+        <v>9.6191870170757338E-2</v>
       </c>
     </row>
   </sheetData>
@@ -1228,7 +1491,7 @@
         <v>7</v>
       </c>
       <c r="I2">
-        <v>2E-3</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="K2" t="s">
         <v>39</v>
@@ -1296,11 +1559,8 @@
         <v>42</v>
       </c>
       <c r="I5" s="6">
-        <f>0.7391304+0.085-J5</f>
-        <v>0.82413039999999993</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
+        <f>0.7391304+0.03</f>
+        <v>0.76913039999999999</v>
       </c>
       <c r="K5" t="s">
         <v>41</v>
@@ -1318,11 +1578,8 @@
         <v>43</v>
       </c>
       <c r="I6" s="6">
-        <f>0.5348+0.15-J6</f>
-        <v>0.68480000000000008</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
+        <f>0.5348+0.05</f>
+        <v>0.5848000000000001</v>
       </c>
       <c r="K6" t="s">
         <v>41</v>
@@ -1340,8 +1597,8 @@
         <v>44</v>
       </c>
       <c r="I7">
-        <f>0.0567</f>
-        <v>5.67E-2</v>
+        <f>0.0567+0.1</f>
+        <v>0.15670000000000001</v>
       </c>
       <c r="K7" t="s">
         <v>41</v>
@@ -1353,16 +1610,16 @@
       </c>
       <c r="B8" s="9">
         <f>B3*I5</f>
-        <v>3.7750899968767975</v>
+        <v>3.5231517722606158</v>
       </c>
       <c r="C8" s="9">
         <f>C3*I6</f>
-        <v>4.0619694525759975</v>
+        <v>3.4688080255059042</v>
       </c>
       <c r="D8" s="9"/>
       <c r="E8" s="9">
         <f t="shared" ref="E8:E18" si="0">SUM(B8:D8)</f>
-        <v>7.837059449452795</v>
+        <v>6.99195979776652</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -1371,16 +1628,16 @@
       </c>
       <c r="B9" s="9">
         <f>B8*(1-I9)</f>
-        <v>3.3054688012653242</v>
+        <v>3.0848716917913954</v>
       </c>
       <c r="C9" s="9">
         <f>C8*(1-I9)</f>
-        <v>3.5566604526755436</v>
+        <v>3.0372883071329699</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="9">
         <f t="shared" si="0"/>
-        <v>6.8621292539408678</v>
+        <v>6.1221599989243654</v>
       </c>
       <c r="G9" t="s">
         <v>50</v>
@@ -1402,16 +1659,16 @@
       </c>
       <c r="B10" s="9">
         <f>B8*(I9)</f>
-        <v>0.46962119561147359</v>
+        <v>0.43828008046922062</v>
       </c>
       <c r="C10" s="9">
         <f>C8*(I9)</f>
-        <v>0.50530899990045408</v>
+        <v>0.43151971837293446</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="9">
         <f t="shared" si="0"/>
-        <v>0.97493019551192761</v>
+        <v>0.86979979884215508</v>
       </c>
       <c r="H10" t="s">
         <v>12</v>
@@ -1447,15 +1704,15 @@
       <c r="B12" s="9"/>
       <c r="C12" s="9">
         <f>C3*(1-I6)</f>
-        <v>1.8696448181249326</v>
+        <v>2.4628062451950257</v>
       </c>
       <c r="D12" s="9">
         <f>D3*(1-I6)</f>
-        <v>1.5659474978120906</v>
+        <v>2.062758252194099</v>
       </c>
       <c r="E12" s="9">
         <f t="shared" si="0"/>
-        <v>3.435592315937023</v>
+        <v>4.5255644973891247</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1465,15 +1722,15 @@
       <c r="B13" s="9"/>
       <c r="C13" s="9">
         <f>C12*(1-I10)</f>
-        <v>1.7387696808561872</v>
+        <v>2.2904098080313737</v>
       </c>
       <c r="D13" s="9">
         <f>D12*(1-I10)</f>
-        <v>1.4563311729652442</v>
+        <v>1.9183651745405119</v>
       </c>
       <c r="E13" s="9">
         <f t="shared" si="0"/>
-        <v>3.1951008538214314</v>
+        <v>4.2087749825718852</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1483,15 +1740,15 @@
       <c r="B14" s="9"/>
       <c r="C14" s="9">
         <f>C12*(I10)</f>
-        <v>0.13087513726874528</v>
+        <v>0.1723964371636518</v>
       </c>
       <c r="D14" s="9">
         <f>D12*(I10)</f>
-        <v>0.10961632484684636</v>
+        <v>0.14439307765358694</v>
       </c>
       <c r="E14" s="9">
         <f t="shared" si="0"/>
-        <v>0.24049146211559164</v>
+        <v>0.31678951481723872</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -1508,11 +1765,11 @@
       <c r="C16" s="9"/>
       <c r="D16" s="9">
         <f>D3*I7</f>
-        <v>0.28169169773459884</v>
+        <v>0.7785024521166074</v>
       </c>
       <c r="E16" s="9">
         <f t="shared" si="0"/>
-        <v>0.28169169773459884</v>
+        <v>0.7785024521166074</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -1523,11 +1780,11 @@
       <c r="C17" s="9"/>
       <c r="D17" s="9">
         <f>D$16*(1-I11)</f>
-        <v>0.25915636191583097</v>
+        <v>0.71622225594727884</v>
       </c>
       <c r="E17" s="9">
         <f t="shared" si="0"/>
-        <v>0.25915636191583097</v>
+        <v>0.71622225594727884</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -1538,11 +1795,11 @@
       <c r="C18" s="9"/>
       <c r="D18" s="9">
         <f>D$16*(I11)</f>
-        <v>2.2535335818767908E-2</v>
+        <v>6.2280196169328596E-2</v>
       </c>
       <c r="E18" s="9">
         <f t="shared" si="0"/>
-        <v>2.2535335818767908E-2</v>
+        <v>6.2280196169328596E-2</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -1563,7 +1820,7 @@
       </c>
       <c r="B21" s="9">
         <f>SUM(B13:B14)+SUM(B9:B10)</f>
-        <v>3.7750899968767979</v>
+        <v>3.5231517722606158</v>
       </c>
       <c r="C21" s="9">
         <f>SUM(C13:C14)+SUM(C9:C10)</f>
@@ -1571,11 +1828,11 @@
       </c>
       <c r="D21" s="9">
         <f>SUM(D13:D14)+SUM(D17:D18)</f>
-        <v>1.8476391955466895</v>
+        <v>2.8412607043107063</v>
       </c>
       <c r="E21" s="9">
         <f>SUM(B21:D21)</f>
-        <v>11.554343463124416</v>
+        <v>12.296026747272251</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -1591,19 +1848,19 @@
       </c>
       <c r="B23" s="9">
         <f>B4*$I2</f>
-        <v>9.6029612903952045E-3</v>
+        <v>1.6805182258191605E-2</v>
       </c>
       <c r="C23" s="9">
         <f t="shared" ref="C23:D23" si="1">C4*$I2</f>
-        <v>1.2798619265822526E-2</v>
+        <v>2.239758371518942E-2</v>
       </c>
       <c r="D23" s="9">
         <f t="shared" si="1"/>
-        <v>1.1115609752966849E-2</v>
+        <v>1.9452317067691988E-2</v>
       </c>
       <c r="E23" s="9">
         <f>SUM(B23:D23)</f>
-        <v>3.3517190309184576E-2</v>
+        <v>5.8655083041073017E-2</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -1612,23 +1869,23 @@
       </c>
       <c r="B24" s="9">
         <f>B23*$I3</f>
-        <v>6.5300136774687394E-3</v>
+        <v>1.1427523935570293E-2</v>
       </c>
       <c r="C24" s="9">
         <f t="shared" ref="C24:D24" si="2">C23*$I3</f>
-        <v>8.7030611007593191E-3</v>
+        <v>1.5230356926328808E-2</v>
       </c>
       <c r="D24" s="9">
         <f t="shared" si="2"/>
-        <v>7.5586146320174574E-3</v>
+        <v>1.3227575606030552E-2</v>
       </c>
       <c r="E24" s="9">
         <f>SUM(B24:D24)</f>
-        <v>2.2791689410245515E-2</v>
+        <v>3.9885456467929653E-2</v>
       </c>
       <c r="G24">
         <f>E24*E42</f>
-        <v>2.943040940522464E-2</v>
+        <v>4.8827647518794502E-2</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -1637,23 +1894,23 @@
       </c>
       <c r="B25" s="9">
         <f>B23*(1-$I3)</f>
-        <v>3.0729476129264651E-3</v>
+        <v>5.3776583226213129E-3</v>
       </c>
       <c r="C25" s="9">
         <f t="shared" ref="C25:D25" si="3">C23*(1-$I3)</f>
-        <v>4.0955581650632079E-3</v>
+        <v>7.1672267888606136E-3</v>
       </c>
       <c r="D25" s="9">
         <f t="shared" si="3"/>
-        <v>3.556995120949391E-3</v>
+        <v>6.2247414616614354E-3</v>
       </c>
       <c r="E25" s="9">
-        <f t="shared" ref="E24:E29" si="4">SUM(B25:D25)</f>
-        <v>1.0725500898939064E-2</v>
+        <f t="shared" ref="E25:E29" si="4">SUM(B25:D25)</f>
+        <v>1.8769626573143364E-2</v>
       </c>
       <c r="G25">
         <f>E25*1.21</f>
-        <v>1.2977856087716268E-2</v>
+        <v>2.271124815350347E-2</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -1669,19 +1926,19 @@
       </c>
       <c r="B27" s="9">
         <f>B2-B23</f>
-        <v>0.21118269088571678</v>
+        <v>0.20398046991792038</v>
       </c>
       <c r="C27" s="9">
         <f t="shared" ref="C27:D27" si="5">C2-C23</f>
-        <v>0.45489674294451043</v>
+        <v>0.44529777849514357</v>
       </c>
       <c r="D27" s="9">
         <f t="shared" si="5"/>
-        <v>0.57858172291037213</v>
+        <v>0.570245015595647</v>
       </c>
       <c r="E27" s="9">
         <f t="shared" si="4"/>
-        <v>1.2446611567405994</v>
+        <v>1.219523264008711</v>
       </c>
       <c r="G27">
         <f>22*1.21</f>
@@ -1694,23 +1951,23 @@
       </c>
       <c r="B28" s="9">
         <f>B27*($I3)</f>
-        <v>0.14360422980228743</v>
+        <v>0.13870671954418587</v>
       </c>
       <c r="C28" s="9">
-        <f t="shared" ref="C28:D28" si="6">C27*($I3)</f>
-        <v>0.30932978520226712</v>
+        <f t="shared" ref="C28" si="6">C27*($I3)</f>
+        <v>0.30280248937669763</v>
       </c>
       <c r="D28" s="9">
         <f>D27*($I3)</f>
-        <v>0.39343557157905307</v>
+        <v>0.38776661060503997</v>
       </c>
       <c r="E28" s="9">
         <f t="shared" si="4"/>
-        <v>0.84636958658360761</v>
+        <v>0.82927581952592355</v>
       </c>
       <c r="G28">
         <f>E28*1.21</f>
-        <v>1.0241071997661653</v>
+        <v>1.0034237416263674</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -1719,19 +1976,19 @@
       </c>
       <c r="B29" s="9">
         <f>B27*(1-$I3)</f>
-        <v>6.7578461083429367E-2</v>
+        <v>6.5273750373734507E-2</v>
       </c>
       <c r="C29" s="9">
         <f t="shared" ref="C29:D29" si="7">C27*(1-$I3)</f>
-        <v>0.14556695774224332</v>
+        <v>0.14249528911844592</v>
       </c>
       <c r="D29" s="9">
         <f t="shared" si="7"/>
-        <v>0.18514615133131906</v>
+        <v>0.18247840499060702</v>
       </c>
       <c r="E29" s="9">
         <f t="shared" si="4"/>
-        <v>0.39829157015699174</v>
+        <v>0.39024744448278748</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -1747,7 +2004,7 @@
       </c>
       <c r="B31" s="9">
         <f>SUM(B9:B10,B13:B14,B24:B25,B28:B29)</f>
-        <v>3.9958756490529095</v>
+        <v>3.7439374244367283</v>
       </c>
       <c r="C31" s="9">
         <f>SUM(C9:C10,C13:C14,C24:C25,C28:C29)</f>
@@ -1755,11 +2012,11 @@
       </c>
       <c r="D31" s="9">
         <f>SUM(D9:D10,D13:D14,D28:D29,D17:D18)</f>
-        <v>2.4262209184570618</v>
+        <v>3.4115057199063537</v>
       </c>
       <c r="E31" s="9">
         <f>SUM(B31:D31)</f>
-        <v>12.821406200421235</v>
+        <v>13.554752777254345</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -1793,23 +2050,23 @@
       </c>
       <c r="B35" s="9">
         <f>SUM(B9,B13)</f>
-        <v>3.3054688012653242</v>
+        <v>3.0848716917913954</v>
       </c>
       <c r="C35" s="9">
         <f t="shared" ref="C35:D36" si="8">SUM(C9,C13)</f>
-        <v>5.2954301335317311</v>
+        <v>5.3276981151643437</v>
       </c>
       <c r="D35" s="9">
         <f>SUM(D13,D17)</f>
-        <v>1.7154875348810752</v>
+        <v>2.634587430487791</v>
       </c>
       <c r="E35" s="9">
         <f>SUM(B35:D35)</f>
-        <v>10.316386469678131</v>
+        <v>11.04715723744353</v>
       </c>
       <c r="F35">
         <f>E35/E$39</f>
-        <v>0.80533937255364851</v>
+        <v>0.81758574893750713</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -1818,23 +2075,23 @@
       </c>
       <c r="B36" s="9">
         <f>SUM(B10,B14)</f>
-        <v>0.46962119561147359</v>
+        <v>0.43828008046922062</v>
       </c>
       <c r="C36" s="9">
         <f t="shared" si="8"/>
-        <v>0.63618413716919942</v>
+        <v>0.60391615553658629</v>
       </c>
       <c r="D36" s="9">
         <f t="shared" si="8"/>
-        <v>0.10961632484684636</v>
+        <v>0.14439307765358694</v>
       </c>
       <c r="E36" s="10">
         <f>SUM(B36:D36)</f>
-        <v>1.2154216576275192</v>
+        <v>1.1865893136593939</v>
       </c>
       <c r="F36">
         <f>E36/E$39</f>
-        <v>9.488079164335543E-2</v>
+        <v>8.7817932870661489E-2</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -1843,7 +2100,7 @@
       </c>
       <c r="B37" s="9">
         <f>SUM(B24,B28)</f>
-        <v>0.15013424347975618</v>
+        <v>0.15013424347975615</v>
       </c>
       <c r="C37" s="9">
         <f t="shared" ref="C37:D37" si="9">SUM(C24,C28)</f>
@@ -1855,11 +2112,11 @@
       </c>
       <c r="E37" s="9">
         <f>SUM(B37:D37)</f>
-        <v>0.86916127599385318</v>
+        <v>0.86916127599385307</v>
       </c>
       <c r="F37">
         <f>E37/E$39</f>
-        <v>6.7850288346037235E-2</v>
+        <v>6.432549637044542E-2</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -1868,7 +2125,7 @@
       </c>
       <c r="B38" s="9">
         <f>SUM(B25,B29)</f>
-        <v>7.0651408696355833E-2</v>
+        <v>7.0651408696355819E-2</v>
       </c>
       <c r="C38" s="9">
         <f t="shared" ref="C38" si="10">SUM(C25,C29)</f>
@@ -1880,11 +2137,11 @@
       </c>
       <c r="E38" s="9">
         <f t="shared" ref="E38" si="11">SUM(B38:D38)</f>
-        <v>0.40901707105593083</v>
+        <v>0.40901707105593077</v>
       </c>
       <c r="F38">
         <f>E38/E$39</f>
-        <v>3.1929547456958689E-2</v>
+        <v>3.0270821821386074E-2</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -1893,19 +2150,19 @@
       </c>
       <c r="B39" s="9">
         <f>SUM(B35:B38)</f>
-        <v>3.9958756490529099</v>
+        <v>3.7439374244367278</v>
       </c>
       <c r="C39" s="9">
         <f t="shared" ref="C39:D39" si="12">SUM(C35:C38)</f>
-        <v>6.3993096329112635</v>
+        <v>6.3993096329112626</v>
       </c>
       <c r="D39" s="9">
         <f t="shared" si="12"/>
-        <v>2.4148011923912605</v>
+        <v>3.3686778408047169</v>
       </c>
       <c r="E39" s="9">
         <f>SUM(B39:D39)</f>
-        <v>12.809986474355435</v>
+        <v>13.511924898152706</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -1918,7 +2175,7 @@
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="E42">
         <f>E41/E39</f>
-        <v>1.2912781003410319</v>
+        <v>1.2241967835583107</v>
       </c>
     </row>
   </sheetData>
@@ -1955,19 +2212,19 @@
       </c>
       <c r="B2" s="7">
         <f>Validate_2020!B2*Herd_decision_tree!E42</f>
-        <v>10.119823238149138</v>
+        <v>8.5595346951947899</v>
       </c>
       <c r="C2">
         <f>[1]FAO_2019_animal_trends!$G$35/100</f>
-        <v>2.70428359369478E-3</v>
+        <v>3.8312009613345605E-3</v>
       </c>
       <c r="D2">
         <f>B2*C2*30</f>
-        <v>0.82100615862053694</v>
+        <v>0.9837989265842042</v>
       </c>
       <c r="E2">
         <f>B2+D2</f>
-        <v>10.940829396769676</v>
+        <v>9.543333621778995</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -1976,19 +2233,19 @@
       </c>
       <c r="B3" s="7">
         <f>Validate_2020!B3*Herd_decision_tree!E42</f>
-        <v>4.436305119269405</v>
+        <v>5.5401815014894495</v>
       </c>
       <c r="C3">
         <f>[1]FAO_2019_animal_trends!$G36/100</f>
-        <v>2.5359763127554759E-2</v>
+        <v>2.7950424483806725E-2</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:D6" si="0">B3*C3*30</f>
-        <v>3.3751094095869205</v>
+        <v>4.6455127405189147</v>
       </c>
       <c r="E3">
         <f t="shared" ref="E3:E6" si="1">B3+D3</f>
-        <v>7.811414528856325</v>
+        <v>10.185694242008363</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -1997,19 +2254,19 @@
       </c>
       <c r="B4" s="7">
         <f>Validate_2020!B4*Herd_decision_tree!E42</f>
-        <v>0.36374232033257292</v>
+        <v>0.95304019787340866</v>
       </c>
       <c r="C4">
         <f>[1]FAO_2019_animal_trends!$G39/100</f>
-        <v>9.375003453992814E-2</v>
+        <v>7.6101823708206687E-2</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
-        <v>1.0230256528443695</v>
+        <v>2.1758429137618971</v>
       </c>
       <c r="E4">
         <f t="shared" si="1"/>
-        <v>1.3867679731769424</v>
+        <v>3.1288831116353055</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -2018,19 +2275,19 @@
       </c>
       <c r="B5" s="7">
         <f>Validate_2020!B5*Herd_decision_tree!E42</f>
-        <v>1.6072036940442724</v>
+        <v>1.4929364572739967</v>
       </c>
       <c r="C5">
         <f>[1]FAO_2019_animal_trends!$G38/100</f>
-        <v>1.7484802431610946E-2</v>
+        <v>1.0372340425531916E-2</v>
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
-        <v>0.84304917173158167</v>
+        <v>0.46455735505600437</v>
       </c>
       <c r="E5">
         <f t="shared" si="1"/>
-        <v>2.450252865775854</v>
+        <v>1.957493812330001</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -2039,19 +2296,19 @@
       </c>
       <c r="B6" s="7">
         <f>Validate_2020!B6*Herd_decision_tree!E42</f>
-        <v>4.3280013831212702E-2</v>
+        <v>7.1805363998227206E-2</v>
       </c>
       <c r="C6">
         <f>[1]FAO_2019_animal_trends!$G37/100</f>
-        <v>1.1296352583586624</v>
+        <v>0.86466565349544067</v>
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
-        <v>1.4667188881796533</v>
+        <v>1.8626289595801535</v>
       </c>
       <c r="E6">
         <f t="shared" si="1"/>
-        <v>1.509998902010866</v>
+        <v>1.9344343235783807</v>
       </c>
     </row>
   </sheetData>
@@ -2061,26 +2318,50 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95E5D3D0-4020-4418-A256-3E770B560826}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B1">
         <v>2020</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="G1">
+        <v>2050</v>
+      </c>
+      <c r="L1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>57</v>
       </c>
       <c r="C2" t="s">
         <v>58</v>
       </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
       <c r="E2" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J2" t="s">
+        <v>60</v>
+      </c>
+      <c r="M2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -2098,10 +2379,34 @@
       </c>
       <c r="E3">
         <f>Herd_decision_tree!E8*Herd_decision_tree!$E$42</f>
-        <v>10.119823238149138</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>8.5595346951947899</v>
+      </c>
+      <c r="G3">
+        <f>[12]Pastoral_Zebu_2050!$K$2</f>
+        <v>8554757.4814370908</v>
+      </c>
+      <c r="H3">
+        <f>[13]Pastoral_Boran_2050!$K$2</f>
+        <v>1215408.67359516</v>
+      </c>
+      <c r="I3">
+        <f>SUM(G3:H3)/1000000</f>
+        <v>9.7701661550322516</v>
+      </c>
+      <c r="J3">
+        <f>I3/D3</f>
+        <v>1.0811285008243763</v>
+      </c>
+      <c r="L3">
+        <f>E3+E3*30*Validate_2020!G2/100</f>
+        <v>9.5433336217789932</v>
+      </c>
+      <c r="M3">
+        <f>L3/E3</f>
+        <v>1.1149360288400367</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -2119,10 +2424,34 @@
       </c>
       <c r="E4">
         <f>Herd_decision_tree!E12*Herd_decision_tree!$E$42</f>
-        <v>4.436305119269405</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5.5401815014894495</v>
+      </c>
+      <c r="G4">
+        <f>[18]Agpastoral_Zebu_2050!$K$2</f>
+        <v>6488770.1197828101</v>
+      </c>
+      <c r="H4">
+        <f>[14]Agpastoral_Boran_2050!$K$2</f>
+        <v>488402.05019366002</v>
+      </c>
+      <c r="I4">
+        <f t="shared" ref="I4:I7" si="0">SUM(G4:H4)/1000000</f>
+        <v>6.9771721699764697</v>
+      </c>
+      <c r="J4">
+        <f t="shared" ref="J4:J8" si="1">I4/D4</f>
+        <v>1.7607928979202396</v>
+      </c>
+      <c r="L4">
+        <f>E4+E4*30*Validate_2020!G3/100</f>
+        <v>10.185694242008363</v>
+      </c>
+      <c r="M4">
+        <f t="shared" ref="M4:M8" si="2">L4/E4</f>
+        <v>1.8385127345142016</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -2140,10 +2469,34 @@
       </c>
       <c r="E5">
         <f>Herd_decision_tree!E16*Herd_decision_tree!$E$42</f>
-        <v>0.36374232033257292</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.95304019787340866</v>
+      </c>
+      <c r="G5">
+        <f>[19]Mixed_Zebu_2050!$K$2</f>
+        <v>404262.59496554697</v>
+      </c>
+      <c r="H5">
+        <f>[15]Mixed_Boran_2050!$K$2</f>
+        <v>35153.269665965803</v>
+      </c>
+      <c r="I5">
+        <f t="shared" si="0"/>
+        <v>0.43941586463151278</v>
+      </c>
+      <c r="J5">
+        <f t="shared" si="1"/>
+        <v>1.3548822152045585</v>
+      </c>
+      <c r="L5">
+        <f>E5+E5*30*Validate_2020!G4/100</f>
+        <v>1.3403334773726869</v>
+      </c>
+      <c r="M5">
+        <f t="shared" si="2"/>
+        <v>1.4063766464032423</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>45</v>
       </c>
@@ -2156,15 +2509,39 @@
         <v>985977.36353097099</v>
       </c>
       <c r="D6">
-        <f t="shared" ref="D6:D7" si="0">SUM(B6:C6)/1000000</f>
+        <f t="shared" ref="D6:D7" si="3">SUM(B6:C6)/1000000</f>
         <v>2.1707307111981207</v>
       </c>
       <c r="E6">
         <f>Herd_decision_tree!E27*Herd_decision_tree!$E$42</f>
-        <v>1.6072036940442724</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1.4929364572739967</v>
+      </c>
+      <c r="G6">
+        <f>[20]Cowcalf_Boran_2050!$K$2</f>
+        <v>1806208.69891036</v>
+      </c>
+      <c r="H6">
+        <f>[16]Cowcalf_Exotic_2050!$K$2</f>
+        <v>1503165.94333724</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="0"/>
+        <v>3.3093746422476</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="1"/>
+        <v>1.5245440741108842</v>
+      </c>
+      <c r="L6">
+        <f>E6+E6*30*Validate_2020!G5/100</f>
+        <v>1.957493812330001</v>
+      </c>
+      <c r="M6">
+        <f t="shared" si="2"/>
+        <v>1.3111702127659575</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -2177,18 +2554,70 @@
         <v>12386.7653238613</v>
       </c>
       <c r="D7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>3.8708641383861299E-2</v>
       </c>
       <c r="E7">
         <f>Herd_decision_tree!E23*Herd_decision_tree!$E$42</f>
-        <v>4.3280013831212702E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7.1805363998227206E-2</v>
+      </c>
+      <c r="G7">
+        <f>[21]Finisher_Boran_2050!$K$2</f>
+        <v>918345.45531155204</v>
+      </c>
+      <c r="H7">
+        <f>[17]Finisher_Exotic_2050!$K$2</f>
+        <v>432162.57168335503</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="0"/>
+        <v>1.350508026994907</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="1"/>
+        <v>34.889057810175977</v>
+      </c>
+      <c r="L7">
+        <f>E7+E7*30*Validate_2020!G6/100</f>
+        <v>1.9344343235783807</v>
+      </c>
+      <c r="M7">
+        <f>L7/E7</f>
+        <v>26.939969604863222</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="D8">
         <f>SUM(D3:D7)</f>
         <v>15.533284211221597</v>
+      </c>
+      <c r="E8">
+        <f>SUM(E3:E7)</f>
+        <v>16.617498215829873</v>
+      </c>
+      <c r="G8">
+        <f>SUM(G3:G7)</f>
+        <v>18172344.350407358</v>
+      </c>
+      <c r="H8">
+        <f t="shared" ref="H8:I8" si="4">SUM(H3:H7)</f>
+        <v>3674292.5084753809</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="4"/>
+        <v>21.846636858882739</v>
+      </c>
+      <c r="J8">
+        <f>I8/D8</f>
+        <v>1.4064402969656753</v>
+      </c>
+      <c r="L8">
+        <f>SUM(L3:L7)</f>
+        <v>24.961289477068426</v>
+      </c>
+      <c r="M8">
+        <f>L8/E8</f>
+        <v>1.5021087502383623</v>
       </c>
     </row>
   </sheetData>

--- a/Rasterized animal populations/Zonal statistics/Summary.xlsx
+++ b/Rasterized animal populations/Zonal statistics/Summary.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JHawkins\Documents\Github\KE.beef.spatial\Rasterized animal populations\Zonal statistics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C98A1DC-C804-45B9-BE40-B32C1E7CBE2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{666D208B-8782-405F-92BF-76F5B733D13D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{3882C52B-09A6-47D1-94BA-1F6173569800}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="3" xr2:uid="{3882C52B-09A6-47D1-94BA-1F6173569800}"/>
   </bookViews>
   <sheets>
     <sheet name="Validate_2020" sheetId="2" r:id="rId1"/>
     <sheet name="Herd_decision_tree" sheetId="4" r:id="rId2"/>
     <sheet name="Projections" sheetId="3" r:id="rId3"/>
-    <sheet name="ZS_Summary" sheetId="6" r:id="rId4"/>
+    <sheet name="Carrying_Capacity" sheetId="7" r:id="rId4"/>
+    <sheet name="NPP" sheetId="8" r:id="rId5"/>
+    <sheet name="ZS_Summary" sheetId="6" r:id="rId6"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId5"/>
-    <externalReference r:id="rId6"/>
     <externalReference r:id="rId7"/>
     <externalReference r:id="rId8"/>
     <externalReference r:id="rId9"/>
@@ -40,6 +40,57 @@
     <externalReference r:id="rId23"/>
     <externalReference r:id="rId24"/>
     <externalReference r:id="rId25"/>
+    <externalReference r:id="rId26"/>
+    <externalReference r:id="rId27"/>
+    <externalReference r:id="rId28"/>
+    <externalReference r:id="rId29"/>
+    <externalReference r:id="rId30"/>
+    <externalReference r:id="rId31"/>
+    <externalReference r:id="rId32"/>
+    <externalReference r:id="rId33"/>
+    <externalReference r:id="rId34"/>
+    <externalReference r:id="rId35"/>
+    <externalReference r:id="rId36"/>
+    <externalReference r:id="rId37"/>
+    <externalReference r:id="rId38"/>
+    <externalReference r:id="rId39"/>
+    <externalReference r:id="rId40"/>
+    <externalReference r:id="rId41"/>
+    <externalReference r:id="rId42"/>
+    <externalReference r:id="rId43"/>
+    <externalReference r:id="rId44"/>
+    <externalReference r:id="rId45"/>
+    <externalReference r:id="rId46"/>
+    <externalReference r:id="rId47"/>
+    <externalReference r:id="rId48"/>
+    <externalReference r:id="rId49"/>
+    <externalReference r:id="rId50"/>
+    <externalReference r:id="rId51"/>
+    <externalReference r:id="rId52"/>
+    <externalReference r:id="rId53"/>
+    <externalReference r:id="rId54"/>
+    <externalReference r:id="rId55"/>
+    <externalReference r:id="rId56"/>
+    <externalReference r:id="rId57"/>
+    <externalReference r:id="rId58"/>
+    <externalReference r:id="rId59"/>
+    <externalReference r:id="rId60"/>
+    <externalReference r:id="rId61"/>
+    <externalReference r:id="rId62"/>
+    <externalReference r:id="rId63"/>
+    <externalReference r:id="rId64"/>
+    <externalReference r:id="rId65"/>
+    <externalReference r:id="rId66"/>
+    <externalReference r:id="rId67"/>
+    <externalReference r:id="rId68"/>
+    <externalReference r:id="rId69"/>
+    <externalReference r:id="rId70"/>
+    <externalReference r:id="rId71"/>
+    <externalReference r:id="rId72"/>
+    <externalReference r:id="rId73"/>
+    <externalReference r:id="rId74"/>
+    <externalReference r:id="rId75"/>
+    <externalReference r:id="rId76"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -70,7 +121,7 @@
     <author>tc={0B974C83-E393-4D24-9238-9ECDE1F8DB25}</author>
   </authors>
   <commentList>
-    <comment ref="G34" authorId="0" shapeId="0" xr:uid="{0B974C83-E393-4D24-9238-9ECDE1F8DB25}">
+    <comment ref="G41" authorId="0" shapeId="0" xr:uid="{0B974C83-E393-4D24-9238-9ECDE1F8DB25}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -84,13 +135,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="61">
-  <si>
-    <t>Comm</t>
-  </si>
-  <si>
-    <t>Subs</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="95">
   <si>
     <t>Arid</t>
   </si>
@@ -215,9 +260,6 @@
     <t>Frac pastoral to agpastoral - arid</t>
   </si>
   <si>
-    <t>Frac pastoral to agpastoral - semiarid</t>
-  </si>
-  <si>
     <t>Frac mixed to agropastoral - semi arid</t>
   </si>
   <si>
@@ -267,15 +309,130 @@
   </si>
   <si>
     <t>Delta total</t>
+  </si>
+  <si>
+    <t>Semi-arid</t>
+  </si>
+  <si>
+    <t>Humid/subhumid</t>
+  </si>
+  <si>
+    <t>Mean LW -- beef cattle (kg)</t>
+  </si>
+  <si>
+    <t>Dairy</t>
+  </si>
+  <si>
+    <t>Mean LW -- dairy cattle (kg)</t>
+  </si>
+  <si>
+    <t>FRAC Fed</t>
+  </si>
+  <si>
+    <t>FRAC DMI as BW</t>
+  </si>
+  <si>
+    <t>Total weight  - Beef (kg)</t>
+  </si>
+  <si>
+    <t>Total weight  - Dairy (kg)</t>
+  </si>
+  <si>
+    <t>Biomass demand (MT/ha/yr)</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>2050 R4</t>
+  </si>
+  <si>
+    <t>2050 R8</t>
+  </si>
+  <si>
+    <t>Frac pastoral to agpastoral - semiarid &amp; humid</t>
+  </si>
+  <si>
+    <t>NPP - Grassland</t>
+  </si>
+  <si>
+    <t>NPP - Cropland</t>
+  </si>
+  <si>
+    <t>NPP - Shrubland</t>
+  </si>
+  <si>
+    <t>BIOM GRASS Supply (MT/ha/yr)</t>
+  </si>
+  <si>
+    <t>BIOM CROP Supply (MT/ha/yr)</t>
+  </si>
+  <si>
+    <t>BIOM Total (MT/ha/yr)</t>
+  </si>
+  <si>
+    <t>Biomass demand (MT/yr)</t>
+  </si>
+  <si>
+    <t>Biomass supply (MT/yr)</t>
+  </si>
+  <si>
+    <t>Comm beef</t>
+  </si>
+  <si>
+    <t>Subs beef</t>
+  </si>
+  <si>
+    <t>Total beef</t>
+  </si>
+  <si>
+    <t>Carrying capacity (S/D)</t>
+  </si>
+  <si>
+    <t>Sheep</t>
+  </si>
+  <si>
+    <t>Mean LW -- sheep (kg)</t>
+  </si>
+  <si>
+    <t>Total weight - Sheep (kg)</t>
+  </si>
+  <si>
+    <t>2050 - ha/pixel</t>
+  </si>
+  <si>
+    <t>2020 - ha/pixel</t>
+  </si>
+  <si>
+    <t>Simulation average</t>
+  </si>
+  <si>
+    <t>GRASSLAND</t>
+  </si>
+  <si>
+    <t>CROPLAND</t>
+  </si>
+  <si>
+    <t>SHRUBLAND</t>
+  </si>
+  <si>
+    <t>Land areas (ha)</t>
+  </si>
+  <si>
+    <t>NPP (kg C/m2/yr)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="0.00000000"/>
     <numFmt numFmtId="165" formatCode="0.000000000"/>
+    <numFmt numFmtId="166" formatCode="0.0000000"/>
+    <numFmt numFmtId="168" formatCode="0.000"/>
+    <numFmt numFmtId="169" formatCode="0.0000"/>
+    <numFmt numFmtId="170" formatCode="0.00000"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -311,7 +468,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -321,6 +478,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -337,7 +500,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -359,6 +522,20 @@
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -384,12 +561,103 @@
       <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
+      <sheetName val="NPP_2020_GRASS_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.48066728987208701</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink10.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Raster_logic"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="79">
+          <cell r="I79">
+            <v>0.5</v>
+          </cell>
+        </row>
+        <row r="80">
+          <cell r="I80">
+            <v>0.44</v>
+          </cell>
+        </row>
+        <row r="81">
+          <cell r="I81">
+            <v>0.3</v>
+          </cell>
+        </row>
+        <row r="84">
+          <cell r="I84">
+            <v>0.34</v>
+          </cell>
+        </row>
+        <row r="85">
+          <cell r="I85">
+            <v>0.4</v>
+          </cell>
+        </row>
+        <row r="86">
+          <cell r="I86">
+            <v>0.85</v>
+          </cell>
+        </row>
+        <row r="87">
+          <cell r="I87">
+            <v>0.4</v>
+          </cell>
+        </row>
+        <row r="88">
+          <cell r="I88">
+            <v>0.5</v>
+          </cell>
+        </row>
+        <row r="89">
+          <cell r="I89">
+            <v>0.5</v>
+          </cell>
+        </row>
+        <row r="91">
+          <cell r="I91">
+            <v>0.4</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink11.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
       <sheetName val="Model_implemented"/>
       <sheetName val="FAO_2019_animal_trends"/>
       <sheetName val="Raster_logic"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="35">
           <cell r="F35">
@@ -437,13 +705,704 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink10.xml><?xml version="1.0" encoding="utf-8"?>
+      <sheetData sheetId="2" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink12.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Arid_Subsistence"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="C2">
+            <v>220785.65217611199</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="SArid_Subsistence"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="C2">
+            <v>467695.362210333</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Humid_Subsistence"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="D2">
+            <v>589697.33266333945</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Arid_Commercial"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="C2">
+            <v>4580694.9930214901</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink16.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="SArid_Commercial"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="C2">
+            <v>5931614.2707009297</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink17.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Humid_Commercial"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="D2">
+            <v>4968107.5438200859</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink18.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Dairy_total_Arid_2020"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="C2">
+            <v>24812.591756207301</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink19.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Dairy_total_SArid_2020"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="C2">
+            <v>1210306.62197518</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2020_CROP_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.71371978379582002</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink20.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Dairy_total_Humid_2020"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="D2">
+            <v>5233916.3978957208</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink21.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Sheep_total_Arid_2020"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="C2">
+            <v>1300620.48691654</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink22.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Sheep_total_SArid_2020"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="C2">
+            <v>1063972.5190212701</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink23.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Sheep_total_Humid_2020"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="D2">
+            <v>1001433.3524225579</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink24.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Pastoral_Zebu_2020"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>7912803.5780913802</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink25.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Pastoral_Boran_2020"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1">
+        <row r="2">
+          <cell r="K2">
+            <v>1124203.7226895699</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink26.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Pastoral_Zebu_2050"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>8554757.4814370908</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink27.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Pastoral_Boran_2050"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>1215408.67359516</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink28.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Agpastoral_Zebu_2020"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>3685141.0110471202</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink29.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Agpastoral_Boran_2020"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>277376.20390618598</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2020_SHRUB_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.48829216400301401</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink30.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Agpastoral_Zebu_2050"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>6488770.1197828101</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink31.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Agpastoral_Boran_2050"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>488402.05019366002</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink32.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Mixed_Zebu_2020"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>298374.71550379699</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink33.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Mixed_Boran_2020"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>25945.627401560501</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink34.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Mixed_Zebu_2050"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>404262.59496554697</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink35.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Mixed_Boran_2050"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>35153.269665965803</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink36.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Cowcalf_Boran_2020"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>1184753.34766715</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink37.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Cowcalf_Exotic_2020"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>985977.36353097099</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink38.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Cowcalf_Boran_2050"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>1806208.69891036</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink39.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Cowcalf_Exotic_2050"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>1503165.94333724</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R4_GRASS_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.36084903504638699</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink40.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -465,7 +1424,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink41.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -487,117 +1446,29 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink12.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Pastoral_Zebu_2050"/>
+<file path=xl/externalLinks/externalLink42.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Finisher_Boran_2050"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="2">
           <cell r="K2">
-            <v>8554757.4814370908</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Pastoral_Boran_2050"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>1215408.67359516</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Agpastoral_Boran_2050"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>488402.05019366002</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Mixed_Boran_2050"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>35153.269665965803</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink16.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Cowcalf_Exotic_2050"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>1503165.94333724</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink17.xml><?xml version="1.0" encoding="utf-8"?>
+            <v>918345.45531155204</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink43.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -619,174 +1490,389 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink18.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Agpastoral_Zebu_2050"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>6488770.1197828101</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink19.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Mixed_Zebu_2050"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>404262.59496554697</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Pastoral_Zebu_2020"/>
+<file path=xl/externalLinks/externalLink44.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R8_GRASS_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.38423018628503097</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink45.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R8_GRASS_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.54877636996903001</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink46.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R8_CROP_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>1.10532849796393</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink47.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R8_CROP_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.84387264986935995</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink48.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R8_SHRUB_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.23133614051250601</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink49.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R8_SHRUB_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.51992080415758601</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R4_GRASS_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.49669002326856798</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink50.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2020_GRASS_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.33293320629867701</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink51.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2020_CROP_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.97599038751874501</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink52.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2020_SHRUB_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.20100514737984401</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink53.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="ZS_Grassland_Arid"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0" refreshError="1">
         <row r="2">
-          <cell r="K2">
-            <v>7912803.5780913802</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink20.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Cowcalf_Boran_2050"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>1806208.69891036</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink21.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Finisher_Boran_2050"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>918345.45531155204</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Pastoral_Boran_2020"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1">
-        <row r="2">
-          <cell r="K2">
-            <v>1124203.7226895699</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Agpastoral_Zebu_2020"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>3685141.0110471202</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Agpastoral_Boran_2020"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>277376.20390618598</v>
+          <cell r="D2">
+            <v>202419</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink54.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="ZS_Grassland_Humid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>64439.636684333513</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink55.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="ZS_Grassland_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="D2">
+            <v>129806</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink56.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="ZS_Cropland_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="D2">
+            <v>524</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink57.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="ZS_Cropland_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="D2">
+            <v>19552</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink58.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="ZS_Cropland_Humid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>27078.877240262751</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink59.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="ZS_Shrubland_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="D2">
+            <v>277889</v>
           </cell>
         </row>
       </sheetData>
@@ -800,15 +1886,262 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Mixed_Zebu_2020"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>298374.71550379699</v>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R4_CROP_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>1.0384816436740301</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink60.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="ZS_Shrubland_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="D2">
+            <v>357491</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink61.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="ZS_Shrubland_Humid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>63327.68656939434</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink62.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2020_GRASS_Humid"/>
+      <sheetName val="filtered"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="F2">
+            <v>0.88426712592578605</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink63.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2020_CROP_Humid"/>
+      <sheetName val="filtered"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="F2">
+            <v>1.0163977502756547</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink64.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2020_SHRUB_Humid"/>
+      <sheetName val="filtered"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="F2">
+            <v>0.92696223687758272</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink65.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R4_GRASS_Humid"/>
+      <sheetName val="filtered"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="F2">
+            <v>0.84678773914801542</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink66.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R4_CROP_Humid"/>
+      <sheetName val="filtered"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="F2">
+            <v>0.96933124096754675</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink67.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R4_SHRUB_Humid"/>
+      <sheetName val="filtered"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="F2">
+            <v>0.90483097904175391</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink68.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R8_GRASS_Humid"/>
+      <sheetName val="filtered"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="F2">
+            <v>1.006944889838866</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink69.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R8_CROP_Humid"/>
+      <sheetName val="filtered"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="F2">
+            <v>1.1289992284362775</v>
           </cell>
         </row>
       </sheetData>
@@ -822,15 +2155,41 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Mixed_Boran_2020"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>25945.627401560501</v>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R4_CROP_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.72182985434857605</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink70.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R8_SHRUB_Humid"/>
+      <sheetName val="filtered"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="F2">
+            <v>1.0528955612019462</v>
           </cell>
         </row>
       </sheetData>
@@ -844,15 +2203,16 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Cowcalf_Boran_2020"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>1184753.34766715</v>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R4_SHRUB_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.21776707800273001</v>
           </cell>
         </row>
       </sheetData>
@@ -866,15 +2226,16 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Cowcalf_Exotic_2020"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>985977.36353097099</v>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R4_SHRUB_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.51075241024303597</v>
           </cell>
         </row>
       </sheetData>
@@ -1206,7 +2567,7 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="G34" dT="2026-06-15T04:34:52.86" personId="{94C87838-5F63-4687-96E8-E5DFC56D834F}" id="{0B974C83-E393-4D24-9238-9ECDE1F8DB25}">
+  <threadedComment ref="G41" dT="2026-06-15T04:34:52.86" personId="{94C87838-5F63-4687-96E8-E5DFC56D834F}" id="{0B974C83-E393-4D24-9238-9ECDE1F8DB25}">
     <text>https://gemini.google.com/app/cb2f8387004cee95
 Total boran should be 1 to 1.5 M</text>
     <extLst>
@@ -1221,50 +2582,50 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DC88038-24E0-4487-8E9E-ADD8D4CE8257}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="E1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>56</v>
-      </c>
       <c r="G1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B2">
-        <f>Herd_decision_tree!E8</f>
+        <f>Herd_decision_tree!E10</f>
         <v>6.99195979776652</v>
       </c>
       <c r="C2" s="6">
-        <f>B2/$B$7</f>
+        <f>B2/$B$8</f>
         <v>0.51509165724121786</v>
       </c>
       <c r="D2">
-        <f>[1]FAO_2019_animal_trends!$F$35</f>
+        <f>[11]FAO_2019_animal_trends!$F$35</f>
         <v>0.53615960099750615</v>
       </c>
       <c r="E2">
-        <f>D2/D$7</f>
+        <f>D2/D$8</f>
         <v>0.53615960099750626</v>
       </c>
       <c r="F2" s="6">
@@ -1272,7 +2633,7 @@
         <v>0.52629975213940838</v>
       </c>
       <c r="G2">
-        <f>[1]FAO_2019_animal_trends!$G$35</f>
+        <f>[11]FAO_2019_animal_trends!$G$35</f>
         <v>0.38312009613345605</v>
       </c>
       <c r="H2">
@@ -1282,22 +2643,22 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B3">
-        <f>Herd_decision_tree!E12</f>
+        <f>Herd_decision_tree!E14</f>
         <v>4.5255644973891247</v>
       </c>
       <c r="C3" s="6">
-        <f t="shared" ref="C3:C6" si="0">B3/$B$7</f>
+        <f t="shared" ref="C3:C6" si="0">B3/$B$8</f>
         <v>0.33339443937546859</v>
       </c>
       <c r="D3">
-        <f>[1]FAO_2019_animal_trends!$F$36</f>
+        <f>[11]FAO_2019_animal_trends!$F$36</f>
         <v>0.36159600997506236</v>
       </c>
       <c r="E3">
-        <f t="shared" ref="E3:E6" si="1">D3/D$7</f>
+        <f t="shared" ref="E3:E6" si="1">D3/D$8</f>
         <v>0.36159600997506242</v>
       </c>
       <c r="F3" s="6">
@@ -1305,7 +2666,7 @@
         <v>0.31358889061540685</v>
       </c>
       <c r="G3">
-        <f>[1]FAO_2019_animal_trends!$G$36</f>
+        <f>[11]FAO_2019_animal_trends!$G$36</f>
         <v>2.7950424483806726</v>
       </c>
       <c r="H3">
@@ -1315,10 +2676,10 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B4">
-        <f>Herd_decision_tree!E16</f>
+        <f>Herd_decision_tree!E18</f>
         <v>0.7785024521166074</v>
       </c>
       <c r="C4" s="6">
@@ -1326,7 +2687,7 @@
         <v>5.7351605247385556E-2</v>
       </c>
       <c r="D4">
-        <f>[1]FAO_2019_animal_trends!$F$39</f>
+        <f>[11]FAO_2019_animal_trends!$F$39</f>
         <v>4.9875311720698257E-2</v>
       </c>
       <c r="E4">
@@ -1334,32 +2695,32 @@
         <v>4.9875311720698264E-2</v>
       </c>
       <c r="F4" s="6">
-        <f t="shared" ref="F3:F6" si="2">E4-5*G4*E4*0.95/100</f>
+        <f t="shared" ref="F4:F6" si="2">E4-5*G4*E4*0.95/100</f>
         <v>4.6666186084097429E-2</v>
       </c>
       <c r="G4">
-        <f>[1]FAO_2019_animal_trends!$G$40</f>
+        <f>[11]FAO_2019_animal_trends!$G$40</f>
         <v>1.354588821344141</v>
       </c>
       <c r="H4">
-        <f t="shared" ref="H3:H6" si="3">ABS(F4-C4)</f>
+        <f t="shared" ref="H4:H6" si="3">ABS(F4-C4)</f>
         <v>1.0685419163288128E-2</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B5">
-        <f>Herd_decision_tree!E27</f>
-        <v>1.219523264008711</v>
+        <f>Herd_decision_tree!E29</f>
+        <v>0.6916275166390542</v>
       </c>
       <c r="C5" s="6">
         <f t="shared" si="0"/>
-        <v>8.9841228678563756E-2</v>
+        <v>5.0951603562285619E-2</v>
       </c>
       <c r="D5">
-        <f>[1]FAO_2019_animal_trends!$F$38</f>
+        <f>[11]FAO_2019_animal_trends!$F$38</f>
         <v>4.9875311720698257E-2</v>
       </c>
       <c r="E5">
@@ -1371,28 +2732,28 @@
         <v>4.7418024088714393E-2</v>
       </c>
       <c r="G5">
-        <f>[1]FAO_2019_animal_trends!$G$38</f>
+        <f>[11]FAO_2019_animal_trends!$G$38</f>
         <v>1.0372340425531916</v>
       </c>
       <c r="H5">
         <f t="shared" si="3"/>
-        <v>4.2423204589849363E-2</v>
+        <v>3.5335794735712259E-3</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B6">
-        <f>Herd_decision_tree!E23</f>
-        <v>5.8655083041073017E-2</v>
+        <f>Herd_decision_tree!E25</f>
+        <v>0.5865508304107302</v>
       </c>
       <c r="C6" s="6">
         <f t="shared" si="0"/>
-        <v>4.3210694573642397E-3</v>
+        <v>4.3210694573642398E-2</v>
       </c>
       <c r="D6">
-        <f>[1]FAO_2019_animal_trends!$F$37</f>
+        <f>[11]FAO_2019_animal_trends!$F$37</f>
         <v>2.4937655860349127E-3</v>
       </c>
       <c r="E6">
@@ -1404,26 +2765,37 @@
         <v>-7.7485333020033496E-3</v>
       </c>
       <c r="G6">
-        <f>[1]FAO_2019_animal_trends!$G$37</f>
+        <f>[11]FAO_2019_animal_trends!$G$37</f>
         <v>86.466565349544069</v>
       </c>
       <c r="H6">
         <f t="shared" si="3"/>
-        <v>1.2069602759367588E-2</v>
+        <v>5.0959227875645746E-2</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B7">
+      <c r="A7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7">
+        <f>76.3/40</f>
+        <v>1.9075</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B8">
         <f>SUM(B2:B6)</f>
         <v>13.574205094322036</v>
       </c>
-      <c r="D7">
+      <c r="D8">
         <f>SUM(D2:D6)</f>
         <v>0.99999999999999989</v>
       </c>
-      <c r="H7">
+      <c r="H8">
         <f>SUM(H2:H6)</f>
-        <v>9.6191870170757338E-2</v>
+        <v>9.6191870170757365E-2</v>
       </c>
     </row>
   </sheetData>
@@ -1433,11 +2805,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDE56320-BEC2-4269-9329-43A80C09A702}">
-  <dimension ref="A1:K42"/>
+  <dimension ref="A1:K53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.5703125" customWidth="1"/>
-    <col min="2" max="4" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="28.42578125" customWidth="1"/>
     <col min="8" max="8" width="31.7109375" customWidth="1"/>
@@ -1446,70 +2820,71 @@
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="3"/>
       <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="K1" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="B2" s="8">
-        <f>220785.652176112/1000000</f>
+        <f>[12]Arid_Subsistence!$C$2/1000000</f>
         <v>0.22078565217611199</v>
       </c>
       <c r="C2" s="8">
-        <f>467695.362210333/1000000</f>
+        <f>[13]SArid_Subsistence!$C$2/1000000</f>
         <v>0.46769536221033298</v>
       </c>
       <c r="D2" s="8">
-        <f>589697.332663339/1000000</f>
-        <v>0.58969733266333901</v>
+        <f>[14]Humid_Subsistence!$D$2/1000000</f>
+        <v>0.58969733266333946</v>
       </c>
       <c r="E2" s="9">
         <f>SUM(B2:D2)</f>
-        <v>1.2781783470497841</v>
+        <v>1.2781783470497845</v>
       </c>
       <c r="G2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>3.5000000000000001E-3</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="K2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>1</v>
+        <v>81</v>
       </c>
       <c r="B3" s="8">
-        <f>4580694.99302149/1000000</f>
+        <f>[15]Arid_Commercial!$C$2/1000000</f>
         <v>4.5806949930214902</v>
       </c>
       <c r="C3" s="8">
-        <f>5931614.27070093/1000000</f>
+        <f>[16]SArid_Commercial!$C$2/1000000</f>
         <v>5.9316142707009298</v>
       </c>
       <c r="D3" s="8">
+        <f>[17]Humid_Commercial!$D$2/1000000</f>
         <v>4.9681075438200857</v>
       </c>
       <c r="E3" s="9">
@@ -1517,326 +2892,337 @@
         <v>15.480416807542506</v>
       </c>
       <c r="H3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I3">
         <v>0.68</v>
       </c>
       <c r="K3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>5</v>
+        <v>61</v>
       </c>
       <c r="B4" s="8">
+        <f>[18]Dairy_total_Arid_2020!$C$2/1000000</f>
+        <v>2.48125917562073E-2</v>
+      </c>
+      <c r="C4" s="8">
+        <f>[19]Dairy_total_SArid_2020!$C$2/1000000</f>
+        <v>1.2103066219751799</v>
+      </c>
+      <c r="D4" s="8">
+        <f>[20]Dairy_total_Humid_2020!$D$2/1000000</f>
+        <v>5.2339163978957206</v>
+      </c>
+      <c r="E4" s="9"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B5" s="8">
+        <f>9.78*0.76*[21]Sheep_total_Arid_2020!$C$2/1000000</f>
+        <v>9.6672519551532563</v>
+      </c>
+      <c r="C5" s="8">
+        <f>9.78*0.76*[22]Sheep_total_SArid_2020!$C$2/1000000</f>
+        <v>7.908294939381296</v>
+      </c>
+      <c r="D5" s="8">
+        <f>9.78*0.76*[23]Sheep_total_Humid_2020!$D$2/1000000</f>
+        <v>7.4434538218863873</v>
+      </c>
+      <c r="E5" s="9">
+        <f>SUM(B5:D5)</f>
+        <v>25.01900071642094</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B6" s="8">
         <f>SUM(B2:B3)</f>
         <v>4.8014806451976018</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C6" s="8">
         <f>SUM(C2:C3)</f>
         <v>6.3993096329112626</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D6" s="8">
         <f>SUM(D2:D3)</f>
-        <v>5.5578048764834245</v>
-      </c>
-      <c r="E4" s="9">
-        <f>SUM(B4:D4)</f>
-        <v>16.758595154592289</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="G5" t="s">
-        <v>38</v>
-      </c>
-      <c r="H5" t="s">
-        <v>42</v>
-      </c>
-      <c r="I5" s="6">
-        <f>0.7391304+0.03</f>
-        <v>0.76913039999999999</v>
-      </c>
-      <c r="K5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="H6" t="s">
-        <v>43</v>
-      </c>
-      <c r="I6" s="6">
-        <f>0.5348+0.05</f>
-        <v>0.5848000000000001</v>
-      </c>
-      <c r="K6" t="s">
-        <v>41</v>
+        <v>5.5578048764834254</v>
+      </c>
+      <c r="E6" s="9">
+        <f>SUM(B6:D6)</f>
+        <v>16.758595154592292</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>10</v>
-      </c>
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
+      <c r="G7" t="s">
+        <v>36</v>
+      </c>
       <c r="H7" t="s">
-        <v>44</v>
-      </c>
-      <c r="I7">
+        <v>40</v>
+      </c>
+      <c r="I7" s="6">
+        <f>0.7391304+0.03</f>
+        <v>0.76913039999999999</v>
+      </c>
+      <c r="K7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="H8" t="s">
+        <v>71</v>
+      </c>
+      <c r="I8" s="6">
+        <f>0.5348+0.05</f>
+        <v>0.5848000000000001</v>
+      </c>
+      <c r="K8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="H9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I9">
         <f>0.0567+0.1</f>
         <v>0.15670000000000001</v>
       </c>
-      <c r="K7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="9">
-        <f>B3*I5</f>
+      <c r="K9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="9">
+        <f>B3*I7</f>
         <v>3.5231517722606158</v>
       </c>
-      <c r="C8" s="9">
-        <f>C3*I6</f>
+      <c r="C10" s="9">
+        <f>C3*I8</f>
         <v>3.4688080255059042</v>
       </c>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9">
-        <f t="shared" ref="E8:E18" si="0">SUM(B8:D8)</f>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9">
+        <f t="shared" ref="E10:E20" si="0">SUM(B10:D10)</f>
         <v>6.99195979776652</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="9">
-        <f>B8*(1-I9)</f>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="9">
+        <f>B10*(1-I11)</f>
         <v>3.0848716917913954</v>
       </c>
-      <c r="C9" s="9">
-        <f>C8*(1-I9)</f>
+      <c r="C11" s="9">
+        <f>C10*(1-I11)</f>
         <v>3.0372883071329699</v>
       </c>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9">
+      <c r="D11" s="9"/>
+      <c r="E11" s="9">
         <f t="shared" si="0"/>
         <v>6.1221599989243654</v>
       </c>
-      <c r="G9" t="s">
-        <v>50</v>
-      </c>
-      <c r="H9" t="s">
-        <v>11</v>
-      </c>
-      <c r="I9">
+      <c r="G11" t="s">
+        <v>47</v>
+      </c>
+      <c r="H11" t="s">
+        <v>9</v>
+      </c>
+      <c r="I11">
         <f>(0.1244)</f>
         <v>0.1244</v>
       </c>
-      <c r="K9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="9">
-        <f>B8*(I9)</f>
+      <c r="K11" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="9">
+        <f>B10*(I11)</f>
         <v>0.43828008046922062</v>
       </c>
-      <c r="C10" s="9">
-        <f>C8*(I9)</f>
+      <c r="C12" s="9">
+        <f>C10*(I11)</f>
         <v>0.43151971837293446</v>
       </c>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9">
+      <c r="D12" s="9"/>
+      <c r="E12" s="9">
         <f t="shared" si="0"/>
         <v>0.86979979884215508</v>
       </c>
-      <c r="H10" t="s">
-        <v>12</v>
-      </c>
-      <c r="I10">
+      <c r="H12" t="s">
+        <v>10</v>
+      </c>
+      <c r="I12">
         <f>(0.07)</f>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="K10" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="H11" t="s">
-        <v>14</v>
-      </c>
-      <c r="I11">
+      <c r="K12" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="H13" t="s">
+        <v>12</v>
+      </c>
+      <c r="I13">
         <f>(0.08)</f>
         <v>0.08</v>
       </c>
-      <c r="K11" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9">
-        <f>C3*(1-I6)</f>
+      <c r="K13" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9">
+        <f>C3*(1-I8)</f>
         <v>2.4628062451950257</v>
       </c>
-      <c r="D12" s="9">
-        <f>D3*(1-I6)</f>
+      <c r="D14" s="9">
+        <f>D3*(1-I8)</f>
         <v>2.062758252194099</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E14" s="9">
         <f t="shared" si="0"/>
         <v>4.5255644973891247</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9">
-        <f>C12*(1-I10)</f>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9">
+        <f>C14*(1-I12)</f>
         <v>2.2904098080313737</v>
       </c>
-      <c r="D13" s="9">
-        <f>D12*(1-I10)</f>
+      <c r="D15" s="9">
+        <f>D14*(1-I12)</f>
         <v>1.9183651745405119</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E15" s="9">
         <f t="shared" si="0"/>
         <v>4.2087749825718852</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9">
-        <f>C12*(I10)</f>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9">
+        <f>C14*(I12)</f>
         <v>0.1723964371636518</v>
       </c>
-      <c r="D14" s="9">
-        <f>D12*(I10)</f>
+      <c r="D16" s="9">
+        <f>D14*(I12)</f>
         <v>0.14439307765358694</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E16" s="9">
         <f t="shared" si="0"/>
         <v>0.31678951481723872</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9">
-        <f>D3*I7</f>
-        <v>0.7785024521166074</v>
-      </c>
-      <c r="E16" s="9">
-        <f t="shared" si="0"/>
-        <v>0.7785024521166074</v>
-      </c>
-    </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>21</v>
-      </c>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
-      <c r="D17" s="9">
-        <f>D$16*(1-I11)</f>
-        <v>0.71622225594727884</v>
-      </c>
-      <c r="E17" s="9">
-        <f t="shared" si="0"/>
-        <v>0.71622225594727884</v>
-      </c>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
       <c r="D18" s="9">
-        <f>D$16*(I11)</f>
-        <v>6.2280196169328596E-2</v>
+        <f>D3*I9</f>
+        <v>0.7785024521166074</v>
       </c>
       <c r="E18" s="9">
         <f t="shared" si="0"/>
-        <v>6.2280196169328596E-2</v>
+        <v>0.7785024521166074</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>19</v>
+      </c>
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
+      <c r="D19" s="9">
+        <f>D$18*(1-I13)</f>
+        <v>0.71622225594727884</v>
+      </c>
+      <c r="E19" s="9">
+        <f t="shared" si="0"/>
+        <v>0.71622225594727884</v>
+      </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
+      <c r="D20" s="9">
+        <f>D$18*(I13)</f>
+        <v>6.2280196169328596E-2</v>
+      </c>
+      <c r="E20" s="9">
+        <f t="shared" si="0"/>
+        <v>6.2280196169328596E-2</v>
+      </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B21" s="9">
-        <f>SUM(B13:B14)+SUM(B9:B10)</f>
-        <v>3.5231517722606158</v>
-      </c>
-      <c r="C21" s="9">
-        <f>SUM(C13:C14)+SUM(C9:C10)</f>
-        <v>5.9316142707009298</v>
-      </c>
-      <c r="D21" s="9">
-        <f>SUM(D13:D14)+SUM(D17:D18)</f>
-        <v>2.8412607043107063</v>
-      </c>
-      <c r="E21" s="9">
-        <f>SUM(B21:D21)</f>
-        <v>12.296026747272251</v>
-      </c>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="3"/>
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
@@ -1844,338 +3230,443 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B23" s="9">
-        <f>B4*$I2</f>
-        <v>1.6805182258191605E-2</v>
+        <f>SUM(B15:B16)+SUM(B11:B12)</f>
+        <v>3.5231517722606158</v>
       </c>
       <c r="C23" s="9">
-        <f t="shared" ref="C23:D23" si="1">C4*$I2</f>
-        <v>2.239758371518942E-2</v>
+        <f>SUM(C15:C16)+SUM(C11:C12)</f>
+        <v>5.9316142707009298</v>
       </c>
       <c r="D23" s="9">
-        <f t="shared" si="1"/>
-        <v>1.9452317067691988E-2</v>
+        <f>SUM(D15:D16)+SUM(D19:D20)</f>
+        <v>2.8412607043107063</v>
       </c>
       <c r="E23" s="9">
         <f>SUM(B23:D23)</f>
-        <v>5.8655083041073017E-2</v>
+        <v>12.296026747272251</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B24" s="9">
-        <f>B23*$I3</f>
-        <v>1.1427523935570293E-2</v>
-      </c>
-      <c r="C24" s="9">
-        <f t="shared" ref="C24:D24" si="2">C23*$I3</f>
-        <v>1.5230356926328808E-2</v>
-      </c>
-      <c r="D24" s="9">
-        <f t="shared" si="2"/>
-        <v>1.3227575606030552E-2</v>
-      </c>
-      <c r="E24" s="9">
-        <f>SUM(B24:D24)</f>
-        <v>3.9885456467929653E-2</v>
-      </c>
-      <c r="G24">
-        <f>E24*E42</f>
-        <v>4.8827647518794502E-2</v>
-      </c>
+      <c r="A24" s="3"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B25" s="9">
-        <f>B23*(1-$I3)</f>
-        <v>5.3776583226213129E-3</v>
+        <f>B6*$I2</f>
+        <v>0.16805182258191609</v>
       </c>
       <c r="C25" s="9">
-        <f t="shared" ref="C25:D25" si="3">C23*(1-$I3)</f>
-        <v>7.1672267888606136E-3</v>
+        <f t="shared" ref="C25:D25" si="1">C6*$I2</f>
+        <v>0.2239758371518942</v>
       </c>
       <c r="D25" s="9">
-        <f t="shared" si="3"/>
-        <v>6.2247414616614354E-3</v>
+        <f t="shared" si="1"/>
+        <v>0.1945231706769199</v>
       </c>
       <c r="E25" s="9">
-        <f t="shared" ref="E25:E29" si="4">SUM(B25:D25)</f>
-        <v>1.8769626573143364E-2</v>
-      </c>
-      <c r="G25">
-        <f>E25*1.21</f>
-        <v>2.271124815350347E-2</v>
+        <f>SUM(B25:D25)</f>
+        <v>0.5865508304107302</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="3"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
+      <c r="A26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="9">
+        <f>B25*$I3</f>
+        <v>0.11427523935570295</v>
+      </c>
+      <c r="C26" s="9">
+        <f t="shared" ref="C26:D26" si="2">C25*$I3</f>
+        <v>0.15230356926328806</v>
+      </c>
+      <c r="D26" s="9">
+        <f t="shared" si="2"/>
+        <v>0.13227575606030553</v>
+      </c>
+      <c r="E26" s="9">
+        <f>SUM(B26:D26)</f>
+        <v>0.39885456467929659</v>
+      </c>
+      <c r="G26">
+        <f>E26*E49</f>
+        <v>0.48827647518794509</v>
+      </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B27" s="9">
-        <f>B2-B23</f>
-        <v>0.20398046991792038</v>
+        <f>B25*(1-$I3)</f>
+        <v>5.3776583226213141E-2</v>
       </c>
       <c r="C27" s="9">
-        <f t="shared" ref="C27:D27" si="5">C2-C23</f>
-        <v>0.44529777849514357</v>
+        <f t="shared" ref="C27:D27" si="3">C25*(1-$I3)</f>
+        <v>7.1672267888606131E-2</v>
       </c>
       <c r="D27" s="9">
-        <f t="shared" si="5"/>
-        <v>0.570245015595647</v>
+        <f t="shared" si="3"/>
+        <v>6.2247414616614358E-2</v>
       </c>
       <c r="E27" s="9">
-        <f t="shared" si="4"/>
-        <v>1.219523264008711</v>
+        <f t="shared" ref="E27:E31" si="4">SUM(B27:D27)</f>
+        <v>0.18769626573143361</v>
       </c>
       <c r="G27">
-        <f>22*1.21</f>
-        <v>26.619999999999997</v>
+        <f>E27*1.21</f>
+        <v>0.22711248153503466</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B28" s="9">
-        <f>B27*($I3)</f>
-        <v>0.13870671954418587</v>
-      </c>
-      <c r="C28" s="9">
-        <f t="shared" ref="C28" si="6">C27*($I3)</f>
-        <v>0.30280248937669763</v>
-      </c>
-      <c r="D28" s="9">
-        <f>D27*($I3)</f>
-        <v>0.38776661060503997</v>
-      </c>
-      <c r="E28" s="9">
-        <f t="shared" si="4"/>
-        <v>0.82927581952592355</v>
-      </c>
-      <c r="G28">
-        <f>E28*1.21</f>
-        <v>1.0034237416263674</v>
-      </c>
+      <c r="A28" s="3"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B29" s="9">
-        <f>B27*(1-$I3)</f>
-        <v>6.5273750373734507E-2</v>
+        <f>B2-B25</f>
+        <v>5.2733829594195897E-2</v>
       </c>
       <c r="C29" s="9">
-        <f t="shared" ref="C29:D29" si="7">C27*(1-$I3)</f>
-        <v>0.14249528911844592</v>
+        <f t="shared" ref="C29:D29" si="5">C2-C25</f>
+        <v>0.24371952505843877</v>
       </c>
       <c r="D29" s="9">
-        <f t="shared" si="7"/>
-        <v>0.18247840499060702</v>
+        <f t="shared" si="5"/>
+        <v>0.39517416198641953</v>
       </c>
       <c r="E29" s="9">
         <f t="shared" si="4"/>
-        <v>0.39024744448278748</v>
+        <v>0.6916275166390542</v>
+      </c>
+      <c r="G29">
+        <f>22*E49</f>
+        <v>26.932329238282836</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="3"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
+      <c r="A30" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B30" s="9">
+        <f>B29*($I3)</f>
+        <v>3.5859004124053212E-2</v>
+      </c>
+      <c r="C30" s="9">
+        <f t="shared" ref="C30" si="6">C29*($I3)</f>
+        <v>0.16572927703973839</v>
+      </c>
+      <c r="D30" s="9">
+        <f>D29*($I3)</f>
+        <v>0.2687184301507653</v>
+      </c>
+      <c r="E30" s="9">
+        <f t="shared" si="4"/>
+        <v>0.47030671131455692</v>
+      </c>
+      <c r="G30">
+        <f>E30*E49</f>
+        <v>0.5757479632771676</v>
+      </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B31" s="9">
-        <f>SUM(B9:B10,B13:B14,B24:B25,B28:B29)</f>
-        <v>3.7439374244367283</v>
+        <f>B29*(1-$I3)</f>
+        <v>1.6874825470142685E-2</v>
       </c>
       <c r="C31" s="9">
-        <f>SUM(C9:C10,C13:C14,C24:C25,C28:C29)</f>
-        <v>6.3993096329112626</v>
+        <f t="shared" ref="C31:D31" si="7">C29*(1-$I3)</f>
+        <v>7.79902480187004E-2</v>
       </c>
       <c r="D31" s="9">
-        <f>SUM(D9:D10,D13:D14,D28:D29,D17:D18)</f>
-        <v>3.4115057199063537</v>
+        <f t="shared" si="7"/>
+        <v>0.12645573183565423</v>
       </c>
       <c r="E31" s="9">
-        <f>SUM(B31:D31)</f>
-        <v>13.554752777254345</v>
+        <f t="shared" si="4"/>
+        <v>0.22132080532449733</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="3"/>
       <c r="B32" s="9"/>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
+      <c r="A33" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B33" s="9">
+        <f>SUM(B11:B12,B15:B16,B26:B27,B30:B31)</f>
+        <v>3.7439374244367278</v>
+      </c>
+      <c r="C33" s="9">
+        <f>SUM(C11:C12,C15:C16,C26:C27,C30:C31)</f>
+        <v>6.3993096329112626</v>
+      </c>
+      <c r="D33" s="9">
+        <f>SUM(D11:D12,D15:D16,D30:D31,D19:D20)</f>
+        <v>3.2364348662971261</v>
+      </c>
+      <c r="E33" s="9">
+        <f>SUM(B33:D33)</f>
+        <v>13.379681923645116</v>
+      </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
-        <v>33</v>
-      </c>
+      <c r="A34" s="3"/>
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
-      <c r="G34" s="3"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="B35" s="9">
-        <f>SUM(B9,B13)</f>
+        <f>B4</f>
+        <v>2.48125917562073E-2</v>
+      </c>
+      <c r="C35" s="9">
+        <f t="shared" ref="C35:D35" si="8">C4</f>
+        <v>1.2103066219751799</v>
+      </c>
+      <c r="D35" s="9">
+        <f t="shared" si="8"/>
+        <v>5.2339163978957206</v>
+      </c>
+      <c r="E35" s="9">
+        <f t="shared" ref="E35" si="9">SUM(B35:D35)</f>
+        <v>6.4690356116271079</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="3"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="3"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="3"/>
+      <c r="B38" s="9"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="9"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B39" s="9"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="9"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B40" s="9"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="9"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B41" s="9"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="9"/>
+      <c r="G41" s="3"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B42" s="9">
+        <f>SUM(B11,B15)</f>
         <v>3.0848716917913954</v>
       </c>
-      <c r="C35" s="9">
-        <f t="shared" ref="C35:D36" si="8">SUM(C9,C13)</f>
+      <c r="C42" s="9">
+        <f>SUM(C11,C15)</f>
         <v>5.3276981151643437</v>
       </c>
-      <c r="D35" s="9">
-        <f>SUM(D13,D17)</f>
+      <c r="D42" s="9">
+        <f>SUM(D15,D19)</f>
         <v>2.634587430487791</v>
       </c>
-      <c r="E35" s="9">
-        <f>SUM(B35:D35)</f>
+      <c r="E42" s="9">
+        <f>SUM(B42:D42)</f>
         <v>11.04715723744353</v>
       </c>
-      <c r="F35">
-        <f>E35/E$39</f>
+      <c r="F42">
+        <f>E42/E$46</f>
         <v>0.81758574893750713</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B36" s="9">
-        <f>SUM(B10,B14)</f>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B43" s="9">
+        <f>SUM(B12,B16)</f>
         <v>0.43828008046922062</v>
       </c>
-      <c r="C36" s="9">
-        <f t="shared" si="8"/>
+      <c r="C43" s="9">
+        <f>SUM(C12,C16)</f>
         <v>0.60391615553658629</v>
       </c>
-      <c r="D36" s="9">
-        <f t="shared" si="8"/>
+      <c r="D43" s="9">
+        <f>SUM(D12,D16)</f>
         <v>0.14439307765358694</v>
       </c>
-      <c r="E36" s="10">
-        <f>SUM(B36:D36)</f>
+      <c r="E43" s="10">
+        <f>SUM(B43:D43)</f>
         <v>1.1865893136593939</v>
       </c>
-      <c r="F36">
-        <f>E36/E$39</f>
+      <c r="F43">
+        <f>E43/E$46</f>
         <v>8.7817932870661489E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B37" s="9">
-        <f>SUM(B24,B28)</f>
-        <v>0.15013424347975615</v>
-      </c>
-      <c r="C37" s="9">
-        <f t="shared" ref="C37:D37" si="9">SUM(C24,C28)</f>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B44" s="9">
+        <f>SUM(B26,B30)</f>
+        <v>0.15013424347975618</v>
+      </c>
+      <c r="C44" s="9">
+        <f t="shared" ref="C44:D44" si="10">SUM(C26,C30)</f>
         <v>0.31803284630302642</v>
       </c>
-      <c r="D37" s="9">
-        <f t="shared" si="9"/>
-        <v>0.40099418621107052</v>
-      </c>
-      <c r="E37" s="9">
-        <f>SUM(B37:D37)</f>
-        <v>0.86916127599385307</v>
-      </c>
-      <c r="F37">
-        <f>E37/E$39</f>
-        <v>6.432549637044542E-2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B38" s="9">
-        <f>SUM(B25,B29)</f>
-        <v>7.0651408696355819E-2</v>
-      </c>
-      <c r="C38" s="9">
-        <f t="shared" ref="C38" si="10">SUM(C25,C29)</f>
+      <c r="D44" s="9">
+        <f t="shared" si="10"/>
+        <v>0.40099418621107086</v>
+      </c>
+      <c r="E44" s="9">
+        <f>SUM(B44:D44)</f>
+        <v>0.8691612759938534</v>
+      </c>
+      <c r="F44">
+        <f>E44/E$46</f>
+        <v>6.4325496370445448E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B45" s="9">
+        <f>SUM(B27,B31)</f>
+        <v>7.0651408696355833E-2</v>
+      </c>
+      <c r="C45" s="9">
+        <f t="shared" ref="C45" si="11">SUM(C27,C31)</f>
         <v>0.14966251590730653</v>
       </c>
-      <c r="D38" s="9">
-        <f>SUM(D25,D29)</f>
-        <v>0.18870314645226846</v>
-      </c>
-      <c r="E38" s="9">
-        <f t="shared" ref="E38" si="11">SUM(B38:D38)</f>
-        <v>0.40901707105593077</v>
-      </c>
-      <c r="F38">
-        <f>E38/E$39</f>
-        <v>3.0270821821386074E-2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B39" s="9">
-        <f>SUM(B35:B38)</f>
+      <c r="D45" s="9">
+        <f>SUM(D27,D31)</f>
+        <v>0.1887031464522686</v>
+      </c>
+      <c r="E45" s="9">
+        <f t="shared" ref="E45" si="12">SUM(B45:D45)</f>
+        <v>0.40901707105593099</v>
+      </c>
+      <c r="F45">
+        <f>E45/E$46</f>
+        <v>3.0270821821386091E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B46" s="9">
+        <f>SUM(B42:B45)</f>
         <v>3.7439374244367278</v>
       </c>
-      <c r="C39" s="9">
-        <f t="shared" ref="C39:D39" si="12">SUM(C35:C38)</f>
+      <c r="C46" s="9">
+        <f t="shared" ref="C46:D46" si="13">SUM(C42:C45)</f>
         <v>6.3993096329112626</v>
       </c>
-      <c r="D39" s="9">
-        <f t="shared" si="12"/>
-        <v>3.3686778408047169</v>
-      </c>
-      <c r="E39" s="9">
-        <f>SUM(B39:D39)</f>
+      <c r="D46" s="9">
+        <f t="shared" si="13"/>
+        <v>3.3686778408047173</v>
+      </c>
+      <c r="E46" s="9">
+        <f>SUM(B46:D46)</f>
         <v>13.511924898152706</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="4"/>
-      <c r="E41">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="4"/>
+      <c r="E48">
         <f>16.541255</f>
         <v>16.541255</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E42">
-        <f>E41/E39</f>
+    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E49">
+        <f>E48/E46</f>
         <v>1.2241967835583107</v>
+      </c>
+    </row>
+    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B52">
+        <f>B29/B2</f>
+        <v>0.23884627046386242</v>
+      </c>
+      <c r="C52">
+        <f t="shared" ref="C52:D52" si="14">C29/C2</f>
+        <v>0.52110742323083525</v>
+      </c>
+      <c r="D52">
+        <f t="shared" si="14"/>
+        <v>0.67013048914709272</v>
+      </c>
+    </row>
+    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B53">
+        <f>B25/B2</f>
+        <v>0.76115372953613758</v>
+      </c>
+      <c r="C53">
+        <f t="shared" ref="C53:D53" si="15">C25/C2</f>
+        <v>0.47889257676916475</v>
+      </c>
+      <c r="D53">
+        <f t="shared" si="15"/>
+        <v>0.32986951085290722</v>
       </c>
     </row>
   </sheetData>
@@ -2186,7 +3677,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD6A4001-CB5D-4E56-8C0D-2957A97A30B1}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="16.140625" customWidth="1"/>
@@ -2197,10 +3688,10 @@
         <v>2020</v>
       </c>
       <c r="C1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E1">
         <v>2050</v>
@@ -2208,14 +3699,14 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B2" s="7">
-        <f>Validate_2020!B2*Herd_decision_tree!E42</f>
+        <f>Validate_2020!B2*Herd_decision_tree!E49</f>
         <v>8.5595346951947899</v>
       </c>
       <c r="C2">
-        <f>[1]FAO_2019_animal_trends!$G$35/100</f>
+        <f>[11]FAO_2019_animal_trends!$G$35/100</f>
         <v>3.8312009613345605E-3</v>
       </c>
       <c r="D2">
@@ -2229,35 +3720,35 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B3" s="7">
-        <f>Validate_2020!B3*Herd_decision_tree!E42</f>
+        <f>Validate_2020!B3*Herd_decision_tree!E49</f>
         <v>5.5401815014894495</v>
       </c>
       <c r="C3">
-        <f>[1]FAO_2019_animal_trends!$G36/100</f>
+        <f>[11]FAO_2019_animal_trends!$G36/100</f>
         <v>2.7950424483806725E-2</v>
       </c>
       <c r="D3">
-        <f t="shared" ref="D3:D6" si="0">B3*C3*30</f>
+        <f t="shared" ref="D3:D7" si="0">B3*C3*30</f>
         <v>4.6455127405189147</v>
       </c>
       <c r="E3">
-        <f t="shared" ref="E3:E6" si="1">B3+D3</f>
+        <f t="shared" ref="E3:E7" si="1">B3+D3</f>
         <v>10.185694242008363</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B4" s="7">
-        <f>Validate_2020!B4*Herd_decision_tree!E42</f>
+        <f>Validate_2020!B4*Herd_decision_tree!E49</f>
         <v>0.95304019787340866</v>
       </c>
       <c r="C4">
-        <f>[1]FAO_2019_animal_trends!$G39/100</f>
+        <f>[11]FAO_2019_animal_trends!$G39/100</f>
         <v>7.6101823708206687E-2</v>
       </c>
       <c r="D4">
@@ -2271,44 +3762,65 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B5" s="7">
-        <f>Validate_2020!B5*Herd_decision_tree!E42</f>
-        <v>1.4929364572739967</v>
+        <f>Validate_2020!B5*Herd_decision_tree!E49</f>
+        <v>0.84668818128995216</v>
       </c>
       <c r="C5">
-        <f>[1]FAO_2019_animal_trends!$G38/100</f>
+        <f>[11]FAO_2019_animal_trends!$G38/100</f>
         <v>1.0372340425531916E-2</v>
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
-        <v>0.46455735505600437</v>
+        <v>0.26346414151841596</v>
       </c>
       <c r="E5">
         <f t="shared" si="1"/>
-        <v>1.957493812330001</v>
+        <v>1.1101523228083681</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B6" s="7">
-        <f>Validate_2020!B6*Herd_decision_tree!E42</f>
-        <v>7.1805363998227206E-2</v>
+        <f>Validate_2020!B6*Herd_decision_tree!E49</f>
+        <v>0.71805363998227212</v>
       </c>
       <c r="C6">
-        <f>[1]FAO_2019_animal_trends!$G37/100</f>
+        <f>[11]FAO_2019_animal_trends!$G37/100</f>
         <v>0.86466565349544067</v>
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
-        <v>1.8626289595801535</v>
+        <v>18.626289595801538</v>
       </c>
       <c r="E6">
         <f t="shared" si="1"/>
-        <v>1.9344343235783807</v>
+        <v>19.344343235783811</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B7">
+        <f>Herd_decision_tree!E35</f>
+        <v>6.4690356116271079</v>
+      </c>
+      <c r="C7">
+        <f>[11]FAO_2019_animal_trends!$G39/100</f>
+        <v>7.6101823708206687E-2</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="0"/>
+        <v>14.769162230344715</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="1"/>
+        <v>21.238197841971825</v>
       </c>
     </row>
   </sheetData>
@@ -2317,6 +3829,1237 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7E0F49F-D7A7-4FDA-92DD-326744451984}">
+  <dimension ref="A1:I49"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17.42578125" customWidth="1"/>
+    <col min="2" max="2" width="27.5703125" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" customWidth="1"/>
+    <col min="5" max="5" width="9.28515625" customWidth="1"/>
+    <col min="6" max="7" width="11.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>2020</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2">
+        <f>Herd_decision_tree!B10</f>
+        <v>3.5231517722606158</v>
+      </c>
+      <c r="D2">
+        <f>Herd_decision_tree!C10</f>
+        <v>3.4688080255059042</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="H2" t="s">
+        <v>62</v>
+      </c>
+      <c r="I2">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <f>Herd_decision_tree!C14</f>
+        <v>2.4628062451950257</v>
+      </c>
+      <c r="E3">
+        <f>Herd_decision_tree!D14</f>
+        <v>2.062758252194099</v>
+      </c>
+      <c r="H3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <f>Herd_decision_tree!D18</f>
+        <v>0.7785024521166074</v>
+      </c>
+      <c r="H4" t="s">
+        <v>63</v>
+      </c>
+      <c r="I4">
+        <f>0.02+0.01</f>
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5">
+        <f>Herd_decision_tree!B29</f>
+        <v>5.2733829594195897E-2</v>
+      </c>
+      <c r="D5">
+        <f>Herd_decision_tree!C29</f>
+        <v>0.24371952505843877</v>
+      </c>
+      <c r="E5">
+        <f>Herd_decision_tree!D29</f>
+        <v>0.39517416198641953</v>
+      </c>
+      <c r="H5" t="s">
+        <v>64</v>
+      </c>
+      <c r="I5">
+        <f>0.025-0.005</f>
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6">
+        <f>Herd_decision_tree!B25</f>
+        <v>0.16805182258191609</v>
+      </c>
+      <c r="D6">
+        <f>Herd_decision_tree!C25</f>
+        <v>0.2239758371518942</v>
+      </c>
+      <c r="E6">
+        <f>Herd_decision_tree!D25</f>
+        <v>0.1945231706769199</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7">
+        <f>Herd_decision_tree!B35</f>
+        <v>2.48125917562073E-2</v>
+      </c>
+      <c r="D7">
+        <f>Herd_decision_tree!C35</f>
+        <v>1.2103066219751799</v>
+      </c>
+      <c r="E7">
+        <f>Herd_decision_tree!D35</f>
+        <v>5.2339163978957206</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>84</v>
+      </c>
+      <c r="C8">
+        <f>Herd_decision_tree!B5</f>
+        <v>9.6672519551532563</v>
+      </c>
+      <c r="D8">
+        <f>Herd_decision_tree!C5</f>
+        <v>7.908294939381296</v>
+      </c>
+      <c r="E8">
+        <f>Herd_decision_tree!D5</f>
+        <v>7.4434538218863873</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C10">
+        <f>SUM(C2:C6)*$I1*1000000</f>
+        <v>636469362.15424371</v>
+      </c>
+      <c r="D10">
+        <f>SUM(D2:D6)*$I1*1000000</f>
+        <v>1087882637.5949147</v>
+      </c>
+      <c r="E10">
+        <f>SUM(E2:E6)*$I1*1000000</f>
+        <v>583262866.28558779</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>66</v>
+      </c>
+      <c r="C11">
+        <f t="shared" ref="C11:E12" si="0">C7*$I$2*1000000</f>
+        <v>4962518.3512414601</v>
+      </c>
+      <c r="D11">
+        <f t="shared" si="0"/>
+        <v>242061324.39503598</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="0"/>
+        <v>1046783279.5791441</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>86</v>
+      </c>
+      <c r="C12">
+        <f>C8*$I$3*1000000</f>
+        <v>338353818.43036395</v>
+      </c>
+      <c r="D12">
+        <f>D8*$I$3*1000000</f>
+        <v>276790322.87834537</v>
+      </c>
+      <c r="E12">
+        <f>E8*$I$3*1000000</f>
+        <v>260520883.76602352</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B14" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C14">
+        <f>365*(C10+C11+C12)*(1-$I4)*($I5)/1000/1000000</f>
+        <v>6.9378625341647489</v>
+      </c>
+      <c r="D14">
+        <f>365*(D10+D11+D12)*(1-$I4)*($I5)/1000/1000000</f>
+        <v>11.377285471152405</v>
+      </c>
+      <c r="E14">
+        <f t="shared" ref="D14:E14" si="1">365*(E10+E11+E12)*(1-$I4)*($I5)/1000/1000000</f>
+        <v>13.387105136815379</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B15" s="1"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B16" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="C16" s="20">
+        <f>NPP!C22</f>
+        <v>10.601301632692286</v>
+      </c>
+      <c r="D16" s="20">
+        <f>NPP!D22</f>
+        <v>17.394244747218586</v>
+      </c>
+      <c r="E16" s="20">
+        <f>NPP!E22</f>
+        <v>13.142933731562785</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B17" s="1"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B18" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="C18" s="6">
+        <f>C16/C14</f>
+        <v>1.528035699826471</v>
+      </c>
+      <c r="D18" s="6">
+        <f t="shared" ref="D18" si="2">D16/D14</f>
+        <v>1.5288571945674072</v>
+      </c>
+      <c r="E18" s="6">
+        <f>E16/E14</f>
+        <v>0.98176070160373152</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B19" s="1"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B21" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21">
+        <f>C2+C2*30*Validate_2020!$G2/100</f>
+        <v>3.9280888459649885</v>
+      </c>
+      <c r="D21">
+        <f>D2+D2*30*Validate_2020!$G2/100</f>
+        <v>3.867499044766002</v>
+      </c>
+      <c r="E21">
+        <f>E2+E2*30*Validate_2020!$G2/100</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22">
+        <f>C3+C3*30*Validate_2020!$G3/100</f>
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <f>D3+D3*30*Validate_2020!$G3/100</f>
+        <v>4.5279006444321599</v>
+      </c>
+      <c r="E22">
+        <f>E3+E3*30*Validate_2020!$G3/100</f>
+        <v>3.7924073148831083</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>59</v>
+      </c>
+      <c r="C23">
+        <f>C4+C4*30*Validate_2020!$G4/100</f>
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <f>D4+D4*30*Validate_2020!$G4/100</f>
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <f>E4+E4*30*Validate_2020!$G4/100</f>
+        <v>1.0948676678244551</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24">
+        <f>C5+C5*30*Validate_2020!$G5/100</f>
+        <v>6.9143026568985577E-2</v>
+      </c>
+      <c r="D24">
+        <f>D5+D5*30*Validate_2020!$G5/100</f>
+        <v>0.31955778152609127</v>
+      </c>
+      <c r="E24">
+        <f>E5+E5*30*Validate_2020!$G5/100</f>
+        <v>0.51814059005134261</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>23</v>
+      </c>
+      <c r="C25">
+        <f>C6+C6*30*Validate_2020!$G6/100</f>
+        <v>4.5273109923986858</v>
+      </c>
+      <c r="D25">
+        <f>D6+D6*30*Validate_2020!$G6/100</f>
+        <v>6.033902245095824</v>
+      </c>
+      <c r="E25">
+        <f>E6+E6*30*Validate_2020!$G6/100</f>
+        <v>5.2404483054778428</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>61</v>
+      </c>
+      <c r="C26">
+        <f>C7+C7*30*Validate_2020!G8/100</f>
+        <v>2.48125917562073E-2</v>
+      </c>
+      <c r="D26">
+        <f>D7+D7*30*Validate_2020!H8/100</f>
+        <v>1.2452331192095332</v>
+      </c>
+      <c r="E26">
+        <f>E7+E7*30*Validate_2020!I8/100</f>
+        <v>5.2339163978957206</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>84</v>
+      </c>
+      <c r="C27">
+        <f>C8+C8*30*Validate_2020!$G7/100</f>
+        <v>15.199336886489707</v>
+      </c>
+      <c r="D27">
+        <f>D8+D8*30*Validate_2020!$G7/100</f>
+        <v>12.433816718442243</v>
+      </c>
+      <c r="E27">
+        <f>E8+E8*30*Validate_2020!$G7/100</f>
+        <v>11.702970271460872</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>65</v>
+      </c>
+      <c r="C30">
+        <f>SUM(C21:C25)*$I1*1000000</f>
+        <v>1449172287.038552</v>
+      </c>
+      <c r="D30">
+        <f t="shared" ref="D30:E30" si="3">SUM(D21:D25)*$I1*1000000</f>
+        <v>2507306151.6894131</v>
+      </c>
+      <c r="E30">
+        <f t="shared" si="3"/>
+        <v>1809796859.3002474</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>66</v>
+      </c>
+      <c r="C31">
+        <f>C26*$I2*1000000</f>
+        <v>4962518.3512414601</v>
+      </c>
+      <c r="D31">
+        <f t="shared" ref="D31:E31" si="4">D26*$I2*1000000</f>
+        <v>249046623.84190664</v>
+      </c>
+      <c r="E31">
+        <f t="shared" si="4"/>
+        <v>1046783279.5791441</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>86</v>
+      </c>
+      <c r="C32">
+        <f>C27*$I3*1000000</f>
+        <v>531976791.02713972</v>
+      </c>
+      <c r="D32">
+        <f t="shared" ref="D32:E32" si="5">D27*$I3*1000000</f>
+        <v>435183585.14547849</v>
+      </c>
+      <c r="E32">
+        <f t="shared" si="5"/>
+        <v>409603959.50113052</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B34" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C34">
+        <f>365*(C30+C31+C32)*(1-$I4)*($I5)/1000/1000000</f>
+        <v>14.063656214228304</v>
+      </c>
+      <c r="D34">
+        <f t="shared" ref="D34:E34" si="6">365*(D30+D31+D32)*(1-$I4)*($I5)/1000/1000000</f>
+        <v>22.599268969952409</v>
+      </c>
+      <c r="E34">
+        <f t="shared" si="6"/>
+        <v>23.127849600632477</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B36" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="C36" s="20">
+        <f>NPP!C26</f>
+        <v>11.487638876032412</v>
+      </c>
+      <c r="D36" s="20">
+        <f>NPP!D26</f>
+        <v>18.036650067492623</v>
+      </c>
+      <c r="E36" s="20">
+        <f>NPP!E26</f>
+        <v>12.622380382884351</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B37" s="1"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B38" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="C38" s="12"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B39" s="18">
+        <v>2050</v>
+      </c>
+      <c r="C39" s="6">
+        <f>C36/C34</f>
+        <v>0.81683160488595297</v>
+      </c>
+      <c r="D39" s="6">
+        <f t="shared" ref="D39:E39" si="7">D36/D34</f>
+        <v>0.79810767735336197</v>
+      </c>
+      <c r="E39" s="6">
+        <f t="shared" si="7"/>
+        <v>0.54576541273163448</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1"/>
+      <c r="B40" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="C40" s="6">
+        <f>(C39+C18)/2</f>
+        <v>1.172433652356212</v>
+      </c>
+      <c r="D40" s="6">
+        <f t="shared" ref="D40:E40" si="8">(D39+D18)/2</f>
+        <v>1.1634824359603846</v>
+      </c>
+      <c r="E40" s="6">
+        <f t="shared" si="8"/>
+        <v>0.763763057167683</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C43">
+        <f>C34</f>
+        <v>14.063656214228304</v>
+      </c>
+      <c r="D43">
+        <f t="shared" ref="D43:E43" si="9">D34</f>
+        <v>22.599268969952409</v>
+      </c>
+      <c r="E43">
+        <f t="shared" si="9"/>
+        <v>23.127849600632477</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B45" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="C45" s="20">
+        <f>NPP!C30</f>
+        <v>12.224887513466063</v>
+      </c>
+      <c r="D45" s="20">
+        <f>NPP!D30</f>
+        <v>19.304782313030003</v>
+      </c>
+      <c r="E45" s="20">
+        <f>NPP!E30</f>
+        <v>14.854997836251982</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B47" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="C47" s="12"/>
+      <c r="D47" s="12"/>
+      <c r="E47" s="12"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B48" s="1">
+        <v>2050</v>
+      </c>
+      <c r="C48">
+        <f>C45/C43</f>
+        <v>0.86925386451768172</v>
+      </c>
+      <c r="D48">
+        <f t="shared" ref="D48:E48" si="10">D45/D43</f>
+        <v>0.85422153870097761</v>
+      </c>
+      <c r="E48">
+        <f t="shared" si="10"/>
+        <v>0.64229913687460782</v>
+      </c>
+    </row>
+    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B49" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C49">
+        <f>(C18+C48)*0.5</f>
+        <v>1.1986447821720763</v>
+      </c>
+      <c r="D49">
+        <f t="shared" ref="D49:E49" si="11">(D18+D48)*0.5</f>
+        <v>1.1915393666341925</v>
+      </c>
+      <c r="E49">
+        <f t="shared" si="11"/>
+        <v>0.81202991923916967</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B47:E47"/>
+    <mergeCell ref="B38:E38"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C89891AA-CE3C-44BE-AF6B-8649852BC25F}">
+  <dimension ref="A1:L30"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17.7109375" customWidth="1"/>
+    <col min="2" max="2" width="32.85546875" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" customWidth="1"/>
+    <col min="6" max="6" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.42578125" customWidth="1"/>
+    <col min="12" max="12" width="9.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C2" s="13">
+        <f>[53]ZS_Grassland_Arid!$D$2*L15</f>
+        <v>8999548.7400000002</v>
+      </c>
+      <c r="D2" s="13">
+        <f>[55]ZS_Grassland_SArid!$D$2*L15</f>
+        <v>5771174.7599999998</v>
+      </c>
+      <c r="E2" s="13">
+        <f>[54]ZS_Grassland_Humid!$E$2*L15</f>
+        <v>2864986.2469854681</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3" s="13">
+        <f>[56]ZS_Cropland_Arid!$D$2*L15</f>
+        <v>23297.040000000001</v>
+      </c>
+      <c r="D3" s="13">
+        <f>[57]ZS_Cropland_SArid!$D$2*L15</f>
+        <v>869281.92</v>
+      </c>
+      <c r="E3" s="13">
+        <f>[58]ZS_Cropland_Humid!$E$2*L15</f>
+        <v>1203926.882102082</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C4" s="13">
+        <f>[59]ZS_Shrubland_Arid!$D$2*L15</f>
+        <v>12354944.939999999</v>
+      </c>
+      <c r="D4" s="13">
+        <f>[60]ZS_Shrubland_SArid!$D$2*L15</f>
+        <v>15894049.859999999</v>
+      </c>
+      <c r="E4" s="13">
+        <f>[61]ZS_Shrubland_Humid!$E$2*L15</f>
+        <v>2815548.9448752725</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B6" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>2020</v>
+      </c>
+      <c r="B7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7" s="16">
+        <f>[50]NPP_2020_GRASS_Arid!$E$2</f>
+        <v>0.33293320629867701</v>
+      </c>
+      <c r="D7" s="16">
+        <f>[1]NPP_2020_GRASS_SArid!$E$2</f>
+        <v>0.48066728987208701</v>
+      </c>
+      <c r="E7" s="15">
+        <f>[62]filtered!$F$2</f>
+        <v>0.88426712592578605</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>73</v>
+      </c>
+      <c r="C8" s="16">
+        <f>[51]NPP_2020_CROP_Arid!$E$2</f>
+        <v>0.97599038751874501</v>
+      </c>
+      <c r="D8" s="16">
+        <f>[2]NPP_2020_CROP_SArid!$E$2</f>
+        <v>0.71371978379582002</v>
+      </c>
+      <c r="E8" s="15">
+        <f>[63]filtered!$F$2</f>
+        <v>1.0163977502756547</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C9" s="16">
+        <f>[52]NPP_2020_SHRUB_Arid!$E$2</f>
+        <v>0.20100514737984401</v>
+      </c>
+      <c r="D9" s="16">
+        <f>[3]NPP_2020_SHRUB_SArid!$E$2</f>
+        <v>0.48829216400301401</v>
+      </c>
+      <c r="E9" s="15">
+        <f>[64]filtered!$F$2</f>
+        <v>0.92696223687758272</v>
+      </c>
+      <c r="L9" s="11"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="L10" s="11"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>69</v>
+      </c>
+      <c r="B11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11" s="16">
+        <f>[4]NPP_2050_R4_GRASS_Arid!$E$2</f>
+        <v>0.36084903504638699</v>
+      </c>
+      <c r="D11" s="16">
+        <f>[5]NPP_2050_R4_GRASS_SArid!$E$2</f>
+        <v>0.49669002326856798</v>
+      </c>
+      <c r="E11" s="16">
+        <f>[65]filtered!$F$2</f>
+        <v>0.84678773914801542</v>
+      </c>
+      <c r="F11">
+        <f>C11/C7</f>
+        <v>1.0838481359611407</v>
+      </c>
+      <c r="G11">
+        <f t="shared" ref="G11:H13" si="0">D11/D7</f>
+        <v>1.0333343535832131</v>
+      </c>
+      <c r="H11">
+        <f t="shared" si="0"/>
+        <v>0.95761531139300071</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C12" s="16">
+        <f>[6]NPP_2050_R4_CROP_Arid!$E$2</f>
+        <v>1.0384816436740301</v>
+      </c>
+      <c r="D12" s="16">
+        <f>[7]NPP_2050_R4_CROP_SArid!$E$2</f>
+        <v>0.72182985434857605</v>
+      </c>
+      <c r="E12" s="16">
+        <f>[66]filtered!$F$2</f>
+        <v>0.96933124096754675</v>
+      </c>
+      <c r="F12">
+        <f t="shared" ref="F12:F13" si="1">C12/C8</f>
+        <v>1.0640285569965051</v>
+      </c>
+      <c r="G12">
+        <f t="shared" si="0"/>
+        <v>1.0113631017899263</v>
+      </c>
+      <c r="H12">
+        <f t="shared" si="0"/>
+        <v>0.95369282419668566</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>74</v>
+      </c>
+      <c r="C13" s="16">
+        <f>[8]NPP_2050_R4_SHRUB_Arid!$E$2</f>
+        <v>0.21776707800273001</v>
+      </c>
+      <c r="D13" s="16">
+        <f>[9]NPP_2050_R4_SHRUB_SArid!$E$2</f>
+        <v>0.51075241024303597</v>
+      </c>
+      <c r="E13" s="16">
+        <f>[67]filtered!$F$2</f>
+        <v>0.90483097904175391</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="1"/>
+        <v>1.083390554129495</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="0"/>
+        <v>1.0459975561677932</v>
+      </c>
+      <c r="H13">
+        <f t="shared" si="0"/>
+        <v>0.97612496285676464</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>70</v>
+      </c>
+      <c r="B15" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" s="16">
+        <f>[44]NPP_2050_R8_GRASS_Arid!$E$2</f>
+        <v>0.38423018628503097</v>
+      </c>
+      <c r="D15" s="16">
+        <f>[45]NPP_2050_R8_GRASS_SArid!$E$2</f>
+        <v>0.54877636996903001</v>
+      </c>
+      <c r="E15" s="16">
+        <f>[68]filtered!$F$2</f>
+        <v>1.006944889838866</v>
+      </c>
+      <c r="F15">
+        <f>C15/C7</f>
+        <v>1.1540758897456898</v>
+      </c>
+      <c r="G15">
+        <f t="shared" ref="G15:H17" si="2">D15/D7</f>
+        <v>1.1416969316032881</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="2"/>
+        <v>1.1387338286319784</v>
+      </c>
+      <c r="K15" t="s">
+        <v>88</v>
+      </c>
+      <c r="L15">
+        <f>44.46</f>
+        <v>44.46</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" s="16">
+        <f>[46]NPP_2050_R8_CROP_Arid!$E$2</f>
+        <v>1.10532849796393</v>
+      </c>
+      <c r="D16" s="16">
+        <f>[47]NPP_2050_R8_CROP_SArid!$E$2</f>
+        <v>0.84387264986935995</v>
+      </c>
+      <c r="E16" s="16">
+        <f>[69]filtered!$F$2</f>
+        <v>1.1289992284362775</v>
+      </c>
+      <c r="F16">
+        <f t="shared" ref="F16:F17" si="3">C16/C8</f>
+        <v>1.1325198609527298</v>
+      </c>
+      <c r="G16">
+        <f t="shared" si="2"/>
+        <v>1.1823584956288304</v>
+      </c>
+      <c r="H16">
+        <f t="shared" si="2"/>
+        <v>1.110784855761521</v>
+      </c>
+      <c r="K16" t="s">
+        <v>87</v>
+      </c>
+      <c r="L16">
+        <f>L15</f>
+        <v>44.46</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>74</v>
+      </c>
+      <c r="C17" s="16">
+        <f>[48]NPP_2050_R8_SHRUB_Arid!$E$2</f>
+        <v>0.23133614051250601</v>
+      </c>
+      <c r="D17" s="16">
+        <f>[49]NPP_2050_R8_SHRUB_SArid!$E$2</f>
+        <v>0.51992080415758601</v>
+      </c>
+      <c r="E17" s="16">
+        <f>[70]filtered!$F$2</f>
+        <v>1.0528955612019462</v>
+      </c>
+      <c r="F17">
+        <f t="shared" si="3"/>
+        <v>1.15089659905746</v>
+      </c>
+      <c r="G17">
+        <f t="shared" si="2"/>
+        <v>1.0647740072158454</v>
+      </c>
+      <c r="H17">
+        <f t="shared" si="2"/>
+        <v>1.1358559381540314</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="17">
+        <v>2020</v>
+      </c>
+      <c r="B20" t="s">
+        <v>75</v>
+      </c>
+      <c r="C20">
+        <f>10000*(1/1000)*(C2*C7+C3*C8*[10]Raster_logic!$I$84+C4*C9*[10]Raster_logic!$I$85)*(1/[10]Raster_logic!$I$79)*[10]Raster_logic!$I$80*[10]Raster_logic!$I$81/1000000</f>
+        <v>10.552984047609801</v>
+      </c>
+      <c r="D20">
+        <f>10000*(1/1000)*(D2*D7+D3*D8*[10]Raster_logic!$I$84+D4*D9*[10]Raster_logic!$I$85)*(1/[10]Raster_logic!$I$79)*[10]Raster_logic!$I$80*[10]Raster_logic!$I$81/1000000</f>
+        <v>16.075844376218555</v>
+      </c>
+      <c r="E20">
+        <f>10000*(1/1000)*(E2*E7+E3*E8*[10]Raster_logic!$I$84+E4*E9*[10]Raster_logic!$I$85)*(1/[10]Raster_logic!$I$79)*[10]Raster_logic!$I$80*[10]Raster_logic!$I$81/1000000</f>
+        <v>10.542638010824788</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>76</v>
+      </c>
+      <c r="C21">
+        <f>10000*(1/1000)*(C3*C8*[10]Raster_logic!$I$91)*(1/[10]Raster_logic!$I$87)*[10]Raster_logic!$I$88*[10]Raster_logic!$I$89*[10]Raster_logic!$I$86/1000000</f>
+        <v>4.831758508248437E-2</v>
+      </c>
+      <c r="D21">
+        <f>10000*(1/1000)*(D3*D8*[10]Raster_logic!$I$91)*(1/[10]Raster_logic!$I$87)*[10]Raster_logic!$I$88*[10]Raster_logic!$I$89*[10]Raster_logic!$I$86/1000000</f>
+        <v>1.3184003710000327</v>
+      </c>
+      <c r="E21">
+        <f>10000*(1/1000)*(E3*E8*[10]Raster_logic!$I$91)*(1/[10]Raster_logic!$I$87)*[10]Raster_logic!$I$88*[10]Raster_logic!$I$89*[10]Raster_logic!$I$86/1000000</f>
+        <v>2.6002957207379964</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>77</v>
+      </c>
+      <c r="C22">
+        <f>SUM(C20:C21)</f>
+        <v>10.601301632692286</v>
+      </c>
+      <c r="D22">
+        <f>SUM(D20:D21)</f>
+        <v>17.394244747218586</v>
+      </c>
+      <c r="E22">
+        <f>SUM(E20:E21)</f>
+        <v>13.142933731562785</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>69</v>
+      </c>
+      <c r="B24" t="str">
+        <f>B20</f>
+        <v>BIOM GRASS Supply (MT/ha/yr)</v>
+      </c>
+      <c r="C24">
+        <f>10000*(1/1000)*(C2*C11+C3*C12*[10]Raster_logic!$I$84+C4*C13*[10]Raster_logic!$I$85)*(1/[10]Raster_logic!$I$79)*[10]Raster_logic!$I$80*[10]Raster_logic!$I$81/1000000</f>
+        <v>11.436227585699539</v>
+      </c>
+      <c r="D24">
+        <f>10000*(1/1000)*(D2*D11+D3*D12*[10]Raster_logic!$I$84+D4*D13*[10]Raster_logic!$I$85)*(1/[10]Raster_logic!$I$79)*[10]Raster_logic!$I$80*[10]Raster_logic!$I$81/1000000</f>
+        <v>16.70326857887704</v>
+      </c>
+      <c r="E24">
+        <f>10000*(1/1000)*(E2*E11+E3*E12*[10]Raster_logic!$I$84+E4*E13*[10]Raster_logic!$I$85)*(1/[10]Raster_logic!$I$79)*[10]Raster_logic!$I$80*[10]Raster_logic!$I$81/1000000</f>
+        <v>10.142497013227176</v>
+      </c>
+      <c r="F24" s="14">
+        <f>C24/C20</f>
+        <v>1.0836960933613644</v>
+      </c>
+      <c r="G24" s="14">
+        <f t="shared" ref="G24:H26" si="4">D24/D20</f>
+        <v>1.0390290045098129</v>
+      </c>
+      <c r="H24" s="14">
+        <f t="shared" si="4"/>
+        <v>0.96204545795969076</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B25" t="str">
+        <f t="shared" ref="B25:B26" si="5">B21</f>
+        <v>BIOM CROP Supply (MT/ha/yr)</v>
+      </c>
+      <c r="C25">
+        <f>10000*(1/1000)*(C12*C3*[10]Raster_logic!$I$91)*(1/[10]Raster_logic!$I$87)*[10]Raster_logic!$I$88*[10]Raster_logic!$I$89*[10]Raster_logic!$I$86/1000000</f>
+        <v>5.1411290332871701E-2</v>
+      </c>
+      <c r="D25">
+        <f>10000*(1/1000)*(D12*D3*[10]Raster_logic!$I$91)*(1/[10]Raster_logic!$I$87)*[10]Raster_logic!$I$88*[10]Raster_logic!$I$89*[10]Raster_logic!$I$86/1000000</f>
+        <v>1.3333814886155824</v>
+      </c>
+      <c r="E25">
+        <f>10000*(1/1000)*(E12*E3*[10]Raster_logic!$I$91)*(1/[10]Raster_logic!$I$87)*[10]Raster_logic!$I$88*[10]Raster_logic!$I$89*[10]Raster_logic!$I$86/1000000</f>
+        <v>2.4798833696571756</v>
+      </c>
+      <c r="F25" s="14">
+        <f t="shared" ref="F25:F26" si="6">C25/C21</f>
+        <v>1.0640285569965051</v>
+      </c>
+      <c r="G25" s="14">
+        <f t="shared" si="4"/>
+        <v>1.0113631017899261</v>
+      </c>
+      <c r="H25" s="14">
+        <f t="shared" si="4"/>
+        <v>0.95369282419668544</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B26" t="str">
+        <f t="shared" si="5"/>
+        <v>BIOM Total (MT/ha/yr)</v>
+      </c>
+      <c r="C26">
+        <f>SUM(C24:C25)</f>
+        <v>11.487638876032412</v>
+      </c>
+      <c r="D26">
+        <f t="shared" ref="D26:E26" si="7">SUM(D24:D25)</f>
+        <v>18.036650067492623</v>
+      </c>
+      <c r="E26">
+        <f t="shared" si="7"/>
+        <v>12.622380382884351</v>
+      </c>
+      <c r="F26" s="14">
+        <f t="shared" si="6"/>
+        <v>1.083606454570337</v>
+      </c>
+      <c r="G26" s="14">
+        <f t="shared" si="4"/>
+        <v>1.036932061702579</v>
+      </c>
+      <c r="H26" s="14">
+        <f t="shared" si="4"/>
+        <v>0.96039291079827005</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>70</v>
+      </c>
+      <c r="B28" t="str">
+        <f>B24</f>
+        <v>BIOM GRASS Supply (MT/ha/yr)</v>
+      </c>
+      <c r="C28">
+        <f>10000*(1/1000)*(C2*C15+C3*C16*[10]Raster_logic!$I$84+C4*C17*[10]Raster_logic!$I$85)*(1/[10]Raster_logic!$I$79)*[10]Raster_logic!$I$80*[10]Raster_logic!$I$81/1000000</f>
+        <v>12.170166888726877</v>
+      </c>
+      <c r="D28">
+        <f>10000*(1/1000)*(D2*D15+D3*D16*[10]Raster_logic!$I$84+D4*D17*[10]Raster_logic!$I$85)*(1/[10]Raster_logic!$I$79)*[10]Raster_logic!$I$80*[10]Raster_logic!$I$81/1000000</f>
+        <v>17.745960433737913</v>
+      </c>
+      <c r="E28">
+        <f>10000*(1/1000)*(E2*E15+E3*E16*[10]Raster_logic!$I$84+E4*E17*[10]Raster_logic!$I$85)*(1/[10]Raster_logic!$I$79)*[10]Raster_logic!$I$80*[10]Raster_logic!$I$81/1000000</f>
+        <v>11.966628729154726</v>
+      </c>
+      <c r="F28" s="14">
+        <f>C28/C20</f>
+        <v>1.1532441282788977</v>
+      </c>
+      <c r="G28" s="14">
+        <f t="shared" ref="G28:H28" si="8">D28/D20</f>
+        <v>1.1038897875865237</v>
+      </c>
+      <c r="H28" s="14">
+        <f t="shared" si="8"/>
+        <v>1.1350696777094913</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B29" t="str">
+        <f t="shared" ref="B29:B30" si="9">B25</f>
+        <v>BIOM CROP Supply (MT/ha/yr)</v>
+      </c>
+      <c r="C29">
+        <f>10000*(1/1000)*(C16*C3*[10]Raster_logic!$I$91)*(1/[10]Raster_logic!$I$87)*[10]Raster_logic!$I$88*[10]Raster_logic!$I$89*[10]Raster_logic!$I$86/1000000</f>
+        <v>5.4720624739186902E-2</v>
+      </c>
+      <c r="D29">
+        <f>10000*(1/1000)*(D16*D3*[10]Raster_logic!$I$91)*(1/[10]Raster_logic!$I$87)*[10]Raster_logic!$I$88*[10]Raster_logic!$I$89*[10]Raster_logic!$I$86/1000000</f>
+        <v>1.5588218792920909</v>
+      </c>
+      <c r="E29">
+        <f>10000*(1/1000)*(E16*E3*[10]Raster_logic!$I$91)*(1/[10]Raster_logic!$I$87)*[10]Raster_logic!$I$88*[10]Raster_logic!$I$89*[10]Raster_logic!$I$86/1000000</f>
+        <v>2.8883691070972564</v>
+      </c>
+      <c r="F29" s="14">
+        <f t="shared" ref="F29:F30" si="10">C29/C21</f>
+        <v>1.1325198609527301</v>
+      </c>
+      <c r="G29" s="14">
+        <f t="shared" ref="G29:G30" si="11">D29/D21</f>
+        <v>1.1823584956288307</v>
+      </c>
+      <c r="H29" s="14">
+        <f t="shared" ref="H29:H30" si="12">E29/E21</f>
+        <v>1.1107848557615212</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B30" t="str">
+        <f t="shared" si="9"/>
+        <v>BIOM Total (MT/ha/yr)</v>
+      </c>
+      <c r="C30">
+        <f>SUM(C28:C29)</f>
+        <v>12.224887513466063</v>
+      </c>
+      <c r="D30">
+        <f>SUM(D28:D29)</f>
+        <v>19.304782313030003</v>
+      </c>
+      <c r="E30">
+        <f t="shared" ref="D30:E30" si="13">SUM(E28:E29)</f>
+        <v>14.854997836251982</v>
+      </c>
+      <c r="F30" s="14">
+        <f t="shared" si="10"/>
+        <v>1.1531496732219151</v>
+      </c>
+      <c r="G30" s="14">
+        <f t="shared" si="11"/>
+        <v>1.1098373395094903</v>
+      </c>
+      <c r="H30" s="14">
+        <f t="shared" si="12"/>
+        <v>1.1302649879895288</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95E5D3D0-4020-4418-A256-3E770B560826}">
   <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2329,48 +5072,48 @@
         <v>2050</v>
       </c>
       <c r="L1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I2" t="s">
+        <v>3</v>
+      </c>
+      <c r="J2" t="s">
         <v>57</v>
       </c>
-      <c r="C2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" t="s">
-        <v>59</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="M2" t="s">
         <v>57</v>
-      </c>
-      <c r="H2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J2" t="s">
-        <v>60</v>
-      </c>
-      <c r="M2" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B3">
-        <f>[2]Pastoral_Zebu_2020!$K$2</f>
+        <f>[24]Pastoral_Zebu_2020!$K$2</f>
         <v>7912803.5780913802</v>
       </c>
       <c r="C3">
-        <f>[3]Pastoral_Boran_2020!$K$2</f>
+        <f>[25]Pastoral_Boran_2020!$K$2</f>
         <v>1124203.7226895699</v>
       </c>
       <c r="D3">
@@ -2378,15 +5121,15 @@
         <v>9.0370073007809495</v>
       </c>
       <c r="E3">
-        <f>Herd_decision_tree!E8*Herd_decision_tree!$E$42</f>
+        <f>Herd_decision_tree!E10*Herd_decision_tree!$E$49</f>
         <v>8.5595346951947899</v>
       </c>
       <c r="G3">
-        <f>[12]Pastoral_Zebu_2050!$K$2</f>
+        <f>[26]Pastoral_Zebu_2050!$K$2</f>
         <v>8554757.4814370908</v>
       </c>
       <c r="H3">
-        <f>[13]Pastoral_Boran_2050!$K$2</f>
+        <f>[27]Pastoral_Boran_2050!$K$2</f>
         <v>1215408.67359516</v>
       </c>
       <c r="I3">
@@ -2408,14 +5151,14 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B4">
-        <f>[4]Agpastoral_Zebu_2020!$K$2</f>
+        <f>[28]Agpastoral_Zebu_2020!$K$2</f>
         <v>3685141.0110471202</v>
       </c>
       <c r="C4">
-        <f>[5]Agpastoral_Boran_2020!$K$2</f>
+        <f>[29]Agpastoral_Boran_2020!$K$2</f>
         <v>277376.20390618598</v>
       </c>
       <c r="D4">
@@ -2423,15 +5166,15 @@
         <v>3.9625172149533063</v>
       </c>
       <c r="E4">
-        <f>Herd_decision_tree!E12*Herd_decision_tree!$E$42</f>
+        <f>Herd_decision_tree!E14*Herd_decision_tree!$E$49</f>
         <v>5.5401815014894495</v>
       </c>
       <c r="G4">
-        <f>[18]Agpastoral_Zebu_2050!$K$2</f>
+        <f>[30]Agpastoral_Zebu_2050!$K$2</f>
         <v>6488770.1197828101</v>
       </c>
       <c r="H4">
-        <f>[14]Agpastoral_Boran_2050!$K$2</f>
+        <f>[31]Agpastoral_Boran_2050!$K$2</f>
         <v>488402.05019366002</v>
       </c>
       <c r="I4">
@@ -2439,7 +5182,7 @@
         <v>6.9771721699764697</v>
       </c>
       <c r="J4">
-        <f t="shared" ref="J4:J8" si="1">I4/D4</f>
+        <f t="shared" ref="J4:J7" si="1">I4/D4</f>
         <v>1.7607928979202396</v>
       </c>
       <c r="L4">
@@ -2447,20 +5190,20 @@
         <v>10.185694242008363</v>
       </c>
       <c r="M4">
-        <f t="shared" ref="M4:M8" si="2">L4/E4</f>
+        <f t="shared" ref="M4:M6" si="2">L4/E4</f>
         <v>1.8385127345142016</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B5">
-        <f>[6]Mixed_Zebu_2020!$K$2</f>
+        <f>[32]Mixed_Zebu_2020!$K$2</f>
         <v>298374.71550379699</v>
       </c>
       <c r="C5">
-        <f>[7]Mixed_Boran_2020!$K$2</f>
+        <f>[33]Mixed_Boran_2020!$K$2</f>
         <v>25945.627401560501</v>
       </c>
       <c r="D5">
@@ -2468,15 +5211,15 @@
         <v>0.32432034290535749</v>
       </c>
       <c r="E5">
-        <f>Herd_decision_tree!E16*Herd_decision_tree!$E$42</f>
+        <f>Herd_decision_tree!E18*Herd_decision_tree!$E$49</f>
         <v>0.95304019787340866</v>
       </c>
       <c r="G5">
-        <f>[19]Mixed_Zebu_2050!$K$2</f>
+        <f>[34]Mixed_Zebu_2050!$K$2</f>
         <v>404262.59496554697</v>
       </c>
       <c r="H5">
-        <f>[15]Mixed_Boran_2050!$K$2</f>
+        <f>[35]Mixed_Boran_2050!$K$2</f>
         <v>35153.269665965803</v>
       </c>
       <c r="I5">
@@ -2498,14 +5241,14 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B6">
-        <f>[8]Cowcalf_Boran_2020!$K$2</f>
+        <f>[36]Cowcalf_Boran_2020!$K$2</f>
         <v>1184753.34766715</v>
       </c>
       <c r="C6">
-        <f>[9]Cowcalf_Exotic_2020!$K$2</f>
+        <f>[37]Cowcalf_Exotic_2020!$K$2</f>
         <v>985977.36353097099</v>
       </c>
       <c r="D6">
@@ -2513,15 +5256,15 @@
         <v>2.1707307111981207</v>
       </c>
       <c r="E6">
-        <f>Herd_decision_tree!E27*Herd_decision_tree!$E$42</f>
-        <v>1.4929364572739967</v>
+        <f>Herd_decision_tree!E29*Herd_decision_tree!$E$49</f>
+        <v>0.84668818128995216</v>
       </c>
       <c r="G6">
-        <f>[20]Cowcalf_Boran_2050!$K$2</f>
+        <f>[38]Cowcalf_Boran_2050!$K$2</f>
         <v>1806208.69891036</v>
       </c>
       <c r="H6">
-        <f>[16]Cowcalf_Exotic_2050!$K$2</f>
+        <f>[39]Cowcalf_Exotic_2050!$K$2</f>
         <v>1503165.94333724</v>
       </c>
       <c r="I6">
@@ -2534,23 +5277,23 @@
       </c>
       <c r="L6">
         <f>E6+E6*30*Validate_2020!G5/100</f>
-        <v>1.957493812330001</v>
+        <v>1.1101523228083683</v>
       </c>
       <c r="M6">
         <f t="shared" si="2"/>
-        <v>1.3111702127659575</v>
+        <v>1.3111702127659577</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B7">
-        <f>[10]Finisher_Boran_2020!$K$2</f>
+        <f>[40]Finisher_Boran_2020!$K$2</f>
         <v>26321.876059999999</v>
       </c>
       <c r="C7">
-        <f>[11]Finisher_Exotic_2020!$K$2</f>
+        <f>[41]Finisher_Exotic_2020!$K$2</f>
         <v>12386.7653238613</v>
       </c>
       <c r="D7">
@@ -2558,15 +5301,15 @@
         <v>3.8708641383861299E-2</v>
       </c>
       <c r="E7">
-        <f>Herd_decision_tree!E23*Herd_decision_tree!$E$42</f>
-        <v>7.1805363998227206E-2</v>
+        <f>Herd_decision_tree!E25*Herd_decision_tree!$E$49</f>
+        <v>0.71805363998227212</v>
       </c>
       <c r="G7">
-        <f>[21]Finisher_Boran_2050!$K$2</f>
+        <f>[42]Finisher_Boran_2050!$K$2</f>
         <v>918345.45531155204</v>
       </c>
       <c r="H7">
-        <f>[17]Finisher_Exotic_2050!$K$2</f>
+        <f>[43]Finisher_Exotic_2050!$K$2</f>
         <v>432162.57168335503</v>
       </c>
       <c r="I7">
@@ -2579,7 +5322,7 @@
       </c>
       <c r="L7">
         <f>E7+E7*30*Validate_2020!G6/100</f>
-        <v>1.9344343235783807</v>
+        <v>19.344343235783811</v>
       </c>
       <c r="M7">
         <f>L7/E7</f>
@@ -2613,11 +5356,11 @@
       </c>
       <c r="L8">
         <f>SUM(L3:L7)</f>
-        <v>24.961289477068426</v>
+        <v>41.523856899752225</v>
       </c>
       <c r="M8">
         <f>L8/E8</f>
-        <v>1.5021087502383623</v>
+        <v>2.4988031507773227</v>
       </c>
     </row>
   </sheetData>

--- a/Rasterized animal populations/Zonal statistics/Summary.xlsx
+++ b/Rasterized animal populations/Zonal statistics/Summary.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JHawkins\Documents\Github\KE.beef.spatial\Rasterized animal populations\Zonal statistics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{666D208B-8782-405F-92BF-76F5B733D13D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF7E624B-02DF-42FC-98F5-2820ECEB88F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="3" xr2:uid="{3882C52B-09A6-47D1-94BA-1F6173569800}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" activeTab="4" xr2:uid="{3882C52B-09A6-47D1-94BA-1F6173569800}"/>
   </bookViews>
   <sheets>
     <sheet name="Validate_2020" sheetId="2" r:id="rId1"/>
     <sheet name="Herd_decision_tree" sheetId="4" r:id="rId2"/>
     <sheet name="Projections" sheetId="3" r:id="rId3"/>
-    <sheet name="Carrying_Capacity" sheetId="7" r:id="rId4"/>
+    <sheet name="ZS_Summary" sheetId="6" r:id="rId4"/>
     <sheet name="NPP" sheetId="8" r:id="rId5"/>
-    <sheet name="ZS_Summary" sheetId="6" r:id="rId6"/>
+    <sheet name="Carrying_Capacity" sheetId="7" r:id="rId6"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId7"/>
@@ -135,7 +135,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="97">
   <si>
     <t>Arid</t>
   </si>
@@ -326,9 +326,6 @@
     <t>Mean LW -- dairy cattle (kg)</t>
   </si>
   <si>
-    <t>FRAC Fed</t>
-  </si>
-  <si>
     <t>FRAC DMI as BW</t>
   </si>
   <si>
@@ -420,6 +417,15 @@
   </si>
   <si>
     <t>NPP (kg C/m2/yr)</t>
+  </si>
+  <si>
+    <t>FRAC Fed -- Arid</t>
+  </si>
+  <si>
+    <t>FRAC Fed -- Semi-arid</t>
+  </si>
+  <si>
+    <t>FRAC Fed -- Humid/Subhumid</t>
   </si>
 </sst>
 </file>
@@ -430,9 +436,9 @@
     <numFmt numFmtId="164" formatCode="0.00000000"/>
     <numFmt numFmtId="165" formatCode="0.000000000"/>
     <numFmt numFmtId="166" formatCode="0.0000000"/>
-    <numFmt numFmtId="168" formatCode="0.000"/>
-    <numFmt numFmtId="169" formatCode="0.0000"/>
-    <numFmt numFmtId="170" formatCode="0.00000"/>
+    <numFmt numFmtId="167" formatCode="0.000"/>
+    <numFmt numFmtId="168" formatCode="0.0000"/>
+    <numFmt numFmtId="169" formatCode="0.00000"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -468,7 +474,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -487,6 +493,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -500,7 +518,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -523,19 +541,42 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="167" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -561,6 +602,52 @@
       <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
+      <sheetName val="ZS_Grassland_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1">
+        <row r="2">
+          <cell r="D2">
+            <v>202419</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink10.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2020_GRASS_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.33293320629867701</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink11.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
       <sheetName val="NPP_2020_GRASS_SArid"/>
     </sheetNames>
     <sheetDataSet>
@@ -576,7 +663,496 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink12.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2020_GRASS_Humid"/>
+      <sheetName val="filtered"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="F2">
+            <v>0.88426712592578605</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2020_CROP_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.97599038751874501</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2020_CROP_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.71371978379582002</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2020_CROP_Humid"/>
+      <sheetName val="filtered"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="F2">
+            <v>1.0163977502756547</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink16.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2020_SHRUB_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.20100514737984401</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink17.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2020_SHRUB_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.48829216400301401</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink18.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2020_SHRUB_Humid"/>
+      <sheetName val="filtered"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="F2">
+            <v>0.92696223687758272</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink19.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R4_GRASS_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1">
+        <row r="2">
+          <cell r="E2">
+            <v>0.21776707800273001</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="ZS_Grassland_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="D2">
+            <v>129806</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink20.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R4_GRASS_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.51075241024303597</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink21.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R4_CROP_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>1.038481644</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink22.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R4_CROP_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.72447113600000002</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink23.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R4_SHRUB_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.21776707800273001</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink24.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R4_SHRUB_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.51075241024303597</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink25.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R8_GRASS_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.38422689204237098</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink26.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R8_GRASS_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.51337712420869996</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink27.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R8_CROP_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>1.10532849796393</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink28.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R8_CROP_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.80695680840268103</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink29.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R8_SHRUB_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.231319877140652</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="ZS_Grassland_Humid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>64439.636684333513</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink30.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R8_SHRUB_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.51046846997934603</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink31.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -644,7 +1220,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink32.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -711,7 +1287,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink33.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -733,7 +1309,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink34.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -755,7 +1331,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink35.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -777,7 +1353,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink36.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -799,7 +1375,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink37.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -821,7 +1397,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink38.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -843,7 +1419,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink39.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -866,7 +1442,30 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="ZS_Cropland_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="D2">
+            <v>524</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink40.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -889,30 +1488,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2020_CROP_SArid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.71371978379582002</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink41.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -935,7 +1511,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink42.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -958,7 +1534,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink43.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -981,7 +1557,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink44.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1004,7 +1580,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink45.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1026,7 +1602,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink46.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1048,7 +1624,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink47.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1070,7 +1646,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink48.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1092,7 +1668,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink49.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1114,7 +1690,30 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="ZS_Cropland_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="D2">
+            <v>19552</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink50.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1136,30 +1735,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2020_SHRUB_SArid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.48829216400301401</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink30.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink51.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1181,7 +1757,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink52.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1203,7 +1779,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink53.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1225,7 +1801,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink54.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1247,7 +1823,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink55.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1269,7 +1845,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink56.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1291,7 +1867,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink57.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1313,7 +1889,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink58.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1335,7 +1911,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink59.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1357,7 +1933,30 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink39.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="ZS_Cropland_Humid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>27078.877240262751</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink60.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1379,30 +1978,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R4_GRASS_Arid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.36084903504638699</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink40.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink61.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1424,7 +2000,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink62.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1446,7 +2022,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink63.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1468,7 +2044,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink64.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1490,7 +2066,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink65.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1498,22 +2074,24 @@
       <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="NPP_2050_R8_GRASS_Arid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.38423018628503097</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink45.xml><?xml version="1.0" encoding="utf-8"?>
+      <sheetName val="NPP_2050_R4_CROP_Humid"/>
+      <sheetName val="filtered"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="F2">
+            <v>0.98649141647533578</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink66.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1521,22 +2099,24 @@
       <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="NPP_2050_R8_GRASS_SArid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.54877636996903001</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink46.xml><?xml version="1.0" encoding="utf-8"?>
+      <sheetName val="NPP_2050_R4_SHRUB_Humid"/>
+      <sheetName val="filtered"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="F2">
+            <v>0.90483097904137921</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink67.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1544,22 +2124,24 @@
       <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="NPP_2050_R8_CROP_Arid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>1.10532849796393</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink47.xml><?xml version="1.0" encoding="utf-8"?>
+      <sheetName val="NPP_2050_R4_GRASS_Humid"/>
+      <sheetName val="filtered"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="F2">
+            <v>0.90483097904137921</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink68.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1567,22 +2149,24 @@
       <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="NPP_2050_R8_CROP_SArid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.84387264986935995</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink48.xml><?xml version="1.0" encoding="utf-8"?>
+      <sheetName val="NPP_2050_R8_GRASS_Humid"/>
+      <sheetName val="filtered"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="F2">
+            <v>0.88457459938562355</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink69.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1590,275 +2174,24 @@
       <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="NPP_2050_R8_SHRUB_Arid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.23133614051250601</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink49.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R8_SHRUB_SArid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.51992080415758601</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R4_GRASS_SArid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.49669002326856798</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink50.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2020_GRASS_Arid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.33293320629867701</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink51.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2020_CROP_Arid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.97599038751874501</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink52.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2020_SHRUB_Arid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.20100514737984401</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink53.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="ZS_Grassland_Arid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1">
-        <row r="2">
-          <cell r="D2">
-            <v>202419</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink54.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="ZS_Grassland_Humid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>64439.636684333513</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink55.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="ZS_Grassland_SArid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="D2">
-            <v>129806</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink56.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="ZS_Cropland_Arid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="D2">
-            <v>524</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink57.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="ZS_Cropland_SArid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="D2">
-            <v>19552</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink58.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="ZS_Cropland_Humid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>27078.877240262751</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink59.xml><?xml version="1.0" encoding="utf-8"?>
+      <sheetName val="NPP_2050_R8_CROP_Humid"/>
+      <sheetName val="filtered"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="F2">
+            <v>1.0242825546815273</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1881,7 +2214,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink70.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1889,22 +2222,24 @@
       <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="NPP_2050_R4_CROP_Arid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>1.0384816436740301</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink60.xml><?xml version="1.0" encoding="utf-8"?>
+      <sheetName val="NPP_2050_R8_SHRUB_Humid"/>
+      <sheetName val="filtered"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="F2">
+            <v>0.93416975929597834</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1927,7 +2262,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink61.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1942,300 +2277,6 @@
         <row r="2">
           <cell r="E2">
             <v>63327.68656939434</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink62.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2020_GRASS_Humid"/>
-      <sheetName val="filtered"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="2">
-          <cell r="F2">
-            <v>0.88426712592578605</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink63.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2020_CROP_Humid"/>
-      <sheetName val="filtered"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="2">
-          <cell r="F2">
-            <v>1.0163977502756547</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink64.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2020_SHRUB_Humid"/>
-      <sheetName val="filtered"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="2">
-          <cell r="F2">
-            <v>0.92696223687758272</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink65.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R4_GRASS_Humid"/>
-      <sheetName val="filtered"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="2">
-          <cell r="F2">
-            <v>0.84678773914801542</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink66.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R4_CROP_Humid"/>
-      <sheetName val="filtered"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="2">
-          <cell r="F2">
-            <v>0.96933124096754675</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink67.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R4_SHRUB_Humid"/>
-      <sheetName val="filtered"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="2">
-          <cell r="F2">
-            <v>0.90483097904175391</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink68.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R8_GRASS_Humid"/>
-      <sheetName val="filtered"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="2">
-          <cell r="F2">
-            <v>1.006944889838866</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink69.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R8_CROP_Humid"/>
-      <sheetName val="filtered"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="2">
-          <cell r="F2">
-            <v>1.1289992284362775</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R4_CROP_SArid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.72182985434857605</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink70.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R8_SHRUB_Humid"/>
-      <sheetName val="filtered"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="2">
-          <cell r="F2">
-            <v>1.0528955612019462</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R4_SHRUB_Arid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.21776707800273001</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R4_SHRUB_SArid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.51075241024303597</v>
           </cell>
         </row>
       </sheetData>
@@ -2621,7 +2662,7 @@
         <v>0.51509165724121786</v>
       </c>
       <c r="D2">
-        <f>[11]FAO_2019_animal_trends!$F$35</f>
+        <f>[32]FAO_2019_animal_trends!$F$35</f>
         <v>0.53615960099750615</v>
       </c>
       <c r="E2">
@@ -2633,7 +2674,7 @@
         <v>0.52629975213940838</v>
       </c>
       <c r="G2">
-        <f>[11]FAO_2019_animal_trends!$G$35</f>
+        <f>[32]FAO_2019_animal_trends!$G$35</f>
         <v>0.38312009613345605</v>
       </c>
       <c r="H2">
@@ -2654,7 +2695,7 @@
         <v>0.33339443937546859</v>
       </c>
       <c r="D3">
-        <f>[11]FAO_2019_animal_trends!$F$36</f>
+        <f>[32]FAO_2019_animal_trends!$F$36</f>
         <v>0.36159600997506236</v>
       </c>
       <c r="E3">
@@ -2666,7 +2707,7 @@
         <v>0.31358889061540685</v>
       </c>
       <c r="G3">
-        <f>[11]FAO_2019_animal_trends!$G$36</f>
+        <f>[32]FAO_2019_animal_trends!$G$36</f>
         <v>2.7950424483806726</v>
       </c>
       <c r="H3">
@@ -2687,7 +2728,7 @@
         <v>5.7351605247385556E-2</v>
       </c>
       <c r="D4">
-        <f>[11]FAO_2019_animal_trends!$F$39</f>
+        <f>[32]FAO_2019_animal_trends!$F$39</f>
         <v>4.9875311720698257E-2</v>
       </c>
       <c r="E4">
@@ -2699,7 +2740,7 @@
         <v>4.6666186084097429E-2</v>
       </c>
       <c r="G4">
-        <f>[11]FAO_2019_animal_trends!$G$40</f>
+        <f>[32]FAO_2019_animal_trends!$G$40</f>
         <v>1.354588821344141</v>
       </c>
       <c r="H4">
@@ -2720,7 +2761,7 @@
         <v>5.0951603562285619E-2</v>
       </c>
       <c r="D5">
-        <f>[11]FAO_2019_animal_trends!$F$38</f>
+        <f>[32]FAO_2019_animal_trends!$F$38</f>
         <v>4.9875311720698257E-2</v>
       </c>
       <c r="E5">
@@ -2732,7 +2773,7 @@
         <v>4.7418024088714393E-2</v>
       </c>
       <c r="G5">
-        <f>[11]FAO_2019_animal_trends!$G$38</f>
+        <f>[32]FAO_2019_animal_trends!$G$38</f>
         <v>1.0372340425531916</v>
       </c>
       <c r="H5">
@@ -2753,7 +2794,7 @@
         <v>4.3210694573642398E-2</v>
       </c>
       <c r="D6">
-        <f>[11]FAO_2019_animal_trends!$F$37</f>
+        <f>[32]FAO_2019_animal_trends!$F$37</f>
         <v>2.4937655860349127E-3</v>
       </c>
       <c r="E6">
@@ -2765,7 +2806,7 @@
         <v>-7.7485333020033496E-3</v>
       </c>
       <c r="G6">
-        <f>[11]FAO_2019_animal_trends!$G$37</f>
+        <f>[32]FAO_2019_animal_trends!$G$37</f>
         <v>86.466565349544069</v>
       </c>
       <c r="H6">
@@ -2775,7 +2816,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C7" s="6"/>
       <c r="F7" s="6"/>
@@ -2840,18 +2881,18 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B2" s="8">
-        <f>[12]Arid_Subsistence!$C$2/1000000</f>
+        <f>[33]Arid_Subsistence!$C$2/1000000</f>
         <v>0.22078565217611199</v>
       </c>
       <c r="C2" s="8">
-        <f>[13]SArid_Subsistence!$C$2/1000000</f>
+        <f>[34]SArid_Subsistence!$C$2/1000000</f>
         <v>0.46769536221033298</v>
       </c>
       <c r="D2" s="8">
-        <f>[14]Humid_Subsistence!$D$2/1000000</f>
+        <f>[35]Humid_Subsistence!$D$2/1000000</f>
         <v>0.58969733266333946</v>
       </c>
       <c r="E2" s="9">
@@ -2873,18 +2914,18 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B3" s="8">
-        <f>[15]Arid_Commercial!$C$2/1000000</f>
+        <f>[36]Arid_Commercial!$C$2/1000000</f>
         <v>4.5806949930214902</v>
       </c>
       <c r="C3" s="8">
-        <f>[16]SArid_Commercial!$C$2/1000000</f>
+        <f>[37]SArid_Commercial!$C$2/1000000</f>
         <v>5.9316142707009298</v>
       </c>
       <c r="D3" s="8">
-        <f>[17]Humid_Commercial!$D$2/1000000</f>
+        <f>[38]Humid_Commercial!$D$2/1000000</f>
         <v>4.9681075438200857</v>
       </c>
       <c r="E3" s="9">
@@ -2906,33 +2947,33 @@
         <v>61</v>
       </c>
       <c r="B4" s="8">
-        <f>[18]Dairy_total_Arid_2020!$C$2/1000000</f>
+        <f>[39]Dairy_total_Arid_2020!$C$2/1000000</f>
         <v>2.48125917562073E-2</v>
       </c>
       <c r="C4" s="8">
-        <f>[19]Dairy_total_SArid_2020!$C$2/1000000</f>
+        <f>[40]Dairy_total_SArid_2020!$C$2/1000000</f>
         <v>1.2103066219751799</v>
       </c>
       <c r="D4" s="8">
-        <f>[20]Dairy_total_Humid_2020!$D$2/1000000</f>
+        <f>[41]Dairy_total_Humid_2020!$D$2/1000000</f>
         <v>5.2339163978957206</v>
       </c>
       <c r="E4" s="9"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B5" s="8">
-        <f>9.78*0.76*[21]Sheep_total_Arid_2020!$C$2/1000000</f>
+        <f>9.78*0.76*[42]Sheep_total_Arid_2020!$C$2/1000000</f>
         <v>9.6672519551532563</v>
       </c>
       <c r="C5" s="8">
-        <f>9.78*0.76*[22]Sheep_total_SArid_2020!$C$2/1000000</f>
+        <f>9.78*0.76*[43]Sheep_total_SArid_2020!$C$2/1000000</f>
         <v>7.908294939381296</v>
       </c>
       <c r="D5" s="8">
-        <f>9.78*0.76*[23]Sheep_total_Humid_2020!$D$2/1000000</f>
+        <f>9.78*0.76*[44]Sheep_total_Humid_2020!$D$2/1000000</f>
         <v>7.4434538218863873</v>
       </c>
       <c r="E5" s="9">
@@ -2942,7 +2983,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B6" s="8">
         <f>SUM(B2:B3)</f>
@@ -2989,7 +3030,7 @@
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
       <c r="H8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I8" s="6">
         <f>0.5348+0.05</f>
@@ -3706,7 +3747,7 @@
         <v>8.5595346951947899</v>
       </c>
       <c r="C2">
-        <f>[11]FAO_2019_animal_trends!$G$35/100</f>
+        <f>[32]FAO_2019_animal_trends!$G$35/100</f>
         <v>3.8312009613345605E-3</v>
       </c>
       <c r="D2">
@@ -3727,7 +3768,7 @@
         <v>5.5401815014894495</v>
       </c>
       <c r="C3">
-        <f>[11]FAO_2019_animal_trends!$G36/100</f>
+        <f>[32]FAO_2019_animal_trends!$G36/100</f>
         <v>2.7950424483806725E-2</v>
       </c>
       <c r="D3">
@@ -3748,7 +3789,7 @@
         <v>0.95304019787340866</v>
       </c>
       <c r="C4">
-        <f>[11]FAO_2019_animal_trends!$G39/100</f>
+        <f>[32]FAO_2019_animal_trends!$G39/100</f>
         <v>7.6101823708206687E-2</v>
       </c>
       <c r="D4">
@@ -3769,7 +3810,7 @@
         <v>0.84668818128995216</v>
       </c>
       <c r="C5">
-        <f>[11]FAO_2019_animal_trends!$G38/100</f>
+        <f>[32]FAO_2019_animal_trends!$G38/100</f>
         <v>1.0372340425531916E-2</v>
       </c>
       <c r="D5">
@@ -3790,7 +3831,7 @@
         <v>0.71805363998227212</v>
       </c>
       <c r="C6">
-        <f>[11]FAO_2019_animal_trends!$G37/100</f>
+        <f>[32]FAO_2019_animal_trends!$G37/100</f>
         <v>0.86466565349544067</v>
       </c>
       <c r="D6">
@@ -3811,7 +3852,7 @@
         <v>6.4690356116271079</v>
       </c>
       <c r="C7">
-        <f>[11]FAO_2019_animal_trends!$G39/100</f>
+        <f>[32]FAO_2019_animal_trends!$G39/100</f>
         <v>7.6101823708206687E-2</v>
       </c>
       <c r="D7">
@@ -3829,633 +3870,311 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7E0F49F-D7A7-4FDA-92DD-326744451984}">
-  <dimension ref="A1:I49"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95E5D3D0-4020-4418-A256-3E770B560826}">
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="17.42578125" customWidth="1"/>
-    <col min="2" max="2" width="27.5703125" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" customWidth="1"/>
-    <col min="5" max="5" width="9.28515625" customWidth="1"/>
-    <col min="6" max="7" width="11.28515625" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H1" t="s">
-        <v>60</v>
-      </c>
-      <c r="I1">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B1">
         <v>2020</v>
       </c>
+      <c r="G1">
+        <v>2050</v>
+      </c>
+      <c r="L1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I2" t="s">
+        <v>3</v>
+      </c>
+      <c r="J2" t="s">
+        <v>57</v>
+      </c>
+      <c r="M2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>13</v>
       </c>
-      <c r="C2">
-        <f>Herd_decision_tree!B10</f>
-        <v>3.5231517722606158</v>
-      </c>
-      <c r="D2">
-        <f>Herd_decision_tree!C10</f>
-        <v>3.4688080255059042</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="H2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I2">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
+      <c r="B3">
+        <f>[45]Pastoral_Zebu_2020!$K$2</f>
+        <v>7912803.5780913802</v>
+      </c>
+      <c r="C3">
+        <f>[46]Pastoral_Boran_2020!$K$2</f>
+        <v>1124203.7226895699</v>
+      </c>
+      <c r="D3">
+        <f>SUM(B3:C3)/1000000</f>
+        <v>9.0370073007809495</v>
+      </c>
+      <c r="E3">
+        <f>Herd_decision_tree!E10*Herd_decision_tree!$E$49</f>
+        <v>8.5595346951947899</v>
+      </c>
+      <c r="G3">
+        <f>[47]Pastoral_Zebu_2050!$K$2</f>
+        <v>8554757.4814370908</v>
+      </c>
+      <c r="H3">
+        <f>[48]Pastoral_Boran_2050!$K$2</f>
+        <v>1215408.67359516</v>
+      </c>
+      <c r="I3">
+        <f>SUM(G3:H3)/1000000</f>
+        <v>9.7701661550322516</v>
+      </c>
+      <c r="J3">
+        <f>I3/D3</f>
+        <v>1.0811285008243763</v>
+      </c>
+      <c r="L3">
+        <f>E3+E3*30*Validate_2020!G2/100</f>
+        <v>9.5433336217789932</v>
+      </c>
+      <c r="M3">
+        <f>L3/E3</f>
+        <v>1.1149360288400367</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>16</v>
       </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <f>Herd_decision_tree!C14</f>
-        <v>2.4628062451950257</v>
-      </c>
-      <c r="E3">
-        <f>Herd_decision_tree!D14</f>
-        <v>2.062758252194099</v>
-      </c>
-      <c r="H3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I3">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>59</v>
+      <c r="B4">
+        <f>[49]Agpastoral_Zebu_2020!$K$2</f>
+        <v>3685141.0110471202</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <f>[50]Agpastoral_Boran_2020!$K$2</f>
+        <v>277376.20390618598</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <f>SUM(B4:C4)/1000000</f>
+        <v>3.9625172149533063</v>
       </c>
       <c r="E4">
-        <f>Herd_decision_tree!D18</f>
-        <v>0.7785024521166074</v>
-      </c>
-      <c r="H4" t="s">
-        <v>63</v>
+        <f>Herd_decision_tree!E14*Herd_decision_tree!$E$49</f>
+        <v>5.5401815014894495</v>
+      </c>
+      <c r="G4">
+        <f>[51]Agpastoral_Zebu_2050!$K$2</f>
+        <v>6488770.1197828101</v>
+      </c>
+      <c r="H4">
+        <f>[52]Agpastoral_Boran_2050!$K$2</f>
+        <v>488402.05019366002</v>
       </c>
       <c r="I4">
-        <f>0.02+0.01</f>
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>22</v>
+        <f t="shared" ref="I4:I7" si="0">SUM(G4:H4)/1000000</f>
+        <v>6.9771721699764697</v>
+      </c>
+      <c r="J4">
+        <f t="shared" ref="J4:J7" si="1">I4/D4</f>
+        <v>1.7607928979202396</v>
+      </c>
+      <c r="L4">
+        <f>E4+E4*30*Validate_2020!G3/100</f>
+        <v>10.185694242008363</v>
+      </c>
+      <c r="M4">
+        <f t="shared" ref="M4:M6" si="2">L4/E4</f>
+        <v>1.8385127345142016</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5">
+        <f>[53]Mixed_Zebu_2020!$K$2</f>
+        <v>298374.71550379699</v>
       </c>
       <c r="C5">
-        <f>Herd_decision_tree!B29</f>
-        <v>5.2733829594195897E-2</v>
+        <f>[54]Mixed_Boran_2020!$K$2</f>
+        <v>25945.627401560501</v>
       </c>
       <c r="D5">
-        <f>Herd_decision_tree!C29</f>
-        <v>0.24371952505843877</v>
+        <f>SUM(B5:C5)/1000000</f>
+        <v>0.32432034290535749</v>
       </c>
       <c r="E5">
-        <f>Herd_decision_tree!D29</f>
-        <v>0.39517416198641953</v>
-      </c>
-      <c r="H5" t="s">
-        <v>64</v>
+        <f>Herd_decision_tree!E18*Herd_decision_tree!$E$49</f>
+        <v>0.95304019787340866</v>
+      </c>
+      <c r="G5">
+        <f>[55]Mixed_Zebu_2050!$K$2</f>
+        <v>404262.59496554697</v>
+      </c>
+      <c r="H5">
+        <f>[56]Mixed_Boran_2050!$K$2</f>
+        <v>35153.269665965803</v>
       </c>
       <c r="I5">
-        <f>0.025-0.005</f>
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
+        <f t="shared" si="0"/>
+        <v>0.43941586463151278</v>
+      </c>
+      <c r="J5">
+        <f t="shared" si="1"/>
+        <v>1.3548822152045585</v>
+      </c>
+      <c r="L5">
+        <f>E5+E5*30*Validate_2020!G4/100</f>
+        <v>1.3403334773726869</v>
+      </c>
+      <c r="M5">
+        <f t="shared" si="2"/>
+        <v>1.4063766464032423</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6">
+        <f>[57]Cowcalf_Boran_2020!$K$2</f>
+        <v>1184753.34766715</v>
+      </c>
+      <c r="C6">
+        <f>[58]Cowcalf_Exotic_2020!$K$2</f>
+        <v>985977.36353097099</v>
+      </c>
+      <c r="D6">
+        <f t="shared" ref="D6:D7" si="3">SUM(B6:C6)/1000000</f>
+        <v>2.1707307111981207</v>
+      </c>
+      <c r="E6">
+        <f>Herd_decision_tree!E29*Herd_decision_tree!$E$49</f>
+        <v>0.84668818128995216</v>
+      </c>
+      <c r="G6">
+        <f>[59]Cowcalf_Boran_2050!$K$2</f>
+        <v>1806208.69891036</v>
+      </c>
+      <c r="H6">
+        <f>[60]Cowcalf_Exotic_2050!$K$2</f>
+        <v>1503165.94333724</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="0"/>
+        <v>3.3093746422476</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="1"/>
+        <v>1.5245440741108842</v>
+      </c>
+      <c r="L6">
+        <f>E6+E6*30*Validate_2020!G5/100</f>
+        <v>1.1101523228083683</v>
+      </c>
+      <c r="M6">
+        <f t="shared" si="2"/>
+        <v>1.3111702127659577</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>23</v>
       </c>
-      <c r="C6">
-        <f>Herd_decision_tree!B25</f>
-        <v>0.16805182258191609</v>
-      </c>
-      <c r="D6">
-        <f>Herd_decision_tree!C25</f>
-        <v>0.2239758371518942</v>
-      </c>
-      <c r="E6">
-        <f>Herd_decision_tree!D25</f>
-        <v>0.1945231706769199</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>61</v>
+      <c r="B7">
+        <f>[61]Finisher_Boran_2020!$K$2</f>
+        <v>26321.876059999999</v>
       </c>
       <c r="C7">
-        <f>Herd_decision_tree!B35</f>
-        <v>2.48125917562073E-2</v>
+        <f>[62]Finisher_Exotic_2020!$K$2</f>
+        <v>12386.7653238613</v>
       </c>
       <c r="D7">
-        <f>Herd_decision_tree!C35</f>
-        <v>1.2103066219751799</v>
+        <f t="shared" si="3"/>
+        <v>3.8708641383861299E-2</v>
       </c>
       <c r="E7">
-        <f>Herd_decision_tree!D35</f>
-        <v>5.2339163978957206</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
-        <v>84</v>
-      </c>
-      <c r="C8">
-        <f>Herd_decision_tree!B5</f>
-        <v>9.6672519551532563</v>
-      </c>
+        <f>Herd_decision_tree!E25*Herd_decision_tree!$E$49</f>
+        <v>0.71805363998227212</v>
+      </c>
+      <c r="G7">
+        <f>[63]Finisher_Boran_2050!$K$2</f>
+        <v>918345.45531155204</v>
+      </c>
+      <c r="H7">
+        <f>[64]Finisher_Exotic_2050!$K$2</f>
+        <v>432162.57168335503</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="0"/>
+        <v>1.350508026994907</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="1"/>
+        <v>34.889057810175977</v>
+      </c>
+      <c r="L7">
+        <f>E7+E7*30*Validate_2020!G6/100</f>
+        <v>19.344343235783811</v>
+      </c>
+      <c r="M7">
+        <f>L7/E7</f>
+        <v>26.939969604863222</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="D8">
-        <f>Herd_decision_tree!C5</f>
-        <v>7.908294939381296</v>
+        <f>SUM(D3:D7)</f>
+        <v>15.533284211221597</v>
       </c>
       <c r="E8">
-        <f>Herd_decision_tree!D5</f>
-        <v>7.4434538218863873</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C10">
-        <f>SUM(C2:C6)*$I1*1000000</f>
-        <v>636469362.15424371</v>
-      </c>
-      <c r="D10">
-        <f>SUM(D2:D6)*$I1*1000000</f>
-        <v>1087882637.5949147</v>
-      </c>
-      <c r="E10">
-        <f>SUM(E2:E6)*$I1*1000000</f>
-        <v>583262866.28558779</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
-        <v>66</v>
-      </c>
-      <c r="C11">
-        <f t="shared" ref="C11:E12" si="0">C7*$I$2*1000000</f>
-        <v>4962518.3512414601</v>
-      </c>
-      <c r="D11">
-        <f t="shared" si="0"/>
-        <v>242061324.39503598</v>
-      </c>
-      <c r="E11">
-        <f t="shared" si="0"/>
-        <v>1046783279.5791441</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
-        <v>86</v>
-      </c>
-      <c r="C12">
-        <f>C8*$I$3*1000000</f>
-        <v>338353818.43036395</v>
-      </c>
-      <c r="D12">
-        <f>D8*$I$3*1000000</f>
-        <v>276790322.87834537</v>
-      </c>
-      <c r="E12">
-        <f>E8*$I$3*1000000</f>
-        <v>260520883.76602352</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B14" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C14">
-        <f>365*(C10+C11+C12)*(1-$I4)*($I5)/1000/1000000</f>
-        <v>6.9378625341647489</v>
-      </c>
-      <c r="D14">
-        <f>365*(D10+D11+D12)*(1-$I4)*($I5)/1000/1000000</f>
-        <v>11.377285471152405</v>
-      </c>
-      <c r="E14">
-        <f t="shared" ref="D14:E14" si="1">365*(E10+E11+E12)*(1-$I4)*($I5)/1000/1000000</f>
-        <v>13.387105136815379</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B15" s="1"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B16" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="C16" s="20">
-        <f>NPP!C22</f>
-        <v>10.601301632692286</v>
-      </c>
-      <c r="D16" s="20">
-        <f>NPP!D22</f>
-        <v>17.394244747218586</v>
-      </c>
-      <c r="E16" s="20">
-        <f>NPP!E22</f>
-        <v>13.142933731562785</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B17" s="1"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B18" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="C18" s="6">
-        <f>C16/C14</f>
-        <v>1.528035699826471</v>
-      </c>
-      <c r="D18" s="6">
-        <f t="shared" ref="D18" si="2">D16/D14</f>
-        <v>1.5288571945674072</v>
-      </c>
-      <c r="E18" s="6">
-        <f>E16/E14</f>
-        <v>0.98176070160373152</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B19" s="1"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B21" t="s">
-        <v>13</v>
-      </c>
-      <c r="C21">
-        <f>C2+C2*30*Validate_2020!$G2/100</f>
-        <v>3.9280888459649885</v>
-      </c>
-      <c r="D21">
-        <f>D2+D2*30*Validate_2020!$G2/100</f>
-        <v>3.867499044766002</v>
-      </c>
-      <c r="E21">
-        <f>E2+E2*30*Validate_2020!$G2/100</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B22" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22">
-        <f>C3+C3*30*Validate_2020!$G3/100</f>
-        <v>0</v>
-      </c>
-      <c r="D22">
-        <f>D3+D3*30*Validate_2020!$G3/100</f>
-        <v>4.5279006444321599</v>
-      </c>
-      <c r="E22">
-        <f>E3+E3*30*Validate_2020!$G3/100</f>
-        <v>3.7924073148831083</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B23" t="s">
-        <v>59</v>
-      </c>
-      <c r="C23">
-        <f>C4+C4*30*Validate_2020!$G4/100</f>
-        <v>0</v>
-      </c>
-      <c r="D23">
-        <f>D4+D4*30*Validate_2020!$G4/100</f>
-        <v>0</v>
-      </c>
-      <c r="E23">
-        <f>E4+E4*30*Validate_2020!$G4/100</f>
-        <v>1.0948676678244551</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B24" t="s">
-        <v>22</v>
-      </c>
-      <c r="C24">
-        <f>C5+C5*30*Validate_2020!$G5/100</f>
-        <v>6.9143026568985577E-2</v>
-      </c>
-      <c r="D24">
-        <f>D5+D5*30*Validate_2020!$G5/100</f>
-        <v>0.31955778152609127</v>
-      </c>
-      <c r="E24">
-        <f>E5+E5*30*Validate_2020!$G5/100</f>
-        <v>0.51814059005134261</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B25" t="s">
-        <v>23</v>
-      </c>
-      <c r="C25">
-        <f>C6+C6*30*Validate_2020!$G6/100</f>
-        <v>4.5273109923986858</v>
-      </c>
-      <c r="D25">
-        <f>D6+D6*30*Validate_2020!$G6/100</f>
-        <v>6.033902245095824</v>
-      </c>
-      <c r="E25">
-        <f>E6+E6*30*Validate_2020!$G6/100</f>
-        <v>5.2404483054778428</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B26" t="s">
-        <v>61</v>
-      </c>
-      <c r="C26">
-        <f>C7+C7*30*Validate_2020!G8/100</f>
-        <v>2.48125917562073E-2</v>
-      </c>
-      <c r="D26">
-        <f>D7+D7*30*Validate_2020!H8/100</f>
-        <v>1.2452331192095332</v>
-      </c>
-      <c r="E26">
-        <f>E7+E7*30*Validate_2020!I8/100</f>
-        <v>5.2339163978957206</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B27" t="s">
-        <v>84</v>
-      </c>
-      <c r="C27">
-        <f>C8+C8*30*Validate_2020!$G7/100</f>
-        <v>15.199336886489707</v>
-      </c>
-      <c r="D27">
-        <f>D8+D8*30*Validate_2020!$G7/100</f>
-        <v>12.433816718442243</v>
-      </c>
-      <c r="E27">
-        <f>E8+E8*30*Validate_2020!$G7/100</f>
-        <v>11.702970271460872</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B30" t="s">
-        <v>65</v>
-      </c>
-      <c r="C30">
-        <f>SUM(C21:C25)*$I1*1000000</f>
-        <v>1449172287.038552</v>
-      </c>
-      <c r="D30">
-        <f t="shared" ref="D30:E30" si="3">SUM(D21:D25)*$I1*1000000</f>
-        <v>2507306151.6894131</v>
-      </c>
-      <c r="E30">
-        <f t="shared" si="3"/>
-        <v>1809796859.3002474</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B31" t="s">
-        <v>66</v>
-      </c>
-      <c r="C31">
-        <f>C26*$I2*1000000</f>
-        <v>4962518.3512414601</v>
-      </c>
-      <c r="D31">
-        <f t="shared" ref="D31:E31" si="4">D26*$I2*1000000</f>
-        <v>249046623.84190664</v>
-      </c>
-      <c r="E31">
+        <f>SUM(E3:E7)</f>
+        <v>16.617498215829873</v>
+      </c>
+      <c r="G8">
+        <f>SUM(G3:G7)</f>
+        <v>18172344.350407358</v>
+      </c>
+      <c r="H8">
+        <f t="shared" ref="H8:I8" si="4">SUM(H3:H7)</f>
+        <v>3674292.5084753809</v>
+      </c>
+      <c r="I8">
         <f t="shared" si="4"/>
-        <v>1046783279.5791441</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B32" t="s">
-        <v>86</v>
-      </c>
-      <c r="C32">
-        <f>C27*$I3*1000000</f>
-        <v>531976791.02713972</v>
-      </c>
-      <c r="D32">
-        <f t="shared" ref="D32:E32" si="5">D27*$I3*1000000</f>
-        <v>435183585.14547849</v>
-      </c>
-      <c r="E32">
-        <f t="shared" si="5"/>
-        <v>409603959.50113052</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B34" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C34">
-        <f>365*(C30+C31+C32)*(1-$I4)*($I5)/1000/1000000</f>
-        <v>14.063656214228304</v>
-      </c>
-      <c r="D34">
-        <f t="shared" ref="D34:E34" si="6">365*(D30+D31+D32)*(1-$I4)*($I5)/1000/1000000</f>
-        <v>22.599268969952409</v>
-      </c>
-      <c r="E34">
-        <f t="shared" si="6"/>
-        <v>23.127849600632477</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B36" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="C36" s="20">
-        <f>NPP!C26</f>
-        <v>11.487638876032412</v>
-      </c>
-      <c r="D36" s="20">
-        <f>NPP!D26</f>
-        <v>18.036650067492623</v>
-      </c>
-      <c r="E36" s="20">
-        <f>NPP!E26</f>
-        <v>12.622380382884351</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B37" s="1"/>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B38" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="C38" s="12"/>
-      <c r="D38" s="12"/>
-      <c r="E38" s="12"/>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B39" s="18">
-        <v>2050</v>
-      </c>
-      <c r="C39" s="6">
-        <f>C36/C34</f>
-        <v>0.81683160488595297</v>
-      </c>
-      <c r="D39" s="6">
-        <f t="shared" ref="D39:E39" si="7">D36/D34</f>
-        <v>0.79810767735336197</v>
-      </c>
-      <c r="E39" s="6">
-        <f t="shared" si="7"/>
-        <v>0.54576541273163448</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="1"/>
-      <c r="B40" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="C40" s="6">
-        <f>(C39+C18)/2</f>
-        <v>1.172433652356212</v>
-      </c>
-      <c r="D40" s="6">
-        <f t="shared" ref="D40:E40" si="8">(D39+D18)/2</f>
-        <v>1.1634824359603846</v>
-      </c>
-      <c r="E40" s="6">
-        <f t="shared" si="8"/>
-        <v>0.763763057167683</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C43">
-        <f>C34</f>
-        <v>14.063656214228304</v>
-      </c>
-      <c r="D43">
-        <f t="shared" ref="D43:E43" si="9">D34</f>
-        <v>22.599268969952409</v>
-      </c>
-      <c r="E43">
-        <f t="shared" si="9"/>
-        <v>23.127849600632477</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B45" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="C45" s="20">
-        <f>NPP!C30</f>
-        <v>12.224887513466063</v>
-      </c>
-      <c r="D45" s="20">
-        <f>NPP!D30</f>
-        <v>19.304782313030003</v>
-      </c>
-      <c r="E45" s="20">
-        <f>NPP!E30</f>
-        <v>14.854997836251982</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B47" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="C47" s="12"/>
-      <c r="D47" s="12"/>
-      <c r="E47" s="12"/>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B48" s="1">
-        <v>2050</v>
-      </c>
-      <c r="C48">
-        <f>C45/C43</f>
-        <v>0.86925386451768172</v>
-      </c>
-      <c r="D48">
-        <f t="shared" ref="D48:E48" si="10">D45/D43</f>
-        <v>0.85422153870097761</v>
-      </c>
-      <c r="E48">
-        <f t="shared" si="10"/>
-        <v>0.64229913687460782</v>
-      </c>
-    </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B49" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C49">
-        <f>(C18+C48)*0.5</f>
-        <v>1.1986447821720763</v>
-      </c>
-      <c r="D49">
-        <f t="shared" ref="D49:E49" si="11">(D18+D48)*0.5</f>
-        <v>1.1915393666341925</v>
-      </c>
-      <c r="E49">
-        <f t="shared" si="11"/>
-        <v>0.81202991923916967</v>
+        <v>21.846636858882739</v>
+      </c>
+      <c r="J8">
+        <f>I8/D8</f>
+        <v>1.4064402969656753</v>
+      </c>
+      <c r="L8">
+        <f>SUM(L3:L7)</f>
+        <v>41.523856899752225</v>
+      </c>
+      <c r="M8">
+        <f>L8/E8</f>
+        <v>2.4988031507773227</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B47:E47"/>
-    <mergeCell ref="B38:E38"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4477,7 +4196,7 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
@@ -4491,66 +4210,66 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C2" s="13">
-        <f>[53]ZS_Grassland_Arid!$D$2*L15</f>
-        <v>8999548.7400000002</v>
-      </c>
-      <c r="D2" s="13">
-        <f>[55]ZS_Grassland_SArid!$D$2*L15</f>
-        <v>5771174.7599999998</v>
-      </c>
-      <c r="E2" s="13">
-        <f>[54]ZS_Grassland_Humid!$E$2*L15</f>
-        <v>2864986.2469854681</v>
+        <v>89</v>
+      </c>
+      <c r="C2" s="12">
+        <f>[1]ZS_Grassland_Arid!$D$2*L15</f>
+        <v>7105918.9949999992</v>
+      </c>
+      <c r="D2" s="12">
+        <f>[2]ZS_Grassland_SArid!$D$2*L15</f>
+        <v>4556839.63</v>
+      </c>
+      <c r="E2" s="12">
+        <f>[3]ZS_Grassland_Humid!$E$2*L15</f>
+        <v>2262153.4458035277</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C3" s="13">
-        <f>[56]ZS_Cropland_Arid!$D$2*L15</f>
-        <v>23297.040000000001</v>
-      </c>
-      <c r="D3" s="13">
-        <f>[57]ZS_Cropland_SArid!$D$2*L15</f>
-        <v>869281.92</v>
-      </c>
-      <c r="E3" s="13">
-        <f>[58]ZS_Cropland_Humid!$E$2*L15</f>
-        <v>1203926.882102082</v>
+        <v>90</v>
+      </c>
+      <c r="C3" s="12">
+        <f>[4]ZS_Cropland_Arid!$D$2*L15</f>
+        <v>18395.019999999997</v>
+      </c>
+      <c r="D3" s="12">
+        <f>[5]ZS_Cropland_SArid!$D$2*L15</f>
+        <v>686372.96</v>
+      </c>
+      <c r="E3" s="12">
+        <f>[6]ZS_Cropland_Humid!$E$2*L15</f>
+        <v>950603.98551942373</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>92</v>
-      </c>
-      <c r="C4" s="13">
-        <f>[59]ZS_Shrubland_Arid!$D$2*L15</f>
-        <v>12354944.939999999</v>
-      </c>
-      <c r="D4" s="13">
-        <f>[60]ZS_Shrubland_SArid!$D$2*L15</f>
-        <v>15894049.859999999</v>
-      </c>
-      <c r="E4" s="13">
-        <f>[61]ZS_Shrubland_Humid!$E$2*L15</f>
-        <v>2815548.9448752725</v>
+        <v>91</v>
+      </c>
+      <c r="C4" s="12">
+        <f>[7]ZS_Shrubland_Arid!$D$2*L15</f>
+        <v>9755293.3449999988</v>
+      </c>
+      <c r="D4" s="12">
+        <f>[8]ZS_Shrubland_SArid!$D$2*L15</f>
+        <v>12549721.555</v>
+      </c>
+      <c r="E4" s="12">
+        <f>[9]ZS_Shrubland_Humid!$E$2*L15</f>
+        <v>2223118.4370185882</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -4558,138 +4277,138 @@
         <v>2020</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C7" s="16">
-        <f>[50]NPP_2020_GRASS_Arid!$E$2</f>
+        <v>71</v>
+      </c>
+      <c r="C7" s="15">
+        <f>[10]NPP_2020_GRASS_Arid!$E$2</f>
         <v>0.33293320629867701</v>
       </c>
-      <c r="D7" s="16">
-        <f>[1]NPP_2020_GRASS_SArid!$E$2</f>
+      <c r="D7" s="15">
+        <f>[11]NPP_2020_GRASS_SArid!$E$2</f>
         <v>0.48066728987208701</v>
       </c>
-      <c r="E7" s="15">
-        <f>[62]filtered!$F$2</f>
+      <c r="E7" s="14">
+        <f>[12]filtered!$F$2</f>
         <v>0.88426712592578605</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>73</v>
-      </c>
-      <c r="C8" s="16">
-        <f>[51]NPP_2020_CROP_Arid!$E$2</f>
+        <v>72</v>
+      </c>
+      <c r="C8" s="15">
+        <f>[13]NPP_2020_CROP_Arid!$E$2</f>
         <v>0.97599038751874501</v>
       </c>
-      <c r="D8" s="16">
-        <f>[2]NPP_2020_CROP_SArid!$E$2</f>
+      <c r="D8" s="15">
+        <f>[14]NPP_2020_CROP_SArid!$E$2</f>
         <v>0.71371978379582002</v>
       </c>
-      <c r="E8" s="15">
-        <f>[63]filtered!$F$2</f>
+      <c r="E8" s="14">
+        <f>[15]filtered!$F$2</f>
         <v>1.0163977502756547</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>74</v>
-      </c>
-      <c r="C9" s="16">
-        <f>[52]NPP_2020_SHRUB_Arid!$E$2</f>
+        <v>73</v>
+      </c>
+      <c r="C9" s="15">
+        <f>[16]NPP_2020_SHRUB_Arid!$E$2</f>
         <v>0.20100514737984401</v>
       </c>
-      <c r="D9" s="16">
-        <f>[3]NPP_2020_SHRUB_SArid!$E$2</f>
+      <c r="D9" s="15">
+        <f>[17]NPP_2020_SHRUB_SArid!$E$2</f>
         <v>0.48829216400301401</v>
       </c>
-      <c r="E9" s="15">
-        <f>[64]filtered!$F$2</f>
+      <c r="E9" s="14">
+        <f>[18]filtered!$F$2</f>
         <v>0.92696223687758272</v>
       </c>
       <c r="L9" s="11"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
       <c r="L10" s="11"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B11" t="s">
-        <v>72</v>
-      </c>
-      <c r="C11" s="16">
-        <f>[4]NPP_2050_R4_GRASS_Arid!$E$2</f>
-        <v>0.36084903504638699</v>
-      </c>
-      <c r="D11" s="16">
-        <f>[5]NPP_2050_R4_GRASS_SArid!$E$2</f>
-        <v>0.49669002326856798</v>
-      </c>
-      <c r="E11" s="16">
-        <f>[65]filtered!$F$2</f>
-        <v>0.84678773914801542</v>
+        <v>71</v>
+      </c>
+      <c r="C11" s="31">
+        <f>[19]NPP_2050_R4_GRASS_Arid!$E$2+0.14</f>
+        <v>0.35776707800273</v>
+      </c>
+      <c r="D11" s="15">
+        <f>[20]NPP_2050_R4_GRASS_SArid!$E$2</f>
+        <v>0.51075241024303597</v>
+      </c>
+      <c r="E11" s="15">
+        <f>[67]filtered!$F$2</f>
+        <v>0.90483097904137921</v>
       </c>
       <c r="F11">
         <f>C11/C7</f>
-        <v>1.0838481359611407</v>
+        <v>1.0745911529226506</v>
       </c>
       <c r="G11">
         <f t="shared" ref="G11:H13" si="0">D11/D7</f>
-        <v>1.0333343535832131</v>
+        <v>1.0625903218397805</v>
       </c>
       <c r="H11">
         <f t="shared" si="0"/>
-        <v>0.95761531139300071</v>
+        <v>1.0232552500400416</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>73</v>
-      </c>
-      <c r="C12" s="16">
-        <f>[6]NPP_2050_R4_CROP_Arid!$E$2</f>
-        <v>1.0384816436740301</v>
-      </c>
-      <c r="D12" s="16">
-        <f>[7]NPP_2050_R4_CROP_SArid!$E$2</f>
-        <v>0.72182985434857605</v>
-      </c>
-      <c r="E12" s="16">
-        <f>[66]filtered!$F$2</f>
-        <v>0.96933124096754675</v>
+        <v>72</v>
+      </c>
+      <c r="C12" s="15">
+        <f>[21]NPP_2050_R4_CROP_Arid!$E$2</f>
+        <v>1.038481644</v>
+      </c>
+      <c r="D12" s="15">
+        <f>[22]NPP_2050_R4_CROP_SArid!$E$2</f>
+        <v>0.72447113600000002</v>
+      </c>
+      <c r="E12" s="15">
+        <f>[65]filtered!$F$2</f>
+        <v>0.98649141647533578</v>
       </c>
       <c r="F12">
         <f t="shared" ref="F12:F13" si="1">C12/C8</f>
-        <v>1.0640285569965051</v>
+        <v>1.064028557330494</v>
       </c>
       <c r="G12">
         <f t="shared" si="0"/>
-        <v>1.0113631017899263</v>
+        <v>1.015063828197392</v>
       </c>
       <c r="H12">
         <f t="shared" si="0"/>
-        <v>0.95369282419668566</v>
+        <v>0.97057615112567097</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>74</v>
-      </c>
-      <c r="C13" s="16">
-        <f>[8]NPP_2050_R4_SHRUB_Arid!$E$2</f>
+        <v>73</v>
+      </c>
+      <c r="C13" s="15">
+        <f>[23]NPP_2050_R4_SHRUB_Arid!$E$2</f>
         <v>0.21776707800273001</v>
       </c>
-      <c r="D13" s="16">
-        <f>[9]NPP_2050_R4_SHRUB_SArid!$E$2</f>
+      <c r="D13" s="15">
+        <f>[24]NPP_2050_R4_SHRUB_SArid!$E$2</f>
         <v>0.51075241024303597</v>
       </c>
-      <c r="E13" s="16">
-        <f>[67]filtered!$F$2</f>
-        <v>0.90483097904175391</v>
+      <c r="E13" s="15">
+        <f>[66]filtered!$F$2</f>
+        <v>0.90483097904137921</v>
       </c>
       <c r="F13">
         <f t="shared" si="1"/>
@@ -4701,203 +4420,203 @@
       </c>
       <c r="H13">
         <f t="shared" si="0"/>
-        <v>0.97612496285676464</v>
+        <v>0.97612496285636041</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B15" t="s">
-        <v>72</v>
-      </c>
-      <c r="C15" s="16">
-        <f>[44]NPP_2050_R8_GRASS_Arid!$E$2</f>
-        <v>0.38423018628503097</v>
-      </c>
-      <c r="D15" s="16">
-        <f>[45]NPP_2050_R8_GRASS_SArid!$E$2</f>
-        <v>0.54877636996903001</v>
-      </c>
-      <c r="E15" s="16">
+        <v>71</v>
+      </c>
+      <c r="C15" s="15">
+        <f>[25]NPP_2050_R8_GRASS_Arid!$E$2</f>
+        <v>0.38422689204237098</v>
+      </c>
+      <c r="D15" s="15">
+        <f>[26]NPP_2050_R8_GRASS_SArid!$E$2</f>
+        <v>0.51337712420869996</v>
+      </c>
+      <c r="E15" s="15">
         <f>[68]filtered!$F$2</f>
-        <v>1.006944889838866</v>
+        <v>0.88457459938562355</v>
       </c>
       <c r="F15">
         <f>C15/C7</f>
-        <v>1.1540758897456898</v>
+        <v>1.1540659951404126</v>
       </c>
       <c r="G15">
         <f t="shared" ref="G15:H17" si="2">D15/D7</f>
-        <v>1.1416969316032881</v>
+        <v>1.0680508847300958</v>
       </c>
       <c r="H15">
         <f t="shared" si="2"/>
-        <v>1.1387338286319784</v>
+        <v>1.0003477155836995</v>
       </c>
       <c r="K15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L15">
-        <f>44.46</f>
-        <v>44.46</v>
+        <f>35.105</f>
+        <v>35.104999999999997</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>73</v>
-      </c>
-      <c r="C16" s="16">
-        <f>[46]NPP_2050_R8_CROP_Arid!$E$2</f>
+        <v>72</v>
+      </c>
+      <c r="C16" s="15">
+        <f>[27]NPP_2050_R8_CROP_Arid!$E$2</f>
         <v>1.10532849796393</v>
       </c>
-      <c r="D16" s="16">
-        <f>[47]NPP_2050_R8_CROP_SArid!$E$2</f>
-        <v>0.84387264986935995</v>
-      </c>
-      <c r="E16" s="16">
+      <c r="D16" s="15">
+        <f>[28]NPP_2050_R8_CROP_SArid!$E$2</f>
+        <v>0.80695680840268103</v>
+      </c>
+      <c r="E16" s="15">
         <f>[69]filtered!$F$2</f>
-        <v>1.1289992284362775</v>
+        <v>1.0242825546815273</v>
       </c>
       <c r="F16">
-        <f t="shared" ref="F16:F17" si="3">C16/C8</f>
+        <f>C16/C8</f>
         <v>1.1325198609527298</v>
       </c>
       <c r="G16">
         <f t="shared" si="2"/>
-        <v>1.1823584956288304</v>
+        <v>1.1306353371781188</v>
       </c>
       <c r="H16">
-        <f t="shared" si="2"/>
-        <v>1.110784855761521</v>
+        <f>E16/E12</f>
+        <v>1.0383086335826586</v>
       </c>
       <c r="K16" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L16">
         <f>L15</f>
-        <v>44.46</v>
+        <v>35.104999999999997</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>74</v>
-      </c>
-      <c r="C17" s="16">
-        <f>[48]NPP_2050_R8_SHRUB_Arid!$E$2</f>
-        <v>0.23133614051250601</v>
-      </c>
-      <c r="D17" s="16">
-        <f>[49]NPP_2050_R8_SHRUB_SArid!$E$2</f>
-        <v>0.51992080415758601</v>
-      </c>
-      <c r="E17" s="16">
+        <v>73</v>
+      </c>
+      <c r="C17" s="15">
+        <f>[29]NPP_2050_R8_SHRUB_Arid!$E$2</f>
+        <v>0.231319877140652</v>
+      </c>
+      <c r="D17" s="15">
+        <f>[30]NPP_2050_R8_SHRUB_SArid!$E$2</f>
+        <v>0.51046846997934603</v>
+      </c>
+      <c r="E17" s="15">
         <f>[70]filtered!$F$2</f>
-        <v>1.0528955612019462</v>
+        <v>0.93416975929597834</v>
       </c>
       <c r="F17">
-        <f t="shared" si="3"/>
-        <v>1.15089659905746</v>
+        <f t="shared" ref="F16:F17" si="3">C17/C9</f>
+        <v>1.1508156888316972</v>
       </c>
       <c r="G17">
         <f t="shared" si="2"/>
-        <v>1.0647740072158454</v>
+        <v>1.0454160595052988</v>
       </c>
       <c r="H17">
         <f t="shared" si="2"/>
-        <v>1.1358559381540314</v>
+        <v>1.0077754218366799</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="17">
+      <c r="A20" s="16">
         <v>2020</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C20">
-        <f>10000*(1/1000)*(C2*C7+C3*C8*[10]Raster_logic!$I$84+C4*C9*[10]Raster_logic!$I$85)*(1/[10]Raster_logic!$I$79)*[10]Raster_logic!$I$80*[10]Raster_logic!$I$81/1000000</f>
-        <v>10.552984047609801</v>
+        <f>10000*(1/1000)*(C2*C7+C3*C8*[31]Raster_logic!$I$84+C4*C9*[31]Raster_logic!$I$85)*(1/[31]Raster_logic!$I$79)*[31]Raster_logic!$I$80*[31]Raster_logic!$I$81/1000000</f>
+        <v>8.332489990808412</v>
       </c>
       <c r="D20">
-        <f>10000*(1/1000)*(D2*D7+D3*D8*[10]Raster_logic!$I$84+D4*D9*[10]Raster_logic!$I$85)*(1/[10]Raster_logic!$I$79)*[10]Raster_logic!$I$80*[10]Raster_logic!$I$81/1000000</f>
-        <v>16.075844376218555</v>
+        <f>10000*(1/1000)*(D2*D7+D3*D8*[31]Raster_logic!$I$84+D4*D9*[31]Raster_logic!$I$85)*(1/[31]Raster_logic!$I$79)*[31]Raster_logic!$I$80*[31]Raster_logic!$I$81/1000000</f>
+        <v>12.693263986215754</v>
       </c>
       <c r="E20">
-        <f>10000*(1/1000)*(E2*E7+E3*E8*[10]Raster_logic!$I$84+E4*E9*[10]Raster_logic!$I$85)*(1/[10]Raster_logic!$I$79)*[10]Raster_logic!$I$80*[10]Raster_logic!$I$81/1000000</f>
-        <v>10.542638010824788</v>
+        <f>10000*(1/1000)*(E2*E7+E3*E8*[31]Raster_logic!$I$84+E4*E9*[31]Raster_logic!$I$85)*(1/[31]Raster_logic!$I$79)*[31]Raster_logic!$I$80*[31]Raster_logic!$I$81/1000000</f>
+        <v>8.3243209035088661</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C21">
-        <f>10000*(1/1000)*(C3*C8*[10]Raster_logic!$I$91)*(1/[10]Raster_logic!$I$87)*[10]Raster_logic!$I$88*[10]Raster_logic!$I$89*[10]Raster_logic!$I$86/1000000</f>
-        <v>4.831758508248437E-2</v>
+        <f>10000*(1/1000)*(C3*C8*[31]Raster_logic!$I$91)*(1/[31]Raster_logic!$I$87)*[31]Raster_logic!$I$88*[31]Raster_logic!$I$89*[31]Raster_logic!$I$86/1000000</f>
+        <v>3.8150895733707002E-2</v>
       </c>
       <c r="D21">
-        <f>10000*(1/1000)*(D3*D8*[10]Raster_logic!$I$91)*(1/[10]Raster_logic!$I$87)*[10]Raster_logic!$I$88*[10]Raster_logic!$I$89*[10]Raster_logic!$I$86/1000000</f>
-        <v>1.3184003710000327</v>
+        <f>10000*(1/1000)*(D3*D8*[31]Raster_logic!$I$91)*(1/[31]Raster_logic!$I$87)*[31]Raster_logic!$I$88*[31]Raster_logic!$I$89*[31]Raster_logic!$I$86/1000000</f>
+        <v>1.0409906663058062</v>
       </c>
       <c r="E21">
-        <f>10000*(1/1000)*(E3*E8*[10]Raster_logic!$I$91)*(1/[10]Raster_logic!$I$87)*[10]Raster_logic!$I$88*[10]Raster_logic!$I$89*[10]Raster_logic!$I$86/1000000</f>
-        <v>2.6002957207379964</v>
+        <f>10000*(1/1000)*(E3*E8*[31]Raster_logic!$I$91)*(1/[31]Raster_logic!$I$87)*[31]Raster_logic!$I$88*[31]Raster_logic!$I$89*[31]Raster_logic!$I$86/1000000</f>
+        <v>2.0531574736056535</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C22">
         <f>SUM(C20:C21)</f>
-        <v>10.601301632692286</v>
+        <v>8.3706408865421196</v>
       </c>
       <c r="D22">
         <f>SUM(D20:D21)</f>
-        <v>17.394244747218586</v>
+        <v>13.73425465252156</v>
       </c>
       <c r="E22">
         <f>SUM(E20:E21)</f>
-        <v>13.142933731562785</v>
+        <v>10.377478377114519</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B24" t="str">
         <f>B20</f>
         <v>BIOM GRASS Supply (MT/ha/yr)</v>
       </c>
       <c r="C24">
-        <f>10000*(1/1000)*(C2*C11+C3*C12*[10]Raster_logic!$I$84+C4*C13*[10]Raster_logic!$I$85)*(1/[10]Raster_logic!$I$79)*[10]Raster_logic!$I$80*[10]Raster_logic!$I$81/1000000</f>
-        <v>11.436227585699539</v>
+        <f>10000*(1/1000)*(C2*C11+C3*C12*[31]Raster_logic!$I$84+C4*C13*[31]Raster_logic!$I$85)*(1/[31]Raster_logic!$I$79)*[31]Raster_logic!$I$80*[31]Raster_logic!$I$81/1000000</f>
+        <v>8.9720704890776268</v>
       </c>
       <c r="D24">
-        <f>10000*(1/1000)*(D2*D11+D3*D12*[10]Raster_logic!$I$84+D4*D13*[10]Raster_logic!$I$85)*(1/[10]Raster_logic!$I$79)*[10]Raster_logic!$I$80*[10]Raster_logic!$I$81/1000000</f>
-        <v>16.70326857887704</v>
+        <f>10000*(1/1000)*(D2*D11+D3*D12*[31]Raster_logic!$I$84+D4*D13*[31]Raster_logic!$I$85)*(1/[31]Raster_logic!$I$79)*[31]Raster_logic!$I$80*[31]Raster_logic!$I$81/1000000</f>
+        <v>13.359468018042634</v>
       </c>
       <c r="E24">
-        <f>10000*(1/1000)*(E2*E11+E3*E12*[10]Raster_logic!$I$84+E4*E13*[10]Raster_logic!$I$85)*(1/[10]Raster_logic!$I$79)*[10]Raster_logic!$I$80*[10]Raster_logic!$I$81/1000000</f>
-        <v>10.142497013227176</v>
-      </c>
-      <c r="F24" s="14">
+        <f>10000*(1/1000)*(E2*E11+E3*E12*[31]Raster_logic!$I$84+E4*E13*[31]Raster_logic!$I$85)*(1/[31]Raster_logic!$I$79)*[31]Raster_logic!$I$80*[31]Raster_logic!$I$81/1000000</f>
+        <v>8.3696564117948942</v>
+      </c>
+      <c r="F24" s="13">
         <f>C24/C20</f>
-        <v>1.0836960933613644</v>
-      </c>
-      <c r="G24" s="14">
+        <v>1.0767574277286547</v>
+      </c>
+      <c r="G24" s="13">
         <f t="shared" ref="G24:H26" si="4">D24/D20</f>
-        <v>1.0390290045098129</v>
-      </c>
-      <c r="H24" s="14">
+        <v>1.0524848480698379</v>
+      </c>
+      <c r="H24" s="13">
         <f t="shared" si="4"/>
-        <v>0.96204545795969076</v>
+        <v>1.0054461509607251</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -4906,28 +4625,28 @@
         <v>BIOM CROP Supply (MT/ha/yr)</v>
       </c>
       <c r="C25">
-        <f>10000*(1/1000)*(C12*C3*[10]Raster_logic!$I$91)*(1/[10]Raster_logic!$I$87)*[10]Raster_logic!$I$88*[10]Raster_logic!$I$89*[10]Raster_logic!$I$86/1000000</f>
-        <v>5.1411290332871701E-2</v>
+        <f>10000*(1/1000)*(C12*C3*[31]Raster_logic!$I$91)*(1/[31]Raster_logic!$I$87)*[31]Raster_logic!$I$88*[31]Raster_logic!$I$89*[31]Raster_logic!$I$86/1000000</f>
+        <v>4.0593642548402364E-2</v>
       </c>
       <c r="D25">
-        <f>10000*(1/1000)*(D12*D3*[10]Raster_logic!$I$91)*(1/[10]Raster_logic!$I$87)*[10]Raster_logic!$I$88*[10]Raster_logic!$I$89*[10]Raster_logic!$I$86/1000000</f>
-        <v>1.3333814886155824</v>
+        <f>10000*(1/1000)*(D12*D3*[31]Raster_logic!$I$91)*(1/[31]Raster_logic!$I$87)*[31]Raster_logic!$I$88*[31]Raster_logic!$I$89*[31]Raster_logic!$I$86/1000000</f>
+        <v>1.0566719708581258</v>
       </c>
       <c r="E25">
-        <f>10000*(1/1000)*(E12*E3*[10]Raster_logic!$I$91)*(1/[10]Raster_logic!$I$87)*[10]Raster_logic!$I$88*[10]Raster_logic!$I$89*[10]Raster_logic!$I$86/1000000</f>
-        <v>2.4798833696571756</v>
-      </c>
-      <c r="F25" s="14">
+        <f>10000*(1/1000)*(E12*E3*[31]Raster_logic!$I$91)*(1/[31]Raster_logic!$I$87)*[31]Raster_logic!$I$88*[31]Raster_logic!$I$89*[31]Raster_logic!$I$86/1000000</f>
+        <v>1.9927456783870812</v>
+      </c>
+      <c r="F25" s="13">
         <f t="shared" ref="F25:F26" si="6">C25/C21</f>
-        <v>1.0640285569965051</v>
-      </c>
-      <c r="G25" s="14">
+        <v>1.0640285573304942</v>
+      </c>
+      <c r="G25" s="13">
         <f t="shared" si="4"/>
-        <v>1.0113631017899261</v>
-      </c>
-      <c r="H25" s="14">
+        <v>1.0150638281973923</v>
+      </c>
+      <c r="H25" s="13">
         <f t="shared" si="4"/>
-        <v>0.95369282419668544</v>
+        <v>0.97057615112567075</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -4937,60 +4656,60 @@
       </c>
       <c r="C26">
         <f>SUM(C24:C25)</f>
-        <v>11.487638876032412</v>
+        <v>9.0126641316260283</v>
       </c>
       <c r="D26">
         <f t="shared" ref="D26:E26" si="7">SUM(D24:D25)</f>
-        <v>18.036650067492623</v>
+        <v>14.41613998890076</v>
       </c>
       <c r="E26">
         <f t="shared" si="7"/>
-        <v>12.622380382884351</v>
-      </c>
-      <c r="F26" s="14">
+        <v>10.362402090181975</v>
+      </c>
+      <c r="F26" s="13">
         <f t="shared" si="6"/>
-        <v>1.083606454570337</v>
-      </c>
-      <c r="G26" s="14">
+        <v>1.0766994133168608</v>
+      </c>
+      <c r="G26" s="13">
         <f t="shared" si="4"/>
-        <v>1.036932061702579</v>
-      </c>
-      <c r="H26" s="14">
+        <v>1.0496485141444503</v>
+      </c>
+      <c r="H26" s="13">
         <f t="shared" si="4"/>
-        <v>0.96039291079827005</v>
+        <v>0.99854721095195997</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B28" t="str">
         <f>B24</f>
         <v>BIOM GRASS Supply (MT/ha/yr)</v>
       </c>
       <c r="C28">
-        <f>10000*(1/1000)*(C2*C15+C3*C16*[10]Raster_logic!$I$84+C4*C17*[10]Raster_logic!$I$85)*(1/[10]Raster_logic!$I$79)*[10]Raster_logic!$I$80*[10]Raster_logic!$I$81/1000000</f>
-        <v>12.170166888726877</v>
+        <f>10000*(1/1000)*(C2*C15+C3*C16*[31]Raster_logic!$I$84+C4*C17*[31]Raster_logic!$I$85)*(1/[31]Raster_logic!$I$79)*[31]Raster_logic!$I$80*[31]Raster_logic!$I$81/1000000</f>
+        <v>9.609165818496594</v>
       </c>
       <c r="D28">
-        <f>10000*(1/1000)*(D2*D15+D3*D16*[10]Raster_logic!$I$84+D4*D17*[10]Raster_logic!$I$85)*(1/[10]Raster_logic!$I$79)*[10]Raster_logic!$I$80*[10]Raster_logic!$I$81/1000000</f>
-        <v>17.745960433737913</v>
+        <f>10000*(1/1000)*(D2*D15+D3*D16*[31]Raster_logic!$I$84+D4*D17*[31]Raster_logic!$I$85)*(1/[31]Raster_logic!$I$79)*[31]Raster_logic!$I$80*[31]Raster_logic!$I$81/1000000</f>
+        <v>13.438099018999708</v>
       </c>
       <c r="E28">
-        <f>10000*(1/1000)*(E2*E15+E3*E16*[10]Raster_logic!$I$84+E4*E17*[10]Raster_logic!$I$85)*(1/[10]Raster_logic!$I$79)*[10]Raster_logic!$I$80*[10]Raster_logic!$I$81/1000000</f>
-        <v>11.966628729154726</v>
-      </c>
-      <c r="F28" s="14">
+        <f>10000*(1/1000)*(E2*E15+E3*E16*[31]Raster_logic!$I$84+E4*E17*[31]Raster_logic!$I$85)*(1/[31]Raster_logic!$I$79)*[31]Raster_logic!$I$80*[31]Raster_logic!$I$81/1000000</f>
+        <v>8.3498054400644932</v>
+      </c>
+      <c r="F28" s="13">
         <f>C28/C20</f>
-        <v>1.1532441282788977</v>
-      </c>
-      <c r="G28" s="14">
+        <v>1.1532166050120056</v>
+      </c>
+      <c r="G28" s="13">
         <f t="shared" ref="G28:H28" si="8">D28/D20</f>
-        <v>1.1038897875865237</v>
-      </c>
-      <c r="H28" s="14">
+        <v>1.058679551106225</v>
+      </c>
+      <c r="H28" s="13">
         <f t="shared" si="8"/>
-        <v>1.1350696777094913</v>
+        <v>1.0030614553248283</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -4999,28 +4718,28 @@
         <v>BIOM CROP Supply (MT/ha/yr)</v>
       </c>
       <c r="C29">
-        <f>10000*(1/1000)*(C16*C3*[10]Raster_logic!$I$91)*(1/[10]Raster_logic!$I$87)*[10]Raster_logic!$I$88*[10]Raster_logic!$I$89*[10]Raster_logic!$I$86/1000000</f>
-        <v>5.4720624739186902E-2</v>
+        <f>10000*(1/1000)*(C16*C3*[31]Raster_logic!$I$91)*(1/[31]Raster_logic!$I$87)*[31]Raster_logic!$I$88*[31]Raster_logic!$I$89*[31]Raster_logic!$I$86/1000000</f>
+        <v>4.3206647131559951E-2</v>
       </c>
       <c r="D29">
-        <f>10000*(1/1000)*(D16*D3*[10]Raster_logic!$I$91)*(1/[10]Raster_logic!$I$87)*[10]Raster_logic!$I$88*[10]Raster_logic!$I$89*[10]Raster_logic!$I$86/1000000</f>
-        <v>1.5588218792920909</v>
+        <f>10000*(1/1000)*(D16*D3*[31]Raster_logic!$I$91)*(1/[31]Raster_logic!$I$87)*[31]Raster_logic!$I$88*[31]Raster_logic!$I$89*[31]Raster_logic!$I$86/1000000</f>
+        <v>1.1769808329979399</v>
       </c>
       <c r="E29">
-        <f>10000*(1/1000)*(E16*E3*[10]Raster_logic!$I$91)*(1/[10]Raster_logic!$I$87)*[10]Raster_logic!$I$88*[10]Raster_logic!$I$89*[10]Raster_logic!$I$86/1000000</f>
-        <v>2.8883691070972564</v>
-      </c>
-      <c r="F29" s="14">
+        <f>10000*(1/1000)*(E16*E3*[31]Raster_logic!$I$91)*(1/[31]Raster_logic!$I$87)*[31]Raster_logic!$I$88*[31]Raster_logic!$I$89*[31]Raster_logic!$I$86/1000000</f>
+        <v>2.0690850424038385</v>
+      </c>
+      <c r="F29" s="13">
         <f t="shared" ref="F29:F30" si="10">C29/C21</f>
-        <v>1.1325198609527301</v>
-      </c>
-      <c r="G29" s="14">
+        <v>1.1325198609527298</v>
+      </c>
+      <c r="G29" s="13">
         <f t="shared" ref="G29:G30" si="11">D29/D21</f>
-        <v>1.1823584956288307</v>
-      </c>
-      <c r="H29" s="14">
+        <v>1.130635337178119</v>
+      </c>
+      <c r="H29" s="13">
         <f t="shared" ref="H29:H30" si="12">E29/E21</f>
-        <v>1.1107848557615212</v>
+        <v>1.0077575972632113</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -5030,27 +4749,27 @@
       </c>
       <c r="C30">
         <f>SUM(C28:C29)</f>
-        <v>12.224887513466063</v>
+        <v>9.6523724656281544</v>
       </c>
       <c r="D30">
         <f>SUM(D28:D29)</f>
-        <v>19.304782313030003</v>
+        <v>14.615079851997647</v>
       </c>
       <c r="E30">
-        <f t="shared" ref="D30:E30" si="13">SUM(E28:E29)</f>
-        <v>14.854997836251982</v>
-      </c>
-      <c r="F30" s="14">
+        <f t="shared" ref="E30" si="13">SUM(E28:E29)</f>
+        <v>10.418890482468331</v>
+      </c>
+      <c r="F30" s="13">
         <f t="shared" si="10"/>
-        <v>1.1531496732219151</v>
-      </c>
-      <c r="G30" s="14">
+        <v>1.1531222753979014</v>
+      </c>
+      <c r="G30" s="13">
         <f t="shared" si="11"/>
-        <v>1.1098373395094903</v>
-      </c>
-      <c r="H30" s="14">
+        <v>1.0641334547640975</v>
+      </c>
+      <c r="H30" s="13">
         <f t="shared" si="12"/>
-        <v>1.1302649879895288</v>
+        <v>1.0039905749594371</v>
       </c>
     </row>
   </sheetData>
@@ -5060,310 +4779,674 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95E5D3D0-4020-4418-A256-3E770B560826}">
-  <dimension ref="A1:M8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7E0F49F-D7A7-4FDA-92DD-326744451984}">
+  <dimension ref="A1:I49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17.42578125" customWidth="1"/>
+    <col min="2" max="2" width="27.5703125" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" customWidth="1"/>
+    <col min="5" max="5" width="9.28515625" customWidth="1"/>
+    <col min="6" max="7" width="11.28515625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B1">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2">
         <v>2020</v>
       </c>
-      <c r="G1">
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2">
+        <f>Herd_decision_tree!B10</f>
+        <v>3.5231517722606158</v>
+      </c>
+      <c r="D2">
+        <f>Herd_decision_tree!C10</f>
+        <v>3.4688080255059042</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="H2" t="s">
+        <v>62</v>
+      </c>
+      <c r="I2">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <f>Herd_decision_tree!C14</f>
+        <v>2.4628062451950257</v>
+      </c>
+      <c r="E3">
+        <f>Herd_decision_tree!D14</f>
+        <v>2.062758252194099</v>
+      </c>
+      <c r="H3" t="s">
+        <v>84</v>
+      </c>
+      <c r="I3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <f>Herd_decision_tree!D18</f>
+        <v>0.7785024521166074</v>
+      </c>
+      <c r="H4" t="s">
+        <v>94</v>
+      </c>
+      <c r="I4">
+        <f>0.035</f>
+        <v>3.5000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5">
+        <f>Herd_decision_tree!B29</f>
+        <v>5.2733829594195897E-2</v>
+      </c>
+      <c r="D5">
+        <f>Herd_decision_tree!C29</f>
+        <v>0.24371952505843877</v>
+      </c>
+      <c r="E5">
+        <f>Herd_decision_tree!D29</f>
+        <v>0.39517416198641953</v>
+      </c>
+      <c r="H5" t="s">
+        <v>95</v>
+      </c>
+      <c r="I5">
+        <f>0.035</f>
+        <v>3.5000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6">
+        <f>Herd_decision_tree!B25</f>
+        <v>0.16805182258191609</v>
+      </c>
+      <c r="D6">
+        <f>Herd_decision_tree!C25</f>
+        <v>0.2239758371518942</v>
+      </c>
+      <c r="E6">
+        <f>Herd_decision_tree!D25</f>
+        <v>0.1945231706769199</v>
+      </c>
+      <c r="H6" t="s">
+        <v>96</v>
+      </c>
+      <c r="I6">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7">
+        <f>Herd_decision_tree!B35</f>
+        <v>2.48125917562073E-2</v>
+      </c>
+      <c r="D7">
+        <f>Herd_decision_tree!C35</f>
+        <v>1.2103066219751799</v>
+      </c>
+      <c r="E7">
+        <f>Herd_decision_tree!D35</f>
+        <v>5.2339163978957206</v>
+      </c>
+      <c r="H7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I7">
+        <f>0.02</f>
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C8">
+        <f>Herd_decision_tree!B5</f>
+        <v>9.6672519551532563</v>
+      </c>
+      <c r="D8">
+        <f>Herd_decision_tree!C5</f>
+        <v>7.908294939381296</v>
+      </c>
+      <c r="E8">
+        <f>Herd_decision_tree!D5</f>
+        <v>7.4434538218863873</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>64</v>
+      </c>
+      <c r="C10">
+        <f>SUM(C2:C6)*$I1*1000000</f>
+        <v>636469362.15424371</v>
+      </c>
+      <c r="D10">
+        <f>SUM(D2:D6)*$I1*1000000</f>
+        <v>1087882637.5949147</v>
+      </c>
+      <c r="E10">
+        <f>SUM(E2:E6)*$I1*1000000</f>
+        <v>583262866.28558779</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>65</v>
+      </c>
+      <c r="C11">
+        <f t="shared" ref="C11:E11" si="0">C7*$I$2*1000000</f>
+        <v>4962518.3512414601</v>
+      </c>
+      <c r="D11">
+        <f t="shared" si="0"/>
+        <v>242061324.39503598</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="0"/>
+        <v>1046783279.5791441</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>85</v>
+      </c>
+      <c r="C12">
+        <f>C8*$I$3*1000000</f>
+        <v>338353818.43036395</v>
+      </c>
+      <c r="D12">
+        <f>D8*$I$3*1000000</f>
+        <v>276790322.87834537</v>
+      </c>
+      <c r="E12">
+        <f>E8*$I$3*1000000</f>
+        <v>260520883.76602352</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B14" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="C14" s="26">
+        <f>365*(C10+C11+C12)*(1-$I4)*($I7)/1000/1000000</f>
+        <v>6.902100356153591</v>
+      </c>
+      <c r="D14" s="26">
+        <f>365*(D10+D11+D12)*(1-$I5)*($I7)/1000/1000000</f>
+        <v>11.318639669754713</v>
+      </c>
+      <c r="E14" s="26">
+        <f>365*(E10+E11+E12)*(1-$I6)*($I7)/1000/1000000</f>
+        <v>12.835059564163199</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B15" s="1"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B16" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="C16" s="19">
+        <f>NPP!C22</f>
+        <v>8.3706408865421196</v>
+      </c>
+      <c r="D16" s="19">
+        <f>NPP!D22</f>
+        <v>13.73425465252156</v>
+      </c>
+      <c r="E16" s="19">
+        <f>NPP!E22</f>
+        <v>10.377478377114519</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B17" s="1"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B18" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="C18" s="6">
+        <f>C16/C14</f>
+        <v>1.2127671947104111</v>
+      </c>
+      <c r="D18" s="6">
+        <f t="shared" ref="D18" si="1">D16/D14</f>
+        <v>1.2134191964094212</v>
+      </c>
+      <c r="E18" s="6">
+        <f>E16/E14</f>
+        <v>0.80852592270701273</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B19" s="1"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B21" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21">
+        <f>C2+C2*30*Validate_2020!$G2/100</f>
+        <v>3.9280888459649885</v>
+      </c>
+      <c r="D21">
+        <f>D2+D2*30*Validate_2020!$G2/100</f>
+        <v>3.867499044766002</v>
+      </c>
+      <c r="E21">
+        <f>E2+E2*30*Validate_2020!$G2/100</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22">
+        <f>C3+C3*30*Validate_2020!$G3/100</f>
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <f>D3+D3*30*Validate_2020!$G3/100</f>
+        <v>4.5279006444321599</v>
+      </c>
+      <c r="E22">
+        <f>E3+E3*30*Validate_2020!$G3/100</f>
+        <v>3.7924073148831083</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>59</v>
+      </c>
+      <c r="C23">
+        <f>C4+C4*30*Validate_2020!$G4/100</f>
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <f>D4+D4*30*Validate_2020!$G4/100</f>
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <f>E4+E4*30*Validate_2020!$G4/100</f>
+        <v>1.0948676678244551</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24">
+        <f>C5+C5*30*Validate_2020!$G5/100</f>
+        <v>6.9143026568985577E-2</v>
+      </c>
+      <c r="D24">
+        <f>D5+D5*30*Validate_2020!$G5/100</f>
+        <v>0.31955778152609127</v>
+      </c>
+      <c r="E24">
+        <f>E5+E5*30*Validate_2020!$G5/100</f>
+        <v>0.51814059005134261</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>23</v>
+      </c>
+      <c r="C25">
+        <f>C6+C6*30*Validate_2020!$G6/100</f>
+        <v>4.5273109923986858</v>
+      </c>
+      <c r="D25">
+        <f>D6+D6*30*Validate_2020!$G6/100</f>
+        <v>6.033902245095824</v>
+      </c>
+      <c r="E25">
+        <f>E6+E6*30*Validate_2020!$G6/100</f>
+        <v>5.2404483054778428</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>61</v>
+      </c>
+      <c r="C26">
+        <f>C7+C7*30*Validate_2020!G8/100</f>
+        <v>2.48125917562073E-2</v>
+      </c>
+      <c r="D26">
+        <f>D7+D7*30*Validate_2020!H8/100</f>
+        <v>1.2452331192095332</v>
+      </c>
+      <c r="E26">
+        <f>E7+E7*30*Validate_2020!I8/100</f>
+        <v>5.2339163978957206</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>83</v>
+      </c>
+      <c r="C27">
+        <f>C8+C8*30*Validate_2020!$G7/100</f>
+        <v>15.199336886489707</v>
+      </c>
+      <c r="D27">
+        <f>D8+D8*30*Validate_2020!$G7/100</f>
+        <v>12.433816718442243</v>
+      </c>
+      <c r="E27">
+        <f>E8+E8*30*Validate_2020!$G7/100</f>
+        <v>11.702970271460872</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>64</v>
+      </c>
+      <c r="C30">
+        <f>SUM(C21:C25)*$I1*1000000</f>
+        <v>1449172287.038552</v>
+      </c>
+      <c r="D30">
+        <f>SUM(D21:D25)*$I1*1000000</f>
+        <v>2507306151.6894131</v>
+      </c>
+      <c r="E30">
+        <f>SUM(E21:E25)*$I1*1000000</f>
+        <v>1809796859.3002474</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>65</v>
+      </c>
+      <c r="C31">
+        <f>C26*$I2*1000000</f>
+        <v>4962518.3512414601</v>
+      </c>
+      <c r="D31">
+        <f>D26*$I2*1000000</f>
+        <v>249046623.84190664</v>
+      </c>
+      <c r="E31">
+        <f>E26*$I2*1000000</f>
+        <v>1046783279.5791441</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>85</v>
+      </c>
+      <c r="C32">
+        <f>C27*$I3*1000000</f>
+        <v>531976791.02713972</v>
+      </c>
+      <c r="D32">
+        <f>D27*$I3*1000000</f>
+        <v>435183585.14547849</v>
+      </c>
+      <c r="E32">
+        <f>E27*$I3*1000000</f>
+        <v>409603959.50113052</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B34" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="C34" s="27">
+        <f>365*(C30+C31+C32)*(1-$I4)*($I7)/1000/1000000</f>
+        <v>13.991163140959086</v>
+      </c>
+      <c r="D34" s="27">
+        <f>365*(D30+D31+D32)*(1-$I5)*($I7)/1000/1000000</f>
+        <v>22.482777892787702</v>
+      </c>
+      <c r="E34" s="27">
+        <f>365*(E30+E31+E32)*(1-$I6)*($I7)/1000/1000000</f>
+        <v>22.174123843905363</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="13"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B36" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="C36" s="28">
+        <f>NPP!C26</f>
+        <v>9.0126641316260283</v>
+      </c>
+      <c r="D36" s="28">
+        <f>NPP!D26</f>
+        <v>14.41613998890076</v>
+      </c>
+      <c r="E36" s="28">
+        <f>NPP!E26</f>
+        <v>10.362402090181975</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B37" s="1"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B38" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="C38" s="20"/>
+      <c r="D38" s="20"/>
+      <c r="E38" s="20"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B39" s="21">
         <v>2050</v>
       </c>
-      <c r="L1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" t="s">
-        <v>56</v>
-      </c>
-      <c r="G2" t="s">
-        <v>54</v>
-      </c>
-      <c r="H2" t="s">
-        <v>55</v>
-      </c>
-      <c r="I2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J2" t="s">
-        <v>57</v>
-      </c>
-      <c r="M2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3">
-        <f>[24]Pastoral_Zebu_2020!$K$2</f>
-        <v>7912803.5780913802</v>
-      </c>
-      <c r="C3">
-        <f>[25]Pastoral_Boran_2020!$K$2</f>
-        <v>1124203.7226895699</v>
-      </c>
-      <c r="D3">
-        <f>SUM(B3:C3)/1000000</f>
-        <v>9.0370073007809495</v>
-      </c>
-      <c r="E3">
-        <f>Herd_decision_tree!E10*Herd_decision_tree!$E$49</f>
-        <v>8.5595346951947899</v>
-      </c>
-      <c r="G3">
-        <f>[26]Pastoral_Zebu_2050!$K$2</f>
-        <v>8554757.4814370908</v>
-      </c>
-      <c r="H3">
-        <f>[27]Pastoral_Boran_2050!$K$2</f>
-        <v>1215408.67359516</v>
-      </c>
-      <c r="I3">
-        <f>SUM(G3:H3)/1000000</f>
-        <v>9.7701661550322516</v>
-      </c>
-      <c r="J3">
-        <f>I3/D3</f>
-        <v>1.0811285008243763</v>
-      </c>
-      <c r="L3">
-        <f>E3+E3*30*Validate_2020!G2/100</f>
-        <v>9.5433336217789932</v>
-      </c>
-      <c r="M3">
-        <f>L3/E3</f>
-        <v>1.1149360288400367</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4">
-        <f>[28]Agpastoral_Zebu_2020!$K$2</f>
-        <v>3685141.0110471202</v>
-      </c>
-      <c r="C4">
-        <f>[29]Agpastoral_Boran_2020!$K$2</f>
-        <v>277376.20390618598</v>
-      </c>
-      <c r="D4">
-        <f>SUM(B4:C4)/1000000</f>
-        <v>3.9625172149533063</v>
-      </c>
-      <c r="E4">
-        <f>Herd_decision_tree!E14*Herd_decision_tree!$E$49</f>
-        <v>5.5401815014894495</v>
-      </c>
-      <c r="G4">
-        <f>[30]Agpastoral_Zebu_2050!$K$2</f>
-        <v>6488770.1197828101</v>
-      </c>
-      <c r="H4">
-        <f>[31]Agpastoral_Boran_2050!$K$2</f>
-        <v>488402.05019366002</v>
-      </c>
-      <c r="I4">
-        <f t="shared" ref="I4:I7" si="0">SUM(G4:H4)/1000000</f>
-        <v>6.9771721699764697</v>
-      </c>
-      <c r="J4">
-        <f t="shared" ref="J4:J7" si="1">I4/D4</f>
-        <v>1.7607928979202396</v>
-      </c>
-      <c r="L4">
-        <f>E4+E4*30*Validate_2020!G3/100</f>
-        <v>10.185694242008363</v>
-      </c>
-      <c r="M4">
-        <f t="shared" ref="M4:M6" si="2">L4/E4</f>
-        <v>1.8385127345142016</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5">
-        <f>[32]Mixed_Zebu_2020!$K$2</f>
-        <v>298374.71550379699</v>
-      </c>
-      <c r="C5">
-        <f>[33]Mixed_Boran_2020!$K$2</f>
-        <v>25945.627401560501</v>
-      </c>
-      <c r="D5">
-        <f>SUM(B5:C5)/1000000</f>
-        <v>0.32432034290535749</v>
-      </c>
-      <c r="E5">
-        <f>Herd_decision_tree!E18*Herd_decision_tree!$E$49</f>
-        <v>0.95304019787340866</v>
-      </c>
-      <c r="G5">
-        <f>[34]Mixed_Zebu_2050!$K$2</f>
-        <v>404262.59496554697</v>
-      </c>
-      <c r="H5">
-        <f>[35]Mixed_Boran_2050!$K$2</f>
-        <v>35153.269665965803</v>
-      </c>
-      <c r="I5">
-        <f t="shared" si="0"/>
-        <v>0.43941586463151278</v>
-      </c>
-      <c r="J5">
-        <f t="shared" si="1"/>
-        <v>1.3548822152045585</v>
-      </c>
-      <c r="L5">
-        <f>E5+E5*30*Validate_2020!G4/100</f>
-        <v>1.3403334773726869</v>
-      </c>
-      <c r="M5">
+      <c r="C39" s="22">
+        <f>C36/C34</f>
+        <v>0.64416832545119018</v>
+      </c>
+      <c r="D39" s="22">
+        <f t="shared" ref="D39:E39" si="2">D36/D34</f>
+        <v>0.64120813084780526</v>
+      </c>
+      <c r="E39" s="22">
         <f t="shared" si="2"/>
-        <v>1.4063766464032423</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B6">
-        <f>[36]Cowcalf_Boran_2020!$K$2</f>
-        <v>1184753.34766715</v>
-      </c>
-      <c r="C6">
-        <f>[37]Cowcalf_Exotic_2020!$K$2</f>
-        <v>985977.36353097099</v>
-      </c>
-      <c r="D6">
-        <f t="shared" ref="D6:D7" si="3">SUM(B6:C6)/1000000</f>
-        <v>2.1707307111981207</v>
-      </c>
-      <c r="E6">
-        <f>Herd_decision_tree!E29*Herd_decision_tree!$E$49</f>
-        <v>0.84668818128995216</v>
-      </c>
-      <c r="G6">
-        <f>[38]Cowcalf_Boran_2050!$K$2</f>
-        <v>1806208.69891036</v>
-      </c>
-      <c r="H6">
-        <f>[39]Cowcalf_Exotic_2050!$K$2</f>
-        <v>1503165.94333724</v>
-      </c>
-      <c r="I6">
-        <f t="shared" si="0"/>
-        <v>3.3093746422476</v>
-      </c>
-      <c r="J6">
-        <f t="shared" si="1"/>
-        <v>1.5245440741108842</v>
-      </c>
-      <c r="L6">
-        <f>E6+E6*30*Validate_2020!G5/100</f>
-        <v>1.1101523228083683</v>
-      </c>
-      <c r="M6">
-        <f t="shared" si="2"/>
-        <v>1.3111702127659577</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7">
-        <f>[40]Finisher_Boran_2020!$K$2</f>
-        <v>26321.876059999999</v>
-      </c>
-      <c r="C7">
-        <f>[41]Finisher_Exotic_2020!$K$2</f>
-        <v>12386.7653238613</v>
-      </c>
-      <c r="D7">
+        <v>0.46731957317132594</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1"/>
+      <c r="B40" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="C40" s="22">
+        <f>(C39+C18)/2</f>
+        <v>0.92846776008080067</v>
+      </c>
+      <c r="D40" s="22">
+        <f t="shared" ref="D40:E40" si="3">(D39+D18)/2</f>
+        <v>0.92731366362861323</v>
+      </c>
+      <c r="E40" s="22">
         <f t="shared" si="3"/>
-        <v>3.8708641383861299E-2</v>
-      </c>
-      <c r="E7">
-        <f>Herd_decision_tree!E25*Herd_decision_tree!$E$49</f>
-        <v>0.71805363998227212</v>
-      </c>
-      <c r="G7">
-        <f>[42]Finisher_Boran_2050!$K$2</f>
-        <v>918345.45531155204</v>
-      </c>
-      <c r="H7">
-        <f>[43]Finisher_Exotic_2050!$K$2</f>
-        <v>432162.57168335503</v>
-      </c>
-      <c r="I7">
-        <f t="shared" si="0"/>
-        <v>1.350508026994907</v>
-      </c>
-      <c r="J7">
-        <f t="shared" si="1"/>
-        <v>34.889057810175977</v>
-      </c>
-      <c r="L7">
-        <f>E7+E7*30*Validate_2020!G6/100</f>
-        <v>19.344343235783811</v>
-      </c>
-      <c r="M7">
-        <f>L7/E7</f>
-        <v>26.939969604863222</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D8">
-        <f>SUM(D3:D7)</f>
-        <v>15.533284211221597</v>
-      </c>
-      <c r="E8">
-        <f>SUM(E3:E7)</f>
-        <v>16.617498215829873</v>
-      </c>
-      <c r="G8">
-        <f>SUM(G3:G7)</f>
-        <v>18172344.350407358</v>
-      </c>
-      <c r="H8">
-        <f t="shared" ref="H8:I8" si="4">SUM(H3:H7)</f>
-        <v>3674292.5084753809</v>
-      </c>
-      <c r="I8">
+        <v>0.63792274793916937</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B43" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="C43" s="30">
+        <f>C34</f>
+        <v>13.991163140959086</v>
+      </c>
+      <c r="D43" s="30">
+        <f t="shared" ref="D43:E43" si="4">D34</f>
+        <v>22.482777892787702</v>
+      </c>
+      <c r="E43" s="30">
         <f t="shared" si="4"/>
-        <v>21.846636858882739</v>
-      </c>
-      <c r="J8">
-        <f>I8/D8</f>
-        <v>1.4064402969656753</v>
-      </c>
-      <c r="L8">
-        <f>SUM(L3:L7)</f>
-        <v>41.523856899752225</v>
-      </c>
-      <c r="M8">
-        <f>L8/E8</f>
-        <v>2.4988031507773227</v>
+        <v>22.174123843905363</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="3"/>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B45" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="C45" s="24">
+        <f>NPP!C30</f>
+        <v>9.6523724656281544</v>
+      </c>
+      <c r="D45" s="24">
+        <f>NPP!D30</f>
+        <v>14.615079851997647</v>
+      </c>
+      <c r="E45" s="24">
+        <f>NPP!E30</f>
+        <v>10.418890482468331</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B46" s="3"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B47" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="C47" s="20"/>
+      <c r="D47" s="20"/>
+      <c r="E47" s="20"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B48" s="21">
+        <v>2050</v>
+      </c>
+      <c r="C48" s="22">
+        <f>C45/C43</f>
+        <v>0.68989063799641248</v>
+      </c>
+      <c r="D48" s="22">
+        <f t="shared" ref="D48:E48" si="5">D45/D43</f>
+        <v>0.65005667545584078</v>
+      </c>
+      <c r="E48" s="22">
+        <f>E45/E43</f>
+        <v>0.46986706468368539</v>
+      </c>
+    </row>
+    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B49" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="C49" s="22">
+        <f>(C18+C48)*0.5</f>
+        <v>0.95132891635341177</v>
+      </c>
+      <c r="D49" s="22">
+        <f t="shared" ref="D49:E49" si="6">(D18+D48)*0.5</f>
+        <v>0.93173793593263099</v>
+      </c>
+      <c r="E49" s="22">
+        <f t="shared" si="6"/>
+        <v>0.63919649369534903</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B47:E47"/>
+    <mergeCell ref="B38:E38"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Rasterized animal populations/Zonal statistics/Summary.xlsx
+++ b/Rasterized animal populations/Zonal statistics/Summary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JHawkins\Documents\Github\KE.beef.spatial\Rasterized animal populations\Zonal statistics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF7E624B-02DF-42FC-98F5-2820ECEB88F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08A47564-C67D-49E3-9C3A-DC6484DD3231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" activeTab="4" xr2:uid="{3882C52B-09A6-47D1-94BA-1F6173569800}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" activeTab="5" xr2:uid="{3882C52B-09A6-47D1-94BA-1F6173569800}"/>
   </bookViews>
   <sheets>
     <sheet name="Validate_2020" sheetId="2" r:id="rId1"/>
@@ -440,7 +440,7 @@
     <numFmt numFmtId="168" formatCode="0.0000"/>
     <numFmt numFmtId="169" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -473,8 +473,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -499,12 +505,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -518,7 +518,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -551,9 +551,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -576,7 +573,11 @@
     <xf numFmtId="167" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -631,7 +632,7 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="E2">
-            <v>0.33293320629867701</v>
+            <v>0.33293323112310402</v>
           </cell>
         </row>
       </sheetData>
@@ -654,7 +655,7 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="E2">
-            <v>0.48066728987208701</v>
+            <v>0.48080803465972</v>
           </cell>
         </row>
       </sheetData>
@@ -671,7 +672,381 @@
       <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="NPP_2020_GRASS_Humid"/>
+      <sheetName val="NPP_2020_CROP_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.97599038751874501</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2020_CROP_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.71416468993051396</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2020_SHRUB_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.20100553202445001</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2020_SHRUB_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.48842843619779902</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink16.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R4_GRASS_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.36084903504638699</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink17.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R4_GRASS_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.51075241024303597</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink18.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R4_GRASS_Humid"/>
+      <sheetName val="filtered"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="F2">
+            <v>0.90483097904137921</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink19.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R4_CROP_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>1.0384816436740301</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="ZS_Grassland_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="D2">
+            <v>129806</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink20.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R4_CROP_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.72447113600000002</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink21.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R4_CROP_Humid"/>
+      <sheetName val="filtered"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="F2">
+            <v>0.98649141647533578</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink22.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R4_SHRUB_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.21776707800273001</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink23.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R4_SHRUB_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.51075241024303597</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink24.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R4_SHRUB_Humid"/>
+      <sheetName val="filtered"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="F2">
+            <v>0.90483097904137921</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink25.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R8_GRASS_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.38422689204237098</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink26.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R8_GRASS_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.51337712420869996</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink27.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R8_GRASS_Humid"/>
       <sheetName val="filtered"/>
     </sheetNames>
     <sheetDataSet>
@@ -679,16 +1054,16 @@
       <sheetData sheetId="1">
         <row r="2">
           <cell r="F2">
-            <v>0.88426712592578605</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
+            <v>0.88457459938562355</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink28.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -696,22 +1071,22 @@
       <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="NPP_2020_CROP_Arid"/>
+      <sheetName val="NPP_2050_R8_CROP_Arid"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="2">
           <cell r="E2">
-            <v>0.97599038751874501</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
+            <v>1.10532849796393</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink29.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -719,22 +1094,22 @@
       <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="NPP_2020_CROP_SArid"/>
+      <sheetName val="NPP_2050_R8_CROP_SArid"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="2">
           <cell r="E2">
-            <v>0.71371978379582002</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
+            <v>0.80695680840268103</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -742,7 +1117,30 @@
       <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="NPP_2020_CROP_Humid"/>
+      <sheetName val="ZS_Grassland_Humid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>64439.636684333513</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink30.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R8_CROP_Humid"/>
       <sheetName val="filtered"/>
     </sheetNames>
     <sheetDataSet>
@@ -750,16 +1148,16 @@
       <sheetData sheetId="1">
         <row r="2">
           <cell r="F2">
-            <v>1.0163977502756547</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink16.xml><?xml version="1.0" encoding="utf-8"?>
+            <v>1.0242825546815273</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink31.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -767,22 +1165,22 @@
       <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="NPP_2020_SHRUB_Arid"/>
+      <sheetName val="NPP_2050_R8_SHRUB_Arid"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="2">
           <cell r="E2">
-            <v>0.20100514737984401</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink17.xml><?xml version="1.0" encoding="utf-8"?>
+            <v>0.231319877140652</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink32.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -790,22 +1188,22 @@
       <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="NPP_2020_SHRUB_SArid"/>
+      <sheetName val="NPP_2050_R8_SHRUB_SArid"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="2">
           <cell r="E2">
-            <v>0.48829216400301401</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink18.xml><?xml version="1.0" encoding="utf-8"?>
+            <v>0.51046846997934603</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink33.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -813,7 +1211,7 @@
       <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="NPP_2020_SHRUB_Humid"/>
+      <sheetName val="NPP_2050_R8_SHRUB_Humid"/>
       <sheetName val="filtered"/>
     </sheetNames>
     <sheetDataSet>
@@ -821,338 +1219,16 @@
       <sheetData sheetId="1">
         <row r="2">
           <cell r="F2">
-            <v>0.92696223687758272</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink19.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R4_GRASS_Arid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1">
-        <row r="2">
-          <cell r="E2">
-            <v>0.21776707800273001</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="ZS_Grassland_SArid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="D2">
-            <v>129806</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink20.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R4_GRASS_SArid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.51075241024303597</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink21.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R4_CROP_Arid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>1.038481644</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink22.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R4_CROP_SArid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.72447113600000002</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink23.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R4_SHRUB_Arid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.21776707800273001</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink24.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R4_SHRUB_SArid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.51075241024303597</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink25.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R8_GRASS_Arid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.38422689204237098</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink26.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R8_GRASS_SArid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.51337712420869996</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink27.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R8_CROP_Arid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>1.10532849796393</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink28.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R8_CROP_SArid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.80695680840268103</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink29.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R8_SHRUB_Arid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.231319877140652</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="ZS_Grassland_Humid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>64439.636684333513</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink30.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R8_SHRUB_SArid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.51046846997934603</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink31.xml><?xml version="1.0" encoding="utf-8"?>
+            <v>0.93416975929597834</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink34.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1220,7 +1296,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink35.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1287,7 +1363,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink36.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1309,7 +1385,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink37.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1331,7 +1407,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink38.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1353,7 +1429,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink39.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1375,7 +1451,30 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="ZS_Cropland_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="D2">
+            <v>524</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink40.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1397,7 +1496,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink41.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1419,7 +1518,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink39.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink42.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1442,30 +1541,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="ZS_Cropland_Arid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="D2">
-            <v>524</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink40.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink43.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1488,7 +1564,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink44.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1511,7 +1587,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink45.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1534,7 +1610,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink46.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1557,7 +1633,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink47.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1580,7 +1656,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink48.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1602,7 +1678,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink49.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1624,7 +1700,30 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink47.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="ZS_Cropland_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="D2">
+            <v>19552</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink50.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1646,7 +1745,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink48.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink51.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1668,7 +1767,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink49.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink52.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1690,30 +1789,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="ZS_Cropland_SArid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="D2">
-            <v>19552</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink50.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink53.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1735,7 +1811,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink51.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink54.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1757,7 +1833,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink52.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink55.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1779,7 +1855,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink53.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink56.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1801,7 +1877,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink54.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink57.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1823,7 +1899,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink55.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink58.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1845,7 +1921,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink56.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink59.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1867,7 +1943,30 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink57.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="ZS_Cropland_Humid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>27078.877240262751</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink60.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1889,7 +1988,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink58.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink61.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1911,7 +2010,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink59.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink62.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1933,30 +2032,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="ZS_Cropland_Humid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>27078.877240262751</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink60.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink63.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1978,7 +2054,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink61.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink64.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2000,7 +2076,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink62.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink65.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2022,7 +2098,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink63.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink66.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2044,7 +2120,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink64.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink67.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2066,7 +2142,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink65.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink68.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2074,7 +2150,7 @@
       <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="NPP_2050_R4_CROP_Humid"/>
+      <sheetName val="NPP_2020_GRASS_Humid"/>
       <sheetName val="filtered"/>
     </sheetNames>
     <sheetDataSet>
@@ -2082,16 +2158,16 @@
       <sheetData sheetId="1">
         <row r="2">
           <cell r="F2">
-            <v>0.98649141647533578</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink66.xml><?xml version="1.0" encoding="utf-8"?>
+            <v>0.88607168377191448</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink69.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2099,7 +2175,55 @@
       <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="NPP_2050_R4_SHRUB_Humid"/>
+      <sheetName val="NPP_2020_CROP_Humid"/>
+      <sheetName val="filtered"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="F2">
+            <v>1.0193612610195171</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="ZS_Shrubland_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="D2">
+            <v>277889</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink70.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2020_SHRUB_Humid"/>
       <sheetName val="filtered"/>
     </sheetNames>
     <sheetDataSet>
@@ -2107,130 +2231,7 @@
       <sheetData sheetId="1">
         <row r="2">
           <cell r="F2">
-            <v>0.90483097904137921</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink67.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R4_GRASS_Humid"/>
-      <sheetName val="filtered"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="2">
-          <cell r="F2">
-            <v>0.90483097904137921</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink68.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R8_GRASS_Humid"/>
-      <sheetName val="filtered"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="2">
-          <cell r="F2">
-            <v>0.88457459938562355</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink69.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R8_CROP_Humid"/>
-      <sheetName val="filtered"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="2">
-          <cell r="F2">
-            <v>1.0242825546815273</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="ZS_Shrubland_Arid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="D2">
-            <v>277889</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink70.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R8_SHRUB_Humid"/>
-      <sheetName val="filtered"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="2">
-          <cell r="F2">
-            <v>0.93416975929597834</v>
+            <v>0.9284507277249876</v>
           </cell>
         </row>
       </sheetData>
@@ -2662,7 +2663,7 @@
         <v>0.51509165724121786</v>
       </c>
       <c r="D2">
-        <f>[32]FAO_2019_animal_trends!$F$35</f>
+        <f>[35]FAO_2019_animal_trends!$F$35</f>
         <v>0.53615960099750615</v>
       </c>
       <c r="E2">
@@ -2674,7 +2675,7 @@
         <v>0.52629975213940838</v>
       </c>
       <c r="G2">
-        <f>[32]FAO_2019_animal_trends!$G$35</f>
+        <f>[35]FAO_2019_animal_trends!$G$35</f>
         <v>0.38312009613345605</v>
       </c>
       <c r="H2">
@@ -2695,7 +2696,7 @@
         <v>0.33339443937546859</v>
       </c>
       <c r="D3">
-        <f>[32]FAO_2019_animal_trends!$F$36</f>
+        <f>[35]FAO_2019_animal_trends!$F$36</f>
         <v>0.36159600997506236</v>
       </c>
       <c r="E3">
@@ -2707,7 +2708,7 @@
         <v>0.31358889061540685</v>
       </c>
       <c r="G3">
-        <f>[32]FAO_2019_animal_trends!$G$36</f>
+        <f>[35]FAO_2019_animal_trends!$G$36</f>
         <v>2.7950424483806726</v>
       </c>
       <c r="H3">
@@ -2728,7 +2729,7 @@
         <v>5.7351605247385556E-2</v>
       </c>
       <c r="D4">
-        <f>[32]FAO_2019_animal_trends!$F$39</f>
+        <f>[35]FAO_2019_animal_trends!$F$39</f>
         <v>4.9875311720698257E-2</v>
       </c>
       <c r="E4">
@@ -2740,7 +2741,7 @@
         <v>4.6666186084097429E-2</v>
       </c>
       <c r="G4">
-        <f>[32]FAO_2019_animal_trends!$G$40</f>
+        <f>[35]FAO_2019_animal_trends!$G$40</f>
         <v>1.354588821344141</v>
       </c>
       <c r="H4">
@@ -2761,7 +2762,7 @@
         <v>5.0951603562285619E-2</v>
       </c>
       <c r="D5">
-        <f>[32]FAO_2019_animal_trends!$F$38</f>
+        <f>[35]FAO_2019_animal_trends!$F$38</f>
         <v>4.9875311720698257E-2</v>
       </c>
       <c r="E5">
@@ -2773,7 +2774,7 @@
         <v>4.7418024088714393E-2</v>
       </c>
       <c r="G5">
-        <f>[32]FAO_2019_animal_trends!$G$38</f>
+        <f>[35]FAO_2019_animal_trends!$G$38</f>
         <v>1.0372340425531916</v>
       </c>
       <c r="H5">
@@ -2794,7 +2795,7 @@
         <v>4.3210694573642398E-2</v>
       </c>
       <c r="D6">
-        <f>[32]FAO_2019_animal_trends!$F$37</f>
+        <f>[35]FAO_2019_animal_trends!$F$37</f>
         <v>2.4937655860349127E-3</v>
       </c>
       <c r="E6">
@@ -2806,7 +2807,7 @@
         <v>-7.7485333020033496E-3</v>
       </c>
       <c r="G6">
-        <f>[32]FAO_2019_animal_trends!$G$37</f>
+        <f>[35]FAO_2019_animal_trends!$G$37</f>
         <v>86.466565349544069</v>
       </c>
       <c r="H6">
@@ -2821,8 +2822,8 @@
       <c r="C7" s="6"/>
       <c r="F7" s="6"/>
       <c r="G7">
-        <f>76.3/40</f>
-        <v>1.9075</v>
+        <f>76.3/(2012-1978.5)</f>
+        <v>2.2776119402985073</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -2884,15 +2885,15 @@
         <v>79</v>
       </c>
       <c r="B2" s="8">
-        <f>[33]Arid_Subsistence!$C$2/1000000</f>
+        <f>[36]Arid_Subsistence!$C$2/1000000</f>
         <v>0.22078565217611199</v>
       </c>
       <c r="C2" s="8">
-        <f>[34]SArid_Subsistence!$C$2/1000000</f>
+        <f>[37]SArid_Subsistence!$C$2/1000000</f>
         <v>0.46769536221033298</v>
       </c>
       <c r="D2" s="8">
-        <f>[35]Humid_Subsistence!$D$2/1000000</f>
+        <f>[38]Humid_Subsistence!$D$2/1000000</f>
         <v>0.58969733266333946</v>
       </c>
       <c r="E2" s="9">
@@ -2917,15 +2918,15 @@
         <v>80</v>
       </c>
       <c r="B3" s="8">
-        <f>[36]Arid_Commercial!$C$2/1000000</f>
+        <f>[39]Arid_Commercial!$C$2/1000000</f>
         <v>4.5806949930214902</v>
       </c>
       <c r="C3" s="8">
-        <f>[37]SArid_Commercial!$C$2/1000000</f>
+        <f>[40]SArid_Commercial!$C$2/1000000</f>
         <v>5.9316142707009298</v>
       </c>
       <c r="D3" s="8">
-        <f>[38]Humid_Commercial!$D$2/1000000</f>
+        <f>[41]Humid_Commercial!$D$2/1000000</f>
         <v>4.9681075438200857</v>
       </c>
       <c r="E3" s="9">
@@ -2947,15 +2948,15 @@
         <v>61</v>
       </c>
       <c r="B4" s="8">
-        <f>[39]Dairy_total_Arid_2020!$C$2/1000000</f>
+        <f>[42]Dairy_total_Arid_2020!$C$2/1000000</f>
         <v>2.48125917562073E-2</v>
       </c>
       <c r="C4" s="8">
-        <f>[40]Dairy_total_SArid_2020!$C$2/1000000</f>
+        <f>[43]Dairy_total_SArid_2020!$C$2/1000000</f>
         <v>1.2103066219751799</v>
       </c>
       <c r="D4" s="8">
-        <f>[41]Dairy_total_Humid_2020!$D$2/1000000</f>
+        <f>[44]Dairy_total_Humid_2020!$D$2/1000000</f>
         <v>5.2339163978957206</v>
       </c>
       <c r="E4" s="9"/>
@@ -2965,15 +2966,15 @@
         <v>83</v>
       </c>
       <c r="B5" s="8">
-        <f>9.78*0.76*[42]Sheep_total_Arid_2020!$C$2/1000000</f>
+        <f>9.78*0.76*[45]Sheep_total_Arid_2020!$C$2/1000000</f>
         <v>9.6672519551532563</v>
       </c>
       <c r="C5" s="8">
-        <f>9.78*0.76*[43]Sheep_total_SArid_2020!$C$2/1000000</f>
+        <f>9.78*0.76*[46]Sheep_total_SArid_2020!$C$2/1000000</f>
         <v>7.908294939381296</v>
       </c>
       <c r="D5" s="8">
-        <f>9.78*0.76*[44]Sheep_total_Humid_2020!$D$2/1000000</f>
+        <f>9.78*0.76*[47]Sheep_total_Humid_2020!$D$2/1000000</f>
         <v>7.4434538218863873</v>
       </c>
       <c r="E5" s="9">
@@ -3747,7 +3748,7 @@
         <v>8.5595346951947899</v>
       </c>
       <c r="C2">
-        <f>[32]FAO_2019_animal_trends!$G$35/100</f>
+        <f>[35]FAO_2019_animal_trends!$G$35/100</f>
         <v>3.8312009613345605E-3</v>
       </c>
       <c r="D2">
@@ -3768,7 +3769,7 @@
         <v>5.5401815014894495</v>
       </c>
       <c r="C3">
-        <f>[32]FAO_2019_animal_trends!$G36/100</f>
+        <f>[35]FAO_2019_animal_trends!$G36/100</f>
         <v>2.7950424483806725E-2</v>
       </c>
       <c r="D3">
@@ -3789,7 +3790,7 @@
         <v>0.95304019787340866</v>
       </c>
       <c r="C4">
-        <f>[32]FAO_2019_animal_trends!$G39/100</f>
+        <f>[35]FAO_2019_animal_trends!$G39/100</f>
         <v>7.6101823708206687E-2</v>
       </c>
       <c r="D4">
@@ -3810,7 +3811,7 @@
         <v>0.84668818128995216</v>
       </c>
       <c r="C5">
-        <f>[32]FAO_2019_animal_trends!$G38/100</f>
+        <f>[35]FAO_2019_animal_trends!$G38/100</f>
         <v>1.0372340425531916E-2</v>
       </c>
       <c r="D5">
@@ -3831,7 +3832,7 @@
         <v>0.71805363998227212</v>
       </c>
       <c r="C6">
-        <f>[32]FAO_2019_animal_trends!$G37/100</f>
+        <f>[35]FAO_2019_animal_trends!$G37/100</f>
         <v>0.86466565349544067</v>
       </c>
       <c r="D6">
@@ -3852,7 +3853,7 @@
         <v>6.4690356116271079</v>
       </c>
       <c r="C7">
-        <f>[32]FAO_2019_animal_trends!$G39/100</f>
+        <f>[35]FAO_2019_animal_trends!$G39/100</f>
         <v>7.6101823708206687E-2</v>
       </c>
       <c r="D7">
@@ -3919,11 +3920,11 @@
         <v>13</v>
       </c>
       <c r="B3">
-        <f>[45]Pastoral_Zebu_2020!$K$2</f>
+        <f>[48]Pastoral_Zebu_2020!$K$2</f>
         <v>7912803.5780913802</v>
       </c>
       <c r="C3">
-        <f>[46]Pastoral_Boran_2020!$K$2</f>
+        <f>[49]Pastoral_Boran_2020!$K$2</f>
         <v>1124203.7226895699</v>
       </c>
       <c r="D3">
@@ -3935,11 +3936,11 @@
         <v>8.5595346951947899</v>
       </c>
       <c r="G3">
-        <f>[47]Pastoral_Zebu_2050!$K$2</f>
+        <f>[50]Pastoral_Zebu_2050!$K$2</f>
         <v>8554757.4814370908</v>
       </c>
       <c r="H3">
-        <f>[48]Pastoral_Boran_2050!$K$2</f>
+        <f>[51]Pastoral_Boran_2050!$K$2</f>
         <v>1215408.67359516</v>
       </c>
       <c r="I3">
@@ -3964,11 +3965,11 @@
         <v>16</v>
       </c>
       <c r="B4">
-        <f>[49]Agpastoral_Zebu_2020!$K$2</f>
+        <f>[52]Agpastoral_Zebu_2020!$K$2</f>
         <v>3685141.0110471202</v>
       </c>
       <c r="C4">
-        <f>[50]Agpastoral_Boran_2020!$K$2</f>
+        <f>[53]Agpastoral_Boran_2020!$K$2</f>
         <v>277376.20390618598</v>
       </c>
       <c r="D4">
@@ -3980,11 +3981,11 @@
         <v>5.5401815014894495</v>
       </c>
       <c r="G4">
-        <f>[51]Agpastoral_Zebu_2050!$K$2</f>
+        <f>[54]Agpastoral_Zebu_2050!$K$2</f>
         <v>6488770.1197828101</v>
       </c>
       <c r="H4">
-        <f>[52]Agpastoral_Boran_2050!$K$2</f>
+        <f>[55]Agpastoral_Boran_2050!$K$2</f>
         <v>488402.05019366002</v>
       </c>
       <c r="I4">
@@ -4009,11 +4010,11 @@
         <v>11</v>
       </c>
       <c r="B5">
-        <f>[53]Mixed_Zebu_2020!$K$2</f>
+        <f>[56]Mixed_Zebu_2020!$K$2</f>
         <v>298374.71550379699</v>
       </c>
       <c r="C5">
-        <f>[54]Mixed_Boran_2020!$K$2</f>
+        <f>[57]Mixed_Boran_2020!$K$2</f>
         <v>25945.627401560501</v>
       </c>
       <c r="D5">
@@ -4025,11 +4026,11 @@
         <v>0.95304019787340866</v>
       </c>
       <c r="G5">
-        <f>[55]Mixed_Zebu_2050!$K$2</f>
+        <f>[58]Mixed_Zebu_2050!$K$2</f>
         <v>404262.59496554697</v>
       </c>
       <c r="H5">
-        <f>[56]Mixed_Boran_2050!$K$2</f>
+        <f>[59]Mixed_Boran_2050!$K$2</f>
         <v>35153.269665965803</v>
       </c>
       <c r="I5">
@@ -4054,11 +4055,11 @@
         <v>42</v>
       </c>
       <c r="B6">
-        <f>[57]Cowcalf_Boran_2020!$K$2</f>
+        <f>[60]Cowcalf_Boran_2020!$K$2</f>
         <v>1184753.34766715</v>
       </c>
       <c r="C6">
-        <f>[58]Cowcalf_Exotic_2020!$K$2</f>
+        <f>[61]Cowcalf_Exotic_2020!$K$2</f>
         <v>985977.36353097099</v>
       </c>
       <c r="D6">
@@ -4070,11 +4071,11 @@
         <v>0.84668818128995216</v>
       </c>
       <c r="G6">
-        <f>[59]Cowcalf_Boran_2050!$K$2</f>
+        <f>[62]Cowcalf_Boran_2050!$K$2</f>
         <v>1806208.69891036</v>
       </c>
       <c r="H6">
-        <f>[60]Cowcalf_Exotic_2050!$K$2</f>
+        <f>[63]Cowcalf_Exotic_2050!$K$2</f>
         <v>1503165.94333724</v>
       </c>
       <c r="I6">
@@ -4099,11 +4100,11 @@
         <v>23</v>
       </c>
       <c r="B7">
-        <f>[61]Finisher_Boran_2020!$K$2</f>
+        <f>[64]Finisher_Boran_2020!$K$2</f>
         <v>26321.876059999999</v>
       </c>
       <c r="C7">
-        <f>[62]Finisher_Exotic_2020!$K$2</f>
+        <f>[65]Finisher_Exotic_2020!$K$2</f>
         <v>12386.7653238613</v>
       </c>
       <c r="D7">
@@ -4115,11 +4116,11 @@
         <v>0.71805363998227212</v>
       </c>
       <c r="G7">
-        <f>[63]Finisher_Boran_2050!$K$2</f>
+        <f>[66]Finisher_Boran_2050!$K$2</f>
         <v>918345.45531155204</v>
       </c>
       <c r="H7">
-        <f>[64]Finisher_Exotic_2050!$K$2</f>
+        <f>[67]Finisher_Exotic_2050!$K$2</f>
         <v>432162.57168335503</v>
       </c>
       <c r="I7">
@@ -4281,32 +4282,32 @@
       </c>
       <c r="C7" s="15">
         <f>[10]NPP_2020_GRASS_Arid!$E$2</f>
-        <v>0.33293320629867701</v>
+        <v>0.33293323112310402</v>
       </c>
       <c r="D7" s="15">
         <f>[11]NPP_2020_GRASS_SArid!$E$2</f>
-        <v>0.48066728987208701</v>
+        <v>0.48080803465972</v>
       </c>
       <c r="E7" s="14">
-        <f>[12]filtered!$F$2</f>
-        <v>0.88426712592578605</v>
+        <f>[68]filtered!$F$2</f>
+        <v>0.88607168377191448</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>72</v>
       </c>
-      <c r="C8" s="15">
-        <f>[13]NPP_2020_CROP_Arid!$E$2</f>
+      <c r="C8" s="32">
+        <f>[12]NPP_2020_CROP_Arid!$E$2</f>
         <v>0.97599038751874501</v>
       </c>
-      <c r="D8" s="15">
-        <f>[14]NPP_2020_CROP_SArid!$E$2</f>
-        <v>0.71371978379582002</v>
+      <c r="D8" s="32">
+        <f>[13]NPP_2020_CROP_SArid!$E$2</f>
+        <v>0.71416468993051396</v>
       </c>
       <c r="E8" s="14">
-        <f>[15]filtered!$F$2</f>
-        <v>1.0163977502756547</v>
+        <f>[69]filtered!$F$2</f>
+        <v>1.0193612610195171</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -4314,16 +4315,16 @@
         <v>73</v>
       </c>
       <c r="C9" s="15">
-        <f>[16]NPP_2020_SHRUB_Arid!$E$2</f>
-        <v>0.20100514737984401</v>
+        <f>[14]NPP_2020_SHRUB_Arid!$E$2</f>
+        <v>0.20100553202445001</v>
       </c>
       <c r="D9" s="15">
-        <f>[17]NPP_2020_SHRUB_SArid!$E$2</f>
-        <v>0.48829216400301401</v>
+        <f>[15]NPP_2020_SHRUB_SArid!$E$2</f>
+        <v>0.48842843619779902</v>
       </c>
       <c r="E9" s="14">
-        <f>[18]filtered!$F$2</f>
-        <v>0.92696223687758272</v>
+        <f>[70]filtered!$F$2</f>
+        <v>0.9284507277249876</v>
       </c>
       <c r="L9" s="11"/>
     </row>
@@ -4341,28 +4342,28 @@
         <v>71</v>
       </c>
       <c r="C11" s="31">
-        <f>[19]NPP_2050_R4_GRASS_Arid!$E$2+0.14</f>
-        <v>0.35776707800273</v>
+        <f>[16]NPP_2050_R4_GRASS_Arid!$E$2</f>
+        <v>0.36084903504638699</v>
       </c>
       <c r="D11" s="15">
-        <f>[20]NPP_2050_R4_GRASS_SArid!$E$2</f>
+        <f>[17]NPP_2050_R4_GRASS_SArid!$E$2</f>
         <v>0.51075241024303597</v>
       </c>
       <c r="E11" s="15">
-        <f>[67]filtered!$F$2</f>
+        <f>[18]filtered!$F$2</f>
         <v>0.90483097904137921</v>
       </c>
       <c r="F11">
         <f>C11/C7</f>
-        <v>1.0745911529226506</v>
+        <v>1.0838480551464114</v>
       </c>
       <c r="G11">
         <f t="shared" ref="G11:H13" si="0">D11/D7</f>
-        <v>1.0625903218397805</v>
+        <v>1.0622792745227487</v>
       </c>
       <c r="H11">
         <f t="shared" si="0"/>
-        <v>1.0232552500400416</v>
+        <v>1.0211713065805335</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
@@ -4370,28 +4371,28 @@
         <v>72</v>
       </c>
       <c r="C12" s="15">
-        <f>[21]NPP_2050_R4_CROP_Arid!$E$2</f>
-        <v>1.038481644</v>
+        <f>[19]NPP_2050_R4_CROP_Arid!$E$2</f>
+        <v>1.0384816436740301</v>
       </c>
       <c r="D12" s="15">
-        <f>[22]NPP_2050_R4_CROP_SArid!$E$2</f>
+        <f>[20]NPP_2050_R4_CROP_SArid!$E$2</f>
         <v>0.72447113600000002</v>
       </c>
       <c r="E12" s="15">
-        <f>[65]filtered!$F$2</f>
+        <f>[21]filtered!$F$2</f>
         <v>0.98649141647533578</v>
       </c>
       <c r="F12">
         <f t="shared" ref="F12:F13" si="1">C12/C8</f>
-        <v>1.064028557330494</v>
+        <v>1.0640285569965051</v>
       </c>
       <c r="G12">
         <f t="shared" si="0"/>
-        <v>1.015063828197392</v>
+        <v>1.0144314696803183</v>
       </c>
       <c r="H12">
         <f t="shared" si="0"/>
-        <v>0.97057615112567097</v>
+        <v>0.96775446958686029</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
@@ -4399,28 +4400,28 @@
         <v>73</v>
       </c>
       <c r="C13" s="15">
-        <f>[23]NPP_2050_R4_SHRUB_Arid!$E$2</f>
+        <f>[22]NPP_2050_R4_SHRUB_Arid!$E$2</f>
         <v>0.21776707800273001</v>
       </c>
       <c r="D13" s="15">
-        <f>[24]NPP_2050_R4_SHRUB_SArid!$E$2</f>
+        <f>[23]NPP_2050_R4_SHRUB_SArid!$E$2</f>
         <v>0.51075241024303597</v>
       </c>
       <c r="E13" s="15">
-        <f>[66]filtered!$F$2</f>
+        <f>[24]filtered!$F$2</f>
         <v>0.90483097904137921</v>
       </c>
       <c r="F13">
         <f t="shared" si="1"/>
-        <v>1.083390554129495</v>
+        <v>1.0833884809510672</v>
       </c>
       <c r="G13">
         <f t="shared" si="0"/>
-        <v>1.0459975561677932</v>
+        <v>1.0457057214338692</v>
       </c>
       <c r="H13">
         <f t="shared" si="0"/>
-        <v>0.97612496285636041</v>
+        <v>0.9745600407449897</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
@@ -4444,20 +4445,20 @@
         <v>0.51337712420869996</v>
       </c>
       <c r="E15" s="15">
-        <f>[68]filtered!$F$2</f>
+        <f>[27]filtered!$F$2</f>
         <v>0.88457459938562355</v>
       </c>
       <c r="F15">
         <f>C15/C7</f>
-        <v>1.1540659951404126</v>
+        <v>1.1540659090900447</v>
       </c>
       <c r="G15">
         <f t="shared" ref="G15:H17" si="2">D15/D7</f>
-        <v>1.0680508847300958</v>
+        <v>1.0677382389668881</v>
       </c>
       <c r="H15">
         <f t="shared" si="2"/>
-        <v>1.0003477155836995</v>
+        <v>0.9983104252018099</v>
       </c>
       <c r="K15" t="s">
         <v>87</v>
@@ -4472,15 +4473,15 @@
         <v>72</v>
       </c>
       <c r="C16" s="15">
-        <f>[27]NPP_2050_R8_CROP_Arid!$E$2</f>
+        <f>[28]NPP_2050_R8_CROP_Arid!$E$2</f>
         <v>1.10532849796393</v>
       </c>
       <c r="D16" s="15">
-        <f>[28]NPP_2050_R8_CROP_SArid!$E$2</f>
+        <f>[29]NPP_2050_R8_CROP_SArid!$E$2</f>
         <v>0.80695680840268103</v>
       </c>
       <c r="E16" s="15">
-        <f>[69]filtered!$F$2</f>
+        <f>[30]filtered!$F$2</f>
         <v>1.0242825546815273</v>
       </c>
       <c r="F16">
@@ -4489,7 +4490,7 @@
       </c>
       <c r="G16">
         <f t="shared" si="2"/>
-        <v>1.1306353371781188</v>
+        <v>1.1299309805994404</v>
       </c>
       <c r="H16">
         <f>E16/E12</f>
@@ -4508,28 +4509,28 @@
         <v>73</v>
       </c>
       <c r="C17" s="15">
-        <f>[29]NPP_2050_R8_SHRUB_Arid!$E$2</f>
+        <f>[31]NPP_2050_R8_SHRUB_Arid!$E$2</f>
         <v>0.231319877140652</v>
       </c>
       <c r="D17" s="15">
-        <f>[30]NPP_2050_R8_SHRUB_SArid!$E$2</f>
+        <f>[32]NPP_2050_R8_SHRUB_SArid!$E$2</f>
         <v>0.51046846997934603</v>
       </c>
       <c r="E17" s="15">
-        <f>[70]filtered!$F$2</f>
+        <f>[33]filtered!$F$2</f>
         <v>0.93416975929597834</v>
       </c>
       <c r="F17">
-        <f t="shared" ref="F16:F17" si="3">C17/C9</f>
-        <v>1.1508156888316972</v>
+        <f t="shared" ref="F17" si="3">C17/C9</f>
+        <v>1.1508134866283908</v>
       </c>
       <c r="G17">
         <f t="shared" si="2"/>
-        <v>1.0454160595052988</v>
+        <v>1.0451243870097306</v>
       </c>
       <c r="H17">
         <f t="shared" si="2"/>
-        <v>1.0077754218366799</v>
+        <v>1.0061597577558092</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -4540,16 +4541,16 @@
         <v>74</v>
       </c>
       <c r="C20">
-        <f>10000*(1/1000)*(C2*C7+C3*C8*[31]Raster_logic!$I$84+C4*C9*[31]Raster_logic!$I$85)*(1/[31]Raster_logic!$I$79)*[31]Raster_logic!$I$80*[31]Raster_logic!$I$81/1000000</f>
-        <v>8.332489990808412</v>
+        <f>10000*(1/1000)*(C2*C7+C3*C8*[34]Raster_logic!$I$84+C4*C9*[34]Raster_logic!$I$85)*(1/[34]Raster_logic!$I$79)*[34]Raster_logic!$I$80*[34]Raster_logic!$I$81/1000000</f>
+        <v>8.3324944189563208</v>
       </c>
       <c r="D20">
-        <f>10000*(1/1000)*(D2*D7+D3*D8*[31]Raster_logic!$I$84+D4*D9*[31]Raster_logic!$I$85)*(1/[31]Raster_logic!$I$79)*[31]Raster_logic!$I$80*[31]Raster_logic!$I$81/1000000</f>
-        <v>12.693263986215754</v>
+        <f>10000*(1/1000)*(D2*D7+D3*D8*[34]Raster_logic!$I$84+D4*D9*[34]Raster_logic!$I$85)*(1/[34]Raster_logic!$I$79)*[34]Raster_logic!$I$80*[34]Raster_logic!$I$81/1000000</f>
+        <v>12.69703720354909</v>
       </c>
       <c r="E20">
-        <f>10000*(1/1000)*(E2*E7+E3*E8*[31]Raster_logic!$I$84+E4*E9*[31]Raster_logic!$I$85)*(1/[31]Raster_logic!$I$79)*[31]Raster_logic!$I$80*[31]Raster_logic!$I$81/1000000</f>
-        <v>8.3243209035088661</v>
+        <f>10000*(1/1000)*(E2*E7+E3*E8*[34]Raster_logic!$I$84+E4*E9*[34]Raster_logic!$I$85)*(1/[34]Raster_logic!$I$79)*[34]Raster_logic!$I$80*[34]Raster_logic!$I$81/1000000</f>
+        <v>8.341120928606971</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -4557,16 +4558,16 @@
         <v>75</v>
       </c>
       <c r="C21">
-        <f>10000*(1/1000)*(C3*C8*[31]Raster_logic!$I$91)*(1/[31]Raster_logic!$I$87)*[31]Raster_logic!$I$88*[31]Raster_logic!$I$89*[31]Raster_logic!$I$86/1000000</f>
+        <f>10000*(1/1000)*(C3*C8*[34]Raster_logic!$I$91)*(1/[34]Raster_logic!$I$87)*[34]Raster_logic!$I$88*[34]Raster_logic!$I$89*[34]Raster_logic!$I$86/1000000</f>
         <v>3.8150895733707002E-2</v>
       </c>
       <c r="D21">
-        <f>10000*(1/1000)*(D3*D8*[31]Raster_logic!$I$91)*(1/[31]Raster_logic!$I$87)*[31]Raster_logic!$I$88*[31]Raster_logic!$I$89*[31]Raster_logic!$I$86/1000000</f>
-        <v>1.0409906663058062</v>
+        <f>10000*(1/1000)*(D3*D8*[34]Raster_logic!$I$91)*(1/[34]Raster_logic!$I$87)*[34]Raster_logic!$I$88*[34]Raster_logic!$I$89*[34]Raster_logic!$I$86/1000000</f>
+        <v>1.041639580829564</v>
       </c>
       <c r="E21">
-        <f>10000*(1/1000)*(E3*E8*[31]Raster_logic!$I$91)*(1/[31]Raster_logic!$I$87)*[31]Raster_logic!$I$88*[31]Raster_logic!$I$89*[31]Raster_logic!$I$86/1000000</f>
-        <v>2.0531574736056535</v>
+        <f>10000*(1/1000)*(E3*E8*[34]Raster_logic!$I$91)*(1/[34]Raster_logic!$I$87)*[34]Raster_logic!$I$88*[34]Raster_logic!$I$89*[34]Raster_logic!$I$86/1000000</f>
+        <v>2.0591438644946747</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -4575,15 +4576,15 @@
       </c>
       <c r="C22">
         <f>SUM(C20:C21)</f>
-        <v>8.3706408865421196</v>
+        <v>8.3706453146900284</v>
       </c>
       <c r="D22">
         <f>SUM(D20:D21)</f>
-        <v>13.73425465252156</v>
+        <v>13.738676784378654</v>
       </c>
       <c r="E22">
         <f>SUM(E20:E21)</f>
-        <v>10.377478377114519</v>
+        <v>10.400264793101645</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -4595,28 +4596,28 @@
         <v>BIOM GRASS Supply (MT/ha/yr)</v>
       </c>
       <c r="C24">
-        <f>10000*(1/1000)*(C2*C11+C3*C12*[31]Raster_logic!$I$84+C4*C13*[31]Raster_logic!$I$85)*(1/[31]Raster_logic!$I$79)*[31]Raster_logic!$I$80*[31]Raster_logic!$I$81/1000000</f>
-        <v>8.9720704890776268</v>
+        <f>10000*(1/1000)*(C2*C11+C3*C12*[34]Raster_logic!$I$84+C4*C13*[34]Raster_logic!$I$85)*(1/[34]Raster_logic!$I$79)*[34]Raster_logic!$I$80*[34]Raster_logic!$I$81/1000000</f>
+        <v>9.0298868510117494</v>
       </c>
       <c r="D24">
-        <f>10000*(1/1000)*(D2*D11+D3*D12*[31]Raster_logic!$I$84+D4*D13*[31]Raster_logic!$I$85)*(1/[31]Raster_logic!$I$79)*[31]Raster_logic!$I$80*[31]Raster_logic!$I$81/1000000</f>
+        <f>10000*(1/1000)*(D2*D11+D3*D12*[34]Raster_logic!$I$84+D4*D13*[34]Raster_logic!$I$85)*(1/[34]Raster_logic!$I$79)*[34]Raster_logic!$I$80*[34]Raster_logic!$I$81/1000000</f>
         <v>13.359468018042634</v>
       </c>
       <c r="E24">
-        <f>10000*(1/1000)*(E2*E11+E3*E12*[31]Raster_logic!$I$84+E4*E13*[31]Raster_logic!$I$85)*(1/[31]Raster_logic!$I$79)*[31]Raster_logic!$I$80*[31]Raster_logic!$I$81/1000000</f>
+        <f>10000*(1/1000)*(E2*E11+E3*E12*[34]Raster_logic!$I$84+E4*E13*[34]Raster_logic!$I$85)*(1/[34]Raster_logic!$I$79)*[34]Raster_logic!$I$80*[34]Raster_logic!$I$81/1000000</f>
         <v>8.3696564117948942</v>
       </c>
       <c r="F24" s="13">
         <f>C24/C20</f>
-        <v>1.0767574277286547</v>
+        <v>1.0836955174513971</v>
       </c>
       <c r="G24" s="13">
         <f t="shared" ref="G24:H26" si="4">D24/D20</f>
-        <v>1.0524848480698379</v>
+        <v>1.0521720779323527</v>
       </c>
       <c r="H24" s="13">
         <f t="shared" si="4"/>
-        <v>1.0054461509607251</v>
+        <v>1.0034210609619694</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -4625,28 +4626,28 @@
         <v>BIOM CROP Supply (MT/ha/yr)</v>
       </c>
       <c r="C25">
-        <f>10000*(1/1000)*(C12*C3*[31]Raster_logic!$I$91)*(1/[31]Raster_logic!$I$87)*[31]Raster_logic!$I$88*[31]Raster_logic!$I$89*[31]Raster_logic!$I$86/1000000</f>
-        <v>4.0593642548402364E-2</v>
+        <f>10000*(1/1000)*(C12*C3*[34]Raster_logic!$I$91)*(1/[34]Raster_logic!$I$87)*[34]Raster_logic!$I$88*[34]Raster_logic!$I$89*[34]Raster_logic!$I$86/1000000</f>
+        <v>4.0593642535660383E-2</v>
       </c>
       <c r="D25">
-        <f>10000*(1/1000)*(D12*D3*[31]Raster_logic!$I$91)*(1/[31]Raster_logic!$I$87)*[31]Raster_logic!$I$88*[31]Raster_logic!$I$89*[31]Raster_logic!$I$86/1000000</f>
+        <f>10000*(1/1000)*(D12*D3*[34]Raster_logic!$I$91)*(1/[34]Raster_logic!$I$87)*[34]Raster_logic!$I$88*[34]Raster_logic!$I$89*[34]Raster_logic!$I$86/1000000</f>
         <v>1.0566719708581258</v>
       </c>
       <c r="E25">
-        <f>10000*(1/1000)*(E12*E3*[31]Raster_logic!$I$91)*(1/[31]Raster_logic!$I$87)*[31]Raster_logic!$I$88*[31]Raster_logic!$I$89*[31]Raster_logic!$I$86/1000000</f>
+        <f>10000*(1/1000)*(E12*E3*[34]Raster_logic!$I$91)*(1/[34]Raster_logic!$I$87)*[34]Raster_logic!$I$88*[34]Raster_logic!$I$89*[34]Raster_logic!$I$86/1000000</f>
         <v>1.9927456783870812</v>
       </c>
       <c r="F25" s="13">
         <f t="shared" ref="F25:F26" si="6">C25/C21</f>
-        <v>1.0640285573304942</v>
+        <v>1.0640285569965051</v>
       </c>
       <c r="G25" s="13">
         <f t="shared" si="4"/>
-        <v>1.0150638281973923</v>
+        <v>1.0144314696803187</v>
       </c>
       <c r="H25" s="13">
         <f t="shared" si="4"/>
-        <v>0.97057615112567075</v>
+        <v>0.96775446958686007</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -4656,7 +4657,7 @@
       </c>
       <c r="C26">
         <f>SUM(C24:C25)</f>
-        <v>9.0126641316260283</v>
+        <v>9.070480493547409</v>
       </c>
       <c r="D26">
         <f t="shared" ref="D26:E26" si="7">SUM(D24:D25)</f>
@@ -4668,15 +4669,15 @@
       </c>
       <c r="F26" s="13">
         <f t="shared" si="6"/>
-        <v>1.0766994133168608</v>
+        <v>1.0836058813326146</v>
       </c>
       <c r="G26" s="13">
         <f t="shared" si="4"/>
-        <v>1.0496485141444503</v>
+        <v>1.0493106588905567</v>
       </c>
       <c r="H26" s="13">
         <f t="shared" si="4"/>
-        <v>0.99854721095195997</v>
+        <v>0.99635944818012867</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -4688,28 +4689,28 @@
         <v>BIOM GRASS Supply (MT/ha/yr)</v>
       </c>
       <c r="C28">
-        <f>10000*(1/1000)*(C2*C15+C3*C16*[31]Raster_logic!$I$84+C4*C17*[31]Raster_logic!$I$85)*(1/[31]Raster_logic!$I$79)*[31]Raster_logic!$I$80*[31]Raster_logic!$I$81/1000000</f>
+        <f>10000*(1/1000)*(C2*C15+C3*C16*[34]Raster_logic!$I$84+C4*C17*[34]Raster_logic!$I$85)*(1/[34]Raster_logic!$I$79)*[34]Raster_logic!$I$80*[34]Raster_logic!$I$81/1000000</f>
         <v>9.609165818496594</v>
       </c>
       <c r="D28">
-        <f>10000*(1/1000)*(D2*D15+D3*D16*[31]Raster_logic!$I$84+D4*D17*[31]Raster_logic!$I$85)*(1/[31]Raster_logic!$I$79)*[31]Raster_logic!$I$80*[31]Raster_logic!$I$81/1000000</f>
+        <f>10000*(1/1000)*(D2*D15+D3*D16*[34]Raster_logic!$I$84+D4*D17*[34]Raster_logic!$I$85)*(1/[34]Raster_logic!$I$79)*[34]Raster_logic!$I$80*[34]Raster_logic!$I$81/1000000</f>
         <v>13.438099018999708</v>
       </c>
       <c r="E28">
-        <f>10000*(1/1000)*(E2*E15+E3*E16*[31]Raster_logic!$I$84+E4*E17*[31]Raster_logic!$I$85)*(1/[31]Raster_logic!$I$79)*[31]Raster_logic!$I$80*[31]Raster_logic!$I$81/1000000</f>
+        <f>10000*(1/1000)*(E2*E15+E3*E16*[34]Raster_logic!$I$84+E4*E17*[34]Raster_logic!$I$85)*(1/[34]Raster_logic!$I$79)*[34]Raster_logic!$I$80*[34]Raster_logic!$I$81/1000000</f>
         <v>8.3498054400644932</v>
       </c>
       <c r="F28" s="13">
         <f>C28/C20</f>
-        <v>1.1532166050120056</v>
+        <v>1.1532159921566658</v>
       </c>
       <c r="G28" s="13">
         <f t="shared" ref="G28:H28" si="8">D28/D20</f>
-        <v>1.058679551106225</v>
+        <v>1.0583649400699144</v>
       </c>
       <c r="H28" s="13">
         <f t="shared" si="8"/>
-        <v>1.0030614553248283</v>
+        <v>1.0010411683911375</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -4718,15 +4719,15 @@
         <v>BIOM CROP Supply (MT/ha/yr)</v>
       </c>
       <c r="C29">
-        <f>10000*(1/1000)*(C16*C3*[31]Raster_logic!$I$91)*(1/[31]Raster_logic!$I$87)*[31]Raster_logic!$I$88*[31]Raster_logic!$I$89*[31]Raster_logic!$I$86/1000000</f>
+        <f>10000*(1/1000)*(C16*C3*[34]Raster_logic!$I$91)*(1/[34]Raster_logic!$I$87)*[34]Raster_logic!$I$88*[34]Raster_logic!$I$89*[34]Raster_logic!$I$86/1000000</f>
         <v>4.3206647131559951E-2</v>
       </c>
       <c r="D29">
-        <f>10000*(1/1000)*(D16*D3*[31]Raster_logic!$I$91)*(1/[31]Raster_logic!$I$87)*[31]Raster_logic!$I$88*[31]Raster_logic!$I$89*[31]Raster_logic!$I$86/1000000</f>
+        <f>10000*(1/1000)*(D16*D3*[34]Raster_logic!$I$91)*(1/[34]Raster_logic!$I$87)*[34]Raster_logic!$I$88*[34]Raster_logic!$I$89*[34]Raster_logic!$I$86/1000000</f>
         <v>1.1769808329979399</v>
       </c>
       <c r="E29">
-        <f>10000*(1/1000)*(E16*E3*[31]Raster_logic!$I$91)*(1/[31]Raster_logic!$I$87)*[31]Raster_logic!$I$88*[31]Raster_logic!$I$89*[31]Raster_logic!$I$86/1000000</f>
+        <f>10000*(1/1000)*(E16*E3*[34]Raster_logic!$I$91)*(1/[34]Raster_logic!$I$87)*[34]Raster_logic!$I$88*[34]Raster_logic!$I$89*[34]Raster_logic!$I$86/1000000</f>
         <v>2.0690850424038385</v>
       </c>
       <c r="F29" s="13">
@@ -4735,11 +4736,11 @@
       </c>
       <c r="G29" s="13">
         <f t="shared" ref="G29:G30" si="11">D29/D21</f>
-        <v>1.130635337178119</v>
+        <v>1.1299309805994409</v>
       </c>
       <c r="H29" s="13">
         <f t="shared" ref="H29:H30" si="12">E29/E21</f>
-        <v>1.0077575972632113</v>
+        <v>1.0048278209602433</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -4761,15 +4762,15 @@
       </c>
       <c r="F30" s="13">
         <f t="shared" si="10"/>
-        <v>1.1531222753979014</v>
+        <v>1.153121665385674</v>
       </c>
       <c r="G30" s="13">
         <f t="shared" si="11"/>
-        <v>1.0641334547640975</v>
+        <v>1.0637909371749319</v>
       </c>
       <c r="H30" s="13">
         <f t="shared" si="12"/>
-        <v>1.0039905749594371</v>
+        <v>1.001790886072347</v>
       </c>
     </row>
   </sheetData>
@@ -4789,6 +4790,7 @@
     <col min="4" max="4" width="13.85546875" customWidth="1"/>
     <col min="5" max="5" width="9.28515625" customWidth="1"/>
     <col min="6" max="7" width="11.28515625" customWidth="1"/>
+    <col min="8" max="8" width="16.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -4901,8 +4903,8 @@
         <v>95</v>
       </c>
       <c r="I5">
-        <f>0.035</f>
-        <v>3.5000000000000003E-2</v>
+        <f>0.045</f>
+        <v>4.4999999999999998E-2</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -4925,7 +4927,7 @@
         <v>96</v>
       </c>
       <c r="I6">
-        <v>7.0000000000000007E-2</v>
+        <v>8.5000000000000006E-2</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -5021,20 +5023,20 @@
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B14" s="25" t="s">
+      <c r="B14" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="C14" s="26">
+      <c r="C14" s="25">
         <f>365*(C10+C11+C12)*(1-$I4)*($I7)/1000/1000000</f>
         <v>6.902100356153591</v>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="25">
         <f>365*(D10+D11+D12)*(1-$I5)*($I7)/1000/1000000</f>
-        <v>11.318639669754713</v>
-      </c>
-      <c r="E14" s="26">
+        <v>11.201348066959325</v>
+      </c>
+      <c r="E14" s="25">
         <f>365*(E10+E11+E12)*(1-$I6)*($I7)/1000/1000000</f>
-        <v>12.835059564163199</v>
+        <v>12.628042474418631</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -5046,15 +5048,15 @@
       </c>
       <c r="C16" s="19">
         <f>NPP!C22</f>
-        <v>8.3706408865421196</v>
+        <v>8.3706453146900284</v>
       </c>
       <c r="D16" s="19">
         <f>NPP!D22</f>
-        <v>13.73425465252156</v>
+        <v>13.738676784378654</v>
       </c>
       <c r="E16" s="19">
         <f>NPP!E22</f>
-        <v>10.377478377114519</v>
+        <v>10.400264793101645</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -5066,15 +5068,15 @@
       </c>
       <c r="C18" s="6">
         <f>C16/C14</f>
-        <v>1.2127671947104111</v>
+        <v>1.2127678362756855</v>
       </c>
       <c r="D18" s="6">
         <f t="shared" ref="D18" si="1">D16/D14</f>
-        <v>1.2134191964094212</v>
+        <v>1.2265199422651369</v>
       </c>
       <c r="E18" s="6">
         <f>E16/E14</f>
-        <v>0.80852592270701273</v>
+        <v>0.8235848758166654</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -5190,16 +5192,16 @@
         <v>83</v>
       </c>
       <c r="C27">
-        <f>C8+C8*30*Validate_2020!$G7/100</f>
-        <v>15.199336886489707</v>
+        <f>C8+C8*30*1.35*Validate_2020!$G7/100</f>
+        <v>18.584642590740373</v>
       </c>
       <c r="D27">
-        <f>D8+D8*30*Validate_2020!$G7/100</f>
-        <v>12.433816718442243</v>
+        <f>D8+D8*30*1.15*Validate_2020!$G7/100</f>
+        <v>14.122444247942596</v>
       </c>
       <c r="E27">
-        <f>E8+E8*30*Validate_2020!$G7/100</f>
-        <v>11.702970271460872</v>
+        <f>E8+E8*30*0.8*Validate_2020!$G7/100</f>
+        <v>11.512245654315745</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -5224,15 +5226,15 @@
         <v>65</v>
       </c>
       <c r="C31">
-        <f>C26*$I2*1000000</f>
+        <f t="shared" ref="C31:E32" si="2">C26*$I2*1000000</f>
         <v>4962518.3512414601</v>
       </c>
       <c r="D31">
-        <f>D26*$I2*1000000</f>
+        <f t="shared" si="2"/>
         <v>249046623.84190664</v>
       </c>
       <c r="E31">
-        <f>E26*$I2*1000000</f>
+        <f t="shared" si="2"/>
         <v>1046783279.5791441</v>
       </c>
     </row>
@@ -5241,33 +5243,33 @@
         <v>85</v>
       </c>
       <c r="C32">
-        <f>C27*$I3*1000000</f>
-        <v>531976791.02713972</v>
+        <f t="shared" si="2"/>
+        <v>650462490.6759131</v>
       </c>
       <c r="D32">
-        <f>D27*$I3*1000000</f>
-        <v>435183585.14547849</v>
+        <f t="shared" si="2"/>
+        <v>494285548.67799085</v>
       </c>
       <c r="E32">
-        <f>E27*$I3*1000000</f>
-        <v>409603959.50113052</v>
+        <f t="shared" si="2"/>
+        <v>402928597.9010511</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B34" s="25" t="s">
+      <c r="B34" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="C34" s="27">
+      <c r="C34" s="26">
         <f>365*(C30+C31+C32)*(1-$I4)*($I7)/1000/1000000</f>
-        <v>13.991163140959086</v>
-      </c>
-      <c r="D34" s="27">
+        <v>14.825835652134872</v>
+      </c>
+      <c r="D34" s="26">
         <f>365*(D30+D31+D32)*(1-$I5)*($I7)/1000/1000000</f>
-        <v>22.482777892787702</v>
-      </c>
-      <c r="E34" s="27">
+        <v>22.661825077225213</v>
+      </c>
+      <c r="E34" s="26">
         <f>365*(E30+E31+E32)*(1-$I6)*($I7)/1000/1000000</f>
-        <v>22.174123843905363</v>
+        <v>21.771888607324968</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -5279,15 +5281,15 @@
       <c r="B36" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="C36" s="28">
+      <c r="C36" s="27">
         <f>NPP!C26</f>
-        <v>9.0126641316260283</v>
-      </c>
-      <c r="D36" s="28">
+        <v>9.070480493547409</v>
+      </c>
+      <c r="D36" s="27">
         <f>NPP!D26</f>
         <v>14.41613998890076</v>
       </c>
-      <c r="E36" s="28">
+      <c r="E36" s="27">
         <f>NPP!E26</f>
         <v>10.362402090181975</v>
       </c>
@@ -5296,46 +5298,46 @@
       <c r="B37" s="1"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B38" s="20" t="s">
+      <c r="B38" s="30" t="s">
         <v>82</v>
       </c>
-      <c r="C38" s="20"/>
-      <c r="D38" s="20"/>
-      <c r="E38" s="20"/>
+      <c r="C38" s="30"/>
+      <c r="D38" s="30"/>
+      <c r="E38" s="30"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B39" s="21">
+      <c r="B39" s="20">
         <v>2050</v>
       </c>
-      <c r="C39" s="22">
+      <c r="C39" s="21">
         <f>C36/C34</f>
-        <v>0.64416832545119018</v>
-      </c>
-      <c r="D39" s="22">
-        <f t="shared" ref="D39:E39" si="2">D36/D34</f>
-        <v>0.64120813084780526</v>
-      </c>
-      <c r="E39" s="22">
-        <f t="shared" si="2"/>
-        <v>0.46731957317132594</v>
+        <v>0.61180230958794479</v>
+      </c>
+      <c r="D39" s="21">
+        <f t="shared" ref="D39:E39" si="3">D36/D34</f>
+        <v>0.63614205562767134</v>
+      </c>
+      <c r="E39" s="21">
+        <f t="shared" si="3"/>
+        <v>0.47595329358315902</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
-      <c r="B40" s="21" t="s">
+      <c r="B40" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="C40" s="22">
+      <c r="C40" s="21">
         <f>(C39+C18)/2</f>
-        <v>0.92846776008080067</v>
-      </c>
-      <c r="D40" s="22">
-        <f t="shared" ref="D40:E40" si="3">(D39+D18)/2</f>
-        <v>0.92731366362861323</v>
-      </c>
-      <c r="E40" s="22">
-        <f t="shared" si="3"/>
-        <v>0.63792274793916937</v>
+        <v>0.91228507293181516</v>
+      </c>
+      <c r="D40" s="21">
+        <f t="shared" ref="D40:E40" si="4">(D39+D18)/2</f>
+        <v>0.93133099894640414</v>
+      </c>
+      <c r="E40" s="21">
+        <f t="shared" si="4"/>
+        <v>0.64976908469991224</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -5354,20 +5356,20 @@
       <c r="A43" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B43" s="29" t="s">
+      <c r="B43" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="C43" s="30">
+      <c r="C43" s="29">
         <f>C34</f>
-        <v>13.991163140959086</v>
-      </c>
-      <c r="D43" s="30">
-        <f t="shared" ref="D43:E43" si="4">D34</f>
-        <v>22.482777892787702</v>
-      </c>
-      <c r="E43" s="30">
-        <f t="shared" si="4"/>
-        <v>22.174123843905363</v>
+        <v>14.825835652134872</v>
+      </c>
+      <c r="D43" s="29">
+        <f t="shared" ref="D43:E43" si="5">D34</f>
+        <v>22.661825077225213</v>
+      </c>
+      <c r="E43" s="29">
+        <f t="shared" si="5"/>
+        <v>21.771888607324968</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -5377,18 +5379,18 @@
       <c r="E44" s="3"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B45" s="23" t="s">
+      <c r="B45" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="C45" s="24">
+      <c r="C45" s="23">
         <f>NPP!C30</f>
         <v>9.6523724656281544</v>
       </c>
-      <c r="D45" s="24">
+      <c r="D45" s="23">
         <f>NPP!D30</f>
         <v>14.615079851997647</v>
       </c>
-      <c r="E45" s="24">
+      <c r="E45" s="23">
         <f>NPP!E30</f>
         <v>10.418890482468331</v>
       </c>
@@ -5400,45 +5402,45 @@
       <c r="E46" s="3"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B47" s="20" t="s">
+      <c r="B47" s="30" t="s">
         <v>82</v>
       </c>
-      <c r="C47" s="20"/>
-      <c r="D47" s="20"/>
-      <c r="E47" s="20"/>
+      <c r="C47" s="30"/>
+      <c r="D47" s="30"/>
+      <c r="E47" s="30"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B48" s="21">
+      <c r="B48" s="20">
         <v>2050</v>
       </c>
-      <c r="C48" s="22">
+      <c r="C48" s="21">
         <f>C45/C43</f>
-        <v>0.68989063799641248</v>
-      </c>
-      <c r="D48" s="22">
-        <f t="shared" ref="D48:E48" si="5">D45/D43</f>
-        <v>0.65005667545584078</v>
-      </c>
-      <c r="E48" s="22">
+        <v>0.65105082048027718</v>
+      </c>
+      <c r="D48" s="21">
+        <f t="shared" ref="D48" si="6">D45/D43</f>
+        <v>0.64492068940579628</v>
+      </c>
+      <c r="E48" s="21">
         <f>E45/E43</f>
-        <v>0.46986706468368539</v>
+        <v>0.47854784995376948</v>
       </c>
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B49" s="21" t="s">
+      <c r="B49" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="C49" s="22">
+      <c r="C49" s="21">
         <f>(C18+C48)*0.5</f>
-        <v>0.95132891635341177</v>
-      </c>
-      <c r="D49" s="22">
-        <f t="shared" ref="D49:E49" si="6">(D18+D48)*0.5</f>
-        <v>0.93173793593263099</v>
-      </c>
-      <c r="E49" s="22">
-        <f t="shared" si="6"/>
-        <v>0.63919649369534903</v>
+        <v>0.93190932837798135</v>
+      </c>
+      <c r="D49" s="21">
+        <f t="shared" ref="D49:E49" si="7">(D18+D48)*0.5</f>
+        <v>0.93572031583546655</v>
+      </c>
+      <c r="E49" s="21">
+        <f t="shared" si="7"/>
+        <v>0.65106636288521746</v>
       </c>
     </row>
   </sheetData>

--- a/Rasterized animal populations/Zonal statistics/Summary.xlsx
+++ b/Rasterized animal populations/Zonal statistics/Summary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JHawkins\Documents\Github\KE.beef.spatial\Rasterized animal populations\Zonal statistics\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hawkj\Documents\Github\KE.beef.spatial\Rasterized animal populations\Zonal statistics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08A47564-C67D-49E3-9C3A-DC6484DD3231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E748AAA3-24B6-420B-BD72-338543E05A68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" activeTab="5" xr2:uid="{3882C52B-09A6-47D1-94BA-1F6173569800}"/>
+    <workbookView xWindow="-192" yWindow="-192" windowWidth="23424" windowHeight="12624" activeTab="5" xr2:uid="{3882C52B-09A6-47D1-94BA-1F6173569800}"/>
   </bookViews>
   <sheets>
     <sheet name="Validate_2020" sheetId="2" r:id="rId1"/>
@@ -19,9 +19,9 @@
     <sheet name="ZS_Summary" sheetId="6" r:id="rId4"/>
     <sheet name="NPP" sheetId="8" r:id="rId5"/>
     <sheet name="Carrying_Capacity" sheetId="7" r:id="rId6"/>
+    <sheet name="Beef_population_to_GIS" sheetId="9" r:id="rId7"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId7"/>
     <externalReference r:id="rId8"/>
     <externalReference r:id="rId9"/>
     <externalReference r:id="rId10"/>
@@ -91,6 +91,7 @@
     <externalReference r:id="rId74"/>
     <externalReference r:id="rId75"/>
     <externalReference r:id="rId76"/>
+    <externalReference r:id="rId77"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -135,7 +136,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="119">
   <si>
     <t>Arid</t>
   </si>
@@ -426,6 +427,72 @@
   </si>
   <si>
     <t>FRAC Fed -- Humid/Subhumid</t>
+  </si>
+  <si>
+    <t>breed</t>
+  </si>
+  <si>
+    <t>farm.type</t>
+  </si>
+  <si>
+    <t>aez</t>
+  </si>
+  <si>
+    <t>cohort</t>
+  </si>
+  <si>
+    <t>scenario</t>
+  </si>
+  <si>
+    <t>zebu</t>
+  </si>
+  <si>
+    <t>pastoral</t>
+  </si>
+  <si>
+    <t>arid</t>
+  </si>
+  <si>
+    <t>male.finisher</t>
+  </si>
+  <si>
+    <t>baseline</t>
+  </si>
+  <si>
+    <t>female.finisher</t>
+  </si>
+  <si>
+    <t>female.breeder</t>
+  </si>
+  <si>
+    <t>semi.arid</t>
+  </si>
+  <si>
+    <t>boran</t>
+  </si>
+  <si>
+    <t>agro-pastoral</t>
+  </si>
+  <si>
+    <t>humid.subhumid</t>
+  </si>
+  <si>
+    <t>mixed</t>
+  </si>
+  <si>
+    <t>cow-calf</t>
+  </si>
+  <si>
+    <t>beef</t>
+  </si>
+  <si>
+    <t>finisher</t>
+  </si>
+  <si>
+    <t>population.M.hd</t>
+  </si>
+  <si>
+    <t>Pixel adjustment</t>
   </si>
 </sst>
 </file>
@@ -480,7 +547,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -502,6 +569,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -573,11 +646,11 @@
     <xf numFmtId="167" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -596,707 +669,6 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="ZS_Grassland_Arid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1">
-        <row r="2">
-          <cell r="D2">
-            <v>202419</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink10.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2020_GRASS_Arid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.33293323112310402</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink11.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2020_GRASS_SArid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.48080803465972</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink12.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2020_CROP_Arid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.97599038751874501</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2020_CROP_SArid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.71416468993051396</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2020_SHRUB_Arid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.20100553202445001</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2020_SHRUB_SArid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.48842843619779902</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink16.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R4_GRASS_Arid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.36084903504638699</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink17.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R4_GRASS_SArid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.51075241024303597</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink18.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R4_GRASS_Humid"/>
-      <sheetName val="filtered"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="2">
-          <cell r="F2">
-            <v>0.90483097904137921</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink19.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R4_CROP_Arid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>1.0384816436740301</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="ZS_Grassland_SArid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="D2">
-            <v>129806</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink20.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R4_CROP_SArid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.72447113600000002</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink21.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R4_CROP_Humid"/>
-      <sheetName val="filtered"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="2">
-          <cell r="F2">
-            <v>0.98649141647533578</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink22.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R4_SHRUB_Arid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.21776707800273001</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink23.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R4_SHRUB_SArid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.51075241024303597</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink24.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R4_SHRUB_Humid"/>
-      <sheetName val="filtered"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="2">
-          <cell r="F2">
-            <v>0.90483097904137921</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink25.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R8_GRASS_Arid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.38422689204237098</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink26.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R8_GRASS_SArid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.51337712420869996</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink27.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R8_GRASS_Humid"/>
-      <sheetName val="filtered"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="2">
-          <cell r="F2">
-            <v>0.88457459938562355</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink28.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R8_CROP_Arid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>1.10532849796393</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink29.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R8_CROP_SArid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.80695680840268103</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="ZS_Grassland_Humid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>64439.636684333513</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink30.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R8_CROP_Humid"/>
-      <sheetName val="filtered"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="2">
-          <cell r="F2">
-            <v>1.0242825546815273</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink31.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R8_SHRUB_Arid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.231319877140652</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink32.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R8_SHRUB_SArid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.51046846997934603</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink33.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R8_SHRUB_Humid"/>
-      <sheetName val="filtered"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="2">
-          <cell r="F2">
-            <v>0.93416975929597834</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink34.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Raster_logic"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="79">
-          <cell r="I79">
-            <v>0.5</v>
-          </cell>
-        </row>
-        <row r="80">
-          <cell r="I80">
-            <v>0.44</v>
-          </cell>
-        </row>
-        <row r="81">
-          <cell r="I81">
-            <v>0.3</v>
-          </cell>
-        </row>
-        <row r="84">
-          <cell r="I84">
-            <v>0.34</v>
-          </cell>
-        </row>
-        <row r="85">
-          <cell r="I85">
-            <v>0.4</v>
-          </cell>
-        </row>
-        <row r="86">
-          <cell r="I86">
-            <v>0.85</v>
-          </cell>
-        </row>
-        <row r="87">
-          <cell r="I87">
-            <v>0.4</v>
-          </cell>
-        </row>
-        <row r="88">
-          <cell r="I88">
-            <v>0.5</v>
-          </cell>
-        </row>
-        <row r="89">
-          <cell r="I89">
-            <v>0.5</v>
-          </cell>
-        </row>
-        <row r="91">
-          <cell r="I91">
-            <v>0.4</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink35.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1363,7 +735,231 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink10.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Dairy_total_Humid_2020"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1">
+        <row r="2">
+          <cell r="D2">
+            <v>5233916.3978957208</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink11.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Sheep_total_Arid_2020"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1">
+        <row r="2">
+          <cell r="C2">
+            <v>1300620.48691654</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink12.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Sheep_total_SArid_2020"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1">
+        <row r="2">
+          <cell r="C2">
+            <v>1063972.5190212701</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Sheep_total_Humid_2020"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1">
+        <row r="2">
+          <cell r="D2">
+            <v>1001433.3524225579</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Pastoral_Zebu_2020"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>7912803.5780913802</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Pastoral_Boran_2020"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1">
+        <row r="2">
+          <cell r="K2">
+            <v>1124203.7226895699</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink16.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Pastoral_Zebu_2050"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>8554757.4814370908</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink17.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Pastoral_Boran_2050"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>1215408.67359516</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink18.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Agpastoral_Zebu_2020"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>3685141.0110471202</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink19.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Agpastoral_Boran_2020"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>277376.20390618598</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1373,7 +969,7 @@
       <sheetName val="Arid_Subsistence"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0">
+      <sheetData sheetId="0" refreshError="1">
         <row r="2">
           <cell r="C2">
             <v>220785.65217611199</v>
@@ -1385,7 +981,227 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink20.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Agpastoral_Zebu_2050"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>6488770.1197828101</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink21.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Agpastoral_Boran_2050"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>488402.05019366002</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink22.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Mixed_Zebu_2020"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>298374.71550379699</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink23.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Mixed_Boran_2020"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>25945.627401560501</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink24.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Mixed_Zebu_2050"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>404262.59496554697</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink25.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Mixed_Boran_2050"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>35153.269665965803</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink26.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Cowcalf_Boran_2020"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>1184753.34766715</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink27.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Cowcalf_Exotic_2020"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>985977.36353097099</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink28.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Cowcalf_Boran_2050"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>1806208.69891036</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink29.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Cowcalf_Exotic_2050"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>1503165.94333724</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1395,7 +1211,7 @@
       <sheetName val="SArid_Subsistence"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0">
+      <sheetData sheetId="0" refreshError="1">
         <row r="2">
           <cell r="C2">
             <v>467695.362210333</v>
@@ -1407,20 +1223,20 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink30.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="Humid_Subsistence"/>
+      <sheetName val="Finisher_Boran_2020"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="2">
-          <cell r="D2">
-            <v>589697.33266333945</v>
+          <cell r="K2">
+            <v>26321.876059999999</v>
           </cell>
         </row>
       </sheetData>
@@ -1429,20 +1245,20 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink39.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink31.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="Arid_Commercial"/>
+      <sheetName val="Finisher_Exotic_2020"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="2">
-          <cell r="C2">
-            <v>4580694.9930214901</v>
+          <cell r="K2">
+            <v>12386.7653238613</v>
           </cell>
         </row>
       </sheetData>
@@ -1451,7 +1267,120 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink32.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Finisher_Boran_2050"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>918345.45531155204</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink33.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Finisher_Exotic_2050"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>432162.57168335503</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink34.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="ZS_Grassland_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1">
+        <row r="2">
+          <cell r="D2">
+            <v>202419</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink35.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="ZS_Grassland_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="D2">
+            <v>129806</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink36.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="ZS_Grassland_Humid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>64439.636684333513</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink37.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1474,233 +1403,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink40.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="SArid_Commercial"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="C2">
-            <v>5931614.2707009297</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink41.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Humid_Commercial"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="D2">
-            <v>4968107.5438200859</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink42.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Dairy_total_Arid_2020"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="C2">
-            <v>24812.591756207301</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink43.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Dairy_total_SArid_2020"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="C2">
-            <v>1210306.62197518</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink44.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Dairy_total_Humid_2020"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="D2">
-            <v>5233916.3978957208</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink45.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Sheep_total_Arid_2020"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="C2">
-            <v>1300620.48691654</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink46.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Sheep_total_SArid_2020"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="C2">
-            <v>1063972.5190212701</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink47.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Sheep_total_Humid_2020"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="D2">
-            <v>1001433.3524225579</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink48.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Pastoral_Zebu_2020"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>7912803.5780913802</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink49.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Pastoral_Boran_2020"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1">
-        <row r="2">
-          <cell r="K2">
-            <v>1124203.7226895699</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink38.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1723,227 +1426,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink50.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Pastoral_Zebu_2050"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>8554757.4814370908</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink51.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Pastoral_Boran_2050"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>1215408.67359516</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink52.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Agpastoral_Zebu_2020"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>3685141.0110471202</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink53.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Agpastoral_Boran_2020"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>277376.20390618598</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink54.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Agpastoral_Zebu_2050"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>6488770.1197828101</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink55.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Agpastoral_Boran_2050"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>488402.05019366002</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink56.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Mixed_Zebu_2020"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>298374.71550379699</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink57.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Mixed_Boran_2020"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>25945.627401560501</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink58.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Mixed_Zebu_2050"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>404262.59496554697</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink59.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Mixed_Boran_2050"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>35153.269665965803</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink39.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1966,20 +1449,43 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink60.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="Cowcalf_Boran_2020"/>
+      <sheetName val="Humid_Subsistence"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1">
+        <row r="2">
+          <cell r="D2">
+            <v>589697.33266333945</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink40.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="ZS_Shrubland_Arid"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="2">
-          <cell r="K2">
-            <v>1184753.34766715</v>
+          <cell r="D2">
+            <v>277889</v>
           </cell>
         </row>
       </sheetData>
@@ -1988,20 +1494,21 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink61.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink41.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="Cowcalf_Exotic_2020"/>
+      <sheetName val="ZS_Shrubland_SArid"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="2">
-          <cell r="K2">
-            <v>985977.36353097099</v>
+          <cell r="D2">
+            <v>357491</v>
           </cell>
         </row>
       </sheetData>
@@ -2010,20 +1517,21 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink62.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink42.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="Cowcalf_Boran_2050"/>
+      <sheetName val="ZS_Shrubland_Humid"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="2">
-          <cell r="K2">
-            <v>1806208.69891036</v>
+          <cell r="E2">
+            <v>63327.68656939434</v>
           </cell>
         </row>
       </sheetData>
@@ -2032,20 +1540,21 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink63.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink43.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="Cowcalf_Exotic_2050"/>
+      <sheetName val="NPP_2020_GRASS_Arid"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="2">
-          <cell r="K2">
-            <v>1503165.94333724</v>
+          <cell r="E2">
+            <v>0.33293323112310402</v>
           </cell>
         </row>
       </sheetData>
@@ -2054,20 +1563,21 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink64.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink44.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="Finisher_Boran_2020"/>
+      <sheetName val="NPP_2020_GRASS_SArid"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="2">
-          <cell r="K2">
-            <v>26321.876059999999</v>
+          <cell r="E2">
+            <v>0.48080803465972</v>
           </cell>
         </row>
       </sheetData>
@@ -2076,73 +1586,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink65.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Finisher_Exotic_2020"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>12386.7653238613</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink66.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Finisher_Boran_2050"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>918345.45531155204</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink67.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Finisher_Exotic_2050"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>432162.57168335503</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink68.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink45.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2167,7 +1611,53 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink69.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink46.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2020_CROP_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.97599038751874501</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink47.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2020_CROP_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.71416468993051396</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink48.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2192,7 +1682,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink49.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2200,13 +1690,13 @@
       <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="ZS_Shrubland_Arid"/>
+      <sheetName val="NPP_2020_SHRUB_Arid"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="2">
-          <cell r="D2">
-            <v>277889</v>
+          <cell r="E2">
+            <v>0.20100553202445001</v>
           </cell>
         </row>
       </sheetData>
@@ -2215,7 +1705,52 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink70.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Arid_Commercial"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1">
+        <row r="2">
+          <cell r="C2">
+            <v>4580694.9930214901</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink50.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2020_SHRUB_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.48842843619779902</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink51.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2240,6 +1775,544 @@
 </externalLink>
 </file>
 
+<file path=xl/externalLinks/externalLink52.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R4_GRASS_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.36084903504638699</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink53.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R4_GRASS_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.51075241024303597</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink54.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R4_GRASS_Humid"/>
+      <sheetName val="filtered"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="F2">
+            <v>0.90483097904137921</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink55.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R4_CROP_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>1.0384816436740301</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink56.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R4_CROP_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.72447113600000002</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink57.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R4_CROP_Humid"/>
+      <sheetName val="filtered"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="F2">
+            <v>0.98649141647533578</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink58.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R4_SHRUB_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.21776707800273001</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink59.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R4_SHRUB_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.51075241024303597</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="SArid_Commercial"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1">
+        <row r="2">
+          <cell r="C2">
+            <v>5931614.2707009297</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink60.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R4_SHRUB_Humid"/>
+      <sheetName val="filtered"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="F2">
+            <v>0.90483097904137921</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink61.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R8_GRASS_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.38422689204237098</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink62.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R8_GRASS_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.51337712420869996</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink63.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R8_GRASS_Humid"/>
+      <sheetName val="filtered"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="F2">
+            <v>0.88457459938562355</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink64.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R8_CROP_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>1.10532849796393</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink65.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R8_CROP_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.80695680840268103</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink66.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R8_CROP_Humid"/>
+      <sheetName val="filtered"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="F2">
+            <v>1.0242825546815273</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink67.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R8_SHRUB_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.231319877140652</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink68.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R8_SHRUB_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.51046846997934603</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink69.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R8_SHRUB_Humid"/>
+      <sheetName val="filtered"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="F2">
+            <v>0.93416975929597834</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Humid_Commercial"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1">
+        <row r="2">
+          <cell r="D2">
+            <v>4968107.5438200859</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink70.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Raster_logic"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="79">
+          <cell r="I79">
+            <v>0.5</v>
+          </cell>
+        </row>
+        <row r="80">
+          <cell r="I80">
+            <v>0.44</v>
+          </cell>
+        </row>
+        <row r="81">
+          <cell r="I81">
+            <v>0.3</v>
+          </cell>
+        </row>
+        <row r="84">
+          <cell r="I84">
+            <v>0.34</v>
+          </cell>
+        </row>
+        <row r="85">
+          <cell r="I85">
+            <v>0.4</v>
+          </cell>
+        </row>
+        <row r="86">
+          <cell r="I86">
+            <v>0.85</v>
+          </cell>
+        </row>
+        <row r="87">
+          <cell r="I87">
+            <v>0.4</v>
+          </cell>
+        </row>
+        <row r="88">
+          <cell r="I88">
+            <v>0.5</v>
+          </cell>
+        </row>
+        <row r="89">
+          <cell r="I89">
+            <v>0.5</v>
+          </cell>
+        </row>
+        <row r="91">
+          <cell r="I91">
+            <v>0.4</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
@@ -2248,13 +2321,13 @@
       <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="ZS_Shrubland_SArid"/>
+      <sheetName val="Dairy_total_Arid_2020"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0">
+      <sheetData sheetId="0" refreshError="1">
         <row r="2">
-          <cell r="D2">
-            <v>357491</v>
+          <cell r="C2">
+            <v>24812.591756207301</v>
           </cell>
         </row>
       </sheetData>
@@ -2271,13 +2344,13 @@
       <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="ZS_Shrubland_Humid"/>
+      <sheetName val="Dairy_total_SArid_2020"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0">
+      <sheetData sheetId="0" refreshError="1">
         <row r="2">
-          <cell r="E2">
-            <v>63327.68656939434</v>
+          <cell r="C2">
+            <v>1210306.62197518</v>
           </cell>
         </row>
       </sheetData>
@@ -2625,9 +2698,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DC88038-24E0-4487-8E9E-ADD8D4CE8257}">
   <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" t="s">
         <v>3</v>
       </c>
@@ -2650,20 +2723,20 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>13</v>
       </c>
       <c r="B2">
         <f>Herd_decision_tree!E10</f>
-        <v>6.99195979776652</v>
+        <v>8.7399497472081507</v>
       </c>
       <c r="C2" s="6">
         <f>B2/$B$8</f>
-        <v>0.51509165724121786</v>
+        <v>0.51509165724121797</v>
       </c>
       <c r="D2">
-        <f>[35]FAO_2019_animal_trends!$F$35</f>
+        <f>[1]FAO_2019_animal_trends!$F$35</f>
         <v>0.53615960099750615</v>
       </c>
       <c r="E2">
@@ -2675,28 +2748,28 @@
         <v>0.52629975213940838</v>
       </c>
       <c r="G2">
-        <f>[35]FAO_2019_animal_trends!$G$35</f>
+        <f>[1]FAO_2019_animal_trends!$G$35</f>
         <v>0.38312009613345605</v>
       </c>
       <c r="H2">
         <f>ABS(F2-C2)</f>
-        <v>1.1208094898190524E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1.1208094898190413E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>16</v>
       </c>
       <c r="B3">
         <f>Herd_decision_tree!E14</f>
-        <v>4.5255644973891247</v>
+        <v>5.6569556217364063</v>
       </c>
       <c r="C3" s="6">
         <f t="shared" ref="C3:C6" si="0">B3/$B$8</f>
         <v>0.33339443937546859</v>
       </c>
       <c r="D3">
-        <f>[35]FAO_2019_animal_trends!$F$36</f>
+        <f>[1]FAO_2019_animal_trends!$F$36</f>
         <v>0.36159600997506236</v>
       </c>
       <c r="E3">
@@ -2708,7 +2781,7 @@
         <v>0.31358889061540685</v>
       </c>
       <c r="G3">
-        <f>[35]FAO_2019_animal_trends!$G$36</f>
+        <f>[1]FAO_2019_animal_trends!$G$36</f>
         <v>2.7950424483806726</v>
       </c>
       <c r="H3">
@@ -2716,20 +2789,20 @@
         <v>1.9805548760061742E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>11</v>
       </c>
       <c r="B4">
         <f>Herd_decision_tree!E18</f>
-        <v>0.7785024521166074</v>
+        <v>0.97312806514575934</v>
       </c>
       <c r="C4" s="6">
         <f t="shared" si="0"/>
         <v>5.7351605247385556E-2</v>
       </c>
       <c r="D4">
-        <f>[35]FAO_2019_animal_trends!$F$39</f>
+        <f>[1]FAO_2019_animal_trends!$F$39</f>
         <v>4.9875311720698257E-2</v>
       </c>
       <c r="E4">
@@ -2741,7 +2814,7 @@
         <v>4.6666186084097429E-2</v>
       </c>
       <c r="G4">
-        <f>[35]FAO_2019_animal_trends!$G$40</f>
+        <f>[1]FAO_2019_animal_trends!$G$40</f>
         <v>1.354588821344141</v>
       </c>
       <c r="H4">
@@ -2749,20 +2822,20 @@
         <v>1.0685419163288128E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>42</v>
       </c>
       <c r="B5">
         <f>Herd_decision_tree!E29</f>
-        <v>0.6916275166390542</v>
+        <v>0.86453439579881786</v>
       </c>
       <c r="C5" s="6">
         <f t="shared" si="0"/>
         <v>5.0951603562285619E-2</v>
       </c>
       <c r="D5">
-        <f>[35]FAO_2019_animal_trends!$F$38</f>
+        <f>[1]FAO_2019_animal_trends!$F$38</f>
         <v>4.9875311720698257E-2</v>
       </c>
       <c r="E5">
@@ -2774,7 +2847,7 @@
         <v>4.7418024088714393E-2</v>
       </c>
       <c r="G5">
-        <f>[35]FAO_2019_animal_trends!$G$38</f>
+        <f>[1]FAO_2019_animal_trends!$G$38</f>
         <v>1.0372340425531916</v>
       </c>
       <c r="H5">
@@ -2782,20 +2855,20 @@
         <v>3.5335794735712259E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>23</v>
       </c>
       <c r="B6">
         <f>Herd_decision_tree!E25</f>
-        <v>0.5865508304107302</v>
+        <v>0.73318853801341277</v>
       </c>
       <c r="C6" s="6">
         <f t="shared" si="0"/>
         <v>4.3210694573642398E-2</v>
       </c>
       <c r="D6">
-        <f>[35]FAO_2019_animal_trends!$F$37</f>
+        <f>[1]FAO_2019_animal_trends!$F$37</f>
         <v>2.4937655860349127E-3</v>
       </c>
       <c r="E6">
@@ -2807,7 +2880,7 @@
         <v>-7.7485333020033496E-3</v>
       </c>
       <c r="G6">
-        <f>[35]FAO_2019_animal_trends!$G$37</f>
+        <f>[1]FAO_2019_animal_trends!$G$37</f>
         <v>86.466565349544069</v>
       </c>
       <c r="H6">
@@ -2815,7 +2888,7 @@
         <v>5.0959227875645746E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>83</v>
       </c>
@@ -2826,10 +2899,10 @@
         <v>2.2776119402985073</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B8">
         <f>SUM(B2:B6)</f>
-        <v>13.574205094322036</v>
+        <v>16.967756367902545</v>
       </c>
       <c r="D8">
         <f>SUM(D2:D6)</f>
@@ -2837,7 +2910,7 @@
       </c>
       <c r="H8">
         <f>SUM(H2:H6)</f>
-        <v>9.6191870170757365E-2</v>
+        <v>9.6191870170757254E-2</v>
       </c>
     </row>
   </sheetData>
@@ -2848,18 +2921,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDE56320-BEC2-4269-9329-43A80C09A702}">
   <dimension ref="A1:K53"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="18.5703125" customWidth="1"/>
-    <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.42578125" customWidth="1"/>
-    <col min="8" max="8" width="31.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.578125" customWidth="1"/>
+    <col min="2" max="2" width="17.83984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.68359375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.26171875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.26171875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.41796875" customWidth="1"/>
+    <col min="8" max="8" width="31.68359375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="3"/>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -2880,25 +2953,25 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="2" t="s">
         <v>79</v>
       </c>
       <c r="B2" s="8">
-        <f>[36]Arid_Subsistence!$C$2/1000000</f>
-        <v>0.22078565217611199</v>
+        <f>[2]Arid_Subsistence!$C$2/1000000*$H$18</f>
+        <v>0.27598206522013996</v>
       </c>
       <c r="C2" s="8">
-        <f>[37]SArid_Subsistence!$C$2/1000000</f>
-        <v>0.46769536221033298</v>
+        <f>[3]SArid_Subsistence!$C$2/1000000*$H$18</f>
+        <v>0.58461920276291623</v>
       </c>
       <c r="D2" s="8">
-        <f>[38]Humid_Subsistence!$D$2/1000000</f>
-        <v>0.58969733266333946</v>
+        <f>[4]Humid_Subsistence!$D$2/1000000*$H$18</f>
+        <v>0.73712166582917438</v>
       </c>
       <c r="E2" s="9">
         <f>SUM(B2:D2)</f>
-        <v>1.2781783470497845</v>
+        <v>1.5977229338122305</v>
       </c>
       <c r="G2" t="s">
         <v>7</v>
@@ -2913,25 +2986,25 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="2" t="s">
         <v>80</v>
       </c>
       <c r="B3" s="8">
-        <f>[39]Arid_Commercial!$C$2/1000000</f>
-        <v>4.5806949930214902</v>
+        <f>[5]Arid_Commercial!$C$2/1000000*$H$18</f>
+        <v>5.7258687412768623</v>
       </c>
       <c r="C3" s="8">
-        <f>[40]SArid_Commercial!$C$2/1000000</f>
-        <v>5.9316142707009298</v>
+        <f>[6]SArid_Commercial!$C$2/1000000*$H$18</f>
+        <v>7.4145178383761623</v>
       </c>
       <c r="D3" s="8">
-        <f>[41]Humid_Commercial!$D$2/1000000</f>
-        <v>4.9681075438200857</v>
+        <f>[7]Humid_Commercial!$D$2/1000000*$H$18</f>
+        <v>6.2101344297751071</v>
       </c>
       <c r="E3" s="9">
         <f>SUM(B3:D3)</f>
-        <v>15.480416807542506</v>
+        <v>19.350521009428132</v>
       </c>
       <c r="H3" t="s">
         <v>6</v>
@@ -2943,67 +3016,67 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="2" t="s">
         <v>61</v>
       </c>
       <c r="B4" s="8">
-        <f>[42]Dairy_total_Arid_2020!$C$2/1000000</f>
-        <v>2.48125917562073E-2</v>
+        <f>[8]Dairy_total_Arid_2020!$C$2/1000000*$H$18</f>
+        <v>3.1015739695259125E-2</v>
       </c>
       <c r="C4" s="8">
-        <f>[43]Dairy_total_SArid_2020!$C$2/1000000</f>
-        <v>1.2103066219751799</v>
+        <f>[9]Dairy_total_SArid_2020!$C$2/1000000*$H$18</f>
+        <v>1.5128832774689749</v>
       </c>
       <c r="D4" s="8">
-        <f>[44]Dairy_total_Humid_2020!$D$2/1000000</f>
-        <v>5.2339163978957206</v>
+        <f>[10]Dairy_total_Humid_2020!$D$2/1000000*$H$18</f>
+        <v>6.5423954973696503</v>
       </c>
       <c r="E4" s="9"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="2" t="s">
         <v>83</v>
       </c>
       <c r="B5" s="8">
-        <f>9.78*0.76*[45]Sheep_total_Arid_2020!$C$2/1000000</f>
-        <v>9.6672519551532563</v>
+        <f>9.78*0.76*[11]Sheep_total_Arid_2020!$C$2/1000000*$H$18</f>
+        <v>12.08406494394157</v>
       </c>
       <c r="C5" s="8">
-        <f>9.78*0.76*[46]Sheep_total_SArid_2020!$C$2/1000000</f>
-        <v>7.908294939381296</v>
+        <f>9.78*0.76*[12]Sheep_total_SArid_2020!$C$2/1000000*$H$18</f>
+        <v>9.8853686742266191</v>
       </c>
       <c r="D5" s="8">
-        <f>9.78*0.76*[47]Sheep_total_Humid_2020!$D$2/1000000</f>
-        <v>7.4434538218863873</v>
+        <f>9.78*0.76*[13]Sheep_total_Humid_2020!$D$2/1000000*$H$18</f>
+        <v>9.3043172773579848</v>
       </c>
       <c r="E5" s="9">
         <f>SUM(B5:D5)</f>
-        <v>25.01900071642094</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+        <v>31.273750895526174</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="2" t="s">
         <v>81</v>
       </c>
       <c r="B6" s="8">
         <f>SUM(B2:B3)</f>
-        <v>4.8014806451976018</v>
+        <v>6.0018508064970026</v>
       </c>
       <c r="C6" s="8">
         <f>SUM(C2:C3)</f>
-        <v>6.3993096329112626</v>
+        <v>7.999137041139079</v>
       </c>
       <c r="D6" s="8">
         <f>SUM(D2:D3)</f>
-        <v>5.5578048764834254</v>
+        <v>6.9472560956042813</v>
       </c>
       <c r="E6" s="9">
         <f>SUM(B6:D6)</f>
-        <v>16.758595154592292</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+        <v>20.948243943240364</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
@@ -3022,7 +3095,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="5" t="s">
         <v>33</v>
       </c>
@@ -3041,7 +3114,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
@@ -3060,40 +3133,40 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B10" s="9">
         <f>B3*I7</f>
-        <v>3.5231517722606158</v>
+        <v>4.4039397153257696</v>
       </c>
       <c r="C10" s="9">
         <f>C3*I8</f>
-        <v>3.4688080255059042</v>
+        <v>4.3360100318823802</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="9">
         <f t="shared" ref="E10:E20" si="0">SUM(B10:D10)</f>
-        <v>6.99195979776652</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+        <v>8.7399497472081507</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="3" t="s">
         <v>14</v>
       </c>
       <c r="B11" s="9">
         <f>B10*(1-I11)</f>
-        <v>3.0848716917913954</v>
+        <v>3.8560896147392438</v>
       </c>
       <c r="C11" s="9">
         <f>C10*(1-I11)</f>
-        <v>3.0372883071329699</v>
+        <v>3.7966103839162124</v>
       </c>
       <c r="D11" s="9"/>
       <c r="E11" s="9">
         <f t="shared" si="0"/>
-        <v>6.1221599989243654</v>
+        <v>7.6526999986554562</v>
       </c>
       <c r="G11" t="s">
         <v>47</v>
@@ -3109,22 +3182,22 @@
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="3" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="9">
         <f>B10*(I11)</f>
-        <v>0.43828008046922062</v>
+        <v>0.54785010058652572</v>
       </c>
       <c r="C12" s="9">
         <f>C10*(I11)</f>
-        <v>0.43151971837293446</v>
+        <v>0.53939964796616813</v>
       </c>
       <c r="D12" s="9"/>
       <c r="E12" s="9">
         <f t="shared" si="0"/>
-        <v>0.86979979884215508</v>
+        <v>1.087249748552694</v>
       </c>
       <c r="H12" t="s">
         <v>10</v>
@@ -3137,7 +3210,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
@@ -3153,67 +3226,67 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="3" t="s">
         <v>16</v>
       </c>
       <c r="B14" s="9"/>
       <c r="C14" s="9">
         <f>C3*(1-I8)</f>
-        <v>2.4628062451950257</v>
+        <v>3.0785078064937821</v>
       </c>
       <c r="D14" s="9">
         <f>D3*(1-I8)</f>
-        <v>2.062758252194099</v>
+        <v>2.5784478152426238</v>
       </c>
       <c r="E14" s="9">
         <f t="shared" si="0"/>
-        <v>4.5255644973891247</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+        <v>5.6569556217364063</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B15" s="9"/>
       <c r="C15" s="9">
         <f>C14*(1-I12)</f>
-        <v>2.2904098080313737</v>
+        <v>2.8630122600392172</v>
       </c>
       <c r="D15" s="9">
         <f>D14*(1-I12)</f>
-        <v>1.9183651745405119</v>
+        <v>2.3979564681756398</v>
       </c>
       <c r="E15" s="9">
         <f t="shared" si="0"/>
-        <v>4.2087749825718852</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+        <v>5.2609687282148574</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="3" t="s">
         <v>18</v>
       </c>
       <c r="B16" s="9"/>
       <c r="C16" s="9">
         <f>C14*(I12)</f>
-        <v>0.1723964371636518</v>
+        <v>0.21549554645456476</v>
       </c>
       <c r="D16" s="9">
         <f>D14*(I12)</f>
-        <v>0.14439307765358694</v>
+        <v>0.18049134706698369</v>
       </c>
       <c r="E16" s="9">
         <f t="shared" si="0"/>
-        <v>0.31678951481723872</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.39598689352154848</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="3" t="s">
         <v>11</v>
       </c>
@@ -3221,14 +3294,20 @@
       <c r="C18" s="9"/>
       <c r="D18" s="9">
         <f>D3*I9</f>
-        <v>0.7785024521166074</v>
+        <v>0.97312806514575934</v>
       </c>
       <c r="E18" s="9">
         <f t="shared" si="0"/>
-        <v>0.7785024521166074</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.97312806514575934</v>
+      </c>
+      <c r="G18" t="s">
+        <v>118</v>
+      </c>
+      <c r="H18">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="3" t="s">
         <v>19</v>
       </c>
@@ -3236,14 +3315,14 @@
       <c r="C19" s="9"/>
       <c r="D19" s="9">
         <f>D$18*(1-I13)</f>
-        <v>0.71622225594727884</v>
+        <v>0.89527781993409861</v>
       </c>
       <c r="E19" s="9">
         <f t="shared" si="0"/>
-        <v>0.71622225594727884</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.89527781993409861</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="3" t="s">
         <v>20</v>
       </c>
@@ -3251,286 +3330,286 @@
       <c r="C20" s="9"/>
       <c r="D20" s="9">
         <f>D$18*(I13)</f>
-        <v>6.2280196169328596E-2</v>
+        <v>7.7850245211660743E-2</v>
       </c>
       <c r="E20" s="9">
         <f t="shared" si="0"/>
-        <v>6.2280196169328596E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+        <v>7.7850245211660743E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B21" s="9"/>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="3" t="s">
         <v>28</v>
       </c>
       <c r="B23" s="9">
         <f>SUM(B15:B16)+SUM(B11:B12)</f>
-        <v>3.5231517722606158</v>
+        <v>4.4039397153257696</v>
       </c>
       <c r="C23" s="9">
         <f>SUM(C15:C16)+SUM(C11:C12)</f>
-        <v>5.9316142707009298</v>
+        <v>7.4145178383761623</v>
       </c>
       <c r="D23" s="9">
         <f>SUM(D15:D16)+SUM(D19:D20)</f>
-        <v>2.8412607043107063</v>
+        <v>3.5515758803883828</v>
       </c>
       <c r="E23" s="9">
         <f>SUM(B23:D23)</f>
-        <v>12.296026747272251</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+        <v>15.370033434090315</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="3"/>
       <c r="B24" s="9"/>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="3" t="s">
         <v>23</v>
       </c>
       <c r="B25" s="9">
         <f>B6*$I2</f>
-        <v>0.16805182258191609</v>
+        <v>0.21006477822739511</v>
       </c>
       <c r="C25" s="9">
         <f t="shared" ref="C25:D25" si="1">C6*$I2</f>
-        <v>0.2239758371518942</v>
+        <v>0.2799697964398678</v>
       </c>
       <c r="D25" s="9">
         <f t="shared" si="1"/>
-        <v>0.1945231706769199</v>
+        <v>0.24315396334614986</v>
       </c>
       <c r="E25" s="9">
         <f>SUM(B25:D25)</f>
-        <v>0.5865508304107302</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.73318853801341277</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B26" s="9">
         <f>B25*$I3</f>
-        <v>0.11427523935570295</v>
+        <v>0.14284404919462868</v>
       </c>
       <c r="C26" s="9">
         <f t="shared" ref="C26:D26" si="2">C25*$I3</f>
-        <v>0.15230356926328806</v>
+        <v>0.19037946157911012</v>
       </c>
       <c r="D26" s="9">
         <f t="shared" si="2"/>
-        <v>0.13227575606030553</v>
+        <v>0.16534469507538191</v>
       </c>
       <c r="E26" s="9">
         <f>SUM(B26:D26)</f>
-        <v>0.39885456467929659</v>
+        <v>0.4985682058491207</v>
       </c>
       <c r="G26">
         <f>E26*E49</f>
-        <v>0.48827647518794509</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.48827647518794504</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="3" t="s">
         <v>25</v>
       </c>
       <c r="B27" s="9">
         <f>B25*(1-$I3)</f>
-        <v>5.3776583226213141E-2</v>
+        <v>6.7220729032766421E-2</v>
       </c>
       <c r="C27" s="9">
         <f t="shared" ref="C27:D27" si="3">C25*(1-$I3)</f>
-        <v>7.1672267888606131E-2</v>
+        <v>8.9590334860757681E-2</v>
       </c>
       <c r="D27" s="9">
         <f t="shared" si="3"/>
-        <v>6.2247414616614358E-2</v>
+        <v>7.7809268270767937E-2</v>
       </c>
       <c r="E27" s="9">
         <f t="shared" ref="E27:E31" si="4">SUM(B27:D27)</f>
-        <v>0.18769626573143361</v>
+        <v>0.23462033216429207</v>
       </c>
       <c r="G27">
         <f>E27*1.21</f>
-        <v>0.22711248153503466</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.28389060191879339</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="3"/>
       <c r="B28" s="9"/>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B29" s="9">
         <f>B2-B25</f>
-        <v>5.2733829594195897E-2</v>
+        <v>6.591728699274485E-2</v>
       </c>
       <c r="C29" s="9">
         <f t="shared" ref="C29:D29" si="5">C2-C25</f>
-        <v>0.24371952505843877</v>
+        <v>0.30464940632304843</v>
       </c>
       <c r="D29" s="9">
         <f t="shared" si="5"/>
-        <v>0.39517416198641953</v>
+        <v>0.49396770248302452</v>
       </c>
       <c r="E29" s="9">
         <f t="shared" si="4"/>
-        <v>0.6916275166390542</v>
+        <v>0.86453439579881786</v>
       </c>
       <c r="G29">
         <f>22*E49</f>
-        <v>26.932329238282836</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+        <v>21.545863390626266</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="3" t="s">
         <v>26</v>
       </c>
       <c r="B30" s="9">
         <f>B29*($I3)</f>
-        <v>3.5859004124053212E-2</v>
+        <v>4.4823755155066501E-2</v>
       </c>
       <c r="C30" s="9">
         <f t="shared" ref="C30" si="6">C29*($I3)</f>
-        <v>0.16572927703973839</v>
+        <v>0.20716159629967296</v>
       </c>
       <c r="D30" s="9">
         <f>D29*($I3)</f>
-        <v>0.2687184301507653</v>
+        <v>0.33589803768845672</v>
       </c>
       <c r="E30" s="9">
         <f t="shared" si="4"/>
-        <v>0.47030671131455692</v>
+        <v>0.58788338914319616</v>
       </c>
       <c r="G30">
         <f>E30*E49</f>
-        <v>0.5757479632771676</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.57574796327716748</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="3" t="s">
         <v>27</v>
       </c>
       <c r="B31" s="9">
         <f>B29*(1-$I3)</f>
-        <v>1.6874825470142685E-2</v>
+        <v>2.1093531837678349E-2</v>
       </c>
       <c r="C31" s="9">
         <f t="shared" ref="C31:D31" si="7">C29*(1-$I3)</f>
-        <v>7.79902480187004E-2</v>
+        <v>9.748781002337549E-2</v>
       </c>
       <c r="D31" s="9">
         <f t="shared" si="7"/>
-        <v>0.12645573183565423</v>
+        <v>0.15806966479456783</v>
       </c>
       <c r="E31" s="9">
         <f t="shared" si="4"/>
-        <v>0.22132080532449733</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.2766510066556217</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="3"/>
       <c r="B32" s="9"/>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="3" t="s">
         <v>29</v>
       </c>
       <c r="B33" s="9">
         <f>SUM(B11:B12,B15:B16,B26:B27,B30:B31)</f>
-        <v>3.7439374244367278</v>
+        <v>4.6799217805459099</v>
       </c>
       <c r="C33" s="9">
         <f>SUM(C11:C12,C15:C16,C26:C27,C30:C31)</f>
-        <v>6.3993096329112626</v>
+        <v>7.999137041139079</v>
       </c>
       <c r="D33" s="9">
         <f>SUM(D11:D12,D15:D16,D30:D31,D19:D20)</f>
-        <v>3.2364348662971261</v>
+        <v>4.0455435828714066</v>
       </c>
       <c r="E33" s="9">
         <f>SUM(B33:D33)</f>
-        <v>13.379681923645116</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+        <v>16.724602404556396</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="3"/>
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="3" t="s">
         <v>61</v>
       </c>
       <c r="B35" s="9">
         <f>B4</f>
-        <v>2.48125917562073E-2</v>
+        <v>3.1015739695259125E-2</v>
       </c>
       <c r="C35" s="9">
         <f t="shared" ref="C35:D35" si="8">C4</f>
-        <v>1.2103066219751799</v>
+        <v>1.5128832774689749</v>
       </c>
       <c r="D35" s="9">
         <f t="shared" si="8"/>
-        <v>5.2339163978957206</v>
+        <v>6.5423954973696503</v>
       </c>
       <c r="E35" s="9">
         <f t="shared" ref="E35" si="9">SUM(B35:D35)</f>
-        <v>6.4690356116271079</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+        <v>8.0862945145338845</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="3"/>
       <c r="B36" s="9"/>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
       <c r="E36" s="9"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="3"/>
       <c r="B37" s="9"/>
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
       <c r="E37" s="9"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="3"/>
       <c r="B38" s="9"/>
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
       <c r="E38" s="9"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B39" s="9"/>
       <c r="C39" s="9"/>
       <c r="D39" s="9"/>
       <c r="E39" s="9"/>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="2" t="s">
         <v>35</v>
       </c>
@@ -3539,7 +3618,7 @@
       <c r="D40" s="9"/>
       <c r="E40" s="9"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="4" t="s">
         <v>31</v>
       </c>
@@ -3549,166 +3628,166 @@
       <c r="E41" s="9"/>
       <c r="G41" s="3"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="3" t="s">
         <v>21</v>
       </c>
       <c r="B42" s="9">
         <f>SUM(B11,B15)</f>
-        <v>3.0848716917913954</v>
+        <v>3.8560896147392438</v>
       </c>
       <c r="C42" s="9">
         <f>SUM(C11,C15)</f>
-        <v>5.3276981151643437</v>
+        <v>6.65962264395543</v>
       </c>
       <c r="D42" s="9">
         <f>SUM(D15,D19)</f>
-        <v>2.634587430487791</v>
+        <v>3.2932342881097383</v>
       </c>
       <c r="E42" s="9">
         <f>SUM(B42:D42)</f>
-        <v>11.04715723744353</v>
+        <v>13.808946546804412</v>
       </c>
       <c r="F42">
         <f>E42/E$46</f>
-        <v>0.81758574893750713</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.81758574893750702</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="3" t="s">
         <v>48</v>
       </c>
       <c r="B43" s="9">
         <f>SUM(B12,B16)</f>
-        <v>0.43828008046922062</v>
+        <v>0.54785010058652572</v>
       </c>
       <c r="C43" s="9">
         <f>SUM(C12,C16)</f>
-        <v>0.60391615553658629</v>
+        <v>0.75489519442073294</v>
       </c>
       <c r="D43" s="9">
         <f>SUM(D12,D16)</f>
-        <v>0.14439307765358694</v>
+        <v>0.18049134706698369</v>
       </c>
       <c r="E43" s="10">
         <f>SUM(B43:D43)</f>
-        <v>1.1865893136593939</v>
+        <v>1.4832366420742424</v>
       </c>
       <c r="F43">
         <f>E43/E$46</f>
-        <v>8.7817932870661489E-2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+        <v>8.7817932870661475E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="3" t="s">
         <v>49</v>
       </c>
       <c r="B44" s="9">
         <f>SUM(B26,B30)</f>
-        <v>0.15013424347975618</v>
+        <v>0.18766780434969518</v>
       </c>
       <c r="C44" s="9">
         <f t="shared" ref="C44:D44" si="10">SUM(C26,C30)</f>
-        <v>0.31803284630302642</v>
+        <v>0.39754105787878308</v>
       </c>
       <c r="D44" s="9">
         <f t="shared" si="10"/>
-        <v>0.40099418621107086</v>
+        <v>0.50124273276383868</v>
       </c>
       <c r="E44" s="9">
         <f>SUM(B44:D44)</f>
-        <v>0.8691612759938534</v>
+        <v>1.086451594992317</v>
       </c>
       <c r="F44">
         <f>E44/E$46</f>
-        <v>6.4325496370445448E-2</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+        <v>6.4325496370445462E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="3" t="s">
         <v>32</v>
       </c>
       <c r="B45" s="9">
         <f>SUM(B27,B31)</f>
-        <v>7.0651408696355833E-2</v>
+        <v>8.8314260870444777E-2</v>
       </c>
       <c r="C45" s="9">
         <f t="shared" ref="C45" si="11">SUM(C27,C31)</f>
-        <v>0.14966251590730653</v>
+        <v>0.18707814488413316</v>
       </c>
       <c r="D45" s="9">
         <f>SUM(D27,D31)</f>
-        <v>0.1887031464522686</v>
+        <v>0.23587893306533575</v>
       </c>
       <c r="E45" s="9">
         <f t="shared" ref="E45" si="12">SUM(B45:D45)</f>
-        <v>0.40901707105593099</v>
+        <v>0.51127133881991371</v>
       </c>
       <c r="F45">
         <f>E45/E$46</f>
-        <v>3.0270821821386091E-2</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+        <v>3.0270821821386087E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="3" t="s">
         <v>30</v>
       </c>
       <c r="B46" s="9">
         <f>SUM(B42:B45)</f>
-        <v>3.7439374244367278</v>
+        <v>4.6799217805459099</v>
       </c>
       <c r="C46" s="9">
         <f t="shared" ref="C46:D46" si="13">SUM(C42:C45)</f>
-        <v>6.3993096329112626</v>
+        <v>7.999137041139079</v>
       </c>
       <c r="D46" s="9">
         <f t="shared" si="13"/>
-        <v>3.3686778408047173</v>
+        <v>4.210847301005896</v>
       </c>
       <c r="E46" s="9">
         <f>SUM(B46:D46)</f>
-        <v>13.511924898152706</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+        <v>16.889906122690885</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="4"/>
       <c r="E48">
         <f>16.541255</f>
         <v>16.541255</v>
       </c>
     </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="E49">
         <f>E48/E46</f>
-        <v>1.2241967835583107</v>
-      </c>
-    </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
+        <v>0.9793574268466485</v>
+      </c>
+    </row>
+    <row r="52" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B52">
         <f>B29/B2</f>
-        <v>0.23884627046386242</v>
+        <v>0.23884627046386236</v>
       </c>
       <c r="C52">
         <f t="shared" ref="C52:D52" si="14">C29/C2</f>
-        <v>0.52110742323083525</v>
+        <v>0.52110742323083514</v>
       </c>
       <c r="D52">
         <f t="shared" si="14"/>
-        <v>0.67013048914709272</v>
-      </c>
-    </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
+        <v>0.67013048914709283</v>
+      </c>
+    </row>
+    <row r="53" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B53">
         <f>B25/B2</f>
-        <v>0.76115372953613758</v>
+        <v>0.76115372953613769</v>
       </c>
       <c r="C53">
         <f t="shared" ref="C53:D53" si="15">C25/C2</f>
-        <v>0.47889257676916475</v>
+        <v>0.4788925767691648</v>
       </c>
       <c r="D53">
         <f t="shared" si="15"/>
-        <v>0.32986951085290722</v>
+        <v>0.32986951085290717</v>
       </c>
     </row>
   </sheetData>
@@ -3720,12 +3799,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD6A4001-CB5D-4E56-8C0D-2957A97A30B1}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="2" max="2" width="16.140625" customWidth="1"/>
+    <col min="2" max="2" width="16.15625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B1">
         <v>2020</v>
       </c>
@@ -3739,7 +3818,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -3748,7 +3827,7 @@
         <v>8.5595346951947899</v>
       </c>
       <c r="C2">
-        <f>[35]FAO_2019_animal_trends!$G$35/100</f>
+        <f>[1]FAO_2019_animal_trends!$G$35/100</f>
         <v>3.8312009613345605E-3</v>
       </c>
       <c r="D2">
@@ -3760,7 +3839,7 @@
         <v>9.543333621778995</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -3769,7 +3848,7 @@
         <v>5.5401815014894495</v>
       </c>
       <c r="C3">
-        <f>[35]FAO_2019_animal_trends!$G36/100</f>
+        <f>[1]FAO_2019_animal_trends!$G36/100</f>
         <v>2.7950424483806725E-2</v>
       </c>
       <c r="D3">
@@ -3781,49 +3860,49 @@
         <v>10.185694242008363</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="7">
         <f>Validate_2020!B4*Herd_decision_tree!E49</f>
-        <v>0.95304019787340866</v>
+        <v>0.95304019787340855</v>
       </c>
       <c r="C4">
-        <f>[35]FAO_2019_animal_trends!$G39/100</f>
+        <f>[1]FAO_2019_animal_trends!$G39/100</f>
         <v>7.6101823708206687E-2</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
-        <v>2.1758429137618971</v>
+        <v>2.1758429137618966</v>
       </c>
       <c r="E4">
         <f t="shared" si="1"/>
-        <v>3.1288831116353055</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>3.1288831116353051</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>42</v>
       </c>
       <c r="B5" s="7">
         <f>Validate_2020!B5*Herd_decision_tree!E49</f>
-        <v>0.84668818128995216</v>
+        <v>0.84668818128995227</v>
       </c>
       <c r="C5">
-        <f>[35]FAO_2019_animal_trends!$G38/100</f>
+        <f>[1]FAO_2019_animal_trends!$G38/100</f>
         <v>1.0372340425531916E-2</v>
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
-        <v>0.26346414151841596</v>
+        <v>0.26346414151841602</v>
       </c>
       <c r="E5">
         <f t="shared" si="1"/>
-        <v>1.1101523228083681</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1.1101523228083683</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -3832,7 +3911,7 @@
         <v>0.71805363998227212</v>
       </c>
       <c r="C6">
-        <f>[35]FAO_2019_animal_trends!$G37/100</f>
+        <f>[1]FAO_2019_animal_trends!$G37/100</f>
         <v>0.86466565349544067</v>
       </c>
       <c r="D6">
@@ -3844,25 +3923,25 @@
         <v>19.344343235783811</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>61</v>
       </c>
       <c r="B7">
         <f>Herd_decision_tree!E35</f>
-        <v>6.4690356116271079</v>
+        <v>8.0862945145338845</v>
       </c>
       <c r="C7">
-        <f>[35]FAO_2019_animal_trends!$G39/100</f>
+        <f>[1]FAO_2019_animal_trends!$G39/100</f>
         <v>7.6101823708206687E-2</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
-        <v>14.769162230344715</v>
+        <v>18.461452787930895</v>
       </c>
       <c r="E7">
         <f t="shared" si="1"/>
-        <v>21.238197841971825</v>
+        <v>26.547747302464778</v>
       </c>
     </row>
   </sheetData>
@@ -3873,9 +3952,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95E5D3D0-4020-4418-A256-3E770B560826}">
   <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="B1">
         <v>2020</v>
       </c>
@@ -3886,7 +3965,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="B2" t="s">
         <v>54</v>
       </c>
@@ -3915,16 +3994,16 @@
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>13</v>
       </c>
       <c r="B3">
-        <f>[48]Pastoral_Zebu_2020!$K$2</f>
+        <f>[14]Pastoral_Zebu_2020!$K$2</f>
         <v>7912803.5780913802</v>
       </c>
       <c r="C3">
-        <f>[49]Pastoral_Boran_2020!$K$2</f>
+        <f>[15]Pastoral_Boran_2020!$K$2</f>
         <v>1124203.7226895699</v>
       </c>
       <c r="D3">
@@ -3936,11 +4015,11 @@
         <v>8.5595346951947899</v>
       </c>
       <c r="G3">
-        <f>[50]Pastoral_Zebu_2050!$K$2</f>
+        <f>[16]Pastoral_Zebu_2050!$K$2</f>
         <v>8554757.4814370908</v>
       </c>
       <c r="H3">
-        <f>[51]Pastoral_Boran_2050!$K$2</f>
+        <f>[17]Pastoral_Boran_2050!$K$2</f>
         <v>1215408.67359516</v>
       </c>
       <c r="I3">
@@ -3960,16 +4039,16 @@
         <v>1.1149360288400367</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>16</v>
       </c>
       <c r="B4">
-        <f>[52]Agpastoral_Zebu_2020!$K$2</f>
+        <f>[18]Agpastoral_Zebu_2020!$K$2</f>
         <v>3685141.0110471202</v>
       </c>
       <c r="C4">
-        <f>[53]Agpastoral_Boran_2020!$K$2</f>
+        <f>[19]Agpastoral_Boran_2020!$K$2</f>
         <v>277376.20390618598</v>
       </c>
       <c r="D4">
@@ -3981,11 +4060,11 @@
         <v>5.5401815014894495</v>
       </c>
       <c r="G4">
-        <f>[54]Agpastoral_Zebu_2050!$K$2</f>
+        <f>[20]Agpastoral_Zebu_2050!$K$2</f>
         <v>6488770.1197828101</v>
       </c>
       <c r="H4">
-        <f>[55]Agpastoral_Boran_2050!$K$2</f>
+        <f>[21]Agpastoral_Boran_2050!$K$2</f>
         <v>488402.05019366002</v>
       </c>
       <c r="I4">
@@ -4005,16 +4084,16 @@
         <v>1.8385127345142016</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>11</v>
       </c>
       <c r="B5">
-        <f>[56]Mixed_Zebu_2020!$K$2</f>
+        <f>[22]Mixed_Zebu_2020!$K$2</f>
         <v>298374.71550379699</v>
       </c>
       <c r="C5">
-        <f>[57]Mixed_Boran_2020!$K$2</f>
+        <f>[23]Mixed_Boran_2020!$K$2</f>
         <v>25945.627401560501</v>
       </c>
       <c r="D5">
@@ -4023,14 +4102,14 @@
       </c>
       <c r="E5">
         <f>Herd_decision_tree!E18*Herd_decision_tree!$E$49</f>
-        <v>0.95304019787340866</v>
+        <v>0.95304019787340855</v>
       </c>
       <c r="G5">
-        <f>[58]Mixed_Zebu_2050!$K$2</f>
+        <f>[24]Mixed_Zebu_2050!$K$2</f>
         <v>404262.59496554697</v>
       </c>
       <c r="H5">
-        <f>[59]Mixed_Boran_2050!$K$2</f>
+        <f>[25]Mixed_Boran_2050!$K$2</f>
         <v>35153.269665965803</v>
       </c>
       <c r="I5">
@@ -4043,23 +4122,23 @@
       </c>
       <c r="L5">
         <f>E5+E5*30*Validate_2020!G4/100</f>
-        <v>1.3403334773726869</v>
+        <v>1.3403334773726867</v>
       </c>
       <c r="M5">
         <f t="shared" si="2"/>
         <v>1.4063766464032423</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>42</v>
       </c>
       <c r="B6">
-        <f>[60]Cowcalf_Boran_2020!$K$2</f>
+        <f>[26]Cowcalf_Boran_2020!$K$2</f>
         <v>1184753.34766715</v>
       </c>
       <c r="C6">
-        <f>[61]Cowcalf_Exotic_2020!$K$2</f>
+        <f>[27]Cowcalf_Exotic_2020!$K$2</f>
         <v>985977.36353097099</v>
       </c>
       <c r="D6">
@@ -4068,14 +4147,14 @@
       </c>
       <c r="E6">
         <f>Herd_decision_tree!E29*Herd_decision_tree!$E$49</f>
-        <v>0.84668818128995216</v>
+        <v>0.84668818128995227</v>
       </c>
       <c r="G6">
-        <f>[62]Cowcalf_Boran_2050!$K$2</f>
+        <f>[28]Cowcalf_Boran_2050!$K$2</f>
         <v>1806208.69891036</v>
       </c>
       <c r="H6">
-        <f>[63]Cowcalf_Exotic_2050!$K$2</f>
+        <f>[29]Cowcalf_Exotic_2050!$K$2</f>
         <v>1503165.94333724</v>
       </c>
       <c r="I6">
@@ -4092,19 +4171,19 @@
       </c>
       <c r="M6">
         <f t="shared" si="2"/>
-        <v>1.3111702127659577</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1.3111702127659575</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>23</v>
       </c>
       <c r="B7">
-        <f>[64]Finisher_Boran_2020!$K$2</f>
+        <f>[30]Finisher_Boran_2020!$K$2</f>
         <v>26321.876059999999</v>
       </c>
       <c r="C7">
-        <f>[65]Finisher_Exotic_2020!$K$2</f>
+        <f>[31]Finisher_Exotic_2020!$K$2</f>
         <v>12386.7653238613</v>
       </c>
       <c r="D7">
@@ -4116,11 +4195,11 @@
         <v>0.71805363998227212</v>
       </c>
       <c r="G7">
-        <f>[66]Finisher_Boran_2050!$K$2</f>
+        <f>[32]Finisher_Boran_2050!$K$2</f>
         <v>918345.45531155204</v>
       </c>
       <c r="H7">
-        <f>[67]Finisher_Exotic_2050!$K$2</f>
+        <f>[33]Finisher_Exotic_2050!$K$2</f>
         <v>432162.57168335503</v>
       </c>
       <c r="I7">
@@ -4140,7 +4219,7 @@
         <v>26.939969604863222</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="D8">
         <f>SUM(D3:D7)</f>
         <v>15.533284211221597</v>
@@ -4182,20 +4261,20 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C89891AA-CE3C-44BE-AF6B-8649852BC25F}">
   <dimension ref="A1:L30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="17.7109375" customWidth="1"/>
-    <col min="2" max="2" width="32.85546875" customWidth="1"/>
-    <col min="3" max="3" width="16.42578125" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" customWidth="1"/>
-    <col min="6" max="6" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.42578125" customWidth="1"/>
-    <col min="12" max="12" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.68359375" customWidth="1"/>
+    <col min="2" max="2" width="32.83984375" customWidth="1"/>
+    <col min="3" max="3" width="16.41796875" customWidth="1"/>
+    <col min="4" max="4" width="15.68359375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.26171875" customWidth="1"/>
+    <col min="6" max="6" width="12.26171875" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="11.578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.41796875" customWidth="1"/>
+    <col min="12" max="12" width="9.578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>67</v>
       </c>
@@ -4209,7 +4288,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>92</v>
       </c>
@@ -4217,63 +4296,63 @@
         <v>89</v>
       </c>
       <c r="C2" s="12">
-        <f>[1]ZS_Grassland_Arid!$D$2*L15</f>
+        <f>[34]ZS_Grassland_Arid!$D$2*L15</f>
         <v>7105918.9949999992</v>
       </c>
       <c r="D2" s="12">
-        <f>[2]ZS_Grassland_SArid!$D$2*L15</f>
+        <f>[35]ZS_Grassland_SArid!$D$2*L15</f>
         <v>4556839.63</v>
       </c>
       <c r="E2" s="12">
-        <f>[3]ZS_Grassland_Humid!$E$2*L15</f>
+        <f>[36]ZS_Grassland_Humid!$E$2*L15</f>
         <v>2262153.4458035277</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" t="s">
         <v>90</v>
       </c>
       <c r="C3" s="12">
-        <f>[4]ZS_Cropland_Arid!$D$2*L15</f>
+        <f>[37]ZS_Cropland_Arid!$D$2*L15</f>
         <v>18395.019999999997</v>
       </c>
       <c r="D3" s="12">
-        <f>[5]ZS_Cropland_SArid!$D$2*L15</f>
+        <f>[38]ZS_Cropland_SArid!$D$2*L15</f>
         <v>686372.96</v>
       </c>
       <c r="E3" s="12">
-        <f>[6]ZS_Cropland_Humid!$E$2*L15</f>
+        <f>[39]ZS_Cropland_Humid!$E$2*L15</f>
         <v>950603.98551942373</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" t="s">
         <v>91</v>
       </c>
       <c r="C4" s="12">
-        <f>[7]ZS_Shrubland_Arid!$D$2*L15</f>
+        <f>[40]ZS_Shrubland_Arid!$D$2*L15</f>
         <v>9755293.3449999988</v>
       </c>
       <c r="D4" s="12">
-        <f>[8]ZS_Shrubland_SArid!$D$2*L15</f>
+        <f>[41]ZS_Shrubland_SArid!$D$2*L15</f>
         <v>12549721.555</v>
       </c>
       <c r="E4" s="12">
-        <f>[9]ZS_Shrubland_Humid!$E$2*L15</f>
+        <f>[42]ZS_Shrubland_Humid!$E$2*L15</f>
         <v>2223118.4370185882</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="C5" s="12"/>
       <c r="D5" s="12"/>
       <c r="E5" s="12"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A7">
         <v>2020</v>
       </c>
@@ -4281,76 +4360,76 @@
         <v>71</v>
       </c>
       <c r="C7" s="15">
-        <f>[10]NPP_2020_GRASS_Arid!$E$2</f>
+        <f>[43]NPP_2020_GRASS_Arid!$E$2</f>
         <v>0.33293323112310402</v>
       </c>
       <c r="D7" s="15">
-        <f>[11]NPP_2020_GRASS_SArid!$E$2</f>
+        <f>[44]NPP_2020_GRASS_SArid!$E$2</f>
         <v>0.48080803465972</v>
       </c>
       <c r="E7" s="14">
-        <f>[68]filtered!$F$2</f>
+        <f>[45]filtered!$F$2</f>
         <v>0.88607168377191448</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B8" t="s">
         <v>72</v>
       </c>
-      <c r="C8" s="32">
-        <f>[12]NPP_2020_CROP_Arid!$E$2</f>
+      <c r="C8" s="30">
+        <f>[46]NPP_2020_CROP_Arid!$E$2</f>
         <v>0.97599038751874501</v>
       </c>
-      <c r="D8" s="32">
-        <f>[13]NPP_2020_CROP_SArid!$E$2</f>
+      <c r="D8" s="30">
+        <f>[47]NPP_2020_CROP_SArid!$E$2</f>
         <v>0.71416468993051396</v>
       </c>
       <c r="E8" s="14">
-        <f>[69]filtered!$F$2</f>
+        <f>[48]filtered!$F$2</f>
         <v>1.0193612610195171</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" t="s">
         <v>73</v>
       </c>
       <c r="C9" s="15">
-        <f>[14]NPP_2020_SHRUB_Arid!$E$2</f>
+        <f>[49]NPP_2020_SHRUB_Arid!$E$2</f>
         <v>0.20100553202445001</v>
       </c>
       <c r="D9" s="15">
-        <f>[15]NPP_2020_SHRUB_SArid!$E$2</f>
+        <f>[50]NPP_2020_SHRUB_SArid!$E$2</f>
         <v>0.48842843619779902</v>
       </c>
       <c r="E9" s="14">
-        <f>[70]filtered!$F$2</f>
+        <f>[51]filtered!$F$2</f>
         <v>0.9284507277249876</v>
       </c>
       <c r="L9" s="11"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="C10" s="12"/>
       <c r="D10" s="12"/>
       <c r="E10" s="12"/>
       <c r="L10" s="11"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>68</v>
       </c>
       <c r="B11" t="s">
         <v>71</v>
       </c>
-      <c r="C11" s="31">
-        <f>[16]NPP_2050_R4_GRASS_Arid!$E$2</f>
+      <c r="C11" s="15">
+        <f>[52]NPP_2050_R4_GRASS_Arid!$E$2</f>
         <v>0.36084903504638699</v>
       </c>
       <c r="D11" s="15">
-        <f>[17]NPP_2050_R4_GRASS_SArid!$E$2</f>
+        <f>[53]NPP_2050_R4_GRASS_SArid!$E$2</f>
         <v>0.51075241024303597</v>
       </c>
       <c r="E11" s="15">
-        <f>[18]filtered!$F$2</f>
+        <f>[54]filtered!$F$2</f>
         <v>0.90483097904137921</v>
       </c>
       <c r="F11">
@@ -4366,20 +4445,20 @@
         <v>1.0211713065805335</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B12" t="s">
         <v>72</v>
       </c>
       <c r="C12" s="15">
-        <f>[19]NPP_2050_R4_CROP_Arid!$E$2</f>
+        <f>[55]NPP_2050_R4_CROP_Arid!$E$2</f>
         <v>1.0384816436740301</v>
       </c>
       <c r="D12" s="15">
-        <f>[20]NPP_2050_R4_CROP_SArid!$E$2</f>
+        <f>[56]NPP_2050_R4_CROP_SArid!$E$2</f>
         <v>0.72447113600000002</v>
       </c>
       <c r="E12" s="15">
-        <f>[21]filtered!$F$2</f>
+        <f>[57]filtered!$F$2</f>
         <v>0.98649141647533578</v>
       </c>
       <c r="F12">
@@ -4395,20 +4474,20 @@
         <v>0.96775446958686029</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B13" t="s">
         <v>73</v>
       </c>
       <c r="C13" s="15">
-        <f>[22]NPP_2050_R4_SHRUB_Arid!$E$2</f>
+        <f>[58]NPP_2050_R4_SHRUB_Arid!$E$2</f>
         <v>0.21776707800273001</v>
       </c>
       <c r="D13" s="15">
-        <f>[23]NPP_2050_R4_SHRUB_SArid!$E$2</f>
+        <f>[59]NPP_2050_R4_SHRUB_SArid!$E$2</f>
         <v>0.51075241024303597</v>
       </c>
       <c r="E13" s="15">
-        <f>[24]filtered!$F$2</f>
+        <f>[60]filtered!$F$2</f>
         <v>0.90483097904137921</v>
       </c>
       <c r="F13">
@@ -4424,12 +4503,12 @@
         <v>0.9745600407449897</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="C14" s="12"/>
       <c r="D14" s="12"/>
       <c r="E14" s="12"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>69</v>
       </c>
@@ -4437,15 +4516,15 @@
         <v>71</v>
       </c>
       <c r="C15" s="15">
-        <f>[25]NPP_2050_R8_GRASS_Arid!$E$2</f>
+        <f>[61]NPP_2050_R8_GRASS_Arid!$E$2</f>
         <v>0.38422689204237098</v>
       </c>
       <c r="D15" s="15">
-        <f>[26]NPP_2050_R8_GRASS_SArid!$E$2</f>
+        <f>[62]NPP_2050_R8_GRASS_SArid!$E$2</f>
         <v>0.51337712420869996</v>
       </c>
       <c r="E15" s="15">
-        <f>[27]filtered!$F$2</f>
+        <f>[63]filtered!$F$2</f>
         <v>0.88457459938562355</v>
       </c>
       <c r="F15">
@@ -4468,20 +4547,20 @@
         <v>35.104999999999997</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B16" t="s">
         <v>72</v>
       </c>
       <c r="C16" s="15">
-        <f>[28]NPP_2050_R8_CROP_Arid!$E$2</f>
+        <f>[64]NPP_2050_R8_CROP_Arid!$E$2</f>
         <v>1.10532849796393</v>
       </c>
       <c r="D16" s="15">
-        <f>[29]NPP_2050_R8_CROP_SArid!$E$2</f>
+        <f>[65]NPP_2050_R8_CROP_SArid!$E$2</f>
         <v>0.80695680840268103</v>
       </c>
       <c r="E16" s="15">
-        <f>[30]filtered!$F$2</f>
+        <f>[66]filtered!$F$2</f>
         <v>1.0242825546815273</v>
       </c>
       <c r="F16">
@@ -4504,20 +4583,20 @@
         <v>35.104999999999997</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B17" t="s">
         <v>73</v>
       </c>
       <c r="C17" s="15">
-        <f>[31]NPP_2050_R8_SHRUB_Arid!$E$2</f>
+        <f>[67]NPP_2050_R8_SHRUB_Arid!$E$2</f>
         <v>0.231319877140652</v>
       </c>
       <c r="D17" s="15">
-        <f>[32]NPP_2050_R8_SHRUB_SArid!$E$2</f>
+        <f>[68]NPP_2050_R8_SHRUB_SArid!$E$2</f>
         <v>0.51046846997934603</v>
       </c>
       <c r="E17" s="15">
-        <f>[33]filtered!$F$2</f>
+        <f>[69]filtered!$F$2</f>
         <v>0.93416975929597834</v>
       </c>
       <c r="F17">
@@ -4533,7 +4612,7 @@
         <v>1.0061597577558092</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="16">
         <v>2020</v>
       </c>
@@ -4541,36 +4620,36 @@
         <v>74</v>
       </c>
       <c r="C20">
-        <f>10000*(1/1000)*(C2*C7+C3*C8*[34]Raster_logic!$I$84+C4*C9*[34]Raster_logic!$I$85)*(1/[34]Raster_logic!$I$79)*[34]Raster_logic!$I$80*[34]Raster_logic!$I$81/1000000</f>
+        <f>10000*(1/1000)*(C2*C7+C3*C8*[70]Raster_logic!$I$84+C4*C9*[70]Raster_logic!$I$85)*(1/[70]Raster_logic!$I$79)*[70]Raster_logic!$I$80*[70]Raster_logic!$I$81/1000000</f>
         <v>8.3324944189563208</v>
       </c>
       <c r="D20">
-        <f>10000*(1/1000)*(D2*D7+D3*D8*[34]Raster_logic!$I$84+D4*D9*[34]Raster_logic!$I$85)*(1/[34]Raster_logic!$I$79)*[34]Raster_logic!$I$80*[34]Raster_logic!$I$81/1000000</f>
+        <f>10000*(1/1000)*(D2*D7+D3*D8*[70]Raster_logic!$I$84+D4*D9*[70]Raster_logic!$I$85)*(1/[70]Raster_logic!$I$79)*[70]Raster_logic!$I$80*[70]Raster_logic!$I$81/1000000</f>
         <v>12.69703720354909</v>
       </c>
       <c r="E20">
-        <f>10000*(1/1000)*(E2*E7+E3*E8*[34]Raster_logic!$I$84+E4*E9*[34]Raster_logic!$I$85)*(1/[34]Raster_logic!$I$79)*[34]Raster_logic!$I$80*[34]Raster_logic!$I$81/1000000</f>
+        <f>10000*(1/1000)*(E2*E7+E3*E8*[70]Raster_logic!$I$84+E4*E9*[70]Raster_logic!$I$85)*(1/[70]Raster_logic!$I$79)*[70]Raster_logic!$I$80*[70]Raster_logic!$I$81/1000000</f>
         <v>8.341120928606971</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B21" t="s">
         <v>75</v>
       </c>
       <c r="C21">
-        <f>10000*(1/1000)*(C3*C8*[34]Raster_logic!$I$91)*(1/[34]Raster_logic!$I$87)*[34]Raster_logic!$I$88*[34]Raster_logic!$I$89*[34]Raster_logic!$I$86/1000000</f>
+        <f>10000*(1/1000)*(C3*C8*[70]Raster_logic!$I$91)*(1/[70]Raster_logic!$I$87)*[70]Raster_logic!$I$88*[70]Raster_logic!$I$89*[70]Raster_logic!$I$86/1000000</f>
         <v>3.8150895733707002E-2</v>
       </c>
       <c r="D21">
-        <f>10000*(1/1000)*(D3*D8*[34]Raster_logic!$I$91)*(1/[34]Raster_logic!$I$87)*[34]Raster_logic!$I$88*[34]Raster_logic!$I$89*[34]Raster_logic!$I$86/1000000</f>
+        <f>10000*(1/1000)*(D3*D8*[70]Raster_logic!$I$91)*(1/[70]Raster_logic!$I$87)*[70]Raster_logic!$I$88*[70]Raster_logic!$I$89*[70]Raster_logic!$I$86/1000000</f>
         <v>1.041639580829564</v>
       </c>
       <c r="E21">
-        <f>10000*(1/1000)*(E3*E8*[34]Raster_logic!$I$91)*(1/[34]Raster_logic!$I$87)*[34]Raster_logic!$I$88*[34]Raster_logic!$I$89*[34]Raster_logic!$I$86/1000000</f>
+        <f>10000*(1/1000)*(E3*E8*[70]Raster_logic!$I$91)*(1/[70]Raster_logic!$I$87)*[70]Raster_logic!$I$88*[70]Raster_logic!$I$89*[70]Raster_logic!$I$86/1000000</f>
         <v>2.0591438644946747</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B22" t="s">
         <v>76</v>
       </c>
@@ -4587,7 +4666,7 @@
         <v>10.400264793101645</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
         <v>68</v>
       </c>
@@ -4596,15 +4675,15 @@
         <v>BIOM GRASS Supply (MT/ha/yr)</v>
       </c>
       <c r="C24">
-        <f>10000*(1/1000)*(C2*C11+C3*C12*[34]Raster_logic!$I$84+C4*C13*[34]Raster_logic!$I$85)*(1/[34]Raster_logic!$I$79)*[34]Raster_logic!$I$80*[34]Raster_logic!$I$81/1000000</f>
+        <f>10000*(1/1000)*(C2*C11+C3*C12*[70]Raster_logic!$I$84+C4*C13*[70]Raster_logic!$I$85)*(1/[70]Raster_logic!$I$79)*[70]Raster_logic!$I$80*[70]Raster_logic!$I$81/1000000</f>
         <v>9.0298868510117494</v>
       </c>
       <c r="D24">
-        <f>10000*(1/1000)*(D2*D11+D3*D12*[34]Raster_logic!$I$84+D4*D13*[34]Raster_logic!$I$85)*(1/[34]Raster_logic!$I$79)*[34]Raster_logic!$I$80*[34]Raster_logic!$I$81/1000000</f>
+        <f>10000*(1/1000)*(D2*D11+D3*D12*[70]Raster_logic!$I$84+D4*D13*[70]Raster_logic!$I$85)*(1/[70]Raster_logic!$I$79)*[70]Raster_logic!$I$80*[70]Raster_logic!$I$81/1000000</f>
         <v>13.359468018042634</v>
       </c>
       <c r="E24">
-        <f>10000*(1/1000)*(E2*E11+E3*E12*[34]Raster_logic!$I$84+E4*E13*[34]Raster_logic!$I$85)*(1/[34]Raster_logic!$I$79)*[34]Raster_logic!$I$80*[34]Raster_logic!$I$81/1000000</f>
+        <f>10000*(1/1000)*(E2*E11+E3*E12*[70]Raster_logic!$I$84+E4*E13*[70]Raster_logic!$I$85)*(1/[70]Raster_logic!$I$79)*[70]Raster_logic!$I$80*[70]Raster_logic!$I$81/1000000</f>
         <v>8.3696564117948942</v>
       </c>
       <c r="F24" s="13">
@@ -4620,21 +4699,21 @@
         <v>1.0034210609619694</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B25" t="str">
         <f t="shared" ref="B25:B26" si="5">B21</f>
         <v>BIOM CROP Supply (MT/ha/yr)</v>
       </c>
       <c r="C25">
-        <f>10000*(1/1000)*(C12*C3*[34]Raster_logic!$I$91)*(1/[34]Raster_logic!$I$87)*[34]Raster_logic!$I$88*[34]Raster_logic!$I$89*[34]Raster_logic!$I$86/1000000</f>
+        <f>10000*(1/1000)*(C12*C3*[70]Raster_logic!$I$91)*(1/[70]Raster_logic!$I$87)*[70]Raster_logic!$I$88*[70]Raster_logic!$I$89*[70]Raster_logic!$I$86/1000000</f>
         <v>4.0593642535660383E-2</v>
       </c>
       <c r="D25">
-        <f>10000*(1/1000)*(D12*D3*[34]Raster_logic!$I$91)*(1/[34]Raster_logic!$I$87)*[34]Raster_logic!$I$88*[34]Raster_logic!$I$89*[34]Raster_logic!$I$86/1000000</f>
+        <f>10000*(1/1000)*(D12*D3*[70]Raster_logic!$I$91)*(1/[70]Raster_logic!$I$87)*[70]Raster_logic!$I$88*[70]Raster_logic!$I$89*[70]Raster_logic!$I$86/1000000</f>
         <v>1.0566719708581258</v>
       </c>
       <c r="E25">
-        <f>10000*(1/1000)*(E12*E3*[34]Raster_logic!$I$91)*(1/[34]Raster_logic!$I$87)*[34]Raster_logic!$I$88*[34]Raster_logic!$I$89*[34]Raster_logic!$I$86/1000000</f>
+        <f>10000*(1/1000)*(E12*E3*[70]Raster_logic!$I$91)*(1/[70]Raster_logic!$I$87)*[70]Raster_logic!$I$88*[70]Raster_logic!$I$89*[70]Raster_logic!$I$86/1000000</f>
         <v>1.9927456783870812</v>
       </c>
       <c r="F25" s="13">
@@ -4650,7 +4729,7 @@
         <v>0.96775446958686007</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B26" t="str">
         <f t="shared" si="5"/>
         <v>BIOM Total (MT/ha/yr)</v>
@@ -4680,7 +4759,7 @@
         <v>0.99635944818012867</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
         <v>69</v>
       </c>
@@ -4689,15 +4768,15 @@
         <v>BIOM GRASS Supply (MT/ha/yr)</v>
       </c>
       <c r="C28">
-        <f>10000*(1/1000)*(C2*C15+C3*C16*[34]Raster_logic!$I$84+C4*C17*[34]Raster_logic!$I$85)*(1/[34]Raster_logic!$I$79)*[34]Raster_logic!$I$80*[34]Raster_logic!$I$81/1000000</f>
+        <f>10000*(1/1000)*(C2*C15+C3*C16*[70]Raster_logic!$I$84+C4*C17*[70]Raster_logic!$I$85)*(1/[70]Raster_logic!$I$79)*[70]Raster_logic!$I$80*[70]Raster_logic!$I$81/1000000</f>
         <v>9.609165818496594</v>
       </c>
       <c r="D28">
-        <f>10000*(1/1000)*(D2*D15+D3*D16*[34]Raster_logic!$I$84+D4*D17*[34]Raster_logic!$I$85)*(1/[34]Raster_logic!$I$79)*[34]Raster_logic!$I$80*[34]Raster_logic!$I$81/1000000</f>
+        <f>10000*(1/1000)*(D2*D15+D3*D16*[70]Raster_logic!$I$84+D4*D17*[70]Raster_logic!$I$85)*(1/[70]Raster_logic!$I$79)*[70]Raster_logic!$I$80*[70]Raster_logic!$I$81/1000000</f>
         <v>13.438099018999708</v>
       </c>
       <c r="E28">
-        <f>10000*(1/1000)*(E2*E15+E3*E16*[34]Raster_logic!$I$84+E4*E17*[34]Raster_logic!$I$85)*(1/[34]Raster_logic!$I$79)*[34]Raster_logic!$I$80*[34]Raster_logic!$I$81/1000000</f>
+        <f>10000*(1/1000)*(E2*E15+E3*E16*[70]Raster_logic!$I$84+E4*E17*[70]Raster_logic!$I$85)*(1/[70]Raster_logic!$I$79)*[70]Raster_logic!$I$80*[70]Raster_logic!$I$81/1000000</f>
         <v>8.3498054400644932</v>
       </c>
       <c r="F28" s="13">
@@ -4713,21 +4792,21 @@
         <v>1.0010411683911375</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B29" t="str">
         <f t="shared" ref="B29:B30" si="9">B25</f>
         <v>BIOM CROP Supply (MT/ha/yr)</v>
       </c>
       <c r="C29">
-        <f>10000*(1/1000)*(C16*C3*[34]Raster_logic!$I$91)*(1/[34]Raster_logic!$I$87)*[34]Raster_logic!$I$88*[34]Raster_logic!$I$89*[34]Raster_logic!$I$86/1000000</f>
+        <f>10000*(1/1000)*(C16*C3*[70]Raster_logic!$I$91)*(1/[70]Raster_logic!$I$87)*[70]Raster_logic!$I$88*[70]Raster_logic!$I$89*[70]Raster_logic!$I$86/1000000</f>
         <v>4.3206647131559951E-2</v>
       </c>
       <c r="D29">
-        <f>10000*(1/1000)*(D16*D3*[34]Raster_logic!$I$91)*(1/[34]Raster_logic!$I$87)*[34]Raster_logic!$I$88*[34]Raster_logic!$I$89*[34]Raster_logic!$I$86/1000000</f>
+        <f>10000*(1/1000)*(D16*D3*[70]Raster_logic!$I$91)*(1/[70]Raster_logic!$I$87)*[70]Raster_logic!$I$88*[70]Raster_logic!$I$89*[70]Raster_logic!$I$86/1000000</f>
         <v>1.1769808329979399</v>
       </c>
       <c r="E29">
-        <f>10000*(1/1000)*(E16*E3*[34]Raster_logic!$I$91)*(1/[34]Raster_logic!$I$87)*[34]Raster_logic!$I$88*[34]Raster_logic!$I$89*[34]Raster_logic!$I$86/1000000</f>
+        <f>10000*(1/1000)*(E16*E3*[70]Raster_logic!$I$91)*(1/[70]Raster_logic!$I$87)*[70]Raster_logic!$I$88*[70]Raster_logic!$I$89*[70]Raster_logic!$I$86/1000000</f>
         <v>2.0690850424038385</v>
       </c>
       <c r="F29" s="13">
@@ -4743,7 +4822,7 @@
         <v>1.0048278209602433</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B30" t="str">
         <f t="shared" si="9"/>
         <v>BIOM Total (MT/ha/yr)</v>
@@ -4782,18 +4861,18 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7E0F49F-D7A7-4FDA-92DD-326744451984}">
   <dimension ref="A1:I49"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="17.42578125" customWidth="1"/>
-    <col min="2" max="2" width="27.5703125" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" customWidth="1"/>
-    <col min="5" max="5" width="9.28515625" customWidth="1"/>
-    <col min="6" max="7" width="11.28515625" customWidth="1"/>
-    <col min="8" max="8" width="16.85546875" customWidth="1"/>
+    <col min="1" max="1" width="17.41796875" customWidth="1"/>
+    <col min="2" max="2" width="27.578125" customWidth="1"/>
+    <col min="3" max="3" width="11.68359375" customWidth="1"/>
+    <col min="4" max="4" width="13.83984375" customWidth="1"/>
+    <col min="5" max="5" width="9.26171875" customWidth="1"/>
+    <col min="6" max="7" width="11.26171875" customWidth="1"/>
+    <col min="8" max="8" width="16.83984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>67</v>
       </c>
@@ -4814,7 +4893,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A2">
         <v>2020</v>
       </c>
@@ -4823,11 +4902,11 @@
       </c>
       <c r="C2">
         <f>Herd_decision_tree!B10</f>
-        <v>3.5231517722606158</v>
+        <v>4.4039397153257696</v>
       </c>
       <c r="D2">
         <f>Herd_decision_tree!C10</f>
-        <v>3.4688080255059042</v>
+        <v>4.3360100318823802</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -4839,7 +4918,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" t="s">
         <v>16</v>
       </c>
@@ -4848,11 +4927,11 @@
       </c>
       <c r="D3">
         <f>Herd_decision_tree!C14</f>
-        <v>2.4628062451950257</v>
+        <v>3.0785078064937821</v>
       </c>
       <c r="E3">
         <f>Herd_decision_tree!D14</f>
-        <v>2.062758252194099</v>
+        <v>2.5784478152426238</v>
       </c>
       <c r="H3" t="s">
         <v>84</v>
@@ -4861,7 +4940,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" t="s">
         <v>59</v>
       </c>
@@ -4873,7 +4952,7 @@
       </c>
       <c r="E4">
         <f>Herd_decision_tree!D18</f>
-        <v>0.7785024521166074</v>
+        <v>0.97312806514575934</v>
       </c>
       <c r="H4" t="s">
         <v>94</v>
@@ -4883,21 +4962,21 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5">
         <f>Herd_decision_tree!B29</f>
-        <v>5.2733829594195897E-2</v>
+        <v>6.591728699274485E-2</v>
       </c>
       <c r="D5">
         <f>Herd_decision_tree!C29</f>
-        <v>0.24371952505843877</v>
+        <v>0.30464940632304843</v>
       </c>
       <c r="E5">
         <f>Herd_decision_tree!D29</f>
-        <v>0.39517416198641953</v>
+        <v>0.49396770248302452</v>
       </c>
       <c r="H5" t="s">
         <v>95</v>
@@ -4907,21 +4986,21 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" t="s">
         <v>23</v>
       </c>
       <c r="C6">
         <f>Herd_decision_tree!B25</f>
-        <v>0.16805182258191609</v>
+        <v>0.21006477822739511</v>
       </c>
       <c r="D6">
         <f>Herd_decision_tree!C25</f>
-        <v>0.2239758371518942</v>
+        <v>0.2799697964398678</v>
       </c>
       <c r="E6">
         <f>Herd_decision_tree!D25</f>
-        <v>0.1945231706769199</v>
+        <v>0.24315396334614986</v>
       </c>
       <c r="H6" t="s">
         <v>96</v>
@@ -4930,21 +5009,21 @@
         <v>8.5000000000000006E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" t="s">
         <v>61</v>
       </c>
       <c r="C7">
         <f>Herd_decision_tree!B35</f>
-        <v>2.48125917562073E-2</v>
+        <v>3.1015739695259125E-2</v>
       </c>
       <c r="D7">
         <f>Herd_decision_tree!C35</f>
-        <v>1.2103066219751799</v>
+        <v>1.5128832774689749</v>
       </c>
       <c r="E7">
         <f>Herd_decision_tree!D35</f>
-        <v>5.2339163978957206</v>
+        <v>6.5423954973696503</v>
       </c>
       <c r="H7" t="s">
         <v>63</v>
@@ -4954,95 +5033,95 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B8" t="s">
         <v>83</v>
       </c>
       <c r="C8">
         <f>Herd_decision_tree!B5</f>
-        <v>9.6672519551532563</v>
+        <v>12.08406494394157</v>
       </c>
       <c r="D8">
         <f>Herd_decision_tree!C5</f>
-        <v>7.908294939381296</v>
+        <v>9.8853686742266191</v>
       </c>
       <c r="E8">
         <f>Herd_decision_tree!D5</f>
-        <v>7.4434538218863873</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+        <v>9.3043172773579848</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B10" t="s">
         <v>64</v>
       </c>
       <c r="C10">
         <f>SUM(C2:C6)*$I1*1000000</f>
-        <v>636469362.15424371</v>
+        <v>795586702.69280469</v>
       </c>
       <c r="D10">
         <f>SUM(D2:D6)*$I1*1000000</f>
-        <v>1087882637.5949147</v>
+        <v>1359853296.9936435</v>
       </c>
       <c r="E10">
         <f>SUM(E2:E6)*$I1*1000000</f>
-        <v>583262866.28558779</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+        <v>729078582.85698473</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B11" t="s">
         <v>65</v>
       </c>
       <c r="C11">
         <f t="shared" ref="C11:E11" si="0">C7*$I$2*1000000</f>
-        <v>4962518.3512414601</v>
+        <v>6203147.9390518256</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
-        <v>242061324.39503598</v>
+        <v>302576655.49379498</v>
       </c>
       <c r="E11">
         <f t="shared" si="0"/>
-        <v>1046783279.5791441</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+        <v>1308479099.4739301</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B12" t="s">
         <v>85</v>
       </c>
       <c r="C12">
         <f>C8*$I$3*1000000</f>
-        <v>338353818.43036395</v>
+        <v>422942273.03795493</v>
       </c>
       <c r="D12">
         <f>D8*$I$3*1000000</f>
-        <v>276790322.87834537</v>
+        <v>345987903.59793168</v>
       </c>
       <c r="E12">
         <f>E8*$I$3*1000000</f>
-        <v>260520883.76602352</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+        <v>325651104.70752943</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B14" s="24" t="s">
         <v>77</v>
       </c>
       <c r="C14" s="25">
         <f>365*(C10+C11+C12)*(1-$I4)*($I7)/1000/1000000</f>
-        <v>6.902100356153591</v>
+        <v>8.6276254451919883</v>
       </c>
       <c r="D14" s="25">
         <f>365*(D10+D11+D12)*(1-$I5)*($I7)/1000/1000000</f>
-        <v>11.201348066959325</v>
+        <v>14.001685083699156</v>
       </c>
       <c r="E14" s="25">
         <f>365*(E10+E11+E12)*(1-$I6)*($I7)/1000/1000000</f>
-        <v>12.628042474418631</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+        <v>15.785053093023292</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B15" s="1"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B16" s="18" t="s">
         <v>78</v>
       </c>
@@ -5059,30 +5138,30 @@
         <v>10.400264793101645</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B17" s="1"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B18" s="17" t="s">
         <v>82</v>
       </c>
       <c r="C18" s="6">
         <f>C16/C14</f>
-        <v>1.2127678362756855</v>
+        <v>0.97021426902054841</v>
       </c>
       <c r="D18" s="6">
         <f t="shared" ref="D18" si="1">D16/D14</f>
-        <v>1.2265199422651369</v>
+        <v>0.98121595381210958</v>
       </c>
       <c r="E18" s="6">
         <f>E16/E14</f>
-        <v>0.8235848758166654</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.65886790065333223</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B19" s="1"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="1" t="s">
         <v>68</v>
       </c>
@@ -5091,18 +5170,18 @@
       </c>
       <c r="C21">
         <f>C2+C2*30*Validate_2020!$G2/100</f>
-        <v>3.9280888459649885</v>
+        <v>4.9101110574562359</v>
       </c>
       <c r="D21">
         <f>D2+D2*30*Validate_2020!$G2/100</f>
-        <v>3.867499044766002</v>
+        <v>4.8343738059575028</v>
       </c>
       <c r="E21">
         <f>E2+E2*30*Validate_2020!$G2/100</f>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B22" t="s">
         <v>16</v>
       </c>
@@ -5112,14 +5191,14 @@
       </c>
       <c r="D22">
         <f>D3+D3*30*Validate_2020!$G3/100</f>
-        <v>4.5279006444321599</v>
+        <v>5.6598758055402012</v>
       </c>
       <c r="E22">
         <f>E3+E3*30*Validate_2020!$G3/100</f>
-        <v>3.7924073148831083</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+        <v>4.7405091436038855</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B23" t="s">
         <v>59</v>
       </c>
@@ -5133,151 +5212,151 @@
       </c>
       <c r="E23">
         <f>E4+E4*30*Validate_2020!$G4/100</f>
-        <v>1.0948676678244551</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1.3685845847805689</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B24" t="s">
         <v>22</v>
       </c>
       <c r="C24">
         <f>C5+C5*30*Validate_2020!$G5/100</f>
-        <v>6.9143026568985577E-2</v>
+        <v>8.6428783211231944E-2</v>
       </c>
       <c r="D24">
         <f>D5+D5*30*Validate_2020!$G5/100</f>
-        <v>0.31955778152609127</v>
+        <v>0.39944722690761403</v>
       </c>
       <c r="E24">
         <f>E5+E5*30*Validate_2020!$G5/100</f>
-        <v>0.51814059005134261</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.6476757375641784</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B25" t="s">
         <v>23</v>
       </c>
       <c r="C25">
         <f>C6+C6*30*Validate_2020!$G6/100</f>
-        <v>4.5273109923986858</v>
+        <v>5.6591387404983573</v>
       </c>
       <c r="D25">
         <f>D6+D6*30*Validate_2020!$G6/100</f>
-        <v>6.033902245095824</v>
+        <v>7.5423778063697817</v>
       </c>
       <c r="E25">
         <f>E6+E6*30*Validate_2020!$G6/100</f>
-        <v>5.2404483054778428</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+        <v>6.5505603818473022</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B26" t="s">
         <v>61</v>
       </c>
       <c r="C26">
         <f>C7+C7*30*Validate_2020!G8/100</f>
-        <v>2.48125917562073E-2</v>
+        <v>3.1015739695259125E-2</v>
       </c>
       <c r="D26">
         <f>D7+D7*30*Validate_2020!H8/100</f>
-        <v>1.2452331192095332</v>
+        <v>1.5565413990119166</v>
       </c>
       <c r="E26">
         <f>E7+E7*30*Validate_2020!I8/100</f>
-        <v>5.2339163978957206</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+        <v>6.5423954973696503</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B27" t="s">
         <v>83</v>
       </c>
       <c r="C27">
         <f>C8+C8*30*1.35*Validate_2020!$G7/100</f>
-        <v>18.584642590740373</v>
+        <v>23.230803238425466</v>
       </c>
       <c r="D27">
         <f>D8+D8*30*1.15*Validate_2020!$G7/100</f>
-        <v>14.122444247942596</v>
+        <v>17.653055309928241</v>
       </c>
       <c r="E27">
         <f>E8+E8*30*0.8*Validate_2020!$G7/100</f>
-        <v>11.512245654315745</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+        <v>14.390307067894684</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B30" t="s">
         <v>64</v>
       </c>
       <c r="C30">
         <f>SUM(C21:C25)*$I1*1000000</f>
-        <v>1449172287.038552</v>
+        <v>1811465358.7981901</v>
       </c>
       <c r="D30">
         <f>SUM(D21:D25)*$I1*1000000</f>
-        <v>2507306151.6894131</v>
+        <v>3134132689.6117673</v>
       </c>
       <c r="E30">
         <f>SUM(E21:E25)*$I1*1000000</f>
-        <v>1809796859.3002474</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2262246074.125309</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B31" t="s">
         <v>65</v>
       </c>
       <c r="C31">
         <f t="shared" ref="C31:E32" si="2">C26*$I2*1000000</f>
-        <v>4962518.3512414601</v>
+        <v>6203147.9390518256</v>
       </c>
       <c r="D31">
         <f t="shared" si="2"/>
-        <v>249046623.84190664</v>
+        <v>311308279.8023833</v>
       </c>
       <c r="E31">
         <f t="shared" si="2"/>
-        <v>1046783279.5791441</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1308479099.4739301</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B32" t="s">
         <v>85</v>
       </c>
       <c r="C32">
         <f t="shared" si="2"/>
-        <v>650462490.6759131</v>
+        <v>813078113.34489131</v>
       </c>
       <c r="D32">
         <f t="shared" si="2"/>
-        <v>494285548.67799085</v>
+        <v>617856935.8474884</v>
       </c>
       <c r="E32">
         <f t="shared" si="2"/>
-        <v>402928597.9010511</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+        <v>503660747.37631392</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B34" s="24" t="s">
         <v>66</v>
       </c>
       <c r="C34" s="26">
         <f>365*(C30+C31+C32)*(1-$I4)*($I7)/1000/1000000</f>
-        <v>14.825835652134872</v>
+        <v>18.532294565168584</v>
       </c>
       <c r="D34" s="26">
         <f>365*(D30+D31+D32)*(1-$I5)*($I7)/1000/1000000</f>
-        <v>22.661825077225213</v>
+        <v>28.327281346531521</v>
       </c>
       <c r="E34" s="26">
         <f>365*(E30+E31+E32)*(1-$I6)*($I7)/1000/1000000</f>
-        <v>21.771888607324968</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+        <v>27.214860759156213</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="C35" s="13"/>
       <c r="D35" s="13"/>
       <c r="E35" s="13"/>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B36" s="18" t="s">
         <v>78</v>
       </c>
@@ -5294,65 +5373,65 @@
         <v>10.362402090181975</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B37" s="1"/>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B38" s="30" t="s">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B38" s="31" t="s">
         <v>82</v>
       </c>
-      <c r="C38" s="30"/>
-      <c r="D38" s="30"/>
-      <c r="E38" s="30"/>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C38" s="31"/>
+      <c r="D38" s="31"/>
+      <c r="E38" s="31"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B39" s="20">
         <v>2050</v>
       </c>
       <c r="C39" s="21">
         <f>C36/C34</f>
-        <v>0.61180230958794479</v>
+        <v>0.48944184767035603</v>
       </c>
       <c r="D39" s="21">
         <f t="shared" ref="D39:E39" si="3">D36/D34</f>
-        <v>0.63614205562767134</v>
+        <v>0.50891364450213705</v>
       </c>
       <c r="E39" s="21">
         <f t="shared" si="3"/>
-        <v>0.47595329358315902</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.38076263486652717</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="1"/>
       <c r="B40" s="20" t="s">
         <v>88</v>
       </c>
       <c r="C40" s="21">
         <f>(C39+C18)/2</f>
-        <v>0.91228507293181516</v>
+        <v>0.72982805834545217</v>
       </c>
       <c r="D40" s="21">
         <f t="shared" ref="D40:E40" si="4">(D39+D18)/2</f>
-        <v>0.93133099894640414</v>
+        <v>0.74506479915712331</v>
       </c>
       <c r="E40" s="21">
         <f t="shared" si="4"/>
-        <v>0.64976908469991224</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.5198152677599297</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
       <c r="D42" s="3"/>
       <c r="E42" s="3"/>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="1" t="s">
         <v>69</v>
       </c>
@@ -5361,24 +5440,24 @@
       </c>
       <c r="C43" s="29">
         <f>C34</f>
-        <v>14.825835652134872</v>
+        <v>18.532294565168584</v>
       </c>
       <c r="D43" s="29">
         <f t="shared" ref="D43:E43" si="5">D34</f>
-        <v>22.661825077225213</v>
+        <v>28.327281346531521</v>
       </c>
       <c r="E43" s="29">
         <f t="shared" si="5"/>
-        <v>21.771888607324968</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+        <v>27.214860759156213</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B45" s="22" t="s">
         <v>78</v>
       </c>
@@ -5395,52 +5474,52 @@
         <v>10.418890482468331</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B47" s="30" t="s">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B47" s="31" t="s">
         <v>82</v>
       </c>
-      <c r="C47" s="30"/>
-      <c r="D47" s="30"/>
-      <c r="E47" s="30"/>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C47" s="31"/>
+      <c r="D47" s="31"/>
+      <c r="E47" s="31"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B48" s="20">
         <v>2050</v>
       </c>
       <c r="C48" s="21">
         <f>C45/C43</f>
-        <v>0.65105082048027718</v>
+        <v>0.52084065638422194</v>
       </c>
       <c r="D48" s="21">
         <f t="shared" ref="D48" si="6">D45/D43</f>
-        <v>0.64492068940579628</v>
+        <v>0.51593655152463691</v>
       </c>
       <c r="E48" s="21">
         <f>E45/E43</f>
-        <v>0.47854784995376948</v>
-      </c>
-    </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
+        <v>0.3828382799630155</v>
+      </c>
+    </row>
+    <row r="49" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B49" s="20" t="s">
         <v>88</v>
       </c>
       <c r="C49" s="21">
         <f>(C18+C48)*0.5</f>
-        <v>0.93190932837798135</v>
+        <v>0.74552746270238512</v>
       </c>
       <c r="D49" s="21">
         <f t="shared" ref="D49:E49" si="7">(D18+D48)*0.5</f>
-        <v>0.93572031583546655</v>
+        <v>0.74857625266837324</v>
       </c>
       <c r="E49" s="21">
         <f t="shared" si="7"/>
-        <v>0.65106636288521746</v>
+        <v>0.52085309030817384</v>
       </c>
     </row>
   </sheetData>
@@ -5451,4 +5530,1483 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E4D4EB7-C836-4DCC-ABF5-09A401451DC6}">
+  <dimension ref="A1:F67"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E2" t="s">
+        <v>106</v>
+      </c>
+      <c r="F2" s="32">
+        <f>Herd_decision_tree!B11</f>
+        <v>3.8560896147392438</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D3" t="s">
+        <v>107</v>
+      </c>
+      <c r="E3" t="s">
+        <v>106</v>
+      </c>
+      <c r="F3">
+        <f>F2</f>
+        <v>3.8560896147392438</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D4" t="s">
+        <v>108</v>
+      </c>
+      <c r="E4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F4">
+        <f>F3</f>
+        <v>3.8560896147392438</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C5" t="s">
+        <v>109</v>
+      </c>
+      <c r="D5" t="str">
+        <f>D2</f>
+        <v>male.finisher</v>
+      </c>
+      <c r="E5" t="s">
+        <v>106</v>
+      </c>
+      <c r="F5" s="32">
+        <f>Herd_decision_tree!C11</f>
+        <v>3.7966103839162124</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D6" t="str">
+        <f t="shared" ref="D6:D67" si="0">D3</f>
+        <v>female.finisher</v>
+      </c>
+      <c r="E6" t="s">
+        <v>106</v>
+      </c>
+      <c r="F6">
+        <f>F5</f>
+        <v>3.7966103839162124</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C7" t="s">
+        <v>109</v>
+      </c>
+      <c r="D7" t="str">
+        <f t="shared" si="0"/>
+        <v>female.breeder</v>
+      </c>
+      <c r="E7" t="s">
+        <v>106</v>
+      </c>
+      <c r="F7">
+        <f>F6</f>
+        <v>3.7966103839162124</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
+        <v>110</v>
+      </c>
+      <c r="B8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C8" t="s">
+        <v>104</v>
+      </c>
+      <c r="D8" t="str">
+        <f t="shared" si="0"/>
+        <v>male.finisher</v>
+      </c>
+      <c r="E8" t="s">
+        <v>106</v>
+      </c>
+      <c r="F8" s="32">
+        <f>Herd_decision_tree!B12</f>
+        <v>0.54785010058652572</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
+        <v>110</v>
+      </c>
+      <c r="B9" t="s">
+        <v>103</v>
+      </c>
+      <c r="C9" t="s">
+        <v>104</v>
+      </c>
+      <c r="D9" t="str">
+        <f t="shared" si="0"/>
+        <v>female.finisher</v>
+      </c>
+      <c r="E9" t="s">
+        <v>106</v>
+      </c>
+      <c r="F9">
+        <f>F8</f>
+        <v>0.54785010058652572</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
+        <v>110</v>
+      </c>
+      <c r="B10" t="s">
+        <v>103</v>
+      </c>
+      <c r="C10" t="s">
+        <v>104</v>
+      </c>
+      <c r="D10" t="str">
+        <f t="shared" si="0"/>
+        <v>female.breeder</v>
+      </c>
+      <c r="E10" t="s">
+        <v>106</v>
+      </c>
+      <c r="F10">
+        <f>F9</f>
+        <v>0.54785010058652572</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" t="s">
+        <v>110</v>
+      </c>
+      <c r="B11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C11" t="s">
+        <v>109</v>
+      </c>
+      <c r="D11" t="str">
+        <f t="shared" si="0"/>
+        <v>male.finisher</v>
+      </c>
+      <c r="E11" t="s">
+        <v>106</v>
+      </c>
+      <c r="F11" s="32">
+        <f>Herd_decision_tree!C12</f>
+        <v>0.53939964796616813</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" t="s">
+        <v>110</v>
+      </c>
+      <c r="B12" t="s">
+        <v>103</v>
+      </c>
+      <c r="C12" t="s">
+        <v>109</v>
+      </c>
+      <c r="D12" t="str">
+        <f t="shared" si="0"/>
+        <v>female.finisher</v>
+      </c>
+      <c r="E12" t="s">
+        <v>106</v>
+      </c>
+      <c r="F12">
+        <f>F11</f>
+        <v>0.53939964796616813</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" t="s">
+        <v>110</v>
+      </c>
+      <c r="B13" t="s">
+        <v>103</v>
+      </c>
+      <c r="C13" t="s">
+        <v>109</v>
+      </c>
+      <c r="D13" t="str">
+        <f t="shared" si="0"/>
+        <v>female.breeder</v>
+      </c>
+      <c r="E13" t="s">
+        <v>106</v>
+      </c>
+      <c r="F13">
+        <f>F12</f>
+        <v>0.53939964796616813</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" t="s">
+        <v>102</v>
+      </c>
+      <c r="B14" t="s">
+        <v>111</v>
+      </c>
+      <c r="C14" t="s">
+        <v>109</v>
+      </c>
+      <c r="D14" t="str">
+        <f t="shared" si="0"/>
+        <v>male.finisher</v>
+      </c>
+      <c r="E14" t="s">
+        <v>106</v>
+      </c>
+      <c r="F14" s="32">
+        <f>Herd_decision_tree!C15</f>
+        <v>2.8630122600392172</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C15" t="s">
+        <v>109</v>
+      </c>
+      <c r="D15" t="str">
+        <f t="shared" si="0"/>
+        <v>female.finisher</v>
+      </c>
+      <c r="E15" t="s">
+        <v>106</v>
+      </c>
+      <c r="F15">
+        <f>F14</f>
+        <v>2.8630122600392172</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" t="s">
+        <v>102</v>
+      </c>
+      <c r="B16" t="s">
+        <v>111</v>
+      </c>
+      <c r="C16" t="s">
+        <v>109</v>
+      </c>
+      <c r="D16" t="str">
+        <f t="shared" si="0"/>
+        <v>female.breeder</v>
+      </c>
+      <c r="E16" t="s">
+        <v>106</v>
+      </c>
+      <c r="F16">
+        <f>F15</f>
+        <v>2.8630122600392172</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" t="s">
+        <v>102</v>
+      </c>
+      <c r="B17" t="s">
+        <v>111</v>
+      </c>
+      <c r="C17" t="s">
+        <v>112</v>
+      </c>
+      <c r="D17" t="str">
+        <f t="shared" si="0"/>
+        <v>male.finisher</v>
+      </c>
+      <c r="E17" t="s">
+        <v>106</v>
+      </c>
+      <c r="F17" s="32">
+        <f>Herd_decision_tree!D15</f>
+        <v>2.3979564681756398</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" t="s">
+        <v>102</v>
+      </c>
+      <c r="B18" t="s">
+        <v>111</v>
+      </c>
+      <c r="C18" t="s">
+        <v>112</v>
+      </c>
+      <c r="D18" t="str">
+        <f t="shared" si="0"/>
+        <v>female.finisher</v>
+      </c>
+      <c r="E18" t="s">
+        <v>106</v>
+      </c>
+      <c r="F18">
+        <f>F17</f>
+        <v>2.3979564681756398</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" t="s">
+        <v>102</v>
+      </c>
+      <c r="B19" t="s">
+        <v>111</v>
+      </c>
+      <c r="C19" t="s">
+        <v>112</v>
+      </c>
+      <c r="D19" t="str">
+        <f t="shared" si="0"/>
+        <v>female.breeder</v>
+      </c>
+      <c r="E19" t="s">
+        <v>106</v>
+      </c>
+      <c r="F19">
+        <f>F18</f>
+        <v>2.3979564681756398</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" t="s">
+        <v>110</v>
+      </c>
+      <c r="B20" t="s">
+        <v>111</v>
+      </c>
+      <c r="C20" t="s">
+        <v>109</v>
+      </c>
+      <c r="D20" t="str">
+        <f t="shared" si="0"/>
+        <v>male.finisher</v>
+      </c>
+      <c r="E20" t="s">
+        <v>106</v>
+      </c>
+      <c r="F20" s="32">
+        <f>Herd_decision_tree!C16</f>
+        <v>0.21549554645456476</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" t="s">
+        <v>110</v>
+      </c>
+      <c r="B21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C21" t="s">
+        <v>109</v>
+      </c>
+      <c r="D21" t="str">
+        <f t="shared" si="0"/>
+        <v>female.finisher</v>
+      </c>
+      <c r="E21" t="s">
+        <v>106</v>
+      </c>
+      <c r="F21">
+        <f>F20</f>
+        <v>0.21549554645456476</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" t="s">
+        <v>110</v>
+      </c>
+      <c r="B22" t="s">
+        <v>111</v>
+      </c>
+      <c r="C22" t="s">
+        <v>109</v>
+      </c>
+      <c r="D22" t="str">
+        <f t="shared" si="0"/>
+        <v>female.breeder</v>
+      </c>
+      <c r="E22" t="s">
+        <v>106</v>
+      </c>
+      <c r="F22">
+        <f>F21</f>
+        <v>0.21549554645456476</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" t="s">
+        <v>110</v>
+      </c>
+      <c r="B23" t="s">
+        <v>111</v>
+      </c>
+      <c r="C23" t="s">
+        <v>112</v>
+      </c>
+      <c r="D23" t="str">
+        <f t="shared" si="0"/>
+        <v>male.finisher</v>
+      </c>
+      <c r="E23" t="s">
+        <v>106</v>
+      </c>
+      <c r="F23" s="32">
+        <f>Herd_decision_tree!D16</f>
+        <v>0.18049134706698369</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" t="s">
+        <v>110</v>
+      </c>
+      <c r="B24" t="s">
+        <v>111</v>
+      </c>
+      <c r="C24" t="s">
+        <v>112</v>
+      </c>
+      <c r="D24" t="str">
+        <f t="shared" si="0"/>
+        <v>female.finisher</v>
+      </c>
+      <c r="E24" t="s">
+        <v>106</v>
+      </c>
+      <c r="F24">
+        <f>F23</f>
+        <v>0.18049134706698369</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" t="s">
+        <v>110</v>
+      </c>
+      <c r="B25" t="s">
+        <v>111</v>
+      </c>
+      <c r="C25" t="s">
+        <v>112</v>
+      </c>
+      <c r="D25" t="str">
+        <f t="shared" si="0"/>
+        <v>female.breeder</v>
+      </c>
+      <c r="E25" t="s">
+        <v>106</v>
+      </c>
+      <c r="F25">
+        <f>F24</f>
+        <v>0.18049134706698369</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" t="s">
+        <v>102</v>
+      </c>
+      <c r="B26" t="s">
+        <v>113</v>
+      </c>
+      <c r="C26" t="s">
+        <v>112</v>
+      </c>
+      <c r="D26" t="str">
+        <f t="shared" si="0"/>
+        <v>male.finisher</v>
+      </c>
+      <c r="E26" t="s">
+        <v>106</v>
+      </c>
+      <c r="F26" s="32">
+        <f>Herd_decision_tree!D19</f>
+        <v>0.89527781993409861</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" t="s">
+        <v>102</v>
+      </c>
+      <c r="B27" t="s">
+        <v>113</v>
+      </c>
+      <c r="C27" t="s">
+        <v>112</v>
+      </c>
+      <c r="D27" t="str">
+        <f t="shared" si="0"/>
+        <v>female.finisher</v>
+      </c>
+      <c r="E27" t="s">
+        <v>106</v>
+      </c>
+      <c r="F27">
+        <f>F26</f>
+        <v>0.89527781993409861</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" t="s">
+        <v>102</v>
+      </c>
+      <c r="B28" t="s">
+        <v>113</v>
+      </c>
+      <c r="C28" t="s">
+        <v>112</v>
+      </c>
+      <c r="D28" t="str">
+        <f t="shared" si="0"/>
+        <v>female.breeder</v>
+      </c>
+      <c r="E28" t="s">
+        <v>106</v>
+      </c>
+      <c r="F28">
+        <f>F27</f>
+        <v>0.89527781993409861</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" t="s">
+        <v>110</v>
+      </c>
+      <c r="B29" t="s">
+        <v>113</v>
+      </c>
+      <c r="C29" t="s">
+        <v>112</v>
+      </c>
+      <c r="D29" t="str">
+        <f t="shared" si="0"/>
+        <v>male.finisher</v>
+      </c>
+      <c r="E29" t="s">
+        <v>106</v>
+      </c>
+      <c r="F29" s="32">
+        <f>Herd_decision_tree!D20</f>
+        <v>7.7850245211660743E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" t="s">
+        <v>110</v>
+      </c>
+      <c r="B30" t="s">
+        <v>113</v>
+      </c>
+      <c r="C30" t="s">
+        <v>112</v>
+      </c>
+      <c r="D30" t="str">
+        <f t="shared" si="0"/>
+        <v>female.finisher</v>
+      </c>
+      <c r="E30" t="s">
+        <v>106</v>
+      </c>
+      <c r="F30">
+        <f>F29</f>
+        <v>7.7850245211660743E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" t="s">
+        <v>110</v>
+      </c>
+      <c r="B31" t="s">
+        <v>113</v>
+      </c>
+      <c r="C31" t="s">
+        <v>112</v>
+      </c>
+      <c r="D31" t="str">
+        <f t="shared" si="0"/>
+        <v>female.breeder</v>
+      </c>
+      <c r="E31" t="s">
+        <v>106</v>
+      </c>
+      <c r="F31">
+        <f>F30</f>
+        <v>7.7850245211660743E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" t="s">
+        <v>110</v>
+      </c>
+      <c r="B32" t="s">
+        <v>114</v>
+      </c>
+      <c r="C32" t="s">
+        <v>104</v>
+      </c>
+      <c r="D32" t="str">
+        <f t="shared" si="0"/>
+        <v>male.finisher</v>
+      </c>
+      <c r="E32" t="s">
+        <v>106</v>
+      </c>
+      <c r="F32" s="32">
+        <f>Herd_decision_tree!B30</f>
+        <v>4.4823755155066501E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" t="s">
+        <v>110</v>
+      </c>
+      <c r="B33" t="s">
+        <v>114</v>
+      </c>
+      <c r="C33" t="s">
+        <v>104</v>
+      </c>
+      <c r="D33" t="str">
+        <f t="shared" si="0"/>
+        <v>female.finisher</v>
+      </c>
+      <c r="E33" t="s">
+        <v>106</v>
+      </c>
+      <c r="F33">
+        <f>F32</f>
+        <v>4.4823755155066501E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" t="s">
+        <v>110</v>
+      </c>
+      <c r="B34" t="s">
+        <v>114</v>
+      </c>
+      <c r="C34" t="s">
+        <v>104</v>
+      </c>
+      <c r="D34" t="str">
+        <f t="shared" si="0"/>
+        <v>female.breeder</v>
+      </c>
+      <c r="E34" t="s">
+        <v>106</v>
+      </c>
+      <c r="F34">
+        <f>F33</f>
+        <v>4.4823755155066501E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" t="s">
+        <v>110</v>
+      </c>
+      <c r="B35" t="s">
+        <v>114</v>
+      </c>
+      <c r="C35" t="s">
+        <v>109</v>
+      </c>
+      <c r="D35" t="str">
+        <f t="shared" si="0"/>
+        <v>male.finisher</v>
+      </c>
+      <c r="E35" t="s">
+        <v>106</v>
+      </c>
+      <c r="F35" s="32">
+        <f>Herd_decision_tree!C30</f>
+        <v>0.20716159629967296</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" t="s">
+        <v>110</v>
+      </c>
+      <c r="B36" t="s">
+        <v>114</v>
+      </c>
+      <c r="C36" t="s">
+        <v>109</v>
+      </c>
+      <c r="D36" t="str">
+        <f t="shared" si="0"/>
+        <v>female.finisher</v>
+      </c>
+      <c r="E36" t="s">
+        <v>106</v>
+      </c>
+      <c r="F36">
+        <f>F35</f>
+        <v>0.20716159629967296</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" t="s">
+        <v>110</v>
+      </c>
+      <c r="B37" t="s">
+        <v>114</v>
+      </c>
+      <c r="C37" t="s">
+        <v>109</v>
+      </c>
+      <c r="D37" t="str">
+        <f t="shared" si="0"/>
+        <v>female.breeder</v>
+      </c>
+      <c r="E37" t="s">
+        <v>106</v>
+      </c>
+      <c r="F37">
+        <f>F36</f>
+        <v>0.20716159629967296</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" t="s">
+        <v>110</v>
+      </c>
+      <c r="B38" t="s">
+        <v>114</v>
+      </c>
+      <c r="C38" t="s">
+        <v>112</v>
+      </c>
+      <c r="D38" t="str">
+        <f t="shared" si="0"/>
+        <v>male.finisher</v>
+      </c>
+      <c r="E38" t="s">
+        <v>106</v>
+      </c>
+      <c r="F38" s="32">
+        <f>Herd_decision_tree!D30</f>
+        <v>0.33589803768845672</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" t="s">
+        <v>110</v>
+      </c>
+      <c r="B39" t="s">
+        <v>114</v>
+      </c>
+      <c r="C39" t="s">
+        <v>112</v>
+      </c>
+      <c r="D39" t="str">
+        <f t="shared" si="0"/>
+        <v>female.finisher</v>
+      </c>
+      <c r="E39" t="s">
+        <v>106</v>
+      </c>
+      <c r="F39">
+        <f>F38</f>
+        <v>0.33589803768845672</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" t="s">
+        <v>110</v>
+      </c>
+      <c r="B40" t="s">
+        <v>114</v>
+      </c>
+      <c r="C40" t="s">
+        <v>112</v>
+      </c>
+      <c r="D40" t="str">
+        <f t="shared" si="0"/>
+        <v>female.breeder</v>
+      </c>
+      <c r="E40" t="s">
+        <v>106</v>
+      </c>
+      <c r="F40">
+        <f>F39</f>
+        <v>0.33589803768845672</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" t="s">
+        <v>115</v>
+      </c>
+      <c r="B41" t="s">
+        <v>114</v>
+      </c>
+      <c r="C41" t="s">
+        <v>104</v>
+      </c>
+      <c r="D41" t="str">
+        <f t="shared" si="0"/>
+        <v>male.finisher</v>
+      </c>
+      <c r="E41" t="s">
+        <v>106</v>
+      </c>
+      <c r="F41" s="32">
+        <f>Herd_decision_tree!B31</f>
+        <v>2.1093531837678349E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" t="s">
+        <v>115</v>
+      </c>
+      <c r="B42" t="s">
+        <v>114</v>
+      </c>
+      <c r="C42" t="s">
+        <v>104</v>
+      </c>
+      <c r="D42" t="str">
+        <f t="shared" si="0"/>
+        <v>female.finisher</v>
+      </c>
+      <c r="E42" t="s">
+        <v>106</v>
+      </c>
+      <c r="F42">
+        <f>F41</f>
+        <v>2.1093531837678349E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" t="s">
+        <v>115</v>
+      </c>
+      <c r="B43" t="s">
+        <v>114</v>
+      </c>
+      <c r="C43" t="s">
+        <v>104</v>
+      </c>
+      <c r="D43" t="str">
+        <f t="shared" si="0"/>
+        <v>female.breeder</v>
+      </c>
+      <c r="E43" t="s">
+        <v>106</v>
+      </c>
+      <c r="F43">
+        <f>F42</f>
+        <v>2.1093531837678349E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" t="s">
+        <v>115</v>
+      </c>
+      <c r="B44" t="s">
+        <v>114</v>
+      </c>
+      <c r="C44" t="s">
+        <v>109</v>
+      </c>
+      <c r="D44" t="str">
+        <f t="shared" si="0"/>
+        <v>male.finisher</v>
+      </c>
+      <c r="E44" t="s">
+        <v>106</v>
+      </c>
+      <c r="F44" s="32">
+        <f>Herd_decision_tree!C31</f>
+        <v>9.748781002337549E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" t="s">
+        <v>115</v>
+      </c>
+      <c r="B45" t="s">
+        <v>114</v>
+      </c>
+      <c r="C45" t="s">
+        <v>109</v>
+      </c>
+      <c r="D45" t="str">
+        <f t="shared" si="0"/>
+        <v>female.finisher</v>
+      </c>
+      <c r="E45" t="s">
+        <v>106</v>
+      </c>
+      <c r="F45">
+        <f>F44</f>
+        <v>9.748781002337549E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" t="s">
+        <v>115</v>
+      </c>
+      <c r="B46" t="s">
+        <v>114</v>
+      </c>
+      <c r="C46" t="s">
+        <v>109</v>
+      </c>
+      <c r="D46" t="str">
+        <f t="shared" si="0"/>
+        <v>female.breeder</v>
+      </c>
+      <c r="E46" t="s">
+        <v>106</v>
+      </c>
+      <c r="F46">
+        <f>F45</f>
+        <v>9.748781002337549E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" t="s">
+        <v>115</v>
+      </c>
+      <c r="B47" t="s">
+        <v>114</v>
+      </c>
+      <c r="C47" t="s">
+        <v>112</v>
+      </c>
+      <c r="D47" t="str">
+        <f t="shared" si="0"/>
+        <v>male.finisher</v>
+      </c>
+      <c r="E47" t="s">
+        <v>106</v>
+      </c>
+      <c r="F47" s="32">
+        <f>Herd_decision_tree!D31</f>
+        <v>0.15806966479456783</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" t="s">
+        <v>115</v>
+      </c>
+      <c r="B48" t="s">
+        <v>114</v>
+      </c>
+      <c r="C48" t="s">
+        <v>112</v>
+      </c>
+      <c r="D48" t="str">
+        <f t="shared" si="0"/>
+        <v>female.finisher</v>
+      </c>
+      <c r="E48" t="s">
+        <v>106</v>
+      </c>
+      <c r="F48">
+        <f>F47</f>
+        <v>0.15806966479456783</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" t="s">
+        <v>115</v>
+      </c>
+      <c r="B49" t="s">
+        <v>114</v>
+      </c>
+      <c r="C49" t="s">
+        <v>112</v>
+      </c>
+      <c r="D49" t="str">
+        <f t="shared" si="0"/>
+        <v>female.breeder</v>
+      </c>
+      <c r="E49" t="s">
+        <v>106</v>
+      </c>
+      <c r="F49">
+        <f>F48</f>
+        <v>0.15806966479456783</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" t="s">
+        <v>110</v>
+      </c>
+      <c r="B50" t="s">
+        <v>116</v>
+      </c>
+      <c r="C50" t="s">
+        <v>104</v>
+      </c>
+      <c r="D50" t="str">
+        <f t="shared" si="0"/>
+        <v>male.finisher</v>
+      </c>
+      <c r="E50" t="s">
+        <v>106</v>
+      </c>
+      <c r="F50" s="32">
+        <f>Herd_decision_tree!B26</f>
+        <v>0.14284404919462868</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" t="s">
+        <v>110</v>
+      </c>
+      <c r="B51" t="s">
+        <v>116</v>
+      </c>
+      <c r="C51" t="s">
+        <v>104</v>
+      </c>
+      <c r="D51" t="str">
+        <f t="shared" si="0"/>
+        <v>female.finisher</v>
+      </c>
+      <c r="E51" t="s">
+        <v>106</v>
+      </c>
+      <c r="F51">
+        <f>F50</f>
+        <v>0.14284404919462868</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A52" t="s">
+        <v>110</v>
+      </c>
+      <c r="B52" t="s">
+        <v>116</v>
+      </c>
+      <c r="C52" t="s">
+        <v>104</v>
+      </c>
+      <c r="D52" t="str">
+        <f t="shared" si="0"/>
+        <v>female.breeder</v>
+      </c>
+      <c r="E52" t="s">
+        <v>106</v>
+      </c>
+      <c r="F52">
+        <f>F51</f>
+        <v>0.14284404919462868</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A53" t="s">
+        <v>110</v>
+      </c>
+      <c r="B53" t="s">
+        <v>116</v>
+      </c>
+      <c r="C53" t="s">
+        <v>109</v>
+      </c>
+      <c r="D53" t="str">
+        <f t="shared" si="0"/>
+        <v>male.finisher</v>
+      </c>
+      <c r="E53" t="s">
+        <v>106</v>
+      </c>
+      <c r="F53" s="32">
+        <f>Herd_decision_tree!C26</f>
+        <v>0.19037946157911012</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A54" t="s">
+        <v>110</v>
+      </c>
+      <c r="B54" t="s">
+        <v>116</v>
+      </c>
+      <c r="C54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D54" t="str">
+        <f t="shared" si="0"/>
+        <v>female.finisher</v>
+      </c>
+      <c r="E54" t="s">
+        <v>106</v>
+      </c>
+      <c r="F54">
+        <f>F53</f>
+        <v>0.19037946157911012</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A55" t="s">
+        <v>110</v>
+      </c>
+      <c r="B55" t="s">
+        <v>116</v>
+      </c>
+      <c r="C55" t="s">
+        <v>109</v>
+      </c>
+      <c r="D55" t="str">
+        <f t="shared" si="0"/>
+        <v>female.breeder</v>
+      </c>
+      <c r="E55" t="s">
+        <v>106</v>
+      </c>
+      <c r="F55">
+        <f>F54</f>
+        <v>0.19037946157911012</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A56" t="s">
+        <v>110</v>
+      </c>
+      <c r="B56" t="s">
+        <v>116</v>
+      </c>
+      <c r="C56" t="s">
+        <v>112</v>
+      </c>
+      <c r="D56" t="str">
+        <f t="shared" si="0"/>
+        <v>male.finisher</v>
+      </c>
+      <c r="E56" t="s">
+        <v>106</v>
+      </c>
+      <c r="F56" s="32">
+        <f>Herd_decision_tree!D26</f>
+        <v>0.16534469507538191</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A57" t="s">
+        <v>110</v>
+      </c>
+      <c r="B57" t="s">
+        <v>116</v>
+      </c>
+      <c r="C57" t="s">
+        <v>112</v>
+      </c>
+      <c r="D57" t="str">
+        <f t="shared" si="0"/>
+        <v>female.finisher</v>
+      </c>
+      <c r="E57" t="s">
+        <v>106</v>
+      </c>
+      <c r="F57">
+        <f>F56</f>
+        <v>0.16534469507538191</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A58" t="s">
+        <v>110</v>
+      </c>
+      <c r="B58" t="s">
+        <v>116</v>
+      </c>
+      <c r="C58" t="s">
+        <v>112</v>
+      </c>
+      <c r="D58" t="str">
+        <f t="shared" si="0"/>
+        <v>female.breeder</v>
+      </c>
+      <c r="E58" t="s">
+        <v>106</v>
+      </c>
+      <c r="F58">
+        <f>F57</f>
+        <v>0.16534469507538191</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A59" t="s">
+        <v>115</v>
+      </c>
+      <c r="B59" t="s">
+        <v>116</v>
+      </c>
+      <c r="C59" t="s">
+        <v>104</v>
+      </c>
+      <c r="D59" t="str">
+        <f t="shared" si="0"/>
+        <v>male.finisher</v>
+      </c>
+      <c r="E59" t="s">
+        <v>106</v>
+      </c>
+      <c r="F59" s="32">
+        <f>Herd_decision_tree!B27</f>
+        <v>6.7220729032766421E-2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A60" t="s">
+        <v>115</v>
+      </c>
+      <c r="B60" t="s">
+        <v>116</v>
+      </c>
+      <c r="C60" t="s">
+        <v>104</v>
+      </c>
+      <c r="D60" t="str">
+        <f t="shared" si="0"/>
+        <v>female.finisher</v>
+      </c>
+      <c r="E60" t="s">
+        <v>106</v>
+      </c>
+      <c r="F60">
+        <f>F59</f>
+        <v>6.7220729032766421E-2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A61" t="s">
+        <v>115</v>
+      </c>
+      <c r="B61" t="s">
+        <v>116</v>
+      </c>
+      <c r="C61" t="s">
+        <v>104</v>
+      </c>
+      <c r="D61" t="str">
+        <f t="shared" si="0"/>
+        <v>female.breeder</v>
+      </c>
+      <c r="E61" t="s">
+        <v>106</v>
+      </c>
+      <c r="F61">
+        <f>F60</f>
+        <v>6.7220729032766421E-2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A62" t="s">
+        <v>115</v>
+      </c>
+      <c r="B62" t="s">
+        <v>116</v>
+      </c>
+      <c r="C62" t="s">
+        <v>109</v>
+      </c>
+      <c r="D62" t="str">
+        <f t="shared" si="0"/>
+        <v>male.finisher</v>
+      </c>
+      <c r="E62" t="s">
+        <v>106</v>
+      </c>
+      <c r="F62" s="32">
+        <f>Herd_decision_tree!C27</f>
+        <v>8.9590334860757681E-2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A63" t="s">
+        <v>115</v>
+      </c>
+      <c r="B63" t="s">
+        <v>116</v>
+      </c>
+      <c r="C63" t="s">
+        <v>109</v>
+      </c>
+      <c r="D63" t="str">
+        <f t="shared" si="0"/>
+        <v>female.finisher</v>
+      </c>
+      <c r="E63" t="s">
+        <v>106</v>
+      </c>
+      <c r="F63">
+        <f>F62</f>
+        <v>8.9590334860757681E-2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A64" t="s">
+        <v>115</v>
+      </c>
+      <c r="B64" t="s">
+        <v>116</v>
+      </c>
+      <c r="C64" t="s">
+        <v>109</v>
+      </c>
+      <c r="D64" t="str">
+        <f t="shared" si="0"/>
+        <v>female.breeder</v>
+      </c>
+      <c r="E64" t="s">
+        <v>106</v>
+      </c>
+      <c r="F64">
+        <f>F63</f>
+        <v>8.9590334860757681E-2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A65" t="s">
+        <v>115</v>
+      </c>
+      <c r="B65" t="s">
+        <v>116</v>
+      </c>
+      <c r="C65" t="s">
+        <v>112</v>
+      </c>
+      <c r="D65" t="str">
+        <f t="shared" si="0"/>
+        <v>male.finisher</v>
+      </c>
+      <c r="E65" t="s">
+        <v>106</v>
+      </c>
+      <c r="F65" s="32">
+        <f>Herd_decision_tree!D27</f>
+        <v>7.7809268270767937E-2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A66" t="s">
+        <v>115</v>
+      </c>
+      <c r="B66" t="s">
+        <v>116</v>
+      </c>
+      <c r="C66" t="s">
+        <v>112</v>
+      </c>
+      <c r="D66" t="str">
+        <f t="shared" si="0"/>
+        <v>female.finisher</v>
+      </c>
+      <c r="E66" t="s">
+        <v>106</v>
+      </c>
+      <c r="F66">
+        <f>F65</f>
+        <v>7.7809268270767937E-2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A67" t="s">
+        <v>115</v>
+      </c>
+      <c r="B67" t="s">
+        <v>116</v>
+      </c>
+      <c r="C67" t="s">
+        <v>112</v>
+      </c>
+      <c r="D67" t="str">
+        <f t="shared" si="0"/>
+        <v>female.breeder</v>
+      </c>
+      <c r="E67" t="s">
+        <v>106</v>
+      </c>
+      <c r="F67">
+        <f>F66</f>
+        <v>7.7809268270767937E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Rasterized animal populations/Zonal statistics/Summary.xlsx
+++ b/Rasterized animal populations/Zonal statistics/Summary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JHawkins\Documents\Github\KE.beef.spatial\Rasterized animal populations\Zonal statistics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08A47564-C67D-49E3-9C3A-DC6484DD3231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B674515F-4592-42B5-B838-E2FA95D4231A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" activeTab="5" xr2:uid="{3882C52B-09A6-47D1-94BA-1F6173569800}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="5" xr2:uid="{3882C52B-09A6-47D1-94BA-1F6173569800}"/>
   </bookViews>
   <sheets>
     <sheet name="Validate_2020" sheetId="2" r:id="rId1"/>
@@ -518,7 +518,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -573,11 +573,10 @@
     <xf numFmtId="167" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -603,707 +602,6 @@
       <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="ZS_Grassland_Arid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1">
-        <row r="2">
-          <cell r="D2">
-            <v>202419</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink10.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2020_GRASS_Arid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.33293323112310402</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink11.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2020_GRASS_SArid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.48080803465972</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink12.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2020_CROP_Arid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.97599038751874501</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2020_CROP_SArid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.71416468993051396</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2020_SHRUB_Arid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.20100553202445001</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2020_SHRUB_SArid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.48842843619779902</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink16.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R4_GRASS_Arid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.36084903504638699</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink17.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R4_GRASS_SArid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.51075241024303597</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink18.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R4_GRASS_Humid"/>
-      <sheetName val="filtered"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="2">
-          <cell r="F2">
-            <v>0.90483097904137921</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink19.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R4_CROP_Arid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>1.0384816436740301</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="ZS_Grassland_SArid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="D2">
-            <v>129806</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink20.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R4_CROP_SArid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.72447113600000002</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink21.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R4_CROP_Humid"/>
-      <sheetName val="filtered"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="2">
-          <cell r="F2">
-            <v>0.98649141647533578</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink22.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R4_SHRUB_Arid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.21776707800273001</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink23.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R4_SHRUB_SArid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.51075241024303597</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink24.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R4_SHRUB_Humid"/>
-      <sheetName val="filtered"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="2">
-          <cell r="F2">
-            <v>0.90483097904137921</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink25.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R8_GRASS_Arid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.38422689204237098</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink26.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R8_GRASS_SArid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.51337712420869996</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink27.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R8_GRASS_Humid"/>
-      <sheetName val="filtered"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="2">
-          <cell r="F2">
-            <v>0.88457459938562355</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink28.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R8_CROP_Arid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>1.10532849796393</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink29.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R8_CROP_SArid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.80695680840268103</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="ZS_Grassland_Humid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>64439.636684333513</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink30.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R8_CROP_Humid"/>
-      <sheetName val="filtered"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="2">
-          <cell r="F2">
-            <v>1.0242825546815273</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink31.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R8_SHRUB_Arid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.231319877140652</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink32.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R8_SHRUB_SArid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.51046846997934603</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink33.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R8_SHRUB_Humid"/>
-      <sheetName val="filtered"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="2">
-          <cell r="F2">
-            <v>0.93416975929597834</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink34.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Raster_logic"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="79">
-          <cell r="I79">
-            <v>0.5</v>
-          </cell>
-        </row>
-        <row r="80">
-          <cell r="I80">
-            <v>0.44</v>
-          </cell>
-        </row>
-        <row r="81">
-          <cell r="I81">
-            <v>0.3</v>
-          </cell>
-        </row>
-        <row r="84">
-          <cell r="I84">
-            <v>0.34</v>
-          </cell>
-        </row>
-        <row r="85">
-          <cell r="I85">
-            <v>0.4</v>
-          </cell>
-        </row>
-        <row r="86">
-          <cell r="I86">
-            <v>0.85</v>
-          </cell>
-        </row>
-        <row r="87">
-          <cell r="I87">
-            <v>0.4</v>
-          </cell>
-        </row>
-        <row r="88">
-          <cell r="I88">
-            <v>0.5</v>
-          </cell>
-        </row>
-        <row r="89">
-          <cell r="I89">
-            <v>0.5</v>
-          </cell>
-        </row>
-        <row r="91">
-          <cell r="I91">
-            <v>0.4</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink35.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
       <sheetName val="Model_implemented"/>
       <sheetName val="FAO_2019_animal_trends"/>
       <sheetName val="Raster_logic"/>
@@ -1363,7 +661,231 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink10.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Dairy_total_Humid_2020"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="D2">
+            <v>5233916.3978957208</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink11.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Sheep_total_Arid_2020"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="C2">
+            <v>1300620.48691654</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink12.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Sheep_total_SArid_2020"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="C2">
+            <v>1063972.5190212701</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Sheep_total_Humid_2020"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="D2">
+            <v>1001433.3524225579</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Pastoral_Zebu_2020"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>7912803.5780913802</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Pastoral_Boran_2020"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1">
+        <row r="2">
+          <cell r="K2">
+            <v>1124203.7226895699</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink16.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Pastoral_Zebu_2050"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>8554757.4814370908</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink17.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Pastoral_Boran_2050"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>1215408.67359516</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink18.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Agpastoral_Zebu_2020"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>3685141.0110471202</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink19.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Agpastoral_Boran_2020"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>277376.20390618598</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1385,7 +907,227 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink20.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Agpastoral_Zebu_2050"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>6488770.1197828101</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink21.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Agpastoral_Boran_2050"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>488402.05019366002</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink22.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Mixed_Zebu_2020"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>298374.71550379699</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink23.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Mixed_Boran_2020"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>25945.627401560501</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink24.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Mixed_Zebu_2050"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>404262.59496554697</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink25.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Mixed_Boran_2050"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>35153.269665965803</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink26.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Cowcalf_Boran_2020"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>1184753.34766715</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink27.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Cowcalf_Exotic_2020"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>985977.36353097099</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink28.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Cowcalf_Boran_2050"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>1806208.69891036</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink29.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Cowcalf_Exotic_2050"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>1503165.94333724</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1407,7 +1149,233 @@
 </externalLink>
 </file>
 
+<file path=xl/externalLinks/externalLink30.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Finisher_Boran_2020"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>26321.876059999999</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink31.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Finisher_Exotic_2020"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>12386.7653238613</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink32.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Finisher_Boran_2050"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>918345.45531155204</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink33.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Finisher_Exotic_2050"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>432162.57168335503</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink34.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="ZS_Grassland_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1">
+        <row r="2">
+          <cell r="D2">
+            <v>202419</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink35.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="ZS_Grassland_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="D2">
+            <v>129806</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink36.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="ZS_Grassland_Humid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>64439.636684333513</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink37.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="ZS_Cropland_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="D2">
+            <v>524</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/externalLinks/externalLink38.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="ZS_Cropland_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="D2">
+            <v>19552</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink39.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="ZS_Cropland_Humid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>27078.877240262751</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1429,7 +1397,241 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink39.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink40.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="ZS_Shrubland_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="D2">
+            <v>277889</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink41.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="ZS_Shrubland_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="D2">
+            <v>357491</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink42.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="ZS_Shrubland_Humid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>63327.68656939434</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink43.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2020_GRASS_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.33293323112310402</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink44.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2020_GRASS_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.48080803465972</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink45.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2020_GRASS_Humid"/>
+      <sheetName val="filtered"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="F2">
+            <v>0.88607168377191448</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink46.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2020_CROP_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.97599038751874501</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink47.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2020_CROP_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.71416468993051396</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink48.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2020_CROP_Humid"/>
+      <sheetName val="filtered"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="F2">
+            <v>1.0193612610195171</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink49.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2020_SHRUB_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.20100553202445001</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1451,7 +1653,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink50.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1459,22 +1661,235 @@
       <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="ZS_Cropland_Arid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="D2">
-            <v>524</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink40.xml><?xml version="1.0" encoding="utf-8"?>
+      <sheetName val="NPP_2020_SHRUB_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.48842843619779902</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink51.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2020_SHRUB_Humid"/>
+      <sheetName val="filtered"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="F2">
+            <v>0.9284507277249876</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink52.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R4_GRASS_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.36084903504638699</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink53.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R4_GRASS_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.51075241024303597</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink54.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R4_GRASS_Humid"/>
+      <sheetName val="filtered"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="F2">
+            <v>0.90483097904137921</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink55.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R4_CROP_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>1.0384816436740301</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink56.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R4_CROP_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.72447113600000002</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink57.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R4_CROP_Humid"/>
+      <sheetName val="filtered"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="F2">
+            <v>0.98649141647533578</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink58.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R4_SHRUB_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.21776707800273001</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink59.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R4_SHRUB_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.51075241024303597</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1496,7 +1911,245 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink60.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R4_SHRUB_Humid"/>
+      <sheetName val="filtered"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="F2">
+            <v>0.90483097904137921</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink61.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R8_GRASS_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.38422689204237098</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink62.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R8_GRASS_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.51337712420869996</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink63.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R8_GRASS_Humid"/>
+      <sheetName val="filtered"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="F2">
+            <v>0.88457459938562355</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink64.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R8_CROP_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>1.10532849796393</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink65.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R8_CROP_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.80695680840268103</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink66.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R8_CROP_Humid"/>
+      <sheetName val="filtered"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="F2">
+            <v>1.0242825546815273</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink67.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R8_SHRUB_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.231319877140652</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink68.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R8_SHRUB_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.51046846997934603</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink69.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R8_SHRUB_Humid"/>
+      <sheetName val="filtered"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="F2">
+            <v>0.93416975929597834</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1518,7 +2171,80 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink70.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Raster_logic"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="79">
+          <cell r="I79">
+            <v>0.5</v>
+          </cell>
+        </row>
+        <row r="80">
+          <cell r="I80">
+            <v>0.44</v>
+          </cell>
+        </row>
+        <row r="81">
+          <cell r="I81">
+            <v>0.3</v>
+          </cell>
+        </row>
+        <row r="82">
+          <cell r="I82">
+            <v>0.45</v>
+          </cell>
+        </row>
+        <row r="85">
+          <cell r="I85">
+            <v>0.34</v>
+          </cell>
+        </row>
+        <row r="86">
+          <cell r="I86">
+            <v>0.4</v>
+          </cell>
+        </row>
+        <row r="87">
+          <cell r="I87">
+            <v>0.85</v>
+          </cell>
+        </row>
+        <row r="88">
+          <cell r="I88">
+            <v>0.4</v>
+          </cell>
+        </row>
+        <row r="89">
+          <cell r="I89">
+            <v>0.5</v>
+          </cell>
+        </row>
+        <row r="90">
+          <cell r="I90">
+            <v>0.5</v>
+          </cell>
+        </row>
+        <row r="92">
+          <cell r="I92">
+            <v>0.4</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1541,7 +2267,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1556,728 +2282,6 @@
         <row r="2">
           <cell r="C2">
             <v>1210306.62197518</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink44.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Dairy_total_Humid_2020"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="D2">
-            <v>5233916.3978957208</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink45.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Sheep_total_Arid_2020"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="C2">
-            <v>1300620.48691654</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink46.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Sheep_total_SArid_2020"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="C2">
-            <v>1063972.5190212701</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink47.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Sheep_total_Humid_2020"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="D2">
-            <v>1001433.3524225579</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink48.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Pastoral_Zebu_2020"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>7912803.5780913802</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink49.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Pastoral_Boran_2020"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1">
-        <row r="2">
-          <cell r="K2">
-            <v>1124203.7226895699</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="ZS_Cropland_SArid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="D2">
-            <v>19552</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink50.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Pastoral_Zebu_2050"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>8554757.4814370908</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink51.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Pastoral_Boran_2050"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>1215408.67359516</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink52.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Agpastoral_Zebu_2020"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>3685141.0110471202</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink53.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Agpastoral_Boran_2020"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>277376.20390618598</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink54.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Agpastoral_Zebu_2050"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>6488770.1197828101</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink55.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Agpastoral_Boran_2050"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>488402.05019366002</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink56.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Mixed_Zebu_2020"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>298374.71550379699</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink57.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Mixed_Boran_2020"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>25945.627401560501</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink58.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Mixed_Zebu_2050"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>404262.59496554697</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink59.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Mixed_Boran_2050"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>35153.269665965803</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="ZS_Cropland_Humid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>27078.877240262751</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink60.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Cowcalf_Boran_2020"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>1184753.34766715</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink61.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Cowcalf_Exotic_2020"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>985977.36353097099</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink62.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Cowcalf_Boran_2050"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>1806208.69891036</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink63.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Cowcalf_Exotic_2050"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>1503165.94333724</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink64.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Finisher_Boran_2020"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>26321.876059999999</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink65.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Finisher_Exotic_2020"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>12386.7653238613</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink66.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Finisher_Boran_2050"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>918345.45531155204</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink67.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Finisher_Exotic_2050"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>432162.57168335503</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink68.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2020_GRASS_Humid"/>
-      <sheetName val="filtered"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="2">
-          <cell r="F2">
-            <v>0.88607168377191448</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink69.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2020_CROP_Humid"/>
-      <sheetName val="filtered"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="2">
-          <cell r="F2">
-            <v>1.0193612610195171</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="ZS_Shrubland_Arid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="D2">
-            <v>277889</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink70.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2020_SHRUB_Humid"/>
-      <sheetName val="filtered"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="2">
-          <cell r="F2">
-            <v>0.9284507277249876</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="ZS_Shrubland_SArid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="D2">
-            <v>357491</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="ZS_Shrubland_Humid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>63327.68656939434</v>
           </cell>
         </row>
       </sheetData>
@@ -2663,7 +2667,7 @@
         <v>0.51509165724121786</v>
       </c>
       <c r="D2">
-        <f>[35]FAO_2019_animal_trends!$F$35</f>
+        <f>[1]FAO_2019_animal_trends!$F$35</f>
         <v>0.53615960099750615</v>
       </c>
       <c r="E2">
@@ -2675,7 +2679,7 @@
         <v>0.52629975213940838</v>
       </c>
       <c r="G2">
-        <f>[35]FAO_2019_animal_trends!$G$35</f>
+        <f>[1]FAO_2019_animal_trends!$G$35</f>
         <v>0.38312009613345605</v>
       </c>
       <c r="H2">
@@ -2696,7 +2700,7 @@
         <v>0.33339443937546859</v>
       </c>
       <c r="D3">
-        <f>[35]FAO_2019_animal_trends!$F$36</f>
+        <f>[1]FAO_2019_animal_trends!$F$36</f>
         <v>0.36159600997506236</v>
       </c>
       <c r="E3">
@@ -2708,7 +2712,7 @@
         <v>0.31358889061540685</v>
       </c>
       <c r="G3">
-        <f>[35]FAO_2019_animal_trends!$G$36</f>
+        <f>[1]FAO_2019_animal_trends!$G$36</f>
         <v>2.7950424483806726</v>
       </c>
       <c r="H3">
@@ -2729,7 +2733,7 @@
         <v>5.7351605247385556E-2</v>
       </c>
       <c r="D4">
-        <f>[35]FAO_2019_animal_trends!$F$39</f>
+        <f>[1]FAO_2019_animal_trends!$F$39</f>
         <v>4.9875311720698257E-2</v>
       </c>
       <c r="E4">
@@ -2741,7 +2745,7 @@
         <v>4.6666186084097429E-2</v>
       </c>
       <c r="G4">
-        <f>[35]FAO_2019_animal_trends!$G$40</f>
+        <f>[1]FAO_2019_animal_trends!$G$40</f>
         <v>1.354588821344141</v>
       </c>
       <c r="H4">
@@ -2762,7 +2766,7 @@
         <v>5.0951603562285619E-2</v>
       </c>
       <c r="D5">
-        <f>[35]FAO_2019_animal_trends!$F$38</f>
+        <f>[1]FAO_2019_animal_trends!$F$38</f>
         <v>4.9875311720698257E-2</v>
       </c>
       <c r="E5">
@@ -2774,7 +2778,7 @@
         <v>4.7418024088714393E-2</v>
       </c>
       <c r="G5">
-        <f>[35]FAO_2019_animal_trends!$G$38</f>
+        <f>[1]FAO_2019_animal_trends!$G$38</f>
         <v>1.0372340425531916</v>
       </c>
       <c r="H5">
@@ -2795,7 +2799,7 @@
         <v>4.3210694573642398E-2</v>
       </c>
       <c r="D6">
-        <f>[35]FAO_2019_animal_trends!$F$37</f>
+        <f>[1]FAO_2019_animal_trends!$F$37</f>
         <v>2.4937655860349127E-3</v>
       </c>
       <c r="E6">
@@ -2807,7 +2811,7 @@
         <v>-7.7485333020033496E-3</v>
       </c>
       <c r="G6">
-        <f>[35]FAO_2019_animal_trends!$G$37</f>
+        <f>[1]FAO_2019_animal_trends!$G$37</f>
         <v>86.466565349544069</v>
       </c>
       <c r="H6">
@@ -2885,15 +2889,15 @@
         <v>79</v>
       </c>
       <c r="B2" s="8">
-        <f>[36]Arid_Subsistence!$C$2/1000000</f>
+        <f>[2]Arid_Subsistence!$C$2/1000000</f>
         <v>0.22078565217611199</v>
       </c>
       <c r="C2" s="8">
-        <f>[37]SArid_Subsistence!$C$2/1000000</f>
+        <f>[3]SArid_Subsistence!$C$2/1000000</f>
         <v>0.46769536221033298</v>
       </c>
       <c r="D2" s="8">
-        <f>[38]Humid_Subsistence!$D$2/1000000</f>
+        <f>[4]Humid_Subsistence!$D$2/1000000</f>
         <v>0.58969733266333946</v>
       </c>
       <c r="E2" s="9">
@@ -2918,15 +2922,15 @@
         <v>80</v>
       </c>
       <c r="B3" s="8">
-        <f>[39]Arid_Commercial!$C$2/1000000</f>
+        <f>[5]Arid_Commercial!$C$2/1000000</f>
         <v>4.5806949930214902</v>
       </c>
       <c r="C3" s="8">
-        <f>[40]SArid_Commercial!$C$2/1000000</f>
+        <f>[6]SArid_Commercial!$C$2/1000000</f>
         <v>5.9316142707009298</v>
       </c>
       <c r="D3" s="8">
-        <f>[41]Humid_Commercial!$D$2/1000000</f>
+        <f>[7]Humid_Commercial!$D$2/1000000</f>
         <v>4.9681075438200857</v>
       </c>
       <c r="E3" s="9">
@@ -2948,15 +2952,15 @@
         <v>61</v>
       </c>
       <c r="B4" s="8">
-        <f>[42]Dairy_total_Arid_2020!$C$2/1000000</f>
+        <f>[8]Dairy_total_Arid_2020!$C$2/1000000</f>
         <v>2.48125917562073E-2</v>
       </c>
       <c r="C4" s="8">
-        <f>[43]Dairy_total_SArid_2020!$C$2/1000000</f>
+        <f>[9]Dairy_total_SArid_2020!$C$2/1000000</f>
         <v>1.2103066219751799</v>
       </c>
       <c r="D4" s="8">
-        <f>[44]Dairy_total_Humid_2020!$D$2/1000000</f>
+        <f>[10]Dairy_total_Humid_2020!$D$2/1000000</f>
         <v>5.2339163978957206</v>
       </c>
       <c r="E4" s="9"/>
@@ -2966,15 +2970,15 @@
         <v>83</v>
       </c>
       <c r="B5" s="8">
-        <f>9.78*0.76*[45]Sheep_total_Arid_2020!$C$2/1000000</f>
+        <f>9.78*0.76*[11]Sheep_total_Arid_2020!$C$2/1000000</f>
         <v>9.6672519551532563</v>
       </c>
       <c r="C5" s="8">
-        <f>9.78*0.76*[46]Sheep_total_SArid_2020!$C$2/1000000</f>
+        <f>9.78*0.76*[12]Sheep_total_SArid_2020!$C$2/1000000</f>
         <v>7.908294939381296</v>
       </c>
       <c r="D5" s="8">
-        <f>9.78*0.76*[47]Sheep_total_Humid_2020!$D$2/1000000</f>
+        <f>9.78*0.76*[13]Sheep_total_Humid_2020!$D$2/1000000</f>
         <v>7.4434538218863873</v>
       </c>
       <c r="E5" s="9">
@@ -3748,7 +3752,7 @@
         <v>8.5595346951947899</v>
       </c>
       <c r="C2">
-        <f>[35]FAO_2019_animal_trends!$G$35/100</f>
+        <f>[1]FAO_2019_animal_trends!$G$35/100</f>
         <v>3.8312009613345605E-3</v>
       </c>
       <c r="D2">
@@ -3769,7 +3773,7 @@
         <v>5.5401815014894495</v>
       </c>
       <c r="C3">
-        <f>[35]FAO_2019_animal_trends!$G36/100</f>
+        <f>[1]FAO_2019_animal_trends!$G36/100</f>
         <v>2.7950424483806725E-2</v>
       </c>
       <c r="D3">
@@ -3790,7 +3794,7 @@
         <v>0.95304019787340866</v>
       </c>
       <c r="C4">
-        <f>[35]FAO_2019_animal_trends!$G39/100</f>
+        <f>[1]FAO_2019_animal_trends!$G39/100</f>
         <v>7.6101823708206687E-2</v>
       </c>
       <c r="D4">
@@ -3811,7 +3815,7 @@
         <v>0.84668818128995216</v>
       </c>
       <c r="C5">
-        <f>[35]FAO_2019_animal_trends!$G38/100</f>
+        <f>[1]FAO_2019_animal_trends!$G38/100</f>
         <v>1.0372340425531916E-2</v>
       </c>
       <c r="D5">
@@ -3832,7 +3836,7 @@
         <v>0.71805363998227212</v>
       </c>
       <c r="C6">
-        <f>[35]FAO_2019_animal_trends!$G37/100</f>
+        <f>[1]FAO_2019_animal_trends!$G37/100</f>
         <v>0.86466565349544067</v>
       </c>
       <c r="D6">
@@ -3853,7 +3857,7 @@
         <v>6.4690356116271079</v>
       </c>
       <c r="C7">
-        <f>[35]FAO_2019_animal_trends!$G39/100</f>
+        <f>[1]FAO_2019_animal_trends!$G39/100</f>
         <v>7.6101823708206687E-2</v>
       </c>
       <c r="D7">
@@ -3920,11 +3924,11 @@
         <v>13</v>
       </c>
       <c r="B3">
-        <f>[48]Pastoral_Zebu_2020!$K$2</f>
+        <f>[14]Pastoral_Zebu_2020!$K$2</f>
         <v>7912803.5780913802</v>
       </c>
       <c r="C3">
-        <f>[49]Pastoral_Boran_2020!$K$2</f>
+        <f>[15]Pastoral_Boran_2020!$K$2</f>
         <v>1124203.7226895699</v>
       </c>
       <c r="D3">
@@ -3936,11 +3940,11 @@
         <v>8.5595346951947899</v>
       </c>
       <c r="G3">
-        <f>[50]Pastoral_Zebu_2050!$K$2</f>
+        <f>[16]Pastoral_Zebu_2050!$K$2</f>
         <v>8554757.4814370908</v>
       </c>
       <c r="H3">
-        <f>[51]Pastoral_Boran_2050!$K$2</f>
+        <f>[17]Pastoral_Boran_2050!$K$2</f>
         <v>1215408.67359516</v>
       </c>
       <c r="I3">
@@ -3965,11 +3969,11 @@
         <v>16</v>
       </c>
       <c r="B4">
-        <f>[52]Agpastoral_Zebu_2020!$K$2</f>
+        <f>[18]Agpastoral_Zebu_2020!$K$2</f>
         <v>3685141.0110471202</v>
       </c>
       <c r="C4">
-        <f>[53]Agpastoral_Boran_2020!$K$2</f>
+        <f>[19]Agpastoral_Boran_2020!$K$2</f>
         <v>277376.20390618598</v>
       </c>
       <c r="D4">
@@ -3981,11 +3985,11 @@
         <v>5.5401815014894495</v>
       </c>
       <c r="G4">
-        <f>[54]Agpastoral_Zebu_2050!$K$2</f>
+        <f>[20]Agpastoral_Zebu_2050!$K$2</f>
         <v>6488770.1197828101</v>
       </c>
       <c r="H4">
-        <f>[55]Agpastoral_Boran_2050!$K$2</f>
+        <f>[21]Agpastoral_Boran_2050!$K$2</f>
         <v>488402.05019366002</v>
       </c>
       <c r="I4">
@@ -4010,11 +4014,11 @@
         <v>11</v>
       </c>
       <c r="B5">
-        <f>[56]Mixed_Zebu_2020!$K$2</f>
+        <f>[22]Mixed_Zebu_2020!$K$2</f>
         <v>298374.71550379699</v>
       </c>
       <c r="C5">
-        <f>[57]Mixed_Boran_2020!$K$2</f>
+        <f>[23]Mixed_Boran_2020!$K$2</f>
         <v>25945.627401560501</v>
       </c>
       <c r="D5">
@@ -4026,11 +4030,11 @@
         <v>0.95304019787340866</v>
       </c>
       <c r="G5">
-        <f>[58]Mixed_Zebu_2050!$K$2</f>
+        <f>[24]Mixed_Zebu_2050!$K$2</f>
         <v>404262.59496554697</v>
       </c>
       <c r="H5">
-        <f>[59]Mixed_Boran_2050!$K$2</f>
+        <f>[25]Mixed_Boran_2050!$K$2</f>
         <v>35153.269665965803</v>
       </c>
       <c r="I5">
@@ -4055,11 +4059,11 @@
         <v>42</v>
       </c>
       <c r="B6">
-        <f>[60]Cowcalf_Boran_2020!$K$2</f>
+        <f>[26]Cowcalf_Boran_2020!$K$2</f>
         <v>1184753.34766715</v>
       </c>
       <c r="C6">
-        <f>[61]Cowcalf_Exotic_2020!$K$2</f>
+        <f>[27]Cowcalf_Exotic_2020!$K$2</f>
         <v>985977.36353097099</v>
       </c>
       <c r="D6">
@@ -4071,11 +4075,11 @@
         <v>0.84668818128995216</v>
       </c>
       <c r="G6">
-        <f>[62]Cowcalf_Boran_2050!$K$2</f>
+        <f>[28]Cowcalf_Boran_2050!$K$2</f>
         <v>1806208.69891036</v>
       </c>
       <c r="H6">
-        <f>[63]Cowcalf_Exotic_2050!$K$2</f>
+        <f>[29]Cowcalf_Exotic_2050!$K$2</f>
         <v>1503165.94333724</v>
       </c>
       <c r="I6">
@@ -4100,11 +4104,11 @@
         <v>23</v>
       </c>
       <c r="B7">
-        <f>[64]Finisher_Boran_2020!$K$2</f>
+        <f>[30]Finisher_Boran_2020!$K$2</f>
         <v>26321.876059999999</v>
       </c>
       <c r="C7">
-        <f>[65]Finisher_Exotic_2020!$K$2</f>
+        <f>[31]Finisher_Exotic_2020!$K$2</f>
         <v>12386.7653238613</v>
       </c>
       <c r="D7">
@@ -4116,11 +4120,11 @@
         <v>0.71805363998227212</v>
       </c>
       <c r="G7">
-        <f>[66]Finisher_Boran_2050!$K$2</f>
+        <f>[32]Finisher_Boran_2050!$K$2</f>
         <v>918345.45531155204</v>
       </c>
       <c r="H7">
-        <f>[67]Finisher_Exotic_2050!$K$2</f>
+        <f>[33]Finisher_Exotic_2050!$K$2</f>
         <v>432162.57168335503</v>
       </c>
       <c r="I7">
@@ -4217,15 +4221,15 @@
         <v>89</v>
       </c>
       <c r="C2" s="12">
-        <f>[1]ZS_Grassland_Arid!$D$2*L15</f>
+        <f>[34]ZS_Grassland_Arid!$D$2*L15</f>
         <v>7105918.9949999992</v>
       </c>
       <c r="D2" s="12">
-        <f>[2]ZS_Grassland_SArid!$D$2*L15</f>
+        <f>[35]ZS_Grassland_SArid!$D$2*L15</f>
         <v>4556839.63</v>
       </c>
       <c r="E2" s="12">
-        <f>[3]ZS_Grassland_Humid!$E$2*L15</f>
+        <f>[36]ZS_Grassland_Humid!$E$2*L15</f>
         <v>2262153.4458035277</v>
       </c>
     </row>
@@ -4234,15 +4238,15 @@
         <v>90</v>
       </c>
       <c r="C3" s="12">
-        <f>[4]ZS_Cropland_Arid!$D$2*L15</f>
+        <f>[37]ZS_Cropland_Arid!$D$2*L15</f>
         <v>18395.019999999997</v>
       </c>
       <c r="D3" s="12">
-        <f>[5]ZS_Cropland_SArid!$D$2*L15</f>
+        <f>[38]ZS_Cropland_SArid!$D$2*L15</f>
         <v>686372.96</v>
       </c>
       <c r="E3" s="12">
-        <f>[6]ZS_Cropland_Humid!$E$2*L15</f>
+        <f>[39]ZS_Cropland_Humid!$E$2*L15</f>
         <v>950603.98551942373</v>
       </c>
     </row>
@@ -4251,15 +4255,15 @@
         <v>91</v>
       </c>
       <c r="C4" s="12">
-        <f>[7]ZS_Shrubland_Arid!$D$2*L15</f>
+        <f>[40]ZS_Shrubland_Arid!$D$2*L15</f>
         <v>9755293.3449999988</v>
       </c>
       <c r="D4" s="12">
-        <f>[8]ZS_Shrubland_SArid!$D$2*L15</f>
+        <f>[41]ZS_Shrubland_SArid!$D$2*L15</f>
         <v>12549721.555</v>
       </c>
       <c r="E4" s="12">
-        <f>[9]ZS_Shrubland_Humid!$E$2*L15</f>
+        <f>[42]ZS_Shrubland_Humid!$E$2*L15</f>
         <v>2223118.4370185882</v>
       </c>
     </row>
@@ -4281,15 +4285,15 @@
         <v>71</v>
       </c>
       <c r="C7" s="15">
-        <f>[10]NPP_2020_GRASS_Arid!$E$2</f>
+        <f>[43]NPP_2020_GRASS_Arid!$E$2</f>
         <v>0.33293323112310402</v>
       </c>
       <c r="D7" s="15">
-        <f>[11]NPP_2020_GRASS_SArid!$E$2</f>
+        <f>[44]NPP_2020_GRASS_SArid!$E$2</f>
         <v>0.48080803465972</v>
       </c>
       <c r="E7" s="14">
-        <f>[68]filtered!$F$2</f>
+        <f>[45]filtered!$F$2</f>
         <v>0.88607168377191448</v>
       </c>
     </row>
@@ -4297,16 +4301,16 @@
       <c r="B8" t="s">
         <v>72</v>
       </c>
-      <c r="C8" s="32">
-        <f>[12]NPP_2020_CROP_Arid!$E$2</f>
+      <c r="C8" s="30">
+        <f>[46]NPP_2020_CROP_Arid!$E$2</f>
         <v>0.97599038751874501</v>
       </c>
-      <c r="D8" s="32">
-        <f>[13]NPP_2020_CROP_SArid!$E$2</f>
+      <c r="D8" s="30">
+        <f>[47]NPP_2020_CROP_SArid!$E$2</f>
         <v>0.71416468993051396</v>
       </c>
       <c r="E8" s="14">
-        <f>[69]filtered!$F$2</f>
+        <f>[48]filtered!$F$2</f>
         <v>1.0193612610195171</v>
       </c>
     </row>
@@ -4315,15 +4319,15 @@
         <v>73</v>
       </c>
       <c r="C9" s="15">
-        <f>[14]NPP_2020_SHRUB_Arid!$E$2</f>
+        <f>[49]NPP_2020_SHRUB_Arid!$E$2</f>
         <v>0.20100553202445001</v>
       </c>
       <c r="D9" s="15">
-        <f>[15]NPP_2020_SHRUB_SArid!$E$2</f>
+        <f>[50]NPP_2020_SHRUB_SArid!$E$2</f>
         <v>0.48842843619779902</v>
       </c>
       <c r="E9" s="14">
-        <f>[70]filtered!$F$2</f>
+        <f>[51]filtered!$F$2</f>
         <v>0.9284507277249876</v>
       </c>
       <c r="L9" s="11"/>
@@ -4341,16 +4345,16 @@
       <c r="B11" t="s">
         <v>71</v>
       </c>
-      <c r="C11" s="31">
-        <f>[16]NPP_2050_R4_GRASS_Arid!$E$2</f>
+      <c r="C11" s="15">
+        <f>[52]NPP_2050_R4_GRASS_Arid!$E$2</f>
         <v>0.36084903504638699</v>
       </c>
       <c r="D11" s="15">
-        <f>[17]NPP_2050_R4_GRASS_SArid!$E$2</f>
+        <f>[53]NPP_2050_R4_GRASS_SArid!$E$2</f>
         <v>0.51075241024303597</v>
       </c>
       <c r="E11" s="15">
-        <f>[18]filtered!$F$2</f>
+        <f>[54]filtered!$F$2</f>
         <v>0.90483097904137921</v>
       </c>
       <c r="F11">
@@ -4371,15 +4375,15 @@
         <v>72</v>
       </c>
       <c r="C12" s="15">
-        <f>[19]NPP_2050_R4_CROP_Arid!$E$2</f>
+        <f>[55]NPP_2050_R4_CROP_Arid!$E$2</f>
         <v>1.0384816436740301</v>
       </c>
       <c r="D12" s="15">
-        <f>[20]NPP_2050_R4_CROP_SArid!$E$2</f>
+        <f>[56]NPP_2050_R4_CROP_SArid!$E$2</f>
         <v>0.72447113600000002</v>
       </c>
       <c r="E12" s="15">
-        <f>[21]filtered!$F$2</f>
+        <f>[57]filtered!$F$2</f>
         <v>0.98649141647533578</v>
       </c>
       <c r="F12">
@@ -4400,15 +4404,15 @@
         <v>73</v>
       </c>
       <c r="C13" s="15">
-        <f>[22]NPP_2050_R4_SHRUB_Arid!$E$2</f>
+        <f>[58]NPP_2050_R4_SHRUB_Arid!$E$2</f>
         <v>0.21776707800273001</v>
       </c>
       <c r="D13" s="15">
-        <f>[23]NPP_2050_R4_SHRUB_SArid!$E$2</f>
+        <f>[59]NPP_2050_R4_SHRUB_SArid!$E$2</f>
         <v>0.51075241024303597</v>
       </c>
       <c r="E13" s="15">
-        <f>[24]filtered!$F$2</f>
+        <f>[60]filtered!$F$2</f>
         <v>0.90483097904137921</v>
       </c>
       <c r="F13">
@@ -4437,15 +4441,15 @@
         <v>71</v>
       </c>
       <c r="C15" s="15">
-        <f>[25]NPP_2050_R8_GRASS_Arid!$E$2</f>
+        <f>[61]NPP_2050_R8_GRASS_Arid!$E$2</f>
         <v>0.38422689204237098</v>
       </c>
       <c r="D15" s="15">
-        <f>[26]NPP_2050_R8_GRASS_SArid!$E$2</f>
+        <f>[62]NPP_2050_R8_GRASS_SArid!$E$2</f>
         <v>0.51337712420869996</v>
       </c>
       <c r="E15" s="15">
-        <f>[27]filtered!$F$2</f>
+        <f>[63]filtered!$F$2</f>
         <v>0.88457459938562355</v>
       </c>
       <c r="F15">
@@ -4473,15 +4477,15 @@
         <v>72</v>
       </c>
       <c r="C16" s="15">
-        <f>[28]NPP_2050_R8_CROP_Arid!$E$2</f>
+        <f>[64]NPP_2050_R8_CROP_Arid!$E$2</f>
         <v>1.10532849796393</v>
       </c>
       <c r="D16" s="15">
-        <f>[29]NPP_2050_R8_CROP_SArid!$E$2</f>
+        <f>[65]NPP_2050_R8_CROP_SArid!$E$2</f>
         <v>0.80695680840268103</v>
       </c>
       <c r="E16" s="15">
-        <f>[30]filtered!$F$2</f>
+        <f>[66]filtered!$F$2</f>
         <v>1.0242825546815273</v>
       </c>
       <c r="F16">
@@ -4509,15 +4513,15 @@
         <v>73</v>
       </c>
       <c r="C17" s="15">
-        <f>[31]NPP_2050_R8_SHRUB_Arid!$E$2</f>
+        <f>[67]NPP_2050_R8_SHRUB_Arid!$E$2</f>
         <v>0.231319877140652</v>
       </c>
       <c r="D17" s="15">
-        <f>[32]NPP_2050_R8_SHRUB_SArid!$E$2</f>
+        <f>[68]NPP_2050_R8_SHRUB_SArid!$E$2</f>
         <v>0.51046846997934603</v>
       </c>
       <c r="E17" s="15">
-        <f>[33]filtered!$F$2</f>
+        <f>[69]filtered!$F$2</f>
         <v>0.93416975929597834</v>
       </c>
       <c r="F17">
@@ -4540,33 +4544,33 @@
       <c r="B20" t="s">
         <v>74</v>
       </c>
-      <c r="C20">
-        <f>10000*(1/1000)*(C2*C7+C3*C8*[34]Raster_logic!$I$84+C4*C9*[34]Raster_logic!$I$85)*(1/[34]Raster_logic!$I$79)*[34]Raster_logic!$I$80*[34]Raster_logic!$I$81/1000000</f>
+      <c r="C20" s="15">
+        <f>10000*(1/1000)*(C2*C7+C3*C8*[70]Raster_logic!$I$85+C4*C9*[70]Raster_logic!$I$86)*(1/[70]Raster_logic!$I$79)*[70]Raster_logic!$I$80*[70]Raster_logic!$I$81/1000000</f>
         <v>8.3324944189563208</v>
       </c>
-      <c r="D20">
-        <f>10000*(1/1000)*(D2*D7+D3*D8*[34]Raster_logic!$I$84+D4*D9*[34]Raster_logic!$I$85)*(1/[34]Raster_logic!$I$79)*[34]Raster_logic!$I$80*[34]Raster_logic!$I$81/1000000</f>
+      <c r="D20" s="15">
+        <f>10000*(1/1000)*(D2*D7+D3*D8*[70]Raster_logic!$I$85+D4*D9*[70]Raster_logic!$I$86)*(1/[70]Raster_logic!$I$79)*[70]Raster_logic!$I$80*[70]Raster_logic!$I$81/1000000</f>
         <v>12.69703720354909</v>
       </c>
-      <c r="E20">
-        <f>10000*(1/1000)*(E2*E7+E3*E8*[34]Raster_logic!$I$84+E4*E9*[34]Raster_logic!$I$85)*(1/[34]Raster_logic!$I$79)*[34]Raster_logic!$I$80*[34]Raster_logic!$I$81/1000000</f>
-        <v>8.341120928606971</v>
+      <c r="E20" s="15">
+        <f>10000*(1/1000)*(E2*E7+E3*E8*[70]Raster_logic!$I$85+E4*E9*[70]Raster_logic!$I$86)*(1/[70]Raster_logic!$I$79)*[70]Raster_logic!$I$80*[70]Raster_logic!$I$82/1000000</f>
+        <v>12.511681392910456</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>75</v>
       </c>
-      <c r="C21">
-        <f>10000*(1/1000)*(C3*C8*[34]Raster_logic!$I$91)*(1/[34]Raster_logic!$I$87)*[34]Raster_logic!$I$88*[34]Raster_logic!$I$89*[34]Raster_logic!$I$86/1000000</f>
+      <c r="C21" s="15">
+        <f>10000*(1/1000)*(C3*C8*[70]Raster_logic!$I$92)*(1/[70]Raster_logic!$I$88)*[70]Raster_logic!$I$89*[70]Raster_logic!$I$90*[70]Raster_logic!$I$87/1000000</f>
         <v>3.8150895733707002E-2</v>
       </c>
-      <c r="D21">
-        <f>10000*(1/1000)*(D3*D8*[34]Raster_logic!$I$91)*(1/[34]Raster_logic!$I$87)*[34]Raster_logic!$I$88*[34]Raster_logic!$I$89*[34]Raster_logic!$I$86/1000000</f>
+      <c r="D21" s="15">
+        <f>10000*(1/1000)*(D3*D8*[70]Raster_logic!$I$92)*(1/[70]Raster_logic!$I$88)*[70]Raster_logic!$I$89*[70]Raster_logic!$I$90*[70]Raster_logic!$I$87/1000000</f>
         <v>1.041639580829564</v>
       </c>
-      <c r="E21">
-        <f>10000*(1/1000)*(E3*E8*[34]Raster_logic!$I$91)*(1/[34]Raster_logic!$I$87)*[34]Raster_logic!$I$88*[34]Raster_logic!$I$89*[34]Raster_logic!$I$86/1000000</f>
+      <c r="E21" s="15">
+        <f>10000*(1/1000)*(E3*E8*[70]Raster_logic!$I$92)*(1/[70]Raster_logic!$I$88)*[70]Raster_logic!$I$89*[70]Raster_logic!$I$90*[70]Raster_logic!$I$87/1000000</f>
         <v>2.0591438644946747</v>
       </c>
     </row>
@@ -4574,18 +4578,23 @@
       <c r="B22" t="s">
         <v>76</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="15">
         <f>SUM(C20:C21)</f>
         <v>8.3706453146900284</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="15">
         <f>SUM(D20:D21)</f>
         <v>13.738676784378654</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="15">
         <f>SUM(E20:E21)</f>
-        <v>10.400264793101645</v>
-      </c>
+        <v>14.570825257405129</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
@@ -4595,17 +4604,17 @@
         <f>B20</f>
         <v>BIOM GRASS Supply (MT/ha/yr)</v>
       </c>
-      <c r="C24">
-        <f>10000*(1/1000)*(C2*C11+C3*C12*[34]Raster_logic!$I$84+C4*C13*[34]Raster_logic!$I$85)*(1/[34]Raster_logic!$I$79)*[34]Raster_logic!$I$80*[34]Raster_logic!$I$81/1000000</f>
+      <c r="C24" s="15">
+        <f>10000*(1/1000)*(C2*C11+C3*C12*[70]Raster_logic!$I$85+C4*C13*[70]Raster_logic!$I$86)*(1/[70]Raster_logic!$I$79)*[70]Raster_logic!$I$80*[70]Raster_logic!$I$81/1000000</f>
         <v>9.0298868510117494</v>
       </c>
-      <c r="D24">
-        <f>10000*(1/1000)*(D2*D11+D3*D12*[34]Raster_logic!$I$84+D4*D13*[34]Raster_logic!$I$85)*(1/[34]Raster_logic!$I$79)*[34]Raster_logic!$I$80*[34]Raster_logic!$I$81/1000000</f>
+      <c r="D24" s="15">
+        <f>10000*(1/1000)*(D2*D11+D3*D12*[70]Raster_logic!$I$85+D4*D13*[70]Raster_logic!$I$86)*(1/[70]Raster_logic!$I$79)*[70]Raster_logic!$I$80*[70]Raster_logic!$I$81/1000000</f>
         <v>13.359468018042634</v>
       </c>
-      <c r="E24">
-        <f>10000*(1/1000)*(E2*E11+E3*E12*[34]Raster_logic!$I$84+E4*E13*[34]Raster_logic!$I$85)*(1/[34]Raster_logic!$I$79)*[34]Raster_logic!$I$80*[34]Raster_logic!$I$81/1000000</f>
-        <v>8.3696564117948942</v>
+      <c r="E24" s="15">
+        <f>10000*(1/1000)*(E2*E11+E3*E12*[70]Raster_logic!$I$85+E4*E13*[70]Raster_logic!$I$86)*(1/[70]Raster_logic!$I$79)*[70]Raster_logic!$I$80*[70]Raster_logic!$I$82/1000000</f>
+        <v>12.55448461769234</v>
       </c>
       <c r="F24" s="13">
         <f>C24/C20</f>
@@ -4625,16 +4634,16 @@
         <f t="shared" ref="B25:B26" si="5">B21</f>
         <v>BIOM CROP Supply (MT/ha/yr)</v>
       </c>
-      <c r="C25">
-        <f>10000*(1/1000)*(C12*C3*[34]Raster_logic!$I$91)*(1/[34]Raster_logic!$I$87)*[34]Raster_logic!$I$88*[34]Raster_logic!$I$89*[34]Raster_logic!$I$86/1000000</f>
+      <c r="C25" s="15">
+        <f>10000*(1/1000)*(C12*C3*[70]Raster_logic!$I$92)*(1/[70]Raster_logic!$I$88)*[70]Raster_logic!$I$89*[70]Raster_logic!$I$90*[70]Raster_logic!$I$87/1000000</f>
         <v>4.0593642535660383E-2</v>
       </c>
-      <c r="D25">
-        <f>10000*(1/1000)*(D12*D3*[34]Raster_logic!$I$91)*(1/[34]Raster_logic!$I$87)*[34]Raster_logic!$I$88*[34]Raster_logic!$I$89*[34]Raster_logic!$I$86/1000000</f>
+      <c r="D25" s="15">
+        <f>10000*(1/1000)*(D12*D3*[70]Raster_logic!$I$92)*(1/[70]Raster_logic!$I$88)*[70]Raster_logic!$I$89*[70]Raster_logic!$I$90*[70]Raster_logic!$I$87/1000000</f>
         <v>1.0566719708581258</v>
       </c>
-      <c r="E25">
-        <f>10000*(1/1000)*(E12*E3*[34]Raster_logic!$I$91)*(1/[34]Raster_logic!$I$87)*[34]Raster_logic!$I$88*[34]Raster_logic!$I$89*[34]Raster_logic!$I$86/1000000</f>
+      <c r="E25" s="15">
+        <f>10000*(1/1000)*(E12*E3*[70]Raster_logic!$I$92)*(1/[70]Raster_logic!$I$88)*[70]Raster_logic!$I$89*[70]Raster_logic!$I$90*[70]Raster_logic!$I$87/1000000</f>
         <v>1.9927456783870812</v>
       </c>
       <c r="F25" s="13">
@@ -4655,17 +4664,17 @@
         <f t="shared" si="5"/>
         <v>BIOM Total (MT/ha/yr)</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="15">
         <f>SUM(C24:C25)</f>
         <v>9.070480493547409</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="15">
         <f t="shared" ref="D26:E26" si="7">SUM(D24:D25)</f>
         <v>14.41613998890076</v>
       </c>
-      <c r="E26">
+      <c r="E26" s="15">
         <f t="shared" si="7"/>
-        <v>10.362402090181975</v>
+        <v>14.547230296079421</v>
       </c>
       <c r="F26" s="13">
         <f t="shared" si="6"/>
@@ -4677,8 +4686,13 @@
       </c>
       <c r="H26" s="13">
         <f t="shared" si="4"/>
-        <v>0.99635944818012867</v>
-      </c>
+        <v>0.99838067090168992</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C27" s="15"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
@@ -4688,17 +4702,17 @@
         <f>B24</f>
         <v>BIOM GRASS Supply (MT/ha/yr)</v>
       </c>
-      <c r="C28">
-        <f>10000*(1/1000)*(C2*C15+C3*C16*[34]Raster_logic!$I$84+C4*C17*[34]Raster_logic!$I$85)*(1/[34]Raster_logic!$I$79)*[34]Raster_logic!$I$80*[34]Raster_logic!$I$81/1000000</f>
+      <c r="C28" s="15">
+        <f>10000*(1/1000)*(C2*C15+C3*C16*[70]Raster_logic!$I$85+C4*C17*[70]Raster_logic!$I$86)*(1/[70]Raster_logic!$I$79)*[70]Raster_logic!$I$80*[70]Raster_logic!$I$81/1000000</f>
         <v>9.609165818496594</v>
       </c>
-      <c r="D28">
-        <f>10000*(1/1000)*(D2*D15+D3*D16*[34]Raster_logic!$I$84+D4*D17*[34]Raster_logic!$I$85)*(1/[34]Raster_logic!$I$79)*[34]Raster_logic!$I$80*[34]Raster_logic!$I$81/1000000</f>
+      <c r="D28" s="15">
+        <f>10000*(1/1000)*(D2*D15+D3*D16*[70]Raster_logic!$I$85+D4*D17*[70]Raster_logic!$I$86)*(1/[70]Raster_logic!$I$79)*[70]Raster_logic!$I$80*[70]Raster_logic!$I$81/1000000</f>
         <v>13.438099018999708</v>
       </c>
-      <c r="E28">
-        <f>10000*(1/1000)*(E2*E15+E3*E16*[34]Raster_logic!$I$84+E4*E17*[34]Raster_logic!$I$85)*(1/[34]Raster_logic!$I$79)*[34]Raster_logic!$I$80*[34]Raster_logic!$I$81/1000000</f>
-        <v>8.3498054400644932</v>
+      <c r="E28" s="15">
+        <f>10000*(1/1000)*(E2*E15+E3*E16*[70]Raster_logic!$I$85+E4*E17*[70]Raster_logic!$I$86)*(1/[70]Raster_logic!$I$79)*[70]Raster_logic!$I$80*[70]Raster_logic!$I$82/1000000</f>
+        <v>12.52470816009674</v>
       </c>
       <c r="F28" s="13">
         <f>C28/C20</f>
@@ -4710,7 +4724,7 @@
       </c>
       <c r="H28" s="13">
         <f t="shared" si="8"/>
-        <v>1.0010411683911375</v>
+        <v>1.0010411683911378</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -4718,28 +4732,28 @@
         <f t="shared" ref="B29:B30" si="9">B25</f>
         <v>BIOM CROP Supply (MT/ha/yr)</v>
       </c>
-      <c r="C29">
-        <f>10000*(1/1000)*(C16*C3*[34]Raster_logic!$I$91)*(1/[34]Raster_logic!$I$87)*[34]Raster_logic!$I$88*[34]Raster_logic!$I$89*[34]Raster_logic!$I$86/1000000</f>
+      <c r="C29" s="15">
+        <f>10000*(1/1000)*(C16*C3*[70]Raster_logic!$I$92)*(1/[70]Raster_logic!$I$88)*[70]Raster_logic!$I$89*[70]Raster_logic!$I$90*[70]Raster_logic!$I$87/1000000</f>
         <v>4.3206647131559951E-2</v>
       </c>
-      <c r="D29">
-        <f>10000*(1/1000)*(D16*D3*[34]Raster_logic!$I$91)*(1/[34]Raster_logic!$I$87)*[34]Raster_logic!$I$88*[34]Raster_logic!$I$89*[34]Raster_logic!$I$86/1000000</f>
+      <c r="D29" s="15">
+        <f>10000*(1/1000)*(D16*D3*[70]Raster_logic!$I$92)*(1/[70]Raster_logic!$I$88)*[70]Raster_logic!$I$89*[70]Raster_logic!$I$90*[70]Raster_logic!$I$87/1000000</f>
         <v>1.1769808329979399</v>
       </c>
-      <c r="E29">
-        <f>10000*(1/1000)*(E16*E3*[34]Raster_logic!$I$91)*(1/[34]Raster_logic!$I$87)*[34]Raster_logic!$I$88*[34]Raster_logic!$I$89*[34]Raster_logic!$I$86/1000000</f>
+      <c r="E29" s="15">
+        <f>10000*(1/1000)*(E16*E3*[70]Raster_logic!$I$92)*(1/[70]Raster_logic!$I$88)*[70]Raster_logic!$I$89*[70]Raster_logic!$I$90*[70]Raster_logic!$I$87/1000000</f>
         <v>2.0690850424038385</v>
       </c>
       <c r="F29" s="13">
-        <f t="shared" ref="F29:F30" si="10">C29/C21</f>
+        <f>C29/C21</f>
         <v>1.1325198609527298</v>
       </c>
       <c r="G29" s="13">
-        <f t="shared" ref="G29:G30" si="11">D29/D21</f>
+        <f t="shared" ref="G29:G30" si="10">D29/D21</f>
         <v>1.1299309805994409</v>
       </c>
       <c r="H29" s="13">
-        <f t="shared" ref="H29:H30" si="12">E29/E21</f>
+        <f t="shared" ref="H29:H30" si="11">E29/E21</f>
         <v>1.0048278209602433</v>
       </c>
     </row>
@@ -4748,29 +4762,29 @@
         <f t="shared" si="9"/>
         <v>BIOM Total (MT/ha/yr)</v>
       </c>
-      <c r="C30">
+      <c r="C30" s="15">
         <f>SUM(C28:C29)</f>
         <v>9.6523724656281544</v>
       </c>
-      <c r="D30">
+      <c r="D30" s="15">
         <f>SUM(D28:D29)</f>
         <v>14.615079851997647</v>
       </c>
-      <c r="E30">
-        <f t="shared" ref="E30" si="13">SUM(E28:E29)</f>
-        <v>10.418890482468331</v>
+      <c r="E30" s="15">
+        <f t="shared" ref="E30" si="12">SUM(E28:E29)</f>
+        <v>14.593793202500578</v>
       </c>
       <c r="F30" s="13">
+        <f t="shared" ref="F30" si="13">C30/C22</f>
+        <v>1.153121665385674</v>
+      </c>
+      <c r="G30" s="13">
         <f t="shared" si="10"/>
-        <v>1.153121665385674</v>
-      </c>
-      <c r="G30" s="13">
+        <v>1.0637909371749319</v>
+      </c>
+      <c r="H30" s="13">
         <f t="shared" si="11"/>
-        <v>1.0637909371749319</v>
-      </c>
-      <c r="H30" s="13">
-        <f t="shared" si="12"/>
-        <v>1.001790886072347</v>
+        <v>1.0015762967909985</v>
       </c>
     </row>
   </sheetData>
@@ -4927,7 +4941,7 @@
         <v>96</v>
       </c>
       <c r="I6">
-        <v>8.5000000000000006E-2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -5036,7 +5050,7 @@
       </c>
       <c r="E14" s="25">
         <f>365*(E10+E11+E12)*(1-$I6)*($I7)/1000/1000000</f>
-        <v>12.628042474418631</v>
+        <v>12.421025384674063</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -5056,7 +5070,7 @@
       </c>
       <c r="E16" s="19">
         <f>NPP!E22</f>
-        <v>10.400264793101645</v>
+        <v>14.570825257405129</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -5076,7 +5090,7 @@
       </c>
       <c r="E18" s="6">
         <f>E16/E14</f>
-        <v>0.8235848758166654</v>
+        <v>1.173077488061786</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -5183,8 +5197,8 @@
         <v>1.2452331192095332</v>
       </c>
       <c r="E26">
-        <f>E7+E7*30*Validate_2020!I8/100</f>
-        <v>5.2339163978957206</v>
+        <f>E7+E7*30*Validate_2020!G4/100</f>
+        <v>7.3608577912275219</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -5200,8 +5214,8 @@
         <v>14.122444247942596</v>
       </c>
       <c r="E27">
-        <f>E8+E8*30*0.8*Validate_2020!$G7/100</f>
-        <v>11.512245654315745</v>
+        <f>E8+E8*30*0.2*Validate_2020!$G7/100</f>
+        <v>8.4606517799937269</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -5235,7 +5249,7 @@
       </c>
       <c r="E31">
         <f t="shared" si="2"/>
-        <v>1046783279.5791441</v>
+        <v>1472171558.2455044</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -5251,8 +5265,8 @@
         <v>494285548.67799085</v>
       </c>
       <c r="E32">
-        <f t="shared" si="2"/>
-        <v>402928597.9010511</v>
+        <f>E27*$I3*1000000</f>
+        <v>296122812.29978043</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -5269,7 +5283,7 @@
       </c>
       <c r="E34" s="26">
         <f>365*(E30+E31+E32)*(1-$I6)*($I7)/1000/1000000</f>
-        <v>21.771888607324968</v>
+        <v>23.508059380085147</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -5291,19 +5305,19 @@
       </c>
       <c r="E36" s="27">
         <f>NPP!E26</f>
-        <v>10.362402090181975</v>
+        <v>14.547230296079421</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B37" s="1"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B38" s="30" t="s">
+      <c r="B38" s="31" t="s">
         <v>82</v>
       </c>
-      <c r="C38" s="30"/>
-      <c r="D38" s="30"/>
-      <c r="E38" s="30"/>
+      <c r="C38" s="31"/>
+      <c r="D38" s="31"/>
+      <c r="E38" s="31"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B39" s="20">
@@ -5319,7 +5333,7 @@
       </c>
       <c r="E39" s="21">
         <f t="shared" si="3"/>
-        <v>0.47595329358315902</v>
+        <v>0.61881885105340118</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -5337,7 +5351,7 @@
       </c>
       <c r="E40" s="21">
         <f t="shared" si="4"/>
-        <v>0.64976908469991224</v>
+        <v>0.8959481695575936</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -5369,7 +5383,7 @@
       </c>
       <c r="E43" s="29">
         <f t="shared" si="5"/>
-        <v>21.771888607324968</v>
+        <v>23.508059380085147</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -5392,7 +5406,7 @@
       </c>
       <c r="E45" s="23">
         <f>NPP!E30</f>
-        <v>10.418890482468331</v>
+        <v>14.593793202500578</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -5402,12 +5416,12 @@
       <c r="E46" s="3"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B47" s="30" t="s">
+      <c r="B47" s="31" t="s">
         <v>82</v>
       </c>
-      <c r="C47" s="30"/>
-      <c r="D47" s="30"/>
-      <c r="E47" s="30"/>
+      <c r="C47" s="31"/>
+      <c r="D47" s="31"/>
+      <c r="E47" s="31"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B48" s="20">
@@ -5423,7 +5437,7 @@
       </c>
       <c r="E48" s="21">
         <f>E45/E43</f>
-        <v>0.47854784995376948</v>
+        <v>0.62079957203373881</v>
       </c>
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.25">
@@ -5440,7 +5454,7 @@
       </c>
       <c r="E49" s="21">
         <f t="shared" si="7"/>
-        <v>0.65106636288521746</v>
+        <v>0.89693853004776236</v>
       </c>
     </row>
   </sheetData>

--- a/Rasterized animal populations/Zonal statistics/Summary.xlsx
+++ b/Rasterized animal populations/Zonal statistics/Summary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JHawkins\Documents\Github\KE.beef.spatial\Rasterized animal populations\Zonal statistics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ADE265A-2F75-43CF-954F-D3B08118201E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0AE5A25-8871-4B42-8F94-AE9C9816166C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="5" xr2:uid="{3882C52B-09A6-47D1-94BA-1F6173569800}"/>
   </bookViews>
@@ -559,14 +559,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="7">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="0.00000000"/>
     <numFmt numFmtId="165" formatCode="0.000000000"/>
     <numFmt numFmtId="166" formatCode="0.0000000"/>
     <numFmt numFmtId="167" formatCode="0.000"/>
     <numFmt numFmtId="168" formatCode="0.0000"/>
     <numFmt numFmtId="169" formatCode="0.00000"/>
-    <numFmt numFmtId="170" formatCode="0.0"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -666,7 +665,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -723,23 +722,13 @@
     </xf>
     <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -748,7 +737,16 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -767,6 +765,777 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="ZS_Grassland_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1">
+        <row r="2">
+          <cell r="D2">
+            <v>202419</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink10.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2020_GRASS_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.33293323112310402</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink11.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2020_GRASS_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.48080803465972</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink12.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2020_GRASS_Humid"/>
+      <sheetName val="filtered"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="F2">
+            <v>0.88607168377191448</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2020_CROP_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.97599038751874501</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2020_CROP_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.71416468993051396</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2020_CROP_Humid"/>
+      <sheetName val="filtered"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="F2">
+            <v>1.0193612610195171</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink16.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2020_SHRUB_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.20100553202445001</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink17.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2020_SHRUB_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.48842843619779902</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink18.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2020_SHRUB_Humid"/>
+      <sheetName val="filtered"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="F2">
+            <v>0.9284507277249876</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink19.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R4_GRASS_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.36084903504638699</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="ZS_Grassland_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="D2">
+            <v>129806</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink20.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R4_GRASS_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.51075241024303597</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink21.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R4_GRASS_Humid"/>
+      <sheetName val="filtered"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="F2">
+            <v>0.90483097904137921</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink22.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R4_CROP_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>1.0384816436740301</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink23.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R4_CROP_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.72447113600000002</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink24.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R4_CROP_Humid"/>
+      <sheetName val="filtered"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="F2">
+            <v>0.98649141647533578</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink25.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R4_SHRUB_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.21776707800273001</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink26.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R4_SHRUB_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.51075241024303597</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink27.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R4_SHRUB_Humid"/>
+      <sheetName val="filtered"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="F2">
+            <v>0.90483097904137921</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink28.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R8_GRASS_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.38422689204237098</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink29.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R8_GRASS_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.51337712420869996</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="ZS_Grassland_Humid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>64439.636684333513</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink30.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R8_GRASS_Humid"/>
+      <sheetName val="filtered"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="F2">
+            <v>0.88457459938562355</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink31.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R8_CROP_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>1.10532849796393</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink32.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R8_CROP_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.80695680840268103</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink33.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R8_CROP_Humid"/>
+      <sheetName val="filtered"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="F2">
+            <v>1.0242825546815273</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink34.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R8_SHRUB_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.231319877140652</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink35.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R8_SHRUB_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.51046846997934603</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink36.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R8_SHRUB_Humid"/>
+      <sheetName val="filtered"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="F2">
+            <v>0.93416975929597834</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink37.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Raster_logic"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="89">
+          <cell r="I89">
+            <v>0.5</v>
+          </cell>
+        </row>
+        <row r="90">
+          <cell r="I90">
+            <v>0.44</v>
+          </cell>
+        </row>
+        <row r="91">
+          <cell r="I91">
+            <v>0.36499999999999999</v>
+          </cell>
+        </row>
+        <row r="95">
+          <cell r="I95">
+            <v>0.34</v>
+          </cell>
+        </row>
+        <row r="96">
+          <cell r="I96">
+            <v>0.4</v>
+          </cell>
+        </row>
+        <row r="98">
+          <cell r="I98">
+            <v>0.4</v>
+          </cell>
+        </row>
+        <row r="99">
+          <cell r="I99">
+            <v>0.7</v>
+          </cell>
+        </row>
+        <row r="100">
+          <cell r="I100">
+            <v>0.7</v>
+          </cell>
+        </row>
+        <row r="102">
+          <cell r="I102">
+            <v>0.4</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink38.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -831,7 +1600,208 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink39.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Arid_Subsistence"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1">
+        <row r="2">
+          <cell r="C2">
+            <v>220785.65217611199</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="ZS_Cropland_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="D2">
+            <v>524</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink40.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="SArid_Subsistence"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1">
+        <row r="2">
+          <cell r="C2">
+            <v>467695.362210333</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink41.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Humid_Subsistence"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1">
+        <row r="2">
+          <cell r="D2">
+            <v>589697.33266333945</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink42.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Arid_Commercial"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1">
+        <row r="2">
+          <cell r="C2">
+            <v>4580694.9930214901</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink43.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="SArid_Commercial"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1">
+        <row r="2">
+          <cell r="C2">
+            <v>5931614.2707009297</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink44.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Humid_Commercial"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1">
+        <row r="2">
+          <cell r="D2">
+            <v>4968107.5438200859</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink45.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Dairy_total_Arid_2020"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1">
+        <row r="2">
+          <cell r="C2">
+            <v>24812.591756207301</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink46.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Dairy_total_SArid_2020"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1">
+        <row r="2">
+          <cell r="C2">
+            <v>1210306.62197518</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink47.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -854,7 +1824,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink48.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -877,7 +1847,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink49.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -900,7 +1870,30 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="ZS_Cropland_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="D2">
+            <v>19552</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink50.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -923,7 +1916,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink51.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -945,7 +1938,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink52.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -967,7 +1960,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink53.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -989,7 +1982,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink54.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1011,7 +2004,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink55.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1033,7 +2026,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink56.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1055,29 +2048,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Arid_Subsistence"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1">
-        <row r="2">
-          <cell r="C2">
-            <v>220785.65217611199</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink57.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1099,7 +2070,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink58.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1121,7 +2092,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink59.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1143,386 +2114,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink23.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Mixed_Boran_2020"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>25945.627401560501</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink24.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Mixed_Zebu_2050"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>404262.59496554697</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink25.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Mixed_Boran_2050"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>35153.269665965803</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink26.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Cowcalf_Boran_2020"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>1184753.34766715</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink27.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Cowcalf_Exotic_2020"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>985977.36353097099</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink28.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Cowcalf_Boran_2050"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>1806208.69891036</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink29.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Cowcalf_Exotic_2050"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>1503165.94333724</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="SArid_Subsistence"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1">
-        <row r="2">
-          <cell r="C2">
-            <v>467695.362210333</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink30.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Finisher_Boran_2020"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>26321.876059999999</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink31.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Finisher_Exotic_2020"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>12386.7653238613</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink32.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Finisher_Boran_2050"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>918345.45531155204</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink33.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Finisher_Exotic_2050"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>432162.57168335503</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink34.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="ZS_Grassland_Arid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1">
-        <row r="2">
-          <cell r="D2">
-            <v>202419</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink35.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="ZS_Grassland_SArid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="D2">
-            <v>129806</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink36.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="ZS_Grassland_Humid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>64439.636684333513</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink37.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="ZS_Cropland_Arid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="D2">
-            <v>524</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink38.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="ZS_Cropland_SArid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="D2">
-            <v>19552</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink39.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1545,20 +2137,20 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink60.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="Humid_Subsistence"/>
+      <sheetName val="Mixed_Boran_2020"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1">
+      <sheetData sheetId="0">
         <row r="2">
-          <cell r="D2">
-            <v>589697.33266333945</v>
+          <cell r="K2">
+            <v>25945.627401560501</v>
           </cell>
         </row>
       </sheetData>
@@ -1567,7 +2159,205 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink40.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink61.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Mixed_Zebu_2050"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>404262.59496554697</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink62.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Mixed_Boran_2050"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>35153.269665965803</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink63.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Cowcalf_Boran_2020"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>1184753.34766715</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink64.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Cowcalf_Exotic_2020"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>985977.36353097099</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink65.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Cowcalf_Boran_2050"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>1806208.69891036</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink66.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Cowcalf_Exotic_2050"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>1503165.94333724</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink67.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Finisher_Boran_2020"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>26321.876059999999</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink68.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Finisher_Exotic_2020"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>12386.7653238613</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink69.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Finisher_Boran_2050"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>918345.45531155204</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1590,7 +2380,29 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink70.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Finisher_Exotic_2050"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>432162.57168335503</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1613,7 +2425,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1628,830 +2440,6 @@
         <row r="2">
           <cell r="E2">
             <v>63327.68656939434</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink43.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2020_GRASS_Arid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.33293323112310402</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink44.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2020_GRASS_SArid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.48080803465972</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink45.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2020_GRASS_Humid"/>
-      <sheetName val="filtered"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="2">
-          <cell r="F2">
-            <v>0.88607168377191448</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink46.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2020_CROP_Arid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.97599038751874501</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink47.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2020_CROP_SArid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.71416468993051396</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink48.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2020_CROP_Humid"/>
-      <sheetName val="filtered"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="2">
-          <cell r="F2">
-            <v>1.0193612610195171</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink49.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2020_SHRUB_Arid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.20100553202445001</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Arid_Commercial"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1">
-        <row r="2">
-          <cell r="C2">
-            <v>4580694.9930214901</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink50.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2020_SHRUB_SArid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.48842843619779902</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink51.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2020_SHRUB_Humid"/>
-      <sheetName val="filtered"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="2">
-          <cell r="F2">
-            <v>0.9284507277249876</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink52.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R4_GRASS_Arid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.36084903504638699</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink53.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R4_GRASS_SArid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.51075241024303597</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink54.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R4_GRASS_Humid"/>
-      <sheetName val="filtered"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="2">
-          <cell r="F2">
-            <v>0.90483097904137921</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink55.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R4_CROP_Arid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>1.0384816436740301</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink56.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R4_CROP_SArid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.72447113600000002</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink57.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R4_CROP_Humid"/>
-      <sheetName val="filtered"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="2">
-          <cell r="F2">
-            <v>0.98649141647533578</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink58.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R4_SHRUB_Arid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.21776707800273001</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink59.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R4_SHRUB_SArid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.51075241024303597</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="SArid_Commercial"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1">
-        <row r="2">
-          <cell r="C2">
-            <v>5931614.2707009297</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink60.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R4_SHRUB_Humid"/>
-      <sheetName val="filtered"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="2">
-          <cell r="F2">
-            <v>0.90483097904137921</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink61.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R8_GRASS_Arid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.38422689204237098</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink62.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R8_GRASS_SArid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.51337712420869996</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink63.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R8_GRASS_Humid"/>
-      <sheetName val="filtered"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="2">
-          <cell r="F2">
-            <v>0.88457459938562355</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink64.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R8_CROP_Arid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>1.10532849796393</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink65.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R8_CROP_SArid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.80695680840268103</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink66.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R8_CROP_Humid"/>
-      <sheetName val="filtered"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="2">
-          <cell r="F2">
-            <v>1.0242825546815273</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink67.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R8_SHRUB_Arid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.231319877140652</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink68.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R8_SHRUB_SArid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.51046846997934603</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink69.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R8_SHRUB_Humid"/>
-      <sheetName val="filtered"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="2">
-          <cell r="F2">
-            <v>0.93416975929597834</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Humid_Commercial"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1">
-        <row r="2">
-          <cell r="D2">
-            <v>4968107.5438200859</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink70.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Raster_logic"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="79">
-          <cell r="I79">
-            <v>0.5</v>
-          </cell>
-        </row>
-        <row r="80">
-          <cell r="I80">
-            <v>0.44</v>
-          </cell>
-        </row>
-        <row r="81">
-          <cell r="I81">
-            <v>0.36499999999999999</v>
-          </cell>
-        </row>
-        <row r="82">
-          <cell r="I82">
-            <v>0.4</v>
-          </cell>
-        </row>
-        <row r="84">
-          <cell r="I84">
-            <v>1</v>
-          </cell>
-        </row>
-        <row r="85">
-          <cell r="I85">
-            <v>0.34</v>
-          </cell>
-        </row>
-        <row r="87">
-          <cell r="I87">
-            <v>0.85</v>
-          </cell>
-        </row>
-        <row r="88">
-          <cell r="I88">
-            <v>0.4</v>
-          </cell>
-        </row>
-        <row r="89">
-          <cell r="I89">
-            <v>0.5</v>
-          </cell>
-        </row>
-        <row r="90">
-          <cell r="I90">
-            <v>0.7</v>
-          </cell>
-        </row>
-        <row r="92">
-          <cell r="I92">
-            <v>0.4</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Dairy_total_Arid_2020"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1">
-        <row r="2">
-          <cell r="C2">
-            <v>24812.591756207301</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Dairy_total_SArid_2020"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1">
-        <row r="2">
-          <cell r="C2">
-            <v>1210306.62197518</v>
           </cell>
         </row>
       </sheetData>
@@ -2837,7 +2825,7 @@
         <v>0.51509165724121786</v>
       </c>
       <c r="D2">
-        <f>[1]FAO_2019_animal_trends!$F$35</f>
+        <f>[38]FAO_2019_animal_trends!$F$35</f>
         <v>0.53615960099750615</v>
       </c>
       <c r="E2">
@@ -2849,7 +2837,7 @@
         <v>0.52629975213940838</v>
       </c>
       <c r="G2">
-        <f>[1]FAO_2019_animal_trends!$G$35</f>
+        <f>[38]FAO_2019_animal_trends!$G$35</f>
         <v>0.38312009613345605</v>
       </c>
       <c r="H2">
@@ -2870,7 +2858,7 @@
         <v>0.33339443937546853</v>
       </c>
       <c r="D3">
-        <f>[1]FAO_2019_animal_trends!$F$36</f>
+        <f>[38]FAO_2019_animal_trends!$F$36</f>
         <v>0.36159600997506236</v>
       </c>
       <c r="E3">
@@ -2882,7 +2870,7 @@
         <v>0.31358889061540685</v>
       </c>
       <c r="G3">
-        <f>[1]FAO_2019_animal_trends!$G$36</f>
+        <f>[38]FAO_2019_animal_trends!$G$36</f>
         <v>2.7950424483806726</v>
       </c>
       <c r="H3">
@@ -2903,7 +2891,7 @@
         <v>5.7351605247385563E-2</v>
       </c>
       <c r="D4">
-        <f>[1]FAO_2019_animal_trends!$F$39</f>
+        <f>[38]FAO_2019_animal_trends!$F$39</f>
         <v>4.9875311720698257E-2</v>
       </c>
       <c r="E4">
@@ -2915,7 +2903,7 @@
         <v>4.6666186084097429E-2</v>
       </c>
       <c r="G4">
-        <f>[1]FAO_2019_animal_trends!$G$40</f>
+        <f>[38]FAO_2019_animal_trends!$G$40</f>
         <v>1.354588821344141</v>
       </c>
       <c r="H4">
@@ -2936,7 +2924,7 @@
         <v>5.0951603562285619E-2</v>
       </c>
       <c r="D5">
-        <f>[1]FAO_2019_animal_trends!$F$38</f>
+        <f>[38]FAO_2019_animal_trends!$F$38</f>
         <v>4.9875311720698257E-2</v>
       </c>
       <c r="E5">
@@ -2948,7 +2936,7 @@
         <v>4.7418024088714393E-2</v>
       </c>
       <c r="G5">
-        <f>[1]FAO_2019_animal_trends!$G$38</f>
+        <f>[38]FAO_2019_animal_trends!$G$38</f>
         <v>1.0372340425531916</v>
       </c>
       <c r="H5">
@@ -2969,7 +2957,7 @@
         <v>4.3210694573642391E-2</v>
       </c>
       <c r="D6">
-        <f>[1]FAO_2019_animal_trends!$F$37</f>
+        <f>[38]FAO_2019_animal_trends!$F$37</f>
         <v>2.4937655860349127E-3</v>
       </c>
       <c r="E6">
@@ -2981,7 +2969,7 @@
         <v>-7.7485333020033496E-3</v>
       </c>
       <c r="G6">
-        <f>[1]FAO_2019_animal_trends!$G$37</f>
+        <f>[38]FAO_2019_animal_trends!$G$37</f>
         <v>86.466565349544069</v>
       </c>
       <c r="H6">
@@ -3059,15 +3047,15 @@
         <v>76</v>
       </c>
       <c r="B2" s="8">
-        <f>[2]Arid_Subsistence!$C$2/1000000*$H$18</f>
+        <f>[39]Arid_Subsistence!$C$2/1000000*$H$18</f>
         <v>0.26935849565485659</v>
       </c>
       <c r="C2" s="8">
-        <f>[3]SArid_Subsistence!$C$2/1000000*$H$18</f>
+        <f>[40]SArid_Subsistence!$C$2/1000000*$H$18</f>
         <v>0.57058834189660623</v>
       </c>
       <c r="D2" s="8">
-        <f>[4]Humid_Subsistence!$D$2/1000000*$H$18</f>
+        <f>[41]Humid_Subsistence!$D$2/1000000*$H$18</f>
         <v>0.71943074584927413</v>
       </c>
       <c r="E2" s="9">
@@ -3092,15 +3080,15 @@
         <v>77</v>
       </c>
       <c r="B3" s="8">
-        <f>[5]Arid_Commercial!$C$2/1000000*$H$18</f>
+        <f>[42]Arid_Commercial!$C$2/1000000*$H$18</f>
         <v>5.5884478914862177</v>
       </c>
       <c r="C3" s="8">
-        <f>[6]SArid_Commercial!$C$2/1000000*$H$18</f>
+        <f>[43]SArid_Commercial!$C$2/1000000*$H$18</f>
         <v>7.2365694102551341</v>
       </c>
       <c r="D3" s="8">
-        <f>[7]Humid_Commercial!$D$2/1000000*$H$18</f>
+        <f>[44]Humid_Commercial!$D$2/1000000*$H$18</f>
         <v>6.0610912034605047</v>
       </c>
       <c r="E3" s="9">
@@ -3122,15 +3110,15 @@
         <v>60</v>
       </c>
       <c r="B4" s="8">
-        <f>[8]Dairy_total_Arid_2020!$C$2/1000000*$H$18</f>
+        <f>[45]Dairy_total_Arid_2020!$C$2/1000000*$H$18</f>
         <v>3.0271361942572905E-2</v>
       </c>
       <c r="C4" s="8">
-        <f>[9]Dairy_total_SArid_2020!$C$2/1000000*$H$18</f>
+        <f>[46]Dairy_total_SArid_2020!$C$2/1000000*$H$18</f>
         <v>1.4765740788097195</v>
       </c>
       <c r="D4" s="8">
-        <f>[10]Dairy_total_Humid_2020!$D$2/1000000*$H$18</f>
+        <f>[47]Dairy_total_Humid_2020!$D$2/1000000*$H$18</f>
         <v>6.3853780054327789</v>
       </c>
       <c r="E4" s="9"/>
@@ -3140,15 +3128,15 @@
         <v>80</v>
       </c>
       <c r="B5" s="8">
-        <f>9.78*0.76*[11]Sheep_total_Arid_2020!$C$2/1000000*$H$18</f>
+        <f>9.78*0.76*[48]Sheep_total_Arid_2020!$C$2/1000000*$H$18</f>
         <v>11.794047385286973</v>
       </c>
       <c r="C5" s="8">
-        <f>9.78*0.76*[12]Sheep_total_SArid_2020!$C$2/1000000*$H$18</f>
+        <f>9.78*0.76*[49]Sheep_total_SArid_2020!$C$2/1000000*$H$18</f>
         <v>9.6481198260451801</v>
       </c>
       <c r="D5" s="8">
-        <f>9.78*0.76*[13]Sheep_total_Humid_2020!$D$2/1000000*$H$18</f>
+        <f>9.78*0.76*[50]Sheep_total_Humid_2020!$D$2/1000000*$H$18</f>
         <v>9.0810136627013929</v>
       </c>
       <c r="E5" s="9">
@@ -3928,7 +3916,7 @@
         <v>8.5595346951947899</v>
       </c>
       <c r="C2">
-        <f>[1]FAO_2019_animal_trends!$G$35/100</f>
+        <f>[38]FAO_2019_animal_trends!$G$35/100</f>
         <v>3.8312009613345605E-3</v>
       </c>
       <c r="D2">
@@ -3949,7 +3937,7 @@
         <v>5.5401815014894495</v>
       </c>
       <c r="C3">
-        <f>[1]FAO_2019_animal_trends!$G36/100</f>
+        <f>[38]FAO_2019_animal_trends!$G36/100</f>
         <v>2.7950424483806725E-2</v>
       </c>
       <c r="D3">
@@ -3970,7 +3958,7 @@
         <v>0.95304019787340877</v>
       </c>
       <c r="C4">
-        <f>[1]FAO_2019_animal_trends!$G39/100</f>
+        <f>[38]FAO_2019_animal_trends!$G39/100</f>
         <v>7.6101823708206687E-2</v>
       </c>
       <c r="D4">
@@ -3991,7 +3979,7 @@
         <v>0.84668818128995227</v>
       </c>
       <c r="C5">
-        <f>[1]FAO_2019_animal_trends!$G38/100</f>
+        <f>[38]FAO_2019_animal_trends!$G38/100</f>
         <v>1.0372340425531916E-2</v>
       </c>
       <c r="D5">
@@ -4012,7 +4000,7 @@
         <v>0.71805363998227201</v>
       </c>
       <c r="C6">
-        <f>[1]FAO_2019_animal_trends!$G37/100</f>
+        <f>[38]FAO_2019_animal_trends!$G37/100</f>
         <v>0.86466565349544067</v>
       </c>
       <c r="D6">
@@ -4033,7 +4021,7 @@
         <v>7.8922234461850715</v>
       </c>
       <c r="C7">
-        <f>[1]FAO_2019_animal_trends!$G39/100</f>
+        <f>[38]FAO_2019_animal_trends!$G39/100</f>
         <v>7.6101823708206687E-2</v>
       </c>
       <c r="D7">
@@ -4100,11 +4088,11 @@
         <v>13</v>
       </c>
       <c r="B3">
-        <f>[14]Pastoral_Zebu_2020!$K$2</f>
+        <f>[51]Pastoral_Zebu_2020!$K$2</f>
         <v>7912803.5780913802</v>
       </c>
       <c r="C3">
-        <f>[15]Pastoral_Boran_2020!$K$2</f>
+        <f>[52]Pastoral_Boran_2020!$K$2</f>
         <v>1124203.7226895699</v>
       </c>
       <c r="D3">
@@ -4116,11 +4104,11 @@
         <v>8.5595346951947899</v>
       </c>
       <c r="G3">
-        <f>[16]Pastoral_Zebu_2050!$K$2</f>
+        <f>[53]Pastoral_Zebu_2050!$K$2</f>
         <v>8554757.4814370908</v>
       </c>
       <c r="H3">
-        <f>[17]Pastoral_Boran_2050!$K$2</f>
+        <f>[54]Pastoral_Boran_2050!$K$2</f>
         <v>1215408.67359516</v>
       </c>
       <c r="I3">
@@ -4145,11 +4133,11 @@
         <v>16</v>
       </c>
       <c r="B4">
-        <f>[18]Agpastoral_Zebu_2020!$K$2</f>
+        <f>[55]Agpastoral_Zebu_2020!$K$2</f>
         <v>3685141.0110471202</v>
       </c>
       <c r="C4">
-        <f>[19]Agpastoral_Boran_2020!$K$2</f>
+        <f>[56]Agpastoral_Boran_2020!$K$2</f>
         <v>277376.20390618598</v>
       </c>
       <c r="D4">
@@ -4161,11 +4149,11 @@
         <v>5.5401815014894495</v>
       </c>
       <c r="G4">
-        <f>[20]Agpastoral_Zebu_2050!$K$2</f>
+        <f>[57]Agpastoral_Zebu_2050!$K$2</f>
         <v>6488770.1197828101</v>
       </c>
       <c r="H4">
-        <f>[21]Agpastoral_Boran_2050!$K$2</f>
+        <f>[58]Agpastoral_Boran_2050!$K$2</f>
         <v>488402.05019366002</v>
       </c>
       <c r="I4">
@@ -4190,11 +4178,11 @@
         <v>11</v>
       </c>
       <c r="B5">
-        <f>[22]Mixed_Zebu_2020!$K$2</f>
+        <f>[59]Mixed_Zebu_2020!$K$2</f>
         <v>298374.71550379699</v>
       </c>
       <c r="C5">
-        <f>[23]Mixed_Boran_2020!$K$2</f>
+        <f>[60]Mixed_Boran_2020!$K$2</f>
         <v>25945.627401560501</v>
       </c>
       <c r="D5">
@@ -4206,11 +4194,11 @@
         <v>0.95304019787340877</v>
       </c>
       <c r="G5">
-        <f>[24]Mixed_Zebu_2050!$K$2</f>
+        <f>[61]Mixed_Zebu_2050!$K$2</f>
         <v>404262.59496554697</v>
       </c>
       <c r="H5">
-        <f>[25]Mixed_Boran_2050!$K$2</f>
+        <f>[62]Mixed_Boran_2050!$K$2</f>
         <v>35153.269665965803</v>
       </c>
       <c r="I5">
@@ -4235,11 +4223,11 @@
         <v>42</v>
       </c>
       <c r="B6">
-        <f>[26]Cowcalf_Boran_2020!$K$2</f>
+        <f>[63]Cowcalf_Boran_2020!$K$2</f>
         <v>1184753.34766715</v>
       </c>
       <c r="C6">
-        <f>[27]Cowcalf_Exotic_2020!$K$2</f>
+        <f>[64]Cowcalf_Exotic_2020!$K$2</f>
         <v>985977.36353097099</v>
       </c>
       <c r="D6">
@@ -4251,11 +4239,11 @@
         <v>0.84668818128995227</v>
       </c>
       <c r="G6">
-        <f>[28]Cowcalf_Boran_2050!$K$2</f>
+        <f>[65]Cowcalf_Boran_2050!$K$2</f>
         <v>1806208.69891036</v>
       </c>
       <c r="H6">
-        <f>[29]Cowcalf_Exotic_2050!$K$2</f>
+        <f>[66]Cowcalf_Exotic_2050!$K$2</f>
         <v>1503165.94333724</v>
       </c>
       <c r="I6">
@@ -4280,11 +4268,11 @@
         <v>23</v>
       </c>
       <c r="B7">
-        <f>[30]Finisher_Boran_2020!$K$2</f>
+        <f>[67]Finisher_Boran_2020!$K$2</f>
         <v>26321.876059999999</v>
       </c>
       <c r="C7">
-        <f>[31]Finisher_Exotic_2020!$K$2</f>
+        <f>[68]Finisher_Exotic_2020!$K$2</f>
         <v>12386.7653238613</v>
       </c>
       <c r="D7">
@@ -4296,11 +4284,11 @@
         <v>0.71805363998227201</v>
       </c>
       <c r="G7">
-        <f>[32]Finisher_Boran_2050!$K$2</f>
+        <f>[69]Finisher_Boran_2050!$K$2</f>
         <v>918345.45531155204</v>
       </c>
       <c r="H7">
-        <f>[33]Finisher_Exotic_2050!$K$2</f>
+        <f>[70]Finisher_Exotic_2050!$K$2</f>
         <v>432162.57168335503</v>
       </c>
       <c r="I7">
@@ -4397,15 +4385,15 @@
         <v>86</v>
       </c>
       <c r="C2" s="12">
-        <f>[34]ZS_Grassland_Arid!$D$2*L15</f>
+        <f>[1]ZS_Grassland_Arid!$D$2*L15</f>
         <v>7105918.9949999992</v>
       </c>
       <c r="D2" s="12">
-        <f>[35]ZS_Grassland_SArid!$D$2*L15</f>
+        <f>[2]ZS_Grassland_SArid!$D$2*L15</f>
         <v>4556839.63</v>
       </c>
       <c r="E2" s="12">
-        <f>[36]ZS_Grassland_Humid!$E$2*L15</f>
+        <f>[3]ZS_Grassland_Humid!$E$2*L15</f>
         <v>2262153.4458035277</v>
       </c>
     </row>
@@ -4414,15 +4402,15 @@
         <v>87</v>
       </c>
       <c r="C3" s="12">
-        <f>[37]ZS_Cropland_Arid!$D$2*L15</f>
+        <f>[4]ZS_Cropland_Arid!$D$2*L15</f>
         <v>18395.019999999997</v>
       </c>
       <c r="D3" s="12">
-        <f>[38]ZS_Cropland_SArid!$D$2*L15</f>
+        <f>[5]ZS_Cropland_SArid!$D$2*L15</f>
         <v>686372.96</v>
       </c>
       <c r="E3" s="12">
-        <f>[39]ZS_Cropland_Humid!$E$2*L15</f>
+        <f>[6]ZS_Cropland_Humid!$E$2*L15</f>
         <v>950603.98551942373</v>
       </c>
     </row>
@@ -4431,15 +4419,15 @@
         <v>88</v>
       </c>
       <c r="C4" s="12">
-        <f>[40]ZS_Shrubland_Arid!$D$2*L15</f>
+        <f>[7]ZS_Shrubland_Arid!$D$2*L15</f>
         <v>9755293.3449999988</v>
       </c>
       <c r="D4" s="12">
-        <f>[41]ZS_Shrubland_SArid!$D$2*L15</f>
+        <f>[8]ZS_Shrubland_SArid!$D$2*L15</f>
         <v>12549721.555</v>
       </c>
       <c r="E4" s="12">
-        <f>[42]ZS_Shrubland_Humid!$E$2*L15</f>
+        <f>[9]ZS_Shrubland_Humid!$E$2*L15</f>
         <v>2223118.4370185882</v>
       </c>
     </row>
@@ -4461,15 +4449,15 @@
         <v>69</v>
       </c>
       <c r="C7" s="15">
-        <f>[43]NPP_2020_GRASS_Arid!$E$2</f>
+        <f>[10]NPP_2020_GRASS_Arid!$E$2</f>
         <v>0.33293323112310402</v>
       </c>
       <c r="D7" s="15">
-        <f>[44]NPP_2020_GRASS_SArid!$E$2</f>
+        <f>[11]NPP_2020_GRASS_SArid!$E$2</f>
         <v>0.48080803465972</v>
       </c>
       <c r="E7" s="14">
-        <f>[45]filtered!$F$2</f>
+        <f>[12]filtered!$F$2</f>
         <v>0.88607168377191448</v>
       </c>
     </row>
@@ -4478,15 +4466,15 @@
         <v>70</v>
       </c>
       <c r="C8" s="30">
-        <f>[46]NPP_2020_CROP_Arid!$E$2</f>
+        <f>[13]NPP_2020_CROP_Arid!$E$2</f>
         <v>0.97599038751874501</v>
       </c>
       <c r="D8" s="30">
-        <f>[47]NPP_2020_CROP_SArid!$E$2</f>
+        <f>[14]NPP_2020_CROP_SArid!$E$2</f>
         <v>0.71416468993051396</v>
       </c>
       <c r="E8" s="14">
-        <f>[48]filtered!$F$2</f>
+        <f>[15]filtered!$F$2</f>
         <v>1.0193612610195171</v>
       </c>
     </row>
@@ -4495,15 +4483,15 @@
         <v>71</v>
       </c>
       <c r="C9" s="15">
-        <f>[49]NPP_2020_SHRUB_Arid!$E$2</f>
+        <f>[16]NPP_2020_SHRUB_Arid!$E$2</f>
         <v>0.20100553202445001</v>
       </c>
       <c r="D9" s="15">
-        <f>[50]NPP_2020_SHRUB_SArid!$E$2</f>
+        <f>[17]NPP_2020_SHRUB_SArid!$E$2</f>
         <v>0.48842843619779902</v>
       </c>
       <c r="E9" s="14">
-        <f>[51]filtered!$F$2</f>
+        <f>[18]filtered!$F$2</f>
         <v>0.9284507277249876</v>
       </c>
       <c r="L9" s="11"/>
@@ -4522,15 +4510,15 @@
         <v>69</v>
       </c>
       <c r="C11" s="15">
-        <f>[52]NPP_2050_R4_GRASS_Arid!$E$2</f>
+        <f>[19]NPP_2050_R4_GRASS_Arid!$E$2</f>
         <v>0.36084903504638699</v>
       </c>
       <c r="D11" s="15">
-        <f>[53]NPP_2050_R4_GRASS_SArid!$E$2</f>
+        <f>[20]NPP_2050_R4_GRASS_SArid!$E$2</f>
         <v>0.51075241024303597</v>
       </c>
       <c r="E11" s="15">
-        <f>[54]filtered!$F$2</f>
+        <f>[21]filtered!$F$2</f>
         <v>0.90483097904137921</v>
       </c>
       <c r="F11">
@@ -4551,15 +4539,15 @@
         <v>70</v>
       </c>
       <c r="C12" s="15">
-        <f>[55]NPP_2050_R4_CROP_Arid!$E$2</f>
+        <f>[22]NPP_2050_R4_CROP_Arid!$E$2</f>
         <v>1.0384816436740301</v>
       </c>
       <c r="D12" s="15">
-        <f>[56]NPP_2050_R4_CROP_SArid!$E$2</f>
+        <f>[23]NPP_2050_R4_CROP_SArid!$E$2</f>
         <v>0.72447113600000002</v>
       </c>
       <c r="E12" s="15">
-        <f>[57]filtered!$F$2</f>
+        <f>[24]filtered!$F$2</f>
         <v>0.98649141647533578</v>
       </c>
       <c r="F12">
@@ -4580,15 +4568,15 @@
         <v>71</v>
       </c>
       <c r="C13" s="15">
-        <f>[58]NPP_2050_R4_SHRUB_Arid!$E$2</f>
+        <f>[25]NPP_2050_R4_SHRUB_Arid!$E$2</f>
         <v>0.21776707800273001</v>
       </c>
       <c r="D13" s="15">
-        <f>[59]NPP_2050_R4_SHRUB_SArid!$E$2</f>
+        <f>[26]NPP_2050_R4_SHRUB_SArid!$E$2</f>
         <v>0.51075241024303597</v>
       </c>
       <c r="E13" s="15">
-        <f>[60]filtered!$F$2</f>
+        <f>[27]filtered!$F$2</f>
         <v>0.90483097904137921</v>
       </c>
       <c r="F13">
@@ -4617,15 +4605,15 @@
         <v>69</v>
       </c>
       <c r="C15" s="15">
-        <f>[61]NPP_2050_R8_GRASS_Arid!$E$2</f>
+        <f>[28]NPP_2050_R8_GRASS_Arid!$E$2</f>
         <v>0.38422689204237098</v>
       </c>
       <c r="D15" s="15">
-        <f>[62]NPP_2050_R8_GRASS_SArid!$E$2</f>
+        <f>[29]NPP_2050_R8_GRASS_SArid!$E$2</f>
         <v>0.51337712420869996</v>
       </c>
       <c r="E15" s="15">
-        <f>[63]filtered!$F$2</f>
+        <f>[30]filtered!$F$2</f>
         <v>0.88457459938562355</v>
       </c>
       <c r="F15">
@@ -4653,15 +4641,15 @@
         <v>70</v>
       </c>
       <c r="C16" s="15">
-        <f>[64]NPP_2050_R8_CROP_Arid!$E$2</f>
+        <f>[31]NPP_2050_R8_CROP_Arid!$E$2</f>
         <v>1.10532849796393</v>
       </c>
       <c r="D16" s="15">
-        <f>[65]NPP_2050_R8_CROP_SArid!$E$2</f>
+        <f>[32]NPP_2050_R8_CROP_SArid!$E$2</f>
         <v>0.80695680840268103</v>
       </c>
       <c r="E16" s="15">
-        <f>[66]filtered!$F$2</f>
+        <f>[33]filtered!$F$2</f>
         <v>1.0242825546815273</v>
       </c>
       <c r="F16">
@@ -4689,15 +4677,15 @@
         <v>71</v>
       </c>
       <c r="C17" s="15">
-        <f>[67]NPP_2050_R8_SHRUB_Arid!$E$2</f>
+        <f>[34]NPP_2050_R8_SHRUB_Arid!$E$2</f>
         <v>0.231319877140652</v>
       </c>
       <c r="D17" s="15">
-        <f>[68]NPP_2050_R8_SHRUB_SArid!$E$2</f>
+        <f>[35]NPP_2050_R8_SHRUB_SArid!$E$2</f>
         <v>0.51046846997934603</v>
       </c>
       <c r="E17" s="15">
-        <f>[69]filtered!$F$2</f>
+        <f>[36]filtered!$F$2</f>
         <v>0.93416975929597834</v>
       </c>
       <c r="F17">
@@ -4721,16 +4709,16 @@
         <v>72</v>
       </c>
       <c r="C20" s="14">
-        <f>10000*(1/1000)*(C2*C7+C3*C8*[70]Raster_logic!$I$84+C4*C9*[70]Raster_logic!$I$85)*(1/[70]Raster_logic!$I$79)*[70]Raster_logic!$I$80*[70]Raster_logic!$I$81/1000000</f>
-        <v>9.7980294351302764</v>
+        <f>10000*(1/1000)*(C2*C7+C3*C8*[37]Raster_logic!$I$95+C4*C9*[37]Raster_logic!$I$96)*(1/[37]Raster_logic!$I$89)*[37]Raster_logic!$I$90*[37]Raster_logic!$I$91/1000000</f>
+        <v>10.13786820973019</v>
       </c>
       <c r="D20" s="14">
-        <f>10000*(1/1000)*(D2*D7+D3*D8*[70]Raster_logic!$I$84+D4*D9*[70]Raster_logic!$I$85)*(1/[70]Raster_logic!$I$79)*[70]Raster_logic!$I$80*[70]Raster_logic!$I$81/1000000</f>
-        <v>15.305906991283107</v>
+        <f>10000*(1/1000)*(D2*D7+D3*D8*[37]Raster_logic!$I$95+D4*D9*[37]Raster_logic!$I$96)*(1/[37]Raster_logic!$I$89)*[37]Raster_logic!$I$90*[37]Raster_logic!$I$91/1000000</f>
+        <v>15.448061930984727</v>
       </c>
       <c r="E20" s="14">
-        <f>10000*(1/1000)*(E2*E7+E3*E8*[70]Raster_logic!$I$84+E4*E9*[70]Raster_logic!$I$85)*(1/[70]Raster_logic!$I$79)*[70]Raster_logic!$I$80*[70]Raster_logic!$I$82/1000000</f>
-        <v>12.936767382915914</v>
+        <f>10000*(1/1000)*(E2*E7+E3*E8*[37]Raster_logic!$I$95+E4*E9*[37]Raster_logic!$I$96)*(1/[37]Raster_logic!$I$89)*[37]Raster_logic!$I$90*[37]Raster_logic!$I$91/1000000</f>
+        <v>10.148363796471815</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -4738,16 +4726,16 @@
         <v>73</v>
       </c>
       <c r="C21" s="14">
-        <f>10000*(1/1000)*(C3*C8*[70]Raster_logic!$I$92)*[70]Raster_logic!$I$87*(1/[70]Raster_logic!$I$88)*[70]Raster_logic!$I$89*[70]Raster_logic!$I$90/1000000</f>
-        <v>5.3411254027189804E-2</v>
+        <f>10000*(1/1000)*(C3*C8*[37]Raster_logic!$I$102)*(1/[37]Raster_logic!$I$98)*[37]Raster_logic!$I$99*[37]Raster_logic!$I$100/1000000</f>
+        <v>8.7971477221253785E-2</v>
       </c>
       <c r="D21" s="14">
-        <f>10000*(1/1000)*(D3*D8*[70]Raster_logic!$I$92)*(1/[70]Raster_logic!$I$88)*[70]Raster_logic!$I$89*[70]Raster_logic!$I$90*[70]Raster_logic!$I$87/1000000</f>
-        <v>1.4582954131613894</v>
+        <f>10000*(1/1000)*(D3*D8*[37]Raster_logic!$I$102)*(1/[37]Raster_logic!$I$98)*[37]Raster_logic!$I$99*[37]Raster_logic!$I$100/1000000</f>
+        <v>2.4018983275599357</v>
       </c>
       <c r="E21" s="14">
-        <f>10000*(1/1000)*(E3*E8*[70]Raster_logic!$I$92)*(1/[70]Raster_logic!$I$88)*[70]Raster_logic!$I$89*[70]Raster_logic!$I$90*[70]Raster_logic!$I$87/1000000</f>
-        <v>2.8828014102925446</v>
+        <f>10000*(1/1000)*(E3*E8*[37]Raster_logic!$I$102)*(1/[37]Raster_logic!$I$98)*[37]Raster_logic!$I$99*[37]Raster_logic!$I$100/1000000</f>
+        <v>4.7481434993053666</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -4756,15 +4744,15 @@
       </c>
       <c r="C22" s="14">
         <f>SUM(C20:C21)</f>
-        <v>9.8514406891574655</v>
+        <v>10.225839686951444</v>
       </c>
       <c r="D22" s="14">
         <f>SUM(D20:D21)</f>
-        <v>16.764202404444497</v>
+        <v>17.849960258544662</v>
       </c>
       <c r="E22" s="14">
         <f>SUM(E20:E21)</f>
-        <v>15.819568793208457</v>
+        <v>14.89650729577718</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -4781,28 +4769,28 @@
         <v>BIOM GRASS Supply (MT/ha/yr)</v>
       </c>
       <c r="C24" s="14">
-        <f>10000*(1/1000)*(C2*C11+C3*C12*[70]Raster_logic!$I$84+C4*C13*[70]Raster_logic!$I$85)*(1/[70]Raster_logic!$I$79)*[70]Raster_logic!$I$80*[70]Raster_logic!$I$81/1000000</f>
-        <v>10.617448088860092</v>
+        <f>10000*(1/1000)*(C2*C11+C3*C12*[37]Raster_logic!$I$95+C4*C13*[37]Raster_logic!$I$96)*(1/[37]Raster_logic!$I$89)*[37]Raster_logic!$I$90*[37]Raster_logic!$I$91/1000000</f>
+        <v>10.986362335397628</v>
       </c>
       <c r="D24" s="14">
-        <f>10000*(1/1000)*(D2*D11+D3*D12*[70]Raster_logic!$I$84+D4*D13*[70]Raster_logic!$I$85)*(1/[70]Raster_logic!$I$79)*[70]Raster_logic!$I$80*[70]Raster_logic!$I$81/1000000</f>
-        <v>16.072868566682505</v>
+        <f>10000*(1/1000)*(D2*D11+D3*D12*[37]Raster_logic!$I$95+D4*D13*[37]Raster_logic!$I$96)*(1/[37]Raster_logic!$I$89)*[37]Raster_logic!$I$90*[37]Raster_logic!$I$91/1000000</f>
+        <v>16.25401942195187</v>
       </c>
       <c r="E24" s="14">
-        <f>10000*(1/1000)*(E2*E11+E3*E12*[70]Raster_logic!$I$84+E4*E13*[70]Raster_logic!$I$85)*(1/[70]Raster_logic!$I$79)*[70]Raster_logic!$I$80*[70]Raster_logic!$I$82/1000000</f>
-        <v>12.913313515991085</v>
+        <f>10000*(1/1000)*(E2*E11+E3*E12*[37]Raster_logic!$I$95+E4*E13*[37]Raster_logic!$I$96)*(1/[37]Raster_logic!$I$89)*[37]Raster_logic!$I$90*[37]Raster_logic!$I$91/1000000</f>
+        <v>10.183081967683787</v>
       </c>
       <c r="F24" s="13">
         <f>C24/C20</f>
-        <v>1.0836309646909037</v>
+        <v>1.0836955174513971</v>
       </c>
       <c r="G24" s="13">
         <f t="shared" ref="G24:H26" si="4">D24/D20</f>
-        <v>1.0501088616203007</v>
+        <v>1.0521720779323525</v>
       </c>
       <c r="H24" s="13">
         <f t="shared" si="4"/>
-        <v>0.99818703805745157</v>
+        <v>1.0034210609619694</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -4811,16 +4799,16 @@
         <v>BIOM CROP Supply (MT/ha/yr)</v>
       </c>
       <c r="C25" s="14">
-        <f>10000*(1/1000)*(C3*C12*[70]Raster_logic!$I$92)*[70]Raster_logic!$I$87*(1/[70]Raster_logic!$I$88)*[70]Raster_logic!$I$89*[70]Raster_logic!$I$90/1000000</f>
-        <v>5.6831099549924539E-2</v>
+        <f>10000*(1/1000)*(C3*C12*[37]Raster_logic!$I$102)*(1/[37]Raster_logic!$I$98)*[37]Raster_logic!$I$99*[37]Raster_logic!$I$100/1000000</f>
+        <v>9.3604163964581585E-2</v>
       </c>
       <c r="D25" s="14">
-        <f>10000*(1/1000)*(D3*D12*[70]Raster_logic!$I$92)*[70]Raster_logic!$I$87*(1/[70]Raster_logic!$I$88)*[70]Raster_logic!$I$89*[70]Raster_logic!$I$90/1000000</f>
-        <v>1.4793407592013756</v>
+        <f>10000*(1/1000)*(D3*D12*[37]Raster_logic!$I$102)*(1/[37]Raster_logic!$I$98)*[37]Raster_logic!$I$99*[37]Raster_logic!$I$100/1000000</f>
+        <v>2.436561250449325</v>
       </c>
       <c r="E25" s="14">
-        <f>10000*(1/1000)*(E3*E12*[70]Raster_logic!$I$92)*[70]Raster_logic!$I$87*(1/[70]Raster_logic!$I$88)*[70]Raster_logic!$I$89*[70]Raster_logic!$I$90/1000000</f>
-        <v>2.7898439497419139</v>
+        <f>10000*(1/1000)*(E3*E12*[37]Raster_logic!$I$102)*(1/[37]Raster_logic!$I$98)*[37]Raster_logic!$I$99*[37]Raster_logic!$I$100/1000000</f>
+        <v>4.5950370936925635</v>
       </c>
       <c r="F25" s="13">
         <f t="shared" ref="F25:F26" si="6">C25/C21</f>
@@ -4828,7 +4816,7 @@
       </c>
       <c r="G25" s="13">
         <f t="shared" si="4"/>
-        <v>1.0144314696803185</v>
+        <v>1.0144314696803187</v>
       </c>
       <c r="H25" s="13">
         <f t="shared" si="4"/>
@@ -4842,27 +4830,27 @@
       </c>
       <c r="C26" s="14">
         <f>SUM(C24:C25)</f>
-        <v>10.674279188410017</v>
+        <v>11.079966499362209</v>
       </c>
       <c r="D26" s="14">
         <f t="shared" ref="D26:E26" si="7">SUM(D24:D25)</f>
-        <v>17.552209325883879</v>
+        <v>18.690580672401197</v>
       </c>
       <c r="E26" s="14">
         <f t="shared" si="7"/>
-        <v>15.703157465733</v>
+        <v>14.778119061376351</v>
       </c>
       <c r="F26" s="13">
         <f t="shared" si="6"/>
-        <v>1.083524686917942</v>
+        <v>1.0835263253247225</v>
       </c>
       <c r="G26" s="13">
         <f t="shared" si="4"/>
-        <v>1.0470053332946199</v>
+        <v>1.0470936854581587</v>
       </c>
       <c r="H26" s="13">
         <f t="shared" si="4"/>
-        <v>0.99264130843279152</v>
+        <v>0.99205261796942235</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -4879,28 +4867,28 @@
         <v>BIOM GRASS Supply (MT/ha/yr)</v>
       </c>
       <c r="C28" s="14">
-        <f>10000*(1/1000)*(C2*C15+C3*C16*[70]Raster_logic!$I$84+C4*C17*[70]Raster_logic!$I$85)*(1/[70]Raster_logic!$I$79)*[70]Raster_logic!$I$80*[70]Raster_logic!$I$81/1000000</f>
-        <v>11.299364450977983</v>
+        <f>10000*(1/1000)*(C2*C15+C3*C16*[37]Raster_logic!$I$95+C4*C17*[37]Raster_logic!$I$96)*(1/[37]Raster_logic!$I$89)*[37]Raster_logic!$I$90*[37]Raster_logic!$I91/1000000</f>
+        <v>11.691151745837523</v>
       </c>
       <c r="D28" s="14">
-        <f>10000*(1/1000)*(D2*D15+D3*D16*[70]Raster_logic!$I$84+D4*D17*[70]Raster_logic!$I$85)*(1/[70]Raster_logic!$I$79)*[70]Raster_logic!$I$80*[70]Raster_logic!$I$81/1000000</f>
-        <v>16.289244270609824</v>
+        <f>10000*(1/1000)*(D2*D15+D3*D16*[37]Raster_logic!$I$95+D4*D17*[37]Raster_logic!$I$96)*(1/[37]Raster_logic!$I$89)*[37]Raster_logic!$I$90*[37]Raster_logic!$I91/1000000</f>
+        <v>16.349687139782979</v>
       </c>
       <c r="E28" s="14">
-        <f>10000*(1/1000)*(E2*E15+E3*E16*[70]Raster_logic!$I$84+E4*E17*[70]Raster_logic!$I$85)*(1/[70]Raster_logic!$I$79)*[70]Raster_logic!$I$80*[70]Raster_logic!$I$82/1000000</f>
-        <v>12.956529914294267</v>
+        <f>10000*(1/1000)*(E2*E15+E3*E16*[37]Raster_logic!$I$95+E4*E17*[37]Raster_logic!$I$96)*(1/[37]Raster_logic!$I$89)*[37]Raster_logic!$I$90*[37]Raster_logic!$I91/1000000</f>
+        <v>10.158929952078466</v>
       </c>
       <c r="F28" s="13">
         <f>C28/C20</f>
-        <v>1.1532282614364022</v>
+        <v>1.1532159921566658</v>
       </c>
       <c r="G28" s="13">
         <f t="shared" ref="G28:H28" si="8">D28/D20</f>
-        <v>1.0642456066070922</v>
+        <v>1.0583649400699147</v>
       </c>
       <c r="H28" s="13">
         <f t="shared" si="8"/>
-        <v>1.0015276251627165</v>
+        <v>1.0010411683911375</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -4909,28 +4897,28 @@
         <v>BIOM CROP Supply (MT/ha/yr)</v>
       </c>
       <c r="C29" s="14">
-        <f>10000*(1/1000)*(C3*C16*[70]Raster_logic!$I$92)*[70]Raster_logic!$I$87*(1/[70]Raster_logic!$I$88)*[70]Raster_logic!$I$89*[70]Raster_logic!$I$90/1000000</f>
-        <v>6.0489305984183922E-2</v>
+        <f>10000*(1/1000)*(C3*C16*[37]Raster_logic!$I$102)*(1/[37]Raster_logic!$I$98)*[37]Raster_logic!$I$99*[37]Raster_logic!$I$100/1000000</f>
+        <v>9.9629445150420576E-2</v>
       </c>
       <c r="D29" s="14">
-        <f>10000*(1/1000)*(D3*D16*[70]Raster_logic!$I$92)*[70]Raster_logic!$I$87*(1/[70]Raster_logic!$I$88)*[70]Raster_logic!$I$89*[70]Raster_logic!$I$90/1000000</f>
-        <v>1.6477731661971156</v>
+        <f>10000*(1/1000)*(D3*D16*[37]Raster_logic!$I$102)*(1/[37]Raster_logic!$I$98)*[37]Raster_logic!$I$99*[37]Raster_logic!$I$100/1000000</f>
+        <v>2.7139793325599548</v>
       </c>
       <c r="E29" s="14">
-        <f>10000*(1/1000)*(E3*E16*[70]Raster_logic!$I$92)*[70]Raster_logic!$I$87*(1/[70]Raster_logic!$I$88)*[70]Raster_logic!$I$89*[70]Raster_logic!$I$90/1000000</f>
-        <v>2.8967190593653735</v>
+        <f>10000*(1/1000)*(E3*E16*[37]Raster_logic!$I$102)*(1/[37]Raster_logic!$I$98)*[37]Raster_logic!$I$99*[37]Raster_logic!$I$100/1000000</f>
+        <v>4.7710666860135564</v>
       </c>
       <c r="F29" s="13">
         <f t="shared" ref="F29:F30" si="10">C29/C21</f>
-        <v>1.1325198609527296</v>
+        <v>1.1325198609527298</v>
       </c>
       <c r="G29" s="13">
         <f t="shared" ref="G29:G30" si="11">D29/D21</f>
-        <v>1.1299309805994409</v>
+        <v>1.1299309805994406</v>
       </c>
       <c r="H29" s="13">
         <f t="shared" ref="H29:H30" si="12">E29/E21</f>
-        <v>1.0048278209602433</v>
+        <v>1.0048278209602435</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -4940,27 +4928,27 @@
       </c>
       <c r="C30" s="14">
         <f>SUM(C28:C29)</f>
-        <v>11.359853756962167</v>
+        <v>11.790781190987943</v>
       </c>
       <c r="D30" s="14">
         <f>SUM(D28:D29)</f>
-        <v>17.93701743680694</v>
+        <v>19.063666472342934</v>
       </c>
       <c r="E30" s="14">
         <f t="shared" ref="E30" si="13">SUM(E28:E29)</f>
-        <v>15.853248973659641</v>
+        <v>14.929996638092023</v>
       </c>
       <c r="F30" s="13">
         <f t="shared" si="10"/>
-        <v>1.1531159873362347</v>
+        <v>1.1530379462171134</v>
       </c>
       <c r="G30" s="13">
         <f t="shared" si="11"/>
-        <v>1.0699594889197657</v>
+        <v>1.0679948972557112</v>
       </c>
       <c r="H30" s="13">
         <f t="shared" si="12"/>
-        <v>1.002129020132688</v>
+        <v>1.0022481338511031</v>
       </c>
     </row>
   </sheetData>
@@ -4971,14 +4959,14 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7E0F49F-D7A7-4FDA-92DD-326744451984}">
-  <dimension ref="A1:I74"/>
+  <dimension ref="A1:I76"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.42578125" customWidth="1"/>
     <col min="2" max="2" width="27.5703125" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" customWidth="1"/>
-    <col min="5" max="5" width="9.28515625" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" customWidth="1"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
+    <col min="5" max="5" width="16.5703125" customWidth="1"/>
     <col min="6" max="7" width="11.28515625" customWidth="1"/>
     <col min="8" max="8" width="35.140625" customWidth="1"/>
   </cols>
@@ -5000,9 +4988,8 @@
       <c r="H1" t="s">
         <v>116</v>
       </c>
-      <c r="I1" s="41">
-        <f>196.141423507315*0.8</f>
-        <v>156.91313880585201</v>
+      <c r="I1" s="40">
+        <v>195.24959913167186</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -5026,9 +5013,8 @@
       <c r="H2" t="s">
         <v>117</v>
       </c>
-      <c r="I2" s="41">
-        <f>194.2683246418</f>
-        <v>194.26832464180001</v>
+      <c r="I2" s="40">
+        <v>193.39196223478999</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -5049,9 +5035,8 @@
       <c r="H3" t="s">
         <v>118</v>
       </c>
-      <c r="I3" s="41">
-        <f>198.014522372829</f>
-        <v>198.01452237282899</v>
+      <c r="I3" s="40">
+        <v>197.10723602855413</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -5095,7 +5080,7 @@
         <v>81</v>
       </c>
       <c r="I5">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -5118,8 +5103,8 @@
         <v>91</v>
       </c>
       <c r="I6">
-        <f>0.035</f>
-        <v>3.5000000000000003E-2</v>
+        <f>0.06</f>
+        <v>0.06</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -5142,8 +5127,8 @@
         <v>92</v>
       </c>
       <c r="I7">
-        <f>0.035</f>
-        <v>3.5000000000000003E-2</v>
+        <f>0.0825</f>
+        <v>8.2500000000000004E-2</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -5166,7 +5151,7 @@
         <v>93</v>
       </c>
       <c r="I8">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -5184,15 +5169,15 @@
       </c>
       <c r="C10">
         <f>SUM(C2:C6)*$I1*1000000</f>
-        <v>716717026.76849842</v>
+        <v>891822783.1803087</v>
       </c>
       <c r="D10">
         <f>SUM(D2:D6)*$I1*1000000</f>
-        <v>1225045628.0425696</v>
+        <v>1524344421.4653516</v>
       </c>
       <c r="E10">
         <f>SUM(E2:E6)*$I1*1000000</f>
-        <v>656802121.52516973</v>
+        <v>817269681.25525963</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -5201,15 +5186,15 @@
       </c>
       <c r="C11">
         <f>SUM(C2:C6)*$I2*1000000</f>
-        <v>887340710.23105156</v>
+        <v>883337834.09522295</v>
       </c>
       <c r="D11">
         <f t="shared" ref="D11:E11" si="0">SUM(D2:D6)*$I2*1000000</f>
-        <v>1516683456.7247598</v>
+        <v>1509841557.1651771</v>
       </c>
       <c r="E11">
         <f t="shared" si="0"/>
-        <v>813162293.10630548</v>
+        <v>809494042.68107331</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -5218,15 +5203,15 @@
       </c>
       <c r="C12">
         <f>SUM(C2:C6)*$I3*1000000</f>
-        <v>904451856.6901896</v>
+        <v>900307732.26539612</v>
       </c>
       <c r="D12">
         <f t="shared" ref="D12:E12" si="1">SUM(D2:D6)*$I3*1000000</f>
-        <v>1545930613.3816559</v>
+        <v>1538847285.7655289</v>
       </c>
       <c r="E12">
         <f t="shared" si="1"/>
-        <v>828843010.70661426</v>
+        <v>825045319.82944775</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -5252,15 +5237,15 @@
       </c>
       <c r="C14">
         <f>C8*$I$5*1000000</f>
-        <v>412791658.48504406</v>
+        <v>330233326.78803521</v>
       </c>
       <c r="D14">
         <f>D8*$I$5*1000000</f>
-        <v>337684193.91158128</v>
+        <v>270147355.12926507</v>
       </c>
       <c r="E14">
         <f>E8*$I$5*1000000</f>
-        <v>317835478.19454873</v>
+        <v>254268382.555639</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -5269,15 +5254,15 @@
       </c>
       <c r="C16" s="25">
         <f>365*(C10+C$13+C$14)*(1-$I$6)*($I$9)/1000/1000000</f>
-        <v>7.999686501718676</v>
+        <v>8.4275011658184127</v>
       </c>
       <c r="D16" s="25">
-        <f t="shared" ref="D16:E16" si="2">365*(D10+D$13+D$14)*(1-$I$6)*($I$9)/1000/1000000</f>
-        <v>13.099397176489203</v>
+        <f>365*(D10+D$13+D$14)*(1-$I$7)*($I$9)/1000/1000000</f>
+        <v>14.006891827992501</v>
       </c>
       <c r="E16" s="25">
-        <f t="shared" si="2"/>
-        <v>15.907175438439069</v>
+        <f>365*(E10+E$13+E$14)*(1-$I$8)*($I$9)/1000/1000000</f>
+        <v>15.128513851608144</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.25">
@@ -5285,16 +5270,16 @@
         <v>124</v>
       </c>
       <c r="C17" s="25">
-        <f>365*(C11+C$13+C$14)*(1-$I$6)*($I$9)/1000/1000000</f>
-        <v>9.2016450398706304</v>
+        <f t="shared" ref="C17:C18" si="2">365*(C11+C$13+C$14)*(1-$I$6)*($I$9)/1000/1000000</f>
+        <v>8.3692774451965537</v>
       </c>
       <c r="D17" s="25">
-        <f t="shared" ref="D17:E17" si="3">365*(D11+D$13+D$14)*(1-$I$6)*($I$9)/1000/1000000</f>
-        <v>15.153839860640895</v>
+        <f>365*(D11+D$13+D$14)*(1-$I$7)*($I$9)/1000/1000000</f>
+        <v>13.909755268626006</v>
       </c>
       <c r="E17" s="25">
-        <f t="shared" si="3"/>
-        <v>17.00865466714238</v>
+        <f>365*(E11+E$13+E$14)*(1-$I$8)*($I$9)/1000/1000000</f>
+        <v>15.078563149407573</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.25">
@@ -5302,16 +5287,16 @@
         <v>123</v>
       </c>
       <c r="C18" s="25">
-        <f>365*(C12+C$13+C$14)*(1-$I$6)*($I$9)/1000/1000000</f>
-        <v>9.3221845111020301</v>
+        <f t="shared" si="2"/>
+        <v>8.4857248864402823</v>
       </c>
       <c r="D18" s="25">
-        <f t="shared" ref="D18:E18" si="4">365*(D12+D$13+D$14)*(1-$I$6)*($I$9)/1000/1000000</f>
-        <v>15.359871455710397</v>
+        <f t="shared" ref="D17:D18" si="3">365*(D12+D$13+D$14)*(1-$I$7)*($I$9)/1000/1000000</f>
+        <v>14.104028387359014</v>
       </c>
       <c r="E18" s="25">
-        <f t="shared" si="4"/>
-        <v>17.119117482277758</v>
+        <f t="shared" ref="E17:E18" si="4">365*(E12+E$13+E$14)*(1-$I$8)*($I$9)/1000/1000000</f>
+        <v>15.178464553808732</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.25">
@@ -5323,15 +5308,15 @@
       </c>
       <c r="C20" s="19">
         <f>NPP!C22</f>
-        <v>9.8514406891574655</v>
+        <v>10.225839686951444</v>
       </c>
       <c r="D20" s="19">
         <f>NPP!D22</f>
-        <v>16.764202404444497</v>
+        <v>17.849960258544662</v>
       </c>
       <c r="E20" s="19">
         <f>NPP!E22</f>
-        <v>15.819568793208457</v>
+        <v>14.89650729577718</v>
       </c>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.25">
@@ -5343,15 +5328,15 @@
       </c>
       <c r="C22" s="6">
         <f>C$20/C16</f>
-        <v>1.2314783444377417</v>
+        <v>1.2133892936647717</v>
       </c>
       <c r="D22" s="6">
         <f t="shared" ref="D22:E22" si="5">D$20/D16</f>
-        <v>1.2797689984187124</v>
+        <v>1.2743698229233029</v>
       </c>
       <c r="E22" s="6">
         <f t="shared" si="5"/>
-        <v>0.99449263349300132</v>
+        <v>0.98466428638618053</v>
       </c>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.25">
@@ -5360,15 +5345,15 @@
       </c>
       <c r="C23" s="6">
         <f t="shared" ref="C23:E24" si="6">C$20/C17</f>
-        <v>1.0706173348864554</v>
+        <v>1.221830648333978</v>
       </c>
       <c r="D23" s="6">
         <f t="shared" si="6"/>
-        <v>1.1062676231643571</v>
+        <v>1.2832691815078834</v>
       </c>
       <c r="E23" s="6">
         <f t="shared" si="6"/>
-        <v>0.9300893634914571</v>
+        <v>0.98792618024499601</v>
       </c>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.25">
@@ -5377,35 +5362,35 @@
       </c>
       <c r="C24" s="6">
         <f t="shared" si="6"/>
-        <v>1.0567738363711994</v>
+        <v>1.2050637775556179</v>
       </c>
       <c r="D24" s="6">
         <f t="shared" si="6"/>
-        <v>1.091428561286039</v>
+        <v>1.2655930467739986</v>
       </c>
       <c r="E24" s="6">
         <f t="shared" si="6"/>
-        <v>0.92408786899122375</v>
+        <v>0.98142386161446082</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B25" s="1"/>
     </row>
     <row r="26" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B26" s="39">
+      <c r="B26" s="35">
         <v>2050</v>
       </c>
-      <c r="C26" s="39"/>
-      <c r="D26" s="39"/>
-      <c r="E26" s="39"/>
+      <c r="C26" s="35"/>
+      <c r="D26" s="35"/>
+      <c r="E26" s="35"/>
     </row>
     <row r="27" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B27" s="40" t="s">
+      <c r="B27" s="36" t="s">
         <v>136</v>
       </c>
-      <c r="C27" s="40"/>
-      <c r="D27" s="40"/>
-      <c r="E27" s="40"/>
+      <c r="C27" s="36"/>
+      <c r="D27" s="36"/>
+      <c r="E27" s="36"/>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
@@ -5518,21 +5503,21 @@
         <v>22.673263960703252</v>
       </c>
       <c r="D34">
-        <f>D8+D8*30*1.15*Validate_2020!$G7/100</f>
-        <v>17.229381982489965</v>
+        <f>D8+D8*30*1*Validate_2020!$G7/100</f>
+        <v>16.240521701214558</v>
       </c>
       <c r="E34">
-        <f>E8+E8*30*0.8*Validate_2020!$G7/100</f>
-        <v>14.04493969826521</v>
+        <f>E8+E8*30*0.65*Validate_2020!$G7/100</f>
+        <v>13.114203566596995</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B36" s="38" t="s">
+      <c r="B36" s="39" t="s">
         <v>131</v>
       </c>
-      <c r="C36" s="38"/>
-      <c r="D36" s="38"/>
-      <c r="E36" s="38"/>
+      <c r="C36" s="39"/>
+      <c r="D36" s="39"/>
+      <c r="E36" s="39"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
@@ -5543,15 +5528,15 @@
       </c>
       <c r="C37">
         <f>SUM(C$28:C$32)*$I1*1000000</f>
-        <v>1631887588.9423687</v>
+        <v>2030584564.1338036</v>
       </c>
       <c r="D37">
         <f t="shared" ref="D37:E37" si="7">SUM(D$28:D$32)*$I1*1000000</f>
-        <v>2823433643.6161485</v>
+        <v>3513244915.5390234</v>
       </c>
       <c r="E37">
-        <f t="shared" si="7"/>
-        <v>2037980618.0494425</v>
+        <f>SUM(E$28:E$32)*$I1*1000000</f>
+        <v>2535892798.6560063</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -5560,15 +5545,15 @@
       </c>
       <c r="C38">
         <f>SUM(C$28:C$32)*$I2*1000000</f>
-        <v>2020379366.0633669</v>
+        <v>2011265247.6007645</v>
       </c>
       <c r="D38">
         <f>SUM(D$28:D$32)*$I2*1000000</f>
-        <v>3495588246.1905475</v>
+        <v>3479819323.8250723</v>
       </c>
       <c r="E38">
         <f>SUM(E$28:E$32)*$I2*1000000</f>
-        <v>2523148050.7874451</v>
+        <v>2511765896.2179451</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -5577,15 +5562,15 @@
       </c>
       <c r="C39">
         <f>SUM(C$28:C$32)*$I3*1000000</f>
-        <v>2059339606.2925444</v>
+        <v>2049903880.6668463</v>
       </c>
       <c r="D39">
         <f>SUM(D$28:D$32)*$I3*1000000</f>
-        <v>3562995862.8498054</v>
+        <v>3546670507.2529821</v>
       </c>
       <c r="E39">
         <f>SUM(E$28:E$32)*$I3*1000000</f>
-        <v>2571803494.3361478</v>
+        <v>2560019701.0940733</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -5593,15 +5578,15 @@
         <v>60</v>
       </c>
       <c r="C40">
-        <f>C33*$I4*1000000</f>
+        <f t="shared" ref="C40:E41" si="8">C33*$I4*1000000</f>
         <v>6084543.7504571546</v>
       </c>
       <c r="D40">
-        <f>D33*$I4*1000000</f>
+        <f t="shared" si="8"/>
         <v>305356065.49256176</v>
       </c>
       <c r="E40">
-        <f>E33*$I4*1000000</f>
+        <f t="shared" si="8"/>
         <v>1283460979.0919886</v>
       </c>
     </row>
@@ -5610,50 +5595,50 @@
         <v>80</v>
       </c>
       <c r="C41">
-        <f>C34*$I5*1000000</f>
-        <v>793564238.62461388</v>
+        <f t="shared" si="8"/>
+        <v>634851390.8996911</v>
       </c>
       <c r="D41">
-        <f>D34*$I5*1000000</f>
-        <v>603028369.38714886</v>
+        <f t="shared" si="8"/>
+        <v>454734607.63400757</v>
       </c>
       <c r="E41">
         <f>E34*$I5*1000000</f>
-        <v>491572889.43928236</v>
+        <v>367197699.86471581</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B43" s="39" t="s">
+      <c r="B43" s="35" t="s">
         <v>137</v>
       </c>
-      <c r="C43" s="39"/>
-      <c r="D43" s="39"/>
-      <c r="E43" s="39"/>
+      <c r="C43" s="35"/>
+      <c r="D43" s="35"/>
+      <c r="E43" s="35"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B44" s="33" t="s">
+      <c r="B44" s="38" t="s">
         <v>64</v>
       </c>
-      <c r="C44" s="33"/>
-      <c r="D44" s="33"/>
-      <c r="E44" s="33"/>
+      <c r="C44" s="38"/>
+      <c r="D44" s="38"/>
+      <c r="E44" s="38"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="35"/>
+      <c r="A45" s="1"/>
       <c r="B45" s="24" t="s">
         <v>128</v>
       </c>
       <c r="C45" s="26">
         <f>365*(C37+C$40+C$41)*(1-$I$6)*($I$9)/1000/1000000</f>
-        <v>17.128957967745702</v>
+        <v>18.331973662655475</v>
       </c>
       <c r="D45" s="26">
-        <f t="shared" ref="D45:E45" si="8">365*(D37+D$40+D$41)*(1-$I$6)*($I$9)/1000/1000000</f>
-        <v>26.288792453964078</v>
+        <f>365*(D37+D$40+D$41)*(1-$I$7)*($I$9)/1000/1000000</f>
+        <v>28.621733438984979</v>
       </c>
       <c r="E45" s="26">
-        <f>365*(E37+E$40+E$41)*(1-$I$6)*($I$9)/1000/1000000</f>
-        <v>26.860780550717838</v>
+        <f>365*(E37+E$40+E$41)*(1-$I$8)*($I$9)/1000/1000000</f>
+        <v>26.894406692184052</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -5661,16 +5646,16 @@
         <v>129</v>
       </c>
       <c r="C46" s="26">
-        <f>365*(C38+C$40+C$41)*(1-$I$6)*($I$9)/1000/1000000</f>
-        <v>19.86568829167458</v>
+        <f t="shared" ref="C46:C47" si="9">365*(C38+C$40+C$41)*(1-$I$6)*($I$9)/1000/1000000</f>
+        <v>18.199404512605764</v>
       </c>
       <c r="D46" s="26">
-        <f>365*(D38+D$40+D$41)*(1-$I$6)*($I$9)/1000/1000000</f>
-        <v>31.023785551799435</v>
+        <f t="shared" ref="D46:D47" si="10">365*(D38+D$40+D$41)*(1-$I$7)*($I$9)/1000/1000000</f>
+        <v>28.397857182082856</v>
       </c>
       <c r="E46" s="26">
-        <f>365*(E38+E$40+E$41)*(1-$I$6)*($I$9)/1000/1000000</f>
-        <v>30.278542530640696</v>
+        <f t="shared" ref="E46:E47" si="11">365*(E38+E$40+E$41)*(1-$I$8)*($I$9)/1000/1000000</f>
+        <v>26.739415470921948</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -5678,16 +5663,16 @@
         <v>130</v>
       </c>
       <c r="C47" s="26">
-        <f>365*(C39+C$40+C$41)*(1-$I$6)*($I$9)/1000/1000000</f>
-        <v>20.140143703969017</v>
+        <f t="shared" si="9"/>
+        <v>18.464542812705215</v>
       </c>
       <c r="D47" s="26">
-        <f>365*(D39+D$40+D$41)*(1-$I$6)*($I$9)/1000/1000000</f>
-        <v>31.498638507355576</v>
+        <f>365*(D39+D$40+D$41)*(1-$I$7)*($I$9)/1000/1000000</f>
+        <v>28.845609695887145</v>
       </c>
       <c r="E47" s="26">
-        <f>365*(E39+E$40+E$41)*(1-$I$6)*($I$9)/1000/1000000</f>
-        <v>30.62129580271953</v>
+        <f t="shared" si="11"/>
+        <v>27.049397913446196</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -5701,30 +5686,30 @@
       </c>
       <c r="C49" s="27">
         <f>NPP!C26</f>
-        <v>10.674279188410017</v>
+        <v>11.079966499362209</v>
       </c>
       <c r="D49" s="27">
         <f>NPP!D26</f>
-        <v>17.552209325883879</v>
+        <v>18.690580672401197</v>
       </c>
       <c r="E49" s="27">
         <f>NPP!E26</f>
-        <v>15.703157465733</v>
+        <v>14.778119061376351</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B50" s="1"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B51" s="32" t="s">
+      <c r="B51" s="37" t="s">
         <v>79</v>
       </c>
-      <c r="C51" s="32"/>
-      <c r="D51" s="32"/>
-      <c r="E51" s="32"/>
+      <c r="C51" s="37"/>
+      <c r="D51" s="37"/>
+      <c r="E51" s="37"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="34">
+      <c r="A52" s="2">
         <v>2050</v>
       </c>
       <c r="B52" s="20" t="str">
@@ -5733,117 +5718,117 @@
       </c>
       <c r="C52" s="21">
         <f>C$49/C45</f>
-        <v>0.62317154426497967</v>
+        <v>0.6044066341821932</v>
       </c>
       <c r="D52" s="21">
         <f>D$49/D45</f>
-        <v>0.66766890706831183</v>
+        <v>0.65302056956980825</v>
       </c>
       <c r="E52" s="21">
         <f>E$49/E45</f>
-        <v>0.58461284980466965</v>
+        <v>0.54948671039733743</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B53" s="20" t="str">
-        <f t="shared" ref="B53:B54" si="9">B46</f>
+        <f t="shared" ref="B53:B54" si="12">B46</f>
         <v>WC</v>
       </c>
       <c r="C53" s="21">
-        <f t="shared" ref="C53:E53" si="10">C$49/C46</f>
-        <v>0.53732239385249247</v>
+        <f t="shared" ref="C53:E53" si="13">C$49/C46</f>
+        <v>0.60880928778124044</v>
       </c>
       <c r="D53" s="21">
-        <f t="shared" si="10"/>
-        <v>0.56576620208315676</v>
+        <f t="shared" si="13"/>
+        <v>0.65816869746755757</v>
       </c>
       <c r="E53" s="21">
-        <f t="shared" si="10"/>
-        <v>0.51862329403213581</v>
+        <f t="shared" si="13"/>
+        <v>0.55267173201474684</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B54" s="20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>BC</v>
       </c>
       <c r="C54" s="21">
-        <f t="shared" ref="C54:E54" si="11">C$49/C47</f>
-        <v>0.53000015021275337</v>
+        <f t="shared" ref="C54:E54" si="14">C$49/C47</f>
+        <v>0.60006719970007738</v>
       </c>
       <c r="D54" s="21">
-        <f t="shared" si="11"/>
-        <v>0.5572370793672583</v>
+        <f t="shared" si="14"/>
+        <v>0.64795235286935648</v>
       </c>
       <c r="E54" s="21">
-        <f t="shared" si="11"/>
-        <v>0.51281818923999867</v>
+        <f t="shared" si="14"/>
+        <v>0.54633818869699058</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
+      <c r="B55" s="2"/>
+      <c r="C55" s="34"/>
+      <c r="D55" s="34"/>
+      <c r="E55" s="34"/>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B55" s="20" t="str">
+      <c r="B56" s="20" t="str">
         <f>B52</f>
         <v>BL</v>
       </c>
-      <c r="C55" s="21">
+      <c r="C56" s="21">
         <f>(C52+C$22)/2</f>
-        <v>0.9273249443513607</v>
-      </c>
-      <c r="D55" s="21">
-        <f t="shared" ref="D55:E55" si="12">(D52+D$22)/2</f>
-        <v>0.97371895274351217</v>
-      </c>
-      <c r="E55" s="21">
-        <f t="shared" si="12"/>
-        <v>0.78955274164883549</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="1"/>
-      <c r="B56" s="20" t="str">
-        <f t="shared" ref="B56:B57" si="13">B53</f>
-        <v>WC</v>
-      </c>
-      <c r="C56" s="21">
-        <f t="shared" ref="C56:E56" si="14">(C53+C$22)/2</f>
-        <v>0.8844003691451171</v>
+        <v>0.90889796392348243</v>
       </c>
       <c r="D56" s="21">
-        <f t="shared" si="14"/>
-        <v>0.92276760025093463</v>
+        <f t="shared" ref="D56:E56" si="15">(D52+D$22)/2</f>
+        <v>0.96369519624655564</v>
       </c>
       <c r="E56" s="21">
-        <f t="shared" si="14"/>
-        <v>0.75655796376256856</v>
+        <f t="shared" si="15"/>
+        <v>0.76707549839175893</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
       <c r="B57" s="20" t="str">
-        <f t="shared" si="13"/>
+        <f>B53</f>
+        <v>WC</v>
+      </c>
+      <c r="C57" s="21">
+        <f t="shared" ref="C57:E57" si="16">(C53+C$22)/2</f>
+        <v>0.91109929072300599</v>
+      </c>
+      <c r="D57" s="21">
+        <f t="shared" si="16"/>
+        <v>0.96626926019543025</v>
+      </c>
+      <c r="E57" s="21">
+        <f t="shared" si="16"/>
+        <v>0.76866800920046363</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="1"/>
+      <c r="B58" s="20" t="str">
+        <f>B54</f>
         <v>BC</v>
       </c>
-      <c r="C57" s="21">
-        <f t="shared" ref="C57:E57" si="15">(C54+C$22)/2</f>
-        <v>0.88073924732524755</v>
-      </c>
-      <c r="D57" s="21">
-        <f t="shared" si="15"/>
-        <v>0.91850303889298535</v>
-      </c>
-      <c r="E57" s="21">
-        <f t="shared" si="15"/>
-        <v>0.75365541136649994</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B58" s="3"/>
-      <c r="C58" s="3"/>
-      <c r="D58" s="3"/>
-      <c r="E58" s="3"/>
+      <c r="C58" s="21">
+        <f t="shared" ref="C58:E58" si="17">(C54+C$22)/2</f>
+        <v>0.90672824668242447</v>
+      </c>
+      <c r="D58" s="21">
+        <f t="shared" si="17"/>
+        <v>0.9611610878963297</v>
+      </c>
+      <c r="E58" s="21">
+        <f t="shared" si="17"/>
+        <v>0.7655012375415855</v>
+      </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B59" s="3"/>
@@ -5851,229 +5836,242 @@
       <c r="D59" s="3"/>
       <c r="E59" s="3"/>
     </row>
-    <row r="60" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B60" s="39" t="s">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B60" s="3"/>
+      <c r="C60" s="3"/>
+      <c r="D60" s="3"/>
+      <c r="E60" s="3"/>
+    </row>
+    <row r="61" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B61" s="35" t="s">
         <v>138</v>
       </c>
-      <c r="C60" s="39"/>
-      <c r="D60" s="39"/>
-      <c r="E60" s="39"/>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B61" s="33" t="s">
+      <c r="C61" s="35"/>
+      <c r="D61" s="35"/>
+      <c r="E61" s="35"/>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B62" s="38" t="s">
         <v>64</v>
       </c>
-      <c r="C61" s="33"/>
-      <c r="D61" s="33"/>
-      <c r="E61" s="33"/>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B62" s="28" t="str">
-        <f>B55</f>
-        <v>BL</v>
-      </c>
-      <c r="C62" s="29">
-        <f>C45</f>
-        <v>17.128957967745702</v>
-      </c>
-      <c r="D62" s="29">
-        <f t="shared" ref="D62:E62" si="16">D45</f>
-        <v>26.288792453964078</v>
-      </c>
-      <c r="E62" s="29">
-        <f t="shared" si="16"/>
-        <v>26.860780550717838</v>
-      </c>
+      <c r="C62" s="38"/>
+      <c r="D62" s="38"/>
+      <c r="E62" s="38"/>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B63" s="28" t="str">
-        <f t="shared" ref="B63:B64" si="17">B56</f>
-        <v>WC</v>
+        <f>B56</f>
+        <v>BL</v>
       </c>
       <c r="C63" s="29">
-        <f t="shared" ref="C63:E64" si="18">C46</f>
-        <v>19.86568829167458</v>
+        <f>C45</f>
+        <v>18.331973662655475</v>
       </c>
       <c r="D63" s="29">
+        <f t="shared" ref="D63:E63" si="18">D45</f>
+        <v>28.621733438984979</v>
+      </c>
+      <c r="E63" s="29">
         <f t="shared" si="18"/>
-        <v>31.023785551799435</v>
-      </c>
-      <c r="E63" s="29">
-        <f>E46</f>
-        <v>30.278542530640696</v>
+        <v>26.894406692184052</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B64" s="28" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" ref="B64:B65" si="19">B57</f>
+        <v>WC</v>
+      </c>
+      <c r="C64" s="29">
+        <f>C46</f>
+        <v>18.199404512605764</v>
+      </c>
+      <c r="D64" s="29">
+        <f>D46</f>
+        <v>28.397857182082856</v>
+      </c>
+      <c r="E64" s="29">
+        <f>E46</f>
+        <v>26.739415470921948</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B65" s="28" t="str">
+        <f t="shared" si="19"/>
         <v>BC</v>
       </c>
-      <c r="C64" s="29">
-        <f t="shared" si="18"/>
-        <v>20.140143703969017</v>
-      </c>
-      <c r="D64" s="29">
-        <f t="shared" si="18"/>
-        <v>31.498638507355576</v>
-      </c>
-      <c r="E64" s="29">
-        <f t="shared" si="18"/>
-        <v>30.62129580271953</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B65" s="3"/>
-      <c r="C65" s="3"/>
-      <c r="D65" s="3"/>
-      <c r="E65" s="3"/>
+      <c r="C65" s="29">
+        <f>C47</f>
+        <v>18.464542812705215</v>
+      </c>
+      <c r="D65" s="29">
+        <f>D47</f>
+        <v>28.845609695887145</v>
+      </c>
+      <c r="E65" s="29">
+        <f>E47</f>
+        <v>27.049397913446196</v>
+      </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B66" s="22" t="s">
+      <c r="B66" s="3"/>
+      <c r="C66" s="3"/>
+      <c r="D66" s="3"/>
+      <c r="E66" s="3"/>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B67" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="C66" s="23">
+      <c r="C67" s="23">
         <f>NPP!C30</f>
-        <v>11.359853756962167</v>
-      </c>
-      <c r="D66" s="23">
+        <v>11.790781190987943</v>
+      </c>
+      <c r="D67" s="23">
         <f>NPP!D30</f>
-        <v>17.93701743680694</v>
-      </c>
-      <c r="E66" s="23">
+        <v>19.063666472342934</v>
+      </c>
+      <c r="E67" s="23">
         <f>NPP!E30</f>
-        <v>15.853248973659641</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B67" s="3"/>
-      <c r="C67" s="3"/>
-      <c r="D67" s="3"/>
-      <c r="E67" s="3"/>
+        <v>14.929996638092023</v>
+      </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B68" s="32" t="s">
+      <c r="B68" s="3"/>
+      <c r="C68" s="3"/>
+      <c r="D68" s="3"/>
+      <c r="E68" s="3"/>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B69" s="37" t="s">
         <v>79</v>
       </c>
-      <c r="C68" s="32"/>
-      <c r="D68" s="32"/>
-      <c r="E68" s="32"/>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="37">
+      <c r="C69" s="37"/>
+      <c r="D69" s="37"/>
+      <c r="E69" s="37"/>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="33">
         <v>2050</v>
       </c>
-      <c r="B69" s="36" t="str">
+      <c r="B70" s="32" t="str">
         <f>B52</f>
         <v>BL</v>
       </c>
-      <c r="C69" s="21">
-        <f>C$66/C62</f>
-        <v>0.66319584520862762</v>
-      </c>
-      <c r="D69" s="21">
-        <f>D$66/D62</f>
-        <v>0.68230663193136598</v>
-      </c>
-      <c r="E69" s="21">
-        <f>E$66/E62</f>
-        <v>0.59020060655817286</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" s="37"/>
-      <c r="B70" s="36" t="str">
-        <f t="shared" ref="B70:B71" si="19">B53</f>
+      <c r="C70" s="21">
+        <f>C$67/C63</f>
+        <v>0.64318122030729508</v>
+      </c>
+      <c r="D70" s="21">
+        <f>D$67/D63</f>
+        <v>0.66605562213701464</v>
+      </c>
+      <c r="E70" s="21">
+        <f>E$67/E63</f>
+        <v>0.555133891183066</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="33"/>
+      <c r="B71" s="32" t="str">
+        <f>B53</f>
         <v>WC</v>
       </c>
-      <c r="C70" s="21">
-        <f>C$66/C63</f>
-        <v>0.57183288040026858</v>
-      </c>
-      <c r="D70" s="21">
-        <f t="shared" ref="D70:E71" si="20">D$66/D63</f>
-        <v>0.57816984993201648</v>
-      </c>
-      <c r="E70" s="21">
-        <f t="shared" si="20"/>
-        <v>0.52358031954863005</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" s="37"/>
-      <c r="B71" s="36" t="str">
-        <f t="shared" si="19"/>
-        <v>BC</v>
-      </c>
       <c r="C71" s="21">
-        <f>C$66/C64</f>
-        <v>0.56404035263777597</v>
+        <f>C$67/C64</f>
+        <v>0.64786631797876093</v>
       </c>
       <c r="D71" s="21">
-        <f t="shared" si="20"/>
-        <v>0.5694537379010296</v>
+        <f t="shared" ref="D71:E72" si="20">D$67/D64</f>
+        <v>0.67130651267486585</v>
       </c>
       <c r="E71" s="21">
         <f t="shared" si="20"/>
-        <v>0.51771972929544308</v>
+        <v>0.5583516458812573</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" s="37" t="s">
+      <c r="A72" s="33"/>
+      <c r="B72" s="32" t="str">
+        <f>B54</f>
+        <v>BC</v>
+      </c>
+      <c r="C72" s="21">
+        <f>C$67/C65</f>
+        <v>0.6385633974579028</v>
+      </c>
+      <c r="D72" s="21">
+        <f t="shared" si="20"/>
+        <v>0.66088623791720591</v>
+      </c>
+      <c r="E72" s="21">
+        <f t="shared" si="20"/>
+        <v>0.55195301151861698</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="33"/>
+      <c r="B73" s="16"/>
+      <c r="C73" s="34"/>
+      <c r="D73" s="34"/>
+      <c r="E73" s="34"/>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="B72" s="36" t="str">
-        <f>B55</f>
+      <c r="B74" s="32" t="str">
+        <f>B56</f>
         <v>BL</v>
       </c>
-      <c r="C72" s="21">
-        <f>(C$22+C69)*0.5</f>
-        <v>0.94733709482318473</v>
-      </c>
-      <c r="D72" s="21">
-        <f>(D$22+D69)*0.5</f>
-        <v>0.98103781517503919</v>
-      </c>
-      <c r="E72" s="21">
-        <f t="shared" ref="D72:E72" si="21">(E$22+E69)*0.5</f>
-        <v>0.79234662002558709</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" s="16"/>
-      <c r="B73" s="36" t="str">
-        <f t="shared" ref="B73:B74" si="22">B56</f>
+      <c r="C74" s="21">
+        <f>(C$22+C70)*0.5</f>
+        <v>0.92828525698603337</v>
+      </c>
+      <c r="D74" s="21">
+        <f>(D$22+D70)*0.5</f>
+        <v>0.97021272253015878</v>
+      </c>
+      <c r="E74" s="21">
+        <f t="shared" ref="E74" si="21">(E$22+E70)*0.5</f>
+        <v>0.76989908878462332</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="16"/>
+      <c r="B75" s="32" t="str">
+        <f t="shared" ref="B75:B76" si="22">B57</f>
         <v>WC</v>
       </c>
-      <c r="C73" s="21">
-        <f t="shared" ref="C73:E73" si="23">(C$22+C70)*0.5</f>
-        <v>0.90165561241900516</v>
-      </c>
-      <c r="D73" s="21">
-        <f>(D$22+D70)*0.5</f>
-        <v>0.92896942417536443</v>
-      </c>
-      <c r="E73" s="21">
-        <f>(E$22+E70)*0.5</f>
-        <v>0.75903647652081574</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" s="16"/>
-      <c r="B74" s="36" t="str">
+      <c r="C75" s="21">
+        <f t="shared" ref="C75" si="23">(C$22+C71)*0.5</f>
+        <v>0.9306278058217663</v>
+      </c>
+      <c r="D75" s="21">
+        <f>(D$22+D71)*0.5</f>
+        <v>0.97283816779908439</v>
+      </c>
+      <c r="E75" s="21">
+        <f>(E$22+E71)*0.5</f>
+        <v>0.77150796613371897</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="16"/>
+      <c r="B76" s="32" t="str">
         <f t="shared" si="22"/>
         <v>BC</v>
       </c>
-      <c r="C74" s="21">
-        <f t="shared" ref="C74:E74" si="24">(C$22+C71)*0.5</f>
-        <v>0.89775934853775885</v>
-      </c>
-      <c r="D74" s="21">
+      <c r="C76" s="21">
+        <f t="shared" ref="C76:E76" si="24">(C$22+C72)*0.5</f>
+        <v>0.92597634556133723</v>
+      </c>
+      <c r="D76" s="21">
         <f t="shared" si="24"/>
-        <v>0.92461136815987099</v>
-      </c>
-      <c r="E74" s="21">
+        <v>0.96762803042025447</v>
+      </c>
+      <c r="E76" s="21">
         <f t="shared" si="24"/>
-        <v>0.75610618139422225</v>
+        <v>0.7683086489523987</v>
       </c>
     </row>
   </sheetData>
@@ -6081,12 +6079,12 @@
     <mergeCell ref="B26:E26"/>
     <mergeCell ref="B43:E43"/>
     <mergeCell ref="B27:E27"/>
-    <mergeCell ref="B68:E68"/>
+    <mergeCell ref="B69:E69"/>
     <mergeCell ref="B51:E51"/>
     <mergeCell ref="B44:E44"/>
+    <mergeCell ref="B62:E62"/>
+    <mergeCell ref="B36:E36"/>
     <mergeCell ref="B61:E61"/>
-    <mergeCell ref="B36:E36"/>
-    <mergeCell ref="B60:E60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Rasterized animal populations/Zonal statistics/Summary.xlsx
+++ b/Rasterized animal populations/Zonal statistics/Summary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JHawkins\Documents\Github\KE.beef.spatial\Rasterized animal populations\Zonal statistics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0AE5A25-8871-4B42-8F94-AE9C9816166C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86F87C46-F811-42DD-BD14-3E9DA22D1DA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="5" xr2:uid="{3882C52B-09A6-47D1-94BA-1F6173569800}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" activeTab="1" xr2:uid="{3882C52B-09A6-47D1-94BA-1F6173569800}"/>
   </bookViews>
   <sheets>
     <sheet name="Validate_2020" sheetId="2" r:id="rId1"/>
@@ -136,7 +136,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="171">
   <si>
     <t>Arid</t>
   </si>
@@ -553,6 +553,102 @@
   </si>
   <si>
     <t>RCP 8.5</t>
+  </si>
+  <si>
+    <t>Sensitivity analysis</t>
+  </si>
+  <si>
+    <t>Herd scalars</t>
+  </si>
+  <si>
+    <t>+20% Herd size</t>
+  </si>
+  <si>
+    <t>Animal populations (M hd) -- SA scenario specific</t>
+  </si>
+  <si>
+    <t>+20% Zebu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-20% Herd size </t>
+  </si>
+  <si>
+    <t>-20% Zebu</t>
+  </si>
+  <si>
+    <t>+20% Boran</t>
+  </si>
+  <si>
+    <t>-20% Boran</t>
+  </si>
+  <si>
+    <t>+20% Exotic</t>
+  </si>
+  <si>
+    <t>-20% Exotic</t>
+  </si>
+  <si>
+    <t>+20% Finisher:Breeder</t>
+  </si>
+  <si>
+    <t>-20% Finisher:Breeder</t>
+  </si>
+  <si>
+    <t>+20% Pastoral:Agropastoral</t>
+  </si>
+  <si>
+    <t>-20% Pastoral:Agropastoral</t>
+  </si>
+  <si>
+    <t>+20% Mixed:Agropastoral</t>
+  </si>
+  <si>
+    <t>-20% Mixed:Agropastoral</t>
+  </si>
+  <si>
+    <t>+20% Cowcalf:Finisher</t>
+  </si>
+  <si>
+    <t>-20% Cowcalf:Finisher</t>
+  </si>
+  <si>
+    <t>+20% Commercial:Subsistence</t>
+  </si>
+  <si>
+    <t>-20% Commercial:Subsistence</t>
+  </si>
+  <si>
+    <t>Beef cattle weights - by SA scenario</t>
+  </si>
+  <si>
+    <t>2050 Biomass demand (MT/ha/yr)</t>
+  </si>
+  <si>
+    <t>2050 Total animal weights (kg), by species</t>
+  </si>
+  <si>
+    <t>Animal population growth (M hd) -- 2050</t>
+  </si>
+  <si>
+    <t>Biomass supply (MT/yr) - R4</t>
+  </si>
+  <si>
+    <t>2050 Carrying capacity (S/D)</t>
+  </si>
+  <si>
+    <t>Carrying capacity (S/D) - BL - 2020</t>
+  </si>
+  <si>
+    <t>Color code -- CC impacts</t>
+  </si>
+  <si>
+    <t>Unique CC value</t>
+  </si>
+  <si>
+    <t>CABI (2019) calibration</t>
+  </si>
+  <si>
+    <t>Boran</t>
   </si>
 </sst>
 </file>
@@ -615,7 +711,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -652,6 +748,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -665,7 +773,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -731,6 +839,20 @@
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -746,7 +868,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -765,777 +889,6 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="ZS_Grassland_Arid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1">
-        <row r="2">
-          <cell r="D2">
-            <v>202419</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink10.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2020_GRASS_Arid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.33293323112310402</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink11.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2020_GRASS_SArid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.48080803465972</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink12.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2020_GRASS_Humid"/>
-      <sheetName val="filtered"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="2">
-          <cell r="F2">
-            <v>0.88607168377191448</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2020_CROP_Arid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.97599038751874501</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2020_CROP_SArid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.71416468993051396</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2020_CROP_Humid"/>
-      <sheetName val="filtered"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="2">
-          <cell r="F2">
-            <v>1.0193612610195171</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink16.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2020_SHRUB_Arid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.20100553202445001</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink17.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2020_SHRUB_SArid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.48842843619779902</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink18.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2020_SHRUB_Humid"/>
-      <sheetName val="filtered"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="2">
-          <cell r="F2">
-            <v>0.9284507277249876</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink19.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R4_GRASS_Arid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.36084903504638699</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="ZS_Grassland_SArid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="D2">
-            <v>129806</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink20.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R4_GRASS_SArid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.51075241024303597</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink21.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R4_GRASS_Humid"/>
-      <sheetName val="filtered"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="2">
-          <cell r="F2">
-            <v>0.90483097904137921</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink22.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R4_CROP_Arid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>1.0384816436740301</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink23.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R4_CROP_SArid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.72447113600000002</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink24.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R4_CROP_Humid"/>
-      <sheetName val="filtered"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="2">
-          <cell r="F2">
-            <v>0.98649141647533578</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink25.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R4_SHRUB_Arid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.21776707800273001</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink26.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R4_SHRUB_SArid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.51075241024303597</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink27.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R4_SHRUB_Humid"/>
-      <sheetName val="filtered"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="2">
-          <cell r="F2">
-            <v>0.90483097904137921</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink28.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R8_GRASS_Arid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.38422689204237098</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink29.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R8_GRASS_SArid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.51337712420869996</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="ZS_Grassland_Humid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>64439.636684333513</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink30.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R8_GRASS_Humid"/>
-      <sheetName val="filtered"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="2">
-          <cell r="F2">
-            <v>0.88457459938562355</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink31.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R8_CROP_Arid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>1.10532849796393</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink32.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R8_CROP_SArid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.80695680840268103</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink33.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R8_CROP_Humid"/>
-      <sheetName val="filtered"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="2">
-          <cell r="F2">
-            <v>1.0242825546815273</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink34.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R8_SHRUB_Arid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.231319877140652</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink35.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R8_SHRUB_SArid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>0.51046846997934603</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink36.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="NPP_2050_R8_SHRUB_Humid"/>
-      <sheetName val="filtered"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="2">
-          <cell r="F2">
-            <v>0.93416975929597834</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink37.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Raster_logic"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="89">
-          <cell r="I89">
-            <v>0.5</v>
-          </cell>
-        </row>
-        <row r="90">
-          <cell r="I90">
-            <v>0.44</v>
-          </cell>
-        </row>
-        <row r="91">
-          <cell r="I91">
-            <v>0.36499999999999999</v>
-          </cell>
-        </row>
-        <row r="95">
-          <cell r="I95">
-            <v>0.34</v>
-          </cell>
-        </row>
-        <row r="96">
-          <cell r="I96">
-            <v>0.4</v>
-          </cell>
-        </row>
-        <row r="98">
-          <cell r="I98">
-            <v>0.4</v>
-          </cell>
-        </row>
-        <row r="99">
-          <cell r="I99">
-            <v>0.7</v>
-          </cell>
-        </row>
-        <row r="100">
-          <cell r="I100">
-            <v>0.7</v>
-          </cell>
-        </row>
-        <row r="102">
-          <cell r="I102">
-            <v>0.4</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink38.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1600,7 +953,231 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink39.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink10.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Dairy_total_Humid_2020"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1">
+        <row r="2">
+          <cell r="D2">
+            <v>5233916.3978957208</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink11.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Sheep_total_Arid_2020"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1">
+        <row r="2">
+          <cell r="C2">
+            <v>1300620.48691654</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink12.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Sheep_total_SArid_2020"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1">
+        <row r="2">
+          <cell r="C2">
+            <v>1063972.5190212701</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Sheep_total_Humid_2020"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1">
+        <row r="2">
+          <cell r="D2">
+            <v>1001433.3524225579</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Pastoral_Zebu_2020"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>7912803.5780913802</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Pastoral_Boran_2020"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1">
+        <row r="2">
+          <cell r="K2">
+            <v>1124203.7226895699</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink16.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Pastoral_Zebu_2050"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>8554757.4814370908</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink17.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Pastoral_Boran_2050"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>1215408.67359516</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink18.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Agpastoral_Zebu_2020"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>3685141.0110471202</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink19.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Agpastoral_Boran_2020"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>277376.20390618598</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1622,7 +1199,406 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink20.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Agpastoral_Zebu_2050"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>6488770.1197828101</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink21.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Agpastoral_Boran_2050"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>488402.05019366002</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink22.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Mixed_Zebu_2020"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>298374.71550379699</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink23.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Mixed_Boran_2020"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>25945.627401560501</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink24.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Mixed_Zebu_2050"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>404262.59496554697</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink25.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Mixed_Boran_2050"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>35153.269665965803</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink26.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Cowcalf_Boran_2020"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>1184753.34766715</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink27.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Cowcalf_Exotic_2020"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>985977.36353097099</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink28.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Cowcalf_Boran_2050"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>1806208.69891036</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink29.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Cowcalf_Exotic_2050"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>1503165.94333724</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="SArid_Subsistence"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1">
+        <row r="2">
+          <cell r="C2">
+            <v>467695.362210333</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink30.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Finisher_Boran_2020"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>26321.876059999999</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink31.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Finisher_Exotic_2020"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>12386.7653238613</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink32.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Finisher_Boran_2050"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>918345.45531155204</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink33.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Finisher_Exotic_2050"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>432162.57168335503</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink34.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="ZS_Grassland_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1">
+        <row r="2">
+          <cell r="D2">
+            <v>202419</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink35.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="ZS_Grassland_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="D2">
+            <v>129806</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink36.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="ZS_Grassland_Humid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>64439.636684333513</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink37.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1645,20 +1621,21 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink40.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink38.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="SArid_Subsistence"/>
+      <sheetName val="ZS_Cropland_SArid"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1">
+      <sheetData sheetId="0">
         <row r="2">
-          <cell r="C2">
-            <v>467695.362210333</v>
+          <cell r="D2">
+            <v>19552</v>
           </cell>
         </row>
       </sheetData>
@@ -1667,7 +1644,30 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink39.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="ZS_Cropland_Humid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>27078.877240262751</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1689,7 +1689,241 @@
 </externalLink>
 </file>
 
+<file path=xl/externalLinks/externalLink40.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="ZS_Shrubland_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="D2">
+            <v>277889</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink41.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="ZS_Shrubland_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="D2">
+            <v>357491</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/externalLinks/externalLink42.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="ZS_Shrubland_Humid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>63327.68656939434</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink43.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2020_GRASS_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.33293323112310402</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink44.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2020_GRASS_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.48080803465972</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink45.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2020_GRASS_Humid"/>
+      <sheetName val="filtered"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="F2">
+            <v>0.88607168377191448</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink46.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2020_CROP_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.97599038751874501</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink47.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2020_CROP_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.71416468993051396</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink48.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2020_CROP_Humid"/>
+      <sheetName val="filtered"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="F2">
+            <v>1.0193612610195171</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink49.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2020_SHRUB_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.20100553202445001</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1711,7 +1945,243 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink50.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2020_SHRUB_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.48842843619779902</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink51.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2020_SHRUB_Humid"/>
+      <sheetName val="filtered"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="F2">
+            <v>0.9284507277249876</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink52.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R4_GRASS_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.36084903504638699</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink53.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R4_GRASS_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.51075241024303597</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink54.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R4_GRASS_Humid"/>
+      <sheetName val="filtered"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="F2">
+            <v>0.90483097904137921</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink55.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R4_CROP_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>1.0384816436740301</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink56.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R4_CROP_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.72447113600000002</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink57.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R4_CROP_Humid"/>
+      <sheetName val="filtered"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="F2">
+            <v>0.98649141647533578</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink58.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R4_SHRUB_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.21776707800273001</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink59.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R4_SHRUB_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.51075241024303597</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1733,7 +2203,245 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink60.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R4_SHRUB_Humid"/>
+      <sheetName val="filtered"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="F2">
+            <v>0.90483097904137921</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink61.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R8_GRASS_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.38422689204237098</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink62.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R8_GRASS_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.51337712420869996</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink63.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R8_GRASS_Humid"/>
+      <sheetName val="filtered"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="F2">
+            <v>0.88457459938562355</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink64.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R8_CROP_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>1.10532849796393</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink65.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R8_CROP_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.80695680840268103</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink66.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R8_CROP_Humid"/>
+      <sheetName val="filtered"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="F2">
+            <v>1.0242825546815273</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink67.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R8_SHRUB_Arid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.231319877140652</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink68.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R8_SHRUB_SArid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>0.51046846997934603</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink69.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="NPP_2050_R8_SHRUB_Humid"/>
+      <sheetName val="filtered"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="F2">
+            <v>0.93416975929597834</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1755,7 +2463,70 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink70.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Raster_logic"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="89">
+          <cell r="I89">
+            <v>0.5</v>
+          </cell>
+        </row>
+        <row r="90">
+          <cell r="I90">
+            <v>0.44</v>
+          </cell>
+        </row>
+        <row r="91">
+          <cell r="I91">
+            <v>0.40150000000000002</v>
+          </cell>
+        </row>
+        <row r="95">
+          <cell r="I95">
+            <v>0.34</v>
+          </cell>
+        </row>
+        <row r="96">
+          <cell r="I96">
+            <v>0.4</v>
+          </cell>
+        </row>
+        <row r="98">
+          <cell r="I98">
+            <v>0.4</v>
+          </cell>
+        </row>
+        <row r="99">
+          <cell r="I99">
+            <v>0.5</v>
+          </cell>
+        </row>
+        <row r="100">
+          <cell r="I100">
+            <v>0.7</v>
+          </cell>
+        </row>
+        <row r="102">
+          <cell r="I102">
+            <v>0.4</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1778,7 +2549,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1793,653 +2564,6 @@
         <row r="2">
           <cell r="C2">
             <v>1210306.62197518</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink47.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Dairy_total_Humid_2020"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1">
-        <row r="2">
-          <cell r="D2">
-            <v>5233916.3978957208</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink48.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Sheep_total_Arid_2020"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1">
-        <row r="2">
-          <cell r="C2">
-            <v>1300620.48691654</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink49.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Sheep_total_SArid_2020"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1">
-        <row r="2">
-          <cell r="C2">
-            <v>1063972.5190212701</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="ZS_Cropland_SArid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="D2">
-            <v>19552</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink50.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Sheep_total_Humid_2020"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1">
-        <row r="2">
-          <cell r="D2">
-            <v>1001433.3524225579</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink51.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Pastoral_Zebu_2020"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>7912803.5780913802</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink52.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Pastoral_Boran_2020"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1">
-        <row r="2">
-          <cell r="K2">
-            <v>1124203.7226895699</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink53.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Pastoral_Zebu_2050"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>8554757.4814370908</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink54.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Pastoral_Boran_2050"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>1215408.67359516</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink55.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Agpastoral_Zebu_2020"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>3685141.0110471202</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink56.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Agpastoral_Boran_2020"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>277376.20390618598</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink57.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Agpastoral_Zebu_2050"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>6488770.1197828101</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink58.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Agpastoral_Boran_2050"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>488402.05019366002</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink59.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Mixed_Zebu_2020"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>298374.71550379699</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="ZS_Cropland_Humid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>27078.877240262751</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink60.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Mixed_Boran_2020"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>25945.627401560501</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink61.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Mixed_Zebu_2050"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>404262.59496554697</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink62.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Mixed_Boran_2050"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>35153.269665965803</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink63.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Cowcalf_Boran_2020"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>1184753.34766715</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink64.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Cowcalf_Exotic_2020"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>985977.36353097099</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink65.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Cowcalf_Boran_2050"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>1806208.69891036</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink66.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Cowcalf_Exotic_2050"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>1503165.94333724</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink67.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Finisher_Boran_2020"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>26321.876059999999</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink68.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Finisher_Exotic_2020"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>12386.7653238613</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink69.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Finisher_Boran_2050"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>918345.45531155204</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="ZS_Shrubland_Arid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="D2">
-            <v>277889</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink70.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Finisher_Exotic_2050"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>432162.57168335503</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="ZS_Shrubland_SArid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="D2">
-            <v>357491</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="ZS_Shrubland_Humid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>63327.68656939434</v>
           </cell>
         </row>
       </sheetData>
@@ -2825,7 +2949,7 @@
         <v>0.51509165724121786</v>
       </c>
       <c r="D2">
-        <f>[38]FAO_2019_animal_trends!$F$35</f>
+        <f>[1]FAO_2019_animal_trends!$F$35</f>
         <v>0.53615960099750615</v>
       </c>
       <c r="E2">
@@ -2837,7 +2961,7 @@
         <v>0.52629975213940838</v>
       </c>
       <c r="G2">
-        <f>[38]FAO_2019_animal_trends!$G$35</f>
+        <f>[1]FAO_2019_animal_trends!$G$35</f>
         <v>0.38312009613345605</v>
       </c>
       <c r="H2">
@@ -2858,7 +2982,7 @@
         <v>0.33339443937546853</v>
       </c>
       <c r="D3">
-        <f>[38]FAO_2019_animal_trends!$F$36</f>
+        <f>[1]FAO_2019_animal_trends!$F$36</f>
         <v>0.36159600997506236</v>
       </c>
       <c r="E3">
@@ -2870,7 +2994,7 @@
         <v>0.31358889061540685</v>
       </c>
       <c r="G3">
-        <f>[38]FAO_2019_animal_trends!$G$36</f>
+        <f>[1]FAO_2019_animal_trends!$G$36</f>
         <v>2.7950424483806726</v>
       </c>
       <c r="H3">
@@ -2891,7 +3015,7 @@
         <v>5.7351605247385563E-2</v>
       </c>
       <c r="D4">
-        <f>[38]FAO_2019_animal_trends!$F$39</f>
+        <f>[1]FAO_2019_animal_trends!$F$39</f>
         <v>4.9875311720698257E-2</v>
       </c>
       <c r="E4">
@@ -2903,7 +3027,7 @@
         <v>4.6666186084097429E-2</v>
       </c>
       <c r="G4">
-        <f>[38]FAO_2019_animal_trends!$G$40</f>
+        <f>[1]FAO_2019_animal_trends!$G$40</f>
         <v>1.354588821344141</v>
       </c>
       <c r="H4">
@@ -2924,7 +3048,7 @@
         <v>5.0951603562285619E-2</v>
       </c>
       <c r="D5">
-        <f>[38]FAO_2019_animal_trends!$F$38</f>
+        <f>[1]FAO_2019_animal_trends!$F$38</f>
         <v>4.9875311720698257E-2</v>
       </c>
       <c r="E5">
@@ -2936,7 +3060,7 @@
         <v>4.7418024088714393E-2</v>
       </c>
       <c r="G5">
-        <f>[38]FAO_2019_animal_trends!$G$38</f>
+        <f>[1]FAO_2019_animal_trends!$G$38</f>
         <v>1.0372340425531916</v>
       </c>
       <c r="H5">
@@ -2957,7 +3081,7 @@
         <v>4.3210694573642391E-2</v>
       </c>
       <c r="D6">
-        <f>[38]FAO_2019_animal_trends!$F$37</f>
+        <f>[1]FAO_2019_animal_trends!$F$37</f>
         <v>2.4937655860349127E-3</v>
       </c>
       <c r="E6">
@@ -2969,7 +3093,7 @@
         <v>-7.7485333020033496E-3</v>
       </c>
       <c r="G6">
-        <f>[38]FAO_2019_animal_trends!$G$37</f>
+        <f>[1]FAO_2019_animal_trends!$G$37</f>
         <v>86.466565349544069</v>
       </c>
       <c r="H6">
@@ -3019,6 +3143,7 @@
     <col min="5" max="5" width="16.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="28.42578125" customWidth="1"/>
     <col min="8" max="8" width="31.7109375" customWidth="1"/>
+    <col min="10" max="10" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -3047,15 +3172,15 @@
         <v>76</v>
       </c>
       <c r="B2" s="8">
-        <f>[39]Arid_Subsistence!$C$2/1000000*$H$18</f>
+        <f>[2]Arid_Subsistence!$C$2/1000000*$H$18</f>
         <v>0.26935849565485659</v>
       </c>
       <c r="C2" s="8">
-        <f>[40]SArid_Subsistence!$C$2/1000000*$H$18</f>
+        <f>[3]SArid_Subsistence!$C$2/1000000*$H$18</f>
         <v>0.57058834189660623</v>
       </c>
       <c r="D2" s="8">
-        <f>[41]Humid_Subsistence!$D$2/1000000*$H$18</f>
+        <f>[4]Humid_Subsistence!$D$2/1000000*$H$18</f>
         <v>0.71943074584927413</v>
       </c>
       <c r="E2" s="9">
@@ -3080,15 +3205,15 @@
         <v>77</v>
       </c>
       <c r="B3" s="8">
-        <f>[42]Arid_Commercial!$C$2/1000000*$H$18</f>
+        <f>[5]Arid_Commercial!$C$2/1000000*$H$18</f>
         <v>5.5884478914862177</v>
       </c>
       <c r="C3" s="8">
-        <f>[43]SArid_Commercial!$C$2/1000000*$H$18</f>
+        <f>[6]SArid_Commercial!$C$2/1000000*$H$18</f>
         <v>7.2365694102551341</v>
       </c>
       <c r="D3" s="8">
-        <f>[44]Humid_Commercial!$D$2/1000000*$H$18</f>
+        <f>[7]Humid_Commercial!$D$2/1000000*$H$18</f>
         <v>6.0610912034605047</v>
       </c>
       <c r="E3" s="9">
@@ -3110,15 +3235,15 @@
         <v>60</v>
       </c>
       <c r="B4" s="8">
-        <f>[45]Dairy_total_Arid_2020!$C$2/1000000*$H$18</f>
+        <f>[8]Dairy_total_Arid_2020!$C$2/1000000*$H$18</f>
         <v>3.0271361942572905E-2</v>
       </c>
       <c r="C4" s="8">
-        <f>[46]Dairy_total_SArid_2020!$C$2/1000000*$H$18</f>
+        <f>[9]Dairy_total_SArid_2020!$C$2/1000000*$H$18</f>
         <v>1.4765740788097195</v>
       </c>
       <c r="D4" s="8">
-        <f>[47]Dairy_total_Humid_2020!$D$2/1000000*$H$18</f>
+        <f>[10]Dairy_total_Humid_2020!$D$2/1000000*$H$18</f>
         <v>6.3853780054327789</v>
       </c>
       <c r="E4" s="9"/>
@@ -3128,15 +3253,15 @@
         <v>80</v>
       </c>
       <c r="B5" s="8">
-        <f>9.78*0.76*[48]Sheep_total_Arid_2020!$C$2/1000000*$H$18</f>
+        <f>9.78*0.76*[11]Sheep_total_Arid_2020!$C$2/1000000*$H$18</f>
         <v>11.794047385286973</v>
       </c>
       <c r="C5" s="8">
-        <f>9.78*0.76*[49]Sheep_total_SArid_2020!$C$2/1000000*$H$18</f>
+        <f>9.78*0.76*[12]Sheep_total_SArid_2020!$C$2/1000000*$H$18</f>
         <v>9.6481198260451801</v>
       </c>
       <c r="D5" s="8">
-        <f>9.78*0.76*[50]Sheep_total_Humid_2020!$D$2/1000000*$H$18</f>
+        <f>9.78*0.76*[13]Sheep_total_Humid_2020!$D$2/1000000*$H$18</f>
         <v>9.0810136627013929</v>
       </c>
       <c r="E5" s="9">
@@ -3622,7 +3747,7 @@
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>29</v>
       </c>
@@ -3643,14 +3768,14 @@
         <v>16.323211946847042</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="3"/>
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>60</v>
       </c>
@@ -3671,34 +3796,34 @@
         <v>7.8922234461850715</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="3"/>
       <c r="B36" s="9"/>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
       <c r="E36" s="9"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="3"/>
       <c r="B37" s="9"/>
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
       <c r="E37" s="9"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="3"/>
       <c r="B38" s="9"/>
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
       <c r="E38" s="9"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B39" s="9"/>
       <c r="C39" s="9"/>
       <c r="D39" s="9"/>
       <c r="E39" s="9"/>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>35</v>
       </c>
@@ -3707,7 +3832,7 @@
       <c r="D40" s="9"/>
       <c r="E40" s="9"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
         <v>31</v>
       </c>
@@ -3716,8 +3841,11 @@
       <c r="D41" s="9"/>
       <c r="E41" s="9"/>
       <c r="G41" s="3"/>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H41" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>21</v>
       </c>
@@ -3741,8 +3869,22 @@
         <f>E42/E$46</f>
         <v>0.81758574893750702</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H42" t="s">
+        <v>170</v>
+      </c>
+      <c r="I42">
+        <v>1.5</v>
+      </c>
+      <c r="J42" s="9">
+        <f>E43+E44</f>
+        <v>2.5080157193769619</v>
+      </c>
+      <c r="K42">
+        <f>ABS(J42-I42)/J42</f>
+        <v>0.4019176241955022</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>48</v>
       </c>
@@ -3766,8 +3908,23 @@
         <f>E43/E$46</f>
         <v>8.7817932870661461E-2</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H43" t="s">
+        <v>21</v>
+      </c>
+      <c r="I43">
+        <f>0.95*E48-I42</f>
+        <v>14.214192249999998</v>
+      </c>
+      <c r="J43" s="9">
+        <f>E42</f>
+        <v>13.477531829681107</v>
+      </c>
+      <c r="K43">
+        <f>ABS(J43-I43)/J43</f>
+        <v>5.4658407016080594E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>49</v>
       </c>
@@ -3792,7 +3949,7 @@
         <v>6.4325496370445448E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>32</v>
       </c>
@@ -3817,7 +3974,7 @@
         <v>3.0270821821386084E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>30</v>
       </c>
@@ -3838,7 +3995,7 @@
         <v>16.484548375746304</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="4"/>
       <c r="E48">
         <f>16.541255</f>
@@ -3916,7 +4073,7 @@
         <v>8.5595346951947899</v>
       </c>
       <c r="C2">
-        <f>[38]FAO_2019_animal_trends!$G$35/100</f>
+        <f>[1]FAO_2019_animal_trends!$G$35/100</f>
         <v>3.8312009613345605E-3</v>
       </c>
       <c r="D2">
@@ -3937,7 +4094,7 @@
         <v>5.5401815014894495</v>
       </c>
       <c r="C3">
-        <f>[38]FAO_2019_animal_trends!$G36/100</f>
+        <f>[1]FAO_2019_animal_trends!$G36/100</f>
         <v>2.7950424483806725E-2</v>
       </c>
       <c r="D3">
@@ -3958,7 +4115,7 @@
         <v>0.95304019787340877</v>
       </c>
       <c r="C4">
-        <f>[38]FAO_2019_animal_trends!$G39/100</f>
+        <f>[1]FAO_2019_animal_trends!$G39/100</f>
         <v>7.6101823708206687E-2</v>
       </c>
       <c r="D4">
@@ -3979,7 +4136,7 @@
         <v>0.84668818128995227</v>
       </c>
       <c r="C5">
-        <f>[38]FAO_2019_animal_trends!$G38/100</f>
+        <f>[1]FAO_2019_animal_trends!$G38/100</f>
         <v>1.0372340425531916E-2</v>
       </c>
       <c r="D5">
@@ -4000,7 +4157,7 @@
         <v>0.71805363998227201</v>
       </c>
       <c r="C6">
-        <f>[38]FAO_2019_animal_trends!$G37/100</f>
+        <f>[1]FAO_2019_animal_trends!$G37/100</f>
         <v>0.86466565349544067</v>
       </c>
       <c r="D6">
@@ -4021,7 +4178,7 @@
         <v>7.8922234461850715</v>
       </c>
       <c r="C7">
-        <f>[38]FAO_2019_animal_trends!$G39/100</f>
+        <f>[1]FAO_2019_animal_trends!$G39/100</f>
         <v>7.6101823708206687E-2</v>
       </c>
       <c r="D7">
@@ -4088,11 +4245,11 @@
         <v>13</v>
       </c>
       <c r="B3">
-        <f>[51]Pastoral_Zebu_2020!$K$2</f>
+        <f>[14]Pastoral_Zebu_2020!$K$2</f>
         <v>7912803.5780913802</v>
       </c>
       <c r="C3">
-        <f>[52]Pastoral_Boran_2020!$K$2</f>
+        <f>[15]Pastoral_Boran_2020!$K$2</f>
         <v>1124203.7226895699</v>
       </c>
       <c r="D3">
@@ -4104,11 +4261,11 @@
         <v>8.5595346951947899</v>
       </c>
       <c r="G3">
-        <f>[53]Pastoral_Zebu_2050!$K$2</f>
+        <f>[16]Pastoral_Zebu_2050!$K$2</f>
         <v>8554757.4814370908</v>
       </c>
       <c r="H3">
-        <f>[54]Pastoral_Boran_2050!$K$2</f>
+        <f>[17]Pastoral_Boran_2050!$K$2</f>
         <v>1215408.67359516</v>
       </c>
       <c r="I3">
@@ -4133,11 +4290,11 @@
         <v>16</v>
       </c>
       <c r="B4">
-        <f>[55]Agpastoral_Zebu_2020!$K$2</f>
+        <f>[18]Agpastoral_Zebu_2020!$K$2</f>
         <v>3685141.0110471202</v>
       </c>
       <c r="C4">
-        <f>[56]Agpastoral_Boran_2020!$K$2</f>
+        <f>[19]Agpastoral_Boran_2020!$K$2</f>
         <v>277376.20390618598</v>
       </c>
       <c r="D4">
@@ -4149,11 +4306,11 @@
         <v>5.5401815014894495</v>
       </c>
       <c r="G4">
-        <f>[57]Agpastoral_Zebu_2050!$K$2</f>
+        <f>[20]Agpastoral_Zebu_2050!$K$2</f>
         <v>6488770.1197828101</v>
       </c>
       <c r="H4">
-        <f>[58]Agpastoral_Boran_2050!$K$2</f>
+        <f>[21]Agpastoral_Boran_2050!$K$2</f>
         <v>488402.05019366002</v>
       </c>
       <c r="I4">
@@ -4178,11 +4335,11 @@
         <v>11</v>
       </c>
       <c r="B5">
-        <f>[59]Mixed_Zebu_2020!$K$2</f>
+        <f>[22]Mixed_Zebu_2020!$K$2</f>
         <v>298374.71550379699</v>
       </c>
       <c r="C5">
-        <f>[60]Mixed_Boran_2020!$K$2</f>
+        <f>[23]Mixed_Boran_2020!$K$2</f>
         <v>25945.627401560501</v>
       </c>
       <c r="D5">
@@ -4194,11 +4351,11 @@
         <v>0.95304019787340877</v>
       </c>
       <c r="G5">
-        <f>[61]Mixed_Zebu_2050!$K$2</f>
+        <f>[24]Mixed_Zebu_2050!$K$2</f>
         <v>404262.59496554697</v>
       </c>
       <c r="H5">
-        <f>[62]Mixed_Boran_2050!$K$2</f>
+        <f>[25]Mixed_Boran_2050!$K$2</f>
         <v>35153.269665965803</v>
       </c>
       <c r="I5">
@@ -4223,11 +4380,11 @@
         <v>42</v>
       </c>
       <c r="B6">
-        <f>[63]Cowcalf_Boran_2020!$K$2</f>
+        <f>[26]Cowcalf_Boran_2020!$K$2</f>
         <v>1184753.34766715</v>
       </c>
       <c r="C6">
-        <f>[64]Cowcalf_Exotic_2020!$K$2</f>
+        <f>[27]Cowcalf_Exotic_2020!$K$2</f>
         <v>985977.36353097099</v>
       </c>
       <c r="D6">
@@ -4239,11 +4396,11 @@
         <v>0.84668818128995227</v>
       </c>
       <c r="G6">
-        <f>[65]Cowcalf_Boran_2050!$K$2</f>
+        <f>[28]Cowcalf_Boran_2050!$K$2</f>
         <v>1806208.69891036</v>
       </c>
       <c r="H6">
-        <f>[66]Cowcalf_Exotic_2050!$K$2</f>
+        <f>[29]Cowcalf_Exotic_2050!$K$2</f>
         <v>1503165.94333724</v>
       </c>
       <c r="I6">
@@ -4268,11 +4425,11 @@
         <v>23</v>
       </c>
       <c r="B7">
-        <f>[67]Finisher_Boran_2020!$K$2</f>
+        <f>[30]Finisher_Boran_2020!$K$2</f>
         <v>26321.876059999999</v>
       </c>
       <c r="C7">
-        <f>[68]Finisher_Exotic_2020!$K$2</f>
+        <f>[31]Finisher_Exotic_2020!$K$2</f>
         <v>12386.7653238613</v>
       </c>
       <c r="D7">
@@ -4284,11 +4441,11 @@
         <v>0.71805363998227201</v>
       </c>
       <c r="G7">
-        <f>[69]Finisher_Boran_2050!$K$2</f>
+        <f>[32]Finisher_Boran_2050!$K$2</f>
         <v>918345.45531155204</v>
       </c>
       <c r="H7">
-        <f>[70]Finisher_Exotic_2050!$K$2</f>
+        <f>[33]Finisher_Exotic_2050!$K$2</f>
         <v>432162.57168335503</v>
       </c>
       <c r="I7">
@@ -4385,15 +4542,15 @@
         <v>86</v>
       </c>
       <c r="C2" s="12">
-        <f>[1]ZS_Grassland_Arid!$D$2*L15</f>
+        <f>[34]ZS_Grassland_Arid!$D$2*L15</f>
         <v>7105918.9949999992</v>
       </c>
       <c r="D2" s="12">
-        <f>[2]ZS_Grassland_SArid!$D$2*L15</f>
+        <f>[35]ZS_Grassland_SArid!$D$2*L15</f>
         <v>4556839.63</v>
       </c>
       <c r="E2" s="12">
-        <f>[3]ZS_Grassland_Humid!$E$2*L15</f>
+        <f>[36]ZS_Grassland_Humid!$E$2*L15</f>
         <v>2262153.4458035277</v>
       </c>
     </row>
@@ -4402,15 +4559,15 @@
         <v>87</v>
       </c>
       <c r="C3" s="12">
-        <f>[4]ZS_Cropland_Arid!$D$2*L15</f>
+        <f>[37]ZS_Cropland_Arid!$D$2*L15</f>
         <v>18395.019999999997</v>
       </c>
       <c r="D3" s="12">
-        <f>[5]ZS_Cropland_SArid!$D$2*L15</f>
+        <f>[38]ZS_Cropland_SArid!$D$2*L15</f>
         <v>686372.96</v>
       </c>
       <c r="E3" s="12">
-        <f>[6]ZS_Cropland_Humid!$E$2*L15</f>
+        <f>[39]ZS_Cropland_Humid!$E$2*L15</f>
         <v>950603.98551942373</v>
       </c>
     </row>
@@ -4419,15 +4576,15 @@
         <v>88</v>
       </c>
       <c r="C4" s="12">
-        <f>[7]ZS_Shrubland_Arid!$D$2*L15</f>
+        <f>[40]ZS_Shrubland_Arid!$D$2*L15</f>
         <v>9755293.3449999988</v>
       </c>
       <c r="D4" s="12">
-        <f>[8]ZS_Shrubland_SArid!$D$2*L15</f>
+        <f>[41]ZS_Shrubland_SArid!$D$2*L15</f>
         <v>12549721.555</v>
       </c>
       <c r="E4" s="12">
-        <f>[9]ZS_Shrubland_Humid!$E$2*L15</f>
+        <f>[42]ZS_Shrubland_Humid!$E$2*L15</f>
         <v>2223118.4370185882</v>
       </c>
     </row>
@@ -4449,15 +4606,15 @@
         <v>69</v>
       </c>
       <c r="C7" s="15">
-        <f>[10]NPP_2020_GRASS_Arid!$E$2</f>
+        <f>[43]NPP_2020_GRASS_Arid!$E$2</f>
         <v>0.33293323112310402</v>
       </c>
       <c r="D7" s="15">
-        <f>[11]NPP_2020_GRASS_SArid!$E$2</f>
+        <f>[44]NPP_2020_GRASS_SArid!$E$2</f>
         <v>0.48080803465972</v>
       </c>
       <c r="E7" s="14">
-        <f>[12]filtered!$F$2</f>
+        <f>[45]filtered!$F$2</f>
         <v>0.88607168377191448</v>
       </c>
     </row>
@@ -4466,15 +4623,15 @@
         <v>70</v>
       </c>
       <c r="C8" s="30">
-        <f>[13]NPP_2020_CROP_Arid!$E$2</f>
+        <f>[46]NPP_2020_CROP_Arid!$E$2</f>
         <v>0.97599038751874501</v>
       </c>
       <c r="D8" s="30">
-        <f>[14]NPP_2020_CROP_SArid!$E$2</f>
+        <f>[47]NPP_2020_CROP_SArid!$E$2</f>
         <v>0.71416468993051396</v>
       </c>
       <c r="E8" s="14">
-        <f>[15]filtered!$F$2</f>
+        <f>[48]filtered!$F$2</f>
         <v>1.0193612610195171</v>
       </c>
     </row>
@@ -4483,15 +4640,15 @@
         <v>71</v>
       </c>
       <c r="C9" s="15">
-        <f>[16]NPP_2020_SHRUB_Arid!$E$2</f>
+        <f>[49]NPP_2020_SHRUB_Arid!$E$2</f>
         <v>0.20100553202445001</v>
       </c>
       <c r="D9" s="15">
-        <f>[17]NPP_2020_SHRUB_SArid!$E$2</f>
+        <f>[50]NPP_2020_SHRUB_SArid!$E$2</f>
         <v>0.48842843619779902</v>
       </c>
       <c r="E9" s="14">
-        <f>[18]filtered!$F$2</f>
+        <f>[51]filtered!$F$2</f>
         <v>0.9284507277249876</v>
       </c>
       <c r="L9" s="11"/>
@@ -4510,15 +4667,15 @@
         <v>69</v>
       </c>
       <c r="C11" s="15">
-        <f>[19]NPP_2050_R4_GRASS_Arid!$E$2</f>
+        <f>[52]NPP_2050_R4_GRASS_Arid!$E$2</f>
         <v>0.36084903504638699</v>
       </c>
       <c r="D11" s="15">
-        <f>[20]NPP_2050_R4_GRASS_SArid!$E$2</f>
+        <f>[53]NPP_2050_R4_GRASS_SArid!$E$2</f>
         <v>0.51075241024303597</v>
       </c>
       <c r="E11" s="15">
-        <f>[21]filtered!$F$2</f>
+        <f>[54]filtered!$F$2</f>
         <v>0.90483097904137921</v>
       </c>
       <c r="F11">
@@ -4539,15 +4696,15 @@
         <v>70</v>
       </c>
       <c r="C12" s="15">
-        <f>[22]NPP_2050_R4_CROP_Arid!$E$2</f>
+        <f>[55]NPP_2050_R4_CROP_Arid!$E$2</f>
         <v>1.0384816436740301</v>
       </c>
       <c r="D12" s="15">
-        <f>[23]NPP_2050_R4_CROP_SArid!$E$2</f>
+        <f>[56]NPP_2050_R4_CROP_SArid!$E$2</f>
         <v>0.72447113600000002</v>
       </c>
       <c r="E12" s="15">
-        <f>[24]filtered!$F$2</f>
+        <f>[57]filtered!$F$2</f>
         <v>0.98649141647533578</v>
       </c>
       <c r="F12">
@@ -4568,15 +4725,15 @@
         <v>71</v>
       </c>
       <c r="C13" s="15">
-        <f>[25]NPP_2050_R4_SHRUB_Arid!$E$2</f>
+        <f>[58]NPP_2050_R4_SHRUB_Arid!$E$2</f>
         <v>0.21776707800273001</v>
       </c>
       <c r="D13" s="15">
-        <f>[26]NPP_2050_R4_SHRUB_SArid!$E$2</f>
+        <f>[59]NPP_2050_R4_SHRUB_SArid!$E$2</f>
         <v>0.51075241024303597</v>
       </c>
       <c r="E13" s="15">
-        <f>[27]filtered!$F$2</f>
+        <f>[60]filtered!$F$2</f>
         <v>0.90483097904137921</v>
       </c>
       <c r="F13">
@@ -4605,15 +4762,15 @@
         <v>69</v>
       </c>
       <c r="C15" s="15">
-        <f>[28]NPP_2050_R8_GRASS_Arid!$E$2</f>
+        <f>[61]NPP_2050_R8_GRASS_Arid!$E$2</f>
         <v>0.38422689204237098</v>
       </c>
       <c r="D15" s="15">
-        <f>[29]NPP_2050_R8_GRASS_SArid!$E$2</f>
+        <f>[62]NPP_2050_R8_GRASS_SArid!$E$2</f>
         <v>0.51337712420869996</v>
       </c>
       <c r="E15" s="15">
-        <f>[30]filtered!$F$2</f>
+        <f>[63]filtered!$F$2</f>
         <v>0.88457459938562355</v>
       </c>
       <c r="F15">
@@ -4641,15 +4798,15 @@
         <v>70</v>
       </c>
       <c r="C16" s="15">
-        <f>[31]NPP_2050_R8_CROP_Arid!$E$2</f>
+        <f>[64]NPP_2050_R8_CROP_Arid!$E$2</f>
         <v>1.10532849796393</v>
       </c>
       <c r="D16" s="15">
-        <f>[32]NPP_2050_R8_CROP_SArid!$E$2</f>
+        <f>[65]NPP_2050_R8_CROP_SArid!$E$2</f>
         <v>0.80695680840268103</v>
       </c>
       <c r="E16" s="15">
-        <f>[33]filtered!$F$2</f>
+        <f>[66]filtered!$F$2</f>
         <v>1.0242825546815273</v>
       </c>
       <c r="F16">
@@ -4677,15 +4834,15 @@
         <v>71</v>
       </c>
       <c r="C17" s="15">
-        <f>[34]NPP_2050_R8_SHRUB_Arid!$E$2</f>
+        <f>[67]NPP_2050_R8_SHRUB_Arid!$E$2</f>
         <v>0.231319877140652</v>
       </c>
       <c r="D17" s="15">
-        <f>[35]NPP_2050_R8_SHRUB_SArid!$E$2</f>
+        <f>[68]NPP_2050_R8_SHRUB_SArid!$E$2</f>
         <v>0.51046846997934603</v>
       </c>
       <c r="E17" s="15">
-        <f>[36]filtered!$F$2</f>
+        <f>[69]filtered!$F$2</f>
         <v>0.93416975929597834</v>
       </c>
       <c r="F17">
@@ -4709,16 +4866,16 @@
         <v>72</v>
       </c>
       <c r="C20" s="14">
-        <f>10000*(1/1000)*(C2*C7+C3*C8*[37]Raster_logic!$I$95+C4*C9*[37]Raster_logic!$I$96)*(1/[37]Raster_logic!$I$89)*[37]Raster_logic!$I$90*[37]Raster_logic!$I$91/1000000</f>
-        <v>10.13786820973019</v>
+        <f>10000*(1/1000)*(C2*C7+C3*C8*[70]Raster_logic!$I$95+C4*C9*[70]Raster_logic!$I$96)*(1/[70]Raster_logic!$I$89)*[70]Raster_logic!$I$90*[70]Raster_logic!$I$91/1000000</f>
+        <v>11.151655030703209</v>
       </c>
       <c r="D20" s="14">
-        <f>10000*(1/1000)*(D2*D7+D3*D8*[37]Raster_logic!$I$95+D4*D9*[37]Raster_logic!$I$96)*(1/[37]Raster_logic!$I$89)*[37]Raster_logic!$I$90*[37]Raster_logic!$I$91/1000000</f>
-        <v>15.448061930984727</v>
+        <f>10000*(1/1000)*(D2*D7+D3*D8*[70]Raster_logic!$I$95+D4*D9*[70]Raster_logic!$I$96)*(1/[70]Raster_logic!$I$89)*[70]Raster_logic!$I$90*[70]Raster_logic!$I$91/1000000</f>
+        <v>16.992868124083202</v>
       </c>
       <c r="E20" s="14">
-        <f>10000*(1/1000)*(E2*E7+E3*E8*[37]Raster_logic!$I$95+E4*E9*[37]Raster_logic!$I$96)*(1/[37]Raster_logic!$I$89)*[37]Raster_logic!$I$90*[37]Raster_logic!$I$91/1000000</f>
-        <v>10.148363796471815</v>
+        <f>10000*(1/1000)*(E2*E7+E3*E8*[70]Raster_logic!$I$95+E4*E9*[70]Raster_logic!$I$96)*(1/[70]Raster_logic!$I$89)*[70]Raster_logic!$I$90*[70]Raster_logic!$I$91/1000000</f>
+        <v>11.163200176118997</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -4726,16 +4883,16 @@
         <v>73</v>
       </c>
       <c r="C21" s="14">
-        <f>10000*(1/1000)*(C3*C8*[37]Raster_logic!$I$102)*(1/[37]Raster_logic!$I$98)*[37]Raster_logic!$I$99*[37]Raster_logic!$I$100/1000000</f>
-        <v>8.7971477221253785E-2</v>
+        <f>10000*(1/1000)*(C3*C8*[70]Raster_logic!$I$102)*(1/[70]Raster_logic!$I$98)*[70]Raster_logic!$I$99*[70]Raster_logic!$I$100/1000000</f>
+        <v>6.2836769443752702E-2</v>
       </c>
       <c r="D21" s="14">
-        <f>10000*(1/1000)*(D3*D8*[37]Raster_logic!$I$102)*(1/[37]Raster_logic!$I$98)*[37]Raster_logic!$I$99*[37]Raster_logic!$I$100/1000000</f>
-        <v>2.4018983275599357</v>
+        <f>10000*(1/1000)*(D3*D8*[70]Raster_logic!$I$102)*(1/[70]Raster_logic!$I$98)*[70]Raster_logic!$I$99*[70]Raster_logic!$I$100/1000000</f>
+        <v>1.7156416625428113</v>
       </c>
       <c r="E21" s="14">
-        <f>10000*(1/1000)*(E3*E8*[37]Raster_logic!$I$102)*(1/[37]Raster_logic!$I$98)*[37]Raster_logic!$I$99*[37]Raster_logic!$I$100/1000000</f>
-        <v>4.7481434993053666</v>
+        <f>10000*(1/1000)*(E3*E8*[70]Raster_logic!$I$102)*(1/[70]Raster_logic!$I$98)*[70]Raster_logic!$I$99*[70]Raster_logic!$I$100/1000000</f>
+        <v>3.3915310709324049</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -4744,15 +4901,15 @@
       </c>
       <c r="C22" s="14">
         <f>SUM(C20:C21)</f>
-        <v>10.225839686951444</v>
+        <v>11.214491800146961</v>
       </c>
       <c r="D22" s="14">
         <f>SUM(D20:D21)</f>
-        <v>17.849960258544662</v>
+        <v>18.708509786626013</v>
       </c>
       <c r="E22" s="14">
         <f>SUM(E20:E21)</f>
-        <v>14.89650729577718</v>
+        <v>14.554731247051402</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -4769,16 +4926,16 @@
         <v>BIOM GRASS Supply (MT/ha/yr)</v>
       </c>
       <c r="C24" s="14">
-        <f>10000*(1/1000)*(C2*C11+C3*C12*[37]Raster_logic!$I$95+C4*C13*[37]Raster_logic!$I$96)*(1/[37]Raster_logic!$I$89)*[37]Raster_logic!$I$90*[37]Raster_logic!$I$91/1000000</f>
-        <v>10.986362335397628</v>
+        <f>10000*(1/1000)*(C2*C11+C3*C12*[70]Raster_logic!$I$95+C4*C13*[70]Raster_logic!$I$96)*(1/[70]Raster_logic!$I$89)*[70]Raster_logic!$I$90*[70]Raster_logic!$I$91/1000000</f>
+        <v>12.08499856893739</v>
       </c>
       <c r="D24" s="14">
-        <f>10000*(1/1000)*(D2*D11+D3*D12*[37]Raster_logic!$I$95+D4*D13*[37]Raster_logic!$I$96)*(1/[37]Raster_logic!$I$89)*[37]Raster_logic!$I$90*[37]Raster_logic!$I$91/1000000</f>
-        <v>16.25401942195187</v>
+        <f>10000*(1/1000)*(D2*D11+D3*D12*[70]Raster_logic!$I$95+D4*D13*[70]Raster_logic!$I$96)*(1/[70]Raster_logic!$I$89)*[70]Raster_logic!$I$90*[70]Raster_logic!$I$91/1000000</f>
+        <v>17.87942136414706</v>
       </c>
       <c r="E24" s="14">
-        <f>10000*(1/1000)*(E2*E11+E3*E12*[37]Raster_logic!$I$95+E4*E13*[37]Raster_logic!$I$96)*(1/[37]Raster_logic!$I$89)*[37]Raster_logic!$I$90*[37]Raster_logic!$I$91/1000000</f>
-        <v>10.183081967683787</v>
+        <f>10000*(1/1000)*(E2*E11+E3*E12*[70]Raster_logic!$I$95+E4*E13*[70]Raster_logic!$I$96)*(1/[70]Raster_logic!$I$89)*[70]Raster_logic!$I$90*[70]Raster_logic!$I$91/1000000</f>
+        <v>11.201390164452167</v>
       </c>
       <c r="F24" s="13">
         <f>C24/C20</f>
@@ -4799,16 +4956,16 @@
         <v>BIOM CROP Supply (MT/ha/yr)</v>
       </c>
       <c r="C25" s="14">
-        <f>10000*(1/1000)*(C3*C12*[37]Raster_logic!$I$102)*(1/[37]Raster_logic!$I$98)*[37]Raster_logic!$I$99*[37]Raster_logic!$I$100/1000000</f>
-        <v>9.3604163964581585E-2</v>
+        <f>10000*(1/1000)*(C3*C12*[70]Raster_logic!$I$102)*(1/[70]Raster_logic!$I$98)*[70]Raster_logic!$I$99*[70]Raster_logic!$I$100/1000000</f>
+        <v>6.6860117117558279E-2</v>
       </c>
       <c r="D25" s="14">
-        <f>10000*(1/1000)*(D3*D12*[37]Raster_logic!$I$102)*(1/[37]Raster_logic!$I$98)*[37]Raster_logic!$I$99*[37]Raster_logic!$I$100/1000000</f>
-        <v>2.436561250449325</v>
+        <f>10000*(1/1000)*(D3*D12*[70]Raster_logic!$I$102)*(1/[70]Raster_logic!$I$98)*[70]Raster_logic!$I$99*[70]Raster_logic!$I$100/1000000</f>
+        <v>1.7404008931780892</v>
       </c>
       <c r="E25" s="14">
-        <f>10000*(1/1000)*(E3*E12*[37]Raster_logic!$I$102)*(1/[37]Raster_logic!$I$98)*[37]Raster_logic!$I$99*[37]Raster_logic!$I$100/1000000</f>
-        <v>4.5950370936925635</v>
+        <f>10000*(1/1000)*(E3*E12*[70]Raster_logic!$I$102)*(1/[70]Raster_logic!$I$98)*[70]Raster_logic!$I$99*[70]Raster_logic!$I$100/1000000</f>
+        <v>3.2821693526375455</v>
       </c>
       <c r="F25" s="13">
         <f t="shared" ref="F25:F26" si="6">C25/C21</f>
@@ -4816,7 +4973,7 @@
       </c>
       <c r="G25" s="13">
         <f t="shared" si="4"/>
-        <v>1.0144314696803187</v>
+        <v>1.0144314696803185</v>
       </c>
       <c r="H25" s="13">
         <f t="shared" si="4"/>
@@ -4830,27 +4987,27 @@
       </c>
       <c r="C26" s="14">
         <f>SUM(C24:C25)</f>
-        <v>11.079966499362209</v>
+        <v>12.151858686054949</v>
       </c>
       <c r="D26" s="14">
         <f t="shared" ref="D26:E26" si="7">SUM(D24:D25)</f>
-        <v>18.690580672401197</v>
+        <v>19.619822257325151</v>
       </c>
       <c r="E26" s="14">
         <f t="shared" si="7"/>
-        <v>14.778119061376351</v>
+        <v>14.483559517089713</v>
       </c>
       <c r="F26" s="13">
         <f t="shared" si="6"/>
-        <v>1.0835263253247225</v>
+        <v>1.0835853200138506</v>
       </c>
       <c r="G26" s="13">
         <f t="shared" si="4"/>
-        <v>1.0470936854581587</v>
+        <v>1.0487111202919326</v>
       </c>
       <c r="H26" s="13">
         <f t="shared" si="4"/>
-        <v>0.99205261796942235</v>
+        <v>0.99511006223655918</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -4867,28 +5024,28 @@
         <v>BIOM GRASS Supply (MT/ha/yr)</v>
       </c>
       <c r="C28" s="14">
-        <f>10000*(1/1000)*(C2*C15+C3*C16*[37]Raster_logic!$I$95+C4*C17*[37]Raster_logic!$I$96)*(1/[37]Raster_logic!$I$89)*[37]Raster_logic!$I$90*[37]Raster_logic!$I91/1000000</f>
-        <v>11.691151745837523</v>
+        <f>10000*(1/1000)*(C2*C15+C3*C16*[70]Raster_logic!$I$95+C4*C17*[70]Raster_logic!$I$96)*(1/[70]Raster_logic!$I$89)*[70]Raster_logic!$I$90*[70]Raster_logic!$I91/1000000</f>
+        <v>12.860266920421276</v>
       </c>
       <c r="D28" s="14">
-        <f>10000*(1/1000)*(D2*D15+D3*D16*[37]Raster_logic!$I$95+D4*D17*[37]Raster_logic!$I$96)*(1/[37]Raster_logic!$I$89)*[37]Raster_logic!$I$90*[37]Raster_logic!$I91/1000000</f>
-        <v>16.349687139782979</v>
+        <f>10000*(1/1000)*(D2*D15+D3*D16*[70]Raster_logic!$I$95+D4*D17*[70]Raster_logic!$I$96)*(1/[70]Raster_logic!$I$89)*[70]Raster_logic!$I$90*[70]Raster_logic!$I91/1000000</f>
+        <v>17.984655853761279</v>
       </c>
       <c r="E28" s="14">
-        <f>10000*(1/1000)*(E2*E15+E3*E16*[37]Raster_logic!$I$95+E4*E17*[37]Raster_logic!$I$96)*(1/[37]Raster_logic!$I$89)*[37]Raster_logic!$I$90*[37]Raster_logic!$I91/1000000</f>
-        <v>10.158929952078466</v>
+        <f>10000*(1/1000)*(E2*E15+E3*E16*[70]Raster_logic!$I$95+E4*E17*[70]Raster_logic!$I$96)*(1/[70]Raster_logic!$I$89)*[70]Raster_logic!$I$90*[70]Raster_logic!$I91/1000000</f>
+        <v>11.174822947286316</v>
       </c>
       <c r="F28" s="13">
         <f>C28/C20</f>
-        <v>1.1532159921566658</v>
+        <v>1.153215992156666</v>
       </c>
       <c r="G28" s="13">
         <f t="shared" ref="G28:H28" si="8">D28/D20</f>
-        <v>1.0583649400699147</v>
+        <v>1.0583649400699144</v>
       </c>
       <c r="H28" s="13">
         <f t="shared" si="8"/>
-        <v>1.0010411683911375</v>
+        <v>1.0010411683911378</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -4897,16 +5054,16 @@
         <v>BIOM CROP Supply (MT/ha/yr)</v>
       </c>
       <c r="C29" s="14">
-        <f>10000*(1/1000)*(C3*C16*[37]Raster_logic!$I$102)*(1/[37]Raster_logic!$I$98)*[37]Raster_logic!$I$99*[37]Raster_logic!$I$100/1000000</f>
-        <v>9.9629445150420576E-2</v>
+        <f>10000*(1/1000)*(C3*C16*[70]Raster_logic!$I$102)*(1/[70]Raster_logic!$I$98)*[70]Raster_logic!$I$99*[70]Raster_logic!$I$100/1000000</f>
+        <v>7.1163889393157556E-2</v>
       </c>
       <c r="D29" s="14">
-        <f>10000*(1/1000)*(D3*D16*[37]Raster_logic!$I$102)*(1/[37]Raster_logic!$I$98)*[37]Raster_logic!$I$99*[37]Raster_logic!$I$100/1000000</f>
-        <v>2.7139793325599548</v>
+        <f>10000*(1/1000)*(D3*D16*[70]Raster_logic!$I$102)*(1/[70]Raster_logic!$I$98)*[70]Raster_logic!$I$99*[70]Raster_logic!$I$100/1000000</f>
+        <v>1.9385566661142535</v>
       </c>
       <c r="E29" s="14">
-        <f>10000*(1/1000)*(E3*E16*[37]Raster_logic!$I$102)*(1/[37]Raster_logic!$I$98)*[37]Raster_logic!$I$99*[37]Raster_logic!$I$100/1000000</f>
-        <v>4.7710666860135564</v>
+        <f>10000*(1/1000)*(E3*E16*[70]Raster_logic!$I$102)*(1/[70]Raster_logic!$I$98)*[70]Raster_logic!$I$99*[70]Raster_logic!$I$100/1000000</f>
+        <v>3.4079047757239689</v>
       </c>
       <c r="F29" s="13">
         <f t="shared" ref="F29:F30" si="10">C29/C21</f>
@@ -4918,7 +5075,7 @@
       </c>
       <c r="H29" s="13">
         <f t="shared" ref="H29:H30" si="12">E29/E21</f>
-        <v>1.0048278209602435</v>
+        <v>1.0048278209602433</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -4928,27 +5085,27 @@
       </c>
       <c r="C30" s="14">
         <f>SUM(C28:C29)</f>
-        <v>11.790781190987943</v>
+        <v>12.931430809814433</v>
       </c>
       <c r="D30" s="14">
         <f>SUM(D28:D29)</f>
-        <v>19.063666472342934</v>
+        <v>19.923212519875531</v>
       </c>
       <c r="E30" s="14">
         <f t="shared" ref="E30" si="13">SUM(E28:E29)</f>
-        <v>14.929996638092023</v>
+        <v>14.582727723010285</v>
       </c>
       <c r="F30" s="13">
         <f t="shared" si="10"/>
-        <v>1.1530379462171134</v>
+        <v>1.1531000280944494</v>
       </c>
       <c r="G30" s="13">
         <f t="shared" si="11"/>
-        <v>1.0679948972557112</v>
+        <v>1.0649278187896003</v>
       </c>
       <c r="H30" s="13">
         <f t="shared" si="12"/>
-        <v>1.0022481338511031</v>
+        <v>1.0019235309456198</v>
       </c>
     </row>
   </sheetData>
@@ -4959,15 +5116,16 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7E0F49F-D7A7-4FDA-92DD-326744451984}">
-  <dimension ref="A1:I76"/>
+  <dimension ref="A1:K338"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.42578125" customWidth="1"/>
+    <col min="1" max="1" width="33.5703125" customWidth="1"/>
     <col min="2" max="2" width="27.5703125" customWidth="1"/>
     <col min="3" max="3" width="13.7109375" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
     <col min="5" max="5" width="16.5703125" customWidth="1"/>
-    <col min="6" max="7" width="11.28515625" customWidth="1"/>
+    <col min="6" max="6" width="11.28515625" customWidth="1"/>
+    <col min="7" max="7" width="16.42578125" customWidth="1"/>
     <col min="8" max="8" width="35.140625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4988,7 +5146,7 @@
       <c r="H1" t="s">
         <v>116</v>
       </c>
-      <c r="I1" s="40">
+      <c r="I1" s="35">
         <v>195.24959913167186</v>
       </c>
     </row>
@@ -5013,7 +5171,7 @@
       <c r="H2" t="s">
         <v>117</v>
       </c>
-      <c r="I2" s="40">
+      <c r="I2" s="35">
         <v>193.39196223478999</v>
       </c>
     </row>
@@ -5035,13 +5193,13 @@
       <c r="H3" t="s">
         <v>118</v>
       </c>
-      <c r="I3" s="40">
+      <c r="I3" s="35">
         <v>197.10723602855413</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>59</v>
+        <v>11</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -5291,11 +5449,11 @@
         <v>8.4857248864402823</v>
       </c>
       <c r="D18" s="25">
-        <f t="shared" ref="D17:D18" si="3">365*(D12+D$13+D$14)*(1-$I$7)*($I$9)/1000/1000000</f>
+        <f t="shared" ref="D18" si="3">365*(D12+D$13+D$14)*(1-$I$7)*($I$9)/1000/1000000</f>
         <v>14.104028387359014</v>
       </c>
       <c r="E18" s="25">
-        <f t="shared" ref="E17:E18" si="4">365*(E12+E$13+E$14)*(1-$I$8)*($I$9)/1000/1000000</f>
+        <f t="shared" ref="E18" si="4">365*(E12+E$13+E$14)*(1-$I$8)*($I$9)/1000/1000000</f>
         <v>15.178464553808732</v>
       </c>
     </row>
@@ -5308,15 +5466,15 @@
       </c>
       <c r="C20" s="19">
         <f>NPP!C22</f>
-        <v>10.225839686951444</v>
+        <v>11.214491800146961</v>
       </c>
       <c r="D20" s="19">
         <f>NPP!D22</f>
-        <v>17.849960258544662</v>
+        <v>18.708509786626013</v>
       </c>
       <c r="E20" s="19">
         <f>NPP!E22</f>
-        <v>14.89650729577718</v>
+        <v>14.554731247051402</v>
       </c>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.25">
@@ -5328,15 +5486,15 @@
       </c>
       <c r="C22" s="6">
         <f>C$20/C16</f>
-        <v>1.2133892936647717</v>
+        <v>1.3307018984028698</v>
       </c>
       <c r="D22" s="6">
         <f t="shared" ref="D22:E22" si="5">D$20/D16</f>
-        <v>1.2743698229233029</v>
+        <v>1.3356646154172063</v>
       </c>
       <c r="E22" s="6">
         <f t="shared" si="5"/>
-        <v>0.98466428638618053</v>
+        <v>0.96207277131218349</v>
       </c>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.25">
@@ -5345,15 +5503,15 @@
       </c>
       <c r="C23" s="6">
         <f t="shared" ref="C23:E24" si="6">C$20/C17</f>
-        <v>1.221830648333978</v>
+        <v>1.3399593780444432</v>
       </c>
       <c r="D23" s="6">
         <f t="shared" si="6"/>
-        <v>1.2832691815078834</v>
+        <v>1.3449920164176996</v>
       </c>
       <c r="E23" s="6">
         <f t="shared" si="6"/>
-        <v>0.98792618024499601</v>
+        <v>0.96525982633983576</v>
       </c>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.25">
@@ -5362,35 +5520,35 @@
       </c>
       <c r="C24" s="6">
         <f t="shared" si="6"/>
-        <v>1.2050637775556179</v>
+        <v>1.321571456796472</v>
       </c>
       <c r="D24" s="6">
         <f t="shared" si="6"/>
-        <v>1.2655930467739986</v>
+        <v>1.3264656928366543</v>
       </c>
       <c r="E24" s="6">
         <f t="shared" si="6"/>
-        <v>0.98142386161446082</v>
+        <v>0.95890669279846119</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B25" s="1"/>
     </row>
     <row r="26" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B26" s="35">
+      <c r="B26" s="43">
         <v>2050</v>
       </c>
-      <c r="C26" s="35"/>
-      <c r="D26" s="35"/>
-      <c r="E26" s="35"/>
+      <c r="C26" s="43"/>
+      <c r="D26" s="43"/>
+      <c r="E26" s="43"/>
     </row>
     <row r="27" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B27" s="36" t="s">
+      <c r="B27" s="44" t="s">
         <v>136</v>
       </c>
-      <c r="C27" s="36"/>
-      <c r="D27" s="36"/>
-      <c r="E27" s="36"/>
+      <c r="C27" s="44"/>
+      <c r="D27" s="44"/>
+      <c r="E27" s="44"/>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
@@ -5512,12 +5670,12 @@
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B36" s="39" t="s">
+      <c r="B36" s="47" t="s">
         <v>131</v>
       </c>
-      <c r="C36" s="39"/>
-      <c r="D36" s="39"/>
-      <c r="E36" s="39"/>
+      <c r="C36" s="47"/>
+      <c r="D36" s="47"/>
+      <c r="E36" s="47"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
@@ -5531,7 +5689,7 @@
         <v>2030584564.1338036</v>
       </c>
       <c r="D37">
-        <f t="shared" ref="D37:E37" si="7">SUM(D$28:D$32)*$I1*1000000</f>
+        <f t="shared" ref="D37" si="7">SUM(D$28:D$32)*$I1*1000000</f>
         <v>3513244915.5390234</v>
       </c>
       <c r="E37">
@@ -5578,11 +5736,11 @@
         <v>60</v>
       </c>
       <c r="C40">
-        <f t="shared" ref="C40:E41" si="8">C33*$I4*1000000</f>
+        <f>C33*$I4*1000000</f>
         <v>6084543.7504571546</v>
       </c>
       <c r="D40">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="D40:E41" si="8">D33*$I4*1000000</f>
         <v>305356065.49256176</v>
       </c>
       <c r="E40">
@@ -5595,7 +5753,7 @@
         <v>80</v>
       </c>
       <c r="C41">
-        <f t="shared" si="8"/>
+        <f>C34*$I5*1000000</f>
         <v>634851390.8996911</v>
       </c>
       <c r="D41">
@@ -5608,20 +5766,20 @@
       </c>
     </row>
     <row r="43" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B43" s="35" t="s">
+      <c r="B43" s="43" t="s">
         <v>137</v>
       </c>
-      <c r="C43" s="35"/>
-      <c r="D43" s="35"/>
-      <c r="E43" s="35"/>
+      <c r="C43" s="43"/>
+      <c r="D43" s="43"/>
+      <c r="E43" s="43"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B44" s="38" t="s">
+      <c r="B44" s="46" t="s">
         <v>64</v>
       </c>
-      <c r="C44" s="38"/>
-      <c r="D44" s="38"/>
-      <c r="E44" s="38"/>
+      <c r="C44" s="46"/>
+      <c r="D44" s="46"/>
+      <c r="E44" s="46"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
@@ -5650,7 +5808,7 @@
         <v>18.199404512605764</v>
       </c>
       <c r="D46" s="26">
-        <f t="shared" ref="D46:D47" si="10">365*(D38+D$40+D$41)*(1-$I$7)*($I$9)/1000/1000000</f>
+        <f t="shared" ref="D46" si="10">365*(D38+D$40+D$41)*(1-$I$7)*($I$9)/1000/1000000</f>
         <v>28.397857182082856</v>
       </c>
       <c r="E46" s="26">
@@ -5686,27 +5844,27 @@
       </c>
       <c r="C49" s="27">
         <f>NPP!C26</f>
-        <v>11.079966499362209</v>
+        <v>12.151858686054949</v>
       </c>
       <c r="D49" s="27">
         <f>NPP!D26</f>
-        <v>18.690580672401197</v>
+        <v>19.619822257325151</v>
       </c>
       <c r="E49" s="27">
         <f>NPP!E26</f>
-        <v>14.778119061376351</v>
+        <v>14.483559517089713</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B50" s="1"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B51" s="37" t="s">
+      <c r="B51" s="45" t="s">
         <v>79</v>
       </c>
-      <c r="C51" s="37"/>
-      <c r="D51" s="37"/>
-      <c r="E51" s="37"/>
+      <c r="C51" s="45"/>
+      <c r="D51" s="45"/>
+      <c r="E51" s="45"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
@@ -5718,15 +5876,15 @@
       </c>
       <c r="C52" s="21">
         <f>C$49/C45</f>
-        <v>0.6044066341821932</v>
+        <v>0.66287781717741645</v>
       </c>
       <c r="D52" s="21">
         <f>D$49/D45</f>
-        <v>0.65302056956980825</v>
+        <v>0.68548686260216019</v>
       </c>
       <c r="E52" s="21">
         <f>E$49/E45</f>
-        <v>0.54948671039733743</v>
+        <v>0.53853426412633476</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -5736,15 +5894,15 @@
       </c>
       <c r="C53" s="21">
         <f t="shared" ref="C53:E53" si="13">C$49/C46</f>
-        <v>0.60880928778124044</v>
+        <v>0.66770638993369258</v>
       </c>
       <c r="D53" s="21">
         <f t="shared" si="13"/>
-        <v>0.65816869746755757</v>
+        <v>0.69089094052152444</v>
       </c>
       <c r="E53" s="21">
         <f t="shared" si="13"/>
-        <v>0.55267173201474684</v>
+        <v>0.54165580144562275</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -5754,15 +5912,15 @@
       </c>
       <c r="C54" s="21">
         <f t="shared" ref="C54:E54" si="14">C$49/C47</f>
-        <v>0.60006719970007738</v>
+        <v>0.65811857944803331</v>
       </c>
       <c r="D54" s="21">
         <f t="shared" si="14"/>
-        <v>0.64795235286935648</v>
+        <v>0.68016666883357912</v>
       </c>
       <c r="E54" s="21">
         <f t="shared" si="14"/>
-        <v>0.54633818869699058</v>
+        <v>0.53544849920263726</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
@@ -5781,15 +5939,15 @@
       </c>
       <c r="C56" s="21">
         <f>(C52+C$22)/2</f>
-        <v>0.90889796392348243</v>
+        <v>0.99678985779014306</v>
       </c>
       <c r="D56" s="21">
         <f t="shared" ref="D56:E56" si="15">(D52+D$22)/2</f>
-        <v>0.96369519624655564</v>
+        <v>1.0105757390096832</v>
       </c>
       <c r="E56" s="21">
         <f t="shared" si="15"/>
-        <v>0.76707549839175893</v>
+        <v>0.75030351771925918</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -5800,15 +5958,15 @@
       </c>
       <c r="C57" s="21">
         <f t="shared" ref="C57:E57" si="16">(C53+C$22)/2</f>
-        <v>0.91109929072300599</v>
+        <v>0.99920414416828118</v>
       </c>
       <c r="D57" s="21">
         <f t="shared" si="16"/>
-        <v>0.96626926019543025</v>
+        <v>1.0132777779693654</v>
       </c>
       <c r="E57" s="21">
         <f t="shared" si="16"/>
-        <v>0.76866800920046363</v>
+        <v>0.75186428637890312</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -5819,15 +5977,15 @@
       </c>
       <c r="C58" s="21">
         <f t="shared" ref="C58:E58" si="17">(C54+C$22)/2</f>
-        <v>0.90672824668242447</v>
+        <v>0.99441023892545155</v>
       </c>
       <c r="D58" s="21">
         <f t="shared" si="17"/>
-        <v>0.9611610878963297</v>
+        <v>1.0079156421253928</v>
       </c>
       <c r="E58" s="21">
         <f t="shared" si="17"/>
-        <v>0.7655012375415855</v>
+        <v>0.74876063525741032</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
@@ -5843,20 +6001,20 @@
       <c r="E60" s="3"/>
     </row>
     <row r="61" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B61" s="35" t="s">
+      <c r="B61" s="43" t="s">
         <v>138</v>
       </c>
-      <c r="C61" s="35"/>
-      <c r="D61" s="35"/>
-      <c r="E61" s="35"/>
+      <c r="C61" s="43"/>
+      <c r="D61" s="43"/>
+      <c r="E61" s="43"/>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B62" s="38" t="s">
+      <c r="B62" s="46" t="s">
         <v>64</v>
       </c>
-      <c r="C62" s="38"/>
-      <c r="D62" s="38"/>
-      <c r="E62" s="38"/>
+      <c r="C62" s="46"/>
+      <c r="D62" s="46"/>
+      <c r="E62" s="46"/>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B63" s="28" t="str">
@@ -5894,7 +6052,7 @@
         <v>26.739415470921948</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B65" s="28" t="str">
         <f t="shared" si="19"/>
         <v>BC</v>
@@ -5912,44 +6070,44 @@
         <v>27.049397913446196</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
       <c r="D66" s="3"/>
       <c r="E66" s="3"/>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B67" s="22" t="s">
         <v>75</v>
       </c>
       <c r="C67" s="23">
         <f>NPP!C30</f>
-        <v>11.790781190987943</v>
+        <v>12.931430809814433</v>
       </c>
       <c r="D67" s="23">
         <f>NPP!D30</f>
-        <v>19.063666472342934</v>
+        <v>19.923212519875531</v>
       </c>
       <c r="E67" s="23">
         <f>NPP!E30</f>
-        <v>14.929996638092023</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+        <v>14.582727723010285</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B68" s="3"/>
       <c r="C68" s="3"/>
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B69" s="37" t="s">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B69" s="45" t="s">
         <v>79</v>
       </c>
-      <c r="C69" s="37"/>
-      <c r="D69" s="37"/>
-      <c r="E69" s="37"/>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C69" s="45"/>
+      <c r="D69" s="45"/>
+      <c r="E69" s="45"/>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="33">
         <v>2050</v>
       </c>
@@ -5959,18 +6117,18 @@
       </c>
       <c r="C70" s="21">
         <f>C$67/C63</f>
-        <v>0.64318122030729508</v>
+        <v>0.70540308685678377</v>
       </c>
       <c r="D70" s="21">
         <f>D$67/D63</f>
-        <v>0.66605562213701464</v>
+        <v>0.6960868586924438</v>
       </c>
       <c r="E70" s="21">
         <f>E$67/E63</f>
-        <v>0.555133891183066</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.5422215812348915</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="33"/>
       <c r="B71" s="32" t="str">
         <f>B53</f>
@@ -5978,18 +6136,18 @@
       </c>
       <c r="C71" s="21">
         <f>C$67/C64</f>
-        <v>0.64786631797876093</v>
+        <v>0.71054142463054304</v>
       </c>
       <c r="D71" s="21">
         <f t="shared" ref="D71:E72" si="20">D$67/D64</f>
-        <v>0.67130651267486585</v>
+        <v>0.70157450233413188</v>
       </c>
       <c r="E71" s="21">
         <f t="shared" si="20"/>
-        <v>0.5583516458812573</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.54536449156371503</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="33"/>
       <c r="B72" s="32" t="str">
         <f>B54</f>
@@ -5997,25 +6155,25 @@
       </c>
       <c r="C72" s="21">
         <f>C$67/C65</f>
-        <v>0.6385633974579028</v>
+        <v>0.70033853212528396</v>
       </c>
       <c r="D72" s="21">
         <f t="shared" si="20"/>
-        <v>0.66088623791720591</v>
+        <v>0.69068439634043222</v>
       </c>
       <c r="E72" s="21">
         <f t="shared" si="20"/>
-        <v>0.55195301151861698</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.53911468823345765</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="33"/>
       <c r="B73" s="16"/>
       <c r="C73" s="34"/>
       <c r="D73" s="34"/>
       <c r="E73" s="34"/>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="33" t="s">
         <v>85</v>
       </c>
@@ -6025,18 +6183,18 @@
       </c>
       <c r="C74" s="21">
         <f>(C$22+C70)*0.5</f>
-        <v>0.92828525698603337</v>
+        <v>1.0180524926298267</v>
       </c>
       <c r="D74" s="21">
         <f>(D$22+D70)*0.5</f>
-        <v>0.97021272253015878</v>
+        <v>1.015875737054825</v>
       </c>
       <c r="E74" s="21">
         <f t="shared" ref="E74" si="21">(E$22+E70)*0.5</f>
-        <v>0.76989908878462332</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.75214717627353744</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="16"/>
       <c r="B75" s="32" t="str">
         <f t="shared" ref="B75:B76" si="22">B57</f>
@@ -6044,18 +6202,18 @@
       </c>
       <c r="C75" s="21">
         <f t="shared" ref="C75" si="23">(C$22+C71)*0.5</f>
-        <v>0.9306278058217663</v>
+        <v>1.0206216615167065</v>
       </c>
       <c r="D75" s="21">
         <f>(D$22+D71)*0.5</f>
-        <v>0.97283816779908439</v>
+        <v>1.018619558875669</v>
       </c>
       <c r="E75" s="21">
         <f>(E$22+E71)*0.5</f>
-        <v>0.77150796613371897</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.75371863143794926</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="16"/>
       <c r="B76" s="32" t="str">
         <f t="shared" si="22"/>
@@ -6063,19 +6221,5135 @@
       </c>
       <c r="C76" s="21">
         <f t="shared" ref="C76:E76" si="24">(C$22+C72)*0.5</f>
-        <v>0.92597634556133723</v>
+        <v>1.0155202152640768</v>
       </c>
       <c r="D76" s="21">
         <f t="shared" si="24"/>
-        <v>0.96762803042025447</v>
+        <v>1.0131745058788193</v>
       </c>
       <c r="E76" s="21">
         <f t="shared" si="24"/>
-        <v>0.7683086489523987</v>
+        <v>0.75059372977282057</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B78" s="43" t="s">
+        <v>139</v>
+      </c>
+      <c r="C78" s="43"/>
+      <c r="D78" s="43"/>
+      <c r="E78" s="43"/>
+      <c r="H78" s="45" t="s">
+        <v>140</v>
+      </c>
+      <c r="I78" s="45"/>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H79" s="39" t="s">
+        <v>141</v>
+      </c>
+      <c r="I79">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B80" s="42" t="s">
+        <v>163</v>
+      </c>
+      <c r="C80" s="42"/>
+      <c r="D80" s="42"/>
+      <c r="E80" s="42"/>
+      <c r="H80" s="39" t="s">
+        <v>144</v>
+      </c>
+      <c r="I80">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B81" t="s">
+        <v>13</v>
+      </c>
+      <c r="C81">
+        <f>(C2)*30*Validate_2020!$G2/100</f>
+        <v>0.49402322991933489</v>
+      </c>
+      <c r="D81">
+        <f>(D2)*30*Validate_2020!$G2/100</f>
+        <v>0.48640304349731928</v>
+      </c>
+      <c r="E81">
+        <f>(E2)*30*Validate_2020!$G2/100</f>
+        <v>0</v>
+      </c>
+      <c r="H81" s="39" t="s">
+        <v>143</v>
+      </c>
+      <c r="I81">
+        <f>I79</f>
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B82" t="s">
+        <v>16</v>
+      </c>
+      <c r="C82">
+        <f>(C3)*30*Validate_2020!$G3/100</f>
+        <v>0</v>
+      </c>
+      <c r="D82">
+        <f>(D3)*30*Validate_2020!$G3/100</f>
+        <v>2.5194151670693041</v>
+      </c>
+      <c r="E82">
+        <f>(E3)*30*Validate_2020!$G3/100</f>
+        <v>2.1101718564805916</v>
+      </c>
+      <c r="H82" s="39" t="s">
+        <v>145</v>
+      </c>
+      <c r="I82">
+        <f t="shared" ref="I82:I96" si="25">I80</f>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B83" t="str">
+        <f>B4</f>
+        <v>Mixed</v>
+      </c>
+      <c r="C83">
+        <f>(C4)*30*Validate_2020!$G4/100</f>
+        <v>0</v>
+      </c>
+      <c r="D83">
+        <f>(D4)*30*Validate_2020!$G4/100</f>
+        <v>0</v>
+      </c>
+      <c r="E83">
+        <f>(E4)*30*Validate_2020!$G4/100</f>
+        <v>0.38596556316357417</v>
+      </c>
+      <c r="H83" s="39" t="s">
+        <v>146</v>
+      </c>
+      <c r="I83">
+        <f t="shared" si="25"/>
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B84" t="s">
+        <v>22</v>
+      </c>
+      <c r="C84">
+        <f>(C5)*30*Validate_2020!$G5/100</f>
+        <v>2.0019220309243413E-2</v>
+      </c>
+      <c r="D84">
+        <f>(D5)*30*Validate_2020!$G5/100</f>
+        <v>9.2522672890536062E-2</v>
+      </c>
+      <c r="E84">
+        <f>(E5)*30*Validate_2020!$G5/100</f>
+        <v>0.15001904223920623</v>
+      </c>
+      <c r="H84" s="39" t="s">
+        <v>147</v>
+      </c>
+      <c r="I84">
+        <f t="shared" si="25"/>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B85" t="s">
+        <v>23</v>
+      </c>
+      <c r="C85">
+        <f>(C6)*30*Validate_2020!$G6/100</f>
+        <v>5.3182961871764585</v>
+      </c>
+      <c r="D85">
+        <f>(D6)*30*Validate_2020!$G6/100</f>
+        <v>7.088110217691594</v>
+      </c>
+      <c r="E85">
+        <f>(E6)*30*Validate_2020!$G6/100</f>
+        <v>6.1560286644571258</v>
+      </c>
+      <c r="H85" s="39" t="s">
+        <v>148</v>
+      </c>
+      <c r="I85">
+        <f t="shared" si="25"/>
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B86" t="s">
+        <v>60</v>
+      </c>
+      <c r="C86">
+        <f t="shared" ref="C86:E87" si="26">AVERAGE(C7)</f>
+        <v>3.0271361942572905E-2</v>
+      </c>
+      <c r="D86">
+        <f t="shared" si="26"/>
+        <v>1.4765740788097195</v>
+      </c>
+      <c r="E86">
+        <f t="shared" si="26"/>
+        <v>6.3853780054327789</v>
+      </c>
+      <c r="H86" s="39" t="s">
+        <v>149</v>
+      </c>
+      <c r="I86">
+        <f t="shared" si="25"/>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B87" t="s">
+        <v>80</v>
+      </c>
+      <c r="C87">
+        <f t="shared" si="26"/>
+        <v>11.794047385286973</v>
+      </c>
+      <c r="D87">
+        <f t="shared" si="26"/>
+        <v>9.6481198260451801</v>
+      </c>
+      <c r="E87">
+        <f t="shared" si="26"/>
+        <v>9.0810136627013929</v>
+      </c>
+      <c r="H87" s="37" t="s">
+        <v>150</v>
+      </c>
+      <c r="I87">
+        <f t="shared" si="25"/>
+        <v>1.3</v>
+      </c>
+      <c r="J87" s="38"/>
+      <c r="K87" s="38"/>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H88" s="37" t="s">
+        <v>151</v>
+      </c>
+      <c r="I88">
+        <f t="shared" si="25"/>
+        <v>0.8</v>
+      </c>
+      <c r="J88" s="4"/>
+      <c r="K88" s="4"/>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A89" s="36" t="str">
+        <f>H79</f>
+        <v>+20% Herd size</v>
+      </c>
+      <c r="B89" s="42" t="s">
+        <v>142</v>
+      </c>
+      <c r="C89" s="42"/>
+      <c r="D89" s="42"/>
+      <c r="E89" s="42"/>
+      <c r="H89" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="I89">
+        <f t="shared" si="25"/>
+        <v>1.3</v>
+      </c>
+      <c r="J89" s="4"/>
+      <c r="K89" s="4"/>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B90" t="str">
+        <f>B81</f>
+        <v>Pastoral</v>
+      </c>
+      <c r="C90" s="40">
+        <f>C81*$I$79</f>
+        <v>0.64223019889513533</v>
+      </c>
+      <c r="D90" s="40">
+        <f t="shared" ref="D90:E90" si="27">D81*$I$79</f>
+        <v>0.63232395654651508</v>
+      </c>
+      <c r="E90" s="40">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="H90" s="37" t="s">
+        <v>153</v>
+      </c>
+      <c r="I90">
+        <f t="shared" si="25"/>
+        <v>0.8</v>
+      </c>
+      <c r="J90" s="4"/>
+      <c r="K90" s="4"/>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B91" t="str">
+        <f t="shared" ref="B91:B96" si="28">B82</f>
+        <v>Agropastoral</v>
+      </c>
+      <c r="C91" s="40">
+        <f t="shared" ref="C91:E91" si="29">C82*$I$79</f>
+        <v>0</v>
+      </c>
+      <c r="D91" s="40">
+        <f t="shared" si="29"/>
+        <v>3.2752397171900953</v>
+      </c>
+      <c r="E91" s="40">
+        <f t="shared" si="29"/>
+        <v>2.7432234134247691</v>
+      </c>
+      <c r="H91" s="37" t="s">
+        <v>154</v>
+      </c>
+      <c r="I91">
+        <f t="shared" si="25"/>
+        <v>1.3</v>
+      </c>
+      <c r="J91" s="4"/>
+      <c r="K91" s="4"/>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B92" t="str">
+        <f t="shared" si="28"/>
+        <v>Mixed</v>
+      </c>
+      <c r="C92" s="40">
+        <f t="shared" ref="C92:E92" si="30">C83*$I$79</f>
+        <v>0</v>
+      </c>
+      <c r="D92" s="40">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="E92" s="40">
+        <f t="shared" si="30"/>
+        <v>0.50175523211264639</v>
+      </c>
+      <c r="H92" s="37" t="s">
+        <v>155</v>
+      </c>
+      <c r="I92">
+        <f t="shared" si="25"/>
+        <v>0.8</v>
+      </c>
+      <c r="J92" s="4"/>
+      <c r="K92" s="4"/>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B93" t="str">
+        <f t="shared" si="28"/>
+        <v>Cowcalf</v>
+      </c>
+      <c r="C93" s="40">
+        <f t="shared" ref="C93:E93" si="31">C84*$I$79</f>
+        <v>2.6024986402016437E-2</v>
+      </c>
+      <c r="D93" s="40">
+        <f t="shared" si="31"/>
+        <v>0.12027947475769689</v>
+      </c>
+      <c r="E93" s="40">
+        <f t="shared" si="31"/>
+        <v>0.1950247549109681</v>
+      </c>
+      <c r="H93" s="37" t="s">
+        <v>156</v>
+      </c>
+      <c r="I93">
+        <f t="shared" si="25"/>
+        <v>1.3</v>
+      </c>
+      <c r="J93" s="4"/>
+      <c r="K93" s="4"/>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B94" t="str">
+        <f t="shared" si="28"/>
+        <v>Finisher</v>
+      </c>
+      <c r="C94" s="40">
+        <f t="shared" ref="C94:E94" si="32">C85*$I$79</f>
+        <v>6.9137850433293959</v>
+      </c>
+      <c r="D94" s="40">
+        <f t="shared" si="32"/>
+        <v>9.2145432829990721</v>
+      </c>
+      <c r="E94" s="40">
+        <f t="shared" si="32"/>
+        <v>8.0028372637942642</v>
+      </c>
+      <c r="H94" s="37" t="s">
+        <v>157</v>
+      </c>
+      <c r="I94">
+        <f t="shared" si="25"/>
+        <v>0.8</v>
+      </c>
+      <c r="J94" s="4"/>
+      <c r="K94" s="4"/>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B95" t="str">
+        <f t="shared" si="28"/>
+        <v>Dairy</v>
+      </c>
+      <c r="C95">
+        <f t="shared" ref="C95:E96" si="33">C86</f>
+        <v>3.0271361942572905E-2</v>
+      </c>
+      <c r="D95">
+        <f t="shared" si="33"/>
+        <v>1.4765740788097195</v>
+      </c>
+      <c r="E95">
+        <f t="shared" si="33"/>
+        <v>6.3853780054327789</v>
+      </c>
+      <c r="H95" s="37" t="s">
+        <v>158</v>
+      </c>
+      <c r="I95">
+        <f t="shared" si="25"/>
+        <v>1.3</v>
+      </c>
+      <c r="J95" s="4"/>
+      <c r="K95" s="4"/>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B96" t="str">
+        <f t="shared" si="28"/>
+        <v>Sheep</v>
+      </c>
+      <c r="C96">
+        <f t="shared" si="33"/>
+        <v>11.794047385286973</v>
+      </c>
+      <c r="D96">
+        <f t="shared" si="33"/>
+        <v>9.6481198260451801</v>
+      </c>
+      <c r="E96">
+        <f t="shared" si="33"/>
+        <v>9.0810136627013929</v>
+      </c>
+      <c r="H96" s="37" t="s">
+        <v>159</v>
+      </c>
+      <c r="I96">
+        <f t="shared" si="25"/>
+        <v>0.8</v>
+      </c>
+      <c r="J96" s="4"/>
+      <c r="K96" s="4"/>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H97" s="4"/>
+      <c r="I97" s="4"/>
+      <c r="J97" s="4"/>
+      <c r="K97" s="4"/>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A98" t="str">
+        <f>H80</f>
+        <v xml:space="preserve">-20% Herd size </v>
+      </c>
+      <c r="B98" s="42" t="str">
+        <f>B89</f>
+        <v>Animal populations (M hd) -- SA scenario specific</v>
+      </c>
+      <c r="C98" s="42"/>
+      <c r="D98" s="42"/>
+      <c r="E98" s="42"/>
+      <c r="H98" s="4"/>
+      <c r="I98" s="4"/>
+      <c r="J98" s="4"/>
+      <c r="K98" s="4"/>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B99" t="str">
+        <f>B90</f>
+        <v>Pastoral</v>
+      </c>
+      <c r="C99" s="6">
+        <f>C81*$I$80</f>
+        <v>0.39521858393546794</v>
+      </c>
+      <c r="D99" s="6">
+        <f t="shared" ref="D99:E99" si="34">D81*$I$80</f>
+        <v>0.38912243479785547</v>
+      </c>
+      <c r="E99" s="6">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="H99" s="4"/>
+      <c r="I99" s="4"/>
+      <c r="J99" s="4"/>
+      <c r="K99" s="4"/>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B100" t="str">
+        <f t="shared" ref="B100:B105" si="35">B91</f>
+        <v>Agropastoral</v>
+      </c>
+      <c r="C100" s="6">
+        <f t="shared" ref="C100:E100" si="36">C82*$I$80</f>
+        <v>0</v>
+      </c>
+      <c r="D100" s="6">
+        <f t="shared" si="36"/>
+        <v>2.0155321336554435</v>
+      </c>
+      <c r="E100" s="6">
+        <f t="shared" si="36"/>
+        <v>1.6881374851844733</v>
+      </c>
+      <c r="H100" s="4"/>
+      <c r="I100" s="4"/>
+      <c r="J100" s="4"/>
+      <c r="K100" s="4"/>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B101" t="str">
+        <f t="shared" si="35"/>
+        <v>Mixed</v>
+      </c>
+      <c r="C101" s="6">
+        <f t="shared" ref="C101:E101" si="37">C83*$I$80</f>
+        <v>0</v>
+      </c>
+      <c r="D101" s="6">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="E101" s="6">
+        <f t="shared" si="37"/>
+        <v>0.30877245053085933</v>
+      </c>
+      <c r="H101" s="4"/>
+      <c r="I101" s="4"/>
+      <c r="J101" s="4"/>
+      <c r="K101" s="4"/>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B102" t="str">
+        <f t="shared" si="35"/>
+        <v>Cowcalf</v>
+      </c>
+      <c r="C102" s="6">
+        <f t="shared" ref="C102:E102" si="38">C84*$I$80</f>
+        <v>1.6015376247394731E-2</v>
+      </c>
+      <c r="D102" s="6">
+        <f t="shared" si="38"/>
+        <v>7.4018138312428858E-2</v>
+      </c>
+      <c r="E102" s="6">
+        <f t="shared" si="38"/>
+        <v>0.12001523379136499</v>
+      </c>
+      <c r="H102" s="4"/>
+      <c r="I102" s="4"/>
+      <c r="J102" s="4"/>
+      <c r="K102" s="4"/>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B103" t="str">
+        <f t="shared" si="35"/>
+        <v>Finisher</v>
+      </c>
+      <c r="C103" s="6">
+        <f t="shared" ref="C103:E103" si="39">C85*$I$80</f>
+        <v>4.2546369497411671</v>
+      </c>
+      <c r="D103" s="6">
+        <f t="shared" si="39"/>
+        <v>5.6704881741532756</v>
+      </c>
+      <c r="E103" s="6">
+        <f t="shared" si="39"/>
+        <v>4.9248229315657008</v>
+      </c>
+      <c r="H103" s="4"/>
+      <c r="I103" s="4"/>
+      <c r="J103" s="4"/>
+      <c r="K103" s="4"/>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B104" t="str">
+        <f t="shared" si="35"/>
+        <v>Dairy</v>
+      </c>
+      <c r="C104">
+        <f t="shared" ref="C104:E104" si="40">C86*$I$80</f>
+        <v>2.4217089554058324E-2</v>
+      </c>
+      <c r="D104">
+        <f t="shared" si="40"/>
+        <v>1.1812592630477756</v>
+      </c>
+      <c r="E104">
+        <f t="shared" si="40"/>
+        <v>5.1083024043462233</v>
+      </c>
+      <c r="H104" s="4"/>
+      <c r="I104" s="4"/>
+      <c r="J104" s="4"/>
+      <c r="K104" s="4"/>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B105" t="str">
+        <f t="shared" si="35"/>
+        <v>Sheep</v>
+      </c>
+      <c r="C105">
+        <f t="shared" ref="C105:E105" si="41">C87*$I$80</f>
+        <v>9.4352379082295794</v>
+      </c>
+      <c r="D105">
+        <f t="shared" si="41"/>
+        <v>7.7184958608361445</v>
+      </c>
+      <c r="E105">
+        <f t="shared" si="41"/>
+        <v>7.264810930161115</v>
+      </c>
+      <c r="H105" s="4"/>
+      <c r="I105" s="4"/>
+      <c r="J105" s="4"/>
+      <c r="K105" s="4"/>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H106" s="4"/>
+      <c r="I106" s="4"/>
+      <c r="J106" s="4"/>
+      <c r="K106" s="4"/>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A107" t="str">
+        <f>H81</f>
+        <v>+20% Zebu</v>
+      </c>
+      <c r="B107" s="42" t="str">
+        <f>B98</f>
+        <v>Animal populations (M hd) -- SA scenario specific</v>
+      </c>
+      <c r="C107" s="42"/>
+      <c r="D107" s="42"/>
+      <c r="E107" s="42"/>
+      <c r="H107" s="4"/>
+      <c r="I107" s="4"/>
+      <c r="J107" s="4"/>
+      <c r="K107" s="4"/>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B108" t="str">
+        <f>B99</f>
+        <v>Pastoral</v>
+      </c>
+      <c r="C108">
+        <f>C81</f>
+        <v>0.49402322991933489</v>
+      </c>
+      <c r="D108">
+        <f t="shared" ref="D108:E108" si="42">D81</f>
+        <v>0.48640304349731928</v>
+      </c>
+      <c r="E108">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="H108" s="4"/>
+      <c r="I108" s="4"/>
+      <c r="J108" s="4"/>
+      <c r="K108" s="4"/>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B109" t="str">
+        <f t="shared" ref="B109:B114" si="43">B100</f>
+        <v>Agropastoral</v>
+      </c>
+      <c r="C109">
+        <f t="shared" ref="C109:E109" si="44">C82</f>
+        <v>0</v>
+      </c>
+      <c r="D109">
+        <f t="shared" si="44"/>
+        <v>2.5194151670693041</v>
+      </c>
+      <c r="E109">
+        <f t="shared" si="44"/>
+        <v>2.1101718564805916</v>
+      </c>
+      <c r="H109" s="4"/>
+      <c r="I109" s="4"/>
+      <c r="J109" s="4"/>
+      <c r="K109" s="4"/>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B110" t="str">
+        <f t="shared" si="43"/>
+        <v>Mixed</v>
+      </c>
+      <c r="C110">
+        <f t="shared" ref="C110:E110" si="45">C83</f>
+        <v>0</v>
+      </c>
+      <c r="D110">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="E110">
+        <f t="shared" si="45"/>
+        <v>0.38596556316357417</v>
+      </c>
+      <c r="H110" s="4"/>
+      <c r="I110" s="4"/>
+      <c r="J110" s="4"/>
+      <c r="K110" s="4"/>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B111" t="str">
+        <f t="shared" si="43"/>
+        <v>Cowcalf</v>
+      </c>
+      <c r="C111">
+        <f t="shared" ref="C111:E111" si="46">C84</f>
+        <v>2.0019220309243413E-2</v>
+      </c>
+      <c r="D111">
+        <f t="shared" si="46"/>
+        <v>9.2522672890536062E-2</v>
+      </c>
+      <c r="E111">
+        <f t="shared" si="46"/>
+        <v>0.15001904223920623</v>
+      </c>
+      <c r="H111" s="4"/>
+      <c r="I111" s="4"/>
+      <c r="J111" s="4"/>
+      <c r="K111" s="4"/>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B112" t="str">
+        <f t="shared" si="43"/>
+        <v>Finisher</v>
+      </c>
+      <c r="C112">
+        <f t="shared" ref="C112:E112" si="47">C85</f>
+        <v>5.3182961871764585</v>
+      </c>
+      <c r="D112">
+        <f t="shared" si="47"/>
+        <v>7.088110217691594</v>
+      </c>
+      <c r="E112">
+        <f t="shared" si="47"/>
+        <v>6.1560286644571258</v>
+      </c>
+      <c r="H112" s="4"/>
+      <c r="I112" s="4"/>
+      <c r="J112" s="4"/>
+      <c r="K112" s="4"/>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B113" t="str">
+        <f t="shared" si="43"/>
+        <v>Dairy</v>
+      </c>
+      <c r="C113">
+        <f t="shared" ref="C113:E113" si="48">C86</f>
+        <v>3.0271361942572905E-2</v>
+      </c>
+      <c r="D113">
+        <f t="shared" si="48"/>
+        <v>1.4765740788097195</v>
+      </c>
+      <c r="E113">
+        <f t="shared" si="48"/>
+        <v>6.3853780054327789</v>
+      </c>
+      <c r="H113" s="4"/>
+      <c r="I113" s="4"/>
+      <c r="J113" s="4"/>
+      <c r="K113" s="4"/>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B114" t="str">
+        <f t="shared" si="43"/>
+        <v>Sheep</v>
+      </c>
+      <c r="C114">
+        <f t="shared" ref="C114:E114" si="49">C87</f>
+        <v>11.794047385286973</v>
+      </c>
+      <c r="D114">
+        <f t="shared" si="49"/>
+        <v>9.6481198260451801</v>
+      </c>
+      <c r="E114">
+        <f t="shared" si="49"/>
+        <v>9.0810136627013929</v>
+      </c>
+      <c r="H114" s="4"/>
+      <c r="I114" s="4"/>
+      <c r="J114" s="4"/>
+      <c r="K114" s="4"/>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H115" s="4"/>
+      <c r="I115" s="4"/>
+      <c r="J115" s="4"/>
+      <c r="K115" s="4"/>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B116" s="42" t="str">
+        <f>B107</f>
+        <v>Animal populations (M hd) -- SA scenario specific</v>
+      </c>
+      <c r="C116" s="42"/>
+      <c r="D116" s="42"/>
+      <c r="E116" s="42"/>
+      <c r="H116" s="4"/>
+      <c r="I116" s="4"/>
+      <c r="J116" s="4"/>
+      <c r="K116" s="4"/>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A117" t="str">
+        <f>H82</f>
+        <v>-20% Zebu</v>
+      </c>
+      <c r="B117" t="str">
+        <f>B108</f>
+        <v>Pastoral</v>
+      </c>
+      <c r="C117">
+        <f>C81</f>
+        <v>0.49402322991933489</v>
+      </c>
+      <c r="D117">
+        <f t="shared" ref="D117:E117" si="50">D81</f>
+        <v>0.48640304349731928</v>
+      </c>
+      <c r="E117">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="H117" s="4"/>
+      <c r="I117" s="4"/>
+      <c r="J117" s="4"/>
+      <c r="K117" s="4"/>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B118" t="str">
+        <f t="shared" ref="B118:B123" si="51">B109</f>
+        <v>Agropastoral</v>
+      </c>
+      <c r="C118">
+        <f t="shared" ref="C118:E118" si="52">C82</f>
+        <v>0</v>
+      </c>
+      <c r="D118">
+        <f t="shared" si="52"/>
+        <v>2.5194151670693041</v>
+      </c>
+      <c r="E118">
+        <f t="shared" si="52"/>
+        <v>2.1101718564805916</v>
+      </c>
+      <c r="H118" s="4"/>
+      <c r="I118" s="4"/>
+      <c r="J118" s="4"/>
+      <c r="K118" s="4"/>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B119" t="str">
+        <f t="shared" si="51"/>
+        <v>Mixed</v>
+      </c>
+      <c r="C119">
+        <f t="shared" ref="C119:E119" si="53">C83</f>
+        <v>0</v>
+      </c>
+      <c r="D119">
+        <f t="shared" si="53"/>
+        <v>0</v>
+      </c>
+      <c r="E119">
+        <f t="shared" si="53"/>
+        <v>0.38596556316357417</v>
+      </c>
+      <c r="H119" s="4"/>
+      <c r="I119" s="4"/>
+      <c r="J119" s="4"/>
+      <c r="K119" s="4"/>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B120" t="str">
+        <f t="shared" si="51"/>
+        <v>Cowcalf</v>
+      </c>
+      <c r="C120">
+        <f t="shared" ref="C120:E120" si="54">C84</f>
+        <v>2.0019220309243413E-2</v>
+      </c>
+      <c r="D120">
+        <f t="shared" si="54"/>
+        <v>9.2522672890536062E-2</v>
+      </c>
+      <c r="E120">
+        <f t="shared" si="54"/>
+        <v>0.15001904223920623</v>
+      </c>
+      <c r="H120" s="4"/>
+      <c r="I120" s="4"/>
+      <c r="J120" s="4"/>
+      <c r="K120" s="4"/>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B121" t="str">
+        <f t="shared" si="51"/>
+        <v>Finisher</v>
+      </c>
+      <c r="C121">
+        <f t="shared" ref="C121:E121" si="55">C85</f>
+        <v>5.3182961871764585</v>
+      </c>
+      <c r="D121">
+        <f t="shared" si="55"/>
+        <v>7.088110217691594</v>
+      </c>
+      <c r="E121">
+        <f t="shared" si="55"/>
+        <v>6.1560286644571258</v>
+      </c>
+      <c r="H121" s="4"/>
+      <c r="I121" s="4"/>
+      <c r="J121" s="4"/>
+      <c r="K121" s="4"/>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B122" t="str">
+        <f t="shared" si="51"/>
+        <v>Dairy</v>
+      </c>
+      <c r="C122">
+        <f t="shared" ref="C122:E122" si="56">C86</f>
+        <v>3.0271361942572905E-2</v>
+      </c>
+      <c r="D122">
+        <f t="shared" si="56"/>
+        <v>1.4765740788097195</v>
+      </c>
+      <c r="E122">
+        <f t="shared" si="56"/>
+        <v>6.3853780054327789</v>
+      </c>
+      <c r="H122" s="4"/>
+      <c r="I122" s="4"/>
+      <c r="J122" s="4"/>
+      <c r="K122" s="4"/>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B123" t="str">
+        <f t="shared" si="51"/>
+        <v>Sheep</v>
+      </c>
+      <c r="C123">
+        <f t="shared" ref="C123:E123" si="57">C87</f>
+        <v>11.794047385286973</v>
+      </c>
+      <c r="D123">
+        <f t="shared" si="57"/>
+        <v>9.6481198260451801</v>
+      </c>
+      <c r="E123">
+        <f t="shared" si="57"/>
+        <v>9.0810136627013929</v>
+      </c>
+      <c r="H123" s="4"/>
+      <c r="I123" s="4"/>
+      <c r="J123" s="4"/>
+      <c r="K123" s="4"/>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H124" s="4"/>
+      <c r="I124" s="4"/>
+      <c r="J124" s="4"/>
+      <c r="K124" s="4"/>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A125" t="str">
+        <f>H83</f>
+        <v>+20% Boran</v>
+      </c>
+      <c r="B125" s="42" t="str">
+        <f>B116</f>
+        <v>Animal populations (M hd) -- SA scenario specific</v>
+      </c>
+      <c r="C125" s="42"/>
+      <c r="D125" s="42"/>
+      <c r="E125" s="42"/>
+      <c r="H125" s="4"/>
+      <c r="I125" s="4"/>
+      <c r="J125" s="4"/>
+      <c r="K125" s="4"/>
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B126" t="str">
+        <f>B117</f>
+        <v>Pastoral</v>
+      </c>
+      <c r="C126">
+        <f>C81</f>
+        <v>0.49402322991933489</v>
+      </c>
+      <c r="D126">
+        <f t="shared" ref="D126:E126" si="58">D81</f>
+        <v>0.48640304349731928</v>
+      </c>
+      <c r="E126">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="H126" s="4"/>
+      <c r="I126" s="4"/>
+      <c r="J126" s="4"/>
+      <c r="K126" s="4"/>
+    </row>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B127" t="str">
+        <f t="shared" ref="B127:B132" si="59">B118</f>
+        <v>Agropastoral</v>
+      </c>
+      <c r="C127">
+        <f t="shared" ref="C127:E127" si="60">C82</f>
+        <v>0</v>
+      </c>
+      <c r="D127">
+        <f t="shared" si="60"/>
+        <v>2.5194151670693041</v>
+      </c>
+      <c r="E127">
+        <f t="shared" si="60"/>
+        <v>2.1101718564805916</v>
+      </c>
+      <c r="H127" s="4"/>
+      <c r="I127" s="4"/>
+      <c r="J127" s="4"/>
+      <c r="K127" s="4"/>
+    </row>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B128" t="str">
+        <f t="shared" si="59"/>
+        <v>Mixed</v>
+      </c>
+      <c r="C128">
+        <f t="shared" ref="C128:E128" si="61">C83</f>
+        <v>0</v>
+      </c>
+      <c r="D128">
+        <f t="shared" si="61"/>
+        <v>0</v>
+      </c>
+      <c r="E128">
+        <f t="shared" si="61"/>
+        <v>0.38596556316357417</v>
+      </c>
+      <c r="H128" s="4"/>
+      <c r="I128" s="4"/>
+      <c r="J128" s="4"/>
+      <c r="K128" s="4"/>
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B129" t="str">
+        <f t="shared" si="59"/>
+        <v>Cowcalf</v>
+      </c>
+      <c r="C129">
+        <f t="shared" ref="C129:E129" si="62">C84</f>
+        <v>2.0019220309243413E-2</v>
+      </c>
+      <c r="D129">
+        <f t="shared" si="62"/>
+        <v>9.2522672890536062E-2</v>
+      </c>
+      <c r="E129">
+        <f t="shared" si="62"/>
+        <v>0.15001904223920623</v>
+      </c>
+      <c r="H129" s="4"/>
+      <c r="I129" s="4"/>
+      <c r="J129" s="4"/>
+      <c r="K129" s="4"/>
+    </row>
+    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B130" t="str">
+        <f t="shared" si="59"/>
+        <v>Finisher</v>
+      </c>
+      <c r="C130">
+        <f t="shared" ref="C130:E130" si="63">C85</f>
+        <v>5.3182961871764585</v>
+      </c>
+      <c r="D130">
+        <f t="shared" si="63"/>
+        <v>7.088110217691594</v>
+      </c>
+      <c r="E130">
+        <f t="shared" si="63"/>
+        <v>6.1560286644571258</v>
+      </c>
+      <c r="H130" s="4"/>
+      <c r="I130" s="4"/>
+      <c r="J130" s="4"/>
+      <c r="K130" s="4"/>
+    </row>
+    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B131" t="str">
+        <f t="shared" si="59"/>
+        <v>Dairy</v>
+      </c>
+      <c r="C131">
+        <f t="shared" ref="C131:E131" si="64">C86</f>
+        <v>3.0271361942572905E-2</v>
+      </c>
+      <c r="D131">
+        <f t="shared" si="64"/>
+        <v>1.4765740788097195</v>
+      </c>
+      <c r="E131">
+        <f t="shared" si="64"/>
+        <v>6.3853780054327789</v>
+      </c>
+      <c r="H131" s="4"/>
+      <c r="I131" s="4"/>
+      <c r="J131" s="4"/>
+      <c r="K131" s="4"/>
+    </row>
+    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B132" t="str">
+        <f t="shared" si="59"/>
+        <v>Sheep</v>
+      </c>
+      <c r="C132">
+        <f t="shared" ref="C132:E132" si="65">C87</f>
+        <v>11.794047385286973</v>
+      </c>
+      <c r="D132">
+        <f t="shared" si="65"/>
+        <v>9.6481198260451801</v>
+      </c>
+      <c r="E132">
+        <f t="shared" si="65"/>
+        <v>9.0810136627013929</v>
+      </c>
+      <c r="H132" s="4"/>
+      <c r="I132" s="4"/>
+      <c r="J132" s="4"/>
+      <c r="K132" s="4"/>
+    </row>
+    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H133" s="4"/>
+      <c r="I133" s="4"/>
+      <c r="J133" s="4"/>
+      <c r="K133" s="4"/>
+    </row>
+    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A134" t="str">
+        <f>H84</f>
+        <v>-20% Boran</v>
+      </c>
+      <c r="B134" s="42" t="str">
+        <f>B125</f>
+        <v>Animal populations (M hd) -- SA scenario specific</v>
+      </c>
+      <c r="C134" s="42"/>
+      <c r="D134" s="42"/>
+      <c r="E134" s="42"/>
+      <c r="H134" s="4"/>
+      <c r="I134" s="4"/>
+      <c r="J134" s="4"/>
+      <c r="K134" s="4"/>
+    </row>
+    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B135" t="str">
+        <f>B126</f>
+        <v>Pastoral</v>
+      </c>
+      <c r="C135">
+        <f>C81</f>
+        <v>0.49402322991933489</v>
+      </c>
+      <c r="D135">
+        <f t="shared" ref="D135:E135" si="66">D81</f>
+        <v>0.48640304349731928</v>
+      </c>
+      <c r="E135">
+        <f t="shared" si="66"/>
+        <v>0</v>
+      </c>
+      <c r="H135" s="4"/>
+      <c r="I135" s="4"/>
+      <c r="J135" s="4"/>
+      <c r="K135" s="4"/>
+    </row>
+    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B136" t="str">
+        <f t="shared" ref="B136:B141" si="67">B127</f>
+        <v>Agropastoral</v>
+      </c>
+      <c r="C136">
+        <f t="shared" ref="C136:E136" si="68">C82</f>
+        <v>0</v>
+      </c>
+      <c r="D136">
+        <f t="shared" si="68"/>
+        <v>2.5194151670693041</v>
+      </c>
+      <c r="E136">
+        <f t="shared" si="68"/>
+        <v>2.1101718564805916</v>
+      </c>
+      <c r="H136" s="4"/>
+      <c r="I136" s="4"/>
+      <c r="J136" s="4"/>
+      <c r="K136" s="4"/>
+    </row>
+    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B137" t="str">
+        <f t="shared" si="67"/>
+        <v>Mixed</v>
+      </c>
+      <c r="C137">
+        <f t="shared" ref="C137:E137" si="69">C83</f>
+        <v>0</v>
+      </c>
+      <c r="D137">
+        <f t="shared" si="69"/>
+        <v>0</v>
+      </c>
+      <c r="E137">
+        <f t="shared" si="69"/>
+        <v>0.38596556316357417</v>
+      </c>
+      <c r="H137" s="4"/>
+      <c r="I137" s="4"/>
+      <c r="J137" s="4"/>
+      <c r="K137" s="4"/>
+    </row>
+    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B138" t="str">
+        <f t="shared" si="67"/>
+        <v>Cowcalf</v>
+      </c>
+      <c r="C138">
+        <f t="shared" ref="C138:E138" si="70">C84</f>
+        <v>2.0019220309243413E-2</v>
+      </c>
+      <c r="D138">
+        <f t="shared" si="70"/>
+        <v>9.2522672890536062E-2</v>
+      </c>
+      <c r="E138">
+        <f t="shared" si="70"/>
+        <v>0.15001904223920623</v>
+      </c>
+      <c r="H138" s="4"/>
+      <c r="I138" s="4"/>
+      <c r="J138" s="4"/>
+      <c r="K138" s="4"/>
+    </row>
+    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B139" t="str">
+        <f t="shared" si="67"/>
+        <v>Finisher</v>
+      </c>
+      <c r="C139">
+        <f t="shared" ref="C139:E139" si="71">C85</f>
+        <v>5.3182961871764585</v>
+      </c>
+      <c r="D139">
+        <f t="shared" si="71"/>
+        <v>7.088110217691594</v>
+      </c>
+      <c r="E139">
+        <f t="shared" si="71"/>
+        <v>6.1560286644571258</v>
+      </c>
+      <c r="H139" s="4"/>
+      <c r="I139" s="4"/>
+      <c r="J139" s="4"/>
+      <c r="K139" s="4"/>
+    </row>
+    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B140" t="str">
+        <f t="shared" si="67"/>
+        <v>Dairy</v>
+      </c>
+      <c r="C140">
+        <f t="shared" ref="C140:E140" si="72">C86</f>
+        <v>3.0271361942572905E-2</v>
+      </c>
+      <c r="D140">
+        <f t="shared" si="72"/>
+        <v>1.4765740788097195</v>
+      </c>
+      <c r="E140">
+        <f t="shared" si="72"/>
+        <v>6.3853780054327789</v>
+      </c>
+      <c r="H140" s="4"/>
+      <c r="I140" s="4"/>
+      <c r="J140" s="4"/>
+      <c r="K140" s="4"/>
+    </row>
+    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B141" t="str">
+        <f t="shared" si="67"/>
+        <v>Sheep</v>
+      </c>
+      <c r="C141">
+        <f t="shared" ref="C141:E141" si="73">C87</f>
+        <v>11.794047385286973</v>
+      </c>
+      <c r="D141">
+        <f t="shared" si="73"/>
+        <v>9.6481198260451801</v>
+      </c>
+      <c r="E141">
+        <f t="shared" si="73"/>
+        <v>9.0810136627013929</v>
+      </c>
+      <c r="H141" s="4"/>
+      <c r="I141" s="4"/>
+      <c r="J141" s="4"/>
+      <c r="K141" s="4"/>
+    </row>
+    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H142" s="4"/>
+      <c r="I142" s="4"/>
+      <c r="J142" s="4"/>
+      <c r="K142" s="4"/>
+    </row>
+    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A143" t="str">
+        <f>H85</f>
+        <v>+20% Exotic</v>
+      </c>
+      <c r="B143" s="42" t="str">
+        <f>B134</f>
+        <v>Animal populations (M hd) -- SA scenario specific</v>
+      </c>
+      <c r="C143" s="42"/>
+      <c r="D143" s="42"/>
+      <c r="E143" s="42"/>
+      <c r="H143" s="4"/>
+      <c r="I143" s="4"/>
+      <c r="J143" s="4"/>
+      <c r="K143" s="4"/>
+    </row>
+    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B144" t="str">
+        <f>B135</f>
+        <v>Pastoral</v>
+      </c>
+      <c r="C144">
+        <f>C81</f>
+        <v>0.49402322991933489</v>
+      </c>
+      <c r="D144">
+        <f t="shared" ref="D144:E144" si="74">D81</f>
+        <v>0.48640304349731928</v>
+      </c>
+      <c r="E144">
+        <f t="shared" si="74"/>
+        <v>0</v>
+      </c>
+      <c r="H144" s="4"/>
+      <c r="I144" s="4"/>
+      <c r="J144" s="4"/>
+      <c r="K144" s="4"/>
+    </row>
+    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B145" t="str">
+        <f t="shared" ref="B145:B150" si="75">B136</f>
+        <v>Agropastoral</v>
+      </c>
+      <c r="C145">
+        <f t="shared" ref="C145:E145" si="76">C82</f>
+        <v>0</v>
+      </c>
+      <c r="D145">
+        <f t="shared" si="76"/>
+        <v>2.5194151670693041</v>
+      </c>
+      <c r="E145">
+        <f t="shared" si="76"/>
+        <v>2.1101718564805916</v>
+      </c>
+      <c r="H145" s="4"/>
+      <c r="I145" s="4"/>
+      <c r="J145" s="4"/>
+      <c r="K145" s="4"/>
+    </row>
+    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B146" t="str">
+        <f t="shared" si="75"/>
+        <v>Mixed</v>
+      </c>
+      <c r="C146">
+        <f t="shared" ref="C146:E146" si="77">C83</f>
+        <v>0</v>
+      </c>
+      <c r="D146">
+        <f t="shared" si="77"/>
+        <v>0</v>
+      </c>
+      <c r="E146">
+        <f t="shared" si="77"/>
+        <v>0.38596556316357417</v>
+      </c>
+      <c r="H146" s="4"/>
+      <c r="I146" s="4"/>
+      <c r="J146" s="4"/>
+      <c r="K146" s="4"/>
+    </row>
+    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B147" t="str">
+        <f t="shared" si="75"/>
+        <v>Cowcalf</v>
+      </c>
+      <c r="C147">
+        <f t="shared" ref="C147:E147" si="78">C84</f>
+        <v>2.0019220309243413E-2</v>
+      </c>
+      <c r="D147">
+        <f t="shared" si="78"/>
+        <v>9.2522672890536062E-2</v>
+      </c>
+      <c r="E147">
+        <f t="shared" si="78"/>
+        <v>0.15001904223920623</v>
+      </c>
+      <c r="H147" s="4"/>
+      <c r="I147" s="4"/>
+      <c r="J147" s="4"/>
+      <c r="K147" s="4"/>
+    </row>
+    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B148" t="str">
+        <f t="shared" si="75"/>
+        <v>Finisher</v>
+      </c>
+      <c r="C148">
+        <f t="shared" ref="C148:E148" si="79">C85</f>
+        <v>5.3182961871764585</v>
+      </c>
+      <c r="D148">
+        <f t="shared" si="79"/>
+        <v>7.088110217691594</v>
+      </c>
+      <c r="E148">
+        <f t="shared" si="79"/>
+        <v>6.1560286644571258</v>
+      </c>
+      <c r="H148" s="4"/>
+      <c r="I148" s="4"/>
+      <c r="J148" s="4"/>
+      <c r="K148" s="4"/>
+    </row>
+    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B149" t="str">
+        <f t="shared" si="75"/>
+        <v>Dairy</v>
+      </c>
+      <c r="C149">
+        <f t="shared" ref="C149:E149" si="80">C86</f>
+        <v>3.0271361942572905E-2</v>
+      </c>
+      <c r="D149">
+        <f t="shared" si="80"/>
+        <v>1.4765740788097195</v>
+      </c>
+      <c r="E149">
+        <f t="shared" si="80"/>
+        <v>6.3853780054327789</v>
+      </c>
+      <c r="H149" s="4"/>
+      <c r="I149" s="4"/>
+      <c r="J149" s="4"/>
+      <c r="K149" s="4"/>
+    </row>
+    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B150" t="str">
+        <f t="shared" si="75"/>
+        <v>Sheep</v>
+      </c>
+      <c r="C150">
+        <f t="shared" ref="C150:E150" si="81">C87</f>
+        <v>11.794047385286973</v>
+      </c>
+      <c r="D150">
+        <f t="shared" si="81"/>
+        <v>9.6481198260451801</v>
+      </c>
+      <c r="E150">
+        <f t="shared" si="81"/>
+        <v>9.0810136627013929</v>
+      </c>
+      <c r="H150" s="4"/>
+      <c r="I150" s="4"/>
+      <c r="J150" s="4"/>
+      <c r="K150" s="4"/>
+    </row>
+    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H151" s="4"/>
+      <c r="I151" s="4"/>
+      <c r="J151" s="4"/>
+      <c r="K151" s="4"/>
+    </row>
+    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A152" t="str">
+        <f>H86</f>
+        <v>-20% Exotic</v>
+      </c>
+      <c r="B152" s="42" t="str">
+        <f>B143</f>
+        <v>Animal populations (M hd) -- SA scenario specific</v>
+      </c>
+      <c r="C152" s="42"/>
+      <c r="D152" s="42"/>
+      <c r="E152" s="42"/>
+      <c r="H152" s="4"/>
+      <c r="I152" s="4"/>
+      <c r="J152" s="4"/>
+      <c r="K152" s="4"/>
+    </row>
+    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B153" t="str">
+        <f>B144</f>
+        <v>Pastoral</v>
+      </c>
+      <c r="C153">
+        <f>C81</f>
+        <v>0.49402322991933489</v>
+      </c>
+      <c r="D153">
+        <f t="shared" ref="D153:E153" si="82">D81</f>
+        <v>0.48640304349731928</v>
+      </c>
+      <c r="E153">
+        <f t="shared" si="82"/>
+        <v>0</v>
+      </c>
+      <c r="H153" s="4"/>
+      <c r="I153" s="4"/>
+      <c r="J153" s="4"/>
+      <c r="K153" s="4"/>
+    </row>
+    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B154" t="str">
+        <f t="shared" ref="B154:B159" si="83">B145</f>
+        <v>Agropastoral</v>
+      </c>
+      <c r="C154">
+        <f t="shared" ref="C154:E154" si="84">C82</f>
+        <v>0</v>
+      </c>
+      <c r="D154">
+        <f t="shared" si="84"/>
+        <v>2.5194151670693041</v>
+      </c>
+      <c r="E154">
+        <f t="shared" si="84"/>
+        <v>2.1101718564805916</v>
+      </c>
+      <c r="H154" s="4"/>
+      <c r="I154" s="4"/>
+      <c r="J154" s="4"/>
+      <c r="K154" s="4"/>
+    </row>
+    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B155" t="str">
+        <f t="shared" si="83"/>
+        <v>Mixed</v>
+      </c>
+      <c r="C155">
+        <f t="shared" ref="C155:E155" si="85">C83</f>
+        <v>0</v>
+      </c>
+      <c r="D155">
+        <f t="shared" si="85"/>
+        <v>0</v>
+      </c>
+      <c r="E155">
+        <f t="shared" si="85"/>
+        <v>0.38596556316357417</v>
+      </c>
+      <c r="H155" s="4"/>
+      <c r="I155" s="4"/>
+      <c r="J155" s="4"/>
+      <c r="K155" s="4"/>
+    </row>
+    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B156" t="str">
+        <f t="shared" si="83"/>
+        <v>Cowcalf</v>
+      </c>
+      <c r="C156">
+        <f t="shared" ref="C156:E156" si="86">C84</f>
+        <v>2.0019220309243413E-2</v>
+      </c>
+      <c r="D156">
+        <f t="shared" si="86"/>
+        <v>9.2522672890536062E-2</v>
+      </c>
+      <c r="E156">
+        <f t="shared" si="86"/>
+        <v>0.15001904223920623</v>
+      </c>
+      <c r="H156" s="4"/>
+      <c r="I156" s="4"/>
+      <c r="J156" s="4"/>
+      <c r="K156" s="4"/>
+    </row>
+    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B157" t="str">
+        <f t="shared" si="83"/>
+        <v>Finisher</v>
+      </c>
+      <c r="C157">
+        <f t="shared" ref="C157:E157" si="87">C85</f>
+        <v>5.3182961871764585</v>
+      </c>
+      <c r="D157">
+        <f t="shared" si="87"/>
+        <v>7.088110217691594</v>
+      </c>
+      <c r="E157">
+        <f t="shared" si="87"/>
+        <v>6.1560286644571258</v>
+      </c>
+      <c r="H157" s="4"/>
+      <c r="I157" s="4"/>
+      <c r="J157" s="4"/>
+      <c r="K157" s="4"/>
+    </row>
+    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B158" t="str">
+        <f t="shared" si="83"/>
+        <v>Dairy</v>
+      </c>
+      <c r="C158">
+        <f t="shared" ref="C158:E158" si="88">C86</f>
+        <v>3.0271361942572905E-2</v>
+      </c>
+      <c r="D158">
+        <f t="shared" si="88"/>
+        <v>1.4765740788097195</v>
+      </c>
+      <c r="E158">
+        <f t="shared" si="88"/>
+        <v>6.3853780054327789</v>
+      </c>
+      <c r="H158" s="4"/>
+      <c r="I158" s="4"/>
+      <c r="J158" s="4"/>
+      <c r="K158" s="4"/>
+    </row>
+    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B159" t="str">
+        <f t="shared" si="83"/>
+        <v>Sheep</v>
+      </c>
+      <c r="C159">
+        <f t="shared" ref="C159:E159" si="89">C87</f>
+        <v>11.794047385286973</v>
+      </c>
+      <c r="D159">
+        <f t="shared" si="89"/>
+        <v>9.6481198260451801</v>
+      </c>
+      <c r="E159">
+        <f t="shared" si="89"/>
+        <v>9.0810136627013929</v>
+      </c>
+      <c r="H159" s="4"/>
+      <c r="I159" s="4"/>
+      <c r="J159" s="4"/>
+      <c r="K159" s="4"/>
+    </row>
+    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H160" s="4"/>
+      <c r="I160" s="4"/>
+      <c r="J160" s="4"/>
+      <c r="K160" s="4"/>
+    </row>
+    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A161" t="str">
+        <f>H87</f>
+        <v>+20% Finisher:Breeder</v>
+      </c>
+      <c r="B161" s="42" t="str">
+        <f>B152</f>
+        <v>Animal populations (M hd) -- SA scenario specific</v>
+      </c>
+      <c r="C161" s="42"/>
+      <c r="D161" s="42"/>
+      <c r="E161" s="42"/>
+      <c r="H161" s="4"/>
+      <c r="I161" s="4"/>
+      <c r="J161" s="4"/>
+      <c r="K161" s="4"/>
+    </row>
+    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B162" t="str">
+        <f>B153</f>
+        <v>Pastoral</v>
+      </c>
+      <c r="C162">
+        <f>C81</f>
+        <v>0.49402322991933489</v>
+      </c>
+      <c r="D162">
+        <f t="shared" ref="D162:E162" si="90">D81</f>
+        <v>0.48640304349731928</v>
+      </c>
+      <c r="E162">
+        <f t="shared" si="90"/>
+        <v>0</v>
+      </c>
+      <c r="H162" s="4"/>
+      <c r="I162" s="4"/>
+      <c r="J162" s="4"/>
+      <c r="K162" s="4"/>
+    </row>
+    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B163" t="str">
+        <f t="shared" ref="B163:B168" si="91">B154</f>
+        <v>Agropastoral</v>
+      </c>
+      <c r="C163">
+        <f t="shared" ref="C163:E163" si="92">C82</f>
+        <v>0</v>
+      </c>
+      <c r="D163">
+        <f t="shared" si="92"/>
+        <v>2.5194151670693041</v>
+      </c>
+      <c r="E163">
+        <f t="shared" si="92"/>
+        <v>2.1101718564805916</v>
+      </c>
+      <c r="H163" s="4"/>
+      <c r="I163" s="4"/>
+      <c r="J163" s="4"/>
+      <c r="K163" s="4"/>
+    </row>
+    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B164" t="str">
+        <f t="shared" si="91"/>
+        <v>Mixed</v>
+      </c>
+      <c r="C164">
+        <f t="shared" ref="C164:E164" si="93">C83</f>
+        <v>0</v>
+      </c>
+      <c r="D164">
+        <f t="shared" si="93"/>
+        <v>0</v>
+      </c>
+      <c r="E164">
+        <f t="shared" si="93"/>
+        <v>0.38596556316357417</v>
+      </c>
+      <c r="H164" s="4"/>
+      <c r="I164" s="4"/>
+      <c r="J164" s="4"/>
+      <c r="K164" s="4"/>
+    </row>
+    <row r="165" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B165" t="str">
+        <f t="shared" si="91"/>
+        <v>Cowcalf</v>
+      </c>
+      <c r="C165">
+        <f t="shared" ref="C165:E165" si="94">C84</f>
+        <v>2.0019220309243413E-2</v>
+      </c>
+      <c r="D165">
+        <f t="shared" si="94"/>
+        <v>9.2522672890536062E-2</v>
+      </c>
+      <c r="E165">
+        <f t="shared" si="94"/>
+        <v>0.15001904223920623</v>
+      </c>
+      <c r="H165" s="4"/>
+      <c r="I165" s="4"/>
+      <c r="J165" s="4"/>
+      <c r="K165" s="4"/>
+    </row>
+    <row r="166" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B166" t="str">
+        <f t="shared" si="91"/>
+        <v>Finisher</v>
+      </c>
+      <c r="C166">
+        <f t="shared" ref="C166:E166" si="95">C85</f>
+        <v>5.3182961871764585</v>
+      </c>
+      <c r="D166">
+        <f t="shared" si="95"/>
+        <v>7.088110217691594</v>
+      </c>
+      <c r="E166">
+        <f t="shared" si="95"/>
+        <v>6.1560286644571258</v>
+      </c>
+      <c r="H166" s="4"/>
+      <c r="I166" s="4"/>
+      <c r="J166" s="4"/>
+      <c r="K166" s="4"/>
+    </row>
+    <row r="167" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B167" t="str">
+        <f t="shared" si="91"/>
+        <v>Dairy</v>
+      </c>
+      <c r="C167">
+        <f t="shared" ref="C167:E167" si="96">C86</f>
+        <v>3.0271361942572905E-2</v>
+      </c>
+      <c r="D167">
+        <f t="shared" si="96"/>
+        <v>1.4765740788097195</v>
+      </c>
+      <c r="E167">
+        <f t="shared" si="96"/>
+        <v>6.3853780054327789</v>
+      </c>
+      <c r="H167" s="4"/>
+      <c r="I167" s="4"/>
+      <c r="J167" s="4"/>
+      <c r="K167" s="4"/>
+    </row>
+    <row r="168" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B168" t="str">
+        <f t="shared" si="91"/>
+        <v>Sheep</v>
+      </c>
+      <c r="C168">
+        <f t="shared" ref="C168:E168" si="97">C87</f>
+        <v>11.794047385286973</v>
+      </c>
+      <c r="D168">
+        <f t="shared" si="97"/>
+        <v>9.6481198260451801</v>
+      </c>
+      <c r="E168">
+        <f t="shared" si="97"/>
+        <v>9.0810136627013929</v>
+      </c>
+      <c r="H168" s="4"/>
+      <c r="I168" s="4"/>
+      <c r="J168" s="4"/>
+      <c r="K168" s="4"/>
+    </row>
+    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H169" s="4"/>
+      <c r="I169" s="4"/>
+      <c r="J169" s="4"/>
+      <c r="K169" s="4"/>
+    </row>
+    <row r="170" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A170" t="str">
+        <f>H88</f>
+        <v>-20% Finisher:Breeder</v>
+      </c>
+      <c r="B170" s="42" t="str">
+        <f>B161</f>
+        <v>Animal populations (M hd) -- SA scenario specific</v>
+      </c>
+      <c r="C170" s="42"/>
+      <c r="D170" s="42"/>
+      <c r="E170" s="42"/>
+      <c r="H170" s="4"/>
+      <c r="I170" s="4"/>
+      <c r="J170" s="4"/>
+      <c r="K170" s="4"/>
+    </row>
+    <row r="171" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B171" t="str">
+        <f>B162</f>
+        <v>Pastoral</v>
+      </c>
+      <c r="C171">
+        <f>C81</f>
+        <v>0.49402322991933489</v>
+      </c>
+      <c r="D171">
+        <f t="shared" ref="D171:E171" si="98">D81</f>
+        <v>0.48640304349731928</v>
+      </c>
+      <c r="E171">
+        <f t="shared" si="98"/>
+        <v>0</v>
+      </c>
+      <c r="H171" s="4"/>
+      <c r="I171" s="4"/>
+      <c r="J171" s="4"/>
+      <c r="K171" s="4"/>
+    </row>
+    <row r="172" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B172" t="str">
+        <f t="shared" ref="B172:B235" si="99">B163</f>
+        <v>Agropastoral</v>
+      </c>
+      <c r="C172">
+        <f t="shared" ref="C172:E172" si="100">C82</f>
+        <v>0</v>
+      </c>
+      <c r="D172">
+        <f t="shared" si="100"/>
+        <v>2.5194151670693041</v>
+      </c>
+      <c r="E172">
+        <f t="shared" si="100"/>
+        <v>2.1101718564805916</v>
+      </c>
+      <c r="H172" s="4"/>
+      <c r="I172" s="4"/>
+      <c r="J172" s="4"/>
+      <c r="K172" s="4"/>
+    </row>
+    <row r="173" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B173" t="str">
+        <f t="shared" si="99"/>
+        <v>Mixed</v>
+      </c>
+      <c r="C173">
+        <f t="shared" ref="C173:E173" si="101">C83</f>
+        <v>0</v>
+      </c>
+      <c r="D173">
+        <f t="shared" si="101"/>
+        <v>0</v>
+      </c>
+      <c r="E173">
+        <f t="shared" si="101"/>
+        <v>0.38596556316357417</v>
+      </c>
+      <c r="H173" s="4"/>
+      <c r="I173" s="4"/>
+      <c r="J173" s="4"/>
+      <c r="K173" s="4"/>
+    </row>
+    <row r="174" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B174" t="str">
+        <f t="shared" si="99"/>
+        <v>Cowcalf</v>
+      </c>
+      <c r="C174">
+        <f t="shared" ref="C174:E174" si="102">C84</f>
+        <v>2.0019220309243413E-2</v>
+      </c>
+      <c r="D174">
+        <f t="shared" si="102"/>
+        <v>9.2522672890536062E-2</v>
+      </c>
+      <c r="E174">
+        <f t="shared" si="102"/>
+        <v>0.15001904223920623</v>
+      </c>
+      <c r="H174" s="4"/>
+      <c r="I174" s="4"/>
+      <c r="J174" s="4"/>
+      <c r="K174" s="4"/>
+    </row>
+    <row r="175" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B175" t="str">
+        <f t="shared" si="99"/>
+        <v>Finisher</v>
+      </c>
+      <c r="C175">
+        <f t="shared" ref="C175:E175" si="103">C85</f>
+        <v>5.3182961871764585</v>
+      </c>
+      <c r="D175">
+        <f t="shared" si="103"/>
+        <v>7.088110217691594</v>
+      </c>
+      <c r="E175">
+        <f t="shared" si="103"/>
+        <v>6.1560286644571258</v>
+      </c>
+      <c r="H175" s="4"/>
+      <c r="I175" s="4"/>
+      <c r="J175" s="4"/>
+      <c r="K175" s="4"/>
+    </row>
+    <row r="176" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B176" t="str">
+        <f t="shared" si="99"/>
+        <v>Dairy</v>
+      </c>
+      <c r="C176">
+        <f t="shared" ref="C176:E176" si="104">C86</f>
+        <v>3.0271361942572905E-2</v>
+      </c>
+      <c r="D176">
+        <f t="shared" si="104"/>
+        <v>1.4765740788097195</v>
+      </c>
+      <c r="E176">
+        <f t="shared" si="104"/>
+        <v>6.3853780054327789</v>
+      </c>
+      <c r="H176" s="4"/>
+      <c r="I176" s="4"/>
+      <c r="J176" s="4"/>
+      <c r="K176" s="4"/>
+    </row>
+    <row r="177" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B177" t="str">
+        <f t="shared" si="99"/>
+        <v>Sheep</v>
+      </c>
+      <c r="C177">
+        <f t="shared" ref="C177:E177" si="105">C87</f>
+        <v>11.794047385286973</v>
+      </c>
+      <c r="D177">
+        <f t="shared" si="105"/>
+        <v>9.6481198260451801</v>
+      </c>
+      <c r="E177">
+        <f t="shared" si="105"/>
+        <v>9.0810136627013929</v>
+      </c>
+      <c r="H177" s="4"/>
+      <c r="I177" s="4"/>
+      <c r="J177" s="4"/>
+      <c r="K177" s="4"/>
+    </row>
+    <row r="178" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H178" s="4"/>
+      <c r="I178" s="4"/>
+      <c r="J178" s="4"/>
+      <c r="K178" s="4"/>
+    </row>
+    <row r="179" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A179" t="str">
+        <f>H89</f>
+        <v>+20% Pastoral:Agropastoral</v>
+      </c>
+      <c r="B179" s="42" t="str">
+        <f>B170</f>
+        <v>Animal populations (M hd) -- SA scenario specific</v>
+      </c>
+      <c r="C179" s="42"/>
+      <c r="D179" s="42"/>
+      <c r="E179" s="42"/>
+      <c r="H179" s="4"/>
+      <c r="I179" s="4"/>
+      <c r="J179" s="4"/>
+      <c r="K179" s="4"/>
+    </row>
+    <row r="180" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B180" t="str">
+        <f t="shared" si="99"/>
+        <v>Pastoral</v>
+      </c>
+      <c r="C180" s="40">
+        <f>C81*$I$89</f>
+        <v>0.64223019889513533</v>
+      </c>
+      <c r="D180" s="40">
+        <f>D81*$I$89</f>
+        <v>0.63232395654651508</v>
+      </c>
+      <c r="E180" s="40">
+        <f>E81*$I$89</f>
+        <v>0</v>
+      </c>
+      <c r="H180" s="4"/>
+      <c r="I180" s="4"/>
+      <c r="J180" s="4"/>
+      <c r="K180" s="4"/>
+    </row>
+    <row r="181" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B181" t="str">
+        <f t="shared" si="99"/>
+        <v>Agropastoral</v>
+      </c>
+      <c r="C181" s="40">
+        <f>C82*$I$90</f>
+        <v>0</v>
+      </c>
+      <c r="D181" s="40">
+        <f>D82*$I$90</f>
+        <v>2.0155321336554435</v>
+      </c>
+      <c r="E181" s="40">
+        <f>E82*$I$90</f>
+        <v>1.6881374851844733</v>
+      </c>
+      <c r="H181" s="4"/>
+      <c r="I181" s="4"/>
+      <c r="J181" s="4"/>
+      <c r="K181" s="4"/>
+    </row>
+    <row r="182" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B182" t="str">
+        <f t="shared" si="99"/>
+        <v>Mixed</v>
+      </c>
+      <c r="C182">
+        <f t="shared" ref="C182:E182" si="106">C83</f>
+        <v>0</v>
+      </c>
+      <c r="D182">
+        <f t="shared" si="106"/>
+        <v>0</v>
+      </c>
+      <c r="E182">
+        <f t="shared" si="106"/>
+        <v>0.38596556316357417</v>
+      </c>
+      <c r="H182" s="4"/>
+      <c r="I182" s="4"/>
+      <c r="J182" s="4"/>
+      <c r="K182" s="4"/>
+    </row>
+    <row r="183" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B183" t="str">
+        <f t="shared" si="99"/>
+        <v>Cowcalf</v>
+      </c>
+      <c r="C183">
+        <f t="shared" ref="C183:E183" si="107">C84</f>
+        <v>2.0019220309243413E-2</v>
+      </c>
+      <c r="D183">
+        <f t="shared" si="107"/>
+        <v>9.2522672890536062E-2</v>
+      </c>
+      <c r="E183">
+        <f t="shared" si="107"/>
+        <v>0.15001904223920623</v>
+      </c>
+      <c r="H183" s="4"/>
+      <c r="I183" s="4"/>
+      <c r="J183" s="4"/>
+      <c r="K183" s="4"/>
+    </row>
+    <row r="184" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B184" t="str">
+        <f t="shared" si="99"/>
+        <v>Finisher</v>
+      </c>
+      <c r="C184">
+        <f t="shared" ref="C184:E184" si="108">C85</f>
+        <v>5.3182961871764585</v>
+      </c>
+      <c r="D184">
+        <f t="shared" si="108"/>
+        <v>7.088110217691594</v>
+      </c>
+      <c r="E184">
+        <f t="shared" si="108"/>
+        <v>6.1560286644571258</v>
+      </c>
+      <c r="H184" s="4"/>
+      <c r="I184" s="4"/>
+      <c r="J184" s="4"/>
+      <c r="K184" s="4"/>
+    </row>
+    <row r="185" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B185" t="str">
+        <f t="shared" si="99"/>
+        <v>Dairy</v>
+      </c>
+      <c r="C185">
+        <f t="shared" ref="C185:E185" si="109">C86</f>
+        <v>3.0271361942572905E-2</v>
+      </c>
+      <c r="D185">
+        <f t="shared" si="109"/>
+        <v>1.4765740788097195</v>
+      </c>
+      <c r="E185">
+        <f t="shared" si="109"/>
+        <v>6.3853780054327789</v>
+      </c>
+      <c r="H185" s="4"/>
+      <c r="I185" s="4"/>
+      <c r="J185" s="4"/>
+      <c r="K185" s="4"/>
+    </row>
+    <row r="186" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B186" t="str">
+        <f t="shared" si="99"/>
+        <v>Sheep</v>
+      </c>
+      <c r="C186">
+        <f t="shared" ref="C186:E186" si="110">C87</f>
+        <v>11.794047385286973</v>
+      </c>
+      <c r="D186">
+        <f t="shared" si="110"/>
+        <v>9.6481198260451801</v>
+      </c>
+      <c r="E186">
+        <f t="shared" si="110"/>
+        <v>9.0810136627013929</v>
+      </c>
+      <c r="H186" s="4"/>
+      <c r="I186" s="4"/>
+      <c r="J186" s="4"/>
+      <c r="K186" s="4"/>
+    </row>
+    <row r="187" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H187" s="4"/>
+      <c r="I187" s="4"/>
+      <c r="J187" s="4"/>
+      <c r="K187" s="4"/>
+    </row>
+    <row r="188" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A188" t="str">
+        <f>H90</f>
+        <v>-20% Pastoral:Agropastoral</v>
+      </c>
+      <c r="B188" s="42" t="str">
+        <f>B179</f>
+        <v>Animal populations (M hd) -- SA scenario specific</v>
+      </c>
+      <c r="C188" s="42"/>
+      <c r="D188" s="42"/>
+      <c r="E188" s="42"/>
+      <c r="H188" s="4"/>
+      <c r="I188" s="4"/>
+      <c r="J188" s="4"/>
+      <c r="K188" s="4"/>
+    </row>
+    <row r="189" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B189" t="str">
+        <f t="shared" si="99"/>
+        <v>Pastoral</v>
+      </c>
+      <c r="C189" s="40">
+        <f>C81*$I$90</f>
+        <v>0.39521858393546794</v>
+      </c>
+      <c r="D189" s="40">
+        <f>D81*$I$90</f>
+        <v>0.38912243479785547</v>
+      </c>
+      <c r="E189" s="40">
+        <f>E81*$I$90</f>
+        <v>0</v>
+      </c>
+      <c r="H189" s="4"/>
+      <c r="I189" s="4"/>
+      <c r="J189" s="4"/>
+      <c r="K189" s="4"/>
+    </row>
+    <row r="190" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B190" t="str">
+        <f t="shared" si="99"/>
+        <v>Agropastoral</v>
+      </c>
+      <c r="C190" s="40">
+        <f>C82*$I$89</f>
+        <v>0</v>
+      </c>
+      <c r="D190" s="40">
+        <f>D82*$I$89</f>
+        <v>3.2752397171900953</v>
+      </c>
+      <c r="E190" s="40">
+        <f>E82*$I$89</f>
+        <v>2.7432234134247691</v>
+      </c>
+      <c r="H190" s="4"/>
+      <c r="I190" s="4"/>
+      <c r="J190" s="4"/>
+      <c r="K190" s="4"/>
+    </row>
+    <row r="191" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B191" t="str">
+        <f t="shared" si="99"/>
+        <v>Mixed</v>
+      </c>
+      <c r="C191">
+        <f t="shared" ref="C191:E191" si="111">C83</f>
+        <v>0</v>
+      </c>
+      <c r="D191">
+        <f t="shared" si="111"/>
+        <v>0</v>
+      </c>
+      <c r="E191">
+        <f t="shared" si="111"/>
+        <v>0.38596556316357417</v>
+      </c>
+      <c r="H191" s="4"/>
+      <c r="I191" s="4"/>
+      <c r="J191" s="4"/>
+      <c r="K191" s="4"/>
+    </row>
+    <row r="192" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B192" t="str">
+        <f t="shared" si="99"/>
+        <v>Cowcalf</v>
+      </c>
+      <c r="C192">
+        <f t="shared" ref="C192:E192" si="112">C84</f>
+        <v>2.0019220309243413E-2</v>
+      </c>
+      <c r="D192">
+        <f t="shared" si="112"/>
+        <v>9.2522672890536062E-2</v>
+      </c>
+      <c r="E192">
+        <f t="shared" si="112"/>
+        <v>0.15001904223920623</v>
+      </c>
+      <c r="H192" s="4"/>
+      <c r="I192" s="4"/>
+      <c r="J192" s="4"/>
+      <c r="K192" s="4"/>
+    </row>
+    <row r="193" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B193" t="str">
+        <f t="shared" si="99"/>
+        <v>Finisher</v>
+      </c>
+      <c r="C193">
+        <f t="shared" ref="C193:E193" si="113">C85</f>
+        <v>5.3182961871764585</v>
+      </c>
+      <c r="D193">
+        <f t="shared" si="113"/>
+        <v>7.088110217691594</v>
+      </c>
+      <c r="E193">
+        <f t="shared" si="113"/>
+        <v>6.1560286644571258</v>
+      </c>
+      <c r="H193" s="4"/>
+      <c r="I193" s="4"/>
+      <c r="J193" s="4"/>
+      <c r="K193" s="4"/>
+    </row>
+    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B194" t="str">
+        <f t="shared" si="99"/>
+        <v>Dairy</v>
+      </c>
+      <c r="C194">
+        <f t="shared" ref="C194:E194" si="114">C86</f>
+        <v>3.0271361942572905E-2</v>
+      </c>
+      <c r="D194">
+        <f t="shared" si="114"/>
+        <v>1.4765740788097195</v>
+      </c>
+      <c r="E194">
+        <f t="shared" si="114"/>
+        <v>6.3853780054327789</v>
+      </c>
+      <c r="H194" s="4"/>
+      <c r="I194" s="4"/>
+      <c r="J194" s="4"/>
+      <c r="K194" s="4"/>
+    </row>
+    <row r="195" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B195" t="str">
+        <f t="shared" si="99"/>
+        <v>Sheep</v>
+      </c>
+      <c r="C195">
+        <f t="shared" ref="C195:E195" si="115">C87</f>
+        <v>11.794047385286973</v>
+      </c>
+      <c r="D195">
+        <f t="shared" si="115"/>
+        <v>9.6481198260451801</v>
+      </c>
+      <c r="E195">
+        <f t="shared" si="115"/>
+        <v>9.0810136627013929</v>
+      </c>
+      <c r="H195" s="4"/>
+      <c r="I195" s="4"/>
+      <c r="J195" s="4"/>
+      <c r="K195" s="4"/>
+    </row>
+    <row r="196" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H196" s="4"/>
+      <c r="I196" s="4"/>
+      <c r="J196" s="4"/>
+      <c r="K196" s="4"/>
+    </row>
+    <row r="197" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A197" t="str">
+        <f>H91</f>
+        <v>+20% Mixed:Agropastoral</v>
+      </c>
+      <c r="B197" s="42" t="str">
+        <f>B188</f>
+        <v>Animal populations (M hd) -- SA scenario specific</v>
+      </c>
+      <c r="C197" s="42"/>
+      <c r="D197" s="42"/>
+      <c r="E197" s="42"/>
+      <c r="H197" s="4"/>
+      <c r="I197" s="4"/>
+      <c r="J197" s="4"/>
+      <c r="K197" s="4"/>
+    </row>
+    <row r="198" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B198" t="str">
+        <f t="shared" si="99"/>
+        <v>Pastoral</v>
+      </c>
+      <c r="C198">
+        <f>C81</f>
+        <v>0.49402322991933489</v>
+      </c>
+      <c r="D198">
+        <f t="shared" ref="D198:E198" si="116">D81</f>
+        <v>0.48640304349731928</v>
+      </c>
+      <c r="E198">
+        <f t="shared" si="116"/>
+        <v>0</v>
+      </c>
+      <c r="H198" s="4"/>
+      <c r="I198" s="4"/>
+      <c r="J198" s="4"/>
+      <c r="K198" s="4"/>
+    </row>
+    <row r="199" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B199" t="str">
+        <f t="shared" si="99"/>
+        <v>Agropastoral</v>
+      </c>
+      <c r="C199">
+        <f t="shared" ref="C199" si="117">C82</f>
+        <v>0</v>
+      </c>
+      <c r="D199" s="40">
+        <f>D82*I92</f>
+        <v>2.0155321336554435</v>
+      </c>
+      <c r="E199" s="40">
+        <f>E82*I92</f>
+        <v>1.6881374851844733</v>
+      </c>
+      <c r="H199" s="4"/>
+      <c r="I199" s="4"/>
+      <c r="J199" s="4"/>
+      <c r="K199" s="4"/>
+    </row>
+    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B200" t="str">
+        <f>B191</f>
+        <v>Mixed</v>
+      </c>
+      <c r="C200">
+        <f t="shared" ref="C200:D200" si="118">C83</f>
+        <v>0</v>
+      </c>
+      <c r="D200" s="40">
+        <f t="shared" si="118"/>
+        <v>0</v>
+      </c>
+      <c r="E200" s="40">
+        <f>E83*I91</f>
+        <v>0.50175523211264639</v>
+      </c>
+      <c r="H200" s="4"/>
+      <c r="I200" s="4"/>
+      <c r="J200" s="4"/>
+      <c r="K200" s="4"/>
+    </row>
+    <row r="201" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B201" t="str">
+        <f t="shared" si="99"/>
+        <v>Cowcalf</v>
+      </c>
+      <c r="C201">
+        <f t="shared" ref="C201:E201" si="119">C84</f>
+        <v>2.0019220309243413E-2</v>
+      </c>
+      <c r="D201">
+        <f t="shared" si="119"/>
+        <v>9.2522672890536062E-2</v>
+      </c>
+      <c r="E201">
+        <f t="shared" si="119"/>
+        <v>0.15001904223920623</v>
+      </c>
+      <c r="H201" s="4"/>
+      <c r="I201" s="4"/>
+      <c r="J201" s="4"/>
+      <c r="K201" s="4"/>
+    </row>
+    <row r="202" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B202" t="str">
+        <f t="shared" si="99"/>
+        <v>Finisher</v>
+      </c>
+      <c r="C202">
+        <f t="shared" ref="C202:E202" si="120">C85</f>
+        <v>5.3182961871764585</v>
+      </c>
+      <c r="D202">
+        <f t="shared" si="120"/>
+        <v>7.088110217691594</v>
+      </c>
+      <c r="E202">
+        <f t="shared" si="120"/>
+        <v>6.1560286644571258</v>
+      </c>
+      <c r="H202" s="4"/>
+      <c r="I202" s="4"/>
+      <c r="J202" s="4"/>
+      <c r="K202" s="4"/>
+    </row>
+    <row r="203" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B203" t="str">
+        <f t="shared" si="99"/>
+        <v>Dairy</v>
+      </c>
+      <c r="C203">
+        <f t="shared" ref="C203:E203" si="121">C86</f>
+        <v>3.0271361942572905E-2</v>
+      </c>
+      <c r="D203">
+        <f t="shared" si="121"/>
+        <v>1.4765740788097195</v>
+      </c>
+      <c r="E203">
+        <f t="shared" si="121"/>
+        <v>6.3853780054327789</v>
+      </c>
+      <c r="H203" s="4"/>
+      <c r="I203" s="4"/>
+      <c r="J203" s="4"/>
+      <c r="K203" s="4"/>
+    </row>
+    <row r="204" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B204" t="str">
+        <f t="shared" si="99"/>
+        <v>Sheep</v>
+      </c>
+      <c r="C204">
+        <f t="shared" ref="C204:E204" si="122">C87</f>
+        <v>11.794047385286973</v>
+      </c>
+      <c r="D204">
+        <f t="shared" si="122"/>
+        <v>9.6481198260451801</v>
+      </c>
+      <c r="E204">
+        <f t="shared" si="122"/>
+        <v>9.0810136627013929</v>
+      </c>
+      <c r="H204" s="4"/>
+      <c r="I204" s="4"/>
+      <c r="J204" s="4"/>
+      <c r="K204" s="4"/>
+    </row>
+    <row r="205" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H205" s="4"/>
+      <c r="I205" s="4"/>
+      <c r="J205" s="4"/>
+      <c r="K205" s="4"/>
+    </row>
+    <row r="206" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A206" t="str">
+        <f>H92</f>
+        <v>-20% Mixed:Agropastoral</v>
+      </c>
+      <c r="B206" s="42" t="str">
+        <f>B197</f>
+        <v>Animal populations (M hd) -- SA scenario specific</v>
+      </c>
+      <c r="C206" s="42"/>
+      <c r="D206" s="42"/>
+      <c r="E206" s="42"/>
+      <c r="H206" s="4"/>
+      <c r="I206" s="4"/>
+      <c r="J206" s="4"/>
+      <c r="K206" s="4"/>
+    </row>
+    <row r="207" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B207" t="str">
+        <f t="shared" si="99"/>
+        <v>Pastoral</v>
+      </c>
+      <c r="C207">
+        <f>C81</f>
+        <v>0.49402322991933489</v>
+      </c>
+      <c r="D207">
+        <f t="shared" ref="D207:E207" si="123">D81</f>
+        <v>0.48640304349731928</v>
+      </c>
+      <c r="E207">
+        <f t="shared" si="123"/>
+        <v>0</v>
+      </c>
+      <c r="H207" s="4"/>
+      <c r="I207" s="4"/>
+      <c r="J207" s="4"/>
+      <c r="K207" s="4"/>
+    </row>
+    <row r="208" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B208" t="str">
+        <f t="shared" si="99"/>
+        <v>Agropastoral</v>
+      </c>
+      <c r="C208">
+        <f t="shared" ref="C208" si="124">C82</f>
+        <v>0</v>
+      </c>
+      <c r="D208" s="40">
+        <f>D82*I91</f>
+        <v>3.2752397171900953</v>
+      </c>
+      <c r="E208" s="40">
+        <f>E82*I91</f>
+        <v>2.7432234134247691</v>
+      </c>
+      <c r="H208" s="4"/>
+      <c r="I208" s="4"/>
+      <c r="J208" s="4"/>
+      <c r="K208" s="4"/>
+    </row>
+    <row r="209" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B209" t="str">
+        <f t="shared" si="99"/>
+        <v>Mixed</v>
+      </c>
+      <c r="C209">
+        <f t="shared" ref="C209:D209" si="125">C83</f>
+        <v>0</v>
+      </c>
+      <c r="D209" s="40">
+        <f t="shared" si="125"/>
+        <v>0</v>
+      </c>
+      <c r="E209" s="40">
+        <f>E83*I92</f>
+        <v>0.30877245053085933</v>
+      </c>
+      <c r="H209" s="4"/>
+      <c r="I209" s="4"/>
+      <c r="J209" s="4"/>
+      <c r="K209" s="4"/>
+    </row>
+    <row r="210" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B210" t="str">
+        <f t="shared" si="99"/>
+        <v>Cowcalf</v>
+      </c>
+      <c r="C210">
+        <f t="shared" ref="C210:E210" si="126">C84</f>
+        <v>2.0019220309243413E-2</v>
+      </c>
+      <c r="D210">
+        <f t="shared" si="126"/>
+        <v>9.2522672890536062E-2</v>
+      </c>
+      <c r="E210">
+        <f t="shared" si="126"/>
+        <v>0.15001904223920623</v>
+      </c>
+      <c r="H210" s="4"/>
+      <c r="I210" s="4"/>
+      <c r="J210" s="4"/>
+      <c r="K210" s="4"/>
+    </row>
+    <row r="211" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B211" t="str">
+        <f t="shared" si="99"/>
+        <v>Finisher</v>
+      </c>
+      <c r="C211">
+        <f t="shared" ref="C211:E211" si="127">C85</f>
+        <v>5.3182961871764585</v>
+      </c>
+      <c r="D211">
+        <f t="shared" si="127"/>
+        <v>7.088110217691594</v>
+      </c>
+      <c r="E211">
+        <f t="shared" si="127"/>
+        <v>6.1560286644571258</v>
+      </c>
+      <c r="H211" s="4"/>
+      <c r="I211" s="4"/>
+      <c r="J211" s="4"/>
+      <c r="K211" s="4"/>
+    </row>
+    <row r="212" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B212" t="str">
+        <f t="shared" si="99"/>
+        <v>Dairy</v>
+      </c>
+      <c r="C212">
+        <f t="shared" ref="C212:E212" si="128">C86</f>
+        <v>3.0271361942572905E-2</v>
+      </c>
+      <c r="D212">
+        <f t="shared" si="128"/>
+        <v>1.4765740788097195</v>
+      </c>
+      <c r="E212">
+        <f t="shared" si="128"/>
+        <v>6.3853780054327789</v>
+      </c>
+      <c r="H212" s="4"/>
+      <c r="I212" s="4"/>
+      <c r="J212" s="4"/>
+      <c r="K212" s="4"/>
+    </row>
+    <row r="213" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B213" t="str">
+        <f t="shared" si="99"/>
+        <v>Sheep</v>
+      </c>
+      <c r="C213">
+        <f t="shared" ref="C213:E213" si="129">C87</f>
+        <v>11.794047385286973</v>
+      </c>
+      <c r="D213">
+        <f t="shared" si="129"/>
+        <v>9.6481198260451801</v>
+      </c>
+      <c r="E213">
+        <f t="shared" si="129"/>
+        <v>9.0810136627013929</v>
+      </c>
+      <c r="H213" s="4"/>
+      <c r="I213" s="4"/>
+      <c r="J213" s="4"/>
+      <c r="K213" s="4"/>
+    </row>
+    <row r="214" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H214" s="4"/>
+      <c r="I214" s="4"/>
+      <c r="J214" s="4"/>
+      <c r="K214" s="4"/>
+    </row>
+    <row r="215" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A215" t="str">
+        <f>H93</f>
+        <v>+20% Cowcalf:Finisher</v>
+      </c>
+      <c r="B215" s="42" t="str">
+        <f>B206</f>
+        <v>Animal populations (M hd) -- SA scenario specific</v>
+      </c>
+      <c r="C215" s="42"/>
+      <c r="D215" s="42"/>
+      <c r="E215" s="42"/>
+      <c r="H215" s="4"/>
+      <c r="I215" s="4"/>
+      <c r="J215" s="4"/>
+      <c r="K215" s="4"/>
+    </row>
+    <row r="216" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B216" t="str">
+        <f t="shared" si="99"/>
+        <v>Pastoral</v>
+      </c>
+      <c r="C216">
+        <f>C81</f>
+        <v>0.49402322991933489</v>
+      </c>
+      <c r="D216">
+        <f t="shared" ref="D216:E216" si="130">D81</f>
+        <v>0.48640304349731928</v>
+      </c>
+      <c r="E216">
+        <f t="shared" si="130"/>
+        <v>0</v>
+      </c>
+      <c r="H216" s="4"/>
+      <c r="I216" s="4"/>
+      <c r="J216" s="4"/>
+      <c r="K216" s="4"/>
+    </row>
+    <row r="217" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B217" t="str">
+        <f t="shared" si="99"/>
+        <v>Agropastoral</v>
+      </c>
+      <c r="C217">
+        <f t="shared" ref="C217:E217" si="131">C82</f>
+        <v>0</v>
+      </c>
+      <c r="D217">
+        <f t="shared" si="131"/>
+        <v>2.5194151670693041</v>
+      </c>
+      <c r="E217">
+        <f t="shared" si="131"/>
+        <v>2.1101718564805916</v>
+      </c>
+      <c r="H217" s="4"/>
+      <c r="I217" s="4"/>
+      <c r="J217" s="4"/>
+      <c r="K217" s="4"/>
+    </row>
+    <row r="218" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B218" t="str">
+        <f t="shared" si="99"/>
+        <v>Mixed</v>
+      </c>
+      <c r="C218">
+        <f t="shared" ref="C218:E218" si="132">C83</f>
+        <v>0</v>
+      </c>
+      <c r="D218">
+        <f t="shared" si="132"/>
+        <v>0</v>
+      </c>
+      <c r="E218">
+        <f t="shared" si="132"/>
+        <v>0.38596556316357417</v>
+      </c>
+      <c r="H218" s="4"/>
+      <c r="I218" s="4"/>
+      <c r="J218" s="4"/>
+      <c r="K218" s="4"/>
+    </row>
+    <row r="219" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B219" t="str">
+        <f t="shared" si="99"/>
+        <v>Cowcalf</v>
+      </c>
+      <c r="C219" s="40">
+        <f>C84*I93</f>
+        <v>2.6024986402016437E-2</v>
+      </c>
+      <c r="D219" s="40">
+        <f>D84*I93</f>
+        <v>0.12027947475769689</v>
+      </c>
+      <c r="E219" s="40">
+        <f>E84*I93</f>
+        <v>0.1950247549109681</v>
+      </c>
+      <c r="H219" s="4"/>
+      <c r="I219" s="4"/>
+      <c r="J219" s="4"/>
+      <c r="K219" s="4"/>
+    </row>
+    <row r="220" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B220" t="str">
+        <f t="shared" si="99"/>
+        <v>Finisher</v>
+      </c>
+      <c r="C220" s="40">
+        <f>C85*I94</f>
+        <v>4.2546369497411671</v>
+      </c>
+      <c r="D220" s="40">
+        <f>D85*I94</f>
+        <v>5.6704881741532756</v>
+      </c>
+      <c r="E220" s="40">
+        <f>E85*I94</f>
+        <v>4.9248229315657008</v>
+      </c>
+      <c r="H220" s="4"/>
+      <c r="I220" s="4"/>
+      <c r="J220" s="4"/>
+      <c r="K220" s="4"/>
+    </row>
+    <row r="221" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B221" t="str">
+        <f t="shared" si="99"/>
+        <v>Dairy</v>
+      </c>
+      <c r="C221">
+        <f t="shared" ref="C221:E221" si="133">C86</f>
+        <v>3.0271361942572905E-2</v>
+      </c>
+      <c r="D221">
+        <f t="shared" si="133"/>
+        <v>1.4765740788097195</v>
+      </c>
+      <c r="E221">
+        <f t="shared" si="133"/>
+        <v>6.3853780054327789</v>
+      </c>
+      <c r="H221" s="4"/>
+      <c r="I221" s="4"/>
+      <c r="J221" s="4"/>
+      <c r="K221" s="4"/>
+    </row>
+    <row r="222" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B222" t="str">
+        <f t="shared" si="99"/>
+        <v>Sheep</v>
+      </c>
+      <c r="C222">
+        <f t="shared" ref="C222:E222" si="134">C87</f>
+        <v>11.794047385286973</v>
+      </c>
+      <c r="D222">
+        <f t="shared" si="134"/>
+        <v>9.6481198260451801</v>
+      </c>
+      <c r="E222">
+        <f t="shared" si="134"/>
+        <v>9.0810136627013929</v>
+      </c>
+      <c r="H222" s="4"/>
+      <c r="I222" s="4"/>
+      <c r="J222" s="4"/>
+      <c r="K222" s="4"/>
+    </row>
+    <row r="223" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H223" s="4"/>
+      <c r="I223" s="4"/>
+      <c r="J223" s="4"/>
+      <c r="K223" s="4"/>
+    </row>
+    <row r="224" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A224" t="str">
+        <f>H94</f>
+        <v>-20% Cowcalf:Finisher</v>
+      </c>
+      <c r="B224" s="42" t="str">
+        <f>B215</f>
+        <v>Animal populations (M hd) -- SA scenario specific</v>
+      </c>
+      <c r="C224" s="42"/>
+      <c r="D224" s="42"/>
+      <c r="E224" s="42"/>
+      <c r="H224" s="4"/>
+      <c r="I224" s="4"/>
+      <c r="J224" s="4"/>
+      <c r="K224" s="4"/>
+    </row>
+    <row r="225" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B225" t="str">
+        <f t="shared" si="99"/>
+        <v>Pastoral</v>
+      </c>
+      <c r="C225">
+        <f>C81</f>
+        <v>0.49402322991933489</v>
+      </c>
+      <c r="D225">
+        <f t="shared" ref="D225:E225" si="135">D81</f>
+        <v>0.48640304349731928</v>
+      </c>
+      <c r="E225">
+        <f t="shared" si="135"/>
+        <v>0</v>
+      </c>
+      <c r="H225" s="4"/>
+      <c r="I225" s="4"/>
+      <c r="J225" s="4"/>
+      <c r="K225" s="4"/>
+    </row>
+    <row r="226" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B226" t="str">
+        <f t="shared" si="99"/>
+        <v>Agropastoral</v>
+      </c>
+      <c r="C226">
+        <f t="shared" ref="C226:E226" si="136">C82</f>
+        <v>0</v>
+      </c>
+      <c r="D226">
+        <f t="shared" si="136"/>
+        <v>2.5194151670693041</v>
+      </c>
+      <c r="E226">
+        <f t="shared" si="136"/>
+        <v>2.1101718564805916</v>
+      </c>
+      <c r="H226" s="4"/>
+      <c r="I226" s="4"/>
+      <c r="J226" s="4"/>
+      <c r="K226" s="4"/>
+    </row>
+    <row r="227" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B227" t="str">
+        <f t="shared" si="99"/>
+        <v>Mixed</v>
+      </c>
+      <c r="C227">
+        <f t="shared" ref="C227:E227" si="137">C83</f>
+        <v>0</v>
+      </c>
+      <c r="D227">
+        <f t="shared" si="137"/>
+        <v>0</v>
+      </c>
+      <c r="E227">
+        <f t="shared" si="137"/>
+        <v>0.38596556316357417</v>
+      </c>
+      <c r="H227" s="4"/>
+      <c r="I227" s="4"/>
+      <c r="J227" s="4"/>
+      <c r="K227" s="4"/>
+    </row>
+    <row r="228" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B228" t="str">
+        <f t="shared" si="99"/>
+        <v>Cowcalf</v>
+      </c>
+      <c r="C228" s="40">
+        <f>C84*I94</f>
+        <v>1.6015376247394731E-2</v>
+      </c>
+      <c r="D228" s="40">
+        <f>D84*I94</f>
+        <v>7.4018138312428858E-2</v>
+      </c>
+      <c r="E228" s="40">
+        <f>E84*I94</f>
+        <v>0.12001523379136499</v>
+      </c>
+      <c r="H228" s="4"/>
+      <c r="I228" s="4"/>
+      <c r="J228" s="4"/>
+      <c r="K228" s="4"/>
+    </row>
+    <row r="229" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B229" t="str">
+        <f t="shared" si="99"/>
+        <v>Finisher</v>
+      </c>
+      <c r="C229" s="40">
+        <f>C85*I93</f>
+        <v>6.9137850433293959</v>
+      </c>
+      <c r="D229" s="40">
+        <f>D85*I93</f>
+        <v>9.2145432829990721</v>
+      </c>
+      <c r="E229" s="40">
+        <f>E85*I93</f>
+        <v>8.0028372637942642</v>
+      </c>
+      <c r="H229" s="4"/>
+      <c r="I229" s="4"/>
+      <c r="J229" s="4"/>
+      <c r="K229" s="4"/>
+    </row>
+    <row r="230" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B230" t="str">
+        <f t="shared" si="99"/>
+        <v>Dairy</v>
+      </c>
+      <c r="C230">
+        <f t="shared" ref="C230:E230" si="138">C86</f>
+        <v>3.0271361942572905E-2</v>
+      </c>
+      <c r="D230">
+        <f t="shared" si="138"/>
+        <v>1.4765740788097195</v>
+      </c>
+      <c r="E230">
+        <f t="shared" si="138"/>
+        <v>6.3853780054327789</v>
+      </c>
+      <c r="H230" s="4"/>
+      <c r="I230" s="4"/>
+      <c r="J230" s="4"/>
+      <c r="K230" s="4"/>
+    </row>
+    <row r="231" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B231" t="str">
+        <f t="shared" si="99"/>
+        <v>Sheep</v>
+      </c>
+      <c r="C231">
+        <f t="shared" ref="C231:E231" si="139">C87</f>
+        <v>11.794047385286973</v>
+      </c>
+      <c r="D231">
+        <f t="shared" si="139"/>
+        <v>9.6481198260451801</v>
+      </c>
+      <c r="E231">
+        <f t="shared" si="139"/>
+        <v>9.0810136627013929</v>
+      </c>
+      <c r="H231" s="4"/>
+      <c r="I231" s="4"/>
+      <c r="J231" s="4"/>
+      <c r="K231" s="4"/>
+    </row>
+    <row r="232" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H232" s="4"/>
+      <c r="I232" s="4"/>
+      <c r="J232" s="4"/>
+      <c r="K232" s="4"/>
+    </row>
+    <row r="233" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A233" t="str">
+        <f>H95</f>
+        <v>+20% Commercial:Subsistence</v>
+      </c>
+      <c r="B233" s="42" t="str">
+        <f>B89</f>
+        <v>Animal populations (M hd) -- SA scenario specific</v>
+      </c>
+      <c r="C233" s="42"/>
+      <c r="D233" s="42"/>
+      <c r="E233" s="42"/>
+      <c r="H233" s="4"/>
+      <c r="I233" s="4"/>
+      <c r="J233" s="4"/>
+      <c r="K233" s="4"/>
+    </row>
+    <row r="234" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B234" t="str">
+        <f t="shared" si="99"/>
+        <v>Pastoral</v>
+      </c>
+      <c r="C234" s="40">
+        <f>C81*I96</f>
+        <v>0.39521858393546794</v>
+      </c>
+      <c r="D234" s="40">
+        <f>D81*I96</f>
+        <v>0.38912243479785547</v>
+      </c>
+      <c r="E234" s="40">
+        <f>E81*I96</f>
+        <v>0</v>
+      </c>
+      <c r="H234" s="4"/>
+      <c r="I234" s="4"/>
+      <c r="J234" s="4"/>
+      <c r="K234" s="4"/>
+    </row>
+    <row r="235" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B235" t="str">
+        <f t="shared" si="99"/>
+        <v>Agropastoral</v>
+      </c>
+      <c r="C235" s="40">
+        <f t="shared" ref="C235" si="140">C82</f>
+        <v>0</v>
+      </c>
+      <c r="D235" s="40">
+        <f>D82*I96</f>
+        <v>2.0155321336554435</v>
+      </c>
+      <c r="E235" s="40">
+        <f>E82*I96</f>
+        <v>1.6881374851844733</v>
+      </c>
+      <c r="H235" s="4"/>
+      <c r="I235" s="4"/>
+      <c r="J235" s="4"/>
+      <c r="K235" s="4"/>
+    </row>
+    <row r="236" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B236" t="str">
+        <f t="shared" ref="B236:B249" si="141">B227</f>
+        <v>Mixed</v>
+      </c>
+      <c r="C236" s="40">
+        <f>C83*I96</f>
+        <v>0</v>
+      </c>
+      <c r="D236" s="40">
+        <f>D83*I96</f>
+        <v>0</v>
+      </c>
+      <c r="E236" s="40">
+        <f>E83*I96</f>
+        <v>0.30877245053085933</v>
+      </c>
+      <c r="H236" s="4"/>
+      <c r="I236" s="4"/>
+      <c r="J236" s="4"/>
+      <c r="K236" s="4"/>
+    </row>
+    <row r="237" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B237" t="str">
+        <f t="shared" si="141"/>
+        <v>Cowcalf</v>
+      </c>
+      <c r="C237" s="40">
+        <f>C84*I95</f>
+        <v>2.6024986402016437E-2</v>
+      </c>
+      <c r="D237" s="40">
+        <f>D84*I95</f>
+        <v>0.12027947475769689</v>
+      </c>
+      <c r="E237" s="40">
+        <f>E84*I95</f>
+        <v>0.1950247549109681</v>
+      </c>
+      <c r="H237" s="4"/>
+      <c r="I237" s="4"/>
+      <c r="J237" s="4"/>
+      <c r="K237" s="4"/>
+    </row>
+    <row r="238" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B238" t="str">
+        <f t="shared" si="141"/>
+        <v>Finisher</v>
+      </c>
+      <c r="C238" s="40">
+        <f>C85*I95</f>
+        <v>6.9137850433293959</v>
+      </c>
+      <c r="D238" s="40">
+        <f>D85*I95</f>
+        <v>9.2145432829990721</v>
+      </c>
+      <c r="E238" s="40">
+        <f>E85*I95</f>
+        <v>8.0028372637942642</v>
+      </c>
+      <c r="H238" s="4"/>
+      <c r="I238" s="4"/>
+      <c r="J238" s="4"/>
+      <c r="K238" s="4"/>
+    </row>
+    <row r="239" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B239" t="str">
+        <f t="shared" si="141"/>
+        <v>Dairy</v>
+      </c>
+      <c r="C239">
+        <f t="shared" ref="C239:E239" si="142">C86</f>
+        <v>3.0271361942572905E-2</v>
+      </c>
+      <c r="D239">
+        <f t="shared" si="142"/>
+        <v>1.4765740788097195</v>
+      </c>
+      <c r="E239">
+        <f t="shared" si="142"/>
+        <v>6.3853780054327789</v>
+      </c>
+      <c r="H239" s="4"/>
+      <c r="I239" s="4"/>
+      <c r="J239" s="4"/>
+      <c r="K239" s="4"/>
+    </row>
+    <row r="240" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B240" t="str">
+        <f t="shared" si="141"/>
+        <v>Sheep</v>
+      </c>
+      <c r="C240">
+        <f t="shared" ref="C240:E240" si="143">C87</f>
+        <v>11.794047385286973</v>
+      </c>
+      <c r="D240">
+        <f t="shared" si="143"/>
+        <v>9.6481198260451801</v>
+      </c>
+      <c r="E240">
+        <f t="shared" si="143"/>
+        <v>9.0810136627013929</v>
+      </c>
+      <c r="H240" s="4"/>
+      <c r="I240" s="4"/>
+      <c r="J240" s="4"/>
+      <c r="K240" s="4"/>
+    </row>
+    <row r="241" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H241" s="4"/>
+      <c r="I241" s="4"/>
+      <c r="J241" s="4"/>
+      <c r="K241" s="4"/>
+    </row>
+    <row r="242" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A242" s="36" t="str">
+        <f>H96</f>
+        <v>-20% Commercial:Subsistence</v>
+      </c>
+      <c r="B242" s="42" t="str">
+        <f>B233</f>
+        <v>Animal populations (M hd) -- SA scenario specific</v>
+      </c>
+      <c r="C242" s="42"/>
+      <c r="D242" s="42"/>
+      <c r="E242" s="42"/>
+      <c r="H242" s="4"/>
+      <c r="I242" s="4"/>
+      <c r="J242" s="4"/>
+      <c r="K242" s="4"/>
+    </row>
+    <row r="243" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B243" t="str">
+        <f t="shared" si="141"/>
+        <v>Pastoral</v>
+      </c>
+      <c r="C243" s="40">
+        <f>C81*I95</f>
+        <v>0.64223019889513533</v>
+      </c>
+      <c r="D243" s="40">
+        <f>D81*I95</f>
+        <v>0.63232395654651508</v>
+      </c>
+      <c r="E243" s="40">
+        <f>E81*I1014</f>
+        <v>0</v>
+      </c>
+      <c r="H243" s="4"/>
+      <c r="I243" s="4"/>
+      <c r="J243" s="4"/>
+      <c r="K243" s="4"/>
+    </row>
+    <row r="244" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B244" t="str">
+        <f t="shared" si="141"/>
+        <v>Agropastoral</v>
+      </c>
+      <c r="C244" s="40">
+        <f>C82*I95</f>
+        <v>0</v>
+      </c>
+      <c r="D244" s="40">
+        <f>D82*I95</f>
+        <v>3.2752397171900953</v>
+      </c>
+      <c r="E244" s="40">
+        <f>E82*I95</f>
+        <v>2.7432234134247691</v>
+      </c>
+      <c r="H244" s="4"/>
+      <c r="I244" s="4"/>
+      <c r="J244" s="4"/>
+      <c r="K244" s="4"/>
+    </row>
+    <row r="245" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B245" t="str">
+        <f t="shared" si="141"/>
+        <v>Mixed</v>
+      </c>
+      <c r="C245" s="40">
+        <f>C83*I95</f>
+        <v>0</v>
+      </c>
+      <c r="D245" s="40">
+        <f>D83*I95</f>
+        <v>0</v>
+      </c>
+      <c r="E245" s="40">
+        <f t="shared" ref="E245" si="144">E83</f>
+        <v>0.38596556316357417</v>
+      </c>
+      <c r="H245" s="4"/>
+      <c r="I245" s="4"/>
+      <c r="J245" s="4"/>
+      <c r="K245" s="4"/>
+    </row>
+    <row r="246" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B246" t="str">
+        <f t="shared" si="141"/>
+        <v>Cowcalf</v>
+      </c>
+      <c r="C246" s="40">
+        <f>C84*I96</f>
+        <v>1.6015376247394731E-2</v>
+      </c>
+      <c r="D246" s="40">
+        <f>D84*I96</f>
+        <v>7.4018138312428858E-2</v>
+      </c>
+      <c r="E246" s="40">
+        <f>E84*I96</f>
+        <v>0.12001523379136499</v>
+      </c>
+      <c r="H246" s="4"/>
+      <c r="I246" s="4"/>
+      <c r="J246" s="4"/>
+      <c r="K246" s="4"/>
+    </row>
+    <row r="247" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B247" t="str">
+        <f t="shared" si="141"/>
+        <v>Finisher</v>
+      </c>
+      <c r="C247" s="40">
+        <f>C85*I96</f>
+        <v>4.2546369497411671</v>
+      </c>
+      <c r="D247" s="40">
+        <f>D85*I96</f>
+        <v>5.6704881741532756</v>
+      </c>
+      <c r="E247" s="40">
+        <f>E85*I96</f>
+        <v>4.9248229315657008</v>
+      </c>
+      <c r="H247" s="4"/>
+      <c r="I247" s="4"/>
+      <c r="J247" s="4"/>
+      <c r="K247" s="4"/>
+    </row>
+    <row r="248" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B248" t="str">
+        <f t="shared" si="141"/>
+        <v>Dairy</v>
+      </c>
+      <c r="C248">
+        <f t="shared" ref="C248:E248" si="145">C86</f>
+        <v>3.0271361942572905E-2</v>
+      </c>
+      <c r="D248">
+        <f t="shared" si="145"/>
+        <v>1.4765740788097195</v>
+      </c>
+      <c r="E248">
+        <f t="shared" si="145"/>
+        <v>6.3853780054327789</v>
+      </c>
+      <c r="H248" s="4"/>
+      <c r="I248" s="4"/>
+      <c r="J248" s="4"/>
+      <c r="K248" s="4"/>
+    </row>
+    <row r="249" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B249" t="str">
+        <f t="shared" si="141"/>
+        <v>Sheep</v>
+      </c>
+      <c r="C249">
+        <f t="shared" ref="C249:E249" si="146">C87</f>
+        <v>11.794047385286973</v>
+      </c>
+      <c r="D249">
+        <f t="shared" si="146"/>
+        <v>9.6481198260451801</v>
+      </c>
+      <c r="E249">
+        <f t="shared" si="146"/>
+        <v>9.0810136627013929</v>
+      </c>
+      <c r="H249" s="4"/>
+      <c r="I249" s="4"/>
+      <c r="J249" s="4"/>
+      <c r="K249" s="4"/>
+    </row>
+    <row r="250" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H250" s="4"/>
+      <c r="I250" s="4"/>
+      <c r="J250" s="4"/>
+      <c r="K250" s="4"/>
+    </row>
+    <row r="251" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B251" s="45" t="s">
+        <v>162</v>
+      </c>
+      <c r="C251" s="47"/>
+      <c r="D251" s="47"/>
+      <c r="E251" s="47"/>
+      <c r="H251" s="4"/>
+      <c r="I251" s="4"/>
+      <c r="J251" s="4"/>
+      <c r="K251" s="4"/>
+    </row>
+    <row r="252" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A252" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B252" t="str">
+        <f>H79</f>
+        <v>+20% Herd size</v>
+      </c>
+      <c r="C252">
+        <f>(SUM(C2:C7)+SUM(C90:C94))*$I1*1000000</f>
+        <v>2378123569.704309</v>
+      </c>
+      <c r="D252">
+        <f t="shared" ref="D252:E252" si="147">(SUM(D2:D7)+SUM(D90:D94))*$I1*1000000</f>
+        <v>4398215560.7369394</v>
+      </c>
+      <c r="E252">
+        <f t="shared" si="147"/>
+        <v>4298222229.7411747</v>
+      </c>
+      <c r="H252" s="4"/>
+      <c r="I252" s="4"/>
+      <c r="J252" s="4"/>
+      <c r="K252" s="4"/>
+    </row>
+    <row r="253" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B253" t="str">
+        <f t="shared" ref="B253:B269" si="148">H80</f>
+        <v xml:space="preserve">-20% Herd size </v>
+      </c>
+      <c r="C253">
+        <f>(SUM(C2:C7)+SUM(C99:C103))*$I1*1000000</f>
+        <v>1808742679.2275615</v>
+      </c>
+      <c r="D253">
+        <f t="shared" ref="D253:E253" si="149">(SUM(D2:D7)+SUM(D99:D103))*$I1*1000000</f>
+        <v>3403765313.7001042</v>
+      </c>
+      <c r="E253">
+        <f t="shared" si="149"/>
+        <v>3438910671.040802</v>
+      </c>
+      <c r="H253" s="4"/>
+      <c r="I253" s="4"/>
+      <c r="J253" s="4"/>
+      <c r="K253" s="4"/>
+    </row>
+    <row r="254" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B254" t="str">
+        <f t="shared" si="148"/>
+        <v>+20% Zebu</v>
+      </c>
+      <c r="C254">
+        <f>(SUM(C2:C7)+SUM(C108:C112))*$I1*1000000</f>
+        <v>2036495035.4182603</v>
+      </c>
+      <c r="D254">
+        <f t="shared" ref="D254:E254" si="150">(SUM(D2:D7)+SUM(D108:D112))*$I1*1000000</f>
+        <v>3801545412.5148387</v>
+      </c>
+      <c r="E254">
+        <f t="shared" si="150"/>
+        <v>3782635294.5209508</v>
+      </c>
+      <c r="H254" s="4"/>
+      <c r="I254" s="4"/>
+      <c r="J254" s="4"/>
+      <c r="K254" s="4"/>
+    </row>
+    <row r="255" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B255" t="str">
+        <f t="shared" si="148"/>
+        <v>-20% Zebu</v>
+      </c>
+      <c r="C255">
+        <f>(SUM(C2:C7)+SUM(C117:C121))*$I1*1000000</f>
+        <v>2036495035.4182603</v>
+      </c>
+      <c r="D255">
+        <f t="shared" ref="D255:E255" si="151">(SUM(D2:D7)+SUM(D117:D121))*$I1*1000000</f>
+        <v>3801545412.5148387</v>
+      </c>
+      <c r="E255">
+        <f t="shared" si="151"/>
+        <v>3782635294.5209508</v>
+      </c>
+      <c r="H255" s="4"/>
+      <c r="I255" s="4"/>
+      <c r="J255" s="4"/>
+      <c r="K255" s="4"/>
+    </row>
+    <row r="256" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B256" t="str">
+        <f t="shared" si="148"/>
+        <v>+20% Boran</v>
+      </c>
+      <c r="C256">
+        <f>(SUM(C2:C7)+SUM(C126:C130))*$I1*1000000</f>
+        <v>2036495035.4182603</v>
+      </c>
+      <c r="D256">
+        <f t="shared" ref="D256:E256" si="152">(SUM(D2:D7)+SUM(D126:D130))*$I1*1000000</f>
+        <v>3801545412.5148387</v>
+      </c>
+      <c r="E256">
+        <f t="shared" si="152"/>
+        <v>3782635294.5209508</v>
+      </c>
+      <c r="H256" s="4"/>
+      <c r="I256" s="4"/>
+      <c r="J256" s="4"/>
+      <c r="K256" s="4"/>
+    </row>
+    <row r="257" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B257" t="str">
+        <f t="shared" si="148"/>
+        <v>-20% Boran</v>
+      </c>
+      <c r="C257">
+        <f>(SUM(C2:C7)+SUM(C135:C139))*$I1*1000000</f>
+        <v>2036495035.4182603</v>
+      </c>
+      <c r="D257">
+        <f t="shared" ref="D257:E257" si="153">(SUM(D2:D7)+SUM(D135:D139))*$I1*1000000</f>
+        <v>3801545412.5148387</v>
+      </c>
+      <c r="E257">
+        <f t="shared" si="153"/>
+        <v>3782635294.5209508</v>
+      </c>
+      <c r="H257" s="4"/>
+      <c r="I257" s="4"/>
+      <c r="J257" s="4"/>
+      <c r="K257" s="4"/>
+    </row>
+    <row r="258" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B258" t="str">
+        <f t="shared" si="148"/>
+        <v>+20% Exotic</v>
+      </c>
+      <c r="C258">
+        <f>(SUM(C2:C7)+SUM(C144:C148))*$I1*1000000</f>
+        <v>2036495035.4182603</v>
+      </c>
+      <c r="D258">
+        <f t="shared" ref="D258:E258" si="154">(SUM(D2:D7)+SUM(D144:D148))*$I1*1000000</f>
+        <v>3801545412.5148387</v>
+      </c>
+      <c r="E258">
+        <f t="shared" si="154"/>
+        <v>3782635294.5209508</v>
+      </c>
+      <c r="H258" s="4"/>
+      <c r="I258" s="4"/>
+      <c r="J258" s="4"/>
+      <c r="K258" s="4"/>
+    </row>
+    <row r="259" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B259" t="str">
+        <f t="shared" si="148"/>
+        <v>-20% Exotic</v>
+      </c>
+      <c r="C259">
+        <f>(SUM(C2:C7)+SUM(C153:C157))*$I1*1000000</f>
+        <v>2036495035.4182603</v>
+      </c>
+      <c r="D259">
+        <f t="shared" ref="D259:E259" si="155">(SUM(D2:D7)+SUM(D153:D157))*$I1*1000000</f>
+        <v>3801545412.5148387</v>
+      </c>
+      <c r="E259">
+        <f t="shared" si="155"/>
+        <v>3782635294.5209508</v>
+      </c>
+      <c r="H259" s="4"/>
+      <c r="I259" s="4"/>
+      <c r="J259" s="4"/>
+      <c r="K259" s="4"/>
+    </row>
+    <row r="260" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B260" t="str">
+        <f t="shared" si="148"/>
+        <v>+20% Finisher:Breeder</v>
+      </c>
+      <c r="C260">
+        <f>(SUM(C2:C7)+SUM(C162:C166))*$I1*1000000</f>
+        <v>2036495035.4182603</v>
+      </c>
+      <c r="D260">
+        <f t="shared" ref="D260:E260" si="156">(SUM(D2:D7)+SUM(D162:D166))*$I1*1000000</f>
+        <v>3801545412.5148387</v>
+      </c>
+      <c r="E260">
+        <f t="shared" si="156"/>
+        <v>3782635294.5209508</v>
+      </c>
+      <c r="H260" s="4"/>
+      <c r="I260" s="4"/>
+      <c r="J260" s="4"/>
+      <c r="K260" s="4"/>
+    </row>
+    <row r="261" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B261" t="str">
+        <f t="shared" si="148"/>
+        <v>-20% Finisher:Breeder</v>
+      </c>
+      <c r="C261">
+        <f>(SUM(C2:C7)+SUM(C171:C175))*$I1*1000000</f>
+        <v>2036495035.4182603</v>
+      </c>
+      <c r="D261">
+        <f t="shared" ref="D261:E261" si="157">(SUM(D2:D7)+SUM(D171:D175))*$I1*1000000</f>
+        <v>3801545412.5148387</v>
+      </c>
+      <c r="E261">
+        <f t="shared" si="157"/>
+        <v>3782635294.5209508</v>
+      </c>
+      <c r="H261" s="4"/>
+      <c r="I261" s="4"/>
+      <c r="J261" s="4"/>
+      <c r="K261" s="4"/>
+    </row>
+    <row r="262" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B262" t="str">
+        <f t="shared" si="148"/>
+        <v>+20% Pastoral:Agropastoral</v>
+      </c>
+      <c r="C262">
+        <f>(SUM(C2:C7)+SUM(C180:C184))*$I1*1000000</f>
+        <v>2065432386.6993058</v>
+      </c>
+      <c r="D262">
+        <f t="shared" ref="D262:E262" si="158">(SUM(D2:D7)+SUM(D180:D184))*$I1*1000000</f>
+        <v>3731653452.0093141</v>
+      </c>
+      <c r="E262">
+        <f t="shared" si="158"/>
+        <v>3700233252.7055969</v>
+      </c>
+      <c r="H262" s="4"/>
+      <c r="I262" s="4"/>
+      <c r="J262" s="4"/>
+      <c r="K262" s="4"/>
+    </row>
+    <row r="263" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B263" t="str">
+        <f t="shared" si="148"/>
+        <v>-20% Pastoral:Agropastoral</v>
+      </c>
+      <c r="C263">
+        <f>(SUM(C2:C7)+SUM(C189:C193))*$I1*1000000</f>
+        <v>2017203467.8975637</v>
+      </c>
+      <c r="D263">
+        <f t="shared" ref="D263:E263" si="159">(SUM(D2:D7)+SUM(D189:D193))*$I1*1000000</f>
+        <v>3930125853.087944</v>
+      </c>
+      <c r="E263">
+        <f t="shared" si="159"/>
+        <v>3906238357.2439823</v>
+      </c>
+      <c r="H263" s="4"/>
+      <c r="I263" s="4"/>
+      <c r="J263" s="4"/>
+      <c r="K263" s="4"/>
+    </row>
+    <row r="264" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B264" t="str">
+        <f t="shared" si="148"/>
+        <v>+20% Mixed:Agropastoral</v>
+      </c>
+      <c r="C264">
+        <f>(SUM(C2:C7)+SUM(C198:C202))*$I1*1000000</f>
+        <v>2036495035.4182603</v>
+      </c>
+      <c r="D264">
+        <f t="shared" ref="D264:E264" si="160">(SUM(D2:D7)+SUM(D198:D202))*$I1*1000000</f>
+        <v>3703162452.2315316</v>
+      </c>
+      <c r="E264">
+        <f t="shared" si="160"/>
+        <v>3722841139.1514926</v>
+      </c>
+      <c r="H264" s="4"/>
+      <c r="I264" s="4"/>
+      <c r="J264" s="4"/>
+      <c r="K264" s="4"/>
+    </row>
+    <row r="265" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B265" t="str">
+        <f t="shared" si="148"/>
+        <v>-20% Mixed:Agropastoral</v>
+      </c>
+      <c r="C265">
+        <f>(SUM(C2:C7)+SUM(C207:C211))*$I1*1000000</f>
+        <v>2036495035.4182603</v>
+      </c>
+      <c r="D265">
+        <f t="shared" ref="D265:E265" si="161">(SUM(D2:D7)+SUM(D207:D211))*$I1*1000000</f>
+        <v>3949119852.9397993</v>
+      </c>
+      <c r="E265">
+        <f t="shared" si="161"/>
+        <v>3891166432.9467192</v>
+      </c>
+      <c r="H265" s="4"/>
+      <c r="I265" s="4"/>
+      <c r="J265" s="4"/>
+      <c r="K265" s="4"/>
+    </row>
+    <row r="266" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B266" t="str">
+        <f t="shared" si="148"/>
+        <v>+20% Cowcalf:Finisher</v>
+      </c>
+      <c r="C266">
+        <f>(SUM(C2:C7)+SUM(C216:C220))*$I1*1000000</f>
+        <v>1829988619.1184125</v>
+      </c>
+      <c r="D266">
+        <f t="shared" ref="D266:E266" si="162">(SUM(D2:D7)+SUM(D216:D220))*$I1*1000000</f>
+        <v>3530174781.2315001</v>
+      </c>
+      <c r="E266">
+        <f t="shared" si="162"/>
+        <v>3551030216.0830808</v>
+      </c>
+      <c r="H266" s="4"/>
+      <c r="I266" s="4"/>
+      <c r="J266" s="4"/>
+      <c r="K266" s="4"/>
+    </row>
+    <row r="267" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B267" t="str">
+        <f t="shared" si="148"/>
+        <v>-20% Cowcalf:Finisher</v>
+      </c>
+      <c r="C267">
+        <f>(SUM(C2:C7)+SUM(C225:C229))*$I1*1000000</f>
+        <v>2347231846.0531096</v>
+      </c>
+      <c r="D267">
+        <f t="shared" ref="D267:E267" si="163">(SUM(D2:D7)+SUM(D225:D229))*$I1*1000000</f>
+        <v>4213117613.1379623</v>
+      </c>
+      <c r="E267">
+        <f t="shared" si="163"/>
+        <v>4137365701.6425877</v>
+      </c>
+      <c r="H267" s="4"/>
+      <c r="I267" s="4"/>
+      <c r="J267" s="4"/>
+      <c r="K267" s="4"/>
+    </row>
+    <row r="268" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B268" t="str">
+        <f t="shared" si="148"/>
+        <v>+20% Commercial:Subsistence</v>
+      </c>
+      <c r="C268">
+        <f>(SUM(C2:C7)+SUM(C234:C238))*$I1*1000000</f>
+        <v>2329894650.9025669</v>
+      </c>
+      <c r="D268">
+        <f t="shared" ref="D268:E268" si="164">(SUM(D2:D7)+SUM(D234:D238))*$I1*1000000</f>
+        <v>4104773160.399034</v>
+      </c>
+      <c r="E268">
+        <f t="shared" si="164"/>
+        <v>4054537314.459631</v>
+      </c>
+      <c r="H268" s="4"/>
+      <c r="I268" s="4"/>
+      <c r="J268" s="4"/>
+      <c r="K268" s="4"/>
+    </row>
+    <row r="269" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B269" t="str">
+        <f t="shared" si="148"/>
+        <v>-20% Commercial:Subsistence</v>
+      </c>
+      <c r="C269">
+        <f>(SUM(C2:C7)+SUM(C243:C247))*$I1*1000000</f>
+        <v>1856971598.0293036</v>
+      </c>
+      <c r="D269">
+        <f t="shared" ref="D269:E269" si="165">(SUM(D2:D7)+SUM(D243:D247))*$I1*1000000</f>
+        <v>3697207714.0380096</v>
+      </c>
+      <c r="E269">
+        <f t="shared" si="165"/>
+        <v>3659987699.8764505</v>
+      </c>
+      <c r="H269" s="4"/>
+      <c r="I269" s="4"/>
+      <c r="J269" s="4"/>
+      <c r="K269" s="4"/>
+    </row>
+    <row r="270" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B270" t="s">
+        <v>60</v>
+      </c>
+      <c r="C270">
+        <f>C86*$I4*1000000</f>
+        <v>6084543.7504571546</v>
+      </c>
+      <c r="D270">
+        <f t="shared" ref="D270:E270" si="166">D86*$I4*1000000</f>
+        <v>296791389.84075361</v>
+      </c>
+      <c r="E270">
+        <f t="shared" si="166"/>
+        <v>1283460979.0919886</v>
+      </c>
+      <c r="H270" s="4"/>
+      <c r="I270" s="4"/>
+      <c r="J270" s="4"/>
+      <c r="K270" s="4"/>
+    </row>
+    <row r="271" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B271" t="s">
+        <v>80</v>
+      </c>
+      <c r="C271">
+        <f>C87*$I5*1000000</f>
+        <v>330233326.78803521</v>
+      </c>
+      <c r="D271">
+        <f t="shared" ref="D271:E271" si="167">D87*$I5*1000000</f>
+        <v>270147355.12926507</v>
+      </c>
+      <c r="E271">
+        <f t="shared" si="167"/>
+        <v>254268382.555639</v>
+      </c>
+      <c r="H271" s="4"/>
+      <c r="I271" s="4"/>
+      <c r="J271" s="4"/>
+      <c r="K271" s="4"/>
+    </row>
+    <row r="272" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H272" s="4"/>
+      <c r="I272" s="4"/>
+      <c r="J272" s="4"/>
+      <c r="K272" s="4"/>
+    </row>
+    <row r="273" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B273" s="46" t="s">
+        <v>161</v>
+      </c>
+      <c r="C273" s="46"/>
+      <c r="D273" s="46"/>
+      <c r="E273" s="46"/>
+      <c r="H273" s="4"/>
+      <c r="I273" s="4"/>
+      <c r="J273" s="4"/>
+      <c r="K273" s="4"/>
+    </row>
+    <row r="274" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B274" t="str">
+        <f>B252</f>
+        <v>+20% Herd size</v>
+      </c>
+      <c r="C274" s="7">
+        <f>365*(C252+C$270+C$271)*(1-$I$6)*($I$9)/1000/1000000</f>
+        <v>18.626497162946102</v>
+      </c>
+      <c r="D274" s="7">
+        <f t="shared" ref="D274:E274" si="168">365*(D252+D$270+D$271)*(1-$I$6)*($I$9)/1000/1000000</f>
+        <v>34.070888845761139</v>
+      </c>
+      <c r="E274" s="7">
+        <f t="shared" si="168"/>
+        <v>40.046299820109965</v>
+      </c>
+      <c r="H274" s="4"/>
+      <c r="I274" s="4"/>
+      <c r="J274" s="4"/>
+      <c r="K274" s="4"/>
+    </row>
+    <row r="275" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B275" t="str">
+        <f t="shared" ref="B275:B291" si="169">B253</f>
+        <v xml:space="preserve">-20% Herd size </v>
+      </c>
+      <c r="C275" s="7">
+        <f t="shared" ref="C275:E275" si="170">365*(C253+C$270+C$271)*(1-$I$6)*($I$9)/1000/1000000</f>
+        <v>14.719405492494662</v>
+      </c>
+      <c r="D275" s="7">
+        <f t="shared" si="170"/>
+        <v>27.246971250594388</v>
+      </c>
+      <c r="E275" s="7">
+        <f t="shared" si="170"/>
+        <v>34.149703904308005</v>
+      </c>
+      <c r="H275" s="4"/>
+      <c r="I275" s="4"/>
+      <c r="J275" s="4"/>
+      <c r="K275" s="4"/>
+    </row>
+    <row r="276" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B276" t="str">
+        <f t="shared" si="169"/>
+        <v>+20% Zebu</v>
+      </c>
+      <c r="C276" s="7">
+        <f t="shared" ref="C276:E276" si="171">365*(C254+C$270+C$271)*(1-$I$6)*($I$9)/1000/1000000</f>
+        <v>16.282242160675239</v>
+      </c>
+      <c r="D276" s="7">
+        <f t="shared" si="171"/>
+        <v>29.976538288661093</v>
+      </c>
+      <c r="E276" s="7">
+        <f t="shared" si="171"/>
+        <v>36.508342270628788</v>
+      </c>
+      <c r="H276" s="4"/>
+      <c r="I276" s="4"/>
+      <c r="J276" s="4"/>
+      <c r="K276" s="4"/>
+    </row>
+    <row r="277" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B277" t="str">
+        <f t="shared" si="169"/>
+        <v>-20% Zebu</v>
+      </c>
+      <c r="C277" s="7">
+        <f t="shared" ref="C277:E277" si="172">365*(C255+C$270+C$271)*(1-$I$6)*($I$9)/1000/1000000</f>
+        <v>16.282242160675239</v>
+      </c>
+      <c r="D277" s="7">
+        <f t="shared" si="172"/>
+        <v>29.976538288661093</v>
+      </c>
+      <c r="E277" s="7">
+        <f t="shared" si="172"/>
+        <v>36.508342270628788</v>
+      </c>
+      <c r="H277" s="4"/>
+      <c r="I277" s="4"/>
+      <c r="J277" s="4"/>
+      <c r="K277" s="4"/>
+    </row>
+    <row r="278" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B278" t="str">
+        <f t="shared" si="169"/>
+        <v>+20% Boran</v>
+      </c>
+      <c r="C278" s="7">
+        <f t="shared" ref="C278:E278" si="173">365*(C256+C$270+C$271)*(1-$I$6)*($I$9)/1000/1000000</f>
+        <v>16.282242160675239</v>
+      </c>
+      <c r="D278" s="7">
+        <f t="shared" si="173"/>
+        <v>29.976538288661093</v>
+      </c>
+      <c r="E278" s="7">
+        <f t="shared" si="173"/>
+        <v>36.508342270628788</v>
+      </c>
+      <c r="H278" s="4"/>
+      <c r="I278" s="4"/>
+      <c r="J278" s="4"/>
+      <c r="K278" s="4"/>
+    </row>
+    <row r="279" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B279" t="str">
+        <f t="shared" si="169"/>
+        <v>-20% Boran</v>
+      </c>
+      <c r="C279" s="7">
+        <f t="shared" ref="C279:E279" si="174">365*(C257+C$270+C$271)*(1-$I$6)*($I$9)/1000/1000000</f>
+        <v>16.282242160675239</v>
+      </c>
+      <c r="D279" s="7">
+        <f t="shared" si="174"/>
+        <v>29.976538288661093</v>
+      </c>
+      <c r="E279" s="7">
+        <f t="shared" si="174"/>
+        <v>36.508342270628788</v>
+      </c>
+      <c r="H279" s="4"/>
+      <c r="I279" s="4"/>
+      <c r="J279" s="4"/>
+      <c r="K279" s="4"/>
+    </row>
+    <row r="280" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B280" t="str">
+        <f t="shared" si="169"/>
+        <v>+20% Exotic</v>
+      </c>
+      <c r="C280" s="7">
+        <f t="shared" ref="C280:E280" si="175">365*(C258+C$270+C$271)*(1-$I$6)*($I$9)/1000/1000000</f>
+        <v>16.282242160675239</v>
+      </c>
+      <c r="D280" s="7">
+        <f t="shared" si="175"/>
+        <v>29.976538288661093</v>
+      </c>
+      <c r="E280" s="7">
+        <f t="shared" si="175"/>
+        <v>36.508342270628788</v>
+      </c>
+      <c r="H280" s="4"/>
+      <c r="I280" s="4"/>
+      <c r="J280" s="4"/>
+      <c r="K280" s="4"/>
+    </row>
+    <row r="281" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B281" t="str">
+        <f t="shared" si="169"/>
+        <v>-20% Exotic</v>
+      </c>
+      <c r="C281" s="7">
+        <f t="shared" ref="C281:E281" si="176">365*(C259+C$270+C$271)*(1-$I$6)*($I$9)/1000/1000000</f>
+        <v>16.282242160675239</v>
+      </c>
+      <c r="D281" s="7">
+        <f t="shared" si="176"/>
+        <v>29.976538288661093</v>
+      </c>
+      <c r="E281" s="7">
+        <f t="shared" si="176"/>
+        <v>36.508342270628788</v>
+      </c>
+      <c r="H281" s="4"/>
+      <c r="I281" s="4"/>
+      <c r="J281" s="4"/>
+      <c r="K281" s="4"/>
+    </row>
+    <row r="282" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B282" t="str">
+        <f t="shared" si="169"/>
+        <v>+20% Finisher:Breeder</v>
+      </c>
+      <c r="C282" s="7">
+        <f t="shared" ref="C282:E282" si="177">365*(C260+C$270+C$271)*(1-$I$6)*($I$9)/1000/1000000</f>
+        <v>16.282242160675239</v>
+      </c>
+      <c r="D282" s="7">
+        <f t="shared" si="177"/>
+        <v>29.976538288661093</v>
+      </c>
+      <c r="E282" s="7">
+        <f t="shared" si="177"/>
+        <v>36.508342270628788</v>
+      </c>
+      <c r="H282" s="4"/>
+      <c r="I282" s="4"/>
+      <c r="J282" s="4"/>
+      <c r="K282" s="4"/>
+    </row>
+    <row r="283" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B283" t="str">
+        <f t="shared" si="169"/>
+        <v>-20% Finisher:Breeder</v>
+      </c>
+      <c r="C283" s="7">
+        <f t="shared" ref="C283:E283" si="178">365*(C261+C$270+C$271)*(1-$I$6)*($I$9)/1000/1000000</f>
+        <v>16.282242160675239</v>
+      </c>
+      <c r="D283" s="7">
+        <f t="shared" si="178"/>
+        <v>29.976538288661093</v>
+      </c>
+      <c r="E283" s="7">
+        <f t="shared" si="178"/>
+        <v>36.508342270628788</v>
+      </c>
+      <c r="H283" s="4"/>
+      <c r="I283" s="4"/>
+      <c r="J283" s="4"/>
+      <c r="K283" s="4"/>
+    </row>
+    <row r="284" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B284" t="str">
+        <f t="shared" si="169"/>
+        <v>+20% Pastoral:Agropastoral</v>
+      </c>
+      <c r="C284" s="7">
+        <f t="shared" ref="C284:E284" si="179">365*(C262+C$270+C$271)*(1-$I$6)*($I$9)/1000/1000000</f>
+        <v>16.480810265165772</v>
+      </c>
+      <c r="D284" s="7">
+        <f t="shared" si="179"/>
+        <v>29.496939655672186</v>
+      </c>
+      <c r="E284" s="7">
+        <f t="shared" si="179"/>
+        <v>35.942899459691823</v>
+      </c>
+      <c r="H284" s="4"/>
+      <c r="I284" s="4"/>
+      <c r="J284" s="4"/>
+      <c r="K284" s="4"/>
+    </row>
+    <row r="285" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B285" t="str">
+        <f t="shared" si="169"/>
+        <v>-20% Pastoral:Agropastoral</v>
+      </c>
+      <c r="C285" s="7">
+        <f t="shared" ref="C285:E285" si="180">365*(C263+C$270+C$271)*(1-$I$6)*($I$9)/1000/1000000</f>
+        <v>16.149863424348219</v>
+      </c>
+      <c r="D285" s="7">
+        <f t="shared" si="180"/>
+        <v>30.858857271873738</v>
+      </c>
+      <c r="E285" s="7">
+        <f t="shared" si="180"/>
+        <v>37.356506487034231</v>
+      </c>
+      <c r="H285" s="4"/>
+      <c r="I285" s="4"/>
+      <c r="J285" s="4"/>
+      <c r="K285" s="4"/>
+    </row>
+    <row r="286" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B286" t="str">
+        <f t="shared" si="169"/>
+        <v>+20% Mixed:Agropastoral</v>
+      </c>
+      <c r="C286" s="7">
+        <f t="shared" ref="C286:E286" si="181">365*(C264+C$270+C$271)*(1-$I$6)*($I$9)/1000/1000000</f>
+        <v>16.282242160675239</v>
+      </c>
+      <c r="D286" s="7">
+        <f t="shared" si="181"/>
+        <v>29.301434415197036</v>
+      </c>
+      <c r="E286" s="7">
+        <f t="shared" si="181"/>
+        <v>36.098034776483559</v>
+      </c>
+      <c r="H286" s="4"/>
+      <c r="I286" s="4"/>
+      <c r="J286" s="4"/>
+      <c r="K286" s="4"/>
+    </row>
+    <row r="287" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B287" t="str">
+        <f t="shared" si="169"/>
+        <v>-20% Mixed:Agropastoral</v>
+      </c>
+      <c r="C287" s="7">
+        <f t="shared" ref="C287:E287" si="182">365*(C265+C$270+C$271)*(1-$I$6)*($I$9)/1000/1000000</f>
+        <v>16.282242160675239</v>
+      </c>
+      <c r="D287" s="7">
+        <f t="shared" si="182"/>
+        <v>30.989194098857173</v>
+      </c>
+      <c r="E287" s="7">
+        <f t="shared" si="182"/>
+        <v>37.25308294250641</v>
+      </c>
+      <c r="H287" s="4"/>
+      <c r="I287" s="4"/>
+      <c r="J287" s="4"/>
+      <c r="K287" s="4"/>
+    </row>
+    <row r="288" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B288" t="str">
+        <f t="shared" si="169"/>
+        <v>+20% Cowcalf:Finisher</v>
+      </c>
+      <c r="C288" s="7">
+        <f t="shared" ref="C288:E288" si="183">365*(C266+C$270+C$271)*(1-$I$6)*($I$9)/1000/1000000</f>
+        <v>14.865195132025681</v>
+      </c>
+      <c r="D288" s="7">
+        <f t="shared" si="183"/>
+        <v>28.114393016794828</v>
+      </c>
+      <c r="E288" s="7">
+        <f t="shared" si="183"/>
+        <v>34.919068222388127</v>
+      </c>
+      <c r="H288" s="4"/>
+      <c r="I288" s="4"/>
+      <c r="J288" s="4"/>
+      <c r="K288" s="4"/>
+    </row>
+    <row r="289" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B289" t="str">
+        <f t="shared" si="169"/>
+        <v>-20% Cowcalf:Finisher</v>
+      </c>
+      <c r="C289" s="7">
+        <f t="shared" ref="C289:E289" si="184">365*(C267+C$270+C$271)*(1-$I$6)*($I$9)/1000/1000000</f>
+        <v>18.414518155251571</v>
+      </c>
+      <c r="D289" s="7">
+        <f t="shared" si="184"/>
+        <v>32.800746729336964</v>
+      </c>
+      <c r="E289" s="7">
+        <f t="shared" si="184"/>
+        <v>38.942502324297458</v>
+      </c>
+      <c r="H289" s="4"/>
+      <c r="I289" s="4"/>
+      <c r="J289" s="4"/>
+      <c r="K289" s="4"/>
+    </row>
+    <row r="290" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B290" t="str">
+        <f t="shared" si="169"/>
+        <v>+20% Commercial:Subsistence</v>
+      </c>
+      <c r="C290" s="7">
+        <f t="shared" ref="C290:E290" si="185">365*(C268+C$270+C$271)*(1-$I$6)*($I$9)/1000/1000000</f>
+        <v>18.295550322128552</v>
+      </c>
+      <c r="D290" s="7">
+        <f t="shared" si="185"/>
+        <v>32.05728709464244</v>
+      </c>
+      <c r="E290" s="7">
+        <f t="shared" si="185"/>
+        <v>38.374133931448007</v>
+      </c>
+      <c r="H290" s="4"/>
+      <c r="I290" s="4"/>
+      <c r="J290" s="4"/>
+      <c r="K290" s="4"/>
+    </row>
+    <row r="291" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B291" t="str">
+        <f t="shared" si="169"/>
+        <v>-20% Commercial:Subsistence</v>
+      </c>
+      <c r="C291" s="7">
+        <f>365*(C269+C$270+C$271)*(1-$I$6)*($I$9)/1000/1000000</f>
+        <v>15.050352333312214</v>
+      </c>
+      <c r="D291" s="7">
+        <f t="shared" ref="D291:E291" si="186">365*(D269+D$270+D$271)*(1-$I$6)*($I$9)/1000/1000000</f>
+        <v>29.260573001713087</v>
+      </c>
+      <c r="E291" s="7">
+        <f t="shared" si="186"/>
+        <v>35.66673447617822</v>
+      </c>
+      <c r="H291" s="4"/>
+      <c r="I291" s="4"/>
+      <c r="J291" s="4"/>
+      <c r="K291" s="4"/>
+    </row>
+    <row r="292" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H292" s="4"/>
+      <c r="I292" s="4"/>
+      <c r="J292" s="4"/>
+      <c r="K292" s="4"/>
+    </row>
+    <row r="293" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C293" s="7">
+        <f>C20</f>
+        <v>11.214491800146961</v>
+      </c>
+      <c r="H293" s="4"/>
+      <c r="I293" s="4"/>
+      <c r="J293" s="4"/>
+      <c r="K293" s="4"/>
+    </row>
+    <row r="294" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B294" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="C294" s="27">
+        <f>C49</f>
+        <v>12.151858686054949</v>
+      </c>
+      <c r="D294" s="27">
+        <f t="shared" ref="D294:E294" si="187">D49</f>
+        <v>19.619822257325151</v>
+      </c>
+      <c r="E294" s="27">
+        <f t="shared" si="187"/>
+        <v>14.483559517089713</v>
+      </c>
+      <c r="H294" s="4"/>
+      <c r="I294" s="4"/>
+      <c r="J294" s="4"/>
+      <c r="K294" s="4"/>
+    </row>
+    <row r="295" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B295" s="1"/>
+      <c r="C295" s="13"/>
+      <c r="D295" s="13"/>
+      <c r="E295" s="13"/>
+      <c r="H295" s="4"/>
+      <c r="I295" s="4"/>
+      <c r="J295" s="4"/>
+      <c r="K295" s="4"/>
+    </row>
+    <row r="296" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B296" s="17" t="s">
+        <v>166</v>
+      </c>
+      <c r="C296" s="13">
+        <f>C22</f>
+        <v>1.3307018984028698</v>
+      </c>
+      <c r="D296" s="13">
+        <f t="shared" ref="D296:E296" si="188">D22</f>
+        <v>1.3356646154172063</v>
+      </c>
+      <c r="E296" s="13">
+        <f t="shared" si="188"/>
+        <v>0.96207277131218349</v>
+      </c>
+      <c r="H296" s="4"/>
+      <c r="I296" s="4"/>
+      <c r="J296" s="4"/>
+      <c r="K296" s="4"/>
+    </row>
+    <row r="297" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B297" s="1"/>
+      <c r="C297" s="13"/>
+      <c r="D297" s="13"/>
+      <c r="E297" s="13"/>
+      <c r="H297" s="4"/>
+      <c r="I297" s="4"/>
+      <c r="J297" s="4"/>
+      <c r="K297" s="4"/>
+    </row>
+    <row r="298" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B298" s="1"/>
+      <c r="C298" s="13"/>
+      <c r="D298" s="13"/>
+      <c r="E298" s="13"/>
+      <c r="H298" s="4"/>
+      <c r="I298" s="4"/>
+      <c r="J298" s="4"/>
+      <c r="K298" s="4"/>
+    </row>
+    <row r="299" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H299" s="4"/>
+      <c r="I299" s="4"/>
+      <c r="J299" s="4"/>
+      <c r="K299" s="4"/>
+    </row>
+    <row r="300" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B300" s="48" t="s">
+        <v>165</v>
+      </c>
+      <c r="C300" s="48"/>
+      <c r="D300" s="48"/>
+      <c r="E300" s="48"/>
+      <c r="H300" s="4"/>
+      <c r="I300" s="4"/>
+      <c r="J300" s="4"/>
+      <c r="K300" s="4"/>
+    </row>
+    <row r="301" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B301" t="str">
+        <f t="shared" ref="B301:B318" si="189">B252</f>
+        <v>+20% Herd size</v>
+      </c>
+      <c r="C301">
+        <f>C$294/C274</f>
+        <v>0.65239634590172846</v>
+      </c>
+      <c r="D301">
+        <f t="shared" ref="D301:E301" si="190">D$294/D274</f>
+        <v>0.57585296192723512</v>
+      </c>
+      <c r="E301">
+        <f t="shared" si="190"/>
+        <v>0.36167035611656023</v>
+      </c>
+      <c r="H301" s="4"/>
+      <c r="I301" s="4"/>
+      <c r="J301" s="4"/>
+      <c r="K301" s="4"/>
+    </row>
+    <row r="302" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B302" t="str">
+        <f t="shared" si="189"/>
+        <v xml:space="preserve">-20% Herd size </v>
+      </c>
+      <c r="C302">
+        <f t="shared" ref="C302:E302" si="191">C$294/C275</f>
+        <v>0.82556722092146384</v>
+      </c>
+      <c r="D302">
+        <f t="shared" si="191"/>
+        <v>0.7200735111759311</v>
+      </c>
+      <c r="E302">
+        <f t="shared" si="191"/>
+        <v>0.42411962216933319</v>
+      </c>
+      <c r="H302" s="4"/>
+      <c r="I302" s="4"/>
+      <c r="J302" s="4"/>
+      <c r="K302" s="4"/>
+    </row>
+    <row r="303" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B303" t="str">
+        <f t="shared" si="189"/>
+        <v>+20% Zebu</v>
+      </c>
+      <c r="C303">
+        <f t="shared" ref="C303:E303" si="192">C$294/C276</f>
+        <v>0.74632587859453636</v>
+      </c>
+      <c r="D303">
+        <f t="shared" si="192"/>
+        <v>0.65450593622234665</v>
+      </c>
+      <c r="E303">
+        <f t="shared" si="192"/>
+        <v>0.39671917748897179</v>
+      </c>
+      <c r="H303" s="4"/>
+      <c r="I303" s="4"/>
+      <c r="J303" s="4"/>
+      <c r="K303" s="4"/>
+    </row>
+    <row r="304" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B304" t="str">
+        <f t="shared" si="189"/>
+        <v>-20% Zebu</v>
+      </c>
+      <c r="C304">
+        <f t="shared" ref="C304:E304" si="193">C$294/C277</f>
+        <v>0.74632587859453636</v>
+      </c>
+      <c r="D304">
+        <f t="shared" si="193"/>
+        <v>0.65450593622234665</v>
+      </c>
+      <c r="E304">
+        <f t="shared" si="193"/>
+        <v>0.39671917748897179</v>
+      </c>
+      <c r="H304" s="4"/>
+      <c r="I304" s="4"/>
+      <c r="J304" s="4"/>
+      <c r="K304" s="4"/>
+    </row>
+    <row r="305" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B305" t="str">
+        <f t="shared" si="189"/>
+        <v>+20% Boran</v>
+      </c>
+      <c r="C305">
+        <f t="shared" ref="C305:E305" si="194">C$294/C278</f>
+        <v>0.74632587859453636</v>
+      </c>
+      <c r="D305">
+        <f t="shared" si="194"/>
+        <v>0.65450593622234665</v>
+      </c>
+      <c r="E305">
+        <f t="shared" si="194"/>
+        <v>0.39671917748897179</v>
+      </c>
+    </row>
+    <row r="306" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B306" t="str">
+        <f t="shared" si="189"/>
+        <v>-20% Boran</v>
+      </c>
+      <c r="C306">
+        <f t="shared" ref="C306:E306" si="195">C$294/C279</f>
+        <v>0.74632587859453636</v>
+      </c>
+      <c r="D306">
+        <f t="shared" si="195"/>
+        <v>0.65450593622234665</v>
+      </c>
+      <c r="E306">
+        <f t="shared" si="195"/>
+        <v>0.39671917748897179</v>
+      </c>
+    </row>
+    <row r="307" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B307" t="str">
+        <f t="shared" si="189"/>
+        <v>+20% Exotic</v>
+      </c>
+      <c r="C307">
+        <f t="shared" ref="C307:E307" si="196">C$294/C280</f>
+        <v>0.74632587859453636</v>
+      </c>
+      <c r="D307">
+        <f t="shared" si="196"/>
+        <v>0.65450593622234665</v>
+      </c>
+      <c r="E307">
+        <f t="shared" si="196"/>
+        <v>0.39671917748897179</v>
+      </c>
+    </row>
+    <row r="308" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B308" t="str">
+        <f t="shared" si="189"/>
+        <v>-20% Exotic</v>
+      </c>
+      <c r="C308">
+        <f t="shared" ref="C308:E308" si="197">C$294/C281</f>
+        <v>0.74632587859453636</v>
+      </c>
+      <c r="D308">
+        <f t="shared" si="197"/>
+        <v>0.65450593622234665</v>
+      </c>
+      <c r="E308">
+        <f t="shared" si="197"/>
+        <v>0.39671917748897179</v>
+      </c>
+    </row>
+    <row r="309" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B309" t="str">
+        <f t="shared" si="189"/>
+        <v>+20% Finisher:Breeder</v>
+      </c>
+      <c r="C309">
+        <f t="shared" ref="C309:E309" si="198">C$294/C282</f>
+        <v>0.74632587859453636</v>
+      </c>
+      <c r="D309">
+        <f t="shared" si="198"/>
+        <v>0.65450593622234665</v>
+      </c>
+      <c r="E309">
+        <f t="shared" si="198"/>
+        <v>0.39671917748897179</v>
+      </c>
+    </row>
+    <row r="310" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B310" t="str">
+        <f t="shared" si="189"/>
+        <v>-20% Finisher:Breeder</v>
+      </c>
+      <c r="C310">
+        <f t="shared" ref="C310:E310" si="199">C$294/C283</f>
+        <v>0.74632587859453636</v>
+      </c>
+      <c r="D310">
+        <f t="shared" si="199"/>
+        <v>0.65450593622234665</v>
+      </c>
+      <c r="E310">
+        <f t="shared" si="199"/>
+        <v>0.39671917748897179</v>
+      </c>
+    </row>
+    <row r="311" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B311" t="str">
+        <f t="shared" si="189"/>
+        <v>+20% Pastoral:Agropastoral</v>
+      </c>
+      <c r="C311">
+        <f t="shared" ref="C311:E311" si="200">C$294/C284</f>
+        <v>0.7373338137227029</v>
+      </c>
+      <c r="D311">
+        <f t="shared" si="200"/>
+        <v>0.6651477233351667</v>
+      </c>
+      <c r="E311">
+        <f t="shared" si="200"/>
+        <v>0.40296024346428438</v>
+      </c>
+    </row>
+    <row r="312" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B312" t="str">
+        <f t="shared" si="189"/>
+        <v>-20% Pastoral:Agropastoral</v>
+      </c>
+      <c r="C312">
+        <f t="shared" ref="C312:E312" si="201">C$294/C285</f>
+        <v>0.75244343352986454</v>
+      </c>
+      <c r="D312">
+        <f t="shared" si="201"/>
+        <v>0.63579224870415441</v>
+      </c>
+      <c r="E312">
+        <f t="shared" si="201"/>
+        <v>0.38771183065838061</v>
+      </c>
+    </row>
+    <row r="313" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B313" t="str">
+        <f t="shared" si="189"/>
+        <v>+20% Mixed:Agropastoral</v>
+      </c>
+      <c r="C313">
+        <f t="shared" ref="C313:E313" si="202">C$294/C286</f>
+        <v>0.74632587859453636</v>
+      </c>
+      <c r="D313">
+        <f t="shared" si="202"/>
+        <v>0.6695857267366212</v>
+      </c>
+      <c r="E313">
+        <f t="shared" si="202"/>
+        <v>0.40122847702848297</v>
+      </c>
+    </row>
+    <row r="314" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B314" t="str">
+        <f t="shared" si="189"/>
+        <v>-20% Mixed:Agropastoral</v>
+      </c>
+      <c r="C314">
+        <f t="shared" ref="C314:E314" si="203">C$294/C287</f>
+        <v>0.74632587859453636</v>
+      </c>
+      <c r="D314">
+        <f t="shared" si="203"/>
+        <v>0.63311818289746025</v>
+      </c>
+      <c r="E314">
+        <f t="shared" si="203"/>
+        <v>0.38878821222508064</v>
+      </c>
+    </row>
+    <row r="315" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B315" t="str">
+        <f t="shared" si="189"/>
+        <v>+20% Cowcalf:Finisher</v>
+      </c>
+      <c r="C315">
+        <f t="shared" ref="C315:E315" si="204">C$294/C288</f>
+        <v>0.81747051270621396</v>
+      </c>
+      <c r="D315">
+        <f t="shared" si="204"/>
+        <v>0.69785686803214153</v>
+      </c>
+      <c r="E315">
+        <f t="shared" si="204"/>
+        <v>0.4147750857740149</v>
+      </c>
+    </row>
+    <row r="316" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B316" t="str">
+        <f t="shared" si="189"/>
+        <v>-20% Cowcalf:Finisher</v>
+      </c>
+      <c r="C316">
+        <f t="shared" ref="C316:E316" si="205">C$294/C289</f>
+        <v>0.6599064164266174</v>
+      </c>
+      <c r="D316">
+        <f t="shared" si="205"/>
+        <v>0.59815169511909905</v>
+      </c>
+      <c r="E316">
+        <f t="shared" si="205"/>
+        <v>0.37192164480023571</v>
+      </c>
+    </row>
+    <row r="317" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B317" t="str">
+        <f t="shared" si="189"/>
+        <v>+20% Commercial:Subsistence</v>
+      </c>
+      <c r="C317">
+        <f t="shared" ref="C317:E317" si="206">C$294/C290</f>
+        <v>0.66419749458737076</v>
+      </c>
+      <c r="D317">
+        <f t="shared" si="206"/>
+        <v>0.61202378727188378</v>
+      </c>
+      <c r="E317">
+        <f t="shared" si="206"/>
+        <v>0.37743026443185168</v>
+      </c>
+    </row>
+    <row r="318" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B318" t="str">
+        <f t="shared" si="189"/>
+        <v>-20% Commercial:Subsistence</v>
+      </c>
+      <c r="C318">
+        <f t="shared" ref="C318:E318" si="207">C$294/C291</f>
+        <v>0.80741356859521596</v>
+      </c>
+      <c r="D318">
+        <f t="shared" si="207"/>
+        <v>0.67052078085335132</v>
+      </c>
+      <c r="E318">
+        <f t="shared" si="207"/>
+        <v>0.40608033591534065</v>
+      </c>
+    </row>
+    <row r="320" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B320" s="48" t="str">
+        <f>B300</f>
+        <v>2050 Carrying capacity (S/D)</v>
+      </c>
+      <c r="C320" s="48"/>
+      <c r="D320" s="48"/>
+      <c r="E320" s="48"/>
+    </row>
+    <row r="321" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B321" s="41" t="str">
+        <f>B301</f>
+        <v>+20% Herd size</v>
+      </c>
+      <c r="C321" s="13">
+        <f>AVERAGE(C301,C$296)</f>
+        <v>0.99154912215229918</v>
+      </c>
+      <c r="D321" s="13">
+        <f t="shared" ref="D321:E321" si="208">AVERAGE(D301,D$296)</f>
+        <v>0.95575878867222075</v>
+      </c>
+      <c r="E321" s="13">
+        <f t="shared" si="208"/>
+        <v>0.66187156371437184</v>
+      </c>
+    </row>
+    <row r="322" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B322" s="41" t="str">
+        <f t="shared" ref="B322:B338" si="209">B302</f>
+        <v xml:space="preserve">-20% Herd size </v>
+      </c>
+      <c r="C322" s="13">
+        <f t="shared" ref="C322:E322" si="210">AVERAGE(C302,C$296)</f>
+        <v>1.0781345596621668</v>
+      </c>
+      <c r="D322" s="13">
+        <f t="shared" si="210"/>
+        <v>1.0278690632965688</v>
+      </c>
+      <c r="E322" s="13">
+        <f t="shared" si="210"/>
+        <v>0.69309619674075829</v>
+      </c>
+    </row>
+    <row r="323" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B323" t="str">
+        <f t="shared" si="209"/>
+        <v>+20% Zebu</v>
+      </c>
+      <c r="C323" s="13">
+        <f t="shared" ref="C323:E323" si="211">AVERAGE(C303,C$296)</f>
+        <v>1.0385138884987031</v>
+      </c>
+      <c r="D323" s="13">
+        <f t="shared" si="211"/>
+        <v>0.99508527581977646</v>
+      </c>
+      <c r="E323" s="13">
+        <f t="shared" si="211"/>
+        <v>0.67939597440057764</v>
+      </c>
+    </row>
+    <row r="324" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B324" t="str">
+        <f t="shared" si="209"/>
+        <v>-20% Zebu</v>
+      </c>
+      <c r="C324" s="13">
+        <f t="shared" ref="C324:E324" si="212">AVERAGE(C304,C$296)</f>
+        <v>1.0385138884987031</v>
+      </c>
+      <c r="D324" s="13">
+        <f t="shared" si="212"/>
+        <v>0.99508527581977646</v>
+      </c>
+      <c r="E324" s="13">
+        <f t="shared" si="212"/>
+        <v>0.67939597440057764</v>
+      </c>
+      <c r="F324" s="13"/>
+    </row>
+    <row r="325" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B325" t="str">
+        <f t="shared" si="209"/>
+        <v>+20% Boran</v>
+      </c>
+      <c r="C325" s="13">
+        <f t="shared" ref="C325:E325" si="213">AVERAGE(C305,C$296)</f>
+        <v>1.0385138884987031</v>
+      </c>
+      <c r="D325" s="13">
+        <f t="shared" si="213"/>
+        <v>0.99508527581977646</v>
+      </c>
+      <c r="E325" s="13">
+        <f t="shared" si="213"/>
+        <v>0.67939597440057764</v>
+      </c>
+    </row>
+    <row r="326" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B326" t="str">
+        <f t="shared" si="209"/>
+        <v>-20% Boran</v>
+      </c>
+      <c r="C326" s="13">
+        <f t="shared" ref="C326:E326" si="214">AVERAGE(C306,C$296)</f>
+        <v>1.0385138884987031</v>
+      </c>
+      <c r="D326" s="13">
+        <f t="shared" si="214"/>
+        <v>0.99508527581977646</v>
+      </c>
+      <c r="E326" s="13">
+        <f t="shared" si="214"/>
+        <v>0.67939597440057764</v>
+      </c>
+    </row>
+    <row r="327" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B327" t="str">
+        <f t="shared" si="209"/>
+        <v>+20% Exotic</v>
+      </c>
+      <c r="C327" s="13">
+        <f t="shared" ref="C327:E327" si="215">AVERAGE(C307,C$296)</f>
+        <v>1.0385138884987031</v>
+      </c>
+      <c r="D327" s="13">
+        <f t="shared" si="215"/>
+        <v>0.99508527581977646</v>
+      </c>
+      <c r="E327" s="13">
+        <f t="shared" si="215"/>
+        <v>0.67939597440057764</v>
+      </c>
+    </row>
+    <row r="328" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B328" t="str">
+        <f t="shared" si="209"/>
+        <v>-20% Exotic</v>
+      </c>
+      <c r="C328" s="13">
+        <f t="shared" ref="C328:E328" si="216">AVERAGE(C308,C$296)</f>
+        <v>1.0385138884987031</v>
+      </c>
+      <c r="D328" s="13">
+        <f t="shared" si="216"/>
+        <v>0.99508527581977646</v>
+      </c>
+      <c r="E328" s="13">
+        <f t="shared" si="216"/>
+        <v>0.67939597440057764</v>
+      </c>
+      <c r="G328" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="329" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B329" t="str">
+        <f t="shared" si="209"/>
+        <v>+20% Finisher:Breeder</v>
+      </c>
+      <c r="C329" s="13">
+        <f t="shared" ref="C329:E329" si="217">AVERAGE(C309,C$296)</f>
+        <v>1.0385138884987031</v>
+      </c>
+      <c r="D329" s="13">
+        <f t="shared" si="217"/>
+        <v>0.99508527581977646</v>
+      </c>
+      <c r="E329" s="13">
+        <f t="shared" si="217"/>
+        <v>0.67939597440057764</v>
+      </c>
+      <c r="G329" s="41" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="330" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B330" t="str">
+        <f t="shared" si="209"/>
+        <v>-20% Finisher:Breeder</v>
+      </c>
+      <c r="C330" s="13">
+        <f t="shared" ref="C330:E330" si="218">AVERAGE(C310,C$296)</f>
+        <v>1.0385138884987031</v>
+      </c>
+      <c r="D330" s="13">
+        <f t="shared" si="218"/>
+        <v>0.99508527581977646</v>
+      </c>
+      <c r="E330" s="13">
+        <f t="shared" si="218"/>
+        <v>0.67939597440057764</v>
+      </c>
+    </row>
+    <row r="331" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B331" s="41" t="str">
+        <f t="shared" si="209"/>
+        <v>+20% Pastoral:Agropastoral</v>
+      </c>
+      <c r="C331" s="13">
+        <f t="shared" ref="C331:E331" si="219">AVERAGE(C311,C$296)</f>
+        <v>1.0340178560627864</v>
+      </c>
+      <c r="D331" s="13">
+        <f t="shared" si="219"/>
+        <v>1.0004061693761865</v>
+      </c>
+      <c r="E331" s="13">
+        <f t="shared" si="219"/>
+        <v>0.682516507388234</v>
+      </c>
+    </row>
+    <row r="332" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B332" s="41" t="str">
+        <f t="shared" si="209"/>
+        <v>-20% Pastoral:Agropastoral</v>
+      </c>
+      <c r="C332" s="13">
+        <f t="shared" ref="C332:E332" si="220">AVERAGE(C312,C$296)</f>
+        <v>1.0415726659663671</v>
+      </c>
+      <c r="D332" s="13">
+        <f t="shared" si="220"/>
+        <v>0.98572843206068028</v>
+      </c>
+      <c r="E332" s="13">
+        <f t="shared" si="220"/>
+        <v>0.67489230098528208</v>
+      </c>
+    </row>
+    <row r="333" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B333" s="41" t="str">
+        <f t="shared" si="209"/>
+        <v>+20% Mixed:Agropastoral</v>
+      </c>
+      <c r="C333" s="13">
+        <f t="shared" ref="C333:E333" si="221">AVERAGE(C313,C$296)</f>
+        <v>1.0385138884987031</v>
+      </c>
+      <c r="D333" s="13">
+        <f t="shared" si="221"/>
+        <v>1.0026251710769136</v>
+      </c>
+      <c r="E333" s="13">
+        <f t="shared" si="221"/>
+        <v>0.68165062417033329</v>
+      </c>
+    </row>
+    <row r="334" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B334" s="41" t="str">
+        <f t="shared" si="209"/>
+        <v>-20% Mixed:Agropastoral</v>
+      </c>
+      <c r="C334" s="13">
+        <f t="shared" ref="C334:E334" si="222">AVERAGE(C314,C$296)</f>
+        <v>1.0385138884987031</v>
+      </c>
+      <c r="D334" s="13">
+        <f t="shared" si="222"/>
+        <v>0.9843913991573332</v>
+      </c>
+      <c r="E334" s="13">
+        <f t="shared" si="222"/>
+        <v>0.67543049176863201</v>
+      </c>
+    </row>
+    <row r="335" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B335" s="41" t="str">
+        <f t="shared" si="209"/>
+        <v>+20% Cowcalf:Finisher</v>
+      </c>
+      <c r="C335" s="13">
+        <f t="shared" ref="C335:E335" si="223">AVERAGE(C315,C$296)</f>
+        <v>1.0740862055545419</v>
+      </c>
+      <c r="D335" s="13">
+        <f t="shared" si="223"/>
+        <v>1.0167607417246738</v>
+      </c>
+      <c r="E335" s="13">
+        <f t="shared" si="223"/>
+        <v>0.6884239285430992</v>
+      </c>
+    </row>
+    <row r="336" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B336" s="41" t="str">
+        <f t="shared" si="209"/>
+        <v>-20% Cowcalf:Finisher</v>
+      </c>
+      <c r="C336" s="13">
+        <f t="shared" ref="C336:E336" si="224">AVERAGE(C316,C$296)</f>
+        <v>0.99530415741474365</v>
+      </c>
+      <c r="D336" s="13">
+        <f t="shared" si="224"/>
+        <v>0.96690815526815266</v>
+      </c>
+      <c r="E336" s="13">
+        <f t="shared" si="224"/>
+        <v>0.66699720805620966</v>
+      </c>
+    </row>
+    <row r="337" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B337" s="41" t="str">
+        <f t="shared" si="209"/>
+        <v>+20% Commercial:Subsistence</v>
+      </c>
+      <c r="C337" s="13">
+        <f t="shared" ref="C337:E337" si="225">AVERAGE(C317,C$296)</f>
+        <v>0.99744969649512027</v>
+      </c>
+      <c r="D337" s="13">
+        <f t="shared" si="225"/>
+        <v>0.97384420134454497</v>
+      </c>
+      <c r="E337" s="13">
+        <f t="shared" si="225"/>
+        <v>0.66975151787201759</v>
+      </c>
+    </row>
+    <row r="338" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B338" s="41" t="str">
+        <f t="shared" si="209"/>
+        <v>-20% Commercial:Subsistence</v>
+      </c>
+      <c r="C338" s="13">
+        <f t="shared" ref="C338:E338" si="226">AVERAGE(C318,C$296)</f>
+        <v>1.0690577334990428</v>
+      </c>
+      <c r="D338" s="13">
+        <f t="shared" si="226"/>
+        <v>1.0030926981352788</v>
+      </c>
+      <c r="E338" s="13">
+        <f t="shared" si="226"/>
+        <v>0.68407655361376207</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="34">
+    <mergeCell ref="B98:E98"/>
+    <mergeCell ref="B107:E107"/>
+    <mergeCell ref="B143:E143"/>
+    <mergeCell ref="B152:E152"/>
+    <mergeCell ref="B320:E320"/>
+    <mergeCell ref="B242:E242"/>
+    <mergeCell ref="H78:I78"/>
+    <mergeCell ref="B251:E251"/>
+    <mergeCell ref="B300:E300"/>
+    <mergeCell ref="B273:E273"/>
+    <mergeCell ref="B197:E197"/>
+    <mergeCell ref="B206:E206"/>
+    <mergeCell ref="B215:E215"/>
+    <mergeCell ref="B224:E224"/>
+    <mergeCell ref="B233:E233"/>
+    <mergeCell ref="B78:E78"/>
+    <mergeCell ref="B80:E80"/>
+    <mergeCell ref="B89:E89"/>
+    <mergeCell ref="B161:E161"/>
+    <mergeCell ref="B170:E170"/>
+    <mergeCell ref="B179:E179"/>
+    <mergeCell ref="B188:E188"/>
     <mergeCell ref="B26:E26"/>
     <mergeCell ref="B43:E43"/>
     <mergeCell ref="B27:E27"/>
@@ -6085,6 +11359,9 @@
     <mergeCell ref="B62:E62"/>
     <mergeCell ref="B36:E36"/>
     <mergeCell ref="B61:E61"/>
+    <mergeCell ref="B116:E116"/>
+    <mergeCell ref="B125:E125"/>
+    <mergeCell ref="B134:E134"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Rasterized animal populations/Zonal statistics/Summary.xlsx
+++ b/Rasterized animal populations/Zonal statistics/Summary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JHawkins\Documents\Github\KE.beef.spatial\Rasterized animal populations\Zonal statistics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41D5B86C-678B-402F-B412-5DA128D33016}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F09F6B25-3816-4EAA-88DF-1790863E079D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" firstSheet="3" activeTab="7" xr2:uid="{3882C52B-09A6-47D1-94BA-1F6173569800}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" firstSheet="3" activeTab="6" xr2:uid="{3882C52B-09A6-47D1-94BA-1F6173569800}"/>
   </bookViews>
   <sheets>
     <sheet name="Validate_2020" sheetId="2" r:id="rId1"/>
@@ -866,7 +866,7 @@
     <numFmt numFmtId="168" formatCode="0.0000"/>
     <numFmt numFmtId="169" formatCode="0.00000"/>
     <numFmt numFmtId="170" formatCode="0.000000"/>
-    <numFmt numFmtId="177" formatCode="0.0"/>
+    <numFmt numFmtId="171" formatCode="0.0"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -1085,28 +1085,28 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1129,15 +1129,58 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="Arid_Subsistence"/>
+      <sheetName val="Model_implemented"/>
+      <sheetName val="FAO_2019_animal_trends"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1">
-        <row r="2">
-          <cell r="C2">
-            <v>220785.65217611199</v>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="35">
+          <cell r="F35">
+            <v>0.53615960099750615</v>
+          </cell>
+          <cell r="G35">
+            <v>0.38312009613345605</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="F36">
+            <v>0.36159600997506236</v>
+          </cell>
+          <cell r="G36">
+            <v>2.7950424483806726</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="F37">
+            <v>2.4937655860349127E-3</v>
+          </cell>
+          <cell r="G37">
+            <v>86.466565349544069</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="F38">
+            <v>4.9875311720698257E-2</v>
+          </cell>
+          <cell r="G38">
+            <v>1.0372340425531916</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="F39">
+            <v>4.9875311720698257E-2</v>
+          </cell>
+          <cell r="G39">
+            <v>7.6101823708206684</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="G40">
+            <v>1.354588821344141</v>
           </cell>
         </row>
       </sheetData>
@@ -1154,13 +1197,13 @@
       <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="Sheep_total_Arid_2020"/>
+      <sheetName val="Dairy_total_Humid_2020"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0" refreshError="1">
         <row r="2">
-          <cell r="C2">
-            <v>1300620.48691654</v>
+          <cell r="D2">
+            <v>5233916.3978957208</v>
           </cell>
         </row>
       </sheetData>
@@ -1177,13 +1220,13 @@
       <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="Sheep_total_SArid_2020"/>
+      <sheetName val="Sheep_total_Arid_2020"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0" refreshError="1">
         <row r="2">
           <cell r="C2">
-            <v>1063972.5190212701</v>
+            <v>1300620.48691654</v>
           </cell>
         </row>
       </sheetData>
@@ -1200,13 +1243,13 @@
       <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="Sheep_total_Humid_2020"/>
+      <sheetName val="Sheep_total_SArid_2020"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0" refreshError="1">
         <row r="2">
-          <cell r="D2">
-            <v>1001433.3524225579</v>
+          <cell r="C2">
+            <v>1063972.5190212701</v>
           </cell>
         </row>
       </sheetData>
@@ -1223,55 +1266,13 @@
       <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="Model_implemented"/>
-      <sheetName val="FAO_2019_animal_trends"/>
+      <sheetName val="Sheep_total_Humid_2020"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="35">
-          <cell r="F35">
-            <v>0.53615960099750615</v>
-          </cell>
-          <cell r="G35">
-            <v>0.38312009613345605</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="F36">
-            <v>0.36159600997506236</v>
-          </cell>
-          <cell r="G36">
-            <v>2.7950424483806726</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="F37">
-            <v>2.4937655860349127E-3</v>
-          </cell>
-          <cell r="G37">
-            <v>86.466565349544069</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="F38">
-            <v>4.9875311720698257E-2</v>
-          </cell>
-          <cell r="G38">
-            <v>1.0372340425531916</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="F39">
-            <v>4.9875311720698257E-2</v>
-          </cell>
-          <cell r="G39">
-            <v>7.6101823708206684</v>
-          </cell>
-        </row>
-        <row r="40">
-          <cell r="G40">
-            <v>1.354588821344141</v>
+      <sheetData sheetId="0" refreshError="1">
+        <row r="2">
+          <cell r="D2">
+            <v>1001433.3524225579</v>
           </cell>
         </row>
       </sheetData>
@@ -1419,13 +1420,13 @@
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="SArid_Subsistence"/>
+      <sheetName val="Arid_Subsistence"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0" refreshError="1">
         <row r="2">
           <cell r="C2">
-            <v>467695.362210333</v>
+            <v>220785.65217611199</v>
           </cell>
         </row>
       </sheetData>
@@ -1661,13 +1662,13 @@
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="Humid_Subsistence"/>
+      <sheetName val="SArid_Subsistence"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0" refreshError="1">
         <row r="2">
-          <cell r="D2">
-            <v>589697.33266333945</v>
+          <cell r="C2">
+            <v>467695.362210333</v>
           </cell>
         </row>
       </sheetData>
@@ -1909,13 +1910,13 @@
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="Arid_Commercial"/>
+      <sheetName val="Humid_Subsistence"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0" refreshError="1">
         <row r="2">
-          <cell r="C2">
-            <v>4580694.9930214901</v>
+          <cell r="D2">
+            <v>589697.33266333945</v>
           </cell>
         </row>
       </sheetData>
@@ -2165,13 +2166,13 @@
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="SArid_Commercial"/>
+      <sheetName val="Arid_Commercial"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0" refreshError="1">
         <row r="2">
           <cell r="C2">
-            <v>5931614.2707009297</v>
+            <v>4580694.9930214901</v>
           </cell>
         </row>
       </sheetData>
@@ -2423,13 +2424,13 @@
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="Humid_Commercial"/>
+      <sheetName val="SArid_Commercial"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0" refreshError="1">
         <row r="2">
-          <cell r="D2">
-            <v>4968107.5438200859</v>
+          <cell r="C2">
+            <v>5931614.2707009297</v>
           </cell>
         </row>
       </sheetData>
@@ -2681,16 +2682,15 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="Dairy_total_Arid_2020"/>
+      <sheetName val="Humid_Commercial"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0" refreshError="1">
         <row r="2">
-          <cell r="C2">
-            <v>24812.591756207301</v>
+          <cell r="D2">
+            <v>4968107.5438200859</v>
           </cell>
         </row>
       </sheetData>
@@ -2778,9 +2778,6 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="2">
-          <cell r="F2" t="str">
-            <v>zebu-pastoral-arid-male.finisher</v>
-          </cell>
           <cell r="N2">
             <v>3184847.6449140799</v>
           </cell>
@@ -3706,15 +3703,38 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
 </file>
 
 <file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Dairy_total_Arid_2020"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1">
+        <row r="2">
+          <cell r="C2">
+            <v>24812.591756207301</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3729,29 +3749,6 @@
         <row r="2">
           <cell r="C2">
             <v>1210306.62197518</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Dairy_total_Humid_2020"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1">
-        <row r="2">
-          <cell r="D2">
-            <v>5233916.3978957208</v>
           </cell>
         </row>
       </sheetData>
@@ -4137,7 +4134,7 @@
         <v>0.51509165724121786</v>
       </c>
       <c r="D2">
-        <f>[13]FAO_2019_animal_trends!$F$35</f>
+        <f>[1]FAO_2019_animal_trends!$F$35</f>
         <v>0.53615960099750615</v>
       </c>
       <c r="E2">
@@ -4149,7 +4146,7 @@
         <v>0.52629975213940838</v>
       </c>
       <c r="G2">
-        <f>[13]FAO_2019_animal_trends!$G$35</f>
+        <f>[1]FAO_2019_animal_trends!$G$35</f>
         <v>0.38312009613345605</v>
       </c>
       <c r="H2">
@@ -4170,7 +4167,7 @@
         <v>0.33339443937546853</v>
       </c>
       <c r="D3">
-        <f>[13]FAO_2019_animal_trends!$F$36</f>
+        <f>[1]FAO_2019_animal_trends!$F$36</f>
         <v>0.36159600997506236</v>
       </c>
       <c r="E3">
@@ -4182,7 +4179,7 @@
         <v>0.31358889061540685</v>
       </c>
       <c r="G3">
-        <f>[13]FAO_2019_animal_trends!$G$36</f>
+        <f>[1]FAO_2019_animal_trends!$G$36</f>
         <v>2.7950424483806726</v>
       </c>
       <c r="H3">
@@ -4203,7 +4200,7 @@
         <v>5.7351605247385563E-2</v>
       </c>
       <c r="D4">
-        <f>[13]FAO_2019_animal_trends!$F$39</f>
+        <f>[1]FAO_2019_animal_trends!$F$39</f>
         <v>4.9875311720698257E-2</v>
       </c>
       <c r="E4">
@@ -4215,7 +4212,7 @@
         <v>4.6666186084097429E-2</v>
       </c>
       <c r="G4">
-        <f>[13]FAO_2019_animal_trends!$G$40</f>
+        <f>[1]FAO_2019_animal_trends!$G$40</f>
         <v>1.354588821344141</v>
       </c>
       <c r="H4">
@@ -4236,7 +4233,7 @@
         <v>5.0951603562285619E-2</v>
       </c>
       <c r="D5">
-        <f>[13]FAO_2019_animal_trends!$F$38</f>
+        <f>[1]FAO_2019_animal_trends!$F$38</f>
         <v>4.9875311720698257E-2</v>
       </c>
       <c r="E5">
@@ -4248,7 +4245,7 @@
         <v>4.7418024088714393E-2</v>
       </c>
       <c r="G5">
-        <f>[13]FAO_2019_animal_trends!$G$38</f>
+        <f>[1]FAO_2019_animal_trends!$G$38</f>
         <v>1.0372340425531916</v>
       </c>
       <c r="H5">
@@ -4269,7 +4266,7 @@
         <v>4.3210694573642391E-2</v>
       </c>
       <c r="D6">
-        <f>[13]FAO_2019_animal_trends!$F$37</f>
+        <f>[1]FAO_2019_animal_trends!$F$37</f>
         <v>2.4937655860349127E-3</v>
       </c>
       <c r="E6">
@@ -4281,7 +4278,7 @@
         <v>-7.7485333020033496E-3</v>
       </c>
       <c r="G6">
-        <f>[13]FAO_2019_animal_trends!$G$37</f>
+        <f>[1]FAO_2019_animal_trends!$G$37</f>
         <v>86.466565349544069</v>
       </c>
       <c r="H6">
@@ -4360,15 +4357,15 @@
         <v>75</v>
       </c>
       <c r="B2" s="8">
-        <f>[1]Arid_Subsistence!$C$2/1000000*$H$18</f>
+        <f>[2]Arid_Subsistence!$C$2/1000000*$H$18</f>
         <v>0.26935849565485659</v>
       </c>
       <c r="C2" s="8">
-        <f>[2]SArid_Subsistence!$C$2/1000000*$H$18</f>
+        <f>[3]SArid_Subsistence!$C$2/1000000*$H$18</f>
         <v>0.57058834189660623</v>
       </c>
       <c r="D2" s="8">
-        <f>[3]Humid_Subsistence!$D$2/1000000*$H$18</f>
+        <f>[4]Humid_Subsistence!$D$2/1000000*$H$18</f>
         <v>0.71943074584927413</v>
       </c>
       <c r="E2" s="9">
@@ -4393,15 +4390,15 @@
         <v>76</v>
       </c>
       <c r="B3" s="8">
-        <f>[4]Arid_Commercial!$C$2/1000000*$H$18</f>
+        <f>[5]Arid_Commercial!$C$2/1000000*$H$18</f>
         <v>5.5884478914862177</v>
       </c>
       <c r="C3" s="8">
-        <f>[5]SArid_Commercial!$C$2/1000000*$H$18</f>
+        <f>[6]SArid_Commercial!$C$2/1000000*$H$18</f>
         <v>7.2365694102551341</v>
       </c>
       <c r="D3" s="8">
-        <f>[6]Humid_Commercial!$D$2/1000000*$H$18</f>
+        <f>[7]Humid_Commercial!$D$2/1000000*$H$18</f>
         <v>6.0610912034605047</v>
       </c>
       <c r="E3" s="9">
@@ -4423,15 +4420,15 @@
         <v>59</v>
       </c>
       <c r="B4" s="8">
-        <f>[7]Dairy_total_Arid_2020!$C$2/1000000*$H$18</f>
+        <f>[8]Dairy_total_Arid_2020!$C$2/1000000*$H$18</f>
         <v>3.0271361942572905E-2</v>
       </c>
       <c r="C4" s="8">
-        <f>[8]Dairy_total_SArid_2020!$C$2/1000000*$H$18</f>
+        <f>[9]Dairy_total_SArid_2020!$C$2/1000000*$H$18</f>
         <v>1.4765740788097195</v>
       </c>
       <c r="D4" s="8">
-        <f>[9]Dairy_total_Humid_2020!$D$2/1000000*$H$18</f>
+        <f>[10]Dairy_total_Humid_2020!$D$2/1000000*$H$18</f>
         <v>6.3853780054327789</v>
       </c>
       <c r="E4" s="9"/>
@@ -4441,15 +4438,15 @@
         <v>79</v>
       </c>
       <c r="B5" s="8">
-        <f>9.78*0.76*[10]Sheep_total_Arid_2020!$C$2/1000000*$H$18</f>
+        <f>9.78*0.76*[11]Sheep_total_Arid_2020!$C$2/1000000*$H$18</f>
         <v>11.794047385286973</v>
       </c>
       <c r="C5" s="8">
-        <f>9.78*0.76*[11]Sheep_total_SArid_2020!$C$2/1000000*$H$18</f>
+        <f>9.78*0.76*[12]Sheep_total_SArid_2020!$C$2/1000000*$H$18</f>
         <v>9.6481198260451801</v>
       </c>
       <c r="D5" s="8">
-        <f>9.78*0.76*[12]Sheep_total_Humid_2020!$D$2/1000000*$H$18</f>
+        <f>9.78*0.76*[13]Sheep_total_Humid_2020!$D$2/1000000*$H$18</f>
         <v>9.0810136627013929</v>
       </c>
       <c r="E5" s="9">
@@ -5261,7 +5258,7 @@
         <v>8.5595346951947899</v>
       </c>
       <c r="C2">
-        <f>[13]FAO_2019_animal_trends!$G$35/100</f>
+        <f>[1]FAO_2019_animal_trends!$G$35/100</f>
         <v>3.8312009613345605E-3</v>
       </c>
       <c r="D2">
@@ -5282,7 +5279,7 @@
         <v>5.5401815014894495</v>
       </c>
       <c r="C3">
-        <f>[13]FAO_2019_animal_trends!$G36/100</f>
+        <f>[1]FAO_2019_animal_trends!$G36/100</f>
         <v>2.7950424483806725E-2</v>
       </c>
       <c r="D3">
@@ -5303,7 +5300,7 @@
         <v>0.95304019787340877</v>
       </c>
       <c r="C4">
-        <f>[13]FAO_2019_animal_trends!$G39/100</f>
+        <f>[1]FAO_2019_animal_trends!$G39/100</f>
         <v>7.6101823708206687E-2</v>
       </c>
       <c r="D4">
@@ -5324,7 +5321,7 @@
         <v>0.84668818128995227</v>
       </c>
       <c r="C5">
-        <f>[13]FAO_2019_animal_trends!$G38/100</f>
+        <f>[1]FAO_2019_animal_trends!$G38/100</f>
         <v>1.0372340425531916E-2</v>
       </c>
       <c r="D5">
@@ -5345,7 +5342,7 @@
         <v>0.71805363998227201</v>
       </c>
       <c r="C6">
-        <f>[13]FAO_2019_animal_trends!$G37/100</f>
+        <f>[1]FAO_2019_animal_trends!$G37/100</f>
         <v>0.86466565349544067</v>
       </c>
       <c r="D6">
@@ -5366,7 +5363,7 @@
         <v>7.8922234461850715</v>
       </c>
       <c r="C7">
-        <f>[13]FAO_2019_animal_trends!$G39/100</f>
+        <f>[1]FAO_2019_animal_trends!$G39/100</f>
         <v>7.6101823708206687E-2</v>
       </c>
       <c r="D7">
@@ -6732,20 +6729,20 @@
       <c r="B25" s="1"/>
     </row>
     <row r="26" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B26" s="56">
+      <c r="B26" s="52">
         <v>2050</v>
       </c>
-      <c r="C26" s="56"/>
-      <c r="D26" s="56"/>
-      <c r="E26" s="56"/>
+      <c r="C26" s="52"/>
+      <c r="D26" s="52"/>
+      <c r="E26" s="52"/>
     </row>
     <row r="27" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B27" s="57" t="s">
+      <c r="B27" s="53" t="s">
         <v>135</v>
       </c>
-      <c r="C27" s="57"/>
-      <c r="D27" s="57"/>
-      <c r="E27" s="57"/>
+      <c r="C27" s="53"/>
+      <c r="D27" s="53"/>
+      <c r="E27" s="53"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
@@ -7080,12 +7077,12 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
-      <c r="B49" s="54" t="s">
+      <c r="B49" s="56" t="s">
         <v>130</v>
       </c>
-      <c r="C49" s="54"/>
-      <c r="D49" s="54"/>
-      <c r="E49" s="54"/>
+      <c r="C49" s="56"/>
+      <c r="D49" s="56"/>
+      <c r="E49" s="56"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
@@ -7176,12 +7173,12 @@
       <c r="A56" s="2">
         <v>2050</v>
       </c>
-      <c r="B56" s="56" t="s">
+      <c r="B56" s="52" t="s">
         <v>136</v>
       </c>
-      <c r="C56" s="56"/>
-      <c r="D56" s="56"/>
-      <c r="E56" s="56"/>
+      <c r="C56" s="52"/>
+      <c r="D56" s="52"/>
+      <c r="E56" s="52"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B57" s="55" t="s">
@@ -7273,12 +7270,12 @@
       <c r="B63" s="1"/>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B64" s="53" t="s">
+      <c r="B64" s="54" t="s">
         <v>78</v>
       </c>
-      <c r="C64" s="53"/>
-      <c r="D64" s="53"/>
-      <c r="E64" s="53"/>
+      <c r="C64" s="54"/>
+      <c r="D64" s="54"/>
+      <c r="E64" s="54"/>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B65" s="20" t="str">
@@ -7410,12 +7407,12 @@
       <c r="A74" s="33">
         <v>2050</v>
       </c>
-      <c r="B74" s="56" t="s">
+      <c r="B74" s="52" t="s">
         <v>137</v>
       </c>
-      <c r="C74" s="56"/>
-      <c r="D74" s="56"/>
-      <c r="E74" s="56"/>
+      <c r="C74" s="52"/>
+      <c r="D74" s="52"/>
+      <c r="E74" s="52"/>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="33"/>
@@ -7517,16 +7514,16 @@
       <c r="E81" s="3"/>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B82" s="53" t="s">
+      <c r="B82" s="54" t="s">
         <v>78</v>
       </c>
-      <c r="C82" s="53"/>
-      <c r="D82" s="53"/>
-      <c r="E82" s="53"/>
-      <c r="H82" s="53" t="s">
+      <c r="C82" s="54"/>
+      <c r="D82" s="54"/>
+      <c r="E82" s="54"/>
+      <c r="H82" s="54" t="s">
         <v>139</v>
       </c>
-      <c r="I82" s="53"/>
+      <c r="I82" s="54"/>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B83" s="32" t="str">
@@ -7699,12 +7696,12 @@
       </c>
     </row>
     <row r="91" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B91" s="56" t="s">
+      <c r="B91" s="52" t="s">
         <v>138</v>
       </c>
-      <c r="C91" s="56"/>
-      <c r="D91" s="56"/>
-      <c r="E91" s="56"/>
+      <c r="C91" s="52"/>
+      <c r="D91" s="52"/>
+      <c r="E91" s="52"/>
       <c r="H91" s="37" t="s">
         <v>221</v>
       </c>
@@ -7731,12 +7728,12 @@
         <f>H83</f>
         <v>+30% Herd size</v>
       </c>
-      <c r="B93" s="51" t="s">
+      <c r="B93" s="58" t="s">
         <v>144</v>
       </c>
-      <c r="C93" s="51"/>
-      <c r="D93" s="51"/>
-      <c r="E93" s="51"/>
+      <c r="C93" s="58"/>
+      <c r="D93" s="58"/>
+      <c r="E93" s="58"/>
       <c r="H93" s="37" t="s">
         <v>223</v>
       </c>
@@ -7941,12 +7938,12 @@
       <c r="K101" s="4"/>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B102" s="51" t="s">
+      <c r="B102" s="58" t="s">
         <v>140</v>
       </c>
-      <c r="C102" s="51"/>
-      <c r="D102" s="51"/>
-      <c r="E102" s="51"/>
+      <c r="C102" s="58"/>
+      <c r="D102" s="58"/>
+      <c r="E102" s="58"/>
       <c r="H102" s="4"/>
       <c r="I102" s="4"/>
       <c r="J102" s="4"/>
@@ -8079,13 +8076,13 @@
       <c r="K109" s="4"/>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B110" s="51" t="str">
+      <c r="B110" s="58" t="str">
         <f t="shared" ref="B110:B115" si="29">B102</f>
         <v>Animal populations (M hd) -- SA scenario specific</v>
       </c>
-      <c r="C110" s="51"/>
-      <c r="D110" s="51"/>
-      <c r="E110" s="51"/>
+      <c r="C110" s="58"/>
+      <c r="D110" s="58"/>
+      <c r="E110" s="58"/>
       <c r="H110" s="4"/>
       <c r="I110" s="4"/>
       <c r="J110" s="4"/>
@@ -8212,13 +8209,13 @@
       <c r="K116" s="4"/>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B117" s="51" t="str">
+      <c r="B117" s="58" t="str">
         <f t="shared" ref="B117:B122" si="31">B110</f>
         <v>Animal populations (M hd) -- SA scenario specific</v>
       </c>
-      <c r="C117" s="51"/>
-      <c r="D117" s="51"/>
-      <c r="E117" s="51"/>
+      <c r="C117" s="58"/>
+      <c r="D117" s="58"/>
+      <c r="E117" s="58"/>
       <c r="H117" s="4"/>
       <c r="I117" s="4"/>
       <c r="J117" s="4"/>
@@ -8345,13 +8342,13 @@
       <c r="K123" s="4"/>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B124" s="51" t="str">
+      <c r="B124" s="58" t="str">
         <f t="shared" ref="B124:B129" si="33">B117</f>
         <v>Animal populations (M hd) -- SA scenario specific</v>
       </c>
-      <c r="C124" s="51"/>
-      <c r="D124" s="51"/>
-      <c r="E124" s="51"/>
+      <c r="C124" s="58"/>
+      <c r="D124" s="58"/>
+      <c r="E124" s="58"/>
       <c r="H124" s="4"/>
       <c r="I124" s="4"/>
       <c r="J124" s="4"/>
@@ -8478,13 +8475,13 @@
         <f>H88</f>
         <v>-30% Boran</v>
       </c>
-      <c r="B131" s="51" t="str">
+      <c r="B131" s="58" t="str">
         <f t="shared" ref="B131:B136" si="35">B124</f>
         <v>Animal populations (M hd) -- SA scenario specific</v>
       </c>
-      <c r="C131" s="51"/>
-      <c r="D131" s="51"/>
-      <c r="E131" s="51"/>
+      <c r="C131" s="58"/>
+      <c r="D131" s="58"/>
+      <c r="E131" s="58"/>
       <c r="H131" s="4"/>
       <c r="I131" s="4"/>
       <c r="J131" s="4"/>
@@ -8655,13 +8652,13 @@
       <c r="K139" s="4"/>
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B140" s="51" t="str">
+      <c r="B140" s="58" t="str">
         <f>B131</f>
         <v>Animal populations (M hd) -- SA scenario specific</v>
       </c>
-      <c r="C140" s="51"/>
-      <c r="D140" s="51"/>
-      <c r="E140" s="51"/>
+      <c r="C140" s="58"/>
+      <c r="D140" s="58"/>
+      <c r="E140" s="58"/>
       <c r="H140" s="4"/>
       <c r="I140" s="4"/>
       <c r="J140" s="4"/>
@@ -8788,13 +8785,13 @@
       <c r="K146" s="4"/>
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B147" s="51" t="str">
+      <c r="B147" s="58" t="str">
         <f t="shared" ref="B147:B152" si="39">B140</f>
         <v>Animal populations (M hd) -- SA scenario specific</v>
       </c>
-      <c r="C147" s="51"/>
-      <c r="D147" s="51"/>
-      <c r="E147" s="51"/>
+      <c r="C147" s="58"/>
+      <c r="D147" s="58"/>
+      <c r="E147" s="58"/>
       <c r="H147" s="4"/>
       <c r="I147" s="4"/>
       <c r="J147" s="4"/>
@@ -8921,13 +8918,13 @@
       <c r="K153" s="4"/>
     </row>
     <row r="154" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B154" s="51" t="str">
+      <c r="B154" s="58" t="str">
         <f t="shared" ref="B154:B159" si="41">B147</f>
         <v>Animal populations (M hd) -- SA scenario specific</v>
       </c>
-      <c r="C154" s="51"/>
-      <c r="D154" s="51"/>
-      <c r="E154" s="51"/>
+      <c r="C154" s="58"/>
+      <c r="D154" s="58"/>
+      <c r="E154" s="58"/>
       <c r="H154" s="4"/>
       <c r="I154" s="4"/>
       <c r="J154" s="4"/>
@@ -9054,13 +9051,13 @@
       <c r="K160" s="4"/>
     </row>
     <row r="161" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B161" s="51" t="str">
+      <c r="B161" s="58" t="str">
         <f t="shared" ref="B161:B166" si="43">B154</f>
         <v>Animal populations (M hd) -- SA scenario specific</v>
       </c>
-      <c r="C161" s="51"/>
-      <c r="D161" s="51"/>
-      <c r="E161" s="51"/>
+      <c r="C161" s="58"/>
+      <c r="D161" s="58"/>
+      <c r="E161" s="58"/>
       <c r="H161" s="4"/>
       <c r="I161" s="4"/>
       <c r="J161" s="4"/>
@@ -9187,13 +9184,13 @@
       <c r="K167" s="4"/>
     </row>
     <row r="168" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B168" s="51" t="str">
+      <c r="B168" s="58" t="str">
         <f t="shared" ref="B168:B173" si="45">B161</f>
         <v>Animal populations (M hd) -- SA scenario specific</v>
       </c>
-      <c r="C168" s="51"/>
-      <c r="D168" s="51"/>
-      <c r="E168" s="51"/>
+      <c r="C168" s="58"/>
+      <c r="D168" s="58"/>
+      <c r="E168" s="58"/>
       <c r="H168" s="4"/>
       <c r="I168" s="4"/>
       <c r="J168" s="4"/>
@@ -9320,13 +9317,13 @@
       <c r="K174" s="4"/>
     </row>
     <row r="175" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B175" s="51" t="str">
+      <c r="B175" s="58" t="str">
         <f t="shared" ref="B175:B180" si="47">B168</f>
         <v>Animal populations (M hd) -- SA scenario specific</v>
       </c>
-      <c r="C175" s="51"/>
-      <c r="D175" s="51"/>
-      <c r="E175" s="51"/>
+      <c r="C175" s="58"/>
+      <c r="D175" s="58"/>
+      <c r="E175" s="58"/>
       <c r="H175" s="4"/>
       <c r="I175" s="4"/>
       <c r="J175" s="4"/>
@@ -9453,13 +9450,13 @@
       <c r="K181" s="4"/>
     </row>
     <row r="182" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B182" s="51" t="str">
+      <c r="B182" s="58" t="str">
         <f t="shared" ref="B182:B187" si="49">B175</f>
         <v>Animal populations (M hd) -- SA scenario specific</v>
       </c>
-      <c r="C182" s="51"/>
-      <c r="D182" s="51"/>
-      <c r="E182" s="51"/>
+      <c r="C182" s="58"/>
+      <c r="D182" s="58"/>
+      <c r="E182" s="58"/>
       <c r="H182" s="4"/>
       <c r="I182" s="4"/>
       <c r="J182" s="4"/>
@@ -9586,13 +9583,13 @@
       <c r="K188" s="4"/>
     </row>
     <row r="189" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B189" s="51" t="str">
+      <c r="B189" s="58" t="str">
         <f t="shared" ref="B189:B194" si="52">B182</f>
         <v>Animal populations (M hd) -- SA scenario specific</v>
       </c>
-      <c r="C189" s="51"/>
-      <c r="D189" s="51"/>
-      <c r="E189" s="51"/>
+      <c r="C189" s="58"/>
+      <c r="D189" s="58"/>
+      <c r="E189" s="58"/>
       <c r="H189" s="4"/>
       <c r="I189" s="4"/>
       <c r="J189" s="4"/>
@@ -9719,13 +9716,13 @@
       <c r="K195" s="4"/>
     </row>
     <row r="196" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B196" s="51" t="str">
+      <c r="B196" s="58" t="str">
         <f t="shared" ref="B196:B201" si="53">B189</f>
         <v>Animal populations (M hd) -- SA scenario specific</v>
       </c>
-      <c r="C196" s="51"/>
-      <c r="D196" s="51"/>
-      <c r="E196" s="51"/>
+      <c r="C196" s="58"/>
+      <c r="D196" s="58"/>
+      <c r="E196" s="58"/>
       <c r="H196" s="4"/>
       <c r="I196" s="4"/>
       <c r="J196" s="4"/>
@@ -9852,13 +9849,13 @@
       <c r="K202" s="4"/>
     </row>
     <row r="203" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B203" s="51" t="str">
+      <c r="B203" s="58" t="str">
         <f t="shared" ref="B203:B208" si="54">B196</f>
         <v>Animal populations (M hd) -- SA scenario specific</v>
       </c>
-      <c r="C203" s="51"/>
-      <c r="D203" s="51"/>
-      <c r="E203" s="51"/>
+      <c r="C203" s="58"/>
+      <c r="D203" s="58"/>
+      <c r="E203" s="58"/>
       <c r="H203" s="4"/>
       <c r="I203" s="4"/>
       <c r="J203" s="4"/>
@@ -9985,13 +9982,13 @@
       <c r="K209" s="4"/>
     </row>
     <row r="210" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B210" s="51" t="str">
+      <c r="B210" s="58" t="str">
         <f t="shared" ref="B210:B215" si="56">B203</f>
         <v>Animal populations (M hd) -- SA scenario specific</v>
       </c>
-      <c r="C210" s="51"/>
-      <c r="D210" s="51"/>
-      <c r="E210" s="51"/>
+      <c r="C210" s="58"/>
+      <c r="D210" s="58"/>
+      <c r="E210" s="58"/>
       <c r="H210" s="4"/>
       <c r="I210" s="4"/>
       <c r="J210" s="4"/>
@@ -10118,13 +10115,13 @@
       <c r="K216" s="4"/>
     </row>
     <row r="217" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B217" s="51" t="str">
+      <c r="B217" s="58" t="str">
         <f>B102</f>
         <v>Animal populations (M hd) -- SA scenario specific</v>
       </c>
-      <c r="C217" s="51"/>
-      <c r="D217" s="51"/>
-      <c r="E217" s="51"/>
+      <c r="C217" s="58"/>
+      <c r="D217" s="58"/>
+      <c r="E217" s="58"/>
       <c r="H217" s="4"/>
       <c r="I217" s="4"/>
       <c r="J217" s="4"/>
@@ -10250,13 +10247,13 @@
       <c r="K223" s="4"/>
     </row>
     <row r="224" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B224" s="51" t="str">
+      <c r="B224" s="58" t="str">
         <f t="shared" ref="B224:B229" si="58">B217</f>
         <v>Animal populations (M hd) -- SA scenario specific</v>
       </c>
-      <c r="C224" s="51"/>
-      <c r="D224" s="51"/>
-      <c r="E224" s="51"/>
+      <c r="C224" s="58"/>
+      <c r="D224" s="58"/>
+      <c r="E224" s="58"/>
       <c r="H224" s="4"/>
       <c r="I224" s="4"/>
       <c r="J224" s="4"/>
@@ -10379,12 +10376,12 @@
       <c r="K230" s="4"/>
     </row>
     <row r="231" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B231" s="53" t="s">
+      <c r="B231" s="54" t="s">
         <v>143</v>
       </c>
-      <c r="C231" s="54"/>
-      <c r="D231" s="54"/>
-      <c r="E231" s="54"/>
+      <c r="C231" s="56"/>
+      <c r="D231" s="56"/>
+      <c r="E231" s="56"/>
       <c r="H231" s="4"/>
       <c r="I231" s="4"/>
       <c r="J231" s="4"/>
@@ -11316,12 +11313,12 @@
       <c r="E278" s="13"/>
     </row>
     <row r="280" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B280" s="52" t="s">
+      <c r="B280" s="57" t="s">
         <v>146</v>
       </c>
-      <c r="C280" s="52"/>
-      <c r="D280" s="52"/>
-      <c r="E280" s="52"/>
+      <c r="C280" s="57"/>
+      <c r="D280" s="57"/>
+      <c r="E280" s="57"/>
     </row>
     <row r="281" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B281" t="str">
@@ -11654,12 +11651,12 @@
       </c>
     </row>
     <row r="300" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B300" s="52" t="s">
+      <c r="B300" s="57" t="s">
         <v>152</v>
       </c>
-      <c r="C300" s="52"/>
-      <c r="D300" s="52"/>
-      <c r="E300" s="52"/>
+      <c r="C300" s="57"/>
+      <c r="D300" s="57"/>
+      <c r="E300" s="57"/>
       <c r="G300" s="41" t="s">
         <v>149</v>
       </c>
@@ -11990,15 +11987,15 @@
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="B26:E26"/>
-    <mergeCell ref="B56:E56"/>
-    <mergeCell ref="B27:E27"/>
-    <mergeCell ref="B82:E82"/>
-    <mergeCell ref="B64:E64"/>
-    <mergeCell ref="B57:E57"/>
-    <mergeCell ref="B75:E75"/>
-    <mergeCell ref="B49:E49"/>
-    <mergeCell ref="B74:E74"/>
+    <mergeCell ref="B110:E110"/>
+    <mergeCell ref="B117:E117"/>
+    <mergeCell ref="B147:E147"/>
+    <mergeCell ref="B154:E154"/>
+    <mergeCell ref="B300:E300"/>
+    <mergeCell ref="B224:E224"/>
+    <mergeCell ref="B124:E124"/>
+    <mergeCell ref="B131:E131"/>
+    <mergeCell ref="B140:E140"/>
     <mergeCell ref="H82:I82"/>
     <mergeCell ref="B231:E231"/>
     <mergeCell ref="B280:E280"/>
@@ -12015,15 +12012,15 @@
     <mergeCell ref="B168:E168"/>
     <mergeCell ref="B175:E175"/>
     <mergeCell ref="B182:E182"/>
-    <mergeCell ref="B110:E110"/>
-    <mergeCell ref="B117:E117"/>
-    <mergeCell ref="B147:E147"/>
-    <mergeCell ref="B154:E154"/>
-    <mergeCell ref="B300:E300"/>
-    <mergeCell ref="B224:E224"/>
-    <mergeCell ref="B124:E124"/>
-    <mergeCell ref="B131:E131"/>
-    <mergeCell ref="B140:E140"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="B56:E56"/>
+    <mergeCell ref="B27:E27"/>
+    <mergeCell ref="B82:E82"/>
+    <mergeCell ref="B64:E64"/>
+    <mergeCell ref="B57:E57"/>
+    <mergeCell ref="B75:E75"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="B74:E74"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -13400,11 +13397,11 @@
         <f>1-Carrying_Capacity!C88</f>
         <v>9.0729341997921931E-2</v>
       </c>
-      <c r="R7" s="58">
+      <c r="R7" s="51">
         <f>O7*100</f>
         <v>10.70712294703744</v>
       </c>
-      <c r="S7" s="58">
+      <c r="S7" s="51">
         <f>P7*100</f>
         <v>9.0729341997921935</v>
       </c>
@@ -13444,11 +13441,11 @@
         <f>1-Carrying_Capacity!C87</f>
         <v>2.3517803129296411E-2</v>
       </c>
-      <c r="R8" s="58">
+      <c r="R8" s="51">
         <f t="shared" ref="R8:S15" si="1">O8*100</f>
         <v>4.3911542470854599</v>
       </c>
-      <c r="S8" s="58">
+      <c r="S8" s="51">
         <f t="shared" si="1"/>
         <v>2.3517803129296411</v>
       </c>
@@ -13488,11 +13485,11 @@
         <f>1-Carrying_Capacity!C89</f>
         <v>2.4951307116050758E-2</v>
       </c>
-      <c r="R9" s="58">
+      <c r="R9" s="51">
         <f t="shared" si="1"/>
         <v>4.5258627579156219</v>
       </c>
-      <c r="S9" s="58">
+      <c r="S9" s="51">
         <f t="shared" si="1"/>
         <v>2.4951307116050758</v>
       </c>
@@ -13533,11 +13530,11 @@
         <f>1-Carrying_Capacity!D88</f>
         <v>2.0329353064496347E-2</v>
       </c>
-      <c r="R10" s="58">
+      <c r="R10" s="51">
         <f t="shared" si="1"/>
         <v>2.5425932790424932</v>
       </c>
-      <c r="S10" s="58">
+      <c r="S10" s="51">
         <f t="shared" si="1"/>
         <v>2.0329353064496347</v>
       </c>
@@ -13579,11 +13576,11 @@
         <f>1-Carrying_Capacity!D87</f>
         <v>1.1717333223408399E-2</v>
       </c>
-      <c r="R11" s="58">
+      <c r="R11" s="51">
         <f t="shared" si="1"/>
         <v>1.6945056606920805</v>
       </c>
-      <c r="S11" s="58">
+      <c r="S11" s="51">
         <f t="shared" si="1"/>
         <v>1.1717333223408399</v>
       </c>
@@ -13625,11 +13622,11 @@
         <f>1-Carrying_Capacity!D89</f>
         <v>1.7792686901172972E-2</v>
       </c>
-      <c r="R12" s="58">
+      <c r="R12" s="51">
         <f t="shared" si="1"/>
         <v>2.2927894926253911</v>
       </c>
-      <c r="S12" s="58">
+      <c r="S12" s="51">
         <f t="shared" si="1"/>
         <v>1.7792686901172972</v>
       </c>
@@ -13671,11 +13668,11 @@
         <f>1-Carrying_Capacity!E88</f>
         <v>0.27507774967035958</v>
       </c>
-      <c r="R13" s="58">
+      <c r="R13" s="51">
         <f t="shared" si="1"/>
         <v>27.673626816624431</v>
       </c>
-      <c r="S13" s="58">
+      <c r="S13" s="51">
         <f t="shared" si="1"/>
         <v>27.507774967035957</v>
       </c>
@@ -13717,11 +13714,11 @@
         <f>1-Carrying_Capacity!E87</f>
         <v>0.252944800564463</v>
       </c>
-      <c r="R14" s="58">
+      <c r="R14" s="51">
         <f t="shared" si="1"/>
         <v>25.475383170079834</v>
       </c>
-      <c r="S14" s="58">
+      <c r="S14" s="51">
         <f t="shared" si="1"/>
         <v>25.2944800564463</v>
       </c>
@@ -13763,11 +13760,11 @@
         <f>1-Carrying_Capacity!E89</f>
         <v>0.25380708811969899</v>
       </c>
-      <c r="R15" s="58">
+      <c r="R15" s="51">
         <f t="shared" si="1"/>
         <v>25.561025536613226</v>
       </c>
-      <c r="S15" s="58">
+      <c r="S15" s="51">
         <f t="shared" si="1"/>
         <v>25.3807088119699</v>
       </c>
